--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -4108,7 +4108,7 @@
       <row>12</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="1428750" cy="1428750"/>
+    <ext cx="1438275" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -4183,7 +4183,7 @@
       <row>13</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="1476375" cy="1428750"/>
+    <ext cx="1495425" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -4204,7 +4204,7 @@
   <oneCellAnchor>
     <from>
       <col>5</col>
-      <colOff>1609725</colOff>
+      <colOff>1628775</colOff>
       <row>13</row>
       <rowOff>95250</rowOff>
     </from>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -4433,7 +4433,7 @@
       <row>14</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="1485900" cy="1428750"/>
+    <ext cx="1476375" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -4454,11 +4454,11 @@
   <oneCellAnchor>
     <from>
       <col>15</col>
-      <colOff>1619250</colOff>
+      <colOff>1609725</colOff>
       <row>14</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="2381250" cy="1428750"/>
+    <ext cx="2419350" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -4508,7 +4508,7 @@
       <row>15</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="1428750" cy="1428750"/>
+    <ext cx="1419225" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -4529,11 +4529,11 @@
   <oneCellAnchor>
     <from>
       <col>15</col>
-      <colOff>1562100</colOff>
+      <colOff>1552575</colOff>
       <row>15</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="1390650" cy="1428750"/>
+    <ext cx="1419225" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -360,13 +360,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFE2E2E2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.09997863704336681"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,31 +378,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FF243F2E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
+        <fgColor rgb="FF2A7050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor rgb="FFC5DFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003A7D22"/>
+        <fgColor rgb="FF243F2E"/>
       </patternFill>
     </fill>
   </fills>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="57">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -349,6 +349,32 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <sz val="48"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1318,7 +1344,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2042,6 +2068,36 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="72" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="38" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="52" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="53" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="52" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3841,7 +3897,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip cstate="print" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3882,7 +3938,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip cstate="print" r:embed="rId24"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3925,7 +3981,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId4"/>
+        <a:blip cstate="print" r:embed="rId25"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3968,7 +4024,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId5"/>
+        <a:blip cstate="print" r:embed="rId26"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -4040,13 +4096,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4065,13 +4124,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4090,13 +4152,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4115,13 +4180,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4140,13 +4208,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4165,13 +4236,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4190,13 +4264,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4215,13 +4292,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4240,13 +4320,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4265,13 +4348,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4290,13 +4376,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4315,13 +4404,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4340,13 +4432,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4365,13 +4460,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4390,13 +4488,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
+        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4415,13 +4516,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
+        <a:blip cstate="print" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4440,13 +4544,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
+        <a:blip cstate="print" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4465,13 +4572,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
+        <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4490,13 +4600,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
+        <a:blip cstate="print" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4515,13 +4628,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
+        <a:blip cstate="print" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4540,13 +4656,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
+        <a:blip cstate="print" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6243,20 +6362,36 @@
       <c r="Y15" s="48" t="n"/>
       <c r="Z15" s="49" t="n"/>
     </row>
-    <row r="16" ht="125.25" customHeight="1">
+    <row r="16">
       <c r="A16" s="45" t="inlineStr">
         <is>
           <t>ANTECÂMARA(ECLUSA PEDESTRE)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
+      <c r="B16" s="269" t="inlineStr">
+        <is>
+          <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C16" s="32" t="n"/>
       <c r="D16" s="32" t="n"/>
       <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
+      <c r="F16" s="270" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G16" s="32" t="n"/>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="33" t="n"/>
+      <c r="H16" s="271" t="inlineStr">
+        <is>
+          <t>PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I16" s="271" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J16" s="32" t="n"/>
       <c r="K16" s="32" t="n"/>
       <c r="L16" s="32" t="n"/>
@@ -6269,26 +6404,51 @@
       <c r="S16" s="32" t="n"/>
       <c r="T16" s="32" t="n"/>
       <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
+      <c r="V16" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W16" s="32" t="n"/>
-      <c r="X16" s="31" t="n"/>
+      <c r="X16" s="269" t="inlineStr">
+        <is>
+          <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
+D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y16" s="31" t="n"/>
       <c r="Z16" s="32" t="n"/>
     </row>
-    <row r="17" ht="125.25" customHeight="1">
+    <row r="17">
       <c r="A17" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">GUARITA </t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
+      <c r="B17" s="269" t="inlineStr">
+        <is>
+          <t>P5 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Rejunte Infinity Hard cor Mocha ou cor Branco Pérola Deverá ser testado as duas opções de rejunte para escolher a que mais se aproxima do tom da peça. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C17" s="32" t="n"/>
       <c r="D17" s="32" t="n"/>
       <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
+      <c r="F17" s="270" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G17" s="32" t="n"/>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="33" t="n"/>
+      <c r="H17" s="271" t="inlineStr">
+        <is>
+          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I17" s="271" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J17" s="32" t="n"/>
       <c r="K17" s="32" t="n"/>
       <c r="L17" s="32" t="n"/>
@@ -6301,7 +6461,11 @@
       <c r="S17" s="32" t="n"/>
       <c r="T17" s="32" t="n"/>
       <c r="U17" s="32" t="n"/>
-      <c r="V17" s="32" t="n"/>
+      <c r="V17" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W17" s="32" t="n"/>
       <c r="X17" s="31" t="n"/>
       <c r="Y17" s="31" t="n"/>
@@ -6371,20 +6535,40 @@
       <c r="Y19" s="31" t="n"/>
       <c r="Z19" s="32" t="n"/>
     </row>
-    <row r="20" ht="125.25" customHeight="1">
+    <row r="20">
       <c r="A20" s="45" t="inlineStr">
         <is>
           <t>LOBBY ENTRADA</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n"/>
+      <c r="B20" s="269" t="inlineStr">
+        <is>
+          <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C20" s="32" t="n"/>
       <c r="D20" s="32" t="n"/>
       <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
+      <c r="F20" s="270" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G20" s="32" t="n"/>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="33" t="n"/>
+      <c r="H20" s="271" t="inlineStr">
+        <is>
+          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA54 - Parede em alvenaria regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I20" s="271" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
+T12 - Forro em chapa metálica dourada colada sobre MDF cru 6mm aparafusado em estrutura auxiliar do guarda corpo em metalon</t>
+        </is>
+      </c>
       <c r="J20" s="32" t="n"/>
       <c r="K20" s="32" t="n"/>
       <c r="L20" s="32" t="n"/>
@@ -6397,26 +6581,57 @@
       <c r="S20" s="32" t="n"/>
       <c r="T20" s="32" t="n"/>
       <c r="U20" s="32" t="n"/>
-      <c r="V20" s="32" t="n"/>
+      <c r="V20" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W20" s="32" t="n"/>
-      <c r="X20" s="31" t="n"/>
+      <c r="X20" s="269" t="inlineStr">
+        <is>
+          <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
+D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="32" t="n"/>
-    </row>
-    <row r="21" ht="125.25" customHeight="1">
+      <c r="Z20" s="270" t="inlineStr">
+        <is>
+          <t>D63 - Guarda corpo em chapa metálica dourada colada sobre fechamento em MDF cru 6mm aparafusado em estrutura auxiliar de metalon. Dimensões e detalhes conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="45" t="inlineStr">
         <is>
           <t>HALL ELEVADORES</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n"/>
+      <c r="B21" s="269" t="inlineStr">
+        <is>
+          <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C21" s="32" t="n"/>
       <c r="D21" s="32" t="n"/>
       <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
+      <c r="F21" s="270" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G21" s="32" t="n"/>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="33" t="n"/>
+      <c r="H21" s="271" t="inlineStr">
+        <is>
+          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA54 - Parede em alvenaria regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I21" s="271" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J21" s="32" t="n"/>
       <c r="K21" s="32" t="n"/>
       <c r="L21" s="32" t="n"/>
@@ -6429,11 +6644,19 @@
       <c r="S21" s="32" t="n"/>
       <c r="T21" s="32" t="n"/>
       <c r="U21" s="32" t="n"/>
-      <c r="V21" s="32" t="n"/>
+      <c r="V21" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W21" s="32" t="n"/>
       <c r="X21" s="31" t="n"/>
       <c r="Y21" s="31" t="n"/>
-      <c r="Z21" s="32" t="n"/>
+      <c r="Z21" s="270" t="inlineStr">
+        <is>
+          <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="125.25" customHeight="1">
       <c r="A22" s="45" t="inlineStr">
@@ -6467,19 +6690,37 @@
       <c r="Y22" s="31" t="n"/>
       <c r="Z22" s="32" t="n"/>
     </row>
-    <row r="23" ht="125.25" customHeight="1">
+    <row r="23">
       <c r="A23" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">HALL GARGEM </t>
         </is>
       </c>
-      <c r="B23" s="31" t="n"/>
+      <c r="B23" s="269" t="inlineStr">
+        <is>
+          <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C23" s="32" t="n"/>
       <c r="D23" s="32" t="n"/>
       <c r="E23" s="32" t="n"/>
+      <c r="F23" s="272" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G23" s="32" t="n"/>
-      <c r="H23" s="33" t="n"/>
-      <c r="I23" s="33" t="n"/>
+      <c r="H23" s="271" t="inlineStr">
+        <is>
+          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I23" s="271" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J23" s="32" t="n"/>
       <c r="K23" s="32" t="n"/>
       <c r="L23" s="32" t="n"/>
@@ -6492,11 +6733,24 @@
       <c r="S23" s="32" t="n"/>
       <c r="T23" s="32" t="n"/>
       <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
+      <c r="V23" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W23" s="32" t="n"/>
-      <c r="X23" s="31" t="n"/>
+      <c r="X23" s="269" t="inlineStr">
+        <is>
+          <t>D44 - Porta pivotante em MDF com acabamento em pintura acrílica fosca. Tom a definir. Dimensões conforme Mapa de Esquadrias. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+D45 - Porta pivotante em MDF com acabamento em pintura acrílica fosca. Tom a definir. Dimensões conforme Mapa de Esquadrias. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="32" t="n"/>
+      <c r="Z23" s="270" t="inlineStr">
+        <is>
+          <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="125.25" customHeight="1">
       <c r="A24" s="45" t="inlineStr">
@@ -6626,52 +6880,120 @@
       <c r="Y27" s="35" t="n"/>
       <c r="Z27" s="35" t="n"/>
     </row>
-    <row r="28" ht="125.25" customHeight="1">
+    <row r="28">
       <c r="A28" s="45" t="inlineStr">
         <is>
           <t>I.S P.C.D</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n"/>
+      <c r="B28" s="269" t="inlineStr">
+        <is>
+          <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C28" s="32" t="n"/>
       <c r="D28" s="35" t="n"/>
       <c r="E28" s="37" t="n"/>
-      <c r="F28" s="35" t="n"/>
+      <c r="F28" s="269" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G28" s="32" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="32" t="n"/>
-      <c r="K28" s="32" t="n"/>
+      <c r="H28" s="269" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I28" s="270" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J28" s="270" t="inlineStr">
+        <is>
+          <t>D65 - Bancada em pedra natural Basaltina com cuba esculpida e bandeja removível. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="K28" s="270" t="inlineStr">
+        <is>
+          <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
+        </is>
+      </c>
       <c r="L28" s="32" t="n"/>
       <c r="M28" s="32" t="n"/>
       <c r="N28" s="32" t="n"/>
-      <c r="O28" s="32" t="n"/>
-      <c r="P28" s="32" t="n"/>
+      <c r="O28" s="270" t="inlineStr">
+        <is>
+          <t>D66 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento grafite escovado, cód.: 01739870. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P28" s="270" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Q28" s="32" t="n"/>
       <c r="R28" s="32" t="n"/>
       <c r="S28" s="32" t="n"/>
-      <c r="T28" s="35" t="n"/>
+      <c r="T28" s="269" t="inlineStr">
+        <is>
+          <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve</t>
+        </is>
+      </c>
       <c r="U28" s="32" t="n"/>
-      <c r="V28" s="31" t="n"/>
+      <c r="V28" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W28" s="35" t="n"/>
-      <c r="X28" s="31" t="n"/>
+      <c r="X28" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y28" s="31" t="n"/>
-      <c r="Z28" s="35" t="n"/>
-    </row>
-    <row r="29" ht="125.25" customHeight="1">
+      <c r="Z28" s="269" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="45" t="inlineStr">
         <is>
           <t>VESTÍBULO</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n"/>
+      <c r="B29" s="269" t="inlineStr">
+        <is>
+          <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C29" s="32" t="n"/>
       <c r="D29" s="32" t="n"/>
       <c r="E29" s="37" t="n"/>
-      <c r="F29" s="32" t="n"/>
+      <c r="F29" s="270" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G29" s="35" t="n"/>
-      <c r="H29" s="35" t="n"/>
-      <c r="I29" s="35" t="n"/>
+      <c r="H29" s="269" t="inlineStr">
+        <is>
+          <t>PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA55 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro 4mm temperado, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I29" s="269" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J29" s="35" t="n"/>
       <c r="K29" s="32" t="n"/>
       <c r="L29" s="35" t="n"/>
@@ -6684,9 +7006,18 @@
       <c r="S29" s="32" t="n"/>
       <c r="T29" s="32" t="n"/>
       <c r="U29" s="32" t="n"/>
-      <c r="V29" s="31" t="n"/>
+      <c r="V29" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W29" s="32" t="n"/>
-      <c r="X29" s="32" t="n"/>
+      <c r="X29" s="270" t="inlineStr">
+        <is>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y29" s="32" t="n"/>
       <c r="Z29" s="35" t="n"/>
     </row>
@@ -7300,6 +7631,10 @@
     </row>
     <row r="49" ht="125.25" customHeight="1"/>
     <row r="50" ht="2.1" customHeight="1"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55">
       <c r="S55" s="3" t="inlineStr">
         <is>
@@ -9157,15 +9492,16 @@
       <c r="Y12" s="241" t="n"/>
       <c r="Z12" s="242" t="n"/>
     </row>
-    <row r="13" ht="409" customHeight="1">
+    <row r="13">
       <c r="A13" s="47" t="inlineStr">
         <is>
           <t>LOBBY PILOTIS</t>
         </is>
       </c>
-      <c r="B13" s="243" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B13" s="273" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C13" s="49" t="n"/>
@@ -9173,25 +9509,27 @@
       <c r="E13" s="49" t="n"/>
       <c r="F13" s="244" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G13" s="49" t="n"/>
-      <c r="H13" s="244" t="inlineStr">
-        <is>
-          <t>PA53 - Revestimento em pedra natural basaltina, dimensões e paginação conforme detalhamento, rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII
-PA44 - Textura acrílica cimento queimado, cor 107. Ref.: Terracor CQ</t>
-        </is>
-      </c>
-      <c r="I13" s="244" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H13" s="274" t="inlineStr">
+        <is>
+          <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
+PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA58 - Pilar em concreto, com enchimento, revestido em pedra natural Basaltina conforme detalhamento.Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I13" s="274" t="inlineStr">
+        <is>
+          <t>FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
+T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J13" s="49" t="n"/>
       <c r="K13" s="244" t="inlineStr">
         <is>
-          <t>D75 - Fechamento decorativo piso teto com quadro fixado no piso e no teto através de espaçadores e fechamento desenho conforme base para corte de molde em CNC - peças em madeira maciça engenheirada, tonalizada, acabamento escovado, calandrados conforme molde. Ref.: Demuner. Atenção: a madeira deve possuir certificação FSC ou CERFLOR</t>
+          <t>D75 - Fechamento decorativo piso teto com quadro fixado no piso e no teto através de espaçadores e fechamento com desenho conforme base para corte de molde em CNC - peças em madeira maciça engenheirada, tonalizada,acabamento escovado, calandradas conforme molde. Ref.: Demuner. ATENÇÃO:a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L13" s="49" t="n"/>
@@ -9204,21 +9542,33 @@
       <c r="S13" s="49" t="n"/>
       <c r="T13" s="49" t="n"/>
       <c r="U13" s="49" t="n"/>
-      <c r="V13" s="49" t="n"/>
+      <c r="V13" s="275" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W13" s="49" t="n"/>
-      <c r="X13" s="48" t="n"/>
+      <c r="X13" s="276" t="inlineStr">
+        <is>
+          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D74 - Porta pivotante estruturada, fechamento em MDF cru, acabamento face interna e externa em micropintura cor S168-Sayerlack. Puxador tipo cava, prever tranca. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+D85 - Porta corta fogo em aço inox escovado. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="Y13" s="48" t="n"/>
       <c r="Z13" s="49" t="n"/>
     </row>
-    <row r="14" ht="409" customHeight="1">
+    <row r="14">
       <c r="A14" s="45" t="inlineStr">
         <is>
           <t>SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B14" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B14" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C14" s="32" t="n"/>
@@ -9226,25 +9576,27 @@
       <c r="E14" s="32" t="n"/>
       <c r="F14" s="246" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G14" s="32" t="n"/>
       <c r="H14" s="246" t="inlineStr">
         <is>
-          <t>PA40 - Revestimento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner.
-PA41 - Revestimento de mármore Dedalus, acabamento escovado, espessura 2cm, rejunte em massa plastica a ser tonalizada de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII
-PA31 - Pintura com tinta mineral, cor 107, acabamento CQ Ref: Terracor</t>
-        </is>
-      </c>
-      <c r="I14" s="246" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA40 - Parede em alvenaria emassada regularizada, revestida em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+PA41 - Parede em alvenaria rebocada regularizada revestida em pedra natural, mármore Dedalus, acabamento escovado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA31 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 107, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I14" s="278" t="inlineStr">
+        <is>
+          <t>FO1 - Forro de absorção acústica composto por 1 manta de lã de pet com 35Kg/m³ de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar
+FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
+T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J14" s="246" t="inlineStr">
         <is>
-          <t>D24 - Bancada em pedra natural, mármore Dedalus, acabamento escovado, espessura 2cm</t>
+          <t>D24 - Bancada em pedra natural, mármore Dedalus, acabamento escovado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K14" s="32" t="n"/>
@@ -9258,9 +9610,18 @@
       <c r="S14" s="32" t="n"/>
       <c r="T14" s="32" t="n"/>
       <c r="U14" s="32" t="n"/>
-      <c r="V14" s="32" t="n"/>
+      <c r="V14" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W14" s="32" t="n"/>
-      <c r="X14" s="31" t="n"/>
+      <c r="X14" s="269" t="inlineStr">
+        <is>
+          <t>D21 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxadores conforme detalhamento. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="Y14" s="31" t="n"/>
       <c r="Z14" s="32" t="n"/>
     </row>
@@ -9328,15 +9689,16 @@
       <c r="Y16" s="31" t="n"/>
       <c r="Z16" s="32" t="n"/>
     </row>
-    <row r="17" ht="409" customHeight="1">
+    <row r="17">
       <c r="A17" s="45" t="inlineStr">
         <is>
           <t>I.S FEMININO</t>
         </is>
       </c>
-      <c r="B17" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B17" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C17" s="32" t="n"/>
@@ -9344,28 +9706,28 @@
       <c r="E17" s="32" t="n"/>
       <c r="F17" s="246" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G17" s="32" t="n"/>
       <c r="H17" s="246" t="inlineStr">
         <is>
-          <t>PA39 - Revestimento de mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran, rejunte em massa plastica a ser tonalizada de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII</t>
-        </is>
-      </c>
-      <c r="I17" s="246" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA39 - Parede em alvenaria rebocada regularizada revestida em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I17" s="278" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J17" s="246" t="inlineStr">
         <is>
-          <t>D25 - Bancada e cuba esculpida com bandeja removível em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Basigran</t>
+          <t>D25 - Bancada e cuba esculpida com bandeja removível em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K17" s="246" t="inlineStr">
         <is>
-          <t>D37 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria</t>
+          <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
       <c r="L17" s="32" t="n"/>
@@ -9373,12 +9735,12 @@
       <c r="N17" s="32" t="n"/>
       <c r="O17" s="246" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água</t>
-        </is>
-      </c>
-      <c r="P17" s="246" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P17" s="278" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q17" s="32" t="n"/>
@@ -9386,27 +9748,36 @@
       <c r="S17" s="32" t="n"/>
       <c r="T17" s="32" t="n"/>
       <c r="U17" s="32" t="n"/>
-      <c r="V17" s="32" t="n"/>
+      <c r="V17" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W17" s="32" t="n"/>
-      <c r="X17" s="31" t="n"/>
+      <c r="X17" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="Y17" s="31" t="n"/>
-      <c r="Z17" s="246" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="409" customHeight="1">
+      <c r="Z17" s="278" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="45" t="inlineStr">
         <is>
           <t>I.S MASCULINO</t>
         </is>
       </c>
-      <c r="B18" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B18" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C18" s="32" t="n"/>
@@ -9414,28 +9785,28 @@
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="246" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G18" s="32" t="n"/>
       <c r="H18" s="246" t="inlineStr">
         <is>
-          <t>PA39 - Revestimento de mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran, rejunte em massa plastica a ser tonalizada de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII</t>
-        </is>
-      </c>
-      <c r="I18" s="246" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA39 - Parede em alvenaria rebocada regularizada revestida em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I18" s="278" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J18" s="246" t="inlineStr">
         <is>
-          <t>D25 - Bancada e cuba esculpida com bandeja removível em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Basigran</t>
+          <t>D25 - Bancada e cuba esculpida com bandeja removível em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K18" s="246" t="inlineStr">
         <is>
-          <t>D37 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria</t>
+          <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
       <c r="L18" s="32" t="n"/>
@@ -9443,12 +9814,12 @@
       <c r="N18" s="32" t="n"/>
       <c r="O18" s="246" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água</t>
-        </is>
-      </c>
-      <c r="P18" s="246" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P18" s="278" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q18" s="32" t="n"/>
@@ -9456,15 +9827,23 @@
       <c r="S18" s="32" t="n"/>
       <c r="T18" s="32" t="n"/>
       <c r="U18" s="32" t="n"/>
-      <c r="V18" s="32" t="n"/>
+      <c r="V18" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W18" s="32" t="n"/>
-      <c r="X18" s="31" t="n"/>
+      <c r="X18" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="Y18" s="31" t="n"/>
-      <c r="Z18" s="246" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
+      <c r="Z18" s="278" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
     </row>
@@ -9500,15 +9879,16 @@
       <c r="Y19" s="31" t="n"/>
       <c r="Z19" s="32" t="n"/>
     </row>
-    <row r="20" ht="409" customHeight="1">
+    <row r="20">
       <c r="A20" s="45" t="inlineStr">
         <is>
           <t>COZINHA SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B20" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B20" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C20" s="32" t="n"/>
@@ -9522,31 +9902,31 @@
       <c r="G20" s="32" t="n"/>
       <c r="H20" s="246" t="inlineStr">
         <is>
-          <t>PA52 - Revestimento de granito cinza Santa Rosa, acabamento ecovado, espessura : 2cm, assentado com argamassa colante em pó ACIII. Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material
-PA43 - Revestimento em fórmica cor Almond L112, acabamento mate.: Ref.: Fórmica</t>
-        </is>
-      </c>
-      <c r="I20" s="246" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA43 - Parede emassada regularizada, revestida com fórmica cor Almond L112, acabamento mate. Ref.: Formica. Dimensões e paginações conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.
+PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+      <c r="I20" s="278" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J20" s="246" t="inlineStr">
         <is>
-          <t>D36 - Bancadas e cuba esculpidas em granito cinza Santa Rosa, acabamento escovado. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra</t>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="K20" s="32" t="n"/>
       <c r="L20" s="246" t="inlineStr">
         <is>
-          <t>D80 - Cuba de embutir, Dora 70 em aço inox, 70x40c, acabamento acetinado, cód.: BL R6 Ref.: Tramontina</t>
+          <t>D80 - Cuba de embutir, Dora 70 em aço inox, 70x40cm, acabamento acetinado, cód.: BL R6. Ref.: Tramontina</t>
         </is>
       </c>
       <c r="M20" s="32" t="n"/>
       <c r="N20" s="32" t="n"/>
       <c r="O20" s="246" t="inlineStr">
         <is>
-          <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scoth Brite, cód.: 94520022. Ref.: Tramontina</t>
+          <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scoth Brite, cód.: 94520022. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
       <c r="P20" s="32" t="n"/>
@@ -9555,11 +9935,24 @@
       <c r="S20" s="32" t="n"/>
       <c r="T20" s="32" t="n"/>
       <c r="U20" s="32" t="n"/>
-      <c r="V20" s="32" t="n"/>
+      <c r="V20" s="270" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W20" s="32" t="n"/>
-      <c r="X20" s="31" t="n"/>
+      <c r="X20" s="269" t="inlineStr">
+        <is>
+          <t>D21 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxadores conforme detalhamento. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+D74 - Porta pivotante estruturada, fechamento em MDF cru, acabamento face interna e externa em micropintura cor S168-Sayerlack. Puxador tipo cava, prever tranca. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="32" t="n"/>
+      <c r="Z20" s="270" t="inlineStr">
+        <is>
+          <t>D82 - Prateleira em granito cinza Santa Rosa, acabamento escovado, embutido na alvenaria. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="335" customHeight="1">
       <c r="A21" s="45" t="inlineStr">
@@ -9649,7 +10042,7 @@
       <c r="Y22" s="31" t="n"/>
       <c r="Z22" s="32" t="n"/>
     </row>
-    <row r="23" ht="409" customHeight="1">
+    <row r="23">
       <c r="A23" s="45" t="inlineStr">
         <is>
           <t>I.S P.C.D</t>
@@ -9657,7 +10050,7 @@
       </c>
       <c r="B23" s="245" t="inlineStr">
         <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+          <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C23" s="32" t="n"/>
@@ -9665,30 +10058,30 @@
       <c r="E23" s="36" t="n"/>
       <c r="F23" s="245" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G23" s="32" t="n"/>
-      <c r="H23" s="245" t="inlineStr">
-        <is>
-          <t>PA32 - Revestimento em mdf cru para regularização da superfície e acabamento em folha de madeia natural carvalho tonalizado
-PA52 - Revestimento de granito cinza Santa Rosa, acabamento ecovado, espessura : 2cm, assentado com argamassa colante em pó ACIII. Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
-        </is>
-      </c>
-      <c r="I23" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H23" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
+PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+      <c r="I23" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J23" s="246" t="inlineStr">
         <is>
-          <t>D30 - Bancada e cuba esculpida com bandeja removível em granito cinza Santa Rosa, acabamento escovado, esp. 2cm</t>
+          <t>D30 - Bancada e cuba eculpida com bandeja removível em granito cinza Santa Rosa, acabamento escovado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="K23" s="246" t="inlineStr">
         <is>
-          <t>D38 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria
-Perfil cantoneira em alumínio para transição de materiais</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L23" s="32" t="n"/>
@@ -9696,12 +10089,12 @@
       <c r="N23" s="32" t="n"/>
       <c r="O23" s="246" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água</t>
-        </is>
-      </c>
-      <c r="P23" s="246" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P23" s="278" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q23" s="32" t="n"/>
@@ -9709,19 +10102,27 @@
       <c r="S23" s="32" t="n"/>
       <c r="T23" s="32" t="n"/>
       <c r="U23" s="32" t="n"/>
-      <c r="V23" s="31" t="n"/>
+      <c r="V23" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W23" s="35" t="n"/>
-      <c r="X23" s="31" t="n"/>
+      <c r="X23" s="269" t="inlineStr">
+        <is>
+          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
+        </is>
+      </c>
       <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="245" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="409" customHeight="1">
+      <c r="Z23" s="277" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">I.S </t>
@@ -9729,7 +10130,7 @@
       </c>
       <c r="B24" s="245" t="inlineStr">
         <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+          <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C24" s="32" t="n"/>
@@ -9737,30 +10138,30 @@
       <c r="E24" s="32" t="n"/>
       <c r="F24" s="245" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G24" s="32" t="n"/>
-      <c r="H24" s="245" t="inlineStr">
-        <is>
-          <t>PA32 - Revestimento em mdf cru para regularização da superfície e acabamento em folha de madeia natural carvalho tonalizado
-PA52 - Revestimento de granito cinza Santa Rosa, acabamento ecovado, espessura : 2cm, assentado com argamassa colante em pó ACIII. Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
-        </is>
-      </c>
-      <c r="I24" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H24" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
+PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+      <c r="I24" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J24" s="245" t="inlineStr">
         <is>
-          <t>D30 - Bancada e cuba esculpida com bandeja removível em granito cinza Santa Rosa, acabamento escovado, esp. 2cm</t>
+          <t>D30 - Bancada e cuba eculpida com bandeja removível em granito cinza Santa Rosa, acabamento escovado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="K24" s="246" t="inlineStr">
         <is>
-          <t>D38 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria
-Perfil cantoneira em alumínio para transição de materiais</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L24" s="32" t="n"/>
@@ -9768,12 +10169,12 @@
       <c r="N24" s="37" t="n"/>
       <c r="O24" s="245" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água</t>
-        </is>
-      </c>
-      <c r="P24" s="245" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P24" s="277" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q24" s="32" t="n"/>
@@ -9781,15 +10182,23 @@
       <c r="S24" s="32" t="n"/>
       <c r="T24" s="35" t="n"/>
       <c r="U24" s="32" t="n"/>
-      <c r="V24" s="31" t="n"/>
+      <c r="V24" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W24" s="35" t="n"/>
-      <c r="X24" s="35" t="n"/>
+      <c r="X24" s="269" t="inlineStr">
+        <is>
+          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
+        </is>
+      </c>
       <c r="Y24" s="35" t="n"/>
-      <c r="Z24" s="245" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
+      <c r="Z24" s="277" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
     </row>
@@ -9825,15 +10234,16 @@
       <c r="Y25" s="31" t="n"/>
       <c r="Z25" s="35" t="n"/>
     </row>
-    <row r="26" ht="409" customHeight="1">
+    <row r="26">
       <c r="A26" s="45" t="inlineStr">
         <is>
           <t>ESPAÇO KIDS</t>
         </is>
       </c>
-      <c r="B26" s="245" t="inlineStr">
-        <is>
-          <t>P24 - Piso vinílico em manta, 2,20m, linha Polysafe verona PUR, acabamento Rock Salt - cód.: LRV-43.</t>
+      <c r="B26" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P24 - Piso em contrapiso regularizado revestido em piso vinílico em manta, 2x20m, linha Polysafe Verona PUR, acabamento Rock Salt - cód: LRV-43. Paginação conforme detalhamento.</t>
         </is>
       </c>
       <c r="C26" s="32" t="n"/>
@@ -9841,22 +10251,24 @@
       <c r="E26" s="37" t="n"/>
       <c r="F26" s="245" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G26" s="32" t="n"/>
       <c r="H26" s="245" t="inlineStr">
         <is>
-          <t>PA34 - Revestimento de granito cinza Santa Rosa, acabamento serrado, espessura : 2cm, assentado com argamassa colante em pó ACIII. Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material
-(Reboco) PA37 - Papel de parede degradê laranja 114-branco casa. Cód.: Ref.: BR0114-B10099- PDP_TM
-PA35 - Revestimento em MDF cru 8mm para regularização da superfície e acabamento em chapa metálica - #16 (aço carbono) colada sobre MDF ou fixada através de fita dupla face 3M - finalização com mkicropintura cor S081 - Sayerlack.
-PA36 - Revestimento em MDF cru 8mm + chapa de 4mm com acabamento em micropintura em cor N081 - Sayerlack colada sobre MDF cru.
-PA38 - Painel de marcenaria MDF Nude-linha VEL- Berneck.</t>
-        </is>
-      </c>
-      <c r="I26" s="246" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA34 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
+PA35 - Parede em alvenaria emassada regularizada, revestida em MDF cru 8mm para regularização da superficie e acabamento em chapa metálica - #16 (aço carbono) colda sobre MDF ou fixada através de fita dupla face 3M -  finalização em micropintura cor S081-Sayerlack. Ver detalhes específicos e amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA36 - Parede em alvenaria emassada regularizada, revestida em painel de MDF cru 8mm + chpa de 4mm com acabamento em mircropintura em cor N081-Sayerlack colada sobre MDF cru. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA37 - Parede emassada regularizada revestida com papel de parede degradê laranja 114-Branco casa. Cód Ref.: BR0114_B10099_PDP_TM. Amostra a ser aprovada pela GPA&amp;A.
+PA38 - Parede em alvenaria emassada regularizada, revestida em painel de marcenaria MDF Nude-linha VEL-Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.</t>
+        </is>
+      </c>
+      <c r="I26" s="278" t="inlineStr">
+        <is>
+          <t>FO1 - Forro de absorção acústica composto por 1 manta de lã de pet com 35Kg/m³ de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar
+FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
+T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J26" s="32" t="n"/>
@@ -9871,21 +10283,36 @@
       <c r="S26" s="32" t="n"/>
       <c r="T26" s="35" t="n"/>
       <c r="U26" s="32" t="n"/>
-      <c r="V26" s="31" t="n"/>
+      <c r="V26" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W26" s="35" t="n"/>
-      <c r="X26" s="31" t="n"/>
+      <c r="X26" s="269" t="inlineStr">
+        <is>
+          <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="35" t="n"/>
-    </row>
-    <row r="27" ht="409" customHeight="1">
+      <c r="Z26" s="269" t="inlineStr">
+        <is>
+          <t>D18 - Módulos compostos por três peças hexagonais com estruturado em peças de madeira maciça,   fechamento em reguas de madeira 25mmx70mm. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D56 - Pendente sob medida em peças de madeira maciça 60x50mm fixados no teto através de cabos de aço e estrutura auxiliar no entreforro, com acabamento no forro em canopla, cor branca. Retroiluminação em fitas de led na parte superior com dimensionamentos conforme projeto luminotécnico. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="45" t="inlineStr">
         <is>
           <t>ESPAÇO GOURMET</t>
         </is>
       </c>
-      <c r="B27" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B27" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C27" s="32" t="n"/>
@@ -9893,24 +10320,26 @@
       <c r="E27" s="37" t="n"/>
       <c r="F27" s="246" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G27" s="35" t="n"/>
-      <c r="H27" s="245" t="inlineStr">
-        <is>
-          <t>PA32 - Revestimento em mdf cru para regularização da superfície e acabamento em folha de madeia natural carvalho tonalizado
-PA44 - Textura acrílica cimento queimado, cor 107. Ref.: Terracor CQ</t>
-        </is>
-      </c>
-      <c r="I27" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H27" s="277" t="inlineStr">
+        <is>
+          <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
+PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
+PA33 - Pilar em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I27" s="277" t="inlineStr">
+        <is>
+          <t>FO1 - Forro de absorção acústica composto por 1 manta de lã de pet com 35Kg/m³ de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar
+FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.</t>
         </is>
       </c>
       <c r="J27" s="245" t="inlineStr">
         <is>
-          <t>D8 - Bancada em pedra natural, quartzito mont blanc acabamento escovado. Espessura: 2cm</t>
+          <t>D8 - Bancada em pedra natural, quartzito mont blanc acabamento escovado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K27" s="246" t="inlineStr">
@@ -9920,14 +10349,14 @@
       </c>
       <c r="L27" s="245" t="inlineStr">
         <is>
-          <t>D10 - Cuba design collection Quadrum 70 em aço inox com acabamento Scotch Brite. Cód ref.: REF 94007103. Ref.: Tramontina</t>
+          <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina</t>
         </is>
       </c>
       <c r="M27" s="35" t="n"/>
       <c r="N27" s="35" t="n"/>
       <c r="O27" s="245" t="inlineStr">
         <is>
-          <t>D9 - Misturador monocomando Monde Filter Plus em aço inox com saída adiconal para água filtrada + Filtro 3m. Cód ref.: REF 94520025. Ref.: Tramontina. Atenção vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
+          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
         </is>
       </c>
       <c r="P27" s="32" t="n"/>
@@ -9936,11 +10365,28 @@
       <c r="S27" s="32" t="n"/>
       <c r="T27" s="32" t="n"/>
       <c r="U27" s="32" t="n"/>
-      <c r="V27" s="31" t="n"/>
+      <c r="V27" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W27" s="32" t="n"/>
-      <c r="X27" s="32" t="n"/>
+      <c r="X27" s="270" t="inlineStr">
+        <is>
+          <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="Y27" s="32" t="n"/>
-      <c r="Z27" s="35" t="n"/>
+      <c r="Z27" s="269" t="inlineStr">
+        <is>
+          <t>D13 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
+D14 - Fechamento cego em mdf cru com acabamento em folha madeira natural caravalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D15 - Armários em mdf cru com acabamento em folha madeira natural carvalho tonalizado. Puxadore integrado linha Sottile ref. ZEN - acabamento bronze 192mm. Consultar detalhamento.Amostra folha natural madeira com acabamenhto deverá ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D16 - Mesa em mdf cru com acabamento em folha madeira natural caravalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D17 - Armários em ripas de madeira maciça tonalizada seguindo cor folha madeira - ripas de 20x20mm espaçadas 15mm. Portas de giro com puxador no trespasse. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="125.25" customHeight="1">
       <c r="A28" s="45" t="inlineStr">
@@ -9974,15 +10420,16 @@
       <c r="Y28" s="32" t="n"/>
       <c r="Z28" s="35" t="n"/>
     </row>
-    <row r="29" ht="293" customHeight="1">
+    <row r="29">
       <c r="A29" s="45" t="inlineStr">
         <is>
           <t>PISCINA DECOBERTA</t>
         </is>
       </c>
-      <c r="B29" s="245" t="inlineStr">
-        <is>
-          <t>P18 - Revestimento em pastilhas de mármore branco selecionado, acabamento levigado 3x3cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="B29" s="277" t="inlineStr">
+        <is>
+          <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm.  Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A
+P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C29" s="32" t="n"/>
@@ -9990,9 +10437,9 @@
       <c r="E29" s="37" t="n"/>
       <c r="F29" s="35" t="n"/>
       <c r="G29" s="32" t="n"/>
-      <c r="H29" s="245" t="inlineStr">
-        <is>
-          <t>P18 - Revestimento em pastilhas de mármore branco selecionado, acabamento levigado 3x3cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="H29" s="277" t="inlineStr">
+        <is>
+          <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614.. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="I29" s="35" t="n"/>
@@ -10010,15 +10457,31 @@
       <c r="Q29" s="32" t="n"/>
       <c r="R29" s="32" t="n"/>
       <c r="S29" s="32" t="n"/>
-      <c r="T29" s="32" t="n"/>
-      <c r="U29" s="32" t="n"/>
+      <c r="T29" s="270" t="inlineStr">
+        <is>
+          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
+      <c r="U29" s="270" t="inlineStr">
+        <is>
+          <t>D79 - Chuveiro de piso para área externa em aço inox 316. cód.: DK5123B. Ref.: Doka</t>
+        </is>
+      </c>
       <c r="V29" s="31" t="n"/>
       <c r="W29" s="35" t="n"/>
-      <c r="X29" s="31" t="n"/>
+      <c r="X29" s="269" t="inlineStr">
+        <is>
+          <t>D77 - Porta pivotante para guarda corpo em vidro temperado laminado liso incolor com tubo para pivô em aço inox polido 1 1/4'' fixado no piso com barra lisa soltada com rosca na extremidade para fixação do vidro com botão de acabamento.</t>
+        </is>
+      </c>
       <c r="Y29" s="31" t="n"/>
-      <c r="Z29" s="35" t="n"/>
-    </row>
-    <row r="30" ht="125.25" customHeight="1">
+      <c r="Z29" s="269" t="inlineStr">
+        <is>
+          <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="45" t="inlineStr">
         <is>
           <t>DECK</t>
@@ -10026,7 +10489,7 @@
       </c>
       <c r="B30" s="245" t="inlineStr">
         <is>
-          <t>P26 - Piso em deck de madeira Cumaru com técnica de carbonização Shugi Ban, réguas 20mmx100mmx2000mm acima. Ref. Madeira carbonizada</t>
+          <t>P26 - Piso em deck de madeira Cumaru com tecnica de carbonização Shugi Ban, reguas 20mmx100mmx2000m-acima. Ref.:Madeira Carbonizada.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="C30" s="32" t="n"/>
@@ -10086,37 +10549,83 @@
       <c r="Y31" s="32" t="n"/>
       <c r="Z31" s="32" t="n"/>
     </row>
-    <row r="32" ht="125.25" customHeight="1">
+    <row r="32">
       <c r="A32" s="45" t="inlineStr">
         <is>
           <t>BAR PISCINA</t>
         </is>
       </c>
-      <c r="B32" s="35" t="n"/>
+      <c r="B32" s="269" t="inlineStr">
+        <is>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C32" s="32" t="n"/>
       <c r="D32" s="37" t="n"/>
       <c r="E32" s="37" t="n"/>
-      <c r="F32" s="35" t="n"/>
+      <c r="F32" s="269" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G32" s="32" t="n"/>
-      <c r="H32" s="35" t="n"/>
-      <c r="I32" s="35" t="n"/>
-      <c r="J32" s="32" t="n"/>
+      <c r="H32" s="269" t="inlineStr">
+        <is>
+          <t>PA42 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento serrado, com arte em baixo relevo, corte a laser, profundidade 4mm Espessura da pedra: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA51 - Pilar em concreto aparente</t>
+        </is>
+      </c>
+      <c r="I32" s="269" t="inlineStr">
+        <is>
+          <t>T4 - Forro em madeira pinho autoclavado tonalizado, espessura de 3cm, réguas de 10cm.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J32" s="270" t="inlineStr">
+        <is>
+          <t>D46 - Bancada/Mesa em pedra sinterizada, Lava satin fusion collection. Espessura: 5mm. Ref: Neo Lhít. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="K32" s="32" t="n"/>
-      <c r="L32" s="32" t="n"/>
+      <c r="L32" s="270" t="inlineStr">
+        <is>
+          <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina</t>
+        </is>
+      </c>
       <c r="M32" s="32" t="n"/>
       <c r="N32" s="32" t="n"/>
-      <c r="O32" s="32" t="n"/>
+      <c r="O32" s="270" t="inlineStr">
+        <is>
+          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
+        </is>
+      </c>
       <c r="P32" s="32" t="n"/>
       <c r="Q32" s="32" t="n"/>
       <c r="R32" s="32" t="n"/>
       <c r="S32" s="32" t="n"/>
-      <c r="T32" s="32" t="n"/>
+      <c r="T32" s="270" t="inlineStr">
+        <is>
+          <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
       <c r="U32" s="32" t="n"/>
-      <c r="V32" s="31" t="n"/>
+      <c r="V32" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W32" s="35" t="n"/>
       <c r="X32" s="31" t="n"/>
       <c r="Y32" s="31" t="n"/>
-      <c r="Z32" s="35" t="n"/>
+      <c r="Z32" s="269" t="inlineStr">
+        <is>
+          <t>D47 - Marcenaria sob bancada em MDF Kashimir ref. Arauco - portas e frente gavetas em reguas de madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador em cava na marcenaria. Apresentar amostra para aprovação GPA&amp;A Obs.: MDF possui certificação FSC. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+D48 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
+D49 - Armários com interior em MDF madeirado e portas de giro ripadas -  ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria - prever fechamento face interna porta em vidro liso incolor 4mm. Prateleiras em MDF madeirado com iluminação em LED. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D50 - Armário sob bancada com portas de giro ripadas para ventilação choppeira. Ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="125.25" customHeight="1">
       <c r="A33" s="45" t="inlineStr">
@@ -10150,20 +10659,32 @@
       <c r="Y33" s="35" t="n"/>
       <c r="Z33" s="32" t="n"/>
     </row>
-    <row r="34" ht="125.25" customHeight="1">
+    <row r="34">
       <c r="A34" s="45" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO VESTIÁRIOS</t>
         </is>
       </c>
-      <c r="B34" s="35" t="n"/>
+      <c r="B34" s="269" t="inlineStr">
+        <is>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C34" s="32" t="n"/>
       <c r="D34" s="35" t="n"/>
       <c r="E34" s="37" t="n"/>
       <c r="F34" s="35" t="n"/>
       <c r="G34" s="32" t="n"/>
-      <c r="H34" s="35" t="n"/>
-      <c r="I34" s="35" t="n"/>
+      <c r="H34" s="269" t="inlineStr">
+        <is>
+          <t>PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+      <c r="I34" s="269" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J34" s="35" t="n"/>
       <c r="K34" s="32" t="n"/>
       <c r="L34" s="35" t="n"/>
@@ -10176,47 +10697,56 @@
       <c r="S34" s="35" t="n"/>
       <c r="T34" s="35" t="n"/>
       <c r="U34" s="32" t="n"/>
-      <c r="V34" s="31" t="n"/>
+      <c r="V34" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W34" s="35" t="n"/>
       <c r="X34" s="35" t="n"/>
       <c r="Y34" s="35" t="n"/>
       <c r="Z34" s="32" t="n"/>
     </row>
-    <row r="35" ht="409" customHeight="1">
+    <row r="35">
       <c r="A35" s="45" t="inlineStr">
         <is>
           <t>VESTIÁRIO FEMININO</t>
         </is>
       </c>
-      <c r="B35" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B35" s="277" t="inlineStr">
+        <is>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C35" s="32" t="n"/>
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="37" t="n"/>
-      <c r="F35" s="35" t="n"/>
+      <c r="F35" s="269" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G35" s="32" t="n"/>
-      <c r="H35" s="245" t="inlineStr">
-        <is>
-          <t>PA52 - Revestimento de granito cinza Santa Rosa, acabamento ecovado, espessura : 2cm, assentado com argamassa colante em pó ACIII. Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material
-PA46 - Revestimento de mármore branco selecionado, espessura 2cm, assentado com argamassa de cimento e areia</t>
-        </is>
-      </c>
-      <c r="I35" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
-        </is>
-      </c>
-      <c r="J35" s="245" t="inlineStr">
-        <is>
-          <t>D73 - Bancada em pedra natural, mármore branco selecionado, acabamento levigado, espessura 2cm</t>
+      <c r="H35" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
+PA60 - Parede revestida em chapa de aço inox 304, acabamento polido. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I35" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J35" s="277" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="K35" s="246" t="inlineStr">
         <is>
-          <t>D37 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria</t>
+          <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
       <c r="L35" s="35" t="n"/>
@@ -10224,79 +10754,92 @@
       <c r="N35" s="38" t="n"/>
       <c r="O35" s="245" t="inlineStr">
         <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e baterail Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
-        </is>
-      </c>
-      <c r="P35" s="245" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P35" s="277" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q35" s="32" t="n"/>
       <c r="R35" s="35" t="n"/>
       <c r="S35" s="245" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.: 90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
         </is>
       </c>
       <c r="T35" s="245" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
-D35 - Ralo linear com tampa lisa em aço inox, linha Square, Ref.: Elleve</t>
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
       <c r="U35" s="246" t="inlineStr">
         <is>
-          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha Docol Eden, acabamento cromado, cód.: 90009312006 Ref. Docol</t>
-        </is>
-      </c>
-      <c r="V35" s="31" t="n"/>
+          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="V35" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W35" s="35" t="n"/>
-      <c r="X35" s="35" t="n"/>
+      <c r="X35" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
+        </is>
+      </c>
       <c r="Y35" s="35" t="n"/>
-      <c r="Z35" s="246" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="409" customHeight="1">
+      <c r="Z35" s="278" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">VESTIÁRIO MASCULINO </t>
         </is>
       </c>
-      <c r="B36" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B36" s="277" t="inlineStr">
+        <is>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C36" s="32" t="n"/>
       <c r="D36" s="35" t="n"/>
       <c r="E36" s="37" t="n"/>
-      <c r="F36" s="35" t="n"/>
+      <c r="F36" s="269" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G36" s="32" t="n"/>
-      <c r="H36" s="245" t="inlineStr">
-        <is>
-          <t>PA52 - Revestimento de granito cinza Santa Rosa, acabamento ecovado, espessura : 2cm, assentado com argamassa colante em pó ACIII. Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material
-PA46 - Revestimento de mármore branco selecionado, espessura 2cm, assentado com argamassa de cimento e areia</t>
-        </is>
-      </c>
-      <c r="I36" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
-        </is>
-      </c>
-      <c r="J36" s="245" t="inlineStr">
-        <is>
-          <t>D73 - Bancada em pedra natural, mármore branco selecionado, acabamento levigado, espessura 2cm</t>
+      <c r="H36" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
+PA60 - Parede revestida em chapa de aço inox 304, acabamento polido. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I36" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J36" s="277" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="K36" s="246" t="inlineStr">
         <is>
-          <t>D37 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria</t>
+          <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
       <c r="L36" s="35" t="n"/>
@@ -10304,53 +10847,62 @@
       <c r="N36" s="38" t="n"/>
       <c r="O36" s="245" t="inlineStr">
         <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e baterail Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
-        </is>
-      </c>
-      <c r="P36" s="245" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P36" s="277" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q36" s="32" t="n"/>
       <c r="R36" s="35" t="n"/>
       <c r="S36" s="245" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.: 90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
         </is>
       </c>
       <c r="T36" s="245" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
-D35 - Ralo linear com tampa lisa em aço inox, linha Square, Ref.: Elleve</t>
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
       <c r="U36" s="246" t="inlineStr">
         <is>
-          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha Docol Eden, acabamento cromado, cód.: 90009312006 Ref. Docol</t>
-        </is>
-      </c>
-      <c r="V36" s="31" t="n"/>
+          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="V36" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W36" s="35" t="n"/>
-      <c r="X36" s="35" t="n"/>
+      <c r="X36" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
+        </is>
+      </c>
       <c r="Y36" s="35" t="n"/>
-      <c r="Z36" s="246" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="409" customHeight="1">
+      <c r="Z36" s="278" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="45" t="inlineStr">
         <is>
           <t>ACADEMIA</t>
         </is>
       </c>
-      <c r="B37" s="245" t="inlineStr">
-        <is>
-          <t>PA22 - Piso emborrachado isolanete e antiderrapante, acabamento preto, placas 100x100cm esp.: 8mm, Ref.: Rubberkap ou similar</t>
+      <c r="B37" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P22 - Piso em contrapiso regularizado, revestido em piso emborrachado isolante e antiderrapante, acabamernto preto, placas 100x100cm. Espessura: 8mm. Paginação conforme detalhamento. Ref.: Rubberkap ou similar. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="C37" s="32" t="n"/>
@@ -10358,20 +10910,23 @@
       <c r="E37" s="37" t="n"/>
       <c r="F37" s="246" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G37" s="32" t="n"/>
-      <c r="H37" s="245" t="inlineStr">
-        <is>
-          <t>PA26 - Espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado ma alvenaria
-PA27 - Espelho liso fumê 4mm colado sobre MDF cru 6mm aparafusado ma alvenaria
-PA28 - Revestimento em painel de MDF Nero Rust. Ref.: Berneck</t>
-        </is>
-      </c>
-      <c r="I37" s="245" t="inlineStr">
-        <is>
-          <t>FO1 - Forro de absorção acústica composto por 1 manta de de lã de pet com 35kg/m3 de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar | 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H37" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA27 - Parede em alvenaria rebocada e regularizada revestida em espelho liso fumê 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA28 - Parede em alvenaria rebocada e regularizada revestida em painel de MDF Nero Rust. Paginação conforme detalhamento. Ref.: Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
+PA29 - Fechamento vertical estruturado com acabamento em painel de MDF Nero Rust. Paginação conforme detalhamento. Ref.: Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
+PA30 - Pilar em concreto com acabamento em textura mineral Arch + Concrete ENG, Ref.: Novacolor. Fornecedor: Icolori (31)99952-2442. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I37" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
+FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.</t>
         </is>
       </c>
       <c r="J37" s="35" t="n"/>
@@ -10386,11 +10941,27 @@
       <c r="S37" s="35" t="n"/>
       <c r="T37" s="35" t="n"/>
       <c r="U37" s="32" t="n"/>
-      <c r="V37" s="31" t="n"/>
+      <c r="V37" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W37" s="35" t="n"/>
-      <c r="X37" s="35" t="n"/>
+      <c r="X37" s="269" t="inlineStr">
+        <is>
+          <t>D57 - Porta de correr com duas folhas em vidro temperado liso incolor, com kit de instalação de sensor, modelo ES200. Ref.: Dorma</t>
+        </is>
+      </c>
       <c r="Y37" s="35" t="n"/>
-      <c r="Z37" s="32" t="n"/>
+      <c r="Z37" s="270" t="inlineStr">
+        <is>
+          <t>D3 - Estante em MDF Nero Rust Ref.: Berneck, desenho conforme detalhamento, Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
+D4 - Armário em marcenaria, estruturado, com espaço para central de sonorização e automação, quadro de distribuição embutido - verificar dimensões com projetos específico, desenho conforme detalhamento. Porta.  de giro com sistema fecho-toque, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
+D5 - Painel estruturado com moldura, para encaixe de equipamento, desenho conforme detalhamento, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
+D6 - Anéis metálicos acabamento em micropintura perolizada, cor L098, Ref.: Sherwin Williams, fixados em pilar de concreto através de espassadores metálicos. Ver detalhamento. Apresentar protótipo e amostra pintura para aprovação GPA&amp;A.
+D7 - Mesa de apoio metálica em micropintura perolizada, cor L098, Ref.: Sherwin Williams, fixados em pilar de concreto através de estrutura auxiliar. Ver detalhamento. Apresentar protótipo e amostra pintura para aprovação GPA&amp;A.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="125.25" customHeight="1">
       <c r="A38" s="45" t="inlineStr">
@@ -10424,15 +10995,15 @@
       <c r="Y38" s="35" t="n"/>
       <c r="Z38" s="32" t="n"/>
     </row>
-    <row r="39" ht="293" customHeight="1">
+    <row r="39">
       <c r="A39" s="45" t="inlineStr">
         <is>
           <t>PISCINA RAIA</t>
         </is>
       </c>
-      <c r="B39" s="245" t="inlineStr">
-        <is>
-          <t>P18 - Revestimento em pastilhas de mármore branco selecionado, acabamento levigado 3x3cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="B39" s="277" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C39" s="32" t="n"/>
@@ -10440,9 +11011,9 @@
       <c r="E39" s="37" t="n"/>
       <c r="F39" s="32" t="n"/>
       <c r="G39" s="32" t="n"/>
-      <c r="H39" s="245" t="inlineStr">
-        <is>
-          <t>P18 - Revestimento em pastilhas de mármore branco selecionado, acabamento levigado 3x3cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="H39" s="277" t="inlineStr">
+        <is>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="I39" s="35" t="n"/>
@@ -10464,7 +11035,7 @@
       <c r="Y39" s="35" t="n"/>
       <c r="Z39" s="32" t="n"/>
     </row>
-    <row r="40" ht="293" customHeight="1">
+    <row r="40">
       <c r="A40" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">SPA </t>
@@ -10472,7 +11043,7 @@
       </c>
       <c r="B40" s="245" t="inlineStr">
         <is>
-          <t>P18 - Revestimento em pastilhas de mármore branco selecionado, acabamento levigado 3x3cm, assentado com argamassa colante em pó ACIII</t>
+          <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm.  Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C40" s="32" t="n"/>
@@ -10480,9 +11051,9 @@
       <c r="E40" s="37" t="n"/>
       <c r="F40" s="32" t="n"/>
       <c r="G40" s="32" t="n"/>
-      <c r="H40" s="245" t="inlineStr">
-        <is>
-          <t>P18 - Revestimento em pastilhas de mármore branco selecionado, acabamento levigado 3x3cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="H40" s="277" t="inlineStr">
+        <is>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="I40" s="35" t="n"/>
@@ -10504,7 +11075,7 @@
       <c r="Y40" s="35" t="n"/>
       <c r="Z40" s="32" t="n"/>
     </row>
-    <row r="41" ht="409" customHeight="1">
+    <row r="41">
       <c r="A41" s="45" t="inlineStr">
         <is>
           <t>ESPAÇO TERMAS</t>
@@ -10512,25 +11083,29 @@
       </c>
       <c r="B41" s="245" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, acabamento levigado, espessura 3cm, com argamassa colante em pó ACIII</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C41" s="32" t="n"/>
       <c r="D41" s="35" t="n"/>
       <c r="E41" s="37" t="n"/>
-      <c r="F41" s="32" t="n"/>
+      <c r="F41" s="270" t="inlineStr">
+        <is>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
+        </is>
+      </c>
       <c r="G41" s="32" t="n"/>
       <c r="H41" s="245" t="inlineStr">
         <is>
-          <t>Painel: PA49 - Revestimento em Mosaico Bisazza 20x20cm, assentado com argamassa colante em pó ACIII. Fundo: NARCISO Shading Blend - 20x20mm. Desenho personalizado: NEW STERLIZIA Shading Blend - 10x10mm. Rejunte Fillgel Plus - 1101 - cor Bianco Alabastro (para o New Sterlizia a Bisazza recomenda Fillgel Plus - 6601 - cor rosa perla). Fabricante do rejunte: Drylevis
-Pilar: PA49 - Revestimento em Mosaico Bisazza 20x20cm. Fundo: NARCISO Shading Blend - 20x20mm. Rejunte Fillgel Plus - 1101 - cor Bianco Alabastro. Fabricante do rejunte: Drylevis
-PA46 - Revestimento de mármore branco selecionado, espessura 2cm, assentado com argamassa de cimento e areia. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra
-PA48 - Revestimento de mármore branco selecionado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm, assentado com argamassa de cimento e areia</t>
-        </is>
-      </c>
-      <c r="I41" s="245" t="inlineStr">
-        <is>
-          <t>T7 - Forro com resistência à umidade, especificação a ser definida | 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+PA49 - Pilar em concreto rebocados e regularizados revestidos em mosaico de pastilhas, módulos de 32x259cm com pastilhas de 20x20mm, NARCISO Shading BlendDesenho e paginação conforme detalhamento. Argamassa e rejunte recomendados: Filgel plus 1101 bianco alabastro. Ref.:Bisazza. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I41" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
+T7 - Forro com resistência à umidade, especificação a ser definida. Projeto técnico a ser desenvolvido pelo fornecedor e validado pela GPAA&amp;A.</t>
         </is>
       </c>
       <c r="J41" s="35" t="n"/>
@@ -10541,21 +11116,37 @@
       <c r="O41" s="35" t="n"/>
       <c r="P41" s="31" t="n"/>
       <c r="Q41" s="32" t="n"/>
-      <c r="R41" s="35" t="n"/>
+      <c r="R41" s="269" t="inlineStr">
+        <is>
+          <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
+        </is>
+      </c>
       <c r="S41" s="35" t="n"/>
-      <c r="T41" s="35" t="n"/>
+      <c r="T41" s="269" t="inlineStr">
+        <is>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
       <c r="U41" s="246" t="inlineStr">
         <is>
-          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca</t>
-        </is>
-      </c>
-      <c r="V41" s="31" t="n"/>
+          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="V41" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W41" s="35" t="n"/>
-      <c r="X41" s="35" t="n"/>
+      <c r="X41" s="269" t="inlineStr">
+        <is>
+          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y41" s="35" t="n"/>
       <c r="Z41" s="32" t="n"/>
     </row>
-    <row r="42" ht="230" customHeight="1">
+    <row r="42">
       <c r="A42" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">SAUNA VAPOR </t>
@@ -10563,7 +11154,7 @@
       </c>
       <c r="B42" s="245" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, acabamento levigado, espessura 3cm, com argamassa colante em pó ACIII</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C42" s="32" t="n"/>
@@ -10573,12 +11164,12 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="245" t="inlineStr">
         <is>
-          <t>PA46 - Revestimento de mármore branco selecionado, espessura 2cm, assentado com argamassa de cimento e areia</t>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="I42" s="245" t="inlineStr">
         <is>
-          <t>T10 - Revestimento em mámore selecionado</t>
+          <t>T10 - Laje em concreto revestida em mármore selecionado, lote a ser aprovado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="J42" s="35" t="n"/>
@@ -10589,17 +11180,29 @@
       <c r="O42" s="35" t="n"/>
       <c r="P42" s="31" t="n"/>
       <c r="Q42" s="32" t="n"/>
-      <c r="R42" s="35" t="n"/>
+      <c r="R42" s="269" t="inlineStr">
+        <is>
+          <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
+        </is>
+      </c>
       <c r="S42" s="35" t="n"/>
-      <c r="T42" s="35" t="n"/>
-      <c r="U42" s="32" t="n"/>
+      <c r="T42" s="269" t="inlineStr">
+        <is>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
+      <c r="U42" s="270" t="inlineStr">
+        <is>
+          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
       <c r="V42" s="31" t="n"/>
       <c r="W42" s="35" t="n"/>
       <c r="X42" s="35" t="n"/>
       <c r="Y42" s="35" t="n"/>
       <c r="Z42" s="32" t="n"/>
     </row>
-    <row r="43" ht="356" customHeight="1">
+    <row r="43">
       <c r="A43" s="45" t="inlineStr">
         <is>
           <t>SAUNA SECA</t>
@@ -10607,7 +11210,7 @@
       </c>
       <c r="B43" s="245" t="inlineStr">
         <is>
-          <t>P19 - Piso Porcelanato padrão, coberto com piso tipo deck, assentado com argamassa colante em pó ACIII| ***P19 - Piso tipo deck de madeira Cedro, réguas 70mmx25mm comprimento variável</t>
+          <t>P19 - Piso em contrapiso regularizado revestido com porcelanato padrão, coberto com piso tipo deck de madeira Cedro.Reguas 70mmx25mmx comprimento variável e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="C43" s="32" t="n"/>
@@ -10617,12 +11220,12 @@
       <c r="G43" s="32" t="n"/>
       <c r="H43" s="245" t="inlineStr">
         <is>
-          <t>PA50 - Revestimento em madeira 2,5x2,5cm a cada 30-40cm, lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro. Réguas 70mmx25mm comprimento variável</t>
+          <t>PA50 - Parede em alvenaria rebocada e regularizada revestida em conjunto com sarrafos de madeira 2,5x5cm a cada 35-40cm, lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro. Reguas 70mmx25mmx comprimento variável e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="I43" s="245" t="inlineStr">
         <is>
-          <t>T11 - Forro em sarrafo de madeira 2,5x2,5cm a cada 30-40cm lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro</t>
+          <t>T11 - Laje em concreto revestida em  conjunto com sarrafos de madeira 2,5x5cm a cada 35-40cm, lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="J43" s="35" t="n"/>
@@ -10675,7 +11278,7 @@
       <c r="Y44" s="35" t="n"/>
       <c r="Z44" s="32" t="n"/>
     </row>
-    <row r="45" ht="356" customHeight="1">
+    <row r="45">
       <c r="A45" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">MASSAGEM </t>
@@ -10683,7 +11286,7 @@
       </c>
       <c r="B45" s="245" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, acabamento levigado, espessura 3cm, com argamassa colante em pó ACIII</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C45" s="32" t="n"/>
@@ -10691,36 +11294,42 @@
       <c r="E45" s="37" t="n"/>
       <c r="F45" s="246" t="inlineStr">
         <is>
-          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, arremate do topo em perfil "U" em aço inox 10x10mm, assentado com argamassa colante em pó ACIII</t>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G45" s="32" t="n"/>
-      <c r="H45" s="245" t="inlineStr">
-        <is>
-          <t>PA47 - Pintura com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor</t>
-        </is>
-      </c>
-      <c r="I45" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H45" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I45" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J45" s="245" t="inlineStr">
         <is>
-          <t>D59| D60|D61 - Bancada em mármore branco selecionado, acabamento abaulado</t>
+          <t>D59 - Bancada com tampo em mármore branco liso selecionado, lote a ser aprovado, com acabamento abaulado e testeira em mármore com acabamento frisado. Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+D60 - Mureta com tampo em mármore branco selecionado, lote a ser aprovado, com acabamento abaulado e fechamento vertical em mármore com acabamento frisado. Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+D61 - Bancada com tampo em mármore branco liso selecionado, lote a ser aprovado, com acabamento abaulado e laterais em mármore com acabamento frisado. Recorte para encaixe de lavatório, conforme manual técnico de instalação Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K45" s="32" t="n"/>
-      <c r="L45" s="245" t="inlineStr">
-        <is>
-          <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.: 121003002, Ref. Sabbia</t>
+      <c r="L45" s="277" t="inlineStr">
+        <is>
+          <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
+D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="M45" s="37" t="n"/>
       <c r="N45" s="38" t="n"/>
-      <c r="O45" s="245" t="inlineStr">
-        <is>
-          <t>D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Socol</t>
+      <c r="O45" s="277" t="inlineStr">
+        <is>
+          <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
       <c r="P45" s="31" t="n"/>
@@ -10729,17 +11338,21 @@
       <c r="S45" s="35" t="n"/>
       <c r="T45" s="35" t="n"/>
       <c r="U45" s="32" t="n"/>
-      <c r="V45" s="31" t="n"/>
+      <c r="V45" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W45" s="35" t="n"/>
-      <c r="X45" s="245" t="inlineStr">
-        <is>
-          <t>P28 (D43) - Painel e porta estruturados em alumínio com fechamento interno em vidro, cor Prada acabamento acidado. Dimensões conforme detalhamento ref.: Cinex. 271x324cm</t>
+      <c r="X45" s="277" t="inlineStr">
+        <is>
+          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y45" s="35" t="n"/>
       <c r="Z45" s="32" t="n"/>
     </row>
-    <row r="46" ht="356" customHeight="1">
+    <row r="46">
       <c r="A46" s="45" t="inlineStr">
         <is>
           <t>BELEZA</t>
@@ -10747,7 +11360,7 @@
       </c>
       <c r="B46" s="245" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, acabamento levigado, espessura 3cm, com argamassa colante em pó ACIII</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C46" s="32" t="n"/>
@@ -10755,33 +11368,42 @@
       <c r="E46" s="37" t="n"/>
       <c r="F46" s="246" t="inlineStr">
         <is>
-          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, arremate do topo em perfil "U" em aço inox 10x10mm, assentado com argamassa colante em pó ACIII</t>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G46" s="32" t="n"/>
-      <c r="H46" s="245" t="inlineStr">
-        <is>
-          <t>PA26 - Espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado ma alvenaria
-PA47 - Pintura com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor</t>
-        </is>
-      </c>
-      <c r="I46" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H46" s="277" t="inlineStr">
+        <is>
+          <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I46" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J46" s="245" t="inlineStr">
         <is>
-          <t>D59| D60|D61 - Bancada em mármore branco selecionado, acabamento abaulado</t>
+          <t>D59 - Bancada com tampo em mármore branco liso selecionado, lote a ser aprovado, com acabamento abaulado e testeira em mármore com acabamento frisado. Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+D60 - Mureta com tampo em mármore branco selecionado, lote a ser aprovado, com acabamento abaulado e fechamento vertical em mármore com acabamento frisado. Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+D61 - Bancada com tampo em mármore branco liso selecionado, lote a ser aprovado, com acabamento abaulado e laterais em mármore com acabamento frisado. Recorte para encaixe de lavatório, conforme manual técnico de instalação Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K46" s="32" t="n"/>
-      <c r="L46" s="35" t="n"/>
+      <c r="L46" s="269" t="inlineStr">
+        <is>
+          <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
+D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="M46" s="37" t="n"/>
       <c r="N46" s="38" t="n"/>
-      <c r="O46" s="245" t="inlineStr">
-        <is>
-          <t>D51 - Torneira de mesa, linha Mix@Match Presence, cor sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Socol</t>
+      <c r="O46" s="277" t="inlineStr">
+        <is>
+          <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
       <c r="P46" s="31" t="n"/>
@@ -10790,26 +11412,51 @@
       <c r="S46" s="35" t="n"/>
       <c r="T46" s="35" t="n"/>
       <c r="U46" s="32" t="n"/>
-      <c r="V46" s="31" t="n"/>
+      <c r="V46" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W46" s="35" t="n"/>
-      <c r="X46" s="35" t="n"/>
+      <c r="X46" s="269" t="inlineStr">
+        <is>
+          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y46" s="35" t="n"/>
       <c r="Z46" s="32" t="n"/>
     </row>
-    <row r="47" ht="125.25" customHeight="1">
+    <row r="47">
       <c r="A47" s="45" t="inlineStr">
         <is>
           <t>HALL VESTIÁRIOS</t>
         </is>
       </c>
-      <c r="B47" s="35" t="n"/>
+      <c r="B47" s="269" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="C47" s="32" t="n"/>
       <c r="D47" s="35" t="n"/>
       <c r="E47" s="37" t="n"/>
-      <c r="F47" s="32" t="n"/>
+      <c r="F47" s="270" t="inlineStr">
+        <is>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
+        </is>
+      </c>
       <c r="G47" s="32" t="n"/>
-      <c r="H47" s="35" t="n"/>
-      <c r="I47" s="35" t="n"/>
+      <c r="H47" s="269" t="inlineStr">
+        <is>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I47" s="269" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J47" s="35" t="n"/>
       <c r="K47" s="32" t="n"/>
       <c r="L47" s="35" t="n"/>
@@ -10824,116 +11471,253 @@
       <c r="U47" s="32" t="n"/>
       <c r="V47" s="31" t="n"/>
       <c r="W47" s="35" t="n"/>
-      <c r="X47" s="35" t="n"/>
+      <c r="X47" s="269" t="inlineStr">
+        <is>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y47" s="35" t="n"/>
       <c r="Z47" s="32" t="n"/>
     </row>
-    <row r="48" ht="125.25" customHeight="1">
+    <row r="48">
       <c r="A48" s="45" t="inlineStr">
         <is>
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n"/>
+      <c r="B48" s="269" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="C48" s="32" t="n"/>
       <c r="D48" s="35" t="n"/>
       <c r="E48" s="37" t="n"/>
-      <c r="F48" s="32" t="n"/>
+      <c r="F48" s="270" t="inlineStr">
+        <is>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
+        </is>
+      </c>
       <c r="G48" s="32" t="n"/>
-      <c r="H48" s="35" t="n"/>
-      <c r="I48" s="35" t="n"/>
-      <c r="J48" s="35" t="n"/>
-      <c r="K48" s="32" t="n"/>
-      <c r="L48" s="35" t="n"/>
+      <c r="H48" s="269" t="inlineStr">
+        <is>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I48" s="269" t="inlineStr">
+        <is>
+          <t>T8 - Forro em gesso acartonado liso hidrofugante, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J48" s="269" t="inlineStr">
+        <is>
+          <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="K48" s="270" t="inlineStr">
+        <is>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+      <c r="L48" s="269" t="inlineStr">
+        <is>
+          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
+        </is>
+      </c>
       <c r="M48" s="37" t="n"/>
       <c r="N48" s="38" t="n"/>
-      <c r="O48" s="35" t="n"/>
-      <c r="P48" s="31" t="n"/>
-      <c r="Q48" s="32" t="n"/>
+      <c r="O48" s="269" t="inlineStr">
+        <is>
+          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
+        </is>
+      </c>
+      <c r="P48" s="269" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="Q48" s="270" t="inlineStr">
+        <is>
+          <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
+        </is>
+      </c>
       <c r="R48" s="35" t="n"/>
-      <c r="S48" s="35" t="n"/>
-      <c r="T48" s="35" t="n"/>
-      <c r="U48" s="32" t="n"/>
-      <c r="V48" s="31" t="n"/>
+      <c r="S48" s="269" t="inlineStr">
+        <is>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+        </is>
+      </c>
+      <c r="T48" s="269" t="inlineStr">
+        <is>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
+      <c r="U48" s="270" t="inlineStr">
+        <is>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="V48" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W48" s="35" t="n"/>
-      <c r="X48" s="35" t="n"/>
+      <c r="X48" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
+        </is>
+      </c>
       <c r="Y48" s="35" t="n"/>
-      <c r="Z48" s="32" t="n"/>
-    </row>
-    <row r="49" ht="125.25" customHeight="1">
+      <c r="Z48" s="270" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="45" t="inlineStr">
         <is>
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n"/>
+      <c r="B49" s="269" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="C49" s="32" t="n"/>
       <c r="D49" s="35" t="n"/>
       <c r="E49" s="37" t="n"/>
-      <c r="F49" s="32" t="n"/>
+      <c r="F49" s="270" t="inlineStr">
+        <is>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
+        </is>
+      </c>
       <c r="G49" s="32" t="n"/>
-      <c r="H49" s="35" t="n"/>
-      <c r="I49" s="35" t="n"/>
-      <c r="J49" s="35" t="n"/>
-      <c r="K49" s="32" t="n"/>
-      <c r="L49" s="35" t="n"/>
+      <c r="H49" s="269" t="inlineStr">
+        <is>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I49" s="269" t="inlineStr">
+        <is>
+          <t>T8 - Forro em gesso acartonado liso hidrofugante, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J49" s="269" t="inlineStr">
+        <is>
+          <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="K49" s="270" t="inlineStr">
+        <is>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+      <c r="L49" s="269" t="inlineStr">
+        <is>
+          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
+        </is>
+      </c>
       <c r="M49" s="37" t="n"/>
       <c r="N49" s="38" t="n"/>
-      <c r="O49" s="35" t="n"/>
-      <c r="P49" s="31" t="n"/>
-      <c r="Q49" s="32" t="n"/>
+      <c r="O49" s="269" t="inlineStr">
+        <is>
+          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
+        </is>
+      </c>
+      <c r="P49" s="269" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="Q49" s="270" t="inlineStr">
+        <is>
+          <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
+        </is>
+      </c>
       <c r="R49" s="35" t="n"/>
-      <c r="S49" s="35" t="n"/>
-      <c r="T49" s="35" t="n"/>
-      <c r="U49" s="32" t="n"/>
-      <c r="V49" s="31" t="n"/>
+      <c r="S49" s="269" t="inlineStr">
+        <is>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+        </is>
+      </c>
+      <c r="T49" s="269" t="inlineStr">
+        <is>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
+      <c r="U49" s="270" t="inlineStr">
+        <is>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="V49" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W49" s="35" t="n"/>
-      <c r="X49" s="35" t="n"/>
+      <c r="X49" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
+        </is>
+      </c>
       <c r="Y49" s="35" t="n"/>
-      <c r="Z49" s="32" t="n"/>
-    </row>
-    <row r="50" ht="335" customHeight="1">
+      <c r="Z49" s="270" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="45" t="inlineStr">
         <is>
           <t>DML</t>
         </is>
       </c>
-      <c r="B50" s="245" t="inlineStr">
-        <is>
-          <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B50" s="277" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C50" s="32" t="n"/>
       <c r="D50" s="35" t="n"/>
       <c r="E50" s="37" t="n"/>
-      <c r="F50" s="246" t="inlineStr">
-        <is>
-          <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="F50" s="278" t="inlineStr">
+        <is>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G50" s="32" t="n"/>
       <c r="H50" s="245" t="inlineStr">
         <is>
-          <t>PA47 - Pintura com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor</t>
-        </is>
-      </c>
-      <c r="I50" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I50" s="277" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J50" s="35" t="n"/>
       <c r="K50" s="32" t="n"/>
       <c r="L50" s="245" t="inlineStr">
         <is>
-          <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.: TQ.01.17, Ref.: Deca</t>
+          <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.TQ.01.17.; Ref.: Deca.</t>
         </is>
       </c>
       <c r="M50" s="37" t="n"/>
       <c r="N50" s="38" t="n"/>
       <c r="O50" s="245" t="inlineStr">
         <is>
-          <t>D67 - Torneira de parede com arejador, para jardim e tanque, linha Izy, acabamento cromado. Cód.: 1154 C37; Ref.: Deca</t>
+          <t>D67 - Torneira de parede com arejador, para Jardim e Tanque, linha Izy, acabamento cromado. Cód. 1154.C37; Ref.: Deca.</t>
         </is>
       </c>
       <c r="P50" s="31" t="n"/>
@@ -11150,7 +11934,7 @@
       <c r="Y54" s="35" t="n"/>
       <c r="Z54" s="32" t="n"/>
     </row>
-    <row r="55" ht="398" customHeight="1">
+    <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
           <t>VESTIÁRIO FEM./MASC. - TERMAS</t>
@@ -11158,74 +11942,93 @@
       </c>
       <c r="B55" s="245" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, acabamento levigado, espessura 3cm, com argamassa colante em pó ACIII</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C55" s="32" t="n"/>
       <c r="D55" s="35" t="n"/>
       <c r="E55" s="37" t="n"/>
-      <c r="F55" s="246" t="n"/>
+      <c r="F55" s="278" t="inlineStr">
+        <is>
+          <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
+        </is>
+      </c>
       <c r="G55" s="32" t="n"/>
-      <c r="H55" s="245" t="inlineStr">
-        <is>
-          <t>PA46 - Revestimento de mármore branco selecionado, espessura 2cm, assentado com argamassa de cimento e areia
-PA47 - Pintura com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor</t>
-        </is>
-      </c>
-      <c r="I55" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H55" s="277" t="inlineStr">
+        <is>
+          <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A
+PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I55" s="277" t="inlineStr">
+        <is>
+          <t>T8 - Forro em gesso acartonado liso hidrofugante, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J55" s="245" t="inlineStr">
         <is>
-          <t>D73 - Bancada em pedra natural, mármore branco selecionado, acabamento levigado, espessura 2cm</t>
+          <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K55" s="246" t="inlineStr">
         <is>
-          <t>D38 - Espelho liso incolor polimento cristal 4mm colado sobre armário em MDF cru 6mm aparafusado na alvenaria</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L55" s="245" t="inlineStr">
         <is>
-          <t>D72 - Cuba de semi-encaixe, linha slim, cor branco, có.: L.61040.M.17. Ref.: Deca</t>
+          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
         </is>
       </c>
       <c r="M55" s="37" t="n"/>
       <c r="N55" s="38" t="n"/>
       <c r="O55" s="245" t="inlineStr">
         <is>
-          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N Ref.: Deca</t>
-        </is>
-      </c>
-      <c r="P55" s="245" t="inlineStr">
-        <is>
-          <t>D22 - Bacia sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P606.17. Ref.: Deca ou Bacia sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0</t>
+          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
+        </is>
+      </c>
+      <c r="P55" s="277" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Q55" s="32" t="n"/>
       <c r="R55" s="35" t="n"/>
       <c r="S55" s="245" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.: 90009312006. Ref.: Docol</t>
-        </is>
-      </c>
-      <c r="T55" s="35" t="n"/>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+        </is>
+      </c>
+      <c r="T55" s="269" t="inlineStr">
+        <is>
+          <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+        </is>
+      </c>
       <c r="U55" s="246" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha Docol Eden, acabamento cromado, cód.: 90008879006 Ref.: Docol.</t>
-        </is>
-      </c>
-      <c r="V55" s="31" t="n"/>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="V55" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W55" s="35" t="n"/>
-      <c r="X55" s="35" t="n"/>
+      <c r="X55" s="269" t="inlineStr">
+        <is>
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="Y55" s="35" t="n"/>
-      <c r="Z55" s="246" t="inlineStr">
-        <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press espuma, cód.: 70.032. Ref.: Draco
-D27 - Porta papel higiênico duplo em aço inox, modelo cai cai, cód.: 70.100. Ref.: Draco
-D28 - Papeleira em aço inox para papel interfolhado, modelo Basic, cód.: 74.103 ref.: Draco</t>
+      <c r="Z55" s="278" t="inlineStr">
+        <is>
+          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
     </row>
@@ -11321,38 +12124,46 @@
       <c r="Y57" s="35" t="n"/>
       <c r="Z57" s="32" t="n"/>
     </row>
-    <row r="58" ht="335" customHeight="1">
+    <row r="58">
       <c r="A58" s="45" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO</t>
         </is>
       </c>
-      <c r="B58" s="245" t="inlineStr">
-        <is>
-          <t>07 - Piso de granito cinza santa rosa, acabamento serrado, espessura: 2cm, dimensões e paginação conforme detalhamento, assentado com argamassa colante em pó ACIII. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B58" s="277" t="inlineStr">
+        <is>
+          <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
+P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C58" s="32" t="n"/>
       <c r="D58" s="35" t="n"/>
       <c r="E58" s="37" t="n"/>
-      <c r="F58" s="246" t="inlineStr">
-        <is>
-          <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII</t>
+      <c r="F58" s="278" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G58" s="32" t="n"/>
-      <c r="H58" s="245" t="inlineStr">
-        <is>
-          <t>01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
-        </is>
-      </c>
-      <c r="I58" s="245" t="inlineStr">
-        <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+      <c r="H58" s="277" t="inlineStr">
+        <is>
+          <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
+PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+PA58 - Pilar em concreto, com enchimento, revestido em pedra natural Basaltina conforme detalhamento.Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="I58" s="277" t="inlineStr">
+        <is>
+          <t>FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
+T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J58" s="245" t="n"/>
-      <c r="K58" s="246" t="n"/>
+      <c r="K58" s="278" t="inlineStr">
+        <is>
+          <t>D75 - Fechamento decorativo piso teto com quadro fixado no piso e no teto através de espaçadores e fechamento com desenho conforme base para corte de molde em CNC - peças em madeira maciça engenheirada, tonalizada,acabamento escovado, calandradas conforme molde. Ref.: Demuner. ATENÇÃO:a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
       <c r="L58" s="245" t="n"/>
       <c r="M58" s="37" t="n"/>
       <c r="N58" s="38" t="n"/>
@@ -11363,21 +12174,26 @@
       <c r="S58" s="35" t="n"/>
       <c r="T58" s="35" t="n"/>
       <c r="U58" s="32" t="n"/>
-      <c r="V58" s="31" t="n"/>
+      <c r="V58" s="269" t="inlineStr">
+        <is>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+        </is>
+      </c>
       <c r="W58" s="35" t="n"/>
       <c r="X58" s="35" t="n"/>
       <c r="Y58" s="35" t="n"/>
       <c r="Z58" s="32" t="n"/>
     </row>
-    <row r="59" ht="209" customHeight="1">
+    <row r="59">
       <c r="A59" s="45" t="inlineStr">
         <is>
           <t>ESTAR PISCINA / CIRCULAÇÃO</t>
         </is>
       </c>
-      <c r="B59" s="245" t="inlineStr">
-        <is>
-          <t>07| P28 - Piso de granito Santa rosa, acabamento serrado. Espessura de 2cm. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+      <c r="B59" s="277" t="inlineStr">
+        <is>
+          <t>P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
+P8 - Piso elevado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofulgante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C59" s="32" t="n"/>
@@ -11399,7 +12215,7 @@
       <c r="S59" s="35" t="n"/>
       <c r="T59" s="245" t="inlineStr">
         <is>
-          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref. Elleve</t>
+          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
       <c r="U59" s="32" t="n"/>
@@ -11407,7 +12223,11 @@
       <c r="W59" s="35" t="n"/>
       <c r="X59" s="35" t="n"/>
       <c r="Y59" s="35" t="n"/>
-      <c r="Z59" s="32" t="n"/>
+      <c r="Z59" s="270" t="inlineStr">
+        <is>
+          <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="125.25" customHeight="1">
       <c r="A60" s="45" t="inlineStr">
@@ -11521,15 +12341,16 @@
       <c r="Y62" s="35" t="n"/>
       <c r="Z62" s="32" t="n"/>
     </row>
-    <row r="63" ht="125.25" customHeight="1">
+    <row r="63">
       <c r="A63" s="45" t="inlineStr">
         <is>
           <t>APOIO QUADRAS</t>
         </is>
       </c>
-      <c r="B63" s="245" t="inlineStr">
-        <is>
-          <t>P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e fêmea, acabamento com cavilha, réguas 200mmx100mmx2000m-acima. Ref.: Indusparquet.</t>
+      <c r="B63" s="277" t="inlineStr">
+        <is>
+          <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
+P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="C63" s="32" t="n"/>
@@ -11538,7 +12359,12 @@
       <c r="F63" s="246" t="n"/>
       <c r="G63" s="32" t="n"/>
       <c r="H63" s="245" t="n"/>
-      <c r="I63" s="245" t="n"/>
+      <c r="I63" s="277" t="inlineStr">
+        <is>
+          <t>FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
+T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J63" s="245" t="n"/>
       <c r="K63" s="246" t="n"/>
       <c r="L63" s="245" t="n"/>
@@ -12551,7 +13377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13960,6 +14786,5767 @@
       </c>
       <c r="E86" s="268" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" s="279" t="inlineStr">
+        <is>
+          <t>3. LEVANTAMENTO PELOS PROJETOS DE DETALHAMENTO R04 (23/04/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="280" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B89" s="280" t="inlineStr">
+        <is>
+          <t>PAVIMENTO / AMBIENTE</t>
+        </is>
+      </c>
+      <c r="C89" s="280" t="inlineStr">
+        <is>
+          <t>COLUNA</t>
+        </is>
+      </c>
+      <c r="D89" s="280" t="inlineStr">
+        <is>
+          <t>ANTES (v00)</t>
+        </is>
+      </c>
+      <c r="E89" s="280" t="inlineStr">
+        <is>
+          <t>AGORA (R04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PILOTIS – LOBBY PILOTIS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PILOTIS – LOBBY PILOTIS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PA44, PA53</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PA44, PA53, PA58</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PILOTIS – LOBBY PILOTIS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>FO2, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PILOTIS – LOBBY PILOTIS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PILOTIS – LOBBY PILOTIS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>D19, D39, D74, D85</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>6</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PILOTIS – SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>7</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PILOTIS – SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>FO1, FO2, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>8</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PILOTIS – SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PILOTIS – SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>D21, D83</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>10</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S FEMININO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>11</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S FEMININO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>12</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S FEMININO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>13</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S FEMININO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>14</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S FEMININO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>D27, D83</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>15</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S FEMININO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>16</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S MASCULINO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>17</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S MASCULINO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>18</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S MASCULINO</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>19</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S MASCULINO</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>20</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S MASCULINO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>D27, D83</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>21</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S MASCULINO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>22</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PILOTIS – COZINHA SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>23</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PILOTIS – COZINHA SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>24</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PILOTIS – COZINHA SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>25</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PILOTIS – COZINHA SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>D21, D74</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>26</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PILOTIS – COZINHA SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>D82</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>27</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PA32, PA52</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PA26, PA32, PA52</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>28</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>29</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>30</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>31</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>D19, D27</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>32</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>33</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>PA32, PA52</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PA26, PA32, PA52</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>34</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>35</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>36</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>37</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>D19, D27</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>38</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PILOTIS – I.S</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>39</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO KIDS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>P24, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>40</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO KIDS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>FO1, FO2, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>41</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO KIDS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>42</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO KIDS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>D11, D39</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>43</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO KIDS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>D18, D56</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>44</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO GOURMET</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>45</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO GOURMET</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PA32, PA44</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PA32, PA33, PA44</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>46</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO GOURMET</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>FO1, FO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>47</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO GOURMET</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>48</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO GOURMET</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>D11, D83</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>49</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO GOURMET</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>D13, D14, D15, D16, D17</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>50</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA DECOBERTA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>P18, P28</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>51</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA DECOBERTA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PA59</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>52</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA DECOBERTA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>53</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA DECOBERTA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>OUTROS  LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>D79</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>54</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA DECOBERTA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>D77</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>55</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA DECOBERTA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>D76</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>56</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>57</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>58</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PA42, PA51</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>59</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>T1, T4</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>60</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>61</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LOUÇAS, CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>62</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>63</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>D34, D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>64</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>65</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PILOTIS – BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>D47, D48, D49, D50</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>66</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>67</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>PA52</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>68</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>69</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>70</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>71</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>72</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PA46, PA52</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PA26, PA52, PA60</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>73</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>74</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>D73</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>75</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>76</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>77</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>D27, D32</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>78</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>79</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>80</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>81</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PA46, PA52</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>PA26, PA52, PA60</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>82</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>83</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>D73</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>84</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>85</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>86</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>D27, D32</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>87</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>88</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PILOTIS – ACADEMIA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PA22</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>P22, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>89</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PILOTIS – ACADEMIA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PA26, PA27, PA28</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>PA26, PA27, PA28, PA29, PA30</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>90</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PILOTIS – ACADEMIA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>FO1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>FO2, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>91</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PILOTIS – ACADEMIA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>92</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PILOTIS – ACADEMIA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>93</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PILOTIS – ACADEMIA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>D3, D4, D5, D6, D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>94</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA RAIA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>95</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PILOTIS – PISCINA RAIA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>PA46</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>96</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PILOTIS – SPA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>PA46</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>97</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO TERMAS</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>PA23</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>98</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO TERMAS</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>T1, T7</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>99</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO TERMAS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS DE REGISTROS GERAL</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>D58</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>100</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO TERMAS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>101</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO TERMAS</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>102</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESPAÇO TERMAS</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>D43</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>103</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PILOTIS – SAUNA VAPOR</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS DE REGISTROS GERAL</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>D58</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>104</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PILOTIS – SAUNA VAPOR</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>105</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PILOTIS – SAUNA VAPOR</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>OUTROS  LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>106</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PILOTIS – MASSAGEM</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PA47</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>PA26, PA46, PA47</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>107</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>PILOTIS – MASSAGEM</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>108</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PILOTIS – MASSAGEM</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>LOUÇAS, CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>D55</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>D55, D62</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>109</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PILOTIS – MASSAGEM</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>D51, D53</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>110</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PILOTIS – MASSAGEM</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>111</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PILOTIS – MASSAGEM</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>D43, P28</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>D43</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>112</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PILOTIS – BELEZA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PA26, PA47</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>PA26, PA46, PA47</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>113</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PILOTIS – BELEZA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>114</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PILOTIS – BELEZA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>LOUÇAS, CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>D55, D62</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>115</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PILOTIS – BELEZA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>D51, D53</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>116</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PILOTIS – BELEZA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>117</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PILOTIS – BELEZA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>D43</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>118</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>PILOTIS – HALL VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>119</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>PILOTIS – HALL VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>PA23</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>120</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>PILOTIS – HALL VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>PA46, PA48</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>121</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PILOTIS – HALL VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>122</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PILOTIS – HALL VESTIÁRIOS</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>D39, D43</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>123</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>124</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>PA23</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>125</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>PA46, PA47</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>126</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>127</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>D73</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>128</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>OUTROS REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>D38</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>129</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>LOUÇAS, CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>130</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>131</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>132</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>DUCHAS HIGIÊNICAS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>133</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ACIONAMENTO DE CHUVEIRO</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>D33</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>134</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>135</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>OUTROS  LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>D70</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>136</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>137</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>D27</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>138</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>139</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>140</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>PA23</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>141</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>PA46, PA47</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>142</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>143</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>D73</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>144</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>OUTROS REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>D38</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>145</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>LOUÇAS, CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>146</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>147</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>148</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>DUCHAS HIGIÊNICAS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>149</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ACIONAMENTO DE CHUVEIRO</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>D33</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>150</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>151</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>OUTROS  LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>D70</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>152</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>153</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>D27</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>154</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>PILOTIS – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>155</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>PILOTIS – DML</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>156</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>PILOTIS – DML</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>PA23</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>157</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>PILOTIS – DML</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>158</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>PA23</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>159</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>PA46, PA47</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>PA46, PA47, PA48</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>160</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>161</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>D22, P606</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>162</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>D34, D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>163</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>164</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>D27, D39, D43</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>165</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>PILOTIS – VESTIÁRIO FEM./MASC. - TERMAS</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>D26, D27, D28</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>166</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>P7, PI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>167</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>168</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>PA44, PA53, PA58</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>169</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>T1, T8</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>FO2, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>170</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>OUTROS REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>171</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>172</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESTAR PISCINA / CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>P28, P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>173</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESTAR PISCINA / CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>D76</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>174</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>PILOTIS – APOIO QUADRAS</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>P27, P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>175</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>PILOTIS – APOIO QUADRAS</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>FO2, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>176</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>TÉRREO – ANTECÂMARA(ECLUSA PEDESTRE)</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>177</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TÉRREO – ANTECÂMARA(ECLUSA PEDESTRE)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>178</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TÉRREO – ANTECÂMARA(ECLUSA PEDESTRE)</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>PA56</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>179</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TÉRREO – ANTECÂMARA(ECLUSA PEDESTRE)</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>180</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TÉRREO – ANTECÂMARA(ECLUSA PEDESTRE)</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>181</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>TÉRREO – ANTECÂMARA(ECLUSA PEDESTRE)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>D41, D42</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>182</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>183</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>184</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>PA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>185</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>186</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>187</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>188</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>189</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>PA1, PA53, PA54, PA56</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>190</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>T1, T12</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>191</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>192</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>D41, D42</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>193</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>TÉRREO – LOBBY ENTRADA</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>D63</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>194</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL ELEVADORES</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>195</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL ELEVADORES</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>196</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL ELEVADORES</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>PA1, PA53, PA54</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>197</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL ELEVADORES</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>198</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL ELEVADORES</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>199</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL ELEVADORES</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>D64</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>200</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>201</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>202</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>PA1, PA53</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>203</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>204</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>205</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>D44, D45</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>206</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>TÉRREO – HALL GARGEM</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>D64</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>207</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>208</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>209</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>PA26, PA53</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>210</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>211</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>212</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>OUTROS REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>D37</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>213</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>D66</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>214</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>215</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>216</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>217</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>D27, D39</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>218</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>TÉRREO – I.S P.C.D</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>OUTROS COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>D26, D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>219</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>TÉRREO – VESTÍBULO</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>220</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>TÉRREO – VESTÍBULO</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>PA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>221</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>TÉRREO – VESTÍBULO</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>PA53, PA55</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>222</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>TÉRREO – VESTÍBULO</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>223</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>TÉRREO – VESTÍBULO</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>224</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>TÉRREO – VESTÍBULO</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>D39, D42</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="279" t="inlineStr">
+        <is>
+          <t>4. OBSERVAÇÕES DO LEVANTAMENTO R04</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>MASSAGEM</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Massagem e Beleza estão juntas na lista R04 e nas pranchas 05 e 06; louças e bancadas listadas nos dois ambientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>BELEZA</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Massagem e Beleza estão juntas na lista R04 e nas pranchas 05 e 06; louças e bancadas listadas nos dois ambientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Vestiários P.C.D. das Termas não têm ampliação própria; itens seguem os vestiários e o DML das Termas (pranchas 10 e 11) e a ducha higiênica D84.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PISCINA RAIA</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Pranchas 01 e 04 indicam piscina revestida em pedra (mármore) com bordas abauladas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO FEMININO / MASCULINO</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Pranchas 37 e 38 citam torneira Argon (Docol) e bancada em granito Branco Siena; a lista R04 traz D29 (Decalux, Deca) e D36 (granito cinza Santa Rosa). Confirmar com a arquitetura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>BAR PISCINA</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Prancha 35 é imagem sem texto; não foi possível conferir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SALÃO DE FESTAS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Prancha 20 é imagem sem texto; divisão conferida nas pranchas 21 a 24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>TÉRREO</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>A lista R04 agrupa antecâmara, guarita, lobby, vestíbulo, I.S., hall de elevadores e hall da garagem; a divisão por ambiente foi feita pelas pranchas 40 a 42.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>GOURMET EXTERNO / VARANDA / GUARITA PILOTIS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Grupos da lista R04 com códigos sem descrição (#N/D); não entraram na grade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2º PAVIMENTO</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>A lista R04 só traz mobiliário do 2º pavimento; aba continua sem especificação de acabamentos.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="59">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -376,8 +376,19 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF9C0006"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -429,6 +440,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF243F2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1344,7 +1360,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2098,6 +2114,13 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6028,8 +6051,12 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
-      <c r="J9" s="193" t="n"/>
-      <c r="K9" s="193" t="n"/>
+      <c r="J9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="K9" s="229" t="n"/>
       <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
@@ -6038,8 +6065,12 @@
       <c r="Q9" s="10" t="n"/>
       <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="n"/>
-      <c r="T9" s="10" t="n"/>
-      <c r="U9" s="10" t="n"/>
+      <c r="T9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="U9" s="229" t="n"/>
       <c r="V9" s="10" t="n"/>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="10" t="n"/>
@@ -6049,8 +6080,12 @@
       <c r="AB9" s="10" t="n"/>
       <c r="AC9" s="10" t="n"/>
       <c r="AD9" s="10" t="n"/>
-      <c r="AE9" s="10" t="n"/>
-      <c r="AF9" s="10" t="n"/>
+      <c r="AE9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="AF9" s="229" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -6951,14 +6986,14 @@
       <c r="W28" s="35" t="n"/>
       <c r="X28" s="269" t="inlineStr">
         <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
-D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y28" s="31" t="n"/>
       <c r="Z28" s="269" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -7643,7 +7678,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="31">
     <mergeCell ref="L10:U10"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="T5:U5"/>
@@ -7651,12 +7686,14 @@
     <mergeCell ref="AE1:AF4"/>
     <mergeCell ref="T1:U4"/>
     <mergeCell ref="A1:A4"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L1:S4"/>
     <mergeCell ref="V10:Z10"/>
     <mergeCell ref="V5:AD6"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="B5:I6"/>
+    <mergeCell ref="T9:U9"/>
     <mergeCell ref="AE8:AF8"/>
     <mergeCell ref="B7:I8"/>
     <mergeCell ref="V1:AD4"/>
@@ -7664,6 +7701,7 @@
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="L7:S8"/>
     <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="J1:K4"/>
@@ -8064,8 +8102,12 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
-      <c r="J9" s="193" t="n"/>
-      <c r="K9" s="193" t="n"/>
+      <c r="J9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="K9" s="229" t="n"/>
       <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
@@ -8074,8 +8116,12 @@
       <c r="Q9" s="10" t="n"/>
       <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="n"/>
-      <c r="T9" s="10" t="n"/>
-      <c r="U9" s="10" t="n"/>
+      <c r="T9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="U9" s="229" t="n"/>
       <c r="V9" s="10" t="n"/>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="10" t="n"/>
@@ -8085,8 +8131,12 @@
       <c r="AB9" s="10" t="n"/>
       <c r="AC9" s="10" t="n"/>
       <c r="AD9" s="10" t="n"/>
-      <c r="AE9" s="10" t="n"/>
-      <c r="AF9" s="10" t="n"/>
+      <c r="AE9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="AF9" s="229" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -8823,7 +8873,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="31">
     <mergeCell ref="L10:U10"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="T5:U5"/>
@@ -8831,12 +8881,14 @@
     <mergeCell ref="AE1:AF4"/>
     <mergeCell ref="T1:U4"/>
     <mergeCell ref="A1:A4"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L1:S4"/>
     <mergeCell ref="V10:Z10"/>
     <mergeCell ref="V5:AD6"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="B5:I6"/>
+    <mergeCell ref="T9:U9"/>
     <mergeCell ref="AE8:AF8"/>
     <mergeCell ref="B7:I8"/>
     <mergeCell ref="V1:AD4"/>
@@ -8844,6 +8896,7 @@
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="L7:S8"/>
     <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="J1:K4"/>
@@ -9254,8 +9307,12 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
-      <c r="J9" s="193" t="n"/>
-      <c r="K9" s="193" t="n"/>
+      <c r="J9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="K9" s="229" t="n"/>
       <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
@@ -9264,8 +9321,12 @@
       <c r="Q9" s="10" t="n"/>
       <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="n"/>
-      <c r="T9" s="10" t="n"/>
-      <c r="U9" s="10" t="n"/>
+      <c r="T9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="U9" s="229" t="n"/>
       <c r="V9" s="10" t="n"/>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="10" t="n"/>
@@ -9275,8 +9336,12 @@
       <c r="AB9" s="10" t="n"/>
       <c r="AC9" s="10" t="n"/>
       <c r="AD9" s="10" t="n"/>
-      <c r="AE9" s="10" t="n"/>
-      <c r="AF9" s="10" t="n"/>
+      <c r="AE9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="AF9" s="229" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -9756,14 +9821,14 @@
       <c r="W17" s="32" t="n"/>
       <c r="X17" s="269" t="inlineStr">
         <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
-D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+          <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y17" s="31" t="n"/>
       <c r="Z17" s="278" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -9835,14 +9900,14 @@
       <c r="W18" s="32" t="n"/>
       <c r="X18" s="269" t="inlineStr">
         <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
-D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+          <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y18" s="31" t="n"/>
       <c r="Z18" s="278" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -10110,14 +10175,14 @@
       <c r="W23" s="35" t="n"/>
       <c r="X23" s="269" t="inlineStr">
         <is>
-          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
-D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
+          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y23" s="31" t="n"/>
       <c r="Z23" s="277" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -10190,14 +10255,14 @@
       <c r="W24" s="35" t="n"/>
       <c r="X24" s="269" t="inlineStr">
         <is>
-          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
-D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
+          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y24" s="35" t="n"/>
       <c r="Z24" s="277" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -10739,9 +10804,10 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J35" s="277" t="inlineStr">
-        <is>
-          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+      <c r="J35" s="283" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
         </is>
       </c>
       <c r="K35" s="246" t="inlineStr">
@@ -10752,9 +10818,10 @@
       <c r="L35" s="35" t="n"/>
       <c r="M35" s="37" t="n"/>
       <c r="N35" s="38" t="n"/>
-      <c r="O35" s="245" t="inlineStr">
-        <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+      <c r="O35" s="283" t="inlineStr">
+        <is>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
       <c r="P35" s="277" t="inlineStr">
@@ -10788,14 +10855,14 @@
       <c r="W35" s="35" t="n"/>
       <c r="X35" s="269" t="inlineStr">
         <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
-D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
+          <t>D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
         </is>
       </c>
       <c r="Y35" s="35" t="n"/>
       <c r="Z35" s="278" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -10832,9 +10899,10 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J36" s="277" t="inlineStr">
-        <is>
-          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+      <c r="J36" s="283" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
         </is>
       </c>
       <c r="K36" s="246" t="inlineStr">
@@ -10845,9 +10913,10 @@
       <c r="L36" s="35" t="n"/>
       <c r="M36" s="37" t="n"/>
       <c r="N36" s="38" t="n"/>
-      <c r="O36" s="245" t="inlineStr">
-        <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+      <c r="O36" s="283" t="inlineStr">
+        <is>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
       <c r="P36" s="277" t="inlineStr">
@@ -10881,14 +10950,14 @@
       <c r="W36" s="35" t="n"/>
       <c r="X36" s="269" t="inlineStr">
         <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
-D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
+          <t>D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
         </is>
       </c>
       <c r="Y36" s="35" t="n"/>
       <c r="Z36" s="278" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -11565,15 +11634,12 @@
         </is>
       </c>
       <c r="W48" s="35" t="n"/>
-      <c r="X48" s="269" t="inlineStr">
-        <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
-        </is>
-      </c>
+      <c r="X48" s="269" t="n"/>
       <c r="Y48" s="35" t="n"/>
       <c r="Z48" s="270" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -11663,15 +11729,12 @@
         </is>
       </c>
       <c r="W49" s="35" t="n"/>
-      <c r="X49" s="269" t="inlineStr">
-        <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco</t>
-        </is>
-      </c>
+      <c r="X49" s="269" t="n"/>
       <c r="Y49" s="35" t="n"/>
       <c r="Z49" s="270" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -12019,15 +12082,15 @@
       <c r="W55" s="35" t="n"/>
       <c r="X55" s="269" t="inlineStr">
         <is>
-          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
-D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
 D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y55" s="35" t="n"/>
       <c r="Z55" s="278" t="inlineStr">
         <is>
-          <t>D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
+          <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
+D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
@@ -12385,7 +12448,7 @@
     </row>
     <row r="64" ht="2.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="31">
     <mergeCell ref="L10:U10"/>
     <mergeCell ref="B10:K10"/>
     <mergeCell ref="J5:K5"/>
@@ -12394,11 +12457,13 @@
     <mergeCell ref="AE1:AF4"/>
     <mergeCell ref="T1:U4"/>
     <mergeCell ref="A1:A4"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L1:S4"/>
     <mergeCell ref="V10:Z10"/>
     <mergeCell ref="V5:AD6"/>
     <mergeCell ref="B5:I6"/>
+    <mergeCell ref="T9:U9"/>
     <mergeCell ref="AE8:AF8"/>
     <mergeCell ref="B7:I8"/>
     <mergeCell ref="V1:AD4"/>
@@ -12406,6 +12471,7 @@
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="L7:S8"/>
     <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="J1:K4"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="AE6:AF6"/>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -386,6 +386,13 @@
       <name val="Aptos Narrow"/>
       <color rgb="FF9C0006"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1360,7 +1367,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="288">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2121,6 +2128,16 @@
     <xf numFmtId="0" fontId="58" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="59" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="57" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="38" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6460,9 +6477,10 @@
           <t xml:space="preserve">GUARITA </t>
         </is>
       </c>
-      <c r="B17" s="269" t="inlineStr">
-        <is>
-          <t>P5 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Rejunte Infinity Hard cor Mocha ou cor Branco Pérola Deverá ser testado as duas opções de rejunte para escolher a que mais se aproxima do tom da peça. Amostra a ser aprovada pela GPA&amp;A.</t>
+      <c r="B17" s="284" t="inlineStr">
+        <is>
+          <t>P5 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Rejunte Infinity Hard cor Mocha ou cor Branco Pérola Deverá ser testado as duas opções de rejunte para escolher a que mais se aproxima do tom da peça. Amostra a ser aprovada pela GPA&amp;A.
+CONFLITO – Arquitetura: ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C17" s="32" t="n"/>
@@ -6470,18 +6488,21 @@
       <c r="E17" s="32" t="n"/>
       <c r="F17" s="270" t="inlineStr">
         <is>
-          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.
+ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G17" s="32" t="n"/>
-      <c r="H17" s="271" t="inlineStr">
-        <is>
-          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+      <c r="H17" s="285" t="inlineStr">
+        <is>
+          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+CONFLITO – Arquitetura: ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
         </is>
       </c>
       <c r="I17" s="271" t="inlineStr">
         <is>
-          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
+ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J17" s="32" t="n"/>
@@ -6506,20 +6527,36 @@
       <c r="Y17" s="31" t="n"/>
       <c r="Z17" s="32" t="n"/>
     </row>
-    <row r="18" ht="125.25" customHeight="1">
+    <row r="18">
       <c r="A18" s="45" t="inlineStr">
         <is>
           <t>LAVABO GUARITA</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
+      <c r="B18" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C18" s="32" t="n"/>
       <c r="D18" s="32" t="n"/>
       <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
+      <c r="F18" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G18" s="32" t="n"/>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="33" t="n"/>
+      <c r="H18" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+      <c r="I18" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J18" s="32" t="n"/>
       <c r="K18" s="32" t="n"/>
       <c r="L18" s="32" t="n"/>
@@ -6538,20 +6575,36 @@
       <c r="Y18" s="31" t="n"/>
       <c r="Z18" s="32" t="n"/>
     </row>
-    <row r="19" ht="125.25" customHeight="1">
+    <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO GUARITA</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
+      <c r="B19" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C19" s="32" t="n"/>
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
+      <c r="F19" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G19" s="32" t="n"/>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="33" t="n"/>
+      <c r="H19" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I19" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J19" s="32" t="n"/>
       <c r="K19" s="32" t="n"/>
       <c r="L19" s="32" t="n"/>
@@ -6693,20 +6746,36 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="125.25" customHeight="1">
+    <row r="22">
       <c r="A22" s="45" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n"/>
+      <c r="B22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="C22" s="32" t="n"/>
       <c r="D22" s="32" t="n"/>
       <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
+      <c r="F22" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G22" s="32" t="n"/>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
+      <c r="H22" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I22" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J22" s="32" t="n"/>
       <c r="K22" s="32" t="n"/>
       <c r="L22" s="32" t="n"/>
@@ -6787,20 +6856,32 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="125.25" customHeight="1">
+    <row r="24">
       <c r="A24" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">GARAGEM </t>
         </is>
       </c>
-      <c r="B24" s="31" t="n"/>
+      <c r="B24" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
       <c r="C24" s="32" t="n"/>
       <c r="D24" s="32" t="n"/>
       <c r="E24" s="32" t="n"/>
       <c r="F24" s="32" t="n"/>
       <c r="G24" s="32" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="33" t="n"/>
+      <c r="H24" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I24" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J24" s="32" t="n"/>
       <c r="K24" s="32" t="n"/>
       <c r="L24" s="32" t="n"/>
@@ -6819,20 +6900,32 @@
       <c r="Y24" s="31" t="n"/>
       <c r="Z24" s="32" t="n"/>
     </row>
-    <row r="25" ht="125.25" customHeight="1">
+    <row r="25">
       <c r="A25" s="45" t="inlineStr">
         <is>
           <t>CASA DE BOMBAS</t>
         </is>
       </c>
-      <c r="B25" s="34" t="n"/>
+      <c r="B25" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C25" s="34" t="n"/>
       <c r="D25" s="32" t="n"/>
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="34" t="n"/>
       <c r="G25" s="32" t="n"/>
-      <c r="H25" s="34" t="n"/>
-      <c r="I25" s="35" t="n"/>
+      <c r="H25" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I25" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J25" s="32" t="n"/>
       <c r="K25" s="32" t="n"/>
       <c r="L25" s="32" t="n"/>
@@ -6883,20 +6976,36 @@
       <c r="Y26" s="31" t="n"/>
       <c r="Z26" s="35" t="n"/>
     </row>
-    <row r="27" ht="125.25" customHeight="1">
+    <row r="27">
       <c r="A27" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">CIRCULAÇÃO </t>
         </is>
       </c>
-      <c r="B27" s="35" t="n"/>
+      <c r="B27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C27" s="32" t="n"/>
       <c r="D27" s="37" t="n"/>
       <c r="E27" s="32" t="n"/>
-      <c r="F27" s="35" t="n"/>
+      <c r="F27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G27" s="32" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
+      <c r="H27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J27" s="35" t="n"/>
       <c r="K27" s="32" t="n"/>
       <c r="L27" s="32" t="n"/>
@@ -7056,20 +7165,36 @@
       <c r="Y29" s="32" t="n"/>
       <c r="Z29" s="35" t="n"/>
     </row>
-    <row r="30" ht="125.25" customHeight="1">
+    <row r="30">
       <c r="A30" s="45" t="inlineStr">
         <is>
           <t>CONCIERGE</t>
         </is>
       </c>
-      <c r="B30" s="35" t="n"/>
+      <c r="B30" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C30" s="32" t="n"/>
       <c r="D30" s="32" t="n"/>
       <c r="E30" s="37" t="n"/>
-      <c r="F30" s="32" t="n"/>
+      <c r="F30" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G30" s="35" t="n"/>
-      <c r="H30" s="35" t="n"/>
-      <c r="I30" s="35" t="n"/>
+      <c r="H30" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I30" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T19 - código não existe no quadro de tetos (01 a 06); conferir na planta</t>
+        </is>
+      </c>
       <c r="J30" s="35" t="n"/>
       <c r="K30" s="32" t="n"/>
       <c r="L30" s="35" t="n"/>
@@ -7088,20 +7213,36 @@
       <c r="Y30" s="32" t="n"/>
       <c r="Z30" s="35" t="n"/>
     </row>
-    <row r="31" ht="125.25" customHeight="1">
+    <row r="31">
       <c r="A31" s="45" t="inlineStr">
         <is>
           <t>DELIVERY</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n"/>
+      <c r="B31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C31" s="32" t="n"/>
       <c r="D31" s="37" t="n"/>
       <c r="E31" s="37" t="n"/>
-      <c r="F31" s="35" t="n"/>
+      <c r="F31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G31" s="32" t="n"/>
-      <c r="H31" s="35" t="n"/>
-      <c r="I31" s="35" t="n"/>
+      <c r="H31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J31" s="32" t="n"/>
       <c r="K31" s="32" t="n"/>
       <c r="L31" s="32" t="n"/>
@@ -7120,20 +7261,36 @@
       <c r="Y31" s="31" t="n"/>
       <c r="Z31" s="35" t="n"/>
     </row>
-    <row r="32" ht="125.25" customHeight="1">
+    <row r="32">
       <c r="A32" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">CIRCULAÇÃO SERVIÇO </t>
         </is>
       </c>
-      <c r="B32" s="35" t="n"/>
+      <c r="B32" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C32" s="32" t="n"/>
       <c r="D32" s="37" t="n"/>
       <c r="E32" s="37" t="n"/>
-      <c r="F32" s="35" t="n"/>
+      <c r="F32" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G32" s="32" t="n"/>
-      <c r="H32" s="35" t="n"/>
-      <c r="I32" s="35" t="n"/>
+      <c r="H32" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I32" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J32" s="32" t="n"/>
       <c r="K32" s="32" t="n"/>
       <c r="L32" s="32" t="n"/>
@@ -7152,20 +7309,32 @@
       <c r="Y32" s="31" t="n"/>
       <c r="Z32" s="35" t="n"/>
     </row>
-    <row r="33" ht="125.25" customHeight="1">
+    <row r="33">
       <c r="A33" s="45" t="inlineStr">
         <is>
           <t>CAR WASH</t>
         </is>
       </c>
-      <c r="B33" s="35" t="n"/>
+      <c r="B33" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
       <c r="C33" s="32" t="n"/>
       <c r="D33" s="32" t="n"/>
       <c r="E33" s="32" t="n"/>
       <c r="F33" s="35" t="n"/>
       <c r="G33" s="32" t="n"/>
-      <c r="H33" s="35" t="n"/>
-      <c r="I33" s="35" t="n"/>
+      <c r="H33" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I33" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J33" s="32" t="n"/>
       <c r="K33" s="32" t="n"/>
       <c r="L33" s="32" t="n"/>
@@ -7184,20 +7353,32 @@
       <c r="Y33" s="32" t="n"/>
       <c r="Z33" s="32" t="n"/>
     </row>
-    <row r="34" ht="125.25" customHeight="1">
+    <row r="34">
       <c r="A34" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">BICICLETÁRIO </t>
         </is>
       </c>
-      <c r="B34" s="35" t="n"/>
+      <c r="B34" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
       <c r="C34" s="32" t="n"/>
       <c r="D34" s="37" t="n"/>
       <c r="E34" s="37" t="n"/>
       <c r="F34" s="35" t="n"/>
       <c r="G34" s="32" t="n"/>
-      <c r="H34" s="35" t="n"/>
-      <c r="I34" s="35" t="n"/>
+      <c r="H34" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I34" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J34" s="32" t="n"/>
       <c r="K34" s="32" t="n"/>
       <c r="L34" s="32" t="n"/>
@@ -7216,20 +7397,36 @@
       <c r="Y34" s="31" t="n"/>
       <c r="Z34" s="35" t="n"/>
     </row>
-    <row r="35" ht="125.25" customHeight="1">
+    <row r="35">
       <c r="A35" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">ZELADORIA </t>
         </is>
       </c>
-      <c r="B35" s="35" t="n"/>
+      <c r="B35" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C35" s="32" t="n"/>
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="37" t="n"/>
-      <c r="F35" s="35" t="n"/>
+      <c r="F35" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G35" s="32" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="35" t="n"/>
+      <c r="H35" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I35" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J35" s="35" t="n"/>
       <c r="K35" s="32" t="n"/>
       <c r="L35" s="35" t="n"/>
@@ -7248,20 +7445,32 @@
       <c r="Y35" s="35" t="n"/>
       <c r="Z35" s="32" t="n"/>
     </row>
-    <row r="36" ht="125.25" customHeight="1">
+    <row r="36">
       <c r="A36" s="45" t="inlineStr">
         <is>
           <t>ARS 1</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n"/>
+      <c r="B36" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C36" s="32" t="n"/>
       <c r="D36" s="35" t="n"/>
       <c r="E36" s="37" t="n"/>
       <c r="F36" s="35" t="n"/>
       <c r="G36" s="32" t="n"/>
-      <c r="H36" s="35" t="n"/>
-      <c r="I36" s="35" t="n"/>
+      <c r="H36" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I36" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J36" s="35" t="n"/>
       <c r="K36" s="32" t="n"/>
       <c r="L36" s="35" t="n"/>
@@ -7280,20 +7489,32 @@
       <c r="Y36" s="35" t="n"/>
       <c r="Z36" s="32" t="n"/>
     </row>
-    <row r="37" ht="125.25" customHeight="1">
+    <row r="37">
       <c r="A37" s="45" t="inlineStr">
         <is>
           <t>ARS 2</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n"/>
+      <c r="B37" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C37" s="32" t="n"/>
       <c r="D37" s="35" t="n"/>
       <c r="E37" s="37" t="n"/>
       <c r="F37" s="35" t="n"/>
       <c r="G37" s="32" t="n"/>
-      <c r="H37" s="35" t="n"/>
-      <c r="I37" s="35" t="n"/>
+      <c r="H37" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I37" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J37" s="35" t="n"/>
       <c r="K37" s="32" t="n"/>
       <c r="L37" s="35" t="n"/>
@@ -7312,20 +7533,32 @@
       <c r="Y37" s="35" t="n"/>
       <c r="Z37" s="32" t="n"/>
     </row>
-    <row r="38" ht="125.25" customHeight="1">
+    <row r="38">
       <c r="A38" s="45" t="inlineStr">
         <is>
           <t>ARS 3</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n"/>
+      <c r="B38" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C38" s="32" t="n"/>
       <c r="D38" s="35" t="n"/>
       <c r="E38" s="37" t="n"/>
       <c r="F38" s="35" t="n"/>
       <c r="G38" s="32" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
+      <c r="H38" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I38" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J38" s="35" t="n"/>
       <c r="K38" s="32" t="n"/>
       <c r="L38" s="35" t="n"/>
@@ -7344,20 +7577,36 @@
       <c r="Y38" s="35" t="n"/>
       <c r="Z38" s="32" t="n"/>
     </row>
-    <row r="39" ht="125.25" customHeight="1">
+    <row r="39">
       <c r="A39" s="45" t="inlineStr">
         <is>
           <t>SALA MOTORISTA</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n"/>
+      <c r="B39" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P06 - Piso em porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C39" s="32" t="n"/>
       <c r="D39" s="35" t="n"/>
       <c r="E39" s="37" t="n"/>
-      <c r="F39" s="35" t="n"/>
+      <c r="F39" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G39" s="32" t="n"/>
-      <c r="H39" s="35" t="n"/>
-      <c r="I39" s="35" t="n"/>
+      <c r="H39" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+      <c r="I39" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J39" s="35" t="n"/>
       <c r="K39" s="32" t="n"/>
       <c r="L39" s="35" t="n"/>
@@ -7376,20 +7625,32 @@
       <c r="Y39" s="35" t="n"/>
       <c r="Z39" s="32" t="n"/>
     </row>
-    <row r="40" ht="125.25" customHeight="1">
+    <row r="40">
       <c r="A40" s="45" t="inlineStr">
         <is>
           <t>DML</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
+      <c r="B40" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C40" s="32" t="n"/>
       <c r="D40" s="35" t="n"/>
       <c r="E40" s="37" t="n"/>
       <c r="F40" s="35" t="n"/>
       <c r="G40" s="32" t="n"/>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="35" t="n"/>
+      <c r="H40" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I40" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J40" s="35" t="n"/>
       <c r="K40" s="32" t="n"/>
       <c r="L40" s="35" t="n"/>
@@ -7408,20 +7669,32 @@
       <c r="Y40" s="35" t="n"/>
       <c r="Z40" s="32" t="n"/>
     </row>
-    <row r="41" ht="125.25" customHeight="1">
+    <row r="41">
       <c r="A41" s="45" t="inlineStr">
         <is>
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n"/>
+      <c r="B41" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C41" s="32" t="n"/>
       <c r="D41" s="35" t="n"/>
       <c r="E41" s="37" t="n"/>
       <c r="F41" s="35" t="n"/>
       <c r="G41" s="32" t="n"/>
-      <c r="H41" s="35" t="n"/>
-      <c r="I41" s="35" t="n"/>
+      <c r="H41" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I41" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J41" s="35" t="n"/>
       <c r="K41" s="32" t="n"/>
       <c r="L41" s="35" t="n"/>
@@ -7440,20 +7713,32 @@
       <c r="Y41" s="35" t="n"/>
       <c r="Z41" s="32" t="n"/>
     </row>
-    <row r="42" ht="125.25" customHeight="1">
+    <row r="42">
       <c r="A42" s="45" t="inlineStr">
         <is>
           <t>VEST. FEMININO</t>
         </is>
       </c>
-      <c r="B42" s="35" t="n"/>
+      <c r="B42" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C42" s="32" t="n"/>
       <c r="D42" s="35" t="n"/>
       <c r="E42" s="37" t="n"/>
       <c r="F42" s="35" t="n"/>
       <c r="G42" s="32" t="n"/>
-      <c r="H42" s="35" t="n"/>
-      <c r="I42" s="35" t="n"/>
+      <c r="H42" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I42" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J42" s="35" t="n"/>
       <c r="K42" s="32" t="n"/>
       <c r="L42" s="35" t="n"/>
@@ -7472,20 +7757,32 @@
       <c r="Y42" s="35" t="n"/>
       <c r="Z42" s="32" t="n"/>
     </row>
-    <row r="43" ht="125.25" customHeight="1">
+    <row r="43">
       <c r="A43" s="45" t="inlineStr">
         <is>
           <t>VEST. MASC.</t>
         </is>
       </c>
-      <c r="B43" s="35" t="n"/>
+      <c r="B43" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C43" s="32" t="n"/>
       <c r="D43" s="35" t="n"/>
       <c r="E43" s="37" t="n"/>
       <c r="F43" s="35" t="n"/>
       <c r="G43" s="32" t="n"/>
-      <c r="H43" s="35" t="n"/>
-      <c r="I43" s="35" t="n"/>
+      <c r="H43" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I43" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J43" s="35" t="n"/>
       <c r="K43" s="32" t="n"/>
       <c r="L43" s="35" t="n"/>
@@ -7504,20 +7801,32 @@
       <c r="Y43" s="35" t="n"/>
       <c r="Z43" s="32" t="n"/>
     </row>
-    <row r="44" ht="125.25" customHeight="1">
+    <row r="44">
       <c r="A44" s="45" t="inlineStr">
         <is>
           <t>ESTAR/COPA FUNCIONÁRIOS</t>
         </is>
       </c>
-      <c r="B44" s="35" t="n"/>
+      <c r="B44" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C44" s="32" t="n"/>
       <c r="D44" s="35" t="n"/>
       <c r="E44" s="37" t="n"/>
       <c r="F44" s="35" t="n"/>
       <c r="G44" s="32" t="n"/>
-      <c r="H44" s="35" t="n"/>
-      <c r="I44" s="35" t="n"/>
+      <c r="H44" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I44" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J44" s="35" t="n"/>
       <c r="K44" s="32" t="n"/>
       <c r="L44" s="35" t="n"/>
@@ -7536,20 +7845,36 @@
       <c r="Y44" s="35" t="n"/>
       <c r="Z44" s="32" t="n"/>
     </row>
-    <row r="45" ht="125.25" customHeight="1">
+    <row r="45">
       <c r="A45" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">CIRCULAÇÃO </t>
         </is>
       </c>
-      <c r="B45" s="35" t="n"/>
+      <c r="B45" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="C45" s="32" t="n"/>
       <c r="D45" s="35" t="n"/>
       <c r="E45" s="37" t="n"/>
-      <c r="F45" s="35" t="n"/>
+      <c r="F45" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
       <c r="G45" s="32" t="n"/>
-      <c r="H45" s="35" t="n"/>
-      <c r="I45" s="35" t="n"/>
+      <c r="H45" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I45" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J45" s="35" t="n"/>
       <c r="K45" s="32" t="n"/>
       <c r="L45" s="35" t="n"/>
@@ -7568,20 +7893,32 @@
       <c r="Y45" s="35" t="n"/>
       <c r="Z45" s="32" t="n"/>
     </row>
-    <row r="46" ht="125.25" customHeight="1">
+    <row r="46">
       <c r="A46" s="45" t="inlineStr">
         <is>
           <t>GERADOR</t>
         </is>
       </c>
-      <c r="B46" s="35" t="n"/>
+      <c r="B46" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C46" s="32" t="n"/>
       <c r="D46" s="35" t="n"/>
       <c r="E46" s="37" t="n"/>
       <c r="F46" s="32" t="n"/>
       <c r="G46" s="32" t="n"/>
-      <c r="H46" s="35" t="n"/>
-      <c r="I46" s="35" t="n"/>
+      <c r="H46" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I46" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J46" s="35" t="n"/>
       <c r="K46" s="32" t="n"/>
       <c r="L46" s="35" t="n"/>
@@ -7600,20 +7937,32 @@
       <c r="Y46" s="35" t="n"/>
       <c r="Z46" s="32" t="n"/>
     </row>
-    <row r="47" ht="125.25" customHeight="1">
+    <row r="47">
       <c r="A47" s="45" t="inlineStr">
         <is>
           <t>VAGAS BOX</t>
         </is>
       </c>
-      <c r="B47" s="35" t="n"/>
+      <c r="B47" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
       <c r="C47" s="32" t="n"/>
       <c r="D47" s="35" t="n"/>
       <c r="E47" s="37" t="n"/>
       <c r="F47" s="32" t="n"/>
       <c r="G47" s="32" t="n"/>
-      <c r="H47" s="35" t="n"/>
-      <c r="I47" s="35" t="n"/>
+      <c r="H47" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I47" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J47" s="35" t="n"/>
       <c r="K47" s="32" t="n"/>
       <c r="L47" s="35" t="n"/>
@@ -7632,20 +7981,32 @@
       <c r="Y47" s="35" t="n"/>
       <c r="Z47" s="32" t="n"/>
     </row>
-    <row r="48" ht="125.25" customHeight="1">
+    <row r="48">
       <c r="A48" s="45" t="inlineStr">
         <is>
           <t>QUADROS ELÉTRICOS</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n"/>
+      <c r="B48" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C48" s="32" t="n"/>
       <c r="D48" s="35" t="n"/>
       <c r="E48" s="37" t="n"/>
       <c r="F48" s="32" t="n"/>
       <c r="G48" s="32" t="n"/>
-      <c r="H48" s="35" t="n"/>
-      <c r="I48" s="35" t="n"/>
+      <c r="H48" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I48" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J48" s="35" t="n"/>
       <c r="K48" s="32" t="n"/>
       <c r="L48" s="35" t="n"/>
@@ -7664,12 +8025,270 @@
       <c r="Y48" s="35" t="n"/>
       <c r="Z48" s="32" t="n"/>
     </row>
-    <row r="49" ht="125.25" customHeight="1"/>
-    <row r="50" ht="2.1" customHeight="1"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>ACESSO E SAÍDA DE VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="B49" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="35" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I49" s="269" t="n"/>
+      <c r="J49" s="35" t="n"/>
+      <c r="K49" s="32" t="n"/>
+      <c r="L49" s="35" t="n"/>
+      <c r="M49" s="37" t="n"/>
+      <c r="N49" s="38" t="n"/>
+      <c r="O49" s="35" t="n"/>
+      <c r="P49" s="31" t="n"/>
+      <c r="Q49" s="32" t="n"/>
+      <c r="R49" s="35" t="n"/>
+      <c r="S49" s="35" t="n"/>
+      <c r="T49" s="35" t="n"/>
+      <c r="U49" s="32" t="n"/>
+      <c r="V49" s="31" t="n"/>
+      <c r="W49" s="35" t="n"/>
+      <c r="X49" s="35" t="n"/>
+      <c r="Y49" s="35" t="n"/>
+      <c r="Z49" s="32" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="inlineStr">
+        <is>
+          <t>ESTACIONAMENTO VISITANTES</t>
+        </is>
+      </c>
+      <c r="B50" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="n"/>
+      <c r="D50" s="35" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="32" t="n"/>
+      <c r="G50" s="32" t="n"/>
+      <c r="H50" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I50" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J50" s="35" t="n"/>
+      <c r="K50" s="32" t="n"/>
+      <c r="L50" s="35" t="n"/>
+      <c r="M50" s="37" t="n"/>
+      <c r="N50" s="38" t="n"/>
+      <c r="O50" s="35" t="n"/>
+      <c r="P50" s="31" t="n"/>
+      <c r="Q50" s="32" t="n"/>
+      <c r="R50" s="35" t="n"/>
+      <c r="S50" s="35" t="n"/>
+      <c r="T50" s="35" t="n"/>
+      <c r="U50" s="32" t="n"/>
+      <c r="V50" s="31" t="n"/>
+      <c r="W50" s="35" t="n"/>
+      <c r="X50" s="35" t="n"/>
+      <c r="Y50" s="35" t="n"/>
+      <c r="Z50" s="32" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="45" t="inlineStr">
+        <is>
+          <t>RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="B51" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="n"/>
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="37" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="32" t="n"/>
+      <c r="H51" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I51" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J51" s="35" t="n"/>
+      <c r="K51" s="32" t="n"/>
+      <c r="L51" s="35" t="n"/>
+      <c r="M51" s="37" t="n"/>
+      <c r="N51" s="38" t="n"/>
+      <c r="O51" s="35" t="n"/>
+      <c r="P51" s="31" t="n"/>
+      <c r="Q51" s="32" t="n"/>
+      <c r="R51" s="35" t="n"/>
+      <c r="S51" s="35" t="n"/>
+      <c r="T51" s="35" t="n"/>
+      <c r="U51" s="32" t="n"/>
+      <c r="V51" s="31" t="n"/>
+      <c r="W51" s="35" t="n"/>
+      <c r="X51" s="35" t="n"/>
+      <c r="Y51" s="35" t="n"/>
+      <c r="Z51" s="32" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>DEPÓSITO (A=8,85 m²)</t>
+        </is>
+      </c>
+      <c r="B52" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="n"/>
+      <c r="D52" s="35" t="n"/>
+      <c r="E52" s="37" t="n"/>
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="32" t="n"/>
+      <c r="H52" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I52" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J52" s="35" t="n"/>
+      <c r="K52" s="32" t="n"/>
+      <c r="L52" s="35" t="n"/>
+      <c r="M52" s="37" t="n"/>
+      <c r="N52" s="38" t="n"/>
+      <c r="O52" s="35" t="n"/>
+      <c r="P52" s="31" t="n"/>
+      <c r="Q52" s="32" t="n"/>
+      <c r="R52" s="35" t="n"/>
+      <c r="S52" s="35" t="n"/>
+      <c r="T52" s="35" t="n"/>
+      <c r="U52" s="32" t="n"/>
+      <c r="V52" s="31" t="n"/>
+      <c r="W52" s="35" t="n"/>
+      <c r="X52" s="35" t="n"/>
+      <c r="Y52" s="35" t="n"/>
+      <c r="Z52" s="32" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="45" t="inlineStr">
+        <is>
+          <t>SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
+        </is>
+      </c>
+      <c r="B53" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="n"/>
+      <c r="D53" s="35" t="n"/>
+      <c r="E53" s="37" t="n"/>
+      <c r="F53" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+      <c r="G53" s="32" t="n"/>
+      <c r="H53" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+      <c r="I53" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="J53" s="35" t="n"/>
+      <c r="K53" s="32" t="n"/>
+      <c r="L53" s="35" t="n"/>
+      <c r="M53" s="37" t="n"/>
+      <c r="N53" s="38" t="n"/>
+      <c r="O53" s="35" t="n"/>
+      <c r="P53" s="31" t="n"/>
+      <c r="Q53" s="32" t="n"/>
+      <c r="R53" s="35" t="n"/>
+      <c r="S53" s="35" t="n"/>
+      <c r="T53" s="35" t="n"/>
+      <c r="U53" s="32" t="n"/>
+      <c r="V53" s="31" t="n"/>
+      <c r="W53" s="35" t="n"/>
+      <c r="X53" s="35" t="n"/>
+      <c r="Y53" s="35" t="n"/>
+      <c r="Z53" s="32" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="45" t="inlineStr">
+        <is>
+          <t>CIRCULAÇÃO JUNTO À ESCADA (A=4,06 m²)</t>
+        </is>
+      </c>
+      <c r="B54" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="35" t="n"/>
+      <c r="E54" s="37" t="n"/>
+      <c r="F54" s="270" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I54" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J54" s="35" t="n"/>
+      <c r="K54" s="32" t="n"/>
+      <c r="L54" s="35" t="n"/>
+      <c r="M54" s="37" t="n"/>
+      <c r="N54" s="38" t="n"/>
+      <c r="O54" s="35" t="n"/>
+      <c r="P54" s="31" t="n"/>
+      <c r="Q54" s="32" t="n"/>
+      <c r="R54" s="35" t="n"/>
+      <c r="S54" s="35" t="n"/>
+      <c r="T54" s="35" t="n"/>
+      <c r="U54" s="32" t="n"/>
+      <c r="V54" s="31" t="n"/>
+      <c r="W54" s="35" t="n"/>
+      <c r="X54" s="35" t="n"/>
+      <c r="Y54" s="35" t="n"/>
+      <c r="Z54" s="32" t="n"/>
+    </row>
     <row r="55">
       <c r="S55" s="3" t="inlineStr">
         <is>
@@ -8352,20 +8971,32 @@
       <c r="Y12" s="241" t="n"/>
       <c r="Z12" s="242" t="n"/>
     </row>
-    <row r="13" ht="125.25" customHeight="1">
+    <row r="13">
       <c r="A13" s="47" t="inlineStr">
         <is>
           <t>CASA DE BOMBAS PISCINA 1</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n"/>
+      <c r="B13" s="276" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C13" s="49" t="n"/>
       <c r="D13" s="49" t="n"/>
       <c r="E13" s="49" t="n"/>
       <c r="F13" s="49" t="n"/>
       <c r="G13" s="49" t="n"/>
-      <c r="H13" s="50" t="n"/>
-      <c r="I13" s="50" t="n"/>
+      <c r="H13" s="286" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I13" s="286" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J13" s="49" t="n"/>
       <c r="K13" s="49" t="n"/>
       <c r="L13" s="49" t="n"/>
@@ -8384,20 +9015,32 @@
       <c r="Y13" s="48" t="n"/>
       <c r="Z13" s="49" t="n"/>
     </row>
-    <row r="14" ht="125.25" customHeight="1">
+    <row r="14">
       <c r="A14" s="45" t="inlineStr">
         <is>
           <t>SHAFT ELÉTRICA</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
+      <c r="B14" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C14" s="32" t="n"/>
       <c r="D14" s="32" t="n"/>
       <c r="E14" s="32" t="n"/>
       <c r="F14" s="32" t="n"/>
       <c r="G14" s="32" t="n"/>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="33" t="n"/>
+      <c r="H14" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I14" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J14" s="32" t="n"/>
       <c r="K14" s="32" t="n"/>
       <c r="L14" s="32" t="n"/>
@@ -8480,20 +9123,37 @@
       <c r="Y16" s="31" t="n"/>
       <c r="Z16" s="32" t="n"/>
     </row>
-    <row r="17" ht="125.25" customHeight="1">
+    <row r="17">
       <c r="A17" s="45" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO/ANTECÂMARA</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
+      <c r="B17" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="C17" s="32" t="n"/>
       <c r="D17" s="32" t="n"/>
       <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
+      <c r="F17" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
       <c r="G17" s="32" t="n"/>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="33" t="n"/>
+      <c r="H17" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I17" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
+ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J17" s="32" t="n"/>
       <c r="K17" s="32" t="n"/>
       <c r="L17" s="32" t="n"/>
@@ -8512,20 +9172,32 @@
       <c r="Y17" s="31" t="n"/>
       <c r="Z17" s="32" t="n"/>
     </row>
-    <row r="18" ht="125.25" customHeight="1">
+    <row r="18">
       <c r="A18" s="45" t="inlineStr">
         <is>
           <t>PRESSURIZAÇÃO/ANTECÂMARA</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
+      <c r="B18" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C18" s="32" t="n"/>
       <c r="D18" s="32" t="n"/>
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="32" t="n"/>
       <c r="G18" s="32" t="n"/>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="33" t="n"/>
+      <c r="H18" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I18" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J18" s="32" t="n"/>
       <c r="K18" s="32" t="n"/>
       <c r="L18" s="32" t="n"/>
@@ -8544,20 +9216,32 @@
       <c r="Y18" s="31" t="n"/>
       <c r="Z18" s="32" t="n"/>
     </row>
-    <row r="19" ht="125.25" customHeight="1">
+    <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
           <t>ÁREA TÉCNICA 1</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
+      <c r="B19" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C19" s="32" t="n"/>
       <c r="D19" s="32" t="n"/>
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="32" t="n"/>
       <c r="G19" s="32" t="n"/>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="33" t="n"/>
+      <c r="H19" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I19" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J19" s="32" t="n"/>
       <c r="K19" s="32" t="n"/>
       <c r="L19" s="32" t="n"/>
@@ -8576,19 +9260,31 @@
       <c r="Y19" s="31" t="n"/>
       <c r="Z19" s="32" t="n"/>
     </row>
-    <row r="20" ht="125.25" customHeight="1">
+    <row r="20">
       <c r="A20" s="45" t="inlineStr">
         <is>
           <t>ÁREA TÉCNICA 2</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n"/>
+      <c r="B20" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C20" s="32" t="n"/>
       <c r="D20" s="32" t="n"/>
       <c r="E20" s="32" t="n"/>
       <c r="G20" s="32" t="n"/>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="33" t="n"/>
+      <c r="H20" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I20" s="271" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J20" s="32" t="n"/>
       <c r="K20" s="32" t="n"/>
       <c r="L20" s="32" t="n"/>
@@ -8607,20 +9303,32 @@
       <c r="Y20" s="31" t="n"/>
       <c r="Z20" s="32" t="n"/>
     </row>
-    <row r="21" ht="125.25" customHeight="1">
+    <row r="21">
       <c r="A21" s="45" t="inlineStr">
         <is>
           <t>GARAGEM</t>
         </is>
       </c>
-      <c r="B21" s="34" t="n"/>
+      <c r="B21" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
       <c r="C21" s="34" t="n"/>
       <c r="D21" s="32" t="n"/>
       <c r="E21" s="32" t="n"/>
       <c r="F21" s="34" t="n"/>
       <c r="G21" s="32" t="n"/>
-      <c r="H21" s="34" t="n"/>
-      <c r="I21" s="35" t="n"/>
+      <c r="H21" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I21" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J21" s="32" t="n"/>
       <c r="K21" s="32" t="n"/>
       <c r="L21" s="32" t="n"/>
@@ -8639,20 +9347,32 @@
       <c r="Y21" s="31" t="n"/>
       <c r="Z21" s="32" t="n"/>
     </row>
-    <row r="22" ht="125.25" customHeight="1">
+    <row r="22">
       <c r="A22" s="45" t="inlineStr">
         <is>
           <t>VAGAS BOX</t>
         </is>
       </c>
-      <c r="B22" s="34" t="n"/>
+      <c r="B22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
       <c r="C22" s="32" t="n"/>
       <c r="D22" s="34" t="n"/>
       <c r="E22" s="36" t="n"/>
       <c r="F22" s="34" t="n"/>
       <c r="G22" s="32" t="n"/>
-      <c r="H22" s="34" t="n"/>
-      <c r="I22" s="35" t="n"/>
+      <c r="H22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J22" s="32" t="n"/>
       <c r="K22" s="32" t="n"/>
       <c r="L22" s="32" t="n"/>
@@ -8671,20 +9391,32 @@
       <c r="Y22" s="31" t="n"/>
       <c r="Z22" s="35" t="n"/>
     </row>
-    <row r="23" ht="125.25" customHeight="1">
+    <row r="23">
       <c r="A23" s="45" t="inlineStr">
         <is>
           <t>TELECOM</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
+      <c r="B23" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C23" s="32" t="n"/>
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="35" t="n"/>
       <c r="G23" s="32" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
+      <c r="H23" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I23" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J23" s="35" t="n"/>
       <c r="K23" s="32" t="n"/>
       <c r="L23" s="32" t="n"/>
@@ -8703,20 +9435,32 @@
       <c r="Y23" s="35" t="n"/>
       <c r="Z23" s="35" t="n"/>
     </row>
-    <row r="24" ht="125.25" customHeight="1">
+    <row r="24">
       <c r="A24" s="45" t="inlineStr">
         <is>
           <t>SALA DE SEGURANÇA</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n"/>
+      <c r="B24" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C24" s="32" t="n"/>
       <c r="D24" s="35" t="n"/>
       <c r="E24" s="37" t="n"/>
       <c r="F24" s="35" t="n"/>
       <c r="G24" s="32" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="32" t="n"/>
+      <c r="H24" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I24" s="270" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J24" s="32" t="n"/>
       <c r="K24" s="32" t="n"/>
       <c r="L24" s="32" t="n"/>
@@ -8735,20 +9479,32 @@
       <c r="Y24" s="31" t="n"/>
       <c r="Z24" s="35" t="n"/>
     </row>
-    <row r="25" ht="125.25" customHeight="1">
+    <row r="25">
       <c r="A25" s="45" t="inlineStr">
         <is>
           <t>CASA DE BOMBAS PISCINA 2 (FUNDO)</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n"/>
+      <c r="B25" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C25" s="32" t="n"/>
       <c r="D25" s="32" t="n"/>
       <c r="E25" s="37" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
+      <c r="H25" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I25" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J25" s="35" t="n"/>
       <c r="K25" s="32" t="n"/>
       <c r="L25" s="35" t="n"/>
@@ -8767,20 +9523,32 @@
       <c r="Y25" s="32" t="n"/>
       <c r="Z25" s="35" t="n"/>
     </row>
-    <row r="26" ht="125.25" customHeight="1">
+    <row r="26">
       <c r="A26" s="45" t="inlineStr">
         <is>
           <t>DML</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n"/>
+      <c r="B26" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C26" s="32" t="n"/>
       <c r="D26" s="32" t="n"/>
       <c r="E26" s="37" t="n"/>
       <c r="F26" s="32" t="n"/>
       <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
+      <c r="H26" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+      <c r="I26" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J26" s="35" t="n"/>
       <c r="K26" s="32" t="n"/>
       <c r="L26" s="35" t="n"/>
@@ -8799,20 +9567,32 @@
       <c r="Y26" s="32" t="n"/>
       <c r="Z26" s="35" t="n"/>
     </row>
-    <row r="27" ht="125.25" customHeight="1">
+    <row r="27">
       <c r="A27" s="45" t="inlineStr">
         <is>
           <t>RESERVATÓRIO INFERIOR</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n"/>
+      <c r="B27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C27" s="32" t="n"/>
       <c r="D27" s="37" t="n"/>
       <c r="E27" s="37" t="n"/>
       <c r="F27" s="35" t="n"/>
       <c r="G27" s="32" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
+      <c r="H27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I27" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J27" s="32" t="n"/>
       <c r="K27" s="32" t="n"/>
       <c r="L27" s="32" t="n"/>
@@ -8831,20 +9611,32 @@
       <c r="Y27" s="31" t="n"/>
       <c r="Z27" s="35" t="n"/>
     </row>
-    <row r="28" ht="125.25" customHeight="1">
+    <row r="28">
       <c r="A28" s="45" t="inlineStr">
         <is>
           <t>HALL TÉCNICO/CIRCULAÇÃO</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n"/>
+      <c r="B28" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
       <c r="C28" s="32" t="n"/>
       <c r="D28" s="37" t="n"/>
       <c r="E28" s="37" t="n"/>
       <c r="F28" s="35" t="n"/>
       <c r="G28" s="32" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="35" t="n"/>
+      <c r="H28" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I28" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
       <c r="J28" s="32" t="n"/>
       <c r="K28" s="32" t="n"/>
       <c r="L28" s="32" t="n"/>
@@ -8863,8 +9655,141 @@
       <c r="Y28" s="31" t="n"/>
       <c r="Z28" s="35" t="n"/>
     </row>
-    <row r="29" ht="125.25" customHeight="1"/>
-    <row r="30" ht="2.1" customHeight="1"/>
+    <row r="29">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="B29" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P04 - Piso em concreto mecanizado com acabamento em ladrilho hidráulico antiderrapante cinza, tom concreto. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="32" t="n"/>
+      <c r="H29" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="I29" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J29" s="32" t="n"/>
+      <c r="K29" s="32" t="n"/>
+      <c r="L29" s="32" t="n"/>
+      <c r="M29" s="32" t="n"/>
+      <c r="N29" s="32" t="n"/>
+      <c r="O29" s="32" t="n"/>
+      <c r="P29" s="32" t="n"/>
+      <c r="Q29" s="32" t="n"/>
+      <c r="R29" s="32" t="n"/>
+      <c r="S29" s="32" t="n"/>
+      <c r="T29" s="32" t="n"/>
+      <c r="U29" s="32" t="n"/>
+      <c r="V29" s="31" t="n"/>
+      <c r="W29" s="35" t="n"/>
+      <c r="X29" s="31" t="n"/>
+      <c r="Y29" s="31" t="n"/>
+      <c r="Z29" s="35" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>CIRCULAÇÃO ÁREA TÉCNICA (A=14,54 m²)</t>
+        </is>
+      </c>
+      <c r="B30" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I30" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J30" s="32" t="n"/>
+      <c r="K30" s="32" t="n"/>
+      <c r="L30" s="32" t="n"/>
+      <c r="M30" s="32" t="n"/>
+      <c r="N30" s="32" t="n"/>
+      <c r="O30" s="32" t="n"/>
+      <c r="P30" s="32" t="n"/>
+      <c r="Q30" s="32" t="n"/>
+      <c r="R30" s="32" t="n"/>
+      <c r="S30" s="32" t="n"/>
+      <c r="T30" s="32" t="n"/>
+      <c r="U30" s="32" t="n"/>
+      <c r="V30" s="31" t="n"/>
+      <c r="W30" s="35" t="n"/>
+      <c r="X30" s="31" t="n"/>
+      <c r="Y30" s="31" t="n"/>
+      <c r="Z30" s="35" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr">
+        <is>
+          <t>CIRCULAÇÃO JUNTO À ESCADA (A=3,07 m²)</t>
+        </is>
+      </c>
+      <c r="B31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="32" t="n"/>
+      <c r="H31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I31" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J31" s="32" t="n"/>
+      <c r="K31" s="32" t="n"/>
+      <c r="L31" s="32" t="n"/>
+      <c r="M31" s="32" t="n"/>
+      <c r="N31" s="32" t="n"/>
+      <c r="O31" s="32" t="n"/>
+      <c r="P31" s="32" t="n"/>
+      <c r="Q31" s="32" t="n"/>
+      <c r="R31" s="32" t="n"/>
+      <c r="S31" s="32" t="n"/>
+      <c r="T31" s="32" t="n"/>
+      <c r="U31" s="32" t="n"/>
+      <c r="V31" s="31" t="n"/>
+      <c r="W31" s="35" t="n"/>
+      <c r="X31" s="31" t="n"/>
+      <c r="Y31" s="31" t="n"/>
+      <c r="Z31" s="35" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="S35" s="3" t="inlineStr">
         <is>
@@ -8931,7 +9856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF63"/>
+  <dimension ref="A1:AF64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
     <col width="44.7109375" customWidth="1" style="14" min="1" max="1"/>
@@ -10075,20 +11000,36 @@
       <c r="Y21" s="31" t="n"/>
       <c r="Z21" s="32" t="n"/>
     </row>
-    <row r="22" ht="125.25" customHeight="1">
+    <row r="22">
       <c r="A22" s="45" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
         </is>
       </c>
-      <c r="B22" s="34" t="n"/>
+      <c r="B22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
       <c r="C22" s="34" t="n"/>
       <c r="D22" s="32" t="n"/>
       <c r="E22" s="32" t="n"/>
-      <c r="F22" s="34" t="n"/>
+      <c r="F22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
       <c r="G22" s="32" t="n"/>
-      <c r="H22" s="34" t="n"/>
-      <c r="I22" s="35" t="n"/>
+      <c r="H22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="I22" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
       <c r="J22" s="32" t="n"/>
       <c r="K22" s="32" t="n"/>
       <c r="L22" s="32" t="n"/>
@@ -11827,7 +12768,7 @@
       <c r="Y51" s="35" t="n"/>
       <c r="Z51" s="32" t="n"/>
     </row>
-    <row r="52" ht="188" customHeight="1">
+    <row r="52">
       <c r="A52" s="45" t="inlineStr">
         <is>
           <t>QUADRA TÊNIS</t>
@@ -11835,7 +12776,8 @@
       </c>
       <c r="B52" s="245" t="inlineStr">
         <is>
-          <t>16 - Piso em pó de saibro com faixa na cor branca para marcação de quadra de tênis fixada com pregos especiais</t>
+          <t>16 - Piso em pó de saibro com faixa na cor branca para marcação de quadra de tênis fixada com pregos especiais
+ARQ-P16 - Piso em pó de saibro com faixa na cor branca para marcação de quadra de tênis fixada com pregos especiais. Verificar detalhes no projeto específico de quadra.</t>
         </is>
       </c>
       <c r="C52" s="32" t="n"/>
@@ -11845,10 +12787,15 @@
       <c r="G52" s="32" t="n"/>
       <c r="H52" s="245" t="inlineStr">
         <is>
-          <t>03 - Pintura acrílica fosca cinza tom a definir - Reboco (2 demãos Latex acrílico)</t>
-        </is>
-      </c>
-      <c r="I52" s="35" t="n"/>
+          <t>03 - Pintura acrílica fosca cinza tom a definir - Reboco (2 demãos Latex acrílico)
+ARQ-PA03 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza, tom a definir.</t>
+        </is>
+      </c>
+      <c r="I52" s="269" t="inlineStr">
+        <is>
+          <t>ARQ-T05 - Cobertura em telha sanduíche com estrutura espacial pintadas na cor cinza tom a definir.</t>
+        </is>
+      </c>
       <c r="J52" s="35" t="n"/>
       <c r="K52" s="32" t="n"/>
       <c r="L52" s="35" t="n"/>
@@ -11867,7 +12814,7 @@
       <c r="Y52" s="35" t="n"/>
       <c r="Z52" s="32" t="n"/>
     </row>
-    <row r="53" ht="409" customHeight="1">
+    <row r="53">
       <c r="A53" s="45" t="inlineStr">
         <is>
           <t>DEP JARDIM</t>
@@ -11875,7 +12822,8 @@
       </c>
       <c r="B53" s="245" t="inlineStr">
         <is>
-          <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+          <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
+ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="C53" s="32" t="n"/>
@@ -11883,19 +12831,22 @@
       <c r="E53" s="37" t="n"/>
       <c r="F53" s="246" t="inlineStr">
         <is>
-          <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+          <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
+ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G53" s="32" t="n"/>
       <c r="H53" s="245" t="inlineStr">
         <is>
           <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
-01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
+ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
       <c r="I53" s="245" t="inlineStr">
         <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)
+ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J53" s="245" t="inlineStr">
@@ -11932,7 +12883,7 @@
       <c r="Y53" s="35" t="n"/>
       <c r="Z53" s="32" t="n"/>
     </row>
-    <row r="54" ht="409" customHeight="1">
+    <row r="54">
       <c r="A54" s="45" t="inlineStr">
         <is>
           <t>DEPÓSITO</t>
@@ -11940,7 +12891,8 @@
       </c>
       <c r="B54" s="245" t="inlineStr">
         <is>
-          <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+          <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
+ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="C54" s="32" t="n"/>
@@ -11948,19 +12900,22 @@
       <c r="E54" s="37" t="n"/>
       <c r="F54" s="246" t="inlineStr">
         <is>
-          <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+          <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
+ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G54" s="32" t="n"/>
       <c r="H54" s="245" t="inlineStr">
         <is>
           <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
-01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
+ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
       <c r="I54" s="245" t="inlineStr">
         <is>
-          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)
+ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J54" s="245" t="inlineStr">
@@ -12139,7 +13094,7 @@
       <c r="Y56" s="35" t="n"/>
       <c r="Z56" s="32" t="n"/>
     </row>
-    <row r="57" ht="314" customHeight="1">
+    <row r="57">
       <c r="A57" s="45" t="inlineStr">
         <is>
           <t>ANTECÂMARA</t>
@@ -12147,7 +13102,8 @@
       </c>
       <c r="B57" s="245" t="inlineStr">
         <is>
-          <t>07 - Piso de granito cinza santa rosa, acabamento serrado, espessura: 2cm, dimensões e paginação conforme detalhamento, assentado com argamassa colante em pó ACIII. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+          <t>07 - Piso de granito cinza santa rosa, acabamento serrado, espessura: 2cm, dimensões e paginação conforme detalhamento, assentado com argamassa colante em pó ACIII. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material
+ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C57" s="32" t="n"/>
@@ -12155,18 +13111,21 @@
       <c r="E57" s="37" t="n"/>
       <c r="F57" s="246" t="inlineStr">
         <is>
-          <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII</t>
+          <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII
+ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="G57" s="32" t="n"/>
       <c r="H57" s="245" t="inlineStr">
         <is>
-          <t>01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+          <t>01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
+ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
       <c r="I57" s="245" t="inlineStr">
         <is>
-          <t>02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural</t>
+          <t>02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural
+ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
       <c r="J57" s="245" t="n"/>
@@ -12328,7 +13287,7 @@
       <c r="Y60" s="35" t="n"/>
       <c r="Z60" s="32" t="n"/>
     </row>
-    <row r="61" ht="125.25" customHeight="1">
+    <row r="61">
       <c r="A61" s="45" t="inlineStr">
         <is>
           <t>ESCADA EXTERNA</t>
@@ -12336,7 +13295,8 @@
       </c>
       <c r="B61" s="245" t="inlineStr">
         <is>
-          <t>07| P28 - Piso de granito Santa rosa, acabamento serrado. Espessura de 2cm. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+          <t>07| P28 - Piso de granito Santa rosa, acabamento serrado. Espessura de 2cm. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material
+ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C61" s="32" t="n"/>
@@ -12344,7 +13304,11 @@
       <c r="E61" s="37" t="n"/>
       <c r="F61" s="246" t="n"/>
       <c r="G61" s="32" t="n"/>
-      <c r="H61" s="245" t="n"/>
+      <c r="H61" s="277" t="inlineStr">
+        <is>
+          <t>ARQ-PA06 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza tom a definir. Meia parede pintada com tinta acrílica fosca na cor verde, tom a definir. Verificar altura conforme detalhamento.</t>
+        </is>
+      </c>
       <c r="I61" s="245" t="n"/>
       <c r="J61" s="245" t="n"/>
       <c r="K61" s="246" t="n"/>
@@ -12364,7 +13328,7 @@
       <c r="Y61" s="35" t="n"/>
       <c r="Z61" s="32" t="n"/>
     </row>
-    <row r="62" ht="335" customHeight="1">
+    <row r="62">
       <c r="A62" s="45" t="inlineStr">
         <is>
           <t>QUADRA INFANTIL</t>
@@ -12372,7 +13336,8 @@
       </c>
       <c r="B62" s="245" t="inlineStr">
         <is>
-          <t>17 - Piso em concreto com acabamento em pintura epóxi nas cores verde e cinza, tons a definir. Faixa de pintura epóxi na cor branca, para a marcação do desenho da miniquadra infantil.</t>
+          <t>17 - Piso em concreto com acabamento em pintura epóxi nas cores verde e cinza, tons a definir. Faixa de pintura epóxi na cor branca, para a marcação do desenho da miniquadra infantil.
+ARQ-P17 - Piso em concreto com acabamento em pintura epóxi nas cores cinza e verde, tons a definir. Faixa de pintura epóxi na cor branca, para marcação do desenho de mini quadra infantil. Verificar dimensões conforme detalhamento.</t>
         </is>
       </c>
       <c r="C62" s="32" t="n"/>
@@ -12382,7 +13347,8 @@
       <c r="G62" s="32" t="n"/>
       <c r="H62" s="245" t="inlineStr">
         <is>
-          <t>06 - Pintura acrílica fosca cinza tom a definir| Meia parede pintada com tinha acrílica fosca na cor verde, tom a definir - Reboco (2 demãos Latex acrílico)</t>
+          <t>06 - Pintura acrílica fosca cinza tom a definir| Meia parede pintada com tinha acrílica fosca na cor verde, tom a definir - Reboco (2 demãos Latex acrílico)
+ARQ-PA06 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza tom a definir. Meia parede pintada com tinta acrílica fosca na cor verde, tom a definir. Verificar altura conforme detalhamento.</t>
         </is>
       </c>
       <c r="I62" s="245" t="n"/>
@@ -12446,7 +13412,50 @@
       <c r="Y63" s="35" t="n"/>
       <c r="Z63" s="32" t="n"/>
     </row>
-    <row r="64" ht="2.1" customHeight="1"/>
+    <row r="64">
+      <c r="A64" s="45" t="inlineStr">
+        <is>
+          <t>CIRCULAÇÃO JUNTO À ESCADA (A=2,91 m²)</t>
+        </is>
+      </c>
+      <c r="B64" s="277" t="inlineStr">
+        <is>
+          <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="n"/>
+      <c r="D64" s="35" t="n"/>
+      <c r="E64" s="37" t="n"/>
+      <c r="F64" s="246" t="n"/>
+      <c r="G64" s="32" t="n"/>
+      <c r="H64" s="277" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+      <c r="I64" s="277" t="inlineStr">
+        <is>
+          <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+      <c r="J64" s="245" t="n"/>
+      <c r="K64" s="246" t="n"/>
+      <c r="L64" s="245" t="n"/>
+      <c r="M64" s="37" t="n"/>
+      <c r="N64" s="38" t="n"/>
+      <c r="O64" s="245" t="n"/>
+      <c r="P64" s="31" t="n"/>
+      <c r="Q64" s="32" t="n"/>
+      <c r="R64" s="35" t="n"/>
+      <c r="S64" s="35" t="n"/>
+      <c r="T64" s="35" t="n"/>
+      <c r="U64" s="32" t="n"/>
+      <c r="V64" s="31" t="n"/>
+      <c r="W64" s="35" t="n"/>
+      <c r="X64" s="35" t="n"/>
+      <c r="Y64" s="35" t="n"/>
+      <c r="Z64" s="32" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="L10:U10"/>
@@ -13443,7 +14452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E325"/>
+  <dimension ref="A1:E532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -20613,6 +21622,4999 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="279" t="inlineStr">
+        <is>
+          <t>5. ESPECIFICAÇÕES DAS PLANTAS DE ARQUITETURA (CDJ-ARQ-EX PR003–PR013, Quadro de Especificações - Geral)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="280" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B328" s="280" t="inlineStr">
+        <is>
+          <t>PAVIMENTO / AMBIENTE</t>
+        </is>
+      </c>
+      <c r="C328" s="280" t="inlineStr">
+        <is>
+          <t>COLUNA</t>
+        </is>
+      </c>
+      <c r="D328" s="280" t="inlineStr">
+        <is>
+          <t>ANTES</t>
+        </is>
+      </c>
+      <c r="E328" s="280" t="inlineStr">
+        <is>
+          <t>ARQUITETURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="287" t="n">
+        <v>1</v>
+      </c>
+      <c r="B329" s="287" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C329" s="287" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D329" s="287" t="inlineStr">
+        <is>
+          <t>CONFLITO: P5 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Rejunte Infinity Hard cor Mocha ou cor Branco Pérola Deverá ser testado as duas opções de rejunte para escolher a que mais se aproxima do tom da peça. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="E329" s="287" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="287" t="n">
+        <v>3</v>
+      </c>
+      <c r="B331" s="287" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C331" s="287" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D331" s="287" t="inlineStr">
+        <is>
+          <t>CONFLITO: PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+      <c r="E331" s="287" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>4</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>TÉRREO – GUARITA</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>5</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>TÉRREO – LAVABO GUARITA</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>6</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>TÉRREO – LAVABO GUARITA</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>7</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>TÉRREO – LAVABO GUARITA</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>8</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>TÉRREO – LAVABO GUARITA</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>9</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO GUARITA</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>10</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO GUARITA</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>11</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO GUARITA</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>12</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO GUARITA</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>13</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>14</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>15</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>16</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>17</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>TÉRREO – GARAGEM</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>18</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>TÉRREO – GARAGEM</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>19</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>TÉRREO – GARAGEM</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>20</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>TÉRREO – CASA DE BOMBAS</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>21</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>TÉRREO – CASA DE BOMBAS</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>22</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>TÉRREO – CASA DE BOMBAS</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>23</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>24</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>25</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>26</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>27</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>TÉRREO – CONCIERGE</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>28</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>TÉRREO – CONCIERGE</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>29</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>TÉRREO – CONCIERGE</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>30</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>TÉRREO – CONCIERGE</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ARQ-T19 - código não existe no quadro de tetos (01 a 06); conferir na planta</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>31</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>TÉRREO – DELIVERY</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>32</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>TÉRREO – DELIVERY</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>33</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>TÉRREO – DELIVERY</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>34</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>TÉRREO – DELIVERY</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>35</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>36</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>37</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>38</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>39</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>TÉRREO – CAR WASH</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>40</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>TÉRREO – CAR WASH</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>41</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>TÉRREO – CAR WASH</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>42</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>TÉRREO – BICICLETÁRIO</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>43</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>TÉRREO – BICICLETÁRIO</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>44</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>TÉRREO – BICICLETÁRIO</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>45</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>TÉRREO – ZELADORIA</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>46</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>TÉRREO – ZELADORIA</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>47</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>TÉRREO – ZELADORIA</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>48</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>TÉRREO – ZELADORIA</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>49</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 1</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>50</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 1</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>51</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 1</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>52</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 2</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>53</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 2</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>54</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 2</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>55</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 3</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>56</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 3</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>57</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 3</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>58</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>TÉRREO – SALA MOTORISTA</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>ARQ-P06 - Piso em porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>59</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>TÉRREO – SALA MOTORISTA</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>60</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>TÉRREO – SALA MOTORISTA</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>61</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>TÉRREO – SALA MOTORISTA</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>62</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>TÉRREO – DML</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>63</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>TÉRREO – DML</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>64</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>TÉRREO – DML</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>65</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>66</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>67</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. P.C.D</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>68</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. FEMININO</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>69</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. FEMININO</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>70</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. FEMININO</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>71</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. MASC.</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>72</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. MASC.</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>73</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>TÉRREO – VEST. MASC.</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>74</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTAR/COPA FUNCIONÁRIOS</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>75</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTAR/COPA FUNCIONÁRIOS</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>76</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTAR/COPA FUNCIONÁRIOS</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>77</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>78</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>79</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>80</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>81</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>TÉRREO – GERADOR</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>82</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TÉRREO – GERADOR</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>83</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>TÉRREO – GERADOR</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>84</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>TÉRREO – VAGAS BOX</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>85</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>TÉRREO – VAGAS BOX</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>86</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>TÉRREO – VAGAS BOX</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>87</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>TÉRREO – QUADROS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>88</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>TÉRREO – QUADROS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>89</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>TÉRREO – QUADROS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>90</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>TÉRREO – ACESSO E SAÍDA DE VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>91</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>TÉRREO – ACESSO E SAÍDA DE VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>92</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>TÉRREO – ACESSO E SAÍDA DE VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>93</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTACIONAMENTO VISITANTES</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>94</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTACIONAMENTO VISITANTES</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>95</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTACIONAMENTO VISITANTES</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>96</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>TÉRREO – ESTACIONAMENTO VISITANTES</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>97</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>TÉRREO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>98</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>TÉRREO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>99</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>TÉRREO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>100</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>TÉRREO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>101</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>TÉRREO – DEPÓSITO (A=8,85 m²)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>102</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>TÉRREO – DEPÓSITO (A=8,85 m²)</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>103</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>TÉRREO – DEPÓSITO (A=8,85 m²)</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>104</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>TÉRREO – DEPÓSITO (A=8,85 m²)</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>105</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>TÉRREO – SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>106</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>TÉRREO – SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>107</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>TÉRREO – SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>108</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>TÉRREO – SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>109</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>TÉRREO – SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>110</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO JUNTO À ESCADA (A=4,06 m²)</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>111</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO JUNTO À ESCADA (A=4,06 m²)</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>112</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO JUNTO À ESCADA (A=4,06 m²)</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>113</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>TÉRREO – CIRCULAÇÃO JUNTO À ESCADA (A=4,06 m²)</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>114</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CASA DE BOMBAS PISCINA 1</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>115</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CASA DE BOMBAS PISCINA 1</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>116</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CASA DE BOMBAS PISCINA 1</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>117</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2° PAVTO – SHAFT ELÉTRICA</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>118</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2° PAVTO – SHAFT ELÉTRICA</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>119</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2° PAVTO – SHAFT ELÉTRICA</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>120</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>121</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>122</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>123</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil | ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>124</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2° PAVTO – PRESSURIZAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>125</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2° PAVTO – PRESSURIZAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>126</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2° PAVTO – PRESSURIZAÇÃO/ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>127</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2° PAVTO – ÁREA TÉCNICA 1</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>128</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2° PAVTO – ÁREA TÉCNICA 1</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>129</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2° PAVTO – ÁREA TÉCNICA 1</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>130</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2° PAVTO – ÁREA TÉCNICA 2</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>131</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2° PAVTO – ÁREA TÉCNICA 2</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>132</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2° PAVTO – ÁREA TÉCNICA 2</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>133</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2° PAVTO – GARAGEM</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>134</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2° PAVTO – GARAGEM</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>135</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2° PAVTO – GARAGEM</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>136</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2° PAVTO – VAGAS BOX</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>137</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2° PAVTO – VAGAS BOX</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>138</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2° PAVTO – VAGAS BOX</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>139</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2° PAVTO – TELECOM</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>140</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2° PAVTO – TELECOM</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>141</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2° PAVTO – TELECOM</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>142</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2° PAVTO – SALA DE SEGURANÇA</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>143</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2° PAVTO – SALA DE SEGURANÇA</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>144</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2° PAVTO – SALA DE SEGURANÇA</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>145</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CASA DE BOMBAS PISCINA 2 (FUNDO)</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>146</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CASA DE BOMBAS PISCINA 2 (FUNDO)</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>147</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CASA DE BOMBAS PISCINA 2 (FUNDO)</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>148</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2° PAVTO – DML</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>149</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2° PAVTO – DML</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>150</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2° PAVTO – DML</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>151</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RESERVATÓRIO INFERIOR</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>152</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RESERVATÓRIO INFERIOR</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>153</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RESERVATÓRIO INFERIOR</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>154</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2° PAVTO – HALL TÉCNICO/CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>155</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2° PAVTO – HALL TÉCNICO/CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>156</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2° PAVTO – HALL TÉCNICO/CIRCULAÇÃO</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>157</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>158</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>ARQ-P04 - Piso em concreto mecanizado com acabamento em ladrilho hidráulico antiderrapante cinza, tom concreto. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>159</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>160</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2° PAVTO – RAMPA VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>161</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO ÁREA TÉCNICA (A=14,54 m²)</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>162</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO ÁREA TÉCNICA (A=14,54 m²)</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>163</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO ÁREA TÉCNICA (A=14,54 m²)</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>164</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO ÁREA TÉCNICA (A=14,54 m²)</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>165</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO JUNTO À ESCADA (A=3,07 m²)</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>166</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO JUNTO À ESCADA (A=3,07 m²)</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>167</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO JUNTO À ESCADA (A=3,07 m²)</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>168</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2° PAVTO – CIRCULAÇÃO JUNTO À ESCADA (A=3,07 m²)</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>169</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>170</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>171</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>172</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>173</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>PILOTIS – ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>07 - Piso de granito cinza santa rosa, acabamento serrado, espessura: 2cm, dimensões e paginação conforme detalhamento, assentado com argamassa colante em pó ACIII. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>174</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>PILOTIS – ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>175</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>PILOTIS – ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>176</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>PILOTIS – ANTECÂMARA</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>177</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>PILOTIS – QUADRA TÊNIS</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>16 - Piso em pó de saibro com faixa na cor branca para marcação de quadra de tênis fixada com pregos especiais</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-P16 - Piso em pó de saibro com faixa na cor branca para marcação de quadra de tênis fixada com pregos especiais. Verificar detalhes no projeto específico de quadra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>178</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>PILOTIS – QUADRA TÊNIS</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>03 - Pintura acrílica fosca cinza tom a definir - Reboco (2 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-PA03 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza, tom a definir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>179</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>PILOTIS – QUADRA TÊNIS</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>ARQ-T05 - Cobertura em telha sanduíche com estrutura espacial pintadas na cor cinza tom a definir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>180</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEP JARDIM</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>181</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEP JARDIM</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>182</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEP JARDIM</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII | 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>183</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEP JARDIM</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>184</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEPÓSITO</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>185</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEPÓSITO</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>186</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEPÓSITO</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII | 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>187</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>PILOTIS – DEPÓSITO</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>188</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>PILOTIS – QUADRA INFANTIL</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>17 - Piso em concreto com acabamento em pintura epóxi nas cores verde e cinza, tons a definir. Faixa de pintura epóxi na cor branca, para a marcação do desenho da miniquadra infantil.</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-P17 - Piso em concreto com acabamento em pintura epóxi nas cores cinza e verde, tons a definir. Faixa de pintura epóxi na cor branca, para marcação do desenho de mini quadra infantil. Verificar dimensões conforme detalhamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>189</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>PILOTIS – QUADRA INFANTIL</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>06 - Pintura acrílica fosca cinza tom a definir| Meia parede pintada com tinha acrílica fosca na cor verde, tom a definir - Reboco (2 demãos Latex acrílico)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-PA06 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza tom a definir. Meia parede pintada com tinta acrílica fosca na cor verde, tom a definir. Verificar altura conforme detalhamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>190</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESCADA EXTERNA</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>07| P28 - Piso de granito Santa rosa, acabamento serrado. Espessura de 2cm. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>mesma especificação na arquitetura: ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>191</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>PILOTIS – ESCADA EXTERNA</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>ARQ-PA06 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza tom a definir. Meia parede pintada com tinta acrílica fosca na cor verde, tom a definir. Verificar altura conforme detalhamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>192</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO JUNTO À ESCADA (A=2,91 m²)</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>linha nova</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>planta de arquitetura</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>193</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO JUNTO À ESCADA (A=2,91 m²)</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>194</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO JUNTO À ESCADA (A=2,91 m²)</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>195</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÃO JUNTO À ESCADA (A=2,91 m²)</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Legenda das plantas</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Etiqueta ○ = piso, △ = parede (códigos 01 a 18) ou rodapé (19 a 25), □ = teto. Na grade os códigos aparecem como ARQ-P (piso), ARQ-PA (parede), ARQ-RD (rodapé) e ARQ-T (teto) para não confundir com os códigos do detalhamento de interiores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Ambientes "ACABAMENTOS VER INTERIORES"</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Lobby, hall de elevadores, antecâmara/eclusa, I.S. P.C.D., vestíbulo (Térreo), halls do 2º pav. e a maior parte do Pilotis remetem ao projeto de interiores; nesses ambientes vale o detalhamento R04 já lançado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>TÉRREO – CONCIERGE</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>A etiqueta de teto da planta PR003 traz □19, mas o quadro de tetos só vai de 01 a 06. Provável erro de etiqueta; confirmar com a arquitetura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>TÉRREO – ARS 1, 2 e 3</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>A planta tem três A.R.S. (24,09 m², 14,93 m² e 4,25 m²) com a mesma especificação; a ordem 1-2-3 da grade foi assumida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>TÉRREO – DML E JARDINAGEM</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Sem etiqueta de acabamento na planta PR003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>PR008 e PR012</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Pranchas de revisão anterior (R11 e R13 de 2025) às demais; não foram usadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Portas, janelas e guarda-corpos</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Os quadros de esquadrias das plantas não foram lançados na grade nesta etapa.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -10,8 +10,9 @@
     <sheet name="TÉRREO " sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2° PAVTO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="PILOTIS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IMAGENS ESPECIFICAÇÕES " sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="PENDÊNCIAS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="APTO TIPO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="IMAGENS ESPECIFICAÇÕES " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PENDÊNCIAS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'TÉRREO '!$1:$11,'TÉRREO '!$A:$A</definedName>
@@ -20,8 +21,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2° PAVTO'!$A$1:$AF$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'PILOTIS'!$1:$11,'PILOTIS'!$A:$A</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PILOTIS'!$A$1:$AF$63</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'IMAGENS ESPECIFICAÇÕES '!$1:$11,'IMAGENS ESPECIFICAÇÕES '!$A:$A</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'IMAGENS ESPECIFICAÇÕES '!$A$1:$U$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'IMAGENS ESPECIFICAÇÕES '!$1:$11,'IMAGENS ESPECIFICAÇÕES '!$A:$A</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'IMAGENS ESPECIFICAÇÕES '!$A$1:$U$26</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="61">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -393,6 +394,12 @@
       <color rgb="FF9C0006"/>
       <sz val="16"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="48"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1367,7 +1374,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="288">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2138,6 +2145,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="60" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3919,6 +3929,548 @@
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>1368136</colOff>
+      <row>7</row>
+      <rowOff>454083</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagem 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3414278" y="2501610"/>
+          <a:ext cx="935183" cy="924273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>831275</colOff>
+      <row>0</row>
+      <rowOff>103909</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>2753592</colOff>
+      <row>3</row>
+      <rowOff>335785</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Imagem 6"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill rotWithShape="1">
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:srcRect b="16485"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="831275" y="103909"/>
+          <a:ext cx="1922317" cy="1470126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>9</col>
+      <colOff>2247902</colOff>
+      <row>0</row>
+      <rowOff>100446</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>1780310</colOff>
+      <row>3</row>
+      <rowOff>332322</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Imagem 7"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill rotWithShape="1">
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:srcRect b="16485"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="25650827" y="100446"/>
+          <a:ext cx="1913658" cy="1470126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>19</col>
+      <colOff>1513612</colOff>
+      <row>0</row>
+      <rowOff>128154</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>1046020</colOff>
+      <row>4</row>
+      <rowOff>2843</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Imagem 8"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill rotWithShape="1">
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:srcRect b="16485"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="49910137" y="128154"/>
+          <a:ext cx="1913658" cy="1470126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>30</col>
+      <colOff>1437412</colOff>
+      <row>0</row>
+      <rowOff>69272</rowOff>
+    </from>
+    <to>
+      <col>31</col>
+      <colOff>969820</colOff>
+      <row>3</row>
+      <rowOff>301148</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Imagem 9"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill rotWithShape="1">
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:srcRect b="16485"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="76218187" y="69272"/>
+          <a:ext cx="1913658" cy="1470126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="944708"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagem 2"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="29779478" y="2501610"/>
+          <a:ext cx="935183" cy="944708"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="944708"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Imagem 3"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="53591978" y="2501610"/>
+          <a:ext cx="935183" cy="944708"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="927787"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Imagem 4"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="29779478" y="2501610"/>
+          <a:ext cx="935183" cy="927787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="927787"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Imagem 5"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="53591978" y="2501610"/>
+          <a:ext cx="935183" cy="927787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="921675"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Imagem 10"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="29779478" y="2501610"/>
+          <a:ext cx="935183" cy="921675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="921675"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Imagem 11"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="53591978" y="2501610"/>
+          <a:ext cx="935183" cy="921675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="944708"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Imagem 12"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="53591978" y="2501610"/>
+          <a:ext cx="935183" cy="944708"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="927787"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Imagem 13"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="53591978" y="2501610"/>
+          <a:ext cx="935183" cy="927787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>432953</colOff>
+      <row>6</row>
+      <rowOff>34635</rowOff>
+    </from>
+    <ext cx="935183" cy="921675"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Imagem 14"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm flipH="1">
+          <a:off x="53591978" y="2501610"/>
+          <a:ext cx="935183" cy="921675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
       <colOff>394853</colOff>
       <row>4</row>
       <rowOff>72735</rowOff>
@@ -9787,9 +10339,6 @@
       <c r="Y31" s="31" t="n"/>
       <c r="Z31" s="35" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="S35" s="3" t="inlineStr">
         <is>
@@ -13515,6 +14064,1649 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AF35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
+  <cols>
+    <col width="50.140625" customWidth="1" style="14" min="1" max="1"/>
+    <col width="56.28515625" customWidth="1" style="3" min="2" max="2"/>
+    <col width="35.7109375" customWidth="1" style="3" min="3" max="10"/>
+    <col width="53.42578125" customWidth="1" style="3" min="11" max="11"/>
+    <col width="35.7109375" customWidth="1" style="3" min="12" max="25"/>
+    <col width="38.5703125" customWidth="1" style="3" min="26" max="26"/>
+    <col width="35.7109375" customWidth="1" style="3" min="27" max="32"/>
+    <col width="9.140625" customWidth="1" style="3" min="33" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34.5" customHeight="1">
+      <c r="A1" s="153" t="n"/>
+      <c r="B1" s="137" t="inlineStr">
+        <is>
+          <t>GRADE DE ESPECIFICAÇÕES – APARTAMENTO TIPO
+EDIFÍCIO JARDIM</t>
+        </is>
+      </c>
+      <c r="C1" s="209" t="n"/>
+      <c r="D1" s="209" t="n"/>
+      <c r="E1" s="209" t="n"/>
+      <c r="F1" s="209" t="n"/>
+      <c r="G1" s="209" t="n"/>
+      <c r="H1" s="209" t="n"/>
+      <c r="I1" s="208" t="n"/>
+      <c r="J1" s="113" t="n"/>
+      <c r="K1" s="208" t="n"/>
+      <c r="L1" s="137">
+        <f>B1</f>
+        <v/>
+      </c>
+      <c r="M1" s="209" t="n"/>
+      <c r="N1" s="209" t="n"/>
+      <c r="O1" s="209" t="n"/>
+      <c r="P1" s="209" t="n"/>
+      <c r="Q1" s="209" t="n"/>
+      <c r="R1" s="209" t="n"/>
+      <c r="S1" s="208" t="n"/>
+      <c r="T1" s="113" t="n"/>
+      <c r="U1" s="208" t="n"/>
+      <c r="V1" s="137">
+        <f>B1</f>
+        <v/>
+      </c>
+      <c r="W1" s="209" t="n"/>
+      <c r="X1" s="209" t="n"/>
+      <c r="Y1" s="209" t="n"/>
+      <c r="Z1" s="209" t="n"/>
+      <c r="AA1" s="209" t="n"/>
+      <c r="AB1" s="209" t="n"/>
+      <c r="AC1" s="209" t="n"/>
+      <c r="AD1" s="208" t="n"/>
+      <c r="AE1" s="113" t="n"/>
+      <c r="AF1" s="208" t="n"/>
+    </row>
+    <row r="2" ht="28.5" customHeight="1">
+      <c r="A2" s="238" t="n"/>
+      <c r="B2" s="210" t="n"/>
+      <c r="I2" s="211" t="n"/>
+      <c r="J2" s="210" t="n"/>
+      <c r="K2" s="211" t="n"/>
+      <c r="L2" s="210" t="n"/>
+      <c r="S2" s="211" t="n"/>
+      <c r="T2" s="210" t="n"/>
+      <c r="U2" s="211" t="n"/>
+      <c r="V2" s="210" t="n"/>
+      <c r="AD2" s="211" t="n"/>
+      <c r="AE2" s="210" t="n"/>
+      <c r="AF2" s="211" t="n"/>
+    </row>
+    <row r="3" ht="34.5" customHeight="1">
+      <c r="A3" s="238" t="n"/>
+      <c r="B3" s="210" t="n"/>
+      <c r="I3" s="211" t="n"/>
+      <c r="J3" s="210" t="n"/>
+      <c r="K3" s="211" t="n"/>
+      <c r="L3" s="210" t="n"/>
+      <c r="S3" s="211" t="n"/>
+      <c r="T3" s="210" t="n"/>
+      <c r="U3" s="211" t="n"/>
+      <c r="V3" s="210" t="n"/>
+      <c r="AD3" s="211" t="n"/>
+      <c r="AE3" s="210" t="n"/>
+      <c r="AF3" s="211" t="n"/>
+    </row>
+    <row r="4" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A4" s="239" t="n"/>
+      <c r="B4" s="213" t="n"/>
+      <c r="C4" s="216" t="n"/>
+      <c r="D4" s="216" t="n"/>
+      <c r="E4" s="216" t="n"/>
+      <c r="F4" s="216" t="n"/>
+      <c r="G4" s="216" t="n"/>
+      <c r="H4" s="216" t="n"/>
+      <c r="I4" s="214" t="n"/>
+      <c r="J4" s="213" t="n"/>
+      <c r="K4" s="214" t="n"/>
+      <c r="L4" s="213" t="n"/>
+      <c r="M4" s="216" t="n"/>
+      <c r="N4" s="216" t="n"/>
+      <c r="O4" s="216" t="n"/>
+      <c r="P4" s="216" t="n"/>
+      <c r="Q4" s="216" t="n"/>
+      <c r="R4" s="216" t="n"/>
+      <c r="S4" s="214" t="n"/>
+      <c r="T4" s="213" t="n"/>
+      <c r="U4" s="214" t="n"/>
+      <c r="V4" s="213" t="n"/>
+      <c r="W4" s="216" t="n"/>
+      <c r="X4" s="216" t="n"/>
+      <c r="Y4" s="216" t="n"/>
+      <c r="Z4" s="216" t="n"/>
+      <c r="AA4" s="216" t="n"/>
+      <c r="AB4" s="216" t="n"/>
+      <c r="AC4" s="216" t="n"/>
+      <c r="AD4" s="214" t="n"/>
+      <c r="AE4" s="213" t="n"/>
+      <c r="AF4" s="214" t="n"/>
+    </row>
+    <row r="5" ht="39.95" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="127" t="inlineStr">
+        <is>
+          <t>PADRÃO DE FORMATAÇÃO: ITEM, LINHA, MARCA, TAMANHO, COR E/OU ACABAMENTOS. CÓDIGO. COR DE REJUNTE.</t>
+        </is>
+      </c>
+      <c r="C5" s="209" t="n"/>
+      <c r="D5" s="209" t="n"/>
+      <c r="E5" s="209" t="n"/>
+      <c r="F5" s="209" t="n"/>
+      <c r="G5" s="209" t="n"/>
+      <c r="H5" s="209" t="n"/>
+      <c r="I5" s="208" t="n"/>
+      <c r="J5" s="119" t="inlineStr">
+        <is>
+          <t>XXXXXXX</t>
+        </is>
+      </c>
+      <c r="K5" s="240" t="n"/>
+      <c r="L5" s="127" t="inlineStr">
+        <is>
+          <t>*ATENÇÃO: PARA TODOS OS REJUNTES, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO
+COM PROJETOS EXECUTIVOS DE ACORDO COM ALTURA DO CONTRAPISO</t>
+        </is>
+      </c>
+      <c r="M5" s="209" t="n"/>
+      <c r="N5" s="209" t="n"/>
+      <c r="O5" s="209" t="n"/>
+      <c r="P5" s="209" t="n"/>
+      <c r="Q5" s="209" t="n"/>
+      <c r="R5" s="209" t="n"/>
+      <c r="S5" s="208" t="n"/>
+      <c r="T5" s="119" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="U5" s="240" t="n"/>
+      <c r="V5" s="127" t="inlineStr">
+        <is>
+          <t>*ATENÇÃO: PARA TODOS OS REJUNTES, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO
+COM PROJETOS EXECUTIVOS DE ACORDO COM ALTURA DO CONTRAPISO</t>
+        </is>
+      </c>
+      <c r="W5" s="209" t="n"/>
+      <c r="X5" s="209" t="n"/>
+      <c r="Y5" s="209" t="n"/>
+      <c r="Z5" s="209" t="n"/>
+      <c r="AA5" s="209" t="n"/>
+      <c r="AB5" s="209" t="n"/>
+      <c r="AC5" s="209" t="n"/>
+      <c r="AD5" s="208" t="n"/>
+      <c r="AE5" s="119" t="inlineStr">
+        <is>
+          <t>XXXXXX</t>
+        </is>
+      </c>
+      <c r="AF5" s="240" t="n"/>
+    </row>
+    <row r="6" ht="28.5" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="B6" s="213" t="n"/>
+      <c r="C6" s="216" t="n"/>
+      <c r="D6" s="216" t="n"/>
+      <c r="E6" s="216" t="n"/>
+      <c r="F6" s="216" t="n"/>
+      <c r="G6" s="216" t="n"/>
+      <c r="H6" s="216" t="n"/>
+      <c r="I6" s="214" t="n"/>
+      <c r="J6" s="201" t="inlineStr">
+        <is>
+          <t>RESPONSÁVEL</t>
+        </is>
+      </c>
+      <c r="K6" s="221" t="n"/>
+      <c r="L6" s="213" t="n"/>
+      <c r="M6" s="216" t="n"/>
+      <c r="N6" s="216" t="n"/>
+      <c r="O6" s="216" t="n"/>
+      <c r="P6" s="216" t="n"/>
+      <c r="Q6" s="216" t="n"/>
+      <c r="R6" s="216" t="n"/>
+      <c r="S6" s="214" t="n"/>
+      <c r="T6" s="201" t="inlineStr">
+        <is>
+          <t>RESPONSÁVEL</t>
+        </is>
+      </c>
+      <c r="U6" s="221" t="n"/>
+      <c r="V6" s="213" t="n"/>
+      <c r="W6" s="216" t="n"/>
+      <c r="X6" s="216" t="n"/>
+      <c r="Y6" s="216" t="n"/>
+      <c r="Z6" s="216" t="n"/>
+      <c r="AA6" s="216" t="n"/>
+      <c r="AB6" s="216" t="n"/>
+      <c r="AC6" s="216" t="n"/>
+      <c r="AD6" s="214" t="n"/>
+      <c r="AE6" s="201" t="inlineStr">
+        <is>
+          <t>RESPONSÁVEL</t>
+        </is>
+      </c>
+      <c r="AF6" s="221" t="n"/>
+    </row>
+    <row r="7" ht="39.95" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>REV. R00</t>
+        </is>
+      </c>
+      <c r="B7" s="131" t="inlineStr">
+        <is>
+          <t>*ATENÇÃO: PARA TODOS OS REJUNTES E TEXTURAS, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO ARQUITETURA DE ACORDO COM ALTURA DO CONTRAPISO. A DEFINIÇÃO DA ALTURA DE RODABANCAS E TESTEIRAS DEVEM SER DEFINIDAS CASO A CASO CONFORME IMAGENS E/OU ELEMENTOS DO PROJETO, COMO PEITORIL E PAGINAÇÃO DA PAREDE. QUANDO O REVESTIMENTO DA PAREDE NÃO FOR CERÂMICO, CONSIDERAR UMA ALTURA MAIOR DE RODABANCA. AS ESPECIFICAÇÕES PODERAM SER ALTERADAS CONFORME DISPONIBILIDADE DE MERCADO, VALIDAR JUNTO A ARQUITETURA CASO NO MOMENTO DA COMPRA O ITEM TENHA SAÍDO DE LINHA.</t>
+        </is>
+      </c>
+      <c r="C7" s="209" t="n"/>
+      <c r="D7" s="209" t="n"/>
+      <c r="E7" s="209" t="n"/>
+      <c r="F7" s="209" t="n"/>
+      <c r="G7" s="209" t="n"/>
+      <c r="H7" s="209" t="n"/>
+      <c r="I7" s="208" t="n"/>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO. ANTERIOR </t>
+        </is>
+      </c>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO. REVISADA </t>
+        </is>
+      </c>
+      <c r="L7" s="131" t="inlineStr">
+        <is>
+          <t>*ATENÇÃO: PARA TODOS OS REJUNTES E TEXTURAS, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO ARQUITETURA DE ACORDO COM ALTURA DO CONTRAPISO. A DEFINIÇÃO DA ALTURA DE RODABANCAS E TESTEIRAS DEVEM SER DEFINIDAS CASO A CASO CONFORME IMAGENS E/OU ELEMENTOS DO PROJETO, COMO PEITORIL E PAGINAÇÃO DA PAREDE. QUANDO O REVESTIMENTO DA PAREDE NÃO FOR CERÂMICO, CONSIDERAR UMA ALTURA MAIOR DE RODABANCA. AS ESPECIFICAÇÕES PODERAM SER ALTERADAS CONFORME DISPONIBILIDADE DE MERCADO, VALIDAR JUNTO A ARQUITETURA CASO NO MOMENTO DA COMPRA O ITEM TENHA SAÍDO DE LINHA.</t>
+        </is>
+      </c>
+      <c r="M7" s="209" t="n"/>
+      <c r="N7" s="209" t="n"/>
+      <c r="O7" s="209" t="n"/>
+      <c r="P7" s="209" t="n"/>
+      <c r="Q7" s="209" t="n"/>
+      <c r="R7" s="209" t="n"/>
+      <c r="S7" s="208" t="n"/>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO. ANTERIOR </t>
+        </is>
+      </c>
+      <c r="U7" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO. REVISADA </t>
+        </is>
+      </c>
+      <c r="V7" s="146" t="inlineStr">
+        <is>
+          <t>*ATENÇÃO: PARA TODOS OS REJUNTES E TEXTURAS, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO ARQUITETURA DE ACORDO COM ALTURA DO CONTRAPISO. A DEFINIÇÃO DA ALTURA DE RODABANCAS E TESTEIRAS DEVEM SER DEFINIDAS CASO A CASO CONFORME IMAGENS E/OU ELEMENTOS DO PROJETO, COMO PEITORIL E PAGINAÇÃO DA PAREDE. QUANDO O REVESTIMENTO DA PAREDE NÃO FOR CERÂMICO, CONSIDERAR UMA ALTURA MAIOR DE RODABANCA. AS ESPECIFICAÇÕES PODERAM SER ALTERADAS CONFORME DISPONIBILIDADE DE MERCADO, VALIDAR JUNTO A ARQUITETURA CASO NO MOMENTO DA COMPRA O ITEM TENHA SAÍDO DE LINHA.</t>
+        </is>
+      </c>
+      <c r="W7" s="209" t="n"/>
+      <c r="X7" s="209" t="n"/>
+      <c r="Y7" s="209" t="n"/>
+      <c r="Z7" s="209" t="n"/>
+      <c r="AA7" s="209" t="n"/>
+      <c r="AB7" s="209" t="n"/>
+      <c r="AC7" s="209" t="n"/>
+      <c r="AD7" s="208" t="n"/>
+      <c r="AE7" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO. ANTERIOR </t>
+        </is>
+      </c>
+      <c r="AF7" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO. REVISADA </t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>REVISÃO</t>
+        </is>
+      </c>
+      <c r="B8" s="213" t="n"/>
+      <c r="C8" s="216" t="n"/>
+      <c r="D8" s="216" t="n"/>
+      <c r="E8" s="216" t="n"/>
+      <c r="F8" s="216" t="n"/>
+      <c r="G8" s="216" t="n"/>
+      <c r="H8" s="216" t="n"/>
+      <c r="I8" s="214" t="n"/>
+      <c r="J8" s="121" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="K8" s="221" t="n"/>
+      <c r="L8" s="213" t="n"/>
+      <c r="M8" s="216" t="n"/>
+      <c r="N8" s="216" t="n"/>
+      <c r="O8" s="216" t="n"/>
+      <c r="P8" s="216" t="n"/>
+      <c r="Q8" s="216" t="n"/>
+      <c r="R8" s="216" t="n"/>
+      <c r="S8" s="214" t="n"/>
+      <c r="T8" s="121" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="U8" s="221" t="n"/>
+      <c r="V8" s="213" t="n"/>
+      <c r="W8" s="216" t="n"/>
+      <c r="X8" s="216" t="n"/>
+      <c r="Y8" s="216" t="n"/>
+      <c r="Z8" s="216" t="n"/>
+      <c r="AA8" s="216" t="n"/>
+      <c r="AB8" s="216" t="n"/>
+      <c r="AC8" s="216" t="n"/>
+      <c r="AD8" s="214" t="n"/>
+      <c r="AE8" s="121" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="AF8" s="221" t="n"/>
+    </row>
+    <row r="9" ht="14.1" customFormat="1" customHeight="1" s="6">
+      <c r="A9" s="5" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="K9" s="229" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="U9" s="229" t="n"/>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="11" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="10" t="n"/>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="281" t="inlineStr">
+        <is>
+          <t>INFO. CONFLITANTE (manter as duas)</t>
+        </is>
+      </c>
+      <c r="AF9" s="229" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="152" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="C10" s="216" t="n"/>
+      <c r="D10" s="216" t="n"/>
+      <c r="E10" s="216" t="n"/>
+      <c r="F10" s="216" t="n"/>
+      <c r="G10" s="216" t="n"/>
+      <c r="H10" s="216" t="n"/>
+      <c r="I10" s="216" t="n"/>
+      <c r="J10" s="216" t="n"/>
+      <c r="K10" s="214" t="n"/>
+      <c r="L10" s="152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOUÇAS E METAIS </t>
+        </is>
+      </c>
+      <c r="M10" s="216" t="n"/>
+      <c r="N10" s="216" t="n"/>
+      <c r="O10" s="216" t="n"/>
+      <c r="P10" s="216" t="n"/>
+      <c r="Q10" s="216" t="n"/>
+      <c r="R10" s="216" t="n"/>
+      <c r="S10" s="216" t="n"/>
+      <c r="T10" s="216" t="n"/>
+      <c r="U10" s="214" t="n"/>
+      <c r="V10" s="152" t="inlineStr">
+        <is>
+          <t>COMPLEMENTARES</t>
+        </is>
+      </c>
+      <c r="W10" s="216" t="n"/>
+      <c r="X10" s="216" t="n"/>
+      <c r="Y10" s="216" t="n"/>
+      <c r="Z10" s="214" t="n"/>
+    </row>
+    <row r="11" ht="93.75" customFormat="1" customHeight="1" s="12" thickBot="1">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>CÔMODO/AMBIENTE</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>SOLEIRA</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>FILETE</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>PEITORIL</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="inlineStr">
+        <is>
+          <t>SÓCULO</t>
+        </is>
+      </c>
+      <c r="H11" s="46" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="I11" s="46" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="K11" s="46" t="inlineStr">
+        <is>
+          <t>OUTROS REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="L11" s="46" t="inlineStr">
+        <is>
+          <t>LOUÇAS, CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="M11" s="46" t="inlineStr">
+        <is>
+          <t>VÁLVULAS DE CUBAS E TANQUES</t>
+        </is>
+      </c>
+      <c r="N11" s="46" t="inlineStr">
+        <is>
+          <t>SIFÕES</t>
+        </is>
+      </c>
+      <c r="O11" s="46" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="P11" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BACIAS SANITÁRIAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="46" t="inlineStr">
+        <is>
+          <t>DUCHAS HIGIÊNICAS</t>
+        </is>
+      </c>
+      <c r="R11" s="46" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS DE REGISTROS GERAL</t>
+        </is>
+      </c>
+      <c r="S11" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACIONAMENTO DE CHUVEIRO </t>
+        </is>
+      </c>
+      <c r="T11" s="46" t="inlineStr">
+        <is>
+          <t>RALOS</t>
+        </is>
+      </c>
+      <c r="U11" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTROS
+ LOUÇAS E METAIS </t>
+        </is>
+      </c>
+      <c r="V11" s="46" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS ELÉTRICOS</t>
+        </is>
+      </c>
+      <c r="W11" s="46" t="inlineStr">
+        <is>
+          <t>MAÇANETAS</t>
+        </is>
+      </c>
+      <c r="X11" s="46" t="inlineStr">
+        <is>
+          <t>PORTAS</t>
+        </is>
+      </c>
+      <c r="Y11" s="46" t="inlineStr">
+        <is>
+          <t>JANELAS</t>
+        </is>
+      </c>
+      <c r="Z11" s="46" t="inlineStr">
+        <is>
+          <t>OUTROS
+COMPLEMENTARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customFormat="1" customHeight="1" s="13" thickBot="1">
+      <c r="A12" s="51" t="n"/>
+      <c r="B12" s="124" t="inlineStr">
+        <is>
+          <t>GERAL — APARTAMENTO TIPO: TABELA JARDIM-ACABAMENTOS R01 E DETALHAMENTO CDJ_DET_EX PR001-PR008, CDJ-ARQ-DT PR406/407 E PR721-728</t>
+        </is>
+      </c>
+      <c r="C12" s="241" t="n"/>
+      <c r="D12" s="241" t="n"/>
+      <c r="E12" s="241" t="n"/>
+      <c r="F12" s="241" t="n"/>
+      <c r="G12" s="241" t="n"/>
+      <c r="H12" s="241" t="n"/>
+      <c r="I12" s="241" t="n"/>
+      <c r="J12" s="241" t="n"/>
+      <c r="K12" s="242" t="n"/>
+      <c r="L12" s="123" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="M12" s="241" t="n"/>
+      <c r="N12" s="241" t="n"/>
+      <c r="O12" s="241" t="n"/>
+      <c r="P12" s="241" t="n"/>
+      <c r="Q12" s="241" t="n"/>
+      <c r="R12" s="241" t="n"/>
+      <c r="S12" s="241" t="n"/>
+      <c r="T12" s="241" t="n"/>
+      <c r="U12" s="242" t="n"/>
+      <c r="V12" s="123" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="W12" s="241" t="n"/>
+      <c r="X12" s="241" t="n"/>
+      <c r="Y12" s="241" t="n"/>
+      <c r="Z12" s="242" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>SALA / VARANDA DA SALA</t>
+        </is>
+      </c>
+      <c r="B13" s="269" t="inlineStr">
+        <is>
+          <t>Piso em mármore travertino romano bruto, 85x130cm, paginação conforme detalhamento. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). (DET PR001/PR002; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="288" t="inlineStr">
+        <is>
+          <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR001/PR002)
+CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="n"/>
+      <c r="H13" s="271" t="inlineStr">
+        <is>
+          <t>Pintura acrílica cor branco neve, acabamento acetinado. (DET PR001; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I13" s="271" t="n"/>
+      <c r="J13" s="32" t="n"/>
+      <c r="K13" s="32" t="n"/>
+      <c r="L13" s="32" t="n"/>
+      <c r="M13" s="32" t="n"/>
+      <c r="N13" s="32" t="n"/>
+      <c r="O13" s="32" t="n"/>
+      <c r="P13" s="32" t="n"/>
+      <c r="Q13" s="32" t="n"/>
+      <c r="R13" s="32" t="n"/>
+      <c r="S13" s="32" t="n"/>
+      <c r="T13" s="32" t="inlineStr">
+        <is>
+          <t>Varanda: ralo linear oculto; caimento do piso para o ralo i=1%. (DET PR001)</t>
+        </is>
+      </c>
+      <c r="U13" s="32" t="n"/>
+      <c r="V13" s="32" t="n"/>
+      <c r="W13" s="32" t="n"/>
+      <c r="X13" s="31" t="n"/>
+      <c r="Y13" s="31" t="n"/>
+      <c r="Z13" s="32" t="inlineStr">
+        <is>
+          <t>Varanda: mureta h=90cm. (DET PR001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t>LAVABO</t>
+        </is>
+      </c>
+      <c r="B14" s="269" t="inlineStr">
+        <is>
+          <t>Piso em mármore travertino romano bruto. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). (DET PR004; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Soleira indicada em planta, material não especificado. (DET PR004)</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="288" t="inlineStr">
+        <is>
+          <t>Rodapé semi-embutido em mármore travertino romano bruto, h=15cm. (DET PR004)
+CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="271" t="inlineStr">
+        <is>
+          <t>Pintura acrílica cor branco neve, acabamento acetinado. (DET PR004; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I14" s="271" t="inlineStr">
+        <is>
+          <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica. PD 298cm. (DET PR004)</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr">
+        <is>
+          <t>Bancada esculpida em mármore travertino romano resinado (cuba esculpida). (DET PR004; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="K14" s="32" t="n"/>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="32" t="n"/>
+      <c r="N14" s="32" t="n"/>
+      <c r="O14" s="32" t="inlineStr">
+        <is>
+          <t>Torneira de mesa bica baixa para lavatório, cromado, linha Unic, cód. 1197.C90. Ref.: Deca. (DET PR004; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="P14" s="32" t="inlineStr">
+        <is>
+          <t>Bacia convencional suspensa branca, linha LK, cód. P.232.17. Ref.: Deca. Caixa de descarga embutida para alvenaria. (DET PR004; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="Q14" s="32" t="n"/>
+      <c r="R14" s="32" t="inlineStr">
+        <is>
+          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Unic, cód. 4900.C90.GD. Ref.: Deca
+Acabamento para caixa de descarga embutida, cromado, H Quadra Duo, cód. 4900.C.HQD.DUO. Ref.: Deca. (DET PR004)</t>
+        </is>
+      </c>
+      <c r="S14" s="32" t="n"/>
+      <c r="T14" s="32" t="inlineStr">
+        <is>
+          <t>Ralo oculto 15x15cm, tampa revestida com o mesmo mármore. (DET PR004)</t>
+        </is>
+      </c>
+      <c r="U14" s="32" t="n"/>
+      <c r="V14" s="32" t="n"/>
+      <c r="W14" s="32" t="inlineStr">
+        <is>
+          <t>Maçaneta Pado Sara, cromo acetinado, interna. (DET PR004)</t>
+        </is>
+      </c>
+      <c r="X14" s="31" t="inlineStr">
+        <is>
+          <t>Porta piso-forro, cor branca, alizar 10cm. (DET PR004)</t>
+        </is>
+      </c>
+      <c r="Y14" s="31" t="n"/>
+      <c r="Z14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>BANHO SUÍTE MASTER</t>
+        </is>
+      </c>
+      <c r="B15" s="269" t="inlineStr">
+        <is>
+          <t>Piso em mármore travertino romano bruto resinado, paginado conforme detalhamento. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="271" t="inlineStr">
+        <is>
+          <t>Parede em mármore travertino romano bruto paginado. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>Bancada em mármore travertino romano resinado. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>Cuba de apoio retangular Jader Almeida, branca. Ref.: Deca ou similar. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="M15" s="32" t="n"/>
+      <c r="N15" s="32" t="n"/>
+      <c r="O15" s="32" t="inlineStr">
+        <is>
+          <t>Misturador monocomando de mesa bica alta para lavatório, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="P15" s="32" t="inlineStr">
+        <is>
+          <t>Bacia convencional Carrara branca com caixa acoplada. Ref.: Deca ou similar
+Bidê 3 furos Carrara branco. Ref.: Deca ou similar. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="Q15" s="32" t="n"/>
+      <c r="R15" s="32" t="n"/>
+      <c r="S15" s="32" t="inlineStr">
+        <is>
+          <t>Acabamento de monocomando de chuveiro, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="T15" s="32" t="n"/>
+      <c r="U15" s="32" t="inlineStr">
+        <is>
+          <t>Misturador para bidê, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="V15" s="32" t="n"/>
+      <c r="W15" s="32" t="n"/>
+      <c r="X15" s="31" t="n"/>
+      <c r="Y15" s="31" t="n"/>
+      <c r="Z15" s="32" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>BANHO SUÍTES</t>
+        </is>
+      </c>
+      <c r="B16" s="269" t="inlineStr">
+        <is>
+          <t>Piso em mármore travertino romano bruto resinado, paginado. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). Desnível do box 1cm. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="271" t="inlineStr">
+        <is>
+          <t>Parede em mármore travertino romano bruto: piso ao teto na área do box e barrado semi-embutido até 110cm nas demais paredes; acima, pintura acrílica cor branco neve, acetinado. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I16" s="271" t="inlineStr">
+        <is>
+          <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica e sanca. PD 298cm. (DET PR008)</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr">
+        <is>
+          <t>Bancada esculpida em mármore travertino romano resinado. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="inlineStr">
+        <is>
+          <t>Cuba retangular de apoio 60cm com deck, branca, linha Slim, cód. L.13060.M.17. Ref.: Deca. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="M16" s="32" t="n"/>
+      <c r="N16" s="32" t="n"/>
+      <c r="O16" s="32" t="inlineStr">
+        <is>
+          <t>Misturador monocomando de mesa bica baixa para lavatório, cromado, linha Level, cód. 2875.C26. Ref.: Deca. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="P16" s="32" t="inlineStr">
+        <is>
+          <t>Bacia convencional Carrara branca com caixa acoplada, cód. KP.606.17. Ref.: Deca. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="Q16" s="32" t="inlineStr">
+        <is>
+          <t>Ducha higiênica com registro e derivação, cromada, linha Level. Ref.: Deca. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="R16" s="32" t="inlineStr">
+        <is>
+          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Level, cód. 4900.C26.GD. Ref.: Deca. (DET PR008)</t>
+        </is>
+      </c>
+      <c r="S16" s="32" t="inlineStr">
+        <is>
+          <t>Acabamento monocomando para chuveiro, cromado, linha Level, cód. 4993.C26.CHU. Ref.: Deca. (DET PR008; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="T16" s="32" t="inlineStr">
+        <is>
+          <t>Ralo oculto 15x15cm e ralo linear oculto 90x5cm, tampas revestidas com a mesma pedra. (DET PR008)</t>
+        </is>
+      </c>
+      <c r="U16" s="32" t="n"/>
+      <c r="V16" s="32" t="n"/>
+      <c r="W16" s="32" t="n"/>
+      <c r="X16" s="31" t="n"/>
+      <c r="Y16" s="31" t="n"/>
+      <c r="Z16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
+        </is>
+      </c>
+      <c r="B17" s="269" t="inlineStr">
+        <is>
+          <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (DET PR001/PR002; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>Transição madeira x pedra: perfil metálico (DET 05) ou filete de mármore (DET 07). (DET PR001)</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="288" t="inlineStr">
+        <is>
+          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
+CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="n"/>
+      <c r="H17" s="271" t="inlineStr">
+        <is>
+          <t>Pintura acrílica cor branco neve. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I17" s="271" t="n"/>
+      <c r="J17" s="32" t="n"/>
+      <c r="K17" s="32" t="n"/>
+      <c r="L17" s="32" t="n"/>
+      <c r="M17" s="32" t="n"/>
+      <c r="N17" s="32" t="n"/>
+      <c r="O17" s="32" t="n"/>
+      <c r="P17" s="32" t="n"/>
+      <c r="Q17" s="32" t="n"/>
+      <c r="R17" s="32" t="n"/>
+      <c r="S17" s="32" t="n"/>
+      <c r="T17" s="32" t="n"/>
+      <c r="U17" s="32" t="n"/>
+      <c r="V17" s="32" t="n"/>
+      <c r="W17" s="32" t="n"/>
+      <c r="X17" s="31" t="n"/>
+      <c r="Y17" s="31" t="n"/>
+      <c r="Z17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>COPA NOTURNA</t>
+        </is>
+      </c>
+      <c r="B18" s="269" t="inlineStr">
+        <is>
+          <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="n"/>
+      <c r="H18" s="271" t="n"/>
+      <c r="I18" s="271" t="n"/>
+      <c r="J18" s="288" t="inlineStr">
+        <is>
+          <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)
+CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
+        </is>
+      </c>
+      <c r="K18" s="32" t="n"/>
+      <c r="L18" s="32" t="inlineStr">
+        <is>
+          <t>Cuba redonda CR-30, escovada, cód. 01018116 / 90010181016. Ref.: Mekal. (DET PR003; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="M18" s="32" t="n"/>
+      <c r="N18" s="32" t="n"/>
+      <c r="O18" s="32" t="inlineStr">
+        <is>
+          <t>Torneira de mesa bica alta para lavatório, cromada, linha Link, cód. 1198.C.LNK. Ref.: Deca. (DET PR003; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="P18" s="32" t="n"/>
+      <c r="Q18" s="32" t="n"/>
+      <c r="R18" s="32" t="n"/>
+      <c r="S18" s="32" t="n"/>
+      <c r="T18" s="32" t="n"/>
+      <c r="U18" s="32" t="n"/>
+      <c r="V18" s="32" t="n"/>
+      <c r="W18" s="32" t="n"/>
+      <c r="X18" s="31" t="n"/>
+      <c r="Y18" s="31" t="n"/>
+      <c r="Z18" s="32" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>COZINHA / DESPENSAS</t>
+        </is>
+      </c>
+      <c r="B19" s="269" t="inlineStr">
+        <is>
+          <t>Piso em granito branco siena escovado, 85x130cm. Rejunte Infinity Hard, cor Branco Pérola ou Palha (validar com o Setor de Produto). (DET PR001, PR406/407; Tab. R01: paginação a definir)</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Soleira em granito branco siena. (PR406)</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé semi-embutido em granito branco siena escovado, h=15cm (DET 22). (DET PR001, PR406/407; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="271" t="inlineStr">
+        <is>
+          <t>Rodabanca em granito branco siena escovado, h=60cm
+Pintura acrílica; cor a definir (Tab. R01). (PR406/407)</t>
+        </is>
+      </c>
+      <c r="I19" s="271" t="n"/>
+      <c r="J19" s="32" t="inlineStr">
+        <is>
+          <t>Bancada e ilha em granito branco siena escovado; parte seca h=90cm, área molhada com desnível 1cm h=92cm; suporte em metalon chumbado na parede; emendas seguem a paginação do piso. (PR406/407; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="K19" s="32" t="n"/>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>Cuba de embutir 600x400x230mm em aço inox, linha Retta. Ref.: Mekal ou similar. (Tab. R01; PR406 sem modelo)</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="n"/>
+      <c r="N19" s="32" t="n"/>
+      <c r="O19" s="32" t="inlineStr">
+        <is>
+          <t>Monocomando de mesa para cozinha, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01; PR406 sem modelo)</t>
+        </is>
+      </c>
+      <c r="P19" s="32" t="n"/>
+      <c r="Q19" s="32" t="n"/>
+      <c r="R19" s="32" t="n"/>
+      <c r="S19" s="32" t="n"/>
+      <c r="T19" s="32" t="n"/>
+      <c r="U19" s="32" t="n"/>
+      <c r="V19" s="32" t="n"/>
+      <c r="W19" s="32" t="n"/>
+      <c r="X19" s="31" t="inlineStr">
+        <is>
+          <t>Porta em marcenaria. (PR406/407)</t>
+        </is>
+      </c>
+      <c r="Y19" s="31" t="n"/>
+      <c r="Z19" s="32" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>ÁREA DE SERVIÇO / CIRCULAÇÃO SERVIÇO</t>
+        </is>
+      </c>
+      <c r="B20" s="269" t="inlineStr">
+        <is>
+          <t>Piso em granito branco siena escovado, 85x130cm, ver paginação. Rejunte Infinity Hard, cor Branco Pérola ou Palha. (DET PR001, PR005; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Soleira indicada em planta, material não especificado. (DET PR005)</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé semi-embutido em granito branco siena escovado, h=15cm. (DET PR005)</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="n"/>
+      <c r="H20" s="271" t="inlineStr">
+        <is>
+          <t>Parede em Formica Branco Real L515, 308x125cm. (DET PR005/PR006; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I20" s="271" t="inlineStr">
+        <is>
+          <t>Forro de gesso com tabica metálica (DET 11) e cortineiro 25x16cm (DET 24). (DET PR006)</t>
+        </is>
+      </c>
+      <c r="J20" s="32" t="inlineStr">
+        <is>
+          <t>Bancada em granito branco siena escovado, molhada com 1cm de rebaixo, rodabanca h=60cm com topo polido; bancada seca com laterais polidas. (DET PR005/PR006; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="K20" s="32" t="n"/>
+      <c r="L20" s="32" t="inlineStr">
+        <is>
+          <t>Tanque para lavanderia CT-60, escovado, cód. 01019616 / 90010196016, 2 unidades, instalados sob a pedra da bancada. Ref.: Mekal. (DET PR005; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="M20" s="32" t="n"/>
+      <c r="N20" s="32" t="n"/>
+      <c r="O20" s="32" t="inlineStr">
+        <is>
+          <t>Torneira de parede com arejador para cozinha, cromada, linha Link, cód. 1159.C.LNK, 2 unidades. Ref.: Deca. (DET PR005; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="P20" s="32" t="n"/>
+      <c r="Q20" s="32" t="n"/>
+      <c r="R20" s="32" t="inlineStr">
+        <is>
+          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Link, cód. 4900.C.GD.LNK. Ref.: Deca. (DET PR005)</t>
+        </is>
+      </c>
+      <c r="S20" s="32" t="n"/>
+      <c r="T20" s="32" t="inlineStr">
+        <is>
+          <t>Ralo oculto 15x15cm, tampa revestida com a mesma pedra (o DET diz "mármore"; o piso é granito). (DET PR005)</t>
+        </is>
+      </c>
+      <c r="U20" s="32" t="n"/>
+      <c r="V20" s="32" t="n"/>
+      <c r="W20" s="32" t="inlineStr">
+        <is>
+          <t>Maçaneta Pado Sara, cromo acetinado, interna. Porta de segurança: fechadura digital FDE-600W. (DET PR005/PR006)</t>
+        </is>
+      </c>
+      <c r="X20" s="31" t="inlineStr">
+        <is>
+          <t>Porta piso-forro, cor branca, alizar 10cm
+Porta piso-forro especial de segurança, cor branca, alizar 10cm. (DET PR006)</t>
+        </is>
+      </c>
+      <c r="Y20" s="31" t="n"/>
+      <c r="Z20" s="32" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>BANHO SERVIÇO</t>
+        </is>
+      </c>
+      <c r="B21" s="269" t="inlineStr">
+        <is>
+          <t>Piso em granito branco siena escovado. (DET PR007; Tab. R01: paginação a definir)</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Filete em granito na transição para o vinílico (DET 04). (DET PR007)</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="271" t="inlineStr">
+        <is>
+          <t>Revestimento Forma Branco AC retificado 32,5x59cm. Ref.: Eliane. (DET PR007; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I21" s="271" t="inlineStr">
+        <is>
+          <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica, sanca 25x16cm. PD 298cm. (DET PR007)</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>Bancada em granito branco siena escovado. (DET PR007; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="K21" s="32" t="n"/>
+      <c r="L21" s="32" t="inlineStr">
+        <is>
+          <t>Cuba redonda de embutir 31cm branca, linha L, cód. L.41.17. Ref.: Deca. (DET PR007; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="M21" s="32" t="n"/>
+      <c r="N21" s="32" t="n"/>
+      <c r="O21" s="32" t="inlineStr">
+        <is>
+          <t>Torneira de mesa bica baixa para lavatório, cromada, linha Link, cód. 1197.C.LNK. Ref.: Deca. (DET PR007; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="P21" s="32" t="inlineStr">
+        <is>
+          <t>Bacia com caixa acoplada branca, linha Axis, cód. KP.470.17. Ref.: Deca. (DET PR007; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="Q21" s="32" t="inlineStr">
+        <is>
+          <t>Ducha higiênica com registro e derivação, cromada, linha Link, cód. 1984.C.ACT.LNK.BR. Ref.: Deca. (DET PR007)</t>
+        </is>
+      </c>
+      <c r="R21" s="32" t="inlineStr">
+        <is>
+          <t>Acabamento para registro de gaveta e pressão até 1", cromado, Link, cód. 4900.C.PQ.LNK. Ref.: Deca. (DET PR007; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="S21" s="32" t="n"/>
+      <c r="T21" s="32" t="inlineStr">
+        <is>
+          <t>Ralo linear oculto e ralo quadrado oculto. (DET PR007)</t>
+        </is>
+      </c>
+      <c r="U21" s="32" t="n"/>
+      <c r="V21" s="32" t="n"/>
+      <c r="W21" s="32" t="n"/>
+      <c r="X21" s="31" t="n"/>
+      <c r="Y21" s="31" t="n"/>
+      <c r="Z21" s="32" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>QUARTO / ESTAR FUNCIONÁRIOS</t>
+        </is>
+      </c>
+      <c r="B22" s="269" t="inlineStr">
+        <is>
+          <t>Piso vinílico Austin, linha Urban, 18x121cm. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>Filete em granito na transição vinílico x granito (DET 04). (DET PR001)</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="n"/>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé Easy Y.01 120. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="G22" s="32" t="n"/>
+      <c r="H22" s="271" t="inlineStr">
+        <is>
+          <t>Pintura acrílica cor branco neve. (Tab. R01)</t>
+        </is>
+      </c>
+      <c r="I22" s="271" t="n"/>
+      <c r="J22" s="32" t="n"/>
+      <c r="K22" s="32" t="n"/>
+      <c r="L22" s="32" t="n"/>
+      <c r="M22" s="32" t="n"/>
+      <c r="N22" s="32" t="n"/>
+      <c r="O22" s="32" t="n"/>
+      <c r="P22" s="32" t="n"/>
+      <c r="Q22" s="32" t="n"/>
+      <c r="R22" s="32" t="n"/>
+      <c r="S22" s="32" t="n"/>
+      <c r="T22" s="32" t="n"/>
+      <c r="U22" s="32" t="n"/>
+      <c r="V22" s="32" t="n"/>
+      <c r="W22" s="32" t="n"/>
+      <c r="X22" s="31" t="n"/>
+      <c r="Y22" s="31" t="n"/>
+      <c r="Z22" s="32" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>VARANDA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="B23" s="269" t="inlineStr">
+        <is>
+          <t>Piso em concreto. (DET PR001)</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="271" t="n"/>
+      <c r="I23" s="271" t="n"/>
+      <c r="J23" s="32" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="32" t="n"/>
+      <c r="M23" s="32" t="n"/>
+      <c r="N23" s="32" t="n"/>
+      <c r="O23" s="32" t="n"/>
+      <c r="P23" s="32" t="n"/>
+      <c r="Q23" s="32" t="n"/>
+      <c r="R23" s="32" t="n"/>
+      <c r="S23" s="32" t="n"/>
+      <c r="T23" s="32" t="n"/>
+      <c r="U23" s="32" t="n"/>
+      <c r="V23" s="32" t="n"/>
+      <c r="W23" s="32" t="n"/>
+      <c r="X23" s="31" t="n"/>
+      <c r="Y23" s="31" t="n"/>
+      <c r="Z23" s="32" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>HALL ELEVADOR SOCIAL (ANDAR)</t>
+        </is>
+      </c>
+      <c r="B24" s="269" t="inlineStr">
+        <is>
+          <t>Piso em mármore travertino romano bruto. (DET PR003)</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR003)</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="271" t="inlineStr">
+        <is>
+          <t>Parede pintada com tinta acrílica cor branco neve, acabamento acetinado
+Aduela do elevador (2cm) em mármore travertino romano bruto. (DET PR003)</t>
+        </is>
+      </c>
+      <c r="I24" s="271" t="n"/>
+      <c r="J24" s="32" t="n"/>
+      <c r="K24" s="32" t="n"/>
+      <c r="L24" s="32" t="n"/>
+      <c r="M24" s="32" t="n"/>
+      <c r="N24" s="32" t="n"/>
+      <c r="O24" s="32" t="n"/>
+      <c r="P24" s="32" t="n"/>
+      <c r="Q24" s="32" t="n"/>
+      <c r="R24" s="32" t="n"/>
+      <c r="S24" s="32" t="n"/>
+      <c r="T24" s="32" t="n"/>
+      <c r="U24" s="32" t="n"/>
+      <c r="V24" s="32" t="n"/>
+      <c r="W24" s="32" t="n"/>
+      <c r="X24" s="31" t="n"/>
+      <c r="Y24" s="31" t="n"/>
+      <c r="Z24" s="32" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>HALL ELEVADOR SERVIÇO (ANDAR)</t>
+        </is>
+      </c>
+      <c r="B25" s="269" t="inlineStr">
+        <is>
+          <t>Piso em granito branco siena escovado. (DET PR003)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé em granito branco siena escovado, semi-embutido, h=15cm. (DET PR003)</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="271" t="inlineStr">
+        <is>
+          <t>Parede pintada com tinta acrílica cor branco neve, acabamento acetinado
+Aduela do elevador (2cm) em granito branco siena escovado. (DET PR003)</t>
+        </is>
+      </c>
+      <c r="I25" s="271" t="n"/>
+      <c r="J25" s="32" t="n"/>
+      <c r="K25" s="32" t="n"/>
+      <c r="L25" s="32" t="n"/>
+      <c r="M25" s="32" t="n"/>
+      <c r="N25" s="32" t="n"/>
+      <c r="O25" s="32" t="n"/>
+      <c r="P25" s="32" t="n"/>
+      <c r="Q25" s="32" t="n"/>
+      <c r="R25" s="32" t="n"/>
+      <c r="S25" s="32" t="n"/>
+      <c r="T25" s="32" t="n"/>
+      <c r="U25" s="32" t="n"/>
+      <c r="V25" s="32" t="n"/>
+      <c r="W25" s="32" t="n"/>
+      <c r="X25" s="31" t="n"/>
+      <c r="Y25" s="31" t="n"/>
+      <c r="Z25" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>HALL SERVIÇO / ANTECÂMARA – GARDEN, TIPO E COBERTURA</t>
+        </is>
+      </c>
+      <c r="B26" s="269" t="inlineStr">
+        <is>
+          <t>Piso em granito ("revestimento conforme ambiente"). (PR721-728)</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>Rodapé em granito semi-embutido, seguir alinhamento do piso (DET 22). (PR722/724/726/728)</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="271" t="inlineStr">
+        <is>
+          <t>Parede pintada. (PR722/724/726/728)</t>
+        </is>
+      </c>
+      <c r="I26" s="271" t="inlineStr">
+        <is>
+          <t>Forro em gesso com sanca: PD 259cm (Garden e Tipo), 267,5cm (Cobertura 1º nível), 272,5cm (Cobertura 2º nível); junta de dilatação em perfil metálico "Z" (DET 09); trechos em laje de concreto aparente. (PR721-728)</t>
+        </is>
+      </c>
+      <c r="J26" s="32" t="n"/>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="32" t="n"/>
+      <c r="M26" s="32" t="n"/>
+      <c r="N26" s="32" t="n"/>
+      <c r="O26" s="32" t="n"/>
+      <c r="P26" s="32" t="n"/>
+      <c r="Q26" s="32" t="n"/>
+      <c r="R26" s="32" t="n"/>
+      <c r="S26" s="32" t="n"/>
+      <c r="T26" s="32" t="n"/>
+      <c r="U26" s="32" t="n"/>
+      <c r="V26" s="32" t="n"/>
+      <c r="W26" s="32" t="n"/>
+      <c r="X26" s="31" t="inlineStr">
+        <is>
+          <t>PCF1, PCF2, PE-A, P13, P23, PA05, PCF3, P15A, P15C (vão 90x240cm); material não especificado nas pranchas de circulação. (PR721-728)</t>
+        </is>
+      </c>
+      <c r="Y26" s="31" t="n"/>
+      <c r="Z26" s="32" t="inlineStr">
+        <is>
+          <t>Sirene de alarme e botoeira; hidrante nos halls conforme projeto PCI. (PR722-728)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n"/>
+      <c r="B27" s="269" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="271" t="n"/>
+      <c r="I27" s="271" t="n"/>
+      <c r="J27" s="32" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="32" t="n"/>
+      <c r="M27" s="32" t="n"/>
+      <c r="N27" s="32" t="n"/>
+      <c r="O27" s="32" t="n"/>
+      <c r="P27" s="32" t="n"/>
+      <c r="Q27" s="32" t="n"/>
+      <c r="R27" s="32" t="n"/>
+      <c r="S27" s="32" t="n"/>
+      <c r="T27" s="32" t="n"/>
+      <c r="U27" s="32" t="n"/>
+      <c r="V27" s="32" t="n"/>
+      <c r="W27" s="32" t="n"/>
+      <c r="X27" s="31" t="n"/>
+      <c r="Y27" s="31" t="n"/>
+      <c r="Z27" s="32" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n"/>
+      <c r="B28" s="269" t="n"/>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="32" t="n"/>
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="32" t="n"/>
+      <c r="H28" s="271" t="n"/>
+      <c r="I28" s="271" t="n"/>
+      <c r="J28" s="32" t="n"/>
+      <c r="K28" s="32" t="n"/>
+      <c r="L28" s="32" t="n"/>
+      <c r="M28" s="32" t="n"/>
+      <c r="N28" s="32" t="n"/>
+      <c r="O28" s="32" t="n"/>
+      <c r="P28" s="32" t="n"/>
+      <c r="Q28" s="32" t="n"/>
+      <c r="R28" s="32" t="n"/>
+      <c r="S28" s="32" t="n"/>
+      <c r="T28" s="32" t="n"/>
+      <c r="U28" s="32" t="n"/>
+      <c r="V28" s="32" t="n"/>
+      <c r="W28" s="32" t="n"/>
+      <c r="X28" s="31" t="n"/>
+      <c r="Y28" s="31" t="n"/>
+      <c r="Z28" s="32" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="n"/>
+      <c r="B29" s="269" t="n"/>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="32" t="n"/>
+      <c r="E29" s="32" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="32" t="n"/>
+      <c r="H29" s="271" t="n"/>
+      <c r="I29" s="271" t="n"/>
+      <c r="J29" s="32" t="n"/>
+      <c r="K29" s="32" t="n"/>
+      <c r="L29" s="32" t="n"/>
+      <c r="M29" s="32" t="n"/>
+      <c r="N29" s="32" t="n"/>
+      <c r="O29" s="32" t="n"/>
+      <c r="P29" s="32" t="n"/>
+      <c r="Q29" s="32" t="n"/>
+      <c r="R29" s="32" t="n"/>
+      <c r="S29" s="32" t="n"/>
+      <c r="T29" s="32" t="n"/>
+      <c r="U29" s="32" t="n"/>
+      <c r="V29" s="32" t="n"/>
+      <c r="W29" s="32" t="n"/>
+      <c r="X29" s="31" t="n"/>
+      <c r="Y29" s="31" t="n"/>
+      <c r="Z29" s="32" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n"/>
+      <c r="B30" s="269" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="271" t="n"/>
+      <c r="I30" s="271" t="n"/>
+      <c r="J30" s="32" t="n"/>
+      <c r="K30" s="32" t="n"/>
+      <c r="L30" s="32" t="n"/>
+      <c r="M30" s="32" t="n"/>
+      <c r="N30" s="32" t="n"/>
+      <c r="O30" s="32" t="n"/>
+      <c r="P30" s="32" t="n"/>
+      <c r="Q30" s="32" t="n"/>
+      <c r="R30" s="32" t="n"/>
+      <c r="S30" s="32" t="n"/>
+      <c r="T30" s="32" t="n"/>
+      <c r="U30" s="32" t="n"/>
+      <c r="V30" s="32" t="n"/>
+      <c r="W30" s="32" t="n"/>
+      <c r="X30" s="31" t="n"/>
+      <c r="Y30" s="31" t="n"/>
+      <c r="Z30" s="32" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="n"/>
+      <c r="B31" s="269" t="n"/>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="32" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="32" t="n"/>
+      <c r="H31" s="271" t="n"/>
+      <c r="I31" s="271" t="n"/>
+      <c r="J31" s="32" t="n"/>
+      <c r="K31" s="32" t="n"/>
+      <c r="L31" s="32" t="n"/>
+      <c r="M31" s="32" t="n"/>
+      <c r="N31" s="32" t="n"/>
+      <c r="O31" s="32" t="n"/>
+      <c r="P31" s="32" t="n"/>
+      <c r="Q31" s="32" t="n"/>
+      <c r="R31" s="32" t="n"/>
+      <c r="S31" s="32" t="n"/>
+      <c r="T31" s="32" t="n"/>
+      <c r="U31" s="32" t="n"/>
+      <c r="V31" s="32" t="n"/>
+      <c r="W31" s="32" t="n"/>
+      <c r="X31" s="31" t="n"/>
+      <c r="Y31" s="31" t="n"/>
+      <c r="Z31" s="32" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="L10:U10"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="B1:I4"/>
+    <mergeCell ref="AE1:AF4"/>
+    <mergeCell ref="T1:U4"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L1:S4"/>
+    <mergeCell ref="V10:Z10"/>
+    <mergeCell ref="V5:AD6"/>
+    <mergeCell ref="B5:I6"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="AE8:AF8"/>
+    <mergeCell ref="B7:I8"/>
+    <mergeCell ref="V1:AD4"/>
+    <mergeCell ref="L12:U12"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="L7:S8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J1:K4"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="L5:S6"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="V12:Z12"/>
+    <mergeCell ref="V7:AD8"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" pageOrder="overThenDown"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
@@ -14446,13 +16638,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E532"/>
+  <dimension ref="A1:E543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -26615,6 +28807,121 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="279" t="inlineStr">
+        <is>
+          <t>6. APARTAMENTO TIPO (pasta DTL - DETALHAMENTO / APARTAMENTOS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>SALA / VARANDA DA SALA</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>RODAPÉ: CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>LAVABO</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>RODAPÉ: CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>RODAPÉ: CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>COPA NOTURNA</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>BANCADA: CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>BANHO SUÍTE MASTER</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Prancha CDJ-ARQ-DT-PR408-ISSM_TIPO-R05 não tem texto legível pelo conector; linha preenchida só com a tabela R01. Anexar o PDF para conferir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>ÁREA DE SERVIÇO</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Ralo com "tampa revestida com o mesmo mármore", mas o piso é granito branco siena. Confirmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>SOLEIRAS</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Indicadas em planta no lavabo e na área de serviço sem material; só a cozinha define (granito branco siena).</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>COZINHA</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>PR406/407 não trazem modelo de cuba e monocomando; valem os da tabela R01 (Mekal Retta e Deca Level).</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>REJUNTES</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>DET indica "validar com o Setor de Produto"; PR001/PR002 "não liberado para execução, paginação poderá sofrer alterações".</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -14823,60 +14823,99 @@
       </c>
       <c r="B15" s="269" t="inlineStr">
         <is>
-          <t>Piso em mármore travertino romano bruto resinado, paginado conforme detalhamento. (Tab. R01)</t>
+          <t>11 - Piso em contrapiso regularizado, revestido em mármore travertino romano resinado. Rejunte creme ou marfim (ver padrão da chapa). Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408; Tab. R01: "bruto resinado")</t>
         </is>
       </c>
       <c r="C15" s="32" t="n"/>
       <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Peitoril a definir conforme projeto de esquadrias. (PR408)</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>23 - Rodapé em mármore travertino romano bruto semi-embutido, h=15cm; paginação segue alinhamento do piso. (PR408)</t>
+        </is>
+      </c>
       <c r="G15" s="32" t="n"/>
-      <c r="H15" s="271" t="inlineStr">
-        <is>
-          <t>Parede em mármore travertino romano bruto paginado. (Tab. R01)</t>
-        </is>
-      </c>
-      <c r="I15" s="271" t="n"/>
+      <c r="H15" s="285" t="inlineStr">
+        <is>
+          <t>14 - Parede revestida em mármore travertino romano resinado. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408)
+1 - Parede em alvenaria emassada e regularizada, pintada com tinta acrílica cor branco neve, acabamento acetinado. Ref.: Suvinil. (PR408)
+CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
+        </is>
+      </c>
+      <c r="I15" s="271" t="inlineStr">
+        <is>
+          <t>1 - Forro em gesso acartonado liso, tinta acrílica cor branco neve, acabamento fosco, junta de dilatação metálica branca. Ref.: Suvinil. Sanca (DET 20). (PR408)</t>
+        </is>
+      </c>
       <c r="J15" s="32" t="inlineStr">
         <is>
-          <t>Bancada em mármore travertino romano resinado. (Tab. R01)</t>
+          <t>35 - Bancada em mármore travertino romano resinado. Rejunte creme ou marfim (ver padrão da chapa). Dimensões conforme detalhamento. (PR408; Tab. R01)</t>
         </is>
       </c>
       <c r="K15" s="32" t="n"/>
       <c r="L15" s="32" t="inlineStr">
         <is>
-          <t>Cuba de apoio retangular Jader Almeida, branca. Ref.: Deca ou similar. (Tab. R01)</t>
+          <t>33 - Cuba de apoio retangular Jader Almeida 670x495x120mm, branca, cód. L.310.17. Ref.: Deca. (PR408; Tab. R01)</t>
         </is>
       </c>
       <c r="M15" s="32" t="n"/>
       <c r="N15" s="32" t="n"/>
       <c r="O15" s="32" t="inlineStr">
         <is>
-          <t>Misturador monocomando de mesa bica alta para lavatório, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01)</t>
+          <t>36 - Misturador monocomando de mesa bica alta para lavatório, Level cromado, cód. 2885.C26. Ref.: Deca. (PR408; Tab. R01)</t>
         </is>
       </c>
       <c r="P15" s="32" t="inlineStr">
         <is>
-          <t>Bacia convencional Carrara branca com caixa acoplada. Ref.: Deca ou similar
-Bidê 3 furos Carrara branco. Ref.: Deca ou similar. (Tab. R01)</t>
-        </is>
-      </c>
-      <c r="Q15" s="32" t="n"/>
-      <c r="R15" s="32" t="n"/>
+          <t>34 - Bacia convencional Carrara branca com caixa acoplada e acionamento duo, cód. P.606.17. Ref.: Deca. (PR408; Tab. R01)
+46 - Bidê 3 furos Carrara branco, cód. B.60.17. Ref.: Deca. (PR408; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="Q15" s="32" t="inlineStr">
+        <is>
+          <t>37 - Ducha higiênica Level cromada, cód. 1984.C26.ACT.CR. (PR408)</t>
+        </is>
+      </c>
+      <c r="R15" s="32" t="inlineStr">
+        <is>
+          <t>49 - Acabamento para registro Level cromado, cód. 4900.C26.PQ. Ref.: Deca. (PR408)</t>
+        </is>
+      </c>
       <c r="S15" s="32" t="inlineStr">
         <is>
-          <t>Acabamento de monocomando de chuveiro, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01)</t>
-        </is>
-      </c>
-      <c r="T15" s="32" t="n"/>
+          <t>44 - Acabamento de monocomando de chuveiro para alta e baixa pressão, Level cromado, cód. 4993.C26.CHU. (PR408; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="T15" s="32" t="inlineStr">
+        <is>
+          <t>47 - Ralo linear oculto Royal 70cm
+48 - Ralo oculto 15x15cm Square. (PR408)</t>
+        </is>
+      </c>
       <c r="U15" s="32" t="inlineStr">
         <is>
-          <t>Misturador para bidê, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01)</t>
-        </is>
-      </c>
-      <c r="V15" s="32" t="n"/>
-      <c r="W15" s="32" t="n"/>
-      <c r="X15" s="31" t="n"/>
+          <t>45 - Misturador para bidê Level cromado, cód. 1895.C26. (PR408; Tab. R01)</t>
+        </is>
+      </c>
+      <c r="V15" s="32" t="inlineStr">
+        <is>
+          <t>39 - Tomadas e interruptores Arteor quadrado branco. Ref.: Legrand. (PR408)</t>
+        </is>
+      </c>
+      <c r="W15" s="32" t="inlineStr">
+        <is>
+          <t>Maçaneta Sara cromo acetinado. Ref.: Pado. (PR408)</t>
+        </is>
+      </c>
+      <c r="X15" s="31" t="inlineStr">
+        <is>
+          <t>38 - Porta em marcenaria piso-forro, cor branca, alizar 10cm. (PR408)</t>
+        </is>
+      </c>
       <c r="Y15" s="31" t="n"/>
       <c r="Z15" s="32" t="n"/>
     </row>
@@ -16644,7 +16683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E543"/>
+  <dimension ref="A1:E544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -28841,82 +28880,94 @@
     <row r="537">
       <c r="B537" t="inlineStr">
         <is>
-          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
+          <t>BANHO SUÍTE MASTER</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>RODAPÉ: CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
+          <t>PAREDE/REJUNTE: CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="B538" t="inlineStr">
         <is>
-          <t>COPA NOTURNA</t>
+          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>BANCADA: CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
+          <t>RODAPÉ: CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="B539" t="inlineStr">
         <is>
-          <t>BANHO SUÍTE MASTER</t>
+          <t>COPA NOTURNA</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Prancha CDJ-ARQ-DT-PR408-ISSM_TIPO-R05 não tem texto legível pelo conector; linha preenchida só com a tabela R01. Anexar o PDF para conferir.</t>
+          <t>BANCADA: CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="B540" t="inlineStr">
         <is>
-          <t>ÁREA DE SERVIÇO</t>
+          <t>BANHO SUÍTE MASTER</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Ralo com "tampa revestida com o mesmo mármore", mas o piso é granito branco siena. Confirmar.</t>
+          <t>Prancha CDJ-ARQ-DT-PR408-ISSM_TIPO-R05 lida pelo PDF anexado (só imagem vetorial, sem texto); códigos da legenda da prancha.</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="B541" t="inlineStr">
         <is>
-          <t>SOLEIRAS</t>
+          <t>ÁREA DE SERVIÇO</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Indicadas em planta no lavabo e na área de serviço sem material; só a cozinha define (granito branco siena).</t>
+          <t>Ralo com "tampa revestida com o mesmo mármore", mas o piso é granito branco siena. Confirmar.</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="B542" t="inlineStr">
         <is>
-          <t>COZINHA</t>
+          <t>SOLEIRAS</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>PR406/407 não trazem modelo de cuba e monocomando; valem os da tabela R01 (Mekal Retta e Deca Level).</t>
+          <t>Indicadas em planta no lavabo e na área de serviço sem material; só a cozinha define (granito branco siena).</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="B543" t="inlineStr">
         <is>
+          <t>COZINHA</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>PR406/407 não trazem modelo de cuba e monocomando; valem os da tabela R01 (Mekal Retta e Deca Level).</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" t="inlineStr">
+        <is>
           <t>REJUNTES</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr">
+      <c r="D544" t="inlineStr">
         <is>
           <t>DET indica "validar com o Setor de Produto"; PR001/PR002 "não liberado para execução, paginação poderá sofrer alterações".</t>
         </is>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -1374,7 +1374,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2148,6 +2148,16 @@
     <xf numFmtId="4" fontId="60" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6877,30 +6887,30 @@
         </is>
       </c>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="49" t="n"/>
-      <c r="G13" s="49" t="n"/>
+      <c r="C13" s="289" t="n"/>
+      <c r="D13" s="289" t="n"/>
+      <c r="E13" s="289" t="n"/>
+      <c r="F13" s="289" t="n"/>
+      <c r="G13" s="289" t="n"/>
       <c r="H13" s="50" t="n"/>
       <c r="I13" s="50" t="n"/>
-      <c r="J13" s="49" t="n"/>
-      <c r="K13" s="49" t="n"/>
-      <c r="L13" s="49" t="n"/>
-      <c r="M13" s="49" t="n"/>
-      <c r="N13" s="49" t="n"/>
-      <c r="O13" s="49" t="n"/>
-      <c r="P13" s="49" t="n"/>
-      <c r="Q13" s="49" t="n"/>
-      <c r="R13" s="49" t="n"/>
-      <c r="S13" s="49" t="n"/>
-      <c r="T13" s="49" t="n"/>
-      <c r="U13" s="49" t="n"/>
-      <c r="V13" s="49" t="n"/>
-      <c r="W13" s="49" t="n"/>
+      <c r="J13" s="289" t="n"/>
+      <c r="K13" s="289" t="n"/>
+      <c r="L13" s="289" t="n"/>
+      <c r="M13" s="289" t="n"/>
+      <c r="N13" s="289" t="n"/>
+      <c r="O13" s="289" t="n"/>
+      <c r="P13" s="289" t="n"/>
+      <c r="Q13" s="289" t="n"/>
+      <c r="R13" s="289" t="n"/>
+      <c r="S13" s="289" t="n"/>
+      <c r="T13" s="289" t="n"/>
+      <c r="U13" s="289" t="n"/>
+      <c r="V13" s="289" t="n"/>
+      <c r="W13" s="289" t="n"/>
       <c r="X13" s="48" t="n"/>
       <c r="Y13" s="48" t="n"/>
-      <c r="Z13" s="49" t="n"/>
+      <c r="Z13" s="289" t="n"/>
     </row>
     <row r="14" ht="125.25" customHeight="1">
       <c r="A14" s="47" t="inlineStr">
@@ -6909,30 +6919,30 @@
         </is>
       </c>
       <c r="B14" s="48" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="49" t="n"/>
-      <c r="G14" s="49" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
       <c r="H14" s="50" t="n"/>
       <c r="I14" s="50" t="n"/>
-      <c r="J14" s="49" t="n"/>
-      <c r="K14" s="49" t="n"/>
-      <c r="L14" s="49" t="n"/>
-      <c r="M14" s="49" t="n"/>
-      <c r="N14" s="49" t="n"/>
-      <c r="O14" s="49" t="n"/>
-      <c r="P14" s="49" t="n"/>
-      <c r="Q14" s="49" t="n"/>
-      <c r="R14" s="49" t="n"/>
-      <c r="S14" s="49" t="n"/>
-      <c r="T14" s="49" t="n"/>
-      <c r="U14" s="49" t="n"/>
-      <c r="V14" s="49" t="n"/>
-      <c r="W14" s="49" t="n"/>
+      <c r="J14" s="289" t="n"/>
+      <c r="K14" s="289" t="n"/>
+      <c r="L14" s="289" t="n"/>
+      <c r="M14" s="289" t="n"/>
+      <c r="N14" s="289" t="n"/>
+      <c r="O14" s="289" t="n"/>
+      <c r="P14" s="289" t="n"/>
+      <c r="Q14" s="289" t="n"/>
+      <c r="R14" s="289" t="n"/>
+      <c r="S14" s="289" t="n"/>
+      <c r="T14" s="289" t="n"/>
+      <c r="U14" s="289" t="n"/>
+      <c r="V14" s="289" t="n"/>
+      <c r="W14" s="289" t="n"/>
       <c r="X14" s="48" t="n"/>
       <c r="Y14" s="48" t="n"/>
-      <c r="Z14" s="49" t="n"/>
+      <c r="Z14" s="289" t="n"/>
     </row>
     <row r="15" ht="125.25" customHeight="1">
       <c r="A15" s="47" t="inlineStr">
@@ -6941,30 +6951,30 @@
         </is>
       </c>
       <c r="B15" s="48" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="49" t="n"/>
-      <c r="G15" s="49" t="n"/>
+      <c r="C15" s="289" t="n"/>
+      <c r="D15" s="289" t="n"/>
+      <c r="E15" s="289" t="n"/>
+      <c r="F15" s="289" t="n"/>
+      <c r="G15" s="289" t="n"/>
       <c r="H15" s="50" t="n"/>
       <c r="I15" s="50" t="n"/>
-      <c r="J15" s="49" t="n"/>
-      <c r="K15" s="49" t="n"/>
-      <c r="L15" s="49" t="n"/>
-      <c r="M15" s="49" t="n"/>
-      <c r="N15" s="49" t="n"/>
-      <c r="O15" s="49" t="n"/>
-      <c r="P15" s="49" t="n"/>
-      <c r="Q15" s="49" t="n"/>
-      <c r="R15" s="49" t="n"/>
-      <c r="S15" s="49" t="n"/>
-      <c r="T15" s="49" t="n"/>
-      <c r="U15" s="49" t="n"/>
-      <c r="V15" s="49" t="n"/>
-      <c r="W15" s="49" t="n"/>
+      <c r="J15" s="289" t="n"/>
+      <c r="K15" s="289" t="n"/>
+      <c r="L15" s="289" t="n"/>
+      <c r="M15" s="289" t="n"/>
+      <c r="N15" s="289" t="n"/>
+      <c r="O15" s="289" t="n"/>
+      <c r="P15" s="289" t="n"/>
+      <c r="Q15" s="289" t="n"/>
+      <c r="R15" s="289" t="n"/>
+      <c r="S15" s="289" t="n"/>
+      <c r="T15" s="289" t="n"/>
+      <c r="U15" s="289" t="n"/>
+      <c r="V15" s="289" t="n"/>
+      <c r="W15" s="289" t="n"/>
       <c r="X15" s="48" t="n"/>
       <c r="Y15" s="48" t="n"/>
-      <c r="Z15" s="49" t="n"/>
+      <c r="Z15" s="289" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="45" t="inlineStr">
@@ -6977,15 +6987,15 @@
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="270" t="inlineStr">
+      <c r="C16" s="290" t="n"/>
+      <c r="D16" s="290" t="n"/>
+      <c r="E16" s="290" t="n"/>
+      <c r="F16" s="271" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G16" s="32" t="n"/>
+      <c r="G16" s="290" t="n"/>
       <c r="H16" s="271" t="inlineStr">
         <is>
           <t>PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -6996,24 +7006,24 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="32" t="n"/>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="32" t="n"/>
-      <c r="S16" s="32" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="270" t="inlineStr">
+      <c r="J16" s="290" t="n"/>
+      <c r="K16" s="290" t="n"/>
+      <c r="L16" s="290" t="n"/>
+      <c r="M16" s="290" t="n"/>
+      <c r="N16" s="290" t="n"/>
+      <c r="O16" s="290" t="n"/>
+      <c r="P16" s="290" t="n"/>
+      <c r="Q16" s="290" t="n"/>
+      <c r="R16" s="290" t="n"/>
+      <c r="S16" s="290" t="n"/>
+      <c r="T16" s="290" t="n"/>
+      <c r="U16" s="290" t="n"/>
+      <c r="V16" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W16" s="32" t="n"/>
+      <c r="W16" s="290" t="n"/>
       <c r="X16" s="269" t="inlineStr">
         <is>
           <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
@@ -7021,7 +7031,7 @@
         </is>
       </c>
       <c r="Y16" s="31" t="n"/>
-      <c r="Z16" s="32" t="n"/>
+      <c r="Z16" s="290" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="45" t="inlineStr">
@@ -7035,16 +7045,16 @@
 CONFLITO – Arquitetura: ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="270" t="inlineStr">
+      <c r="C17" s="290" t="n"/>
+      <c r="D17" s="290" t="n"/>
+      <c r="E17" s="290" t="n"/>
+      <c r="F17" s="271" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.
 ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G17" s="32" t="n"/>
+      <c r="G17" s="290" t="n"/>
       <c r="H17" s="285" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
@@ -7057,27 +7067,27 @@
 ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
-      <c r="O17" s="32" t="n"/>
-      <c r="P17" s="32" t="n"/>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="32" t="n"/>
-      <c r="S17" s="32" t="n"/>
-      <c r="T17" s="32" t="n"/>
-      <c r="U17" s="32" t="n"/>
-      <c r="V17" s="270" t="inlineStr">
+      <c r="J17" s="290" t="n"/>
+      <c r="K17" s="290" t="n"/>
+      <c r="L17" s="290" t="n"/>
+      <c r="M17" s="290" t="n"/>
+      <c r="N17" s="290" t="n"/>
+      <c r="O17" s="290" t="n"/>
+      <c r="P17" s="290" t="n"/>
+      <c r="Q17" s="290" t="n"/>
+      <c r="R17" s="290" t="n"/>
+      <c r="S17" s="290" t="n"/>
+      <c r="T17" s="290" t="n"/>
+      <c r="U17" s="290" t="n"/>
+      <c r="V17" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W17" s="32" t="n"/>
+      <c r="W17" s="290" t="n"/>
       <c r="X17" s="31" t="n"/>
       <c r="Y17" s="31" t="n"/>
-      <c r="Z17" s="32" t="n"/>
+      <c r="Z17" s="290" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="45" t="inlineStr">
@@ -7090,15 +7100,15 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="270" t="inlineStr">
+      <c r="C18" s="290" t="n"/>
+      <c r="D18" s="290" t="n"/>
+      <c r="E18" s="290" t="n"/>
+      <c r="F18" s="271" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G18" s="32" t="n"/>
+      <c r="G18" s="290" t="n"/>
       <c r="H18" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
@@ -7109,23 +7119,23 @@
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="32" t="n"/>
-      <c r="O18" s="32" t="n"/>
-      <c r="P18" s="32" t="n"/>
-      <c r="Q18" s="32" t="n"/>
-      <c r="R18" s="32" t="n"/>
-      <c r="S18" s="32" t="n"/>
-      <c r="T18" s="32" t="n"/>
-      <c r="U18" s="32" t="n"/>
-      <c r="V18" s="32" t="n"/>
-      <c r="W18" s="32" t="n"/>
+      <c r="J18" s="290" t="n"/>
+      <c r="K18" s="290" t="n"/>
+      <c r="L18" s="290" t="n"/>
+      <c r="M18" s="290" t="n"/>
+      <c r="N18" s="290" t="n"/>
+      <c r="O18" s="290" t="n"/>
+      <c r="P18" s="290" t="n"/>
+      <c r="Q18" s="290" t="n"/>
+      <c r="R18" s="290" t="n"/>
+      <c r="S18" s="290" t="n"/>
+      <c r="T18" s="290" t="n"/>
+      <c r="U18" s="290" t="n"/>
+      <c r="V18" s="290" t="n"/>
+      <c r="W18" s="290" t="n"/>
       <c r="X18" s="31" t="n"/>
       <c r="Y18" s="31" t="n"/>
-      <c r="Z18" s="32" t="n"/>
+      <c r="Z18" s="290" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
@@ -7138,15 +7148,15 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="270" t="inlineStr">
+      <c r="C19" s="290" t="n"/>
+      <c r="D19" s="290" t="n"/>
+      <c r="E19" s="290" t="n"/>
+      <c r="F19" s="271" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G19" s="32" t="n"/>
+      <c r="G19" s="290" t="n"/>
       <c r="H19" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -7157,23 +7167,23 @@
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="32" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="32" t="n"/>
-      <c r="U19" s="32" t="n"/>
-      <c r="V19" s="32" t="n"/>
-      <c r="W19" s="32" t="n"/>
+      <c r="J19" s="290" t="n"/>
+      <c r="K19" s="290" t="n"/>
+      <c r="L19" s="290" t="n"/>
+      <c r="M19" s="290" t="n"/>
+      <c r="N19" s="290" t="n"/>
+      <c r="O19" s="290" t="n"/>
+      <c r="P19" s="290" t="n"/>
+      <c r="Q19" s="290" t="n"/>
+      <c r="R19" s="290" t="n"/>
+      <c r="S19" s="290" t="n"/>
+      <c r="T19" s="290" t="n"/>
+      <c r="U19" s="290" t="n"/>
+      <c r="V19" s="290" t="n"/>
+      <c r="W19" s="290" t="n"/>
       <c r="X19" s="31" t="n"/>
       <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="32" t="n"/>
+      <c r="Z19" s="290" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="45" t="inlineStr">
@@ -7186,15 +7196,15 @@
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="270" t="inlineStr">
+      <c r="C20" s="290" t="n"/>
+      <c r="D20" s="290" t="n"/>
+      <c r="E20" s="290" t="n"/>
+      <c r="F20" s="271" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G20" s="32" t="n"/>
+      <c r="G20" s="290" t="n"/>
       <c r="H20" s="271" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
@@ -7209,24 +7219,24 @@
 T12 - Forro em chapa metálica dourada colada sobre MDF cru 6mm aparafusado em estrutura auxiliar do guarda corpo em metalon</t>
         </is>
       </c>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
-      <c r="O20" s="32" t="n"/>
-      <c r="P20" s="32" t="n"/>
-      <c r="Q20" s="32" t="n"/>
-      <c r="R20" s="32" t="n"/>
-      <c r="S20" s="32" t="n"/>
-      <c r="T20" s="32" t="n"/>
-      <c r="U20" s="32" t="n"/>
-      <c r="V20" s="270" t="inlineStr">
+      <c r="J20" s="290" t="n"/>
+      <c r="K20" s="290" t="n"/>
+      <c r="L20" s="290" t="n"/>
+      <c r="M20" s="290" t="n"/>
+      <c r="N20" s="290" t="n"/>
+      <c r="O20" s="290" t="n"/>
+      <c r="P20" s="290" t="n"/>
+      <c r="Q20" s="290" t="n"/>
+      <c r="R20" s="290" t="n"/>
+      <c r="S20" s="290" t="n"/>
+      <c r="T20" s="290" t="n"/>
+      <c r="U20" s="290" t="n"/>
+      <c r="V20" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W20" s="32" t="n"/>
+      <c r="W20" s="290" t="n"/>
       <c r="X20" s="269" t="inlineStr">
         <is>
           <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
@@ -7234,7 +7244,7 @@
         </is>
       </c>
       <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="270" t="inlineStr">
+      <c r="Z20" s="271" t="inlineStr">
         <is>
           <t>D63 - Guarda corpo em chapa metálica dourada colada sobre fechamento em MDF cru 6mm aparafusado em estrutura auxiliar de metalon. Dimensões e detalhes conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -7251,15 +7261,15 @@
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="270" t="inlineStr">
+      <c r="C21" s="290" t="n"/>
+      <c r="D21" s="290" t="n"/>
+      <c r="E21" s="290" t="n"/>
+      <c r="F21" s="271" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G21" s="32" t="n"/>
+      <c r="G21" s="290" t="n"/>
       <c r="H21" s="271" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
@@ -7272,27 +7282,27 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="n"/>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="32" t="n"/>
-      <c r="V21" s="270" t="inlineStr">
+      <c r="J21" s="290" t="n"/>
+      <c r="K21" s="290" t="n"/>
+      <c r="L21" s="290" t="n"/>
+      <c r="M21" s="290" t="n"/>
+      <c r="N21" s="290" t="n"/>
+      <c r="O21" s="290" t="n"/>
+      <c r="P21" s="290" t="n"/>
+      <c r="Q21" s="290" t="n"/>
+      <c r="R21" s="290" t="n"/>
+      <c r="S21" s="290" t="n"/>
+      <c r="T21" s="290" t="n"/>
+      <c r="U21" s="290" t="n"/>
+      <c r="V21" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W21" s="32" t="n"/>
+      <c r="W21" s="290" t="n"/>
       <c r="X21" s="31" t="n"/>
       <c r="Y21" s="31" t="n"/>
-      <c r="Z21" s="270" t="inlineStr">
+      <c r="Z21" s="271" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -7309,15 +7319,15 @@
           <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="270" t="inlineStr">
+      <c r="C22" s="290" t="n"/>
+      <c r="D22" s="290" t="n"/>
+      <c r="E22" s="290" t="n"/>
+      <c r="F22" s="271" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G22" s="32" t="n"/>
+      <c r="G22" s="290" t="n"/>
       <c r="H22" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -7328,23 +7338,23 @@
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="32" t="n"/>
-      <c r="M22" s="32" t="n"/>
-      <c r="N22" s="32" t="n"/>
-      <c r="O22" s="32" t="n"/>
-      <c r="P22" s="32" t="n"/>
-      <c r="Q22" s="32" t="n"/>
-      <c r="R22" s="32" t="n"/>
-      <c r="S22" s="32" t="n"/>
-      <c r="T22" s="32" t="n"/>
-      <c r="U22" s="32" t="n"/>
-      <c r="V22" s="32" t="n"/>
-      <c r="W22" s="32" t="n"/>
+      <c r="J22" s="290" t="n"/>
+      <c r="K22" s="290" t="n"/>
+      <c r="L22" s="290" t="n"/>
+      <c r="M22" s="290" t="n"/>
+      <c r="N22" s="290" t="n"/>
+      <c r="O22" s="290" t="n"/>
+      <c r="P22" s="290" t="n"/>
+      <c r="Q22" s="290" t="n"/>
+      <c r="R22" s="290" t="n"/>
+      <c r="S22" s="290" t="n"/>
+      <c r="T22" s="290" t="n"/>
+      <c r="U22" s="290" t="n"/>
+      <c r="V22" s="290" t="n"/>
+      <c r="W22" s="290" t="n"/>
       <c r="X22" s="31" t="n"/>
       <c r="Y22" s="31" t="n"/>
-      <c r="Z22" s="32" t="n"/>
+      <c r="Z22" s="290" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="45" t="inlineStr">
@@ -7357,15 +7367,15 @@
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="272" t="inlineStr">
+      <c r="C23" s="290" t="n"/>
+      <c r="D23" s="290" t="n"/>
+      <c r="E23" s="290" t="n"/>
+      <c r="F23" s="291" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G23" s="32" t="n"/>
+      <c r="G23" s="290" t="n"/>
       <c r="H23" s="271" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
@@ -7377,24 +7387,24 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="270" t="inlineStr">
+      <c r="J23" s="290" t="n"/>
+      <c r="K23" s="290" t="n"/>
+      <c r="L23" s="290" t="n"/>
+      <c r="M23" s="290" t="n"/>
+      <c r="N23" s="290" t="n"/>
+      <c r="O23" s="290" t="n"/>
+      <c r="P23" s="290" t="n"/>
+      <c r="Q23" s="290" t="n"/>
+      <c r="R23" s="290" t="n"/>
+      <c r="S23" s="290" t="n"/>
+      <c r="T23" s="290" t="n"/>
+      <c r="U23" s="290" t="n"/>
+      <c r="V23" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W23" s="32" t="n"/>
+      <c r="W23" s="290" t="n"/>
       <c r="X23" s="269" t="inlineStr">
         <is>
           <t>D44 - Porta pivotante em MDF com acabamento em pintura acrílica fosca. Tom a definir. Dimensões conforme Mapa de Esquadrias. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -7402,7 +7412,7 @@
         </is>
       </c>
       <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="270" t="inlineStr">
+      <c r="Z23" s="271" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -7419,11 +7429,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
+      <c r="C24" s="290" t="n"/>
+      <c r="D24" s="290" t="n"/>
+      <c r="E24" s="290" t="n"/>
+      <c r="F24" s="290" t="n"/>
+      <c r="G24" s="290" t="n"/>
       <c r="H24" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -7434,23 +7444,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="32" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
-      <c r="T24" s="32" t="n"/>
-      <c r="U24" s="32" t="n"/>
-      <c r="V24" s="32" t="n"/>
-      <c r="W24" s="32" t="n"/>
+      <c r="J24" s="290" t="n"/>
+      <c r="K24" s="290" t="n"/>
+      <c r="L24" s="290" t="n"/>
+      <c r="M24" s="290" t="n"/>
+      <c r="N24" s="290" t="n"/>
+      <c r="O24" s="290" t="n"/>
+      <c r="P24" s="290" t="n"/>
+      <c r="Q24" s="290" t="n"/>
+      <c r="R24" s="290" t="n"/>
+      <c r="S24" s="290" t="n"/>
+      <c r="T24" s="290" t="n"/>
+      <c r="U24" s="290" t="n"/>
+      <c r="V24" s="290" t="n"/>
+      <c r="W24" s="290" t="n"/>
       <c r="X24" s="31" t="n"/>
       <c r="Y24" s="31" t="n"/>
-      <c r="Z24" s="32" t="n"/>
+      <c r="Z24" s="290" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="45" t="inlineStr">
@@ -7464,10 +7474,10 @@
         </is>
       </c>
       <c r="C25" s="34" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
+      <c r="D25" s="290" t="n"/>
+      <c r="E25" s="290" t="n"/>
       <c r="F25" s="34" t="n"/>
-      <c r="G25" s="32" t="n"/>
+      <c r="G25" s="290" t="n"/>
       <c r="H25" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -7478,23 +7488,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="32" t="n"/>
-      <c r="M25" s="32" t="n"/>
-      <c r="N25" s="32" t="n"/>
-      <c r="O25" s="32" t="n"/>
-      <c r="P25" s="32" t="n"/>
-      <c r="Q25" s="32" t="n"/>
-      <c r="R25" s="32" t="n"/>
-      <c r="S25" s="32" t="n"/>
-      <c r="T25" s="32" t="n"/>
-      <c r="U25" s="32" t="n"/>
+      <c r="J25" s="290" t="n"/>
+      <c r="K25" s="290" t="n"/>
+      <c r="L25" s="290" t="n"/>
+      <c r="M25" s="290" t="n"/>
+      <c r="N25" s="290" t="n"/>
+      <c r="O25" s="290" t="n"/>
+      <c r="P25" s="290" t="n"/>
+      <c r="Q25" s="290" t="n"/>
+      <c r="R25" s="290" t="n"/>
+      <c r="S25" s="290" t="n"/>
+      <c r="T25" s="290" t="n"/>
+      <c r="U25" s="290" t="n"/>
       <c r="V25" s="31" t="n"/>
       <c r="W25" s="34" t="n"/>
       <c r="X25" s="31" t="n"/>
       <c r="Y25" s="31" t="n"/>
-      <c r="Z25" s="32" t="n"/>
+      <c r="Z25" s="290" t="n"/>
     </row>
     <row r="26" ht="125.25" customHeight="1">
       <c r="A26" s="45" t="inlineStr">
@@ -7503,25 +7513,25 @@
         </is>
       </c>
       <c r="B26" s="34" t="n"/>
-      <c r="C26" s="32" t="n"/>
+      <c r="C26" s="290" t="n"/>
       <c r="D26" s="34" t="n"/>
-      <c r="E26" s="36" t="n"/>
+      <c r="E26" s="290" t="n"/>
       <c r="F26" s="34" t="n"/>
-      <c r="G26" s="32" t="n"/>
+      <c r="G26" s="290" t="n"/>
       <c r="H26" s="34" t="n"/>
       <c r="I26" s="35" t="n"/>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="32" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="32" t="n"/>
-      <c r="T26" s="32" t="n"/>
-      <c r="U26" s="32" t="n"/>
+      <c r="J26" s="290" t="n"/>
+      <c r="K26" s="290" t="n"/>
+      <c r="L26" s="290" t="n"/>
+      <c r="M26" s="290" t="n"/>
+      <c r="N26" s="290" t="n"/>
+      <c r="O26" s="290" t="n"/>
+      <c r="P26" s="290" t="n"/>
+      <c r="Q26" s="290" t="n"/>
+      <c r="R26" s="290" t="n"/>
+      <c r="S26" s="290" t="n"/>
+      <c r="T26" s="290" t="n"/>
+      <c r="U26" s="290" t="n"/>
       <c r="V26" s="31" t="n"/>
       <c r="W26" s="35" t="n"/>
       <c r="X26" s="31" t="n"/>
@@ -7539,15 +7549,15 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="37" t="n"/>
-      <c r="E27" s="32" t="n"/>
+      <c r="C27" s="290" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="290" t="n"/>
       <c r="F27" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G27" s="32" t="n"/>
+      <c r="G27" s="290" t="n"/>
       <c r="H27" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -7559,17 +7569,17 @@
         </is>
       </c>
       <c r="J27" s="35" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="32" t="n"/>
-      <c r="M27" s="37" t="n"/>
-      <c r="N27" s="37" t="n"/>
+      <c r="K27" s="290" t="n"/>
+      <c r="L27" s="290" t="n"/>
+      <c r="M27" s="38" t="n"/>
+      <c r="N27" s="38" t="n"/>
       <c r="O27" s="31" t="n"/>
       <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="32" t="n"/>
+      <c r="Q27" s="290" t="n"/>
       <c r="R27" s="35" t="n"/>
-      <c r="S27" s="32" t="n"/>
+      <c r="S27" s="290" t="n"/>
       <c r="T27" s="35" t="n"/>
-      <c r="U27" s="32" t="n"/>
+      <c r="U27" s="290" t="n"/>
       <c r="V27" s="31" t="n"/>
       <c r="W27" s="35" t="n"/>
       <c r="X27" s="35" t="n"/>
@@ -7587,58 +7597,58 @@
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C28" s="32" t="n"/>
+      <c r="C28" s="290" t="n"/>
       <c r="D28" s="35" t="n"/>
-      <c r="E28" s="37" t="n"/>
+      <c r="E28" s="38" t="n"/>
       <c r="F28" s="269" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G28" s="32" t="n"/>
+      <c r="G28" s="290" t="n"/>
       <c r="H28" s="269" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I28" s="270" t="inlineStr">
+      <c r="I28" s="271" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J28" s="270" t="inlineStr">
+      <c r="J28" s="271" t="inlineStr">
         <is>
           <t>D65 - Bancada em pedra natural Basaltina com cuba esculpida e bandeja removível. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K28" s="270" t="inlineStr">
+      <c r="K28" s="271" t="inlineStr">
         <is>
           <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
-      <c r="L28" s="32" t="n"/>
-      <c r="M28" s="32" t="n"/>
-      <c r="N28" s="32" t="n"/>
-      <c r="O28" s="270" t="inlineStr">
+      <c r="L28" s="290" t="n"/>
+      <c r="M28" s="290" t="n"/>
+      <c r="N28" s="290" t="n"/>
+      <c r="O28" s="271" t="inlineStr">
         <is>
           <t>D66 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento grafite escovado, cód.: 01739870. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P28" s="270" t="inlineStr">
+      <c r="P28" s="271" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q28" s="32" t="n"/>
-      <c r="R28" s="32" t="n"/>
-      <c r="S28" s="32" t="n"/>
+      <c r="Q28" s="290" t="n"/>
+      <c r="R28" s="290" t="n"/>
+      <c r="S28" s="290" t="n"/>
       <c r="T28" s="269" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U28" s="32" t="n"/>
+      <c r="U28" s="290" t="n"/>
       <c r="V28" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -7670,10 +7680,10 @@
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="32" t="n"/>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="270" t="inlineStr">
+      <c r="C29" s="290" t="n"/>
+      <c r="D29" s="290" t="n"/>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="271" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
@@ -7691,30 +7701,30 @@
         </is>
       </c>
       <c r="J29" s="35" t="n"/>
-      <c r="K29" s="32" t="n"/>
+      <c r="K29" s="290" t="n"/>
       <c r="L29" s="35" t="n"/>
       <c r="M29" s="35" t="n"/>
       <c r="N29" s="35" t="n"/>
       <c r="O29" s="35" t="n"/>
-      <c r="P29" s="32" t="n"/>
-      <c r="Q29" s="32" t="n"/>
+      <c r="P29" s="290" t="n"/>
+      <c r="Q29" s="290" t="n"/>
       <c r="R29" s="35" t="n"/>
-      <c r="S29" s="32" t="n"/>
-      <c r="T29" s="32" t="n"/>
-      <c r="U29" s="32" t="n"/>
+      <c r="S29" s="290" t="n"/>
+      <c r="T29" s="290" t="n"/>
+      <c r="U29" s="290" t="n"/>
       <c r="V29" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W29" s="32" t="n"/>
-      <c r="X29" s="270" t="inlineStr">
+      <c r="W29" s="290" t="n"/>
+      <c r="X29" s="271" t="inlineStr">
         <is>
           <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
 D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Y29" s="32" t="n"/>
+      <c r="Y29" s="290" t="n"/>
       <c r="Z29" s="35" t="n"/>
     </row>
     <row r="30">
@@ -7728,10 +7738,10 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="270" t="inlineStr">
+      <c r="C30" s="290" t="n"/>
+      <c r="D30" s="290" t="n"/>
+      <c r="E30" s="38" t="n"/>
+      <c r="F30" s="271" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7748,21 +7758,21 @@
         </is>
       </c>
       <c r="J30" s="35" t="n"/>
-      <c r="K30" s="32" t="n"/>
+      <c r="K30" s="290" t="n"/>
       <c r="L30" s="35" t="n"/>
       <c r="M30" s="35" t="n"/>
       <c r="N30" s="35" t="n"/>
       <c r="O30" s="35" t="n"/>
-      <c r="P30" s="32" t="n"/>
-      <c r="Q30" s="32" t="n"/>
+      <c r="P30" s="290" t="n"/>
+      <c r="Q30" s="290" t="n"/>
       <c r="R30" s="35" t="n"/>
-      <c r="S30" s="32" t="n"/>
+      <c r="S30" s="290" t="n"/>
       <c r="T30" s="35" t="n"/>
-      <c r="U30" s="32" t="n"/>
+      <c r="U30" s="290" t="n"/>
       <c r="V30" s="31" t="n"/>
-      <c r="W30" s="32" t="n"/>
-      <c r="X30" s="32" t="n"/>
-      <c r="Y30" s="32" t="n"/>
+      <c r="W30" s="290" t="n"/>
+      <c r="X30" s="290" t="n"/>
+      <c r="Y30" s="290" t="n"/>
       <c r="Z30" s="35" t="n"/>
     </row>
     <row r="31">
@@ -7776,15 +7786,15 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="37" t="n"/>
-      <c r="E31" s="37" t="n"/>
+      <c r="C31" s="290" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="E31" s="38" t="n"/>
       <c r="F31" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G31" s="32" t="n"/>
+      <c r="G31" s="290" t="n"/>
       <c r="H31" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -7795,18 +7805,18 @@
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
+      <c r="J31" s="290" t="n"/>
+      <c r="K31" s="290" t="n"/>
+      <c r="L31" s="290" t="n"/>
+      <c r="M31" s="290" t="n"/>
+      <c r="N31" s="290" t="n"/>
+      <c r="O31" s="290" t="n"/>
+      <c r="P31" s="290" t="n"/>
+      <c r="Q31" s="290" t="n"/>
+      <c r="R31" s="290" t="n"/>
+      <c r="S31" s="290" t="n"/>
+      <c r="T31" s="290" t="n"/>
+      <c r="U31" s="290" t="n"/>
       <c r="V31" s="31" t="n"/>
       <c r="W31" s="35" t="n"/>
       <c r="X31" s="31" t="n"/>
@@ -7824,15 +7834,15 @@
           <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="37" t="n"/>
-      <c r="E32" s="37" t="n"/>
+      <c r="C32" s="290" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="E32" s="38" t="n"/>
       <c r="F32" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G32" s="32" t="n"/>
+      <c r="G32" s="290" t="n"/>
       <c r="H32" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -7843,18 +7853,18 @@
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J32" s="32" t="n"/>
-      <c r="K32" s="32" t="n"/>
-      <c r="L32" s="32" t="n"/>
-      <c r="M32" s="32" t="n"/>
-      <c r="N32" s="32" t="n"/>
-      <c r="O32" s="32" t="n"/>
-      <c r="P32" s="32" t="n"/>
-      <c r="Q32" s="32" t="n"/>
-      <c r="R32" s="32" t="n"/>
-      <c r="S32" s="32" t="n"/>
-      <c r="T32" s="32" t="n"/>
-      <c r="U32" s="32" t="n"/>
+      <c r="J32" s="290" t="n"/>
+      <c r="K32" s="290" t="n"/>
+      <c r="L32" s="290" t="n"/>
+      <c r="M32" s="290" t="n"/>
+      <c r="N32" s="290" t="n"/>
+      <c r="O32" s="290" t="n"/>
+      <c r="P32" s="290" t="n"/>
+      <c r="Q32" s="290" t="n"/>
+      <c r="R32" s="290" t="n"/>
+      <c r="S32" s="290" t="n"/>
+      <c r="T32" s="290" t="n"/>
+      <c r="U32" s="290" t="n"/>
       <c r="V32" s="31" t="n"/>
       <c r="W32" s="35" t="n"/>
       <c r="X32" s="31" t="n"/>
@@ -7872,11 +7882,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="32" t="n"/>
-      <c r="E33" s="32" t="n"/>
+      <c r="C33" s="290" t="n"/>
+      <c r="D33" s="290" t="n"/>
+      <c r="E33" s="290" t="n"/>
       <c r="F33" s="35" t="n"/>
-      <c r="G33" s="32" t="n"/>
+      <c r="G33" s="290" t="n"/>
       <c r="H33" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -7887,23 +7897,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J33" s="32" t="n"/>
-      <c r="K33" s="32" t="n"/>
-      <c r="L33" s="32" t="n"/>
-      <c r="M33" s="32" t="n"/>
-      <c r="N33" s="32" t="n"/>
-      <c r="O33" s="32" t="n"/>
-      <c r="P33" s="32" t="n"/>
-      <c r="Q33" s="32" t="n"/>
-      <c r="R33" s="32" t="n"/>
-      <c r="S33" s="32" t="n"/>
-      <c r="T33" s="32" t="n"/>
-      <c r="U33" s="32" t="n"/>
+      <c r="J33" s="290" t="n"/>
+      <c r="K33" s="290" t="n"/>
+      <c r="L33" s="290" t="n"/>
+      <c r="M33" s="290" t="n"/>
+      <c r="N33" s="290" t="n"/>
+      <c r="O33" s="290" t="n"/>
+      <c r="P33" s="290" t="n"/>
+      <c r="Q33" s="290" t="n"/>
+      <c r="R33" s="290" t="n"/>
+      <c r="S33" s="290" t="n"/>
+      <c r="T33" s="290" t="n"/>
+      <c r="U33" s="290" t="n"/>
       <c r="V33" s="31" t="n"/>
-      <c r="W33" s="32" t="n"/>
-      <c r="X33" s="32" t="n"/>
-      <c r="Y33" s="32" t="n"/>
-      <c r="Z33" s="32" t="n"/>
+      <c r="W33" s="290" t="n"/>
+      <c r="X33" s="290" t="n"/>
+      <c r="Y33" s="290" t="n"/>
+      <c r="Z33" s="290" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="45" t="inlineStr">
@@ -7916,11 +7926,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="37" t="n"/>
-      <c r="E34" s="37" t="n"/>
+      <c r="C34" s="290" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="38" t="n"/>
       <c r="F34" s="35" t="n"/>
-      <c r="G34" s="32" t="n"/>
+      <c r="G34" s="290" t="n"/>
       <c r="H34" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -7931,18 +7941,18 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J34" s="32" t="n"/>
-      <c r="K34" s="32" t="n"/>
-      <c r="L34" s="32" t="n"/>
-      <c r="M34" s="32" t="n"/>
-      <c r="N34" s="32" t="n"/>
-      <c r="O34" s="32" t="n"/>
-      <c r="P34" s="32" t="n"/>
-      <c r="Q34" s="32" t="n"/>
-      <c r="R34" s="32" t="n"/>
-      <c r="S34" s="32" t="n"/>
-      <c r="T34" s="32" t="n"/>
-      <c r="U34" s="32" t="n"/>
+      <c r="J34" s="290" t="n"/>
+      <c r="K34" s="290" t="n"/>
+      <c r="L34" s="290" t="n"/>
+      <c r="M34" s="290" t="n"/>
+      <c r="N34" s="290" t="n"/>
+      <c r="O34" s="290" t="n"/>
+      <c r="P34" s="290" t="n"/>
+      <c r="Q34" s="290" t="n"/>
+      <c r="R34" s="290" t="n"/>
+      <c r="S34" s="290" t="n"/>
+      <c r="T34" s="290" t="n"/>
+      <c r="U34" s="290" t="n"/>
       <c r="V34" s="31" t="n"/>
       <c r="W34" s="35" t="n"/>
       <c r="X34" s="31" t="n"/>
@@ -7960,15 +7970,15 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C35" s="32" t="n"/>
+      <c r="C35" s="290" t="n"/>
       <c r="D35" s="35" t="n"/>
-      <c r="E35" s="37" t="n"/>
+      <c r="E35" s="38" t="n"/>
       <c r="F35" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G35" s="32" t="n"/>
+      <c r="G35" s="290" t="n"/>
       <c r="H35" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -7980,22 +7990,22 @@
         </is>
       </c>
       <c r="J35" s="35" t="n"/>
-      <c r="K35" s="32" t="n"/>
+      <c r="K35" s="290" t="n"/>
       <c r="L35" s="35" t="n"/>
-      <c r="M35" s="37" t="n"/>
+      <c r="M35" s="38" t="n"/>
       <c r="N35" s="38" t="n"/>
       <c r="O35" s="35" t="n"/>
       <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="32" t="n"/>
+      <c r="Q35" s="290" t="n"/>
       <c r="R35" s="35" t="n"/>
       <c r="S35" s="35" t="n"/>
       <c r="T35" s="35" t="n"/>
-      <c r="U35" s="32" t="n"/>
+      <c r="U35" s="290" t="n"/>
       <c r="V35" s="31" t="n"/>
       <c r="W35" s="35" t="n"/>
       <c r="X35" s="35" t="n"/>
       <c r="Y35" s="35" t="n"/>
-      <c r="Z35" s="32" t="n"/>
+      <c r="Z35" s="290" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="45" t="inlineStr">
@@ -8008,11 +8018,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
+      <c r="C36" s="290" t="n"/>
       <c r="D36" s="35" t="n"/>
-      <c r="E36" s="37" t="n"/>
+      <c r="E36" s="38" t="n"/>
       <c r="F36" s="35" t="n"/>
-      <c r="G36" s="32" t="n"/>
+      <c r="G36" s="290" t="n"/>
       <c r="H36" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8024,22 +8034,22 @@
         </is>
       </c>
       <c r="J36" s="35" t="n"/>
-      <c r="K36" s="32" t="n"/>
+      <c r="K36" s="290" t="n"/>
       <c r="L36" s="35" t="n"/>
-      <c r="M36" s="37" t="n"/>
+      <c r="M36" s="38" t="n"/>
       <c r="N36" s="38" t="n"/>
       <c r="O36" s="35" t="n"/>
       <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="32" t="n"/>
+      <c r="Q36" s="290" t="n"/>
       <c r="R36" s="35" t="n"/>
       <c r="S36" s="35" t="n"/>
       <c r="T36" s="35" t="n"/>
-      <c r="U36" s="32" t="n"/>
+      <c r="U36" s="290" t="n"/>
       <c r="V36" s="31" t="n"/>
       <c r="W36" s="35" t="n"/>
       <c r="X36" s="35" t="n"/>
       <c r="Y36" s="35" t="n"/>
-      <c r="Z36" s="32" t="n"/>
+      <c r="Z36" s="290" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="45" t="inlineStr">
@@ -8052,11 +8062,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C37" s="32" t="n"/>
+      <c r="C37" s="290" t="n"/>
       <c r="D37" s="35" t="n"/>
-      <c r="E37" s="37" t="n"/>
+      <c r="E37" s="38" t="n"/>
       <c r="F37" s="35" t="n"/>
-      <c r="G37" s="32" t="n"/>
+      <c r="G37" s="290" t="n"/>
       <c r="H37" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8068,22 +8078,22 @@
         </is>
       </c>
       <c r="J37" s="35" t="n"/>
-      <c r="K37" s="32" t="n"/>
+      <c r="K37" s="290" t="n"/>
       <c r="L37" s="35" t="n"/>
-      <c r="M37" s="37" t="n"/>
+      <c r="M37" s="38" t="n"/>
       <c r="N37" s="38" t="n"/>
       <c r="O37" s="35" t="n"/>
       <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="32" t="n"/>
+      <c r="Q37" s="290" t="n"/>
       <c r="R37" s="35" t="n"/>
       <c r="S37" s="35" t="n"/>
       <c r="T37" s="35" t="n"/>
-      <c r="U37" s="32" t="n"/>
+      <c r="U37" s="290" t="n"/>
       <c r="V37" s="31" t="n"/>
       <c r="W37" s="35" t="n"/>
       <c r="X37" s="35" t="n"/>
       <c r="Y37" s="35" t="n"/>
-      <c r="Z37" s="32" t="n"/>
+      <c r="Z37" s="290" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="45" t="inlineStr">
@@ -8096,11 +8106,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C38" s="32" t="n"/>
+      <c r="C38" s="290" t="n"/>
       <c r="D38" s="35" t="n"/>
-      <c r="E38" s="37" t="n"/>
+      <c r="E38" s="38" t="n"/>
       <c r="F38" s="35" t="n"/>
-      <c r="G38" s="32" t="n"/>
+      <c r="G38" s="290" t="n"/>
       <c r="H38" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8112,22 +8122,22 @@
         </is>
       </c>
       <c r="J38" s="35" t="n"/>
-      <c r="K38" s="32" t="n"/>
+      <c r="K38" s="290" t="n"/>
       <c r="L38" s="35" t="n"/>
-      <c r="M38" s="37" t="n"/>
+      <c r="M38" s="38" t="n"/>
       <c r="N38" s="38" t="n"/>
       <c r="O38" s="35" t="n"/>
       <c r="P38" s="31" t="n"/>
-      <c r="Q38" s="32" t="n"/>
+      <c r="Q38" s="290" t="n"/>
       <c r="R38" s="35" t="n"/>
       <c r="S38" s="35" t="n"/>
       <c r="T38" s="35" t="n"/>
-      <c r="U38" s="32" t="n"/>
+      <c r="U38" s="290" t="n"/>
       <c r="V38" s="31" t="n"/>
       <c r="W38" s="35" t="n"/>
       <c r="X38" s="35" t="n"/>
       <c r="Y38" s="35" t="n"/>
-      <c r="Z38" s="32" t="n"/>
+      <c r="Z38" s="290" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="45" t="inlineStr">
@@ -8140,15 +8150,15 @@
           <t>ARQ-P06 - Piso em porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C39" s="32" t="n"/>
+      <c r="C39" s="290" t="n"/>
       <c r="D39" s="35" t="n"/>
-      <c r="E39" s="37" t="n"/>
+      <c r="E39" s="38" t="n"/>
       <c r="F39" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G39" s="32" t="n"/>
+      <c r="G39" s="290" t="n"/>
       <c r="H39" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
@@ -8160,22 +8170,22 @@
         </is>
       </c>
       <c r="J39" s="35" t="n"/>
-      <c r="K39" s="32" t="n"/>
+      <c r="K39" s="290" t="n"/>
       <c r="L39" s="35" t="n"/>
-      <c r="M39" s="37" t="n"/>
+      <c r="M39" s="38" t="n"/>
       <c r="N39" s="38" t="n"/>
       <c r="O39" s="35" t="n"/>
       <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="32" t="n"/>
+      <c r="Q39" s="290" t="n"/>
       <c r="R39" s="35" t="n"/>
       <c r="S39" s="35" t="n"/>
       <c r="T39" s="35" t="n"/>
-      <c r="U39" s="32" t="n"/>
+      <c r="U39" s="290" t="n"/>
       <c r="V39" s="31" t="n"/>
       <c r="W39" s="35" t="n"/>
       <c r="X39" s="35" t="n"/>
       <c r="Y39" s="35" t="n"/>
-      <c r="Z39" s="32" t="n"/>
+      <c r="Z39" s="290" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="45" t="inlineStr">
@@ -8188,11 +8198,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C40" s="32" t="n"/>
+      <c r="C40" s="290" t="n"/>
       <c r="D40" s="35" t="n"/>
-      <c r="E40" s="37" t="n"/>
+      <c r="E40" s="38" t="n"/>
       <c r="F40" s="35" t="n"/>
-      <c r="G40" s="32" t="n"/>
+      <c r="G40" s="290" t="n"/>
       <c r="H40" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8204,22 +8214,22 @@
         </is>
       </c>
       <c r="J40" s="35" t="n"/>
-      <c r="K40" s="32" t="n"/>
+      <c r="K40" s="290" t="n"/>
       <c r="L40" s="35" t="n"/>
-      <c r="M40" s="37" t="n"/>
+      <c r="M40" s="38" t="n"/>
       <c r="N40" s="38" t="n"/>
       <c r="O40" s="35" t="n"/>
       <c r="P40" s="31" t="n"/>
-      <c r="Q40" s="32" t="n"/>
+      <c r="Q40" s="290" t="n"/>
       <c r="R40" s="35" t="n"/>
       <c r="S40" s="35" t="n"/>
       <c r="T40" s="35" t="n"/>
-      <c r="U40" s="32" t="n"/>
+      <c r="U40" s="290" t="n"/>
       <c r="V40" s="31" t="n"/>
       <c r="W40" s="35" t="n"/>
       <c r="X40" s="35" t="n"/>
       <c r="Y40" s="35" t="n"/>
-      <c r="Z40" s="32" t="n"/>
+      <c r="Z40" s="290" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="45" t="inlineStr">
@@ -8232,11 +8242,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C41" s="32" t="n"/>
+      <c r="C41" s="290" t="n"/>
       <c r="D41" s="35" t="n"/>
-      <c r="E41" s="37" t="n"/>
+      <c r="E41" s="38" t="n"/>
       <c r="F41" s="35" t="n"/>
-      <c r="G41" s="32" t="n"/>
+      <c r="G41" s="290" t="n"/>
       <c r="H41" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8248,22 +8258,22 @@
         </is>
       </c>
       <c r="J41" s="35" t="n"/>
-      <c r="K41" s="32" t="n"/>
+      <c r="K41" s="290" t="n"/>
       <c r="L41" s="35" t="n"/>
-      <c r="M41" s="37" t="n"/>
+      <c r="M41" s="38" t="n"/>
       <c r="N41" s="38" t="n"/>
       <c r="O41" s="35" t="n"/>
       <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="32" t="n"/>
+      <c r="Q41" s="290" t="n"/>
       <c r="R41" s="35" t="n"/>
       <c r="S41" s="35" t="n"/>
       <c r="T41" s="35" t="n"/>
-      <c r="U41" s="32" t="n"/>
+      <c r="U41" s="290" t="n"/>
       <c r="V41" s="31" t="n"/>
       <c r="W41" s="35" t="n"/>
       <c r="X41" s="35" t="n"/>
       <c r="Y41" s="35" t="n"/>
-      <c r="Z41" s="32" t="n"/>
+      <c r="Z41" s="290" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
@@ -8276,11 +8286,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C42" s="32" t="n"/>
+      <c r="C42" s="290" t="n"/>
       <c r="D42" s="35" t="n"/>
-      <c r="E42" s="37" t="n"/>
+      <c r="E42" s="38" t="n"/>
       <c r="F42" s="35" t="n"/>
-      <c r="G42" s="32" t="n"/>
+      <c r="G42" s="290" t="n"/>
       <c r="H42" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8292,22 +8302,22 @@
         </is>
       </c>
       <c r="J42" s="35" t="n"/>
-      <c r="K42" s="32" t="n"/>
+      <c r="K42" s="290" t="n"/>
       <c r="L42" s="35" t="n"/>
-      <c r="M42" s="37" t="n"/>
+      <c r="M42" s="38" t="n"/>
       <c r="N42" s="38" t="n"/>
       <c r="O42" s="35" t="n"/>
       <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="32" t="n"/>
+      <c r="Q42" s="290" t="n"/>
       <c r="R42" s="35" t="n"/>
       <c r="S42" s="35" t="n"/>
       <c r="T42" s="35" t="n"/>
-      <c r="U42" s="32" t="n"/>
+      <c r="U42" s="290" t="n"/>
       <c r="V42" s="31" t="n"/>
       <c r="W42" s="35" t="n"/>
       <c r="X42" s="35" t="n"/>
       <c r="Y42" s="35" t="n"/>
-      <c r="Z42" s="32" t="n"/>
+      <c r="Z42" s="290" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="45" t="inlineStr">
@@ -8320,11 +8330,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C43" s="32" t="n"/>
+      <c r="C43" s="290" t="n"/>
       <c r="D43" s="35" t="n"/>
-      <c r="E43" s="37" t="n"/>
+      <c r="E43" s="38" t="n"/>
       <c r="F43" s="35" t="n"/>
-      <c r="G43" s="32" t="n"/>
+      <c r="G43" s="290" t="n"/>
       <c r="H43" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
@@ -8336,22 +8346,22 @@
         </is>
       </c>
       <c r="J43" s="35" t="n"/>
-      <c r="K43" s="32" t="n"/>
+      <c r="K43" s="290" t="n"/>
       <c r="L43" s="35" t="n"/>
-      <c r="M43" s="37" t="n"/>
+      <c r="M43" s="38" t="n"/>
       <c r="N43" s="38" t="n"/>
       <c r="O43" s="35" t="n"/>
       <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="32" t="n"/>
+      <c r="Q43" s="290" t="n"/>
       <c r="R43" s="35" t="n"/>
       <c r="S43" s="35" t="n"/>
       <c r="T43" s="35" t="n"/>
-      <c r="U43" s="32" t="n"/>
+      <c r="U43" s="290" t="n"/>
       <c r="V43" s="31" t="n"/>
       <c r="W43" s="35" t="n"/>
       <c r="X43" s="35" t="n"/>
       <c r="Y43" s="35" t="n"/>
-      <c r="Z43" s="32" t="n"/>
+      <c r="Z43" s="290" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="45" t="inlineStr">
@@ -8364,11 +8374,11 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C44" s="32" t="n"/>
+      <c r="C44" s="290" t="n"/>
       <c r="D44" s="35" t="n"/>
-      <c r="E44" s="37" t="n"/>
+      <c r="E44" s="38" t="n"/>
       <c r="F44" s="35" t="n"/>
-      <c r="G44" s="32" t="n"/>
+      <c r="G44" s="290" t="n"/>
       <c r="H44" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -8380,22 +8390,22 @@
         </is>
       </c>
       <c r="J44" s="35" t="n"/>
-      <c r="K44" s="32" t="n"/>
+      <c r="K44" s="290" t="n"/>
       <c r="L44" s="35" t="n"/>
-      <c r="M44" s="37" t="n"/>
+      <c r="M44" s="38" t="n"/>
       <c r="N44" s="38" t="n"/>
       <c r="O44" s="35" t="n"/>
       <c r="P44" s="31" t="n"/>
-      <c r="Q44" s="32" t="n"/>
+      <c r="Q44" s="290" t="n"/>
       <c r="R44" s="35" t="n"/>
       <c r="S44" s="35" t="n"/>
       <c r="T44" s="35" t="n"/>
-      <c r="U44" s="32" t="n"/>
+      <c r="U44" s="290" t="n"/>
       <c r="V44" s="31" t="n"/>
       <c r="W44" s="35" t="n"/>
       <c r="X44" s="35" t="n"/>
       <c r="Y44" s="35" t="n"/>
-      <c r="Z44" s="32" t="n"/>
+      <c r="Z44" s="290" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="45" t="inlineStr">
@@ -8408,15 +8418,15 @@
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C45" s="32" t="n"/>
+      <c r="C45" s="290" t="n"/>
       <c r="D45" s="35" t="n"/>
-      <c r="E45" s="37" t="n"/>
+      <c r="E45" s="38" t="n"/>
       <c r="F45" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G45" s="32" t="n"/>
+      <c r="G45" s="290" t="n"/>
       <c r="H45" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -8428,22 +8438,22 @@
         </is>
       </c>
       <c r="J45" s="35" t="n"/>
-      <c r="K45" s="32" t="n"/>
+      <c r="K45" s="290" t="n"/>
       <c r="L45" s="35" t="n"/>
-      <c r="M45" s="37" t="n"/>
+      <c r="M45" s="38" t="n"/>
       <c r="N45" s="38" t="n"/>
       <c r="O45" s="35" t="n"/>
       <c r="P45" s="31" t="n"/>
-      <c r="Q45" s="32" t="n"/>
+      <c r="Q45" s="290" t="n"/>
       <c r="R45" s="35" t="n"/>
       <c r="S45" s="35" t="n"/>
       <c r="T45" s="35" t="n"/>
-      <c r="U45" s="32" t="n"/>
+      <c r="U45" s="290" t="n"/>
       <c r="V45" s="31" t="n"/>
       <c r="W45" s="35" t="n"/>
       <c r="X45" s="35" t="n"/>
       <c r="Y45" s="35" t="n"/>
-      <c r="Z45" s="32" t="n"/>
+      <c r="Z45" s="290" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="45" t="inlineStr">
@@ -8456,11 +8466,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C46" s="32" t="n"/>
+      <c r="C46" s="290" t="n"/>
       <c r="D46" s="35" t="n"/>
-      <c r="E46" s="37" t="n"/>
-      <c r="F46" s="32" t="n"/>
-      <c r="G46" s="32" t="n"/>
+      <c r="E46" s="38" t="n"/>
+      <c r="F46" s="290" t="n"/>
+      <c r="G46" s="290" t="n"/>
       <c r="H46" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -8472,22 +8482,22 @@
         </is>
       </c>
       <c r="J46" s="35" t="n"/>
-      <c r="K46" s="32" t="n"/>
+      <c r="K46" s="290" t="n"/>
       <c r="L46" s="35" t="n"/>
-      <c r="M46" s="37" t="n"/>
+      <c r="M46" s="38" t="n"/>
       <c r="N46" s="38" t="n"/>
       <c r="O46" s="35" t="n"/>
       <c r="P46" s="31" t="n"/>
-      <c r="Q46" s="32" t="n"/>
+      <c r="Q46" s="290" t="n"/>
       <c r="R46" s="35" t="n"/>
       <c r="S46" s="35" t="n"/>
       <c r="T46" s="35" t="n"/>
-      <c r="U46" s="32" t="n"/>
+      <c r="U46" s="290" t="n"/>
       <c r="V46" s="31" t="n"/>
       <c r="W46" s="35" t="n"/>
       <c r="X46" s="35" t="n"/>
       <c r="Y46" s="35" t="n"/>
-      <c r="Z46" s="32" t="n"/>
+      <c r="Z46" s="290" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="45" t="inlineStr">
@@ -8500,11 +8510,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C47" s="32" t="n"/>
+      <c r="C47" s="290" t="n"/>
       <c r="D47" s="35" t="n"/>
-      <c r="E47" s="37" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="32" t="n"/>
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="290" t="n"/>
+      <c r="G47" s="290" t="n"/>
       <c r="H47" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -8516,22 +8526,22 @@
         </is>
       </c>
       <c r="J47" s="35" t="n"/>
-      <c r="K47" s="32" t="n"/>
+      <c r="K47" s="290" t="n"/>
       <c r="L47" s="35" t="n"/>
-      <c r="M47" s="37" t="n"/>
+      <c r="M47" s="38" t="n"/>
       <c r="N47" s="38" t="n"/>
       <c r="O47" s="35" t="n"/>
       <c r="P47" s="31" t="n"/>
-      <c r="Q47" s="32" t="n"/>
+      <c r="Q47" s="290" t="n"/>
       <c r="R47" s="35" t="n"/>
       <c r="S47" s="35" t="n"/>
       <c r="T47" s="35" t="n"/>
-      <c r="U47" s="32" t="n"/>
+      <c r="U47" s="290" t="n"/>
       <c r="V47" s="31" t="n"/>
       <c r="W47" s="35" t="n"/>
       <c r="X47" s="35" t="n"/>
       <c r="Y47" s="35" t="n"/>
-      <c r="Z47" s="32" t="n"/>
+      <c r="Z47" s="290" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="45" t="inlineStr">
@@ -8544,11 +8554,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C48" s="32" t="n"/>
+      <c r="C48" s="290" t="n"/>
       <c r="D48" s="35" t="n"/>
-      <c r="E48" s="37" t="n"/>
-      <c r="F48" s="32" t="n"/>
-      <c r="G48" s="32" t="n"/>
+      <c r="E48" s="38" t="n"/>
+      <c r="F48" s="290" t="n"/>
+      <c r="G48" s="290" t="n"/>
       <c r="H48" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -8560,22 +8570,22 @@
         </is>
       </c>
       <c r="J48" s="35" t="n"/>
-      <c r="K48" s="32" t="n"/>
+      <c r="K48" s="290" t="n"/>
       <c r="L48" s="35" t="n"/>
-      <c r="M48" s="37" t="n"/>
+      <c r="M48" s="38" t="n"/>
       <c r="N48" s="38" t="n"/>
       <c r="O48" s="35" t="n"/>
       <c r="P48" s="31" t="n"/>
-      <c r="Q48" s="32" t="n"/>
+      <c r="Q48" s="290" t="n"/>
       <c r="R48" s="35" t="n"/>
       <c r="S48" s="35" t="n"/>
       <c r="T48" s="35" t="n"/>
-      <c r="U48" s="32" t="n"/>
+      <c r="U48" s="290" t="n"/>
       <c r="V48" s="31" t="n"/>
       <c r="W48" s="35" t="n"/>
       <c r="X48" s="35" t="n"/>
       <c r="Y48" s="35" t="n"/>
-      <c r="Z48" s="32" t="n"/>
+      <c r="Z48" s="290" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="45" t="inlineStr">
@@ -8588,11 +8598,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C49" s="32" t="n"/>
+      <c r="C49" s="290" t="n"/>
       <c r="D49" s="35" t="n"/>
-      <c r="E49" s="37" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="32" t="n"/>
+      <c r="E49" s="38" t="n"/>
+      <c r="F49" s="290" t="n"/>
+      <c r="G49" s="290" t="n"/>
       <c r="H49" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -8600,22 +8610,22 @@
       </c>
       <c r="I49" s="269" t="n"/>
       <c r="J49" s="35" t="n"/>
-      <c r="K49" s="32" t="n"/>
+      <c r="K49" s="290" t="n"/>
       <c r="L49" s="35" t="n"/>
-      <c r="M49" s="37" t="n"/>
+      <c r="M49" s="38" t="n"/>
       <c r="N49" s="38" t="n"/>
       <c r="O49" s="35" t="n"/>
       <c r="P49" s="31" t="n"/>
-      <c r="Q49" s="32" t="n"/>
+      <c r="Q49" s="290" t="n"/>
       <c r="R49" s="35" t="n"/>
       <c r="S49" s="35" t="n"/>
       <c r="T49" s="35" t="n"/>
-      <c r="U49" s="32" t="n"/>
+      <c r="U49" s="290" t="n"/>
       <c r="V49" s="31" t="n"/>
       <c r="W49" s="35" t="n"/>
       <c r="X49" s="35" t="n"/>
       <c r="Y49" s="35" t="n"/>
-      <c r="Z49" s="32" t="n"/>
+      <c r="Z49" s="290" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="45" t="inlineStr">
@@ -8628,11 +8638,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C50" s="32" t="n"/>
+      <c r="C50" s="290" t="n"/>
       <c r="D50" s="35" t="n"/>
-      <c r="E50" s="37" t="n"/>
-      <c r="F50" s="32" t="n"/>
-      <c r="G50" s="32" t="n"/>
+      <c r="E50" s="38" t="n"/>
+      <c r="F50" s="290" t="n"/>
+      <c r="G50" s="290" t="n"/>
       <c r="H50" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -8644,22 +8654,22 @@
         </is>
       </c>
       <c r="J50" s="35" t="n"/>
-      <c r="K50" s="32" t="n"/>
+      <c r="K50" s="290" t="n"/>
       <c r="L50" s="35" t="n"/>
-      <c r="M50" s="37" t="n"/>
+      <c r="M50" s="38" t="n"/>
       <c r="N50" s="38" t="n"/>
       <c r="O50" s="35" t="n"/>
       <c r="P50" s="31" t="n"/>
-      <c r="Q50" s="32" t="n"/>
+      <c r="Q50" s="290" t="n"/>
       <c r="R50" s="35" t="n"/>
       <c r="S50" s="35" t="n"/>
       <c r="T50" s="35" t="n"/>
-      <c r="U50" s="32" t="n"/>
+      <c r="U50" s="290" t="n"/>
       <c r="V50" s="31" t="n"/>
       <c r="W50" s="35" t="n"/>
       <c r="X50" s="35" t="n"/>
       <c r="Y50" s="35" t="n"/>
-      <c r="Z50" s="32" t="n"/>
+      <c r="Z50" s="290" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="45" t="inlineStr">
@@ -8672,11 +8682,11 @@
           <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
         </is>
       </c>
-      <c r="C51" s="32" t="n"/>
+      <c r="C51" s="290" t="n"/>
       <c r="D51" s="35" t="n"/>
-      <c r="E51" s="37" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
+      <c r="E51" s="38" t="n"/>
+      <c r="F51" s="290" t="n"/>
+      <c r="G51" s="290" t="n"/>
       <c r="H51" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -8688,22 +8698,22 @@
         </is>
       </c>
       <c r="J51" s="35" t="n"/>
-      <c r="K51" s="32" t="n"/>
+      <c r="K51" s="290" t="n"/>
       <c r="L51" s="35" t="n"/>
-      <c r="M51" s="37" t="n"/>
+      <c r="M51" s="38" t="n"/>
       <c r="N51" s="38" t="n"/>
       <c r="O51" s="35" t="n"/>
       <c r="P51" s="31" t="n"/>
-      <c r="Q51" s="32" t="n"/>
+      <c r="Q51" s="290" t="n"/>
       <c r="R51" s="35" t="n"/>
       <c r="S51" s="35" t="n"/>
       <c r="T51" s="35" t="n"/>
-      <c r="U51" s="32" t="n"/>
+      <c r="U51" s="290" t="n"/>
       <c r="V51" s="31" t="n"/>
       <c r="W51" s="35" t="n"/>
       <c r="X51" s="35" t="n"/>
       <c r="Y51" s="35" t="n"/>
-      <c r="Z51" s="32" t="n"/>
+      <c r="Z51" s="290" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="45" t="inlineStr">
@@ -8716,11 +8726,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C52" s="32" t="n"/>
+      <c r="C52" s="290" t="n"/>
       <c r="D52" s="35" t="n"/>
-      <c r="E52" s="37" t="n"/>
-      <c r="F52" s="32" t="n"/>
-      <c r="G52" s="32" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="F52" s="290" t="n"/>
+      <c r="G52" s="290" t="n"/>
       <c r="H52" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -8732,22 +8742,22 @@
         </is>
       </c>
       <c r="J52" s="35" t="n"/>
-      <c r="K52" s="32" t="n"/>
+      <c r="K52" s="290" t="n"/>
       <c r="L52" s="35" t="n"/>
-      <c r="M52" s="37" t="n"/>
+      <c r="M52" s="38" t="n"/>
       <c r="N52" s="38" t="n"/>
       <c r="O52" s="35" t="n"/>
       <c r="P52" s="31" t="n"/>
-      <c r="Q52" s="32" t="n"/>
+      <c r="Q52" s="290" t="n"/>
       <c r="R52" s="35" t="n"/>
       <c r="S52" s="35" t="n"/>
       <c r="T52" s="35" t="n"/>
-      <c r="U52" s="32" t="n"/>
+      <c r="U52" s="290" t="n"/>
       <c r="V52" s="31" t="n"/>
       <c r="W52" s="35" t="n"/>
       <c r="X52" s="35" t="n"/>
       <c r="Y52" s="35" t="n"/>
-      <c r="Z52" s="32" t="n"/>
+      <c r="Z52" s="290" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="45" t="inlineStr">
@@ -8760,15 +8770,15 @@
           <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C53" s="32" t="n"/>
+      <c r="C53" s="290" t="n"/>
       <c r="D53" s="35" t="n"/>
-      <c r="E53" s="37" t="n"/>
-      <c r="F53" s="270" t="inlineStr">
+      <c r="E53" s="38" t="n"/>
+      <c r="F53" s="271" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G53" s="32" t="n"/>
+      <c r="G53" s="290" t="n"/>
       <c r="H53" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
@@ -8780,22 +8790,22 @@
         </is>
       </c>
       <c r="J53" s="35" t="n"/>
-      <c r="K53" s="32" t="n"/>
+      <c r="K53" s="290" t="n"/>
       <c r="L53" s="35" t="n"/>
-      <c r="M53" s="37" t="n"/>
+      <c r="M53" s="38" t="n"/>
       <c r="N53" s="38" t="n"/>
       <c r="O53" s="35" t="n"/>
       <c r="P53" s="31" t="n"/>
-      <c r="Q53" s="32" t="n"/>
+      <c r="Q53" s="290" t="n"/>
       <c r="R53" s="35" t="n"/>
       <c r="S53" s="35" t="n"/>
       <c r="T53" s="35" t="n"/>
-      <c r="U53" s="32" t="n"/>
+      <c r="U53" s="290" t="n"/>
       <c r="V53" s="31" t="n"/>
       <c r="W53" s="35" t="n"/>
       <c r="X53" s="35" t="n"/>
       <c r="Y53" s="35" t="n"/>
-      <c r="Z53" s="32" t="n"/>
+      <c r="Z53" s="290" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="45" t="inlineStr">
@@ -8808,11 +8818,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C54" s="32" t="n"/>
+      <c r="C54" s="290" t="n"/>
       <c r="D54" s="35" t="n"/>
-      <c r="E54" s="37" t="n"/>
-      <c r="F54" s="270" t="n"/>
-      <c r="G54" s="32" t="n"/>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="271" t="n"/>
+      <c r="G54" s="290" t="n"/>
       <c r="H54" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -8824,22 +8834,22 @@
         </is>
       </c>
       <c r="J54" s="35" t="n"/>
-      <c r="K54" s="32" t="n"/>
+      <c r="K54" s="290" t="n"/>
       <c r="L54" s="35" t="n"/>
-      <c r="M54" s="37" t="n"/>
+      <c r="M54" s="38" t="n"/>
       <c r="N54" s="38" t="n"/>
       <c r="O54" s="35" t="n"/>
       <c r="P54" s="31" t="n"/>
-      <c r="Q54" s="32" t="n"/>
+      <c r="Q54" s="290" t="n"/>
       <c r="R54" s="35" t="n"/>
       <c r="S54" s="35" t="n"/>
       <c r="T54" s="35" t="n"/>
-      <c r="U54" s="32" t="n"/>
+      <c r="U54" s="290" t="n"/>
       <c r="V54" s="31" t="n"/>
       <c r="W54" s="35" t="n"/>
       <c r="X54" s="35" t="n"/>
       <c r="Y54" s="35" t="n"/>
-      <c r="Z54" s="32" t="n"/>
+      <c r="Z54" s="290" t="n"/>
     </row>
     <row r="55">
       <c r="S55" s="3" t="inlineStr">
@@ -9534,11 +9544,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="49" t="n"/>
-      <c r="G13" s="49" t="n"/>
+      <c r="C13" s="289" t="n"/>
+      <c r="D13" s="289" t="n"/>
+      <c r="E13" s="289" t="n"/>
+      <c r="F13" s="289" t="n"/>
+      <c r="G13" s="289" t="n"/>
       <c r="H13" s="286" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9549,23 +9559,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J13" s="49" t="n"/>
-      <c r="K13" s="49" t="n"/>
-      <c r="L13" s="49" t="n"/>
-      <c r="M13" s="49" t="n"/>
-      <c r="N13" s="49" t="n"/>
-      <c r="O13" s="49" t="n"/>
-      <c r="P13" s="49" t="n"/>
-      <c r="Q13" s="49" t="n"/>
-      <c r="R13" s="49" t="n"/>
-      <c r="S13" s="49" t="n"/>
-      <c r="T13" s="49" t="n"/>
-      <c r="U13" s="49" t="n"/>
-      <c r="V13" s="49" t="n"/>
-      <c r="W13" s="49" t="n"/>
+      <c r="J13" s="289" t="n"/>
+      <c r="K13" s="289" t="n"/>
+      <c r="L13" s="289" t="n"/>
+      <c r="M13" s="289" t="n"/>
+      <c r="N13" s="289" t="n"/>
+      <c r="O13" s="289" t="n"/>
+      <c r="P13" s="289" t="n"/>
+      <c r="Q13" s="289" t="n"/>
+      <c r="R13" s="289" t="n"/>
+      <c r="S13" s="289" t="n"/>
+      <c r="T13" s="289" t="n"/>
+      <c r="U13" s="289" t="n"/>
+      <c r="V13" s="289" t="n"/>
+      <c r="W13" s="289" t="n"/>
       <c r="X13" s="48" t="n"/>
       <c r="Y13" s="48" t="n"/>
-      <c r="Z13" s="49" t="n"/>
+      <c r="Z13" s="289" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="45" t="inlineStr">
@@ -9578,11 +9588,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
+      <c r="C14" s="290" t="n"/>
+      <c r="D14" s="290" t="n"/>
+      <c r="E14" s="290" t="n"/>
+      <c r="F14" s="290" t="n"/>
+      <c r="G14" s="290" t="n"/>
       <c r="H14" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9593,23 +9603,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="32" t="n"/>
-      <c r="P14" s="32" t="n"/>
-      <c r="Q14" s="32" t="n"/>
-      <c r="R14" s="32" t="n"/>
-      <c r="S14" s="32" t="n"/>
-      <c r="T14" s="32" t="n"/>
-      <c r="U14" s="32" t="n"/>
-      <c r="V14" s="32" t="n"/>
-      <c r="W14" s="32" t="n"/>
+      <c r="J14" s="290" t="n"/>
+      <c r="K14" s="290" t="n"/>
+      <c r="L14" s="290" t="n"/>
+      <c r="M14" s="290" t="n"/>
+      <c r="N14" s="290" t="n"/>
+      <c r="O14" s="290" t="n"/>
+      <c r="P14" s="290" t="n"/>
+      <c r="Q14" s="290" t="n"/>
+      <c r="R14" s="290" t="n"/>
+      <c r="S14" s="290" t="n"/>
+      <c r="T14" s="290" t="n"/>
+      <c r="U14" s="290" t="n"/>
+      <c r="V14" s="290" t="n"/>
+      <c r="W14" s="290" t="n"/>
       <c r="X14" s="31" t="n"/>
       <c r="Y14" s="31" t="n"/>
-      <c r="Z14" s="32" t="n"/>
+      <c r="Z14" s="290" t="n"/>
     </row>
     <row r="15" ht="125.25" customHeight="1">
       <c r="A15" s="45" t="inlineStr">
@@ -9618,30 +9628,30 @@
         </is>
       </c>
       <c r="B15" s="31" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
+      <c r="C15" s="290" t="n"/>
+      <c r="D15" s="290" t="n"/>
+      <c r="E15" s="290" t="n"/>
+      <c r="F15" s="290" t="n"/>
+      <c r="G15" s="290" t="n"/>
       <c r="H15" s="33" t="n"/>
       <c r="I15" s="33" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="32" t="n"/>
-      <c r="P15" s="32" t="n"/>
-      <c r="Q15" s="32" t="n"/>
-      <c r="R15" s="32" t="n"/>
-      <c r="S15" s="32" t="n"/>
-      <c r="T15" s="32" t="n"/>
-      <c r="U15" s="32" t="n"/>
-      <c r="V15" s="32" t="n"/>
-      <c r="W15" s="32" t="n"/>
+      <c r="J15" s="290" t="n"/>
+      <c r="K15" s="290" t="n"/>
+      <c r="L15" s="290" t="n"/>
+      <c r="M15" s="290" t="n"/>
+      <c r="N15" s="290" t="n"/>
+      <c r="O15" s="290" t="n"/>
+      <c r="P15" s="290" t="n"/>
+      <c r="Q15" s="290" t="n"/>
+      <c r="R15" s="290" t="n"/>
+      <c r="S15" s="290" t="n"/>
+      <c r="T15" s="290" t="n"/>
+      <c r="U15" s="290" t="n"/>
+      <c r="V15" s="290" t="n"/>
+      <c r="W15" s="290" t="n"/>
       <c r="X15" s="31" t="n"/>
       <c r="Y15" s="31" t="n"/>
-      <c r="Z15" s="32" t="n"/>
+      <c r="Z15" s="290" t="n"/>
     </row>
     <row r="16" ht="125.25" customHeight="1">
       <c r="A16" s="45" t="inlineStr">
@@ -9650,30 +9660,30 @@
         </is>
       </c>
       <c r="B16" s="31" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
+      <c r="C16" s="290" t="n"/>
+      <c r="D16" s="290" t="n"/>
+      <c r="E16" s="290" t="n"/>
+      <c r="F16" s="290" t="n"/>
+      <c r="G16" s="290" t="n"/>
       <c r="H16" s="33" t="n"/>
       <c r="I16" s="33" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="32" t="n"/>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="32" t="n"/>
-      <c r="S16" s="32" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
-      <c r="W16" s="32" t="n"/>
+      <c r="J16" s="290" t="n"/>
+      <c r="K16" s="290" t="n"/>
+      <c r="L16" s="290" t="n"/>
+      <c r="M16" s="290" t="n"/>
+      <c r="N16" s="290" t="n"/>
+      <c r="O16" s="290" t="n"/>
+      <c r="P16" s="290" t="n"/>
+      <c r="Q16" s="290" t="n"/>
+      <c r="R16" s="290" t="n"/>
+      <c r="S16" s="290" t="n"/>
+      <c r="T16" s="290" t="n"/>
+      <c r="U16" s="290" t="n"/>
+      <c r="V16" s="290" t="n"/>
+      <c r="W16" s="290" t="n"/>
       <c r="X16" s="31" t="n"/>
       <c r="Y16" s="31" t="n"/>
-      <c r="Z16" s="32" t="n"/>
+      <c r="Z16" s="290" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="45" t="inlineStr">
@@ -9686,15 +9696,15 @@
           <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="270" t="inlineStr">
+      <c r="C17" s="290" t="n"/>
+      <c r="D17" s="290" t="n"/>
+      <c r="E17" s="290" t="n"/>
+      <c r="F17" s="271" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G17" s="32" t="n"/>
+      <c r="G17" s="290" t="n"/>
       <c r="H17" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9706,23 +9716,23 @@
 ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
-      <c r="O17" s="32" t="n"/>
-      <c r="P17" s="32" t="n"/>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="32" t="n"/>
-      <c r="S17" s="32" t="n"/>
-      <c r="T17" s="32" t="n"/>
-      <c r="U17" s="32" t="n"/>
-      <c r="V17" s="32" t="n"/>
-      <c r="W17" s="32" t="n"/>
+      <c r="J17" s="290" t="n"/>
+      <c r="K17" s="290" t="n"/>
+      <c r="L17" s="290" t="n"/>
+      <c r="M17" s="290" t="n"/>
+      <c r="N17" s="290" t="n"/>
+      <c r="O17" s="290" t="n"/>
+      <c r="P17" s="290" t="n"/>
+      <c r="Q17" s="290" t="n"/>
+      <c r="R17" s="290" t="n"/>
+      <c r="S17" s="290" t="n"/>
+      <c r="T17" s="290" t="n"/>
+      <c r="U17" s="290" t="n"/>
+      <c r="V17" s="290" t="n"/>
+      <c r="W17" s="290" t="n"/>
       <c r="X17" s="31" t="n"/>
       <c r="Y17" s="31" t="n"/>
-      <c r="Z17" s="32" t="n"/>
+      <c r="Z17" s="290" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="45" t="inlineStr">
@@ -9735,11 +9745,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
+      <c r="C18" s="290" t="n"/>
+      <c r="D18" s="290" t="n"/>
+      <c r="E18" s="290" t="n"/>
+      <c r="F18" s="290" t="n"/>
+      <c r="G18" s="290" t="n"/>
       <c r="H18" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9750,23 +9760,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="32" t="n"/>
-      <c r="O18" s="32" t="n"/>
-      <c r="P18" s="32" t="n"/>
-      <c r="Q18" s="32" t="n"/>
-      <c r="R18" s="32" t="n"/>
-      <c r="S18" s="32" t="n"/>
-      <c r="T18" s="32" t="n"/>
-      <c r="U18" s="32" t="n"/>
-      <c r="V18" s="32" t="n"/>
-      <c r="W18" s="32" t="n"/>
+      <c r="J18" s="290" t="n"/>
+      <c r="K18" s="290" t="n"/>
+      <c r="L18" s="290" t="n"/>
+      <c r="M18" s="290" t="n"/>
+      <c r="N18" s="290" t="n"/>
+      <c r="O18" s="290" t="n"/>
+      <c r="P18" s="290" t="n"/>
+      <c r="Q18" s="290" t="n"/>
+      <c r="R18" s="290" t="n"/>
+      <c r="S18" s="290" t="n"/>
+      <c r="T18" s="290" t="n"/>
+      <c r="U18" s="290" t="n"/>
+      <c r="V18" s="290" t="n"/>
+      <c r="W18" s="290" t="n"/>
       <c r="X18" s="31" t="n"/>
       <c r="Y18" s="31" t="n"/>
-      <c r="Z18" s="32" t="n"/>
+      <c r="Z18" s="290" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
@@ -9779,11 +9789,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
+      <c r="C19" s="290" t="n"/>
+      <c r="D19" s="290" t="n"/>
+      <c r="E19" s="290" t="n"/>
+      <c r="F19" s="290" t="n"/>
+      <c r="G19" s="290" t="n"/>
       <c r="H19" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9794,23 +9804,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="32" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="32" t="n"/>
-      <c r="U19" s="32" t="n"/>
-      <c r="V19" s="32" t="n"/>
-      <c r="W19" s="32" t="n"/>
+      <c r="J19" s="290" t="n"/>
+      <c r="K19" s="290" t="n"/>
+      <c r="L19" s="290" t="n"/>
+      <c r="M19" s="290" t="n"/>
+      <c r="N19" s="290" t="n"/>
+      <c r="O19" s="290" t="n"/>
+      <c r="P19" s="290" t="n"/>
+      <c r="Q19" s="290" t="n"/>
+      <c r="R19" s="290" t="n"/>
+      <c r="S19" s="290" t="n"/>
+      <c r="T19" s="290" t="n"/>
+      <c r="U19" s="290" t="n"/>
+      <c r="V19" s="290" t="n"/>
+      <c r="W19" s="290" t="n"/>
       <c r="X19" s="31" t="n"/>
       <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="32" t="n"/>
+      <c r="Z19" s="290" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="45" t="inlineStr">
@@ -9823,10 +9833,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="G20" s="32" t="n"/>
+      <c r="C20" s="290" t="n"/>
+      <c r="D20" s="290" t="n"/>
+      <c r="E20" s="290" t="n"/>
+      <c r="F20" s="292" t="n"/>
+      <c r="G20" s="290" t="n"/>
       <c r="H20" s="271" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9837,23 +9848,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
-      <c r="O20" s="32" t="n"/>
-      <c r="P20" s="32" t="n"/>
-      <c r="Q20" s="32" t="n"/>
-      <c r="R20" s="32" t="n"/>
-      <c r="S20" s="32" t="n"/>
-      <c r="T20" s="32" t="n"/>
-      <c r="U20" s="32" t="n"/>
-      <c r="V20" s="32" t="n"/>
-      <c r="W20" s="32" t="n"/>
+      <c r="J20" s="290" t="n"/>
+      <c r="K20" s="290" t="n"/>
+      <c r="L20" s="290" t="n"/>
+      <c r="M20" s="290" t="n"/>
+      <c r="N20" s="290" t="n"/>
+      <c r="O20" s="290" t="n"/>
+      <c r="P20" s="290" t="n"/>
+      <c r="Q20" s="290" t="n"/>
+      <c r="R20" s="290" t="n"/>
+      <c r="S20" s="290" t="n"/>
+      <c r="T20" s="290" t="n"/>
+      <c r="U20" s="290" t="n"/>
+      <c r="V20" s="290" t="n"/>
+      <c r="W20" s="290" t="n"/>
       <c r="X20" s="31" t="n"/>
       <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="32" t="n"/>
+      <c r="Z20" s="290" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="45" t="inlineStr">
@@ -9867,10 +9878,10 @@
         </is>
       </c>
       <c r="C21" s="34" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
+      <c r="D21" s="290" t="n"/>
+      <c r="E21" s="290" t="n"/>
       <c r="F21" s="34" t="n"/>
-      <c r="G21" s="32" t="n"/>
+      <c r="G21" s="290" t="n"/>
       <c r="H21" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -9881,23 +9892,23 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="n"/>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="32" t="n"/>
+      <c r="J21" s="290" t="n"/>
+      <c r="K21" s="290" t="n"/>
+      <c r="L21" s="290" t="n"/>
+      <c r="M21" s="290" t="n"/>
+      <c r="N21" s="290" t="n"/>
+      <c r="O21" s="290" t="n"/>
+      <c r="P21" s="290" t="n"/>
+      <c r="Q21" s="290" t="n"/>
+      <c r="R21" s="290" t="n"/>
+      <c r="S21" s="290" t="n"/>
+      <c r="T21" s="290" t="n"/>
+      <c r="U21" s="290" t="n"/>
       <c r="V21" s="31" t="n"/>
       <c r="W21" s="34" t="n"/>
       <c r="X21" s="31" t="n"/>
       <c r="Y21" s="31" t="n"/>
-      <c r="Z21" s="32" t="n"/>
+      <c r="Z21" s="290" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="45" t="inlineStr">
@@ -9910,11 +9921,11 @@
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n"/>
+      <c r="C22" s="290" t="n"/>
       <c r="D22" s="34" t="n"/>
-      <c r="E22" s="36" t="n"/>
+      <c r="E22" s="290" t="n"/>
       <c r="F22" s="34" t="n"/>
-      <c r="G22" s="32" t="n"/>
+      <c r="G22" s="290" t="n"/>
       <c r="H22" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -9925,18 +9936,18 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="32" t="n"/>
-      <c r="M22" s="32" t="n"/>
-      <c r="N22" s="32" t="n"/>
-      <c r="O22" s="32" t="n"/>
-      <c r="P22" s="32" t="n"/>
-      <c r="Q22" s="32" t="n"/>
-      <c r="R22" s="32" t="n"/>
-      <c r="S22" s="32" t="n"/>
-      <c r="T22" s="32" t="n"/>
-      <c r="U22" s="32" t="n"/>
+      <c r="J22" s="290" t="n"/>
+      <c r="K22" s="290" t="n"/>
+      <c r="L22" s="290" t="n"/>
+      <c r="M22" s="290" t="n"/>
+      <c r="N22" s="290" t="n"/>
+      <c r="O22" s="290" t="n"/>
+      <c r="P22" s="290" t="n"/>
+      <c r="Q22" s="290" t="n"/>
+      <c r="R22" s="290" t="n"/>
+      <c r="S22" s="290" t="n"/>
+      <c r="T22" s="290" t="n"/>
+      <c r="U22" s="290" t="n"/>
       <c r="V22" s="31" t="n"/>
       <c r="W22" s="35" t="n"/>
       <c r="X22" s="31" t="n"/>
@@ -9954,11 +9965,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="32" t="n"/>
+      <c r="C23" s="290" t="n"/>
+      <c r="D23" s="38" t="n"/>
+      <c r="E23" s="290" t="n"/>
       <c r="F23" s="35" t="n"/>
-      <c r="G23" s="32" t="n"/>
+      <c r="G23" s="290" t="n"/>
       <c r="H23" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -9970,17 +9981,17 @@
         </is>
       </c>
       <c r="J23" s="35" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="37" t="n"/>
-      <c r="N23" s="37" t="n"/>
+      <c r="K23" s="290" t="n"/>
+      <c r="L23" s="290" t="n"/>
+      <c r="M23" s="38" t="n"/>
+      <c r="N23" s="38" t="n"/>
       <c r="O23" s="31" t="n"/>
       <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="32" t="n"/>
+      <c r="Q23" s="290" t="n"/>
       <c r="R23" s="35" t="n"/>
-      <c r="S23" s="32" t="n"/>
+      <c r="S23" s="290" t="n"/>
       <c r="T23" s="35" t="n"/>
-      <c r="U23" s="32" t="n"/>
+      <c r="U23" s="290" t="n"/>
       <c r="V23" s="31" t="n"/>
       <c r="W23" s="35" t="n"/>
       <c r="X23" s="35" t="n"/>
@@ -9998,33 +10009,33 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n"/>
+      <c r="C24" s="290" t="n"/>
       <c r="D24" s="35" t="n"/>
-      <c r="E24" s="37" t="n"/>
+      <c r="E24" s="38" t="n"/>
       <c r="F24" s="35" t="n"/>
-      <c r="G24" s="32" t="n"/>
+      <c r="G24" s="290" t="n"/>
       <c r="H24" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I24" s="270" t="inlineStr">
+      <c r="I24" s="271" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="32" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
+      <c r="J24" s="290" t="n"/>
+      <c r="K24" s="290" t="n"/>
+      <c r="L24" s="290" t="n"/>
+      <c r="M24" s="290" t="n"/>
+      <c r="N24" s="290" t="n"/>
+      <c r="O24" s="290" t="n"/>
+      <c r="P24" s="290" t="n"/>
+      <c r="Q24" s="290" t="n"/>
+      <c r="R24" s="290" t="n"/>
+      <c r="S24" s="290" t="n"/>
       <c r="T24" s="35" t="n"/>
-      <c r="U24" s="32" t="n"/>
+      <c r="U24" s="290" t="n"/>
       <c r="V24" s="31" t="n"/>
       <c r="W24" s="35" t="n"/>
       <c r="X24" s="31" t="n"/>
@@ -10042,10 +10053,10 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="32" t="n"/>
+      <c r="C25" s="290" t="n"/>
+      <c r="D25" s="290" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="290" t="n"/>
       <c r="G25" s="35" t="n"/>
       <c r="H25" s="269" t="inlineStr">
         <is>
@@ -10058,21 +10069,21 @@
         </is>
       </c>
       <c r="J25" s="35" t="n"/>
-      <c r="K25" s="32" t="n"/>
+      <c r="K25" s="290" t="n"/>
       <c r="L25" s="35" t="n"/>
       <c r="M25" s="35" t="n"/>
       <c r="N25" s="35" t="n"/>
       <c r="O25" s="35" t="n"/>
-      <c r="P25" s="32" t="n"/>
-      <c r="Q25" s="32" t="n"/>
+      <c r="P25" s="290" t="n"/>
+      <c r="Q25" s="290" t="n"/>
       <c r="R25" s="35" t="n"/>
-      <c r="S25" s="32" t="n"/>
-      <c r="T25" s="32" t="n"/>
-      <c r="U25" s="32" t="n"/>
+      <c r="S25" s="290" t="n"/>
+      <c r="T25" s="290" t="n"/>
+      <c r="U25" s="290" t="n"/>
       <c r="V25" s="31" t="n"/>
-      <c r="W25" s="32" t="n"/>
-      <c r="X25" s="32" t="n"/>
-      <c r="Y25" s="32" t="n"/>
+      <c r="W25" s="290" t="n"/>
+      <c r="X25" s="290" t="n"/>
+      <c r="Y25" s="290" t="n"/>
       <c r="Z25" s="35" t="n"/>
     </row>
     <row r="26">
@@ -10086,10 +10097,10 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="32" t="n"/>
+      <c r="C26" s="290" t="n"/>
+      <c r="D26" s="290" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="290" t="n"/>
       <c r="G26" s="35" t="n"/>
       <c r="H26" s="269" t="inlineStr">
         <is>
@@ -10102,21 +10113,21 @@
         </is>
       </c>
       <c r="J26" s="35" t="n"/>
-      <c r="K26" s="32" t="n"/>
+      <c r="K26" s="290" t="n"/>
       <c r="L26" s="35" t="n"/>
       <c r="M26" s="35" t="n"/>
       <c r="N26" s="35" t="n"/>
       <c r="O26" s="35" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
+      <c r="P26" s="290" t="n"/>
+      <c r="Q26" s="290" t="n"/>
       <c r="R26" s="35" t="n"/>
-      <c r="S26" s="32" t="n"/>
+      <c r="S26" s="290" t="n"/>
       <c r="T26" s="35" t="n"/>
-      <c r="U26" s="32" t="n"/>
+      <c r="U26" s="290" t="n"/>
       <c r="V26" s="31" t="n"/>
-      <c r="W26" s="32" t="n"/>
-      <c r="X26" s="32" t="n"/>
-      <c r="Y26" s="32" t="n"/>
+      <c r="W26" s="290" t="n"/>
+      <c r="X26" s="290" t="n"/>
+      <c r="Y26" s="290" t="n"/>
       <c r="Z26" s="35" t="n"/>
     </row>
     <row r="27">
@@ -10130,11 +10141,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="37" t="n"/>
-      <c r="E27" s="37" t="n"/>
+      <c r="C27" s="290" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
       <c r="F27" s="35" t="n"/>
-      <c r="G27" s="32" t="n"/>
+      <c r="G27" s="290" t="n"/>
       <c r="H27" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -10145,18 +10156,18 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J27" s="32" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="32" t="n"/>
-      <c r="M27" s="32" t="n"/>
-      <c r="N27" s="32" t="n"/>
-      <c r="O27" s="32" t="n"/>
-      <c r="P27" s="32" t="n"/>
-      <c r="Q27" s="32" t="n"/>
-      <c r="R27" s="32" t="n"/>
-      <c r="S27" s="32" t="n"/>
-      <c r="T27" s="32" t="n"/>
-      <c r="U27" s="32" t="n"/>
+      <c r="J27" s="290" t="n"/>
+      <c r="K27" s="290" t="n"/>
+      <c r="L27" s="290" t="n"/>
+      <c r="M27" s="290" t="n"/>
+      <c r="N27" s="290" t="n"/>
+      <c r="O27" s="290" t="n"/>
+      <c r="P27" s="290" t="n"/>
+      <c r="Q27" s="290" t="n"/>
+      <c r="R27" s="290" t="n"/>
+      <c r="S27" s="290" t="n"/>
+      <c r="T27" s="290" t="n"/>
+      <c r="U27" s="290" t="n"/>
       <c r="V27" s="31" t="n"/>
       <c r="W27" s="35" t="n"/>
       <c r="X27" s="31" t="n"/>
@@ -10174,11 +10185,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
+      <c r="C28" s="290" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="38" t="n"/>
       <c r="F28" s="35" t="n"/>
-      <c r="G28" s="32" t="n"/>
+      <c r="G28" s="290" t="n"/>
       <c r="H28" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -10189,18 +10200,18 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J28" s="32" t="n"/>
-      <c r="K28" s="32" t="n"/>
-      <c r="L28" s="32" t="n"/>
-      <c r="M28" s="32" t="n"/>
-      <c r="N28" s="32" t="n"/>
-      <c r="O28" s="32" t="n"/>
-      <c r="P28" s="32" t="n"/>
-      <c r="Q28" s="32" t="n"/>
-      <c r="R28" s="32" t="n"/>
-      <c r="S28" s="32" t="n"/>
-      <c r="T28" s="32" t="n"/>
-      <c r="U28" s="32" t="n"/>
+      <c r="J28" s="290" t="n"/>
+      <c r="K28" s="290" t="n"/>
+      <c r="L28" s="290" t="n"/>
+      <c r="M28" s="290" t="n"/>
+      <c r="N28" s="290" t="n"/>
+      <c r="O28" s="290" t="n"/>
+      <c r="P28" s="290" t="n"/>
+      <c r="Q28" s="290" t="n"/>
+      <c r="R28" s="290" t="n"/>
+      <c r="S28" s="290" t="n"/>
+      <c r="T28" s="290" t="n"/>
+      <c r="U28" s="290" t="n"/>
       <c r="V28" s="31" t="n"/>
       <c r="W28" s="35" t="n"/>
       <c r="X28" s="31" t="n"/>
@@ -10218,11 +10229,11 @@
           <t>ARQ-P04 - Piso em concreto mecanizado com acabamento em ladrilho hidráulico antiderrapante cinza, tom concreto. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="37" t="n"/>
-      <c r="E29" s="37" t="n"/>
+      <c r="C29" s="290" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="38" t="n"/>
       <c r="F29" s="35" t="n"/>
-      <c r="G29" s="32" t="n"/>
+      <c r="G29" s="290" t="n"/>
       <c r="H29" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -10233,18 +10244,18 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J29" s="32" t="n"/>
-      <c r="K29" s="32" t="n"/>
-      <c r="L29" s="32" t="n"/>
-      <c r="M29" s="32" t="n"/>
-      <c r="N29" s="32" t="n"/>
-      <c r="O29" s="32" t="n"/>
-      <c r="P29" s="32" t="n"/>
-      <c r="Q29" s="32" t="n"/>
-      <c r="R29" s="32" t="n"/>
-      <c r="S29" s="32" t="n"/>
-      <c r="T29" s="32" t="n"/>
-      <c r="U29" s="32" t="n"/>
+      <c r="J29" s="290" t="n"/>
+      <c r="K29" s="290" t="n"/>
+      <c r="L29" s="290" t="n"/>
+      <c r="M29" s="290" t="n"/>
+      <c r="N29" s="290" t="n"/>
+      <c r="O29" s="290" t="n"/>
+      <c r="P29" s="290" t="n"/>
+      <c r="Q29" s="290" t="n"/>
+      <c r="R29" s="290" t="n"/>
+      <c r="S29" s="290" t="n"/>
+      <c r="T29" s="290" t="n"/>
+      <c r="U29" s="290" t="n"/>
       <c r="V29" s="31" t="n"/>
       <c r="W29" s="35" t="n"/>
       <c r="X29" s="31" t="n"/>
@@ -10262,11 +10273,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="37" t="n"/>
+      <c r="C30" s="290" t="n"/>
+      <c r="D30" s="38" t="n"/>
+      <c r="E30" s="38" t="n"/>
       <c r="F30" s="35" t="n"/>
-      <c r="G30" s="32" t="n"/>
+      <c r="G30" s="290" t="n"/>
       <c r="H30" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -10277,18 +10288,18 @@
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J30" s="32" t="n"/>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="32" t="n"/>
-      <c r="M30" s="32" t="n"/>
-      <c r="N30" s="32" t="n"/>
-      <c r="O30" s="32" t="n"/>
-      <c r="P30" s="32" t="n"/>
-      <c r="Q30" s="32" t="n"/>
-      <c r="R30" s="32" t="n"/>
-      <c r="S30" s="32" t="n"/>
-      <c r="T30" s="32" t="n"/>
-      <c r="U30" s="32" t="n"/>
+      <c r="J30" s="290" t="n"/>
+      <c r="K30" s="290" t="n"/>
+      <c r="L30" s="290" t="n"/>
+      <c r="M30" s="290" t="n"/>
+      <c r="N30" s="290" t="n"/>
+      <c r="O30" s="290" t="n"/>
+      <c r="P30" s="290" t="n"/>
+      <c r="Q30" s="290" t="n"/>
+      <c r="R30" s="290" t="n"/>
+      <c r="S30" s="290" t="n"/>
+      <c r="T30" s="290" t="n"/>
+      <c r="U30" s="290" t="n"/>
       <c r="V30" s="31" t="n"/>
       <c r="W30" s="35" t="n"/>
       <c r="X30" s="31" t="n"/>
@@ -10306,11 +10317,11 @@
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
       </c>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="37" t="n"/>
-      <c r="E31" s="37" t="n"/>
+      <c r="C31" s="290" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="E31" s="38" t="n"/>
       <c r="F31" s="35" t="n"/>
-      <c r="G31" s="32" t="n"/>
+      <c r="G31" s="290" t="n"/>
       <c r="H31" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -10321,24 +10332,27 @@
           <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
       </c>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
+      <c r="J31" s="290" t="n"/>
+      <c r="K31" s="290" t="n"/>
+      <c r="L31" s="290" t="n"/>
+      <c r="M31" s="290" t="n"/>
+      <c r="N31" s="290" t="n"/>
+      <c r="O31" s="290" t="n"/>
+      <c r="P31" s="290" t="n"/>
+      <c r="Q31" s="290" t="n"/>
+      <c r="R31" s="290" t="n"/>
+      <c r="S31" s="290" t="n"/>
+      <c r="T31" s="290" t="n"/>
+      <c r="U31" s="290" t="n"/>
       <c r="V31" s="31" t="n"/>
       <c r="W31" s="35" t="n"/>
       <c r="X31" s="31" t="n"/>
       <c r="Y31" s="31" t="n"/>
       <c r="Z31" s="35" t="n"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="S35" s="3" t="inlineStr">
         <is>
@@ -11043,15 +11057,15 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
+      <c r="C13" s="289" t="n"/>
+      <c r="D13" s="289" t="n"/>
+      <c r="E13" s="289" t="n"/>
       <c r="F13" s="244" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G13" s="49" t="n"/>
+      <c r="G13" s="289" t="n"/>
       <c r="H13" s="274" t="inlineStr">
         <is>
           <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
@@ -11065,28 +11079,28 @@
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J13" s="49" t="n"/>
+      <c r="J13" s="289" t="n"/>
       <c r="K13" s="244" t="inlineStr">
         <is>
           <t>D75 - Fechamento decorativo piso teto com quadro fixado no piso e no teto através de espaçadores e fechamento com desenho conforme base para corte de molde em CNC - peças em madeira maciça engenheirada, tonalizada,acabamento escovado, calandradas conforme molde. Ref.: Demuner. ATENÇÃO:a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="L13" s="49" t="n"/>
-      <c r="M13" s="49" t="n"/>
-      <c r="N13" s="49" t="n"/>
-      <c r="O13" s="49" t="n"/>
-      <c r="P13" s="49" t="n"/>
-      <c r="Q13" s="49" t="n"/>
-      <c r="R13" s="49" t="n"/>
-      <c r="S13" s="49" t="n"/>
-      <c r="T13" s="49" t="n"/>
-      <c r="U13" s="49" t="n"/>
-      <c r="V13" s="275" t="inlineStr">
+      <c r="L13" s="289" t="n"/>
+      <c r="M13" s="289" t="n"/>
+      <c r="N13" s="289" t="n"/>
+      <c r="O13" s="289" t="n"/>
+      <c r="P13" s="289" t="n"/>
+      <c r="Q13" s="289" t="n"/>
+      <c r="R13" s="289" t="n"/>
+      <c r="S13" s="289" t="n"/>
+      <c r="T13" s="289" t="n"/>
+      <c r="U13" s="289" t="n"/>
+      <c r="V13" s="286" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W13" s="49" t="n"/>
+      <c r="W13" s="289" t="n"/>
       <c r="X13" s="276" t="inlineStr">
         <is>
           <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
@@ -11096,7 +11110,7 @@
         </is>
       </c>
       <c r="Y13" s="48" t="n"/>
-      <c r="Z13" s="49" t="n"/>
+      <c r="Z13" s="289" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="45" t="inlineStr">
@@ -11110,15 +11124,15 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
+      <c r="C14" s="290" t="n"/>
+      <c r="D14" s="290" t="n"/>
+      <c r="E14" s="290" t="n"/>
       <c r="F14" s="246" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G14" s="32" t="n"/>
+      <c r="G14" s="290" t="n"/>
       <c r="H14" s="246" t="inlineStr">
         <is>
           <t>PA40 - Parede em alvenaria emassada regularizada, revestida em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
@@ -11138,23 +11152,23 @@
           <t>D24 - Bancada em pedra natural, mármore Dedalus, acabamento escovado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="32" t="n"/>
-      <c r="P14" s="32" t="n"/>
-      <c r="Q14" s="32" t="n"/>
-      <c r="R14" s="32" t="n"/>
-      <c r="S14" s="32" t="n"/>
-      <c r="T14" s="32" t="n"/>
-      <c r="U14" s="32" t="n"/>
-      <c r="V14" s="270" t="inlineStr">
+      <c r="K14" s="290" t="n"/>
+      <c r="L14" s="290" t="n"/>
+      <c r="M14" s="290" t="n"/>
+      <c r="N14" s="290" t="n"/>
+      <c r="O14" s="290" t="n"/>
+      <c r="P14" s="290" t="n"/>
+      <c r="Q14" s="290" t="n"/>
+      <c r="R14" s="290" t="n"/>
+      <c r="S14" s="290" t="n"/>
+      <c r="T14" s="290" t="n"/>
+      <c r="U14" s="290" t="n"/>
+      <c r="V14" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W14" s="32" t="n"/>
+      <c r="W14" s="290" t="n"/>
       <c r="X14" s="269" t="inlineStr">
         <is>
           <t>D21 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxadores conforme detalhamento. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
@@ -11162,7 +11176,7 @@
         </is>
       </c>
       <c r="Y14" s="31" t="n"/>
-      <c r="Z14" s="32" t="n"/>
+      <c r="Z14" s="290" t="n"/>
     </row>
     <row r="15" ht="125.25" customHeight="1">
       <c r="A15" s="45" t="inlineStr">
@@ -11171,30 +11185,30 @@
         </is>
       </c>
       <c r="B15" s="31" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
+      <c r="C15" s="290" t="n"/>
+      <c r="D15" s="290" t="n"/>
+      <c r="E15" s="290" t="n"/>
+      <c r="F15" s="290" t="n"/>
+      <c r="G15" s="290" t="n"/>
       <c r="H15" s="33" t="n"/>
       <c r="I15" s="33" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="32" t="n"/>
-      <c r="P15" s="32" t="n"/>
-      <c r="Q15" s="32" t="n"/>
-      <c r="R15" s="32" t="n"/>
-      <c r="S15" s="32" t="n"/>
-      <c r="T15" s="32" t="n"/>
-      <c r="U15" s="32" t="n"/>
-      <c r="V15" s="32" t="n"/>
-      <c r="W15" s="32" t="n"/>
+      <c r="J15" s="290" t="n"/>
+      <c r="K15" s="290" t="n"/>
+      <c r="L15" s="290" t="n"/>
+      <c r="M15" s="290" t="n"/>
+      <c r="N15" s="290" t="n"/>
+      <c r="O15" s="290" t="n"/>
+      <c r="P15" s="290" t="n"/>
+      <c r="Q15" s="290" t="n"/>
+      <c r="R15" s="290" t="n"/>
+      <c r="S15" s="290" t="n"/>
+      <c r="T15" s="290" t="n"/>
+      <c r="U15" s="290" t="n"/>
+      <c r="V15" s="290" t="n"/>
+      <c r="W15" s="290" t="n"/>
       <c r="X15" s="31" t="n"/>
       <c r="Y15" s="31" t="n"/>
-      <c r="Z15" s="32" t="n"/>
+      <c r="Z15" s="290" t="n"/>
     </row>
     <row r="16" ht="125.25" customHeight="1">
       <c r="A16" s="45" t="inlineStr">
@@ -11203,30 +11217,30 @@
         </is>
       </c>
       <c r="B16" s="31" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
+      <c r="C16" s="290" t="n"/>
+      <c r="D16" s="290" t="n"/>
+      <c r="E16" s="290" t="n"/>
+      <c r="F16" s="290" t="n"/>
+      <c r="G16" s="290" t="n"/>
       <c r="H16" s="33" t="n"/>
       <c r="I16" s="33" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="32" t="n"/>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="32" t="n"/>
-      <c r="S16" s="32" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
-      <c r="W16" s="32" t="n"/>
+      <c r="J16" s="290" t="n"/>
+      <c r="K16" s="290" t="n"/>
+      <c r="L16" s="290" t="n"/>
+      <c r="M16" s="290" t="n"/>
+      <c r="N16" s="290" t="n"/>
+      <c r="O16" s="290" t="n"/>
+      <c r="P16" s="290" t="n"/>
+      <c r="Q16" s="290" t="n"/>
+      <c r="R16" s="290" t="n"/>
+      <c r="S16" s="290" t="n"/>
+      <c r="T16" s="290" t="n"/>
+      <c r="U16" s="290" t="n"/>
+      <c r="V16" s="290" t="n"/>
+      <c r="W16" s="290" t="n"/>
       <c r="X16" s="31" t="n"/>
       <c r="Y16" s="31" t="n"/>
-      <c r="Z16" s="32" t="n"/>
+      <c r="Z16" s="290" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="45" t="inlineStr">
@@ -11240,15 +11254,15 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
+      <c r="C17" s="290" t="n"/>
+      <c r="D17" s="290" t="n"/>
+      <c r="E17" s="290" t="n"/>
       <c r="F17" s="246" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G17" s="32" t="n"/>
+      <c r="G17" s="290" t="n"/>
       <c r="H17" s="246" t="inlineStr">
         <is>
           <t>PA39 - Parede em alvenaria rebocada regularizada revestida em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -11269,9 +11283,9 @@
           <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
+      <c r="L17" s="290" t="n"/>
+      <c r="M17" s="290" t="n"/>
+      <c r="N17" s="290" t="n"/>
       <c r="O17" s="246" t="inlineStr">
         <is>
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
@@ -11282,17 +11296,17 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="32" t="n"/>
-      <c r="S17" s="32" t="n"/>
-      <c r="T17" s="32" t="n"/>
-      <c r="U17" s="32" t="n"/>
-      <c r="V17" s="270" t="inlineStr">
+      <c r="Q17" s="290" t="n"/>
+      <c r="R17" s="290" t="n"/>
+      <c r="S17" s="290" t="n"/>
+      <c r="T17" s="290" t="n"/>
+      <c r="U17" s="290" t="n"/>
+      <c r="V17" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W17" s="32" t="n"/>
+      <c r="W17" s="290" t="n"/>
       <c r="X17" s="269" t="inlineStr">
         <is>
           <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
@@ -11319,15 +11333,15 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
+      <c r="C18" s="290" t="n"/>
+      <c r="D18" s="290" t="n"/>
+      <c r="E18" s="290" t="n"/>
       <c r="F18" s="246" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G18" s="32" t="n"/>
+      <c r="G18" s="290" t="n"/>
       <c r="H18" s="246" t="inlineStr">
         <is>
           <t>PA39 - Parede em alvenaria rebocada regularizada revestida em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -11348,9 +11362,9 @@
           <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="32" t="n"/>
+      <c r="L18" s="290" t="n"/>
+      <c r="M18" s="290" t="n"/>
+      <c r="N18" s="290" t="n"/>
       <c r="O18" s="246" t="inlineStr">
         <is>
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
@@ -11361,17 +11375,17 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q18" s="32" t="n"/>
-      <c r="R18" s="32" t="n"/>
-      <c r="S18" s="32" t="n"/>
-      <c r="T18" s="32" t="n"/>
-      <c r="U18" s="32" t="n"/>
-      <c r="V18" s="270" t="inlineStr">
+      <c r="Q18" s="290" t="n"/>
+      <c r="R18" s="290" t="n"/>
+      <c r="S18" s="290" t="n"/>
+      <c r="T18" s="290" t="n"/>
+      <c r="U18" s="290" t="n"/>
+      <c r="V18" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W18" s="32" t="n"/>
+      <c r="W18" s="290" t="n"/>
       <c r="X18" s="269" t="inlineStr">
         <is>
           <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
@@ -11393,30 +11407,30 @@
         </is>
       </c>
       <c r="B19" s="31" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
+      <c r="C19" s="290" t="n"/>
+      <c r="D19" s="290" t="n"/>
+      <c r="E19" s="290" t="n"/>
+      <c r="F19" s="290" t="n"/>
+      <c r="G19" s="290" t="n"/>
       <c r="H19" s="33" t="n"/>
       <c r="I19" s="33" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="32" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="32" t="n"/>
-      <c r="U19" s="32" t="n"/>
-      <c r="V19" s="32" t="n"/>
-      <c r="W19" s="32" t="n"/>
+      <c r="J19" s="290" t="n"/>
+      <c r="K19" s="290" t="n"/>
+      <c r="L19" s="290" t="n"/>
+      <c r="M19" s="290" t="n"/>
+      <c r="N19" s="290" t="n"/>
+      <c r="O19" s="290" t="n"/>
+      <c r="P19" s="290" t="n"/>
+      <c r="Q19" s="290" t="n"/>
+      <c r="R19" s="290" t="n"/>
+      <c r="S19" s="290" t="n"/>
+      <c r="T19" s="290" t="n"/>
+      <c r="U19" s="290" t="n"/>
+      <c r="V19" s="290" t="n"/>
+      <c r="W19" s="290" t="n"/>
       <c r="X19" s="31" t="n"/>
       <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="32" t="n"/>
+      <c r="Z19" s="290" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="45" t="inlineStr">
@@ -11430,15 +11444,15 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
+      <c r="C20" s="290" t="n"/>
+      <c r="D20" s="290" t="n"/>
+      <c r="E20" s="290" t="n"/>
       <c r="F20" s="247" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede</t>
         </is>
       </c>
-      <c r="G20" s="32" t="n"/>
+      <c r="G20" s="290" t="n"/>
       <c r="H20" s="246" t="inlineStr">
         <is>
           <t>PA43 - Parede emassada regularizada, revestida com fórmica cor Almond L112, acabamento mate. Ref.: Formica. Dimensões e paginações conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.
@@ -11455,31 +11469,31 @@
           <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="K20" s="32" t="n"/>
+      <c r="K20" s="290" t="n"/>
       <c r="L20" s="246" t="inlineStr">
         <is>
           <t>D80 - Cuba de embutir, Dora 70 em aço inox, 70x40cm, acabamento acetinado, cód.: BL R6. Ref.: Tramontina</t>
         </is>
       </c>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
+      <c r="M20" s="290" t="n"/>
+      <c r="N20" s="290" t="n"/>
       <c r="O20" s="246" t="inlineStr">
         <is>
           <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scoth Brite, cód.: 94520022. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P20" s="32" t="n"/>
-      <c r="Q20" s="32" t="n"/>
-      <c r="R20" s="32" t="n"/>
-      <c r="S20" s="32" t="n"/>
-      <c r="T20" s="32" t="n"/>
-      <c r="U20" s="32" t="n"/>
-      <c r="V20" s="270" t="inlineStr">
+      <c r="P20" s="290" t="n"/>
+      <c r="Q20" s="290" t="n"/>
+      <c r="R20" s="290" t="n"/>
+      <c r="S20" s="290" t="n"/>
+      <c r="T20" s="290" t="n"/>
+      <c r="U20" s="290" t="n"/>
+      <c r="V20" s="271" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W20" s="32" t="n"/>
+      <c r="W20" s="290" t="n"/>
       <c r="X20" s="269" t="inlineStr">
         <is>
           <t>D21 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxadores conforme detalhamento. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
@@ -11487,7 +11501,7 @@
         </is>
       </c>
       <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="270" t="inlineStr">
+      <c r="Z20" s="271" t="inlineStr">
         <is>
           <t>D82 - Prateleira em granito cinza Santa Rosa, acabamento escovado, embutido na alvenaria. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -11504,15 +11518,15 @@
           <t>P7 - Piso de granito cinza Santa Rosa, acabamento escovado, espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizado de acordo com a cor da pedra, assentado com argamassa colante em pó ACIII. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
+      <c r="C21" s="290" t="n"/>
+      <c r="D21" s="290" t="n"/>
+      <c r="E21" s="290" t="n"/>
       <c r="F21" s="246" t="inlineStr">
         <is>
           <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII</t>
         </is>
       </c>
-      <c r="G21" s="32" t="n"/>
+      <c r="G21" s="290" t="n"/>
       <c r="H21" s="246" t="inlineStr">
         <is>
           <t>PA47 - Pintura com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor</t>
@@ -11523,31 +11537,31 @@
           <t>01| T1| T8 - Forro de gesso acartonado liso| 01|07| 08 - Pintura acrílica, cor branca neve, acabamento fosco, Ref.: Suvinil sob tetos (2 demãos Latex acrílico)</t>
         </is>
       </c>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
+      <c r="J21" s="290" t="n"/>
+      <c r="K21" s="290" t="n"/>
       <c r="L21" s="246" t="inlineStr">
         <is>
           <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.: TQ.01.17, Ref.: Deca</t>
         </is>
       </c>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
+      <c r="M21" s="290" t="n"/>
+      <c r="N21" s="290" t="n"/>
       <c r="O21" s="246" t="inlineStr">
         <is>
           <t>D67 - Torneira de parede com arejador, para jardim e tanque, linha Izy, acabamento cromado. Cód.: 1154 C37; Ref.: Deca</t>
         </is>
       </c>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="32" t="n"/>
-      <c r="V21" s="32" t="n"/>
-      <c r="W21" s="32" t="n"/>
+      <c r="P21" s="290" t="n"/>
+      <c r="Q21" s="290" t="n"/>
+      <c r="R21" s="290" t="n"/>
+      <c r="S21" s="290" t="n"/>
+      <c r="T21" s="290" t="n"/>
+      <c r="U21" s="290" t="n"/>
+      <c r="V21" s="290" t="n"/>
+      <c r="W21" s="290" t="n"/>
       <c r="X21" s="31" t="n"/>
       <c r="Y21" s="31" t="n"/>
-      <c r="Z21" s="32" t="n"/>
+      <c r="Z21" s="290" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="45" t="inlineStr">
@@ -11561,14 +11575,14 @@
         </is>
       </c>
       <c r="C22" s="34" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="32" t="n"/>
+      <c r="D22" s="290" t="n"/>
+      <c r="E22" s="290" t="n"/>
       <c r="F22" s="269" t="inlineStr">
         <is>
           <t>ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="G22" s="32" t="n"/>
+      <c r="G22" s="290" t="n"/>
       <c r="H22" s="269" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
@@ -11579,23 +11593,23 @@
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="32" t="n"/>
-      <c r="M22" s="32" t="n"/>
-      <c r="N22" s="32" t="n"/>
-      <c r="O22" s="32" t="n"/>
-      <c r="P22" s="32" t="n"/>
-      <c r="Q22" s="32" t="n"/>
-      <c r="R22" s="32" t="n"/>
-      <c r="S22" s="32" t="n"/>
-      <c r="T22" s="32" t="n"/>
-      <c r="U22" s="32" t="n"/>
+      <c r="J22" s="290" t="n"/>
+      <c r="K22" s="290" t="n"/>
+      <c r="L22" s="290" t="n"/>
+      <c r="M22" s="290" t="n"/>
+      <c r="N22" s="290" t="n"/>
+      <c r="O22" s="290" t="n"/>
+      <c r="P22" s="290" t="n"/>
+      <c r="Q22" s="290" t="n"/>
+      <c r="R22" s="290" t="n"/>
+      <c r="S22" s="290" t="n"/>
+      <c r="T22" s="290" t="n"/>
+      <c r="U22" s="290" t="n"/>
       <c r="V22" s="31" t="n"/>
       <c r="W22" s="34" t="n"/>
       <c r="X22" s="31" t="n"/>
       <c r="Y22" s="31" t="n"/>
-      <c r="Z22" s="32" t="n"/>
+      <c r="Z22" s="290" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="45" t="inlineStr">
@@ -11608,15 +11622,15 @@
           <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n"/>
+      <c r="C23" s="290" t="n"/>
       <c r="D23" s="34" t="n"/>
-      <c r="E23" s="36" t="n"/>
+      <c r="E23" s="290" t="n"/>
       <c r="F23" s="245" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G23" s="32" t="n"/>
+      <c r="G23" s="290" t="n"/>
       <c r="H23" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -11639,9 +11653,9 @@
           <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
+      <c r="L23" s="290" t="n"/>
+      <c r="M23" s="290" t="n"/>
+      <c r="N23" s="290" t="n"/>
       <c r="O23" s="246" t="inlineStr">
         <is>
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
@@ -11652,11 +11666,11 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
+      <c r="Q23" s="290" t="n"/>
+      <c r="R23" s="290" t="n"/>
+      <c r="S23" s="290" t="n"/>
+      <c r="T23" s="290" t="n"/>
+      <c r="U23" s="290" t="n"/>
       <c r="V23" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -11688,15 +11702,15 @@
           <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="32" t="n"/>
+      <c r="C24" s="290" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="290" t="n"/>
       <c r="F24" s="245" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G24" s="32" t="n"/>
+      <c r="G24" s="290" t="n"/>
       <c r="H24" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -11719,9 +11733,9 @@
           <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="37" t="n"/>
-      <c r="N24" s="37" t="n"/>
+      <c r="L24" s="290" t="n"/>
+      <c r="M24" s="38" t="n"/>
+      <c r="N24" s="38" t="n"/>
       <c r="O24" s="245" t="inlineStr">
         <is>
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
@@ -11732,11 +11746,11 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q24" s="32" t="n"/>
+      <c r="Q24" s="290" t="n"/>
       <c r="R24" s="35" t="n"/>
-      <c r="S24" s="32" t="n"/>
+      <c r="S24" s="290" t="n"/>
       <c r="T24" s="35" t="n"/>
-      <c r="U24" s="32" t="n"/>
+      <c r="U24" s="290" t="n"/>
       <c r="V24" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -11764,25 +11778,25 @@
         </is>
       </c>
       <c r="B25" s="35" t="n"/>
-      <c r="C25" s="32" t="n"/>
+      <c r="C25" s="290" t="n"/>
       <c r="D25" s="35" t="n"/>
-      <c r="E25" s="37" t="n"/>
+      <c r="E25" s="38" t="n"/>
       <c r="F25" s="35" t="n"/>
-      <c r="G25" s="32" t="n"/>
+      <c r="G25" s="290" t="n"/>
       <c r="H25" s="35" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="32" t="n"/>
-      <c r="M25" s="32" t="n"/>
-      <c r="N25" s="32" t="n"/>
-      <c r="O25" s="32" t="n"/>
-      <c r="P25" s="32" t="n"/>
-      <c r="Q25" s="32" t="n"/>
-      <c r="R25" s="32" t="n"/>
-      <c r="S25" s="32" t="n"/>
+      <c r="I25" s="290" t="n"/>
+      <c r="J25" s="290" t="n"/>
+      <c r="K25" s="290" t="n"/>
+      <c r="L25" s="290" t="n"/>
+      <c r="M25" s="290" t="n"/>
+      <c r="N25" s="290" t="n"/>
+      <c r="O25" s="290" t="n"/>
+      <c r="P25" s="290" t="n"/>
+      <c r="Q25" s="290" t="n"/>
+      <c r="R25" s="290" t="n"/>
+      <c r="S25" s="290" t="n"/>
       <c r="T25" s="35" t="n"/>
-      <c r="U25" s="32" t="n"/>
+      <c r="U25" s="290" t="n"/>
       <c r="V25" s="31" t="n"/>
       <c r="W25" s="35" t="n"/>
       <c r="X25" s="31" t="n"/>
@@ -11801,15 +11815,15 @@
 P24 - Piso em contrapiso regularizado revestido em piso vinílico em manta, 2x20m, linha Polysafe Verona PUR, acabamento Rock Salt - cód: LRV-43. Paginação conforme detalhamento.</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n"/>
+      <c r="C26" s="290" t="n"/>
       <c r="D26" s="35" t="n"/>
-      <c r="E26" s="37" t="n"/>
+      <c r="E26" s="38" t="n"/>
       <c r="F26" s="245" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G26" s="32" t="n"/>
+      <c r="G26" s="290" t="n"/>
       <c r="H26" s="245" t="inlineStr">
         <is>
           <t>PA34 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
@@ -11826,18 +11840,18 @@
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="32" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="32" t="n"/>
+      <c r="J26" s="290" t="n"/>
+      <c r="K26" s="290" t="n"/>
+      <c r="L26" s="290" t="n"/>
+      <c r="M26" s="290" t="n"/>
+      <c r="N26" s="290" t="n"/>
+      <c r="O26" s="290" t="n"/>
+      <c r="P26" s="290" t="n"/>
+      <c r="Q26" s="290" t="n"/>
+      <c r="R26" s="290" t="n"/>
+      <c r="S26" s="290" t="n"/>
       <c r="T26" s="35" t="n"/>
-      <c r="U26" s="32" t="n"/>
+      <c r="U26" s="290" t="n"/>
       <c r="V26" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -11870,9 +11884,9 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="37" t="n"/>
+      <c r="C27" s="290" t="n"/>
+      <c r="D27" s="290" t="n"/>
+      <c r="E27" s="38" t="n"/>
       <c r="F27" s="246" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
@@ -11914,25 +11928,25 @@
           <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
         </is>
       </c>
-      <c r="P27" s="32" t="n"/>
-      <c r="Q27" s="32" t="n"/>
+      <c r="P27" s="290" t="n"/>
+      <c r="Q27" s="290" t="n"/>
       <c r="R27" s="35" t="n"/>
-      <c r="S27" s="32" t="n"/>
-      <c r="T27" s="32" t="n"/>
-      <c r="U27" s="32" t="n"/>
+      <c r="S27" s="290" t="n"/>
+      <c r="T27" s="290" t="n"/>
+      <c r="U27" s="290" t="n"/>
       <c r="V27" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
-      <c r="W27" s="32" t="n"/>
-      <c r="X27" s="270" t="inlineStr">
+      <c r="W27" s="290" t="n"/>
+      <c r="X27" s="271" t="inlineStr">
         <is>
           <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="Y27" s="32" t="n"/>
+      <c r="Y27" s="290" t="n"/>
       <c r="Z27" s="269" t="inlineStr">
         <is>
           <t>D13 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
@@ -11950,29 +11964,29 @@
         </is>
       </c>
       <c r="B28" s="35" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="32" t="n"/>
+      <c r="C28" s="290" t="n"/>
+      <c r="D28" s="290" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="290" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="35" t="n"/>
       <c r="J28" s="35" t="n"/>
-      <c r="K28" s="32" t="n"/>
+      <c r="K28" s="290" t="n"/>
       <c r="L28" s="35" t="n"/>
       <c r="M28" s="35" t="n"/>
       <c r="N28" s="35" t="n"/>
       <c r="O28" s="35" t="n"/>
-      <c r="P28" s="32" t="n"/>
-      <c r="Q28" s="32" t="n"/>
+      <c r="P28" s="290" t="n"/>
+      <c r="Q28" s="290" t="n"/>
       <c r="R28" s="35" t="n"/>
-      <c r="S28" s="32" t="n"/>
+      <c r="S28" s="290" t="n"/>
       <c r="T28" s="35" t="n"/>
-      <c r="U28" s="32" t="n"/>
+      <c r="U28" s="290" t="n"/>
       <c r="V28" s="31" t="n"/>
-      <c r="W28" s="32" t="n"/>
-      <c r="X28" s="32" t="n"/>
-      <c r="Y28" s="32" t="n"/>
+      <c r="W28" s="290" t="n"/>
+      <c r="X28" s="290" t="n"/>
+      <c r="Y28" s="290" t="n"/>
       <c r="Z28" s="35" t="n"/>
     </row>
     <row r="29">
@@ -11987,37 +12001,37 @@
 P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="37" t="n"/>
-      <c r="E29" s="37" t="n"/>
+      <c r="C29" s="290" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="38" t="n"/>
       <c r="F29" s="35" t="n"/>
-      <c r="G29" s="32" t="n"/>
+      <c r="G29" s="290" t="n"/>
       <c r="H29" s="277" t="inlineStr">
         <is>
           <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614.. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="I29" s="35" t="n"/>
-      <c r="J29" s="32" t="n"/>
+      <c r="J29" s="290" t="n"/>
       <c r="K29" s="246" t="inlineStr">
         <is>
           <t>INT - DET.05 - Testeira em granito acabamento meia esquadria H=7cm</t>
         </is>
       </c>
-      <c r="L29" s="32" t="n"/>
-      <c r="M29" s="32" t="n"/>
-      <c r="N29" s="32" t="n"/>
-      <c r="O29" s="32" t="n"/>
-      <c r="P29" s="32" t="n"/>
-      <c r="Q29" s="32" t="n"/>
-      <c r="R29" s="32" t="n"/>
-      <c r="S29" s="32" t="n"/>
-      <c r="T29" s="270" t="inlineStr">
+      <c r="L29" s="290" t="n"/>
+      <c r="M29" s="290" t="n"/>
+      <c r="N29" s="290" t="n"/>
+      <c r="O29" s="290" t="n"/>
+      <c r="P29" s="290" t="n"/>
+      <c r="Q29" s="290" t="n"/>
+      <c r="R29" s="290" t="n"/>
+      <c r="S29" s="290" t="n"/>
+      <c r="T29" s="271" t="inlineStr">
         <is>
           <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U29" s="270" t="inlineStr">
+      <c r="U29" s="271" t="inlineStr">
         <is>
           <t>D79 - Chuveiro de piso para área externa em aço inox 316. cód.: DK5123B. Ref.: Doka</t>
         </is>
@@ -12047,25 +12061,25 @@
           <t>P26 - Piso em deck de madeira Cumaru com tecnica de carbonização Shugi Ban, reguas 20mmx100mmx2000m-acima. Ref.:Madeira Carbonizada.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="37" t="n"/>
+      <c r="C30" s="290" t="n"/>
+      <c r="D30" s="38" t="n"/>
+      <c r="E30" s="38" t="n"/>
       <c r="F30" s="35" t="n"/>
-      <c r="G30" s="32" t="n"/>
+      <c r="G30" s="290" t="n"/>
       <c r="H30" s="35" t="n"/>
       <c r="I30" s="35" t="n"/>
-      <c r="J30" s="32" t="n"/>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="32" t="n"/>
-      <c r="M30" s="32" t="n"/>
-      <c r="N30" s="32" t="n"/>
-      <c r="O30" s="32" t="n"/>
-      <c r="P30" s="32" t="n"/>
-      <c r="Q30" s="32" t="n"/>
-      <c r="R30" s="32" t="n"/>
-      <c r="S30" s="32" t="n"/>
-      <c r="T30" s="32" t="n"/>
-      <c r="U30" s="32" t="n"/>
+      <c r="J30" s="290" t="n"/>
+      <c r="K30" s="290" t="n"/>
+      <c r="L30" s="290" t="n"/>
+      <c r="M30" s="290" t="n"/>
+      <c r="N30" s="290" t="n"/>
+      <c r="O30" s="290" t="n"/>
+      <c r="P30" s="290" t="n"/>
+      <c r="Q30" s="290" t="n"/>
+      <c r="R30" s="290" t="n"/>
+      <c r="S30" s="290" t="n"/>
+      <c r="T30" s="290" t="n"/>
+      <c r="U30" s="290" t="n"/>
       <c r="V30" s="31" t="n"/>
       <c r="W30" s="35" t="n"/>
       <c r="X30" s="31" t="n"/>
@@ -12079,30 +12093,30 @@
         </is>
       </c>
       <c r="B31" s="35" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
+      <c r="C31" s="290" t="n"/>
+      <c r="D31" s="290" t="n"/>
+      <c r="E31" s="290" t="n"/>
       <c r="F31" s="35" t="n"/>
-      <c r="G31" s="32" t="n"/>
+      <c r="G31" s="290" t="n"/>
       <c r="H31" s="35" t="n"/>
       <c r="I31" s="35" t="n"/>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
+      <c r="J31" s="290" t="n"/>
+      <c r="K31" s="290" t="n"/>
+      <c r="L31" s="290" t="n"/>
+      <c r="M31" s="290" t="n"/>
+      <c r="N31" s="290" t="n"/>
+      <c r="O31" s="290" t="n"/>
+      <c r="P31" s="290" t="n"/>
+      <c r="Q31" s="290" t="n"/>
+      <c r="R31" s="290" t="n"/>
+      <c r="S31" s="290" t="n"/>
+      <c r="T31" s="290" t="n"/>
+      <c r="U31" s="290" t="n"/>
       <c r="V31" s="31" t="n"/>
-      <c r="W31" s="32" t="n"/>
-      <c r="X31" s="32" t="n"/>
-      <c r="Y31" s="32" t="n"/>
-      <c r="Z31" s="32" t="n"/>
+      <c r="W31" s="290" t="n"/>
+      <c r="X31" s="290" t="n"/>
+      <c r="Y31" s="290" t="n"/>
+      <c r="Z31" s="290" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="45" t="inlineStr">
@@ -12115,15 +12129,15 @@
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="37" t="n"/>
-      <c r="E32" s="37" t="n"/>
+      <c r="C32" s="290" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="E32" s="38" t="n"/>
       <c r="F32" s="269" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G32" s="32" t="n"/>
+      <c r="G32" s="290" t="n"/>
       <c r="H32" s="269" t="inlineStr">
         <is>
           <t>PA42 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento serrado, com arte em baixo relevo, corte a laser, profundidade 4mm Espessura da pedra: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -12136,35 +12150,35 @@
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J32" s="270" t="inlineStr">
+      <c r="J32" s="271" t="inlineStr">
         <is>
           <t>D46 - Bancada/Mesa em pedra sinterizada, Lava satin fusion collection. Espessura: 5mm. Ref: Neo Lhít. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K32" s="32" t="n"/>
-      <c r="L32" s="270" t="inlineStr">
+      <c r="K32" s="290" t="n"/>
+      <c r="L32" s="271" t="inlineStr">
         <is>
           <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina</t>
         </is>
       </c>
-      <c r="M32" s="32" t="n"/>
-      <c r="N32" s="32" t="n"/>
-      <c r="O32" s="270" t="inlineStr">
+      <c r="M32" s="290" t="n"/>
+      <c r="N32" s="290" t="n"/>
+      <c r="O32" s="271" t="inlineStr">
         <is>
           <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
         </is>
       </c>
-      <c r="P32" s="32" t="n"/>
-      <c r="Q32" s="32" t="n"/>
-      <c r="R32" s="32" t="n"/>
-      <c r="S32" s="32" t="n"/>
-      <c r="T32" s="270" t="inlineStr">
+      <c r="P32" s="290" t="n"/>
+      <c r="Q32" s="290" t="n"/>
+      <c r="R32" s="290" t="n"/>
+      <c r="S32" s="290" t="n"/>
+      <c r="T32" s="271" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
 D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U32" s="32" t="n"/>
+      <c r="U32" s="290" t="n"/>
       <c r="V32" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -12189,30 +12203,30 @@
         </is>
       </c>
       <c r="B33" s="35" t="n"/>
-      <c r="C33" s="32" t="n"/>
+      <c r="C33" s="290" t="n"/>
       <c r="D33" s="35" t="n"/>
-      <c r="E33" s="37" t="n"/>
+      <c r="E33" s="38" t="n"/>
       <c r="F33" s="35" t="n"/>
-      <c r="G33" s="32" t="n"/>
+      <c r="G33" s="290" t="n"/>
       <c r="H33" s="35" t="n"/>
       <c r="I33" s="35" t="n"/>
       <c r="J33" s="35" t="n"/>
-      <c r="K33" s="32" t="n"/>
+      <c r="K33" s="290" t="n"/>
       <c r="L33" s="35" t="n"/>
-      <c r="M33" s="37" t="n"/>
+      <c r="M33" s="38" t="n"/>
       <c r="N33" s="38" t="n"/>
       <c r="O33" s="35" t="n"/>
       <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="32" t="n"/>
+      <c r="Q33" s="290" t="n"/>
       <c r="R33" s="35" t="n"/>
       <c r="S33" s="35" t="n"/>
       <c r="T33" s="35" t="n"/>
-      <c r="U33" s="32" t="n"/>
+      <c r="U33" s="290" t="n"/>
       <c r="V33" s="31" t="n"/>
       <c r="W33" s="35" t="n"/>
       <c r="X33" s="35" t="n"/>
       <c r="Y33" s="35" t="n"/>
-      <c r="Z33" s="32" t="n"/>
+      <c r="Z33" s="290" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="45" t="inlineStr">
@@ -12225,11 +12239,11 @@
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C34" s="32" t="n"/>
+      <c r="C34" s="290" t="n"/>
       <c r="D34" s="35" t="n"/>
-      <c r="E34" s="37" t="n"/>
+      <c r="E34" s="38" t="n"/>
       <c r="F34" s="35" t="n"/>
-      <c r="G34" s="32" t="n"/>
+      <c r="G34" s="290" t="n"/>
       <c r="H34" s="269" t="inlineStr">
         <is>
           <t>PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -12241,17 +12255,17 @@
         </is>
       </c>
       <c r="J34" s="35" t="n"/>
-      <c r="K34" s="32" t="n"/>
+      <c r="K34" s="290" t="n"/>
       <c r="L34" s="35" t="n"/>
-      <c r="M34" s="37" t="n"/>
+      <c r="M34" s="38" t="n"/>
       <c r="N34" s="38" t="n"/>
       <c r="O34" s="35" t="n"/>
       <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="32" t="n"/>
+      <c r="Q34" s="290" t="n"/>
       <c r="R34" s="35" t="n"/>
       <c r="S34" s="35" t="n"/>
       <c r="T34" s="35" t="n"/>
-      <c r="U34" s="32" t="n"/>
+      <c r="U34" s="290" t="n"/>
       <c r="V34" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -12260,7 +12274,7 @@
       <c r="W34" s="35" t="n"/>
       <c r="X34" s="35" t="n"/>
       <c r="Y34" s="35" t="n"/>
-      <c r="Z34" s="32" t="n"/>
+      <c r="Z34" s="290" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="45" t="inlineStr">
@@ -12273,15 +12287,15 @@
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C35" s="32" t="n"/>
+      <c r="C35" s="290" t="n"/>
       <c r="D35" s="35" t="n"/>
-      <c r="E35" s="37" t="n"/>
+      <c r="E35" s="38" t="n"/>
       <c r="F35" s="269" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G35" s="32" t="n"/>
+      <c r="G35" s="290" t="n"/>
       <c r="H35" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -12306,7 +12320,7 @@
         </is>
       </c>
       <c r="L35" s="35" t="n"/>
-      <c r="M35" s="37" t="n"/>
+      <c r="M35" s="38" t="n"/>
       <c r="N35" s="38" t="n"/>
       <c r="O35" s="283" t="inlineStr">
         <is>
@@ -12319,7 +12333,7 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q35" s="32" t="n"/>
+      <c r="Q35" s="290" t="n"/>
       <c r="R35" s="35" t="n"/>
       <c r="S35" s="245" t="inlineStr">
         <is>
@@ -12368,15 +12382,15 @@
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
+      <c r="C36" s="290" t="n"/>
       <c r="D36" s="35" t="n"/>
-      <c r="E36" s="37" t="n"/>
+      <c r="E36" s="38" t="n"/>
       <c r="F36" s="269" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G36" s="32" t="n"/>
+      <c r="G36" s="290" t="n"/>
       <c r="H36" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -12401,7 +12415,7 @@
         </is>
       </c>
       <c r="L36" s="35" t="n"/>
-      <c r="M36" s="37" t="n"/>
+      <c r="M36" s="38" t="n"/>
       <c r="N36" s="38" t="n"/>
       <c r="O36" s="283" t="inlineStr">
         <is>
@@ -12414,7 +12428,7 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q36" s="32" t="n"/>
+      <c r="Q36" s="290" t="n"/>
       <c r="R36" s="35" t="n"/>
       <c r="S36" s="245" t="inlineStr">
         <is>
@@ -12464,15 +12478,15 @@
 P22 - Piso em contrapiso regularizado, revestido em piso emborrachado isolante e antiderrapante, acabamernto preto, placas 100x100cm. Espessura: 8mm. Paginação conforme detalhamento. Ref.: Rubberkap ou similar. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C37" s="32" t="n"/>
+      <c r="C37" s="290" t="n"/>
       <c r="D37" s="35" t="n"/>
-      <c r="E37" s="37" t="n"/>
+      <c r="E37" s="38" t="n"/>
       <c r="F37" s="246" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G37" s="32" t="n"/>
+      <c r="G37" s="290" t="n"/>
       <c r="H37" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -12489,17 +12503,17 @@
         </is>
       </c>
       <c r="J37" s="35" t="n"/>
-      <c r="K37" s="32" t="n"/>
+      <c r="K37" s="290" t="n"/>
       <c r="L37" s="35" t="n"/>
-      <c r="M37" s="37" t="n"/>
+      <c r="M37" s="38" t="n"/>
       <c r="N37" s="38" t="n"/>
       <c r="O37" s="35" t="n"/>
       <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="32" t="n"/>
+      <c r="Q37" s="290" t="n"/>
       <c r="R37" s="35" t="n"/>
       <c r="S37" s="35" t="n"/>
       <c r="T37" s="35" t="n"/>
-      <c r="U37" s="32" t="n"/>
+      <c r="U37" s="290" t="n"/>
       <c r="V37" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -12512,7 +12526,7 @@
         </is>
       </c>
       <c r="Y37" s="35" t="n"/>
-      <c r="Z37" s="270" t="inlineStr">
+      <c r="Z37" s="271" t="inlineStr">
         <is>
           <t>D3 - Estante em MDF Nero Rust Ref.: Berneck, desenho conforme detalhamento, Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
 D4 - Armário em marcenaria, estruturado, com espaço para central de sonorização e automação, quadro de distribuição embutido - verificar dimensões com projetos específico, desenho conforme detalhamento. Porta.  de giro com sistema fecho-toque, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
@@ -12529,30 +12543,30 @@
         </is>
       </c>
       <c r="B38" s="35" t="n"/>
-      <c r="C38" s="32" t="n"/>
+      <c r="C38" s="290" t="n"/>
       <c r="D38" s="35" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="32" t="n"/>
+      <c r="E38" s="38" t="n"/>
+      <c r="F38" s="290" t="n"/>
+      <c r="G38" s="290" t="n"/>
       <c r="H38" s="35" t="n"/>
       <c r="I38" s="35" t="n"/>
       <c r="J38" s="35" t="n"/>
-      <c r="K38" s="32" t="n"/>
+      <c r="K38" s="290" t="n"/>
       <c r="L38" s="35" t="n"/>
-      <c r="M38" s="37" t="n"/>
+      <c r="M38" s="38" t="n"/>
       <c r="N38" s="38" t="n"/>
       <c r="O38" s="35" t="n"/>
       <c r="P38" s="31" t="n"/>
-      <c r="Q38" s="32" t="n"/>
+      <c r="Q38" s="290" t="n"/>
       <c r="R38" s="35" t="n"/>
       <c r="S38" s="35" t="n"/>
       <c r="T38" s="35" t="n"/>
-      <c r="U38" s="32" t="n"/>
+      <c r="U38" s="290" t="n"/>
       <c r="V38" s="31" t="n"/>
       <c r="W38" s="35" t="n"/>
       <c r="X38" s="35" t="n"/>
       <c r="Y38" s="35" t="n"/>
-      <c r="Z38" s="32" t="n"/>
+      <c r="Z38" s="290" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="45" t="inlineStr">
@@ -12565,11 +12579,11 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C39" s="32" t="n"/>
+      <c r="C39" s="290" t="n"/>
       <c r="D39" s="35" t="n"/>
-      <c r="E39" s="37" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="32" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="290" t="n"/>
+      <c r="G39" s="290" t="n"/>
       <c r="H39" s="277" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12577,22 +12591,22 @@
       </c>
       <c r="I39" s="35" t="n"/>
       <c r="J39" s="35" t="n"/>
-      <c r="K39" s="32" t="n"/>
+      <c r="K39" s="290" t="n"/>
       <c r="L39" s="35" t="n"/>
-      <c r="M39" s="37" t="n"/>
+      <c r="M39" s="38" t="n"/>
       <c r="N39" s="38" t="n"/>
       <c r="O39" s="35" t="n"/>
       <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="32" t="n"/>
+      <c r="Q39" s="290" t="n"/>
       <c r="R39" s="35" t="n"/>
       <c r="S39" s="35" t="n"/>
       <c r="T39" s="35" t="n"/>
-      <c r="U39" s="32" t="n"/>
+      <c r="U39" s="290" t="n"/>
       <c r="V39" s="31" t="n"/>
       <c r="W39" s="35" t="n"/>
       <c r="X39" s="35" t="n"/>
       <c r="Y39" s="35" t="n"/>
-      <c r="Z39" s="32" t="n"/>
+      <c r="Z39" s="290" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="45" t="inlineStr">
@@ -12605,11 +12619,11 @@
           <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm.  Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C40" s="32" t="n"/>
+      <c r="C40" s="290" t="n"/>
       <c r="D40" s="35" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="32" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="290" t="n"/>
+      <c r="G40" s="290" t="n"/>
       <c r="H40" s="277" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12617,22 +12631,22 @@
       </c>
       <c r="I40" s="35" t="n"/>
       <c r="J40" s="35" t="n"/>
-      <c r="K40" s="32" t="n"/>
+      <c r="K40" s="290" t="n"/>
       <c r="L40" s="35" t="n"/>
-      <c r="M40" s="37" t="n"/>
+      <c r="M40" s="38" t="n"/>
       <c r="N40" s="38" t="n"/>
       <c r="O40" s="35" t="n"/>
       <c r="P40" s="31" t="n"/>
-      <c r="Q40" s="32" t="n"/>
+      <c r="Q40" s="290" t="n"/>
       <c r="R40" s="35" t="n"/>
       <c r="S40" s="35" t="n"/>
       <c r="T40" s="35" t="n"/>
-      <c r="U40" s="32" t="n"/>
+      <c r="U40" s="290" t="n"/>
       <c r="V40" s="31" t="n"/>
       <c r="W40" s="35" t="n"/>
       <c r="X40" s="35" t="n"/>
       <c r="Y40" s="35" t="n"/>
-      <c r="Z40" s="32" t="n"/>
+      <c r="Z40" s="290" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="45" t="inlineStr">
@@ -12645,15 +12659,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C41" s="32" t="n"/>
+      <c r="C41" s="290" t="n"/>
       <c r="D41" s="35" t="n"/>
-      <c r="E41" s="37" t="n"/>
-      <c r="F41" s="270" t="inlineStr">
+      <c r="E41" s="38" t="n"/>
+      <c r="F41" s="271" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G41" s="32" t="n"/>
+      <c r="G41" s="290" t="n"/>
       <c r="H41" s="245" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -12668,13 +12682,13 @@
         </is>
       </c>
       <c r="J41" s="35" t="n"/>
-      <c r="K41" s="32" t="n"/>
+      <c r="K41" s="290" t="n"/>
       <c r="L41" s="35" t="n"/>
-      <c r="M41" s="37" t="n"/>
+      <c r="M41" s="38" t="n"/>
       <c r="N41" s="38" t="n"/>
       <c r="O41" s="35" t="n"/>
       <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="32" t="n"/>
+      <c r="Q41" s="290" t="n"/>
       <c r="R41" s="269" t="inlineStr">
         <is>
           <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
@@ -12703,7 +12717,7 @@
         </is>
       </c>
       <c r="Y41" s="35" t="n"/>
-      <c r="Z41" s="32" t="n"/>
+      <c r="Z41" s="290" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
@@ -12716,11 +12730,11 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C42" s="32" t="n"/>
+      <c r="C42" s="290" t="n"/>
       <c r="D42" s="35" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="32" t="n"/>
+      <c r="E42" s="38" t="n"/>
+      <c r="F42" s="290" t="n"/>
+      <c r="G42" s="290" t="n"/>
       <c r="H42" s="245" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12732,13 +12746,13 @@
         </is>
       </c>
       <c r="J42" s="35" t="n"/>
-      <c r="K42" s="32" t="n"/>
+      <c r="K42" s="290" t="n"/>
       <c r="L42" s="35" t="n"/>
-      <c r="M42" s="37" t="n"/>
+      <c r="M42" s="38" t="n"/>
       <c r="N42" s="38" t="n"/>
       <c r="O42" s="35" t="n"/>
       <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="32" t="n"/>
+      <c r="Q42" s="290" t="n"/>
       <c r="R42" s="269" t="inlineStr">
         <is>
           <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
@@ -12750,7 +12764,7 @@
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U42" s="270" t="inlineStr">
+      <c r="U42" s="271" t="inlineStr">
         <is>
           <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
@@ -12759,7 +12773,7 @@
       <c r="W42" s="35" t="n"/>
       <c r="X42" s="35" t="n"/>
       <c r="Y42" s="35" t="n"/>
-      <c r="Z42" s="32" t="n"/>
+      <c r="Z42" s="290" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="45" t="inlineStr">
@@ -12772,11 +12786,11 @@
           <t>P19 - Piso em contrapiso regularizado revestido com porcelanato padrão, coberto com piso tipo deck de madeira Cedro.Reguas 70mmx25mmx comprimento variável e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="C43" s="32" t="n"/>
+      <c r="C43" s="290" t="n"/>
       <c r="D43" s="35" t="n"/>
-      <c r="E43" s="37" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="32" t="n"/>
+      <c r="E43" s="38" t="n"/>
+      <c r="F43" s="290" t="n"/>
+      <c r="G43" s="290" t="n"/>
       <c r="H43" s="245" t="inlineStr">
         <is>
           <t>PA50 - Parede em alvenaria rebocada e regularizada revestida em conjunto com sarrafos de madeira 2,5x5cm a cada 35-40cm, lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro. Reguas 70mmx25mmx comprimento variável e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
@@ -12788,22 +12802,22 @@
         </is>
       </c>
       <c r="J43" s="35" t="n"/>
-      <c r="K43" s="32" t="n"/>
+      <c r="K43" s="290" t="n"/>
       <c r="L43" s="35" t="n"/>
-      <c r="M43" s="37" t="n"/>
+      <c r="M43" s="38" t="n"/>
       <c r="N43" s="38" t="n"/>
       <c r="O43" s="35" t="n"/>
       <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="32" t="n"/>
+      <c r="Q43" s="290" t="n"/>
       <c r="R43" s="35" t="n"/>
       <c r="S43" s="35" t="n"/>
       <c r="T43" s="35" t="n"/>
-      <c r="U43" s="32" t="n"/>
+      <c r="U43" s="290" t="n"/>
       <c r="V43" s="31" t="n"/>
       <c r="W43" s="35" t="n"/>
       <c r="X43" s="35" t="n"/>
       <c r="Y43" s="35" t="n"/>
-      <c r="Z43" s="32" t="n"/>
+      <c r="Z43" s="290" t="n"/>
     </row>
     <row r="44" ht="125.25" customHeight="1">
       <c r="A44" s="45" t="inlineStr">
@@ -12812,30 +12826,30 @@
         </is>
       </c>
       <c r="B44" s="35" t="n"/>
-      <c r="C44" s="32" t="n"/>
+      <c r="C44" s="290" t="n"/>
       <c r="D44" s="35" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="32" t="n"/>
-      <c r="G44" s="32" t="n"/>
+      <c r="E44" s="38" t="n"/>
+      <c r="F44" s="290" t="n"/>
+      <c r="G44" s="290" t="n"/>
       <c r="H44" s="35" t="n"/>
       <c r="I44" s="35" t="n"/>
       <c r="J44" s="35" t="n"/>
-      <c r="K44" s="32" t="n"/>
+      <c r="K44" s="290" t="n"/>
       <c r="L44" s="35" t="n"/>
-      <c r="M44" s="37" t="n"/>
+      <c r="M44" s="38" t="n"/>
       <c r="N44" s="38" t="n"/>
       <c r="O44" s="35" t="n"/>
       <c r="P44" s="31" t="n"/>
-      <c r="Q44" s="32" t="n"/>
+      <c r="Q44" s="290" t="n"/>
       <c r="R44" s="35" t="n"/>
       <c r="S44" s="35" t="n"/>
       <c r="T44" s="35" t="n"/>
-      <c r="U44" s="32" t="n"/>
+      <c r="U44" s="290" t="n"/>
       <c r="V44" s="31" t="n"/>
       <c r="W44" s="35" t="n"/>
       <c r="X44" s="35" t="n"/>
       <c r="Y44" s="35" t="n"/>
-      <c r="Z44" s="32" t="n"/>
+      <c r="Z44" s="290" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="45" t="inlineStr">
@@ -12848,15 +12862,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C45" s="32" t="n"/>
+      <c r="C45" s="290" t="n"/>
       <c r="D45" s="35" t="n"/>
-      <c r="E45" s="37" t="n"/>
+      <c r="E45" s="38" t="n"/>
       <c r="F45" s="246" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G45" s="32" t="n"/>
+      <c r="G45" s="290" t="n"/>
       <c r="H45" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -12876,14 +12890,14 @@
 D61 - Bancada com tampo em mármore branco liso selecionado, lote a ser aprovado, com acabamento abaulado e laterais em mármore com acabamento frisado. Recorte para encaixe de lavatório, conforme manual técnico de instalação Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K45" s="32" t="n"/>
+      <c r="K45" s="290" t="n"/>
       <c r="L45" s="277" t="inlineStr">
         <is>
           <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
 D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="M45" s="37" t="n"/>
+      <c r="M45" s="38" t="n"/>
       <c r="N45" s="38" t="n"/>
       <c r="O45" s="277" t="inlineStr">
         <is>
@@ -12892,11 +12906,11 @@
         </is>
       </c>
       <c r="P45" s="31" t="n"/>
-      <c r="Q45" s="32" t="n"/>
+      <c r="Q45" s="290" t="n"/>
       <c r="R45" s="35" t="n"/>
       <c r="S45" s="35" t="n"/>
       <c r="T45" s="35" t="n"/>
-      <c r="U45" s="32" t="n"/>
+      <c r="U45" s="290" t="n"/>
       <c r="V45" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -12909,7 +12923,7 @@
         </is>
       </c>
       <c r="Y45" s="35" t="n"/>
-      <c r="Z45" s="32" t="n"/>
+      <c r="Z45" s="290" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="45" t="inlineStr">
@@ -12922,15 +12936,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C46" s="32" t="n"/>
+      <c r="C46" s="290" t="n"/>
       <c r="D46" s="35" t="n"/>
-      <c r="E46" s="37" t="n"/>
+      <c r="E46" s="38" t="n"/>
       <c r="F46" s="246" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G46" s="32" t="n"/>
+      <c r="G46" s="290" t="n"/>
       <c r="H46" s="277" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -12950,14 +12964,14 @@
 D61 - Bancada com tampo em mármore branco liso selecionado, lote a ser aprovado, com acabamento abaulado e laterais em mármore com acabamento frisado. Recorte para encaixe de lavatório, conforme manual técnico de instalação Dimensões e detalhes conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K46" s="32" t="n"/>
+      <c r="K46" s="290" t="n"/>
       <c r="L46" s="269" t="inlineStr">
         <is>
           <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
 D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="M46" s="37" t="n"/>
+      <c r="M46" s="38" t="n"/>
       <c r="N46" s="38" t="n"/>
       <c r="O46" s="277" t="inlineStr">
         <is>
@@ -12966,11 +12980,11 @@
         </is>
       </c>
       <c r="P46" s="31" t="n"/>
-      <c r="Q46" s="32" t="n"/>
+      <c r="Q46" s="290" t="n"/>
       <c r="R46" s="35" t="n"/>
       <c r="S46" s="35" t="n"/>
       <c r="T46" s="35" t="n"/>
-      <c r="U46" s="32" t="n"/>
+      <c r="U46" s="290" t="n"/>
       <c r="V46" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -12983,7 +12997,7 @@
         </is>
       </c>
       <c r="Y46" s="35" t="n"/>
-      <c r="Z46" s="32" t="n"/>
+      <c r="Z46" s="290" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="45" t="inlineStr">
@@ -12996,15 +13010,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C47" s="32" t="n"/>
+      <c r="C47" s="290" t="n"/>
       <c r="D47" s="35" t="n"/>
-      <c r="E47" s="37" t="n"/>
-      <c r="F47" s="270" t="inlineStr">
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="271" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G47" s="32" t="n"/>
+      <c r="G47" s="290" t="n"/>
       <c r="H47" s="269" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -13017,17 +13031,17 @@
         </is>
       </c>
       <c r="J47" s="35" t="n"/>
-      <c r="K47" s="32" t="n"/>
+      <c r="K47" s="290" t="n"/>
       <c r="L47" s="35" t="n"/>
-      <c r="M47" s="37" t="n"/>
+      <c r="M47" s="38" t="n"/>
       <c r="N47" s="38" t="n"/>
       <c r="O47" s="35" t="n"/>
       <c r="P47" s="31" t="n"/>
-      <c r="Q47" s="32" t="n"/>
+      <c r="Q47" s="290" t="n"/>
       <c r="R47" s="35" t="n"/>
       <c r="S47" s="35" t="n"/>
       <c r="T47" s="35" t="n"/>
-      <c r="U47" s="32" t="n"/>
+      <c r="U47" s="290" t="n"/>
       <c r="V47" s="31" t="n"/>
       <c r="W47" s="35" t="n"/>
       <c r="X47" s="269" t="inlineStr">
@@ -13037,7 +13051,7 @@
         </is>
       </c>
       <c r="Y47" s="35" t="n"/>
-      <c r="Z47" s="32" t="n"/>
+      <c r="Z47" s="290" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="45" t="inlineStr">
@@ -13050,15 +13064,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C48" s="32" t="n"/>
+      <c r="C48" s="290" t="n"/>
       <c r="D48" s="35" t="n"/>
-      <c r="E48" s="37" t="n"/>
-      <c r="F48" s="270" t="inlineStr">
+      <c r="E48" s="38" t="n"/>
+      <c r="F48" s="271" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G48" s="32" t="n"/>
+      <c r="G48" s="290" t="n"/>
       <c r="H48" s="269" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -13075,7 +13089,7 @@
           <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K48" s="270" t="inlineStr">
+      <c r="K48" s="271" t="inlineStr">
         <is>
           <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
@@ -13085,7 +13099,7 @@
           <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
         </is>
       </c>
-      <c r="M48" s="37" t="n"/>
+      <c r="M48" s="38" t="n"/>
       <c r="N48" s="38" t="n"/>
       <c r="O48" s="269" t="inlineStr">
         <is>
@@ -13097,7 +13111,7 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q48" s="270" t="inlineStr">
+      <c r="Q48" s="271" t="inlineStr">
         <is>
           <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
         </is>
@@ -13113,7 +13127,7 @@
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U48" s="270" t="inlineStr">
+      <c r="U48" s="271" t="inlineStr">
         <is>
           <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
@@ -13126,7 +13140,7 @@
       <c r="W48" s="35" t="n"/>
       <c r="X48" s="269" t="n"/>
       <c r="Y48" s="35" t="n"/>
-      <c r="Z48" s="270" t="inlineStr">
+      <c r="Z48" s="271" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -13145,15 +13159,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C49" s="32" t="n"/>
+      <c r="C49" s="290" t="n"/>
       <c r="D49" s="35" t="n"/>
-      <c r="E49" s="37" t="n"/>
-      <c r="F49" s="270" t="inlineStr">
+      <c r="E49" s="38" t="n"/>
+      <c r="F49" s="271" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G49" s="32" t="n"/>
+      <c r="G49" s="290" t="n"/>
       <c r="H49" s="269" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -13170,7 +13184,7 @@
           <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K49" s="270" t="inlineStr">
+      <c r="K49" s="271" t="inlineStr">
         <is>
           <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
@@ -13180,7 +13194,7 @@
           <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
         </is>
       </c>
-      <c r="M49" s="37" t="n"/>
+      <c r="M49" s="38" t="n"/>
       <c r="N49" s="38" t="n"/>
       <c r="O49" s="269" t="inlineStr">
         <is>
@@ -13192,7 +13206,7 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q49" s="270" t="inlineStr">
+      <c r="Q49" s="271" t="inlineStr">
         <is>
           <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
         </is>
@@ -13208,7 +13222,7 @@
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U49" s="270" t="inlineStr">
+      <c r="U49" s="271" t="inlineStr">
         <is>
           <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
@@ -13221,7 +13235,7 @@
       <c r="W49" s="35" t="n"/>
       <c r="X49" s="269" t="n"/>
       <c r="Y49" s="35" t="n"/>
-      <c r="Z49" s="270" t="inlineStr">
+      <c r="Z49" s="271" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -13240,15 +13254,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C50" s="32" t="n"/>
+      <c r="C50" s="290" t="n"/>
       <c r="D50" s="35" t="n"/>
-      <c r="E50" s="37" t="n"/>
+      <c r="E50" s="38" t="n"/>
       <c r="F50" s="278" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G50" s="32" t="n"/>
+      <c r="G50" s="290" t="n"/>
       <c r="H50" s="245" t="inlineStr">
         <is>
           <t>PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -13260,13 +13274,13 @@
         </is>
       </c>
       <c r="J50" s="35" t="n"/>
-      <c r="K50" s="32" t="n"/>
+      <c r="K50" s="290" t="n"/>
       <c r="L50" s="245" t="inlineStr">
         <is>
           <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.TQ.01.17.; Ref.: Deca.</t>
         </is>
       </c>
-      <c r="M50" s="37" t="n"/>
+      <c r="M50" s="38" t="n"/>
       <c r="N50" s="38" t="n"/>
       <c r="O50" s="245" t="inlineStr">
         <is>
@@ -13274,16 +13288,16 @@
         </is>
       </c>
       <c r="P50" s="31" t="n"/>
-      <c r="Q50" s="32" t="n"/>
+      <c r="Q50" s="290" t="n"/>
       <c r="R50" s="35" t="n"/>
       <c r="S50" s="35" t="n"/>
       <c r="T50" s="35" t="n"/>
-      <c r="U50" s="32" t="n"/>
+      <c r="U50" s="290" t="n"/>
       <c r="V50" s="31" t="n"/>
       <c r="W50" s="35" t="n"/>
       <c r="X50" s="35" t="n"/>
       <c r="Y50" s="35" t="n"/>
-      <c r="Z50" s="32" t="n"/>
+      <c r="Z50" s="290" t="n"/>
     </row>
     <row r="51" ht="125.25" customHeight="1">
       <c r="A51" s="45" t="inlineStr">
@@ -13292,30 +13306,30 @@
         </is>
       </c>
       <c r="B51" s="35" t="n"/>
-      <c r="C51" s="32" t="n"/>
+      <c r="C51" s="290" t="n"/>
       <c r="D51" s="35" t="n"/>
-      <c r="E51" s="37" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
+      <c r="E51" s="38" t="n"/>
+      <c r="F51" s="290" t="n"/>
+      <c r="G51" s="290" t="n"/>
       <c r="H51" s="35" t="n"/>
       <c r="I51" s="35" t="n"/>
       <c r="J51" s="35" t="n"/>
-      <c r="K51" s="32" t="n"/>
+      <c r="K51" s="290" t="n"/>
       <c r="L51" s="35" t="n"/>
-      <c r="M51" s="37" t="n"/>
+      <c r="M51" s="38" t="n"/>
       <c r="N51" s="38" t="n"/>
       <c r="O51" s="35" t="n"/>
       <c r="P51" s="31" t="n"/>
-      <c r="Q51" s="32" t="n"/>
+      <c r="Q51" s="290" t="n"/>
       <c r="R51" s="35" t="n"/>
       <c r="S51" s="35" t="n"/>
       <c r="T51" s="35" t="n"/>
-      <c r="U51" s="32" t="n"/>
+      <c r="U51" s="290" t="n"/>
       <c r="V51" s="31" t="n"/>
       <c r="W51" s="35" t="n"/>
       <c r="X51" s="35" t="n"/>
       <c r="Y51" s="35" t="n"/>
-      <c r="Z51" s="32" t="n"/>
+      <c r="Z51" s="290" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="45" t="inlineStr">
@@ -13329,11 +13343,11 @@
 ARQ-P16 - Piso em pó de saibro com faixa na cor branca para marcação de quadra de tênis fixada com pregos especiais. Verificar detalhes no projeto específico de quadra.</t>
         </is>
       </c>
-      <c r="C52" s="32" t="n"/>
+      <c r="C52" s="290" t="n"/>
       <c r="D52" s="35" t="n"/>
-      <c r="E52" s="37" t="n"/>
-      <c r="F52" s="32" t="n"/>
-      <c r="G52" s="32" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="F52" s="290" t="n"/>
+      <c r="G52" s="290" t="n"/>
       <c r="H52" s="245" t="inlineStr">
         <is>
           <t>03 - Pintura acrílica fosca cinza tom a definir - Reboco (2 demãos Latex acrílico)
@@ -13346,22 +13360,22 @@
         </is>
       </c>
       <c r="J52" s="35" t="n"/>
-      <c r="K52" s="32" t="n"/>
+      <c r="K52" s="290" t="n"/>
       <c r="L52" s="35" t="n"/>
-      <c r="M52" s="37" t="n"/>
+      <c r="M52" s="38" t="n"/>
       <c r="N52" s="38" t="n"/>
       <c r="O52" s="35" t="n"/>
       <c r="P52" s="31" t="n"/>
-      <c r="Q52" s="32" t="n"/>
+      <c r="Q52" s="290" t="n"/>
       <c r="R52" s="35" t="n"/>
       <c r="S52" s="35" t="n"/>
       <c r="T52" s="35" t="n"/>
-      <c r="U52" s="32" t="n"/>
+      <c r="U52" s="290" t="n"/>
       <c r="V52" s="31" t="n"/>
       <c r="W52" s="35" t="n"/>
       <c r="X52" s="35" t="n"/>
       <c r="Y52" s="35" t="n"/>
-      <c r="Z52" s="32" t="n"/>
+      <c r="Z52" s="290" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="45" t="inlineStr">
@@ -13375,16 +13389,16 @@
 ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C53" s="32" t="n"/>
+      <c r="C53" s="290" t="n"/>
       <c r="D53" s="35" t="n"/>
-      <c r="E53" s="37" t="n"/>
+      <c r="E53" s="38" t="n"/>
       <c r="F53" s="246" t="inlineStr">
         <is>
           <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
 ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G53" s="32" t="n"/>
+      <c r="G53" s="290" t="n"/>
       <c r="H53" s="245" t="inlineStr">
         <is>
           <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
@@ -13413,7 +13427,7 @@
           <t>26 - Tanque de embutir CT-50, Mekal, escovado cód.: 90010195016</t>
         </is>
       </c>
-      <c r="M53" s="37" t="n"/>
+      <c r="M53" s="38" t="n"/>
       <c r="N53" s="38" t="n"/>
       <c r="O53" s="245" t="inlineStr">
         <is>
@@ -13421,16 +13435,16 @@
         </is>
       </c>
       <c r="P53" s="31" t="n"/>
-      <c r="Q53" s="32" t="n"/>
+      <c r="Q53" s="290" t="n"/>
       <c r="R53" s="35" t="n"/>
       <c r="S53" s="35" t="n"/>
       <c r="T53" s="35" t="n"/>
-      <c r="U53" s="32" t="n"/>
+      <c r="U53" s="290" t="n"/>
       <c r="V53" s="31" t="n"/>
       <c r="W53" s="35" t="n"/>
       <c r="X53" s="35" t="n"/>
       <c r="Y53" s="35" t="n"/>
-      <c r="Z53" s="32" t="n"/>
+      <c r="Z53" s="290" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="45" t="inlineStr">
@@ -13444,16 +13458,16 @@
 ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="C54" s="32" t="n"/>
+      <c r="C54" s="290" t="n"/>
       <c r="D54" s="35" t="n"/>
-      <c r="E54" s="37" t="n"/>
+      <c r="E54" s="38" t="n"/>
       <c r="F54" s="246" t="inlineStr">
         <is>
           <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
 ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="G54" s="32" t="n"/>
+      <c r="G54" s="290" t="n"/>
       <c r="H54" s="245" t="inlineStr">
         <is>
           <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
@@ -13482,7 +13496,7 @@
           <t>26 - Tanque de embutir CT-50, Mekal, escovado cód.: 90010195016</t>
         </is>
       </c>
-      <c r="M54" s="37" t="n"/>
+      <c r="M54" s="38" t="n"/>
       <c r="N54" s="38" t="n"/>
       <c r="O54" s="245" t="inlineStr">
         <is>
@@ -13490,16 +13504,16 @@
         </is>
       </c>
       <c r="P54" s="31" t="n"/>
-      <c r="Q54" s="32" t="n"/>
+      <c r="Q54" s="290" t="n"/>
       <c r="R54" s="35" t="n"/>
       <c r="S54" s="35" t="n"/>
       <c r="T54" s="35" t="n"/>
-      <c r="U54" s="32" t="n"/>
+      <c r="U54" s="290" t="n"/>
       <c r="V54" s="31" t="n"/>
       <c r="W54" s="35" t="n"/>
       <c r="X54" s="35" t="n"/>
       <c r="Y54" s="35" t="n"/>
-      <c r="Z54" s="32" t="n"/>
+      <c r="Z54" s="290" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
@@ -13512,15 +13526,15 @@
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="C55" s="32" t="n"/>
+      <c r="C55" s="290" t="n"/>
       <c r="D55" s="35" t="n"/>
-      <c r="E55" s="37" t="n"/>
+      <c r="E55" s="38" t="n"/>
       <c r="F55" s="278" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
-      <c r="G55" s="32" t="n"/>
+      <c r="G55" s="290" t="n"/>
       <c r="H55" s="277" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -13548,7 +13562,7 @@
           <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
         </is>
       </c>
-      <c r="M55" s="37" t="n"/>
+      <c r="M55" s="38" t="n"/>
       <c r="N55" s="38" t="n"/>
       <c r="O55" s="245" t="inlineStr">
         <is>
@@ -13560,7 +13574,7 @@
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q55" s="32" t="n"/>
+      <c r="Q55" s="290" t="n"/>
       <c r="R55" s="35" t="n"/>
       <c r="S55" s="245" t="inlineStr">
         <is>
@@ -13610,11 +13624,11 @@
           <t>03 - Piso em concreto mecanizado com acabamento antiderrapante - Escadarias</t>
         </is>
       </c>
-      <c r="C56" s="32" t="n"/>
+      <c r="C56" s="290" t="n"/>
       <c r="D56" s="35" t="n"/>
-      <c r="E56" s="37" t="n"/>
+      <c r="E56" s="38" t="n"/>
       <c r="F56" s="246" t="n"/>
-      <c r="G56" s="32" t="n"/>
+      <c r="G56" s="290" t="n"/>
       <c r="H56" s="245" t="inlineStr">
         <is>
           <t>09 - Textura acrílica rolada fosca branca. Ref.: Branco neve suvinil</t>
@@ -13628,20 +13642,20 @@
       <c r="J56" s="245" t="n"/>
       <c r="K56" s="246" t="n"/>
       <c r="L56" s="245" t="n"/>
-      <c r="M56" s="37" t="n"/>
+      <c r="M56" s="38" t="n"/>
       <c r="N56" s="38" t="n"/>
       <c r="O56" s="245" t="n"/>
       <c r="P56" s="31" t="n"/>
-      <c r="Q56" s="32" t="n"/>
+      <c r="Q56" s="290" t="n"/>
       <c r="R56" s="35" t="n"/>
       <c r="S56" s="35" t="n"/>
       <c r="T56" s="35" t="n"/>
-      <c r="U56" s="32" t="n"/>
+      <c r="U56" s="290" t="n"/>
       <c r="V56" s="31" t="n"/>
       <c r="W56" s="35" t="n"/>
       <c r="X56" s="35" t="n"/>
       <c r="Y56" s="35" t="n"/>
-      <c r="Z56" s="32" t="n"/>
+      <c r="Z56" s="290" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="45" t="inlineStr">
@@ -13655,16 +13669,16 @@
 ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C57" s="32" t="n"/>
+      <c r="C57" s="290" t="n"/>
       <c r="D57" s="35" t="n"/>
-      <c r="E57" s="37" t="n"/>
+      <c r="E57" s="38" t="n"/>
       <c r="F57" s="246" t="inlineStr">
         <is>
           <t>21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm, assentado com argamassa colante em pó ACIII
 ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="G57" s="32" t="n"/>
+      <c r="G57" s="290" t="n"/>
       <c r="H57" s="245" t="inlineStr">
         <is>
           <t>01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
@@ -13680,20 +13694,20 @@
       <c r="J57" s="245" t="n"/>
       <c r="K57" s="246" t="n"/>
       <c r="L57" s="245" t="n"/>
-      <c r="M57" s="37" t="n"/>
+      <c r="M57" s="38" t="n"/>
       <c r="N57" s="38" t="n"/>
       <c r="O57" s="245" t="n"/>
       <c r="P57" s="31" t="n"/>
-      <c r="Q57" s="32" t="n"/>
+      <c r="Q57" s="290" t="n"/>
       <c r="R57" s="35" t="n"/>
       <c r="S57" s="35" t="n"/>
       <c r="T57" s="35" t="n"/>
-      <c r="U57" s="32" t="n"/>
+      <c r="U57" s="290" t="n"/>
       <c r="V57" s="31" t="n"/>
       <c r="W57" s="35" t="n"/>
       <c r="X57" s="35" t="n"/>
       <c r="Y57" s="35" t="n"/>
-      <c r="Z57" s="32" t="n"/>
+      <c r="Z57" s="290" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="45" t="inlineStr">
@@ -13707,15 +13721,15 @@
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C58" s="32" t="n"/>
+      <c r="C58" s="290" t="n"/>
       <c r="D58" s="35" t="n"/>
-      <c r="E58" s="37" t="n"/>
+      <c r="E58" s="38" t="n"/>
       <c r="F58" s="278" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
-      <c r="G58" s="32" t="n"/>
+      <c r="G58" s="290" t="n"/>
       <c r="H58" s="277" t="inlineStr">
         <is>
           <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
@@ -13736,15 +13750,15 @@
         </is>
       </c>
       <c r="L58" s="245" t="n"/>
-      <c r="M58" s="37" t="n"/>
+      <c r="M58" s="38" t="n"/>
       <c r="N58" s="38" t="n"/>
       <c r="O58" s="245" t="n"/>
       <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="32" t="n"/>
+      <c r="Q58" s="290" t="n"/>
       <c r="R58" s="35" t="n"/>
       <c r="S58" s="35" t="n"/>
       <c r="T58" s="35" t="n"/>
-      <c r="U58" s="32" t="n"/>
+      <c r="U58" s="290" t="n"/>
       <c r="V58" s="269" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
@@ -13753,7 +13767,7 @@
       <c r="W58" s="35" t="n"/>
       <c r="X58" s="35" t="n"/>
       <c r="Y58" s="35" t="n"/>
-      <c r="Z58" s="32" t="n"/>
+      <c r="Z58" s="290" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="45" t="inlineStr">
@@ -13767,21 +13781,21 @@
 P8 - Piso elevado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofulgante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C59" s="32" t="n"/>
+      <c r="C59" s="290" t="n"/>
       <c r="D59" s="35" t="n"/>
-      <c r="E59" s="37" t="n"/>
+      <c r="E59" s="38" t="n"/>
       <c r="F59" s="246" t="n"/>
-      <c r="G59" s="32" t="n"/>
+      <c r="G59" s="290" t="n"/>
       <c r="H59" s="245" t="n"/>
       <c r="I59" s="245" t="n"/>
       <c r="J59" s="245" t="n"/>
       <c r="K59" s="246" t="n"/>
       <c r="L59" s="245" t="n"/>
-      <c r="M59" s="37" t="n"/>
+      <c r="M59" s="38" t="n"/>
       <c r="N59" s="38" t="n"/>
       <c r="O59" s="245" t="n"/>
       <c r="P59" s="31" t="n"/>
-      <c r="Q59" s="32" t="n"/>
+      <c r="Q59" s="290" t="n"/>
       <c r="R59" s="35" t="n"/>
       <c r="S59" s="35" t="n"/>
       <c r="T59" s="245" t="inlineStr">
@@ -13789,12 +13803,12 @@
           <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U59" s="32" t="n"/>
+      <c r="U59" s="290" t="n"/>
       <c r="V59" s="31" t="n"/>
       <c r="W59" s="35" t="n"/>
       <c r="X59" s="35" t="n"/>
       <c r="Y59" s="35" t="n"/>
-      <c r="Z59" s="270" t="inlineStr">
+      <c r="Z59" s="271" t="inlineStr">
         <is>
           <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
         </is>
@@ -13811,30 +13825,30 @@
           <t>P8| 8 - Piso elevado em granito cinza Santa rosa, acabamento serrado, espessura de 2cm. Obs.: Resina hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material</t>
         </is>
       </c>
-      <c r="C60" s="32" t="n"/>
+      <c r="C60" s="290" t="n"/>
       <c r="D60" s="35" t="n"/>
-      <c r="E60" s="37" t="n"/>
+      <c r="E60" s="38" t="n"/>
       <c r="F60" s="246" t="n"/>
-      <c r="G60" s="32" t="n"/>
+      <c r="G60" s="290" t="n"/>
       <c r="H60" s="245" t="n"/>
       <c r="I60" s="245" t="n"/>
       <c r="J60" s="245" t="n"/>
       <c r="K60" s="246" t="n"/>
       <c r="L60" s="245" t="n"/>
-      <c r="M60" s="37" t="n"/>
+      <c r="M60" s="38" t="n"/>
       <c r="N60" s="38" t="n"/>
       <c r="O60" s="245" t="n"/>
       <c r="P60" s="31" t="n"/>
-      <c r="Q60" s="32" t="n"/>
+      <c r="Q60" s="290" t="n"/>
       <c r="R60" s="35" t="n"/>
       <c r="S60" s="35" t="n"/>
       <c r="T60" s="35" t="n"/>
-      <c r="U60" s="32" t="n"/>
+      <c r="U60" s="290" t="n"/>
       <c r="V60" s="31" t="n"/>
       <c r="W60" s="35" t="n"/>
       <c r="X60" s="35" t="n"/>
       <c r="Y60" s="35" t="n"/>
-      <c r="Z60" s="32" t="n"/>
+      <c r="Z60" s="290" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="45" t="inlineStr">
@@ -13848,11 +13862,11 @@
 ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="C61" s="32" t="n"/>
+      <c r="C61" s="290" t="n"/>
       <c r="D61" s="35" t="n"/>
-      <c r="E61" s="37" t="n"/>
+      <c r="E61" s="38" t="n"/>
       <c r="F61" s="246" t="n"/>
-      <c r="G61" s="32" t="n"/>
+      <c r="G61" s="290" t="n"/>
       <c r="H61" s="277" t="inlineStr">
         <is>
           <t>ARQ-PA06 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza tom a definir. Meia parede pintada com tinta acrílica fosca na cor verde, tom a definir. Verificar altura conforme detalhamento.</t>
@@ -13862,20 +13876,20 @@
       <c r="J61" s="245" t="n"/>
       <c r="K61" s="246" t="n"/>
       <c r="L61" s="245" t="n"/>
-      <c r="M61" s="37" t="n"/>
+      <c r="M61" s="38" t="n"/>
       <c r="N61" s="38" t="n"/>
       <c r="O61" s="245" t="n"/>
       <c r="P61" s="31" t="n"/>
-      <c r="Q61" s="32" t="n"/>
+      <c r="Q61" s="290" t="n"/>
       <c r="R61" s="35" t="n"/>
       <c r="S61" s="35" t="n"/>
       <c r="T61" s="35" t="n"/>
-      <c r="U61" s="32" t="n"/>
+      <c r="U61" s="290" t="n"/>
       <c r="V61" s="31" t="n"/>
       <c r="W61" s="35" t="n"/>
       <c r="X61" s="35" t="n"/>
       <c r="Y61" s="35" t="n"/>
-      <c r="Z61" s="32" t="n"/>
+      <c r="Z61" s="290" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="45" t="inlineStr">
@@ -13889,11 +13903,11 @@
 ARQ-P17 - Piso em concreto com acabamento em pintura epóxi nas cores cinza e verde, tons a definir. Faixa de pintura epóxi na cor branca, para marcação do desenho de mini quadra infantil. Verificar dimensões conforme detalhamento.</t>
         </is>
       </c>
-      <c r="C62" s="32" t="n"/>
+      <c r="C62" s="290" t="n"/>
       <c r="D62" s="35" t="n"/>
-      <c r="E62" s="37" t="n"/>
+      <c r="E62" s="38" t="n"/>
       <c r="F62" s="246" t="n"/>
-      <c r="G62" s="32" t="n"/>
+      <c r="G62" s="290" t="n"/>
       <c r="H62" s="245" t="inlineStr">
         <is>
           <t>06 - Pintura acrílica fosca cinza tom a definir| Meia parede pintada com tinha acrílica fosca na cor verde, tom a definir - Reboco (2 demãos Latex acrílico)
@@ -13904,20 +13918,20 @@
       <c r="J62" s="245" t="n"/>
       <c r="K62" s="246" t="n"/>
       <c r="L62" s="245" t="n"/>
-      <c r="M62" s="37" t="n"/>
+      <c r="M62" s="38" t="n"/>
       <c r="N62" s="38" t="n"/>
       <c r="O62" s="245" t="n"/>
       <c r="P62" s="31" t="n"/>
-      <c r="Q62" s="32" t="n"/>
+      <c r="Q62" s="290" t="n"/>
       <c r="R62" s="35" t="n"/>
       <c r="S62" s="35" t="n"/>
       <c r="T62" s="35" t="n"/>
-      <c r="U62" s="32" t="n"/>
+      <c r="U62" s="290" t="n"/>
       <c r="V62" s="31" t="n"/>
       <c r="W62" s="35" t="n"/>
       <c r="X62" s="35" t="n"/>
       <c r="Y62" s="35" t="n"/>
-      <c r="Z62" s="32" t="n"/>
+      <c r="Z62" s="290" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="45" t="inlineStr">
@@ -13931,11 +13945,11 @@
 P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="C63" s="32" t="n"/>
+      <c r="C63" s="290" t="n"/>
       <c r="D63" s="35" t="n"/>
-      <c r="E63" s="37" t="n"/>
+      <c r="E63" s="38" t="n"/>
       <c r="F63" s="246" t="n"/>
-      <c r="G63" s="32" t="n"/>
+      <c r="G63" s="290" t="n"/>
       <c r="H63" s="245" t="n"/>
       <c r="I63" s="277" t="inlineStr">
         <is>
@@ -13946,20 +13960,20 @@
       <c r="J63" s="245" t="n"/>
       <c r="K63" s="246" t="n"/>
       <c r="L63" s="245" t="n"/>
-      <c r="M63" s="37" t="n"/>
+      <c r="M63" s="38" t="n"/>
       <c r="N63" s="38" t="n"/>
       <c r="O63" s="245" t="n"/>
       <c r="P63" s="31" t="n"/>
-      <c r="Q63" s="32" t="n"/>
+      <c r="Q63" s="290" t="n"/>
       <c r="R63" s="35" t="n"/>
       <c r="S63" s="35" t="n"/>
       <c r="T63" s="35" t="n"/>
-      <c r="U63" s="32" t="n"/>
+      <c r="U63" s="290" t="n"/>
       <c r="V63" s="31" t="n"/>
       <c r="W63" s="35" t="n"/>
       <c r="X63" s="35" t="n"/>
       <c r="Y63" s="35" t="n"/>
-      <c r="Z63" s="32" t="n"/>
+      <c r="Z63" s="290" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="45" t="inlineStr">
@@ -13972,11 +13986,11 @@
           <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
         </is>
       </c>
-      <c r="C64" s="32" t="n"/>
+      <c r="C64" s="290" t="n"/>
       <c r="D64" s="35" t="n"/>
-      <c r="E64" s="37" t="n"/>
+      <c r="E64" s="38" t="n"/>
       <c r="F64" s="246" t="n"/>
-      <c r="G64" s="32" t="n"/>
+      <c r="G64" s="290" t="n"/>
       <c r="H64" s="277" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
@@ -13990,20 +14004,20 @@
       <c r="J64" s="245" t="n"/>
       <c r="K64" s="246" t="n"/>
       <c r="L64" s="245" t="n"/>
-      <c r="M64" s="37" t="n"/>
+      <c r="M64" s="38" t="n"/>
       <c r="N64" s="38" t="n"/>
       <c r="O64" s="245" t="n"/>
       <c r="P64" s="31" t="n"/>
-      <c r="Q64" s="32" t="n"/>
+      <c r="Q64" s="290" t="n"/>
       <c r="R64" s="35" t="n"/>
       <c r="S64" s="35" t="n"/>
       <c r="T64" s="35" t="n"/>
-      <c r="U64" s="32" t="n"/>
+      <c r="U64" s="290" t="n"/>
       <c r="V64" s="31" t="n"/>
       <c r="W64" s="35" t="n"/>
       <c r="X64" s="35" t="n"/>
       <c r="Y64" s="35" t="n"/>
-      <c r="Z64" s="32" t="n"/>
+      <c r="Z64" s="290" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -14691,43 +14705,43 @@
           <t>Piso em mármore travertino romano bruto, 85x130cm, paginação conforme detalhamento. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). (DET PR001/PR002; Tab. R01)</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="32" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="288" t="inlineStr">
+      <c r="C13" s="290" t="n"/>
+      <c r="D13" s="290" t="n"/>
+      <c r="E13" s="290" t="n"/>
+      <c r="F13" s="285" t="inlineStr">
         <is>
           <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR001/PR002)
 CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
         </is>
       </c>
-      <c r="G13" s="32" t="n"/>
+      <c r="G13" s="290" t="n"/>
       <c r="H13" s="271" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve, acabamento acetinado. (DET PR001; Tab. R01)</t>
         </is>
       </c>
       <c r="I13" s="271" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="32" t="n"/>
-      <c r="M13" s="32" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="32" t="n"/>
-      <c r="P13" s="32" t="n"/>
-      <c r="Q13" s="32" t="n"/>
-      <c r="R13" s="32" t="n"/>
-      <c r="S13" s="32" t="n"/>
-      <c r="T13" s="32" t="inlineStr">
+      <c r="J13" s="290" t="n"/>
+      <c r="K13" s="290" t="n"/>
+      <c r="L13" s="290" t="n"/>
+      <c r="M13" s="290" t="n"/>
+      <c r="N13" s="290" t="n"/>
+      <c r="O13" s="290" t="n"/>
+      <c r="P13" s="290" t="n"/>
+      <c r="Q13" s="290" t="n"/>
+      <c r="R13" s="290" t="n"/>
+      <c r="S13" s="290" t="n"/>
+      <c r="T13" s="290" t="inlineStr">
         <is>
           <t>Varanda: ralo linear oculto; caimento do piso para o ralo i=1%. (DET PR001)</t>
         </is>
       </c>
-      <c r="U13" s="32" t="n"/>
-      <c r="V13" s="32" t="n"/>
-      <c r="W13" s="32" t="n"/>
+      <c r="U13" s="290" t="n"/>
+      <c r="V13" s="290" t="n"/>
+      <c r="W13" s="290" t="n"/>
       <c r="X13" s="31" t="n"/>
       <c r="Y13" s="31" t="n"/>
-      <c r="Z13" s="32" t="inlineStr">
+      <c r="Z13" s="290" t="inlineStr">
         <is>
           <t>Varanda: mureta h=90cm. (DET PR001)</t>
         </is>
@@ -14744,20 +14758,20 @@
           <t>Piso em mármore travertino romano bruto. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). (DET PR004; Tab. R01)</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="290" t="inlineStr">
         <is>
           <t>Soleira indicada em planta, material não especificado. (DET PR004)</t>
         </is>
       </c>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="288" t="inlineStr">
+      <c r="D14" s="290" t="n"/>
+      <c r="E14" s="290" t="n"/>
+      <c r="F14" s="285" t="inlineStr">
         <is>
           <t>Rodapé semi-embutido em mármore travertino romano bruto, h=15cm. (DET PR004)
 CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
         </is>
       </c>
-      <c r="G14" s="32" t="n"/>
+      <c r="G14" s="290" t="n"/>
       <c r="H14" s="271" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve, acabamento acetinado. (DET PR004; Tab. R01)</t>
@@ -14768,41 +14782,41 @@
           <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica. PD 298cm. (DET PR004)</t>
         </is>
       </c>
-      <c r="J14" s="32" t="inlineStr">
+      <c r="J14" s="290" t="inlineStr">
         <is>
           <t>Bancada esculpida em mármore travertino romano resinado (cuba esculpida). (DET PR004; Tab. R01)</t>
         </is>
       </c>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="32" t="inlineStr">
+      <c r="K14" s="290" t="n"/>
+      <c r="L14" s="290" t="n"/>
+      <c r="M14" s="290" t="n"/>
+      <c r="N14" s="290" t="n"/>
+      <c r="O14" s="290" t="inlineStr">
         <is>
           <t>Torneira de mesa bica baixa para lavatório, cromado, linha Unic, cód. 1197.C90. Ref.: Deca. (DET PR004; Tab. R01)</t>
         </is>
       </c>
-      <c r="P14" s="32" t="inlineStr">
+      <c r="P14" s="290" t="inlineStr">
         <is>
           <t>Bacia convencional suspensa branca, linha LK, cód. P.232.17. Ref.: Deca. Caixa de descarga embutida para alvenaria. (DET PR004; Tab. R01)</t>
         </is>
       </c>
-      <c r="Q14" s="32" t="n"/>
-      <c r="R14" s="32" t="inlineStr">
+      <c r="Q14" s="290" t="n"/>
+      <c r="R14" s="290" t="inlineStr">
         <is>
           <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Unic, cód. 4900.C90.GD. Ref.: Deca
 Acabamento para caixa de descarga embutida, cromado, H Quadra Duo, cód. 4900.C.HQD.DUO. Ref.: Deca. (DET PR004)</t>
         </is>
       </c>
-      <c r="S14" s="32" t="n"/>
-      <c r="T14" s="32" t="inlineStr">
+      <c r="S14" s="290" t="n"/>
+      <c r="T14" s="290" t="inlineStr">
         <is>
           <t>Ralo oculto 15x15cm, tampa revestida com o mesmo mármore. (DET PR004)</t>
         </is>
       </c>
-      <c r="U14" s="32" t="n"/>
-      <c r="V14" s="32" t="n"/>
-      <c r="W14" s="32" t="inlineStr">
+      <c r="U14" s="290" t="n"/>
+      <c r="V14" s="290" t="n"/>
+      <c r="W14" s="290" t="inlineStr">
         <is>
           <t>Maçaneta Pado Sara, cromo acetinado, interna. (DET PR004)</t>
         </is>
@@ -14813,7 +14827,7 @@
         </is>
       </c>
       <c r="Y14" s="31" t="n"/>
-      <c r="Z14" s="32" t="n"/>
+      <c r="Z14" s="290" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="45" t="inlineStr">
@@ -14826,19 +14840,19 @@
           <t>11 - Piso em contrapiso regularizado, revestido em mármore travertino romano resinado. Rejunte creme ou marfim (ver padrão da chapa). Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408; Tab. R01: "bruto resinado")</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="C15" s="290" t="n"/>
+      <c r="D15" s="290" t="n"/>
+      <c r="E15" s="290" t="inlineStr">
         <is>
           <t>Peitoril a definir conforme projeto de esquadrias. (PR408)</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="290" t="inlineStr">
         <is>
           <t>23 - Rodapé em mármore travertino romano bruto semi-embutido, h=15cm; paginação segue alinhamento do piso. (PR408)</t>
         </is>
       </c>
-      <c r="G15" s="32" t="n"/>
+      <c r="G15" s="290" t="n"/>
       <c r="H15" s="285" t="inlineStr">
         <is>
           <t>14 - Parede revestida em mármore travertino romano resinado. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408)
@@ -14851,62 +14865,62 @@
           <t>1 - Forro em gesso acartonado liso, tinta acrílica cor branco neve, acabamento fosco, junta de dilatação metálica branca. Ref.: Suvinil. Sanca (DET 20). (PR408)</t>
         </is>
       </c>
-      <c r="J15" s="32" t="inlineStr">
+      <c r="J15" s="290" t="inlineStr">
         <is>
           <t>35 - Bancada em mármore travertino romano resinado. Rejunte creme ou marfim (ver padrão da chapa). Dimensões conforme detalhamento. (PR408; Tab. R01)</t>
         </is>
       </c>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="inlineStr">
+      <c r="K15" s="290" t="n"/>
+      <c r="L15" s="290" t="inlineStr">
         <is>
           <t>33 - Cuba de apoio retangular Jader Almeida 670x495x120mm, branca, cód. L.310.17. Ref.: Deca. (PR408; Tab. R01)</t>
         </is>
       </c>
-      <c r="M15" s="32" t="n"/>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="32" t="inlineStr">
+      <c r="M15" s="290" t="n"/>
+      <c r="N15" s="290" t="n"/>
+      <c r="O15" s="290" t="inlineStr">
         <is>
           <t>36 - Misturador monocomando de mesa bica alta para lavatório, Level cromado, cód. 2885.C26. Ref.: Deca. (PR408; Tab. R01)</t>
         </is>
       </c>
-      <c r="P15" s="32" t="inlineStr">
+      <c r="P15" s="290" t="inlineStr">
         <is>
           <t>34 - Bacia convencional Carrara branca com caixa acoplada e acionamento duo, cód. P.606.17. Ref.: Deca. (PR408; Tab. R01)
 46 - Bidê 3 furos Carrara branco, cód. B.60.17. Ref.: Deca. (PR408; Tab. R01)</t>
         </is>
       </c>
-      <c r="Q15" s="32" t="inlineStr">
+      <c r="Q15" s="290" t="inlineStr">
         <is>
           <t>37 - Ducha higiênica Level cromada, cód. 1984.C26.ACT.CR. (PR408)</t>
         </is>
       </c>
-      <c r="R15" s="32" t="inlineStr">
+      <c r="R15" s="290" t="inlineStr">
         <is>
           <t>49 - Acabamento para registro Level cromado, cód. 4900.C26.PQ. Ref.: Deca. (PR408)</t>
         </is>
       </c>
-      <c r="S15" s="32" t="inlineStr">
+      <c r="S15" s="290" t="inlineStr">
         <is>
           <t>44 - Acabamento de monocomando de chuveiro para alta e baixa pressão, Level cromado, cód. 4993.C26.CHU. (PR408; Tab. R01)</t>
         </is>
       </c>
-      <c r="T15" s="32" t="inlineStr">
+      <c r="T15" s="290" t="inlineStr">
         <is>
           <t>47 - Ralo linear oculto Royal 70cm
 48 - Ralo oculto 15x15cm Square. (PR408)</t>
         </is>
       </c>
-      <c r="U15" s="32" t="inlineStr">
+      <c r="U15" s="290" t="inlineStr">
         <is>
           <t>45 - Misturador para bidê Level cromado, cód. 1895.C26. (PR408; Tab. R01)</t>
         </is>
       </c>
-      <c r="V15" s="32" t="inlineStr">
+      <c r="V15" s="290" t="inlineStr">
         <is>
           <t>39 - Tomadas e interruptores Arteor quadrado branco. Ref.: Legrand. (PR408)</t>
         </is>
       </c>
-      <c r="W15" s="32" t="inlineStr">
+      <c r="W15" s="290" t="inlineStr">
         <is>
           <t>Maçaneta Sara cromo acetinado. Ref.: Pado. (PR408)</t>
         </is>
@@ -14917,7 +14931,7 @@
         </is>
       </c>
       <c r="Y15" s="31" t="n"/>
-      <c r="Z15" s="32" t="n"/>
+      <c r="Z15" s="290" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="45" t="inlineStr">
@@ -14930,11 +14944,11 @@
           <t>Piso em mármore travertino romano bruto resinado, paginado. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). Desnível do box 1cm. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
+      <c r="C16" s="290" t="n"/>
+      <c r="D16" s="290" t="n"/>
+      <c r="E16" s="290" t="n"/>
+      <c r="F16" s="290" t="n"/>
+      <c r="G16" s="290" t="n"/>
       <c r="H16" s="271" t="inlineStr">
         <is>
           <t>Parede em mármore travertino romano bruto: piso ao teto na área do box e barrado semi-embutido até 110cm nas demais paredes; acima, pintura acrílica cor branco neve, acetinado. (DET PR008; Tab. R01)</t>
@@ -14945,55 +14959,55 @@
           <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica e sanca. PD 298cm. (DET PR008)</t>
         </is>
       </c>
-      <c r="J16" s="32" t="inlineStr">
+      <c r="J16" s="290" t="inlineStr">
         <is>
           <t>Bancada esculpida em mármore travertino romano resinado. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="inlineStr">
+      <c r="K16" s="290" t="n"/>
+      <c r="L16" s="290" t="inlineStr">
         <is>
           <t>Cuba retangular de apoio 60cm com deck, branca, linha Slim, cód. L.13060.M.17. Ref.: Deca. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="inlineStr">
+      <c r="M16" s="290" t="n"/>
+      <c r="N16" s="290" t="n"/>
+      <c r="O16" s="290" t="inlineStr">
         <is>
           <t>Misturador monocomando de mesa bica baixa para lavatório, cromado, linha Level, cód. 2875.C26. Ref.: Deca. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="P16" s="32" t="inlineStr">
+      <c r="P16" s="290" t="inlineStr">
         <is>
           <t>Bacia convencional Carrara branca com caixa acoplada, cód. KP.606.17. Ref.: Deca. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="Q16" s="32" t="inlineStr">
+      <c r="Q16" s="290" t="inlineStr">
         <is>
           <t>Ducha higiênica com registro e derivação, cromada, linha Level. Ref.: Deca. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="R16" s="32" t="inlineStr">
+      <c r="R16" s="290" t="inlineStr">
         <is>
           <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Level, cód. 4900.C26.GD. Ref.: Deca. (DET PR008)</t>
         </is>
       </c>
-      <c r="S16" s="32" t="inlineStr">
+      <c r="S16" s="290" t="inlineStr">
         <is>
           <t>Acabamento monocomando para chuveiro, cromado, linha Level, cód. 4993.C26.CHU. Ref.: Deca. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="T16" s="32" t="inlineStr">
+      <c r="T16" s="290" t="inlineStr">
         <is>
           <t>Ralo oculto 15x15cm e ralo linear oculto 90x5cm, tampas revestidas com a mesma pedra. (DET PR008)</t>
         </is>
       </c>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
-      <c r="W16" s="32" t="n"/>
+      <c r="U16" s="290" t="n"/>
+      <c r="V16" s="290" t="n"/>
+      <c r="W16" s="290" t="n"/>
       <c r="X16" s="31" t="n"/>
       <c r="Y16" s="31" t="n"/>
-      <c r="Z16" s="32" t="n"/>
+      <c r="Z16" s="290" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="45" t="inlineStr">
@@ -15006,43 +15020,43 @@
           <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (DET PR001/PR002; Tab. R01)</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="C17" s="290" t="n"/>
+      <c r="D17" s="290" t="inlineStr">
         <is>
           <t>Transição madeira x pedra: perfil metálico (DET 05) ou filete de mármore (DET 07). (DET PR001)</t>
         </is>
       </c>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="288" t="inlineStr">
+      <c r="E17" s="290" t="n"/>
+      <c r="F17" s="285" t="inlineStr">
         <is>
           <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
 CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
         </is>
       </c>
-      <c r="G17" s="32" t="n"/>
+      <c r="G17" s="290" t="n"/>
       <c r="H17" s="271" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve. (Tab. R01)</t>
         </is>
       </c>
       <c r="I17" s="271" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
-      <c r="O17" s="32" t="n"/>
-      <c r="P17" s="32" t="n"/>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="32" t="n"/>
-      <c r="S17" s="32" t="n"/>
-      <c r="T17" s="32" t="n"/>
-      <c r="U17" s="32" t="n"/>
-      <c r="V17" s="32" t="n"/>
-      <c r="W17" s="32" t="n"/>
+      <c r="J17" s="290" t="n"/>
+      <c r="K17" s="290" t="n"/>
+      <c r="L17" s="290" t="n"/>
+      <c r="M17" s="290" t="n"/>
+      <c r="N17" s="290" t="n"/>
+      <c r="O17" s="290" t="n"/>
+      <c r="P17" s="290" t="n"/>
+      <c r="Q17" s="290" t="n"/>
+      <c r="R17" s="290" t="n"/>
+      <c r="S17" s="290" t="n"/>
+      <c r="T17" s="290" t="n"/>
+      <c r="U17" s="290" t="n"/>
+      <c r="V17" s="290" t="n"/>
+      <c r="W17" s="290" t="n"/>
       <c r="X17" s="31" t="n"/>
       <c r="Y17" s="31" t="n"/>
-      <c r="Z17" s="32" t="n"/>
+      <c r="Z17" s="290" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="45" t="inlineStr">
@@ -15055,47 +15069,47 @@
           <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (Tab. R01)</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="C18" s="290" t="n"/>
+      <c r="D18" s="290" t="n"/>
+      <c r="E18" s="290" t="n"/>
+      <c r="F18" s="290" t="inlineStr">
         <is>
           <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01)</t>
         </is>
       </c>
-      <c r="G18" s="32" t="n"/>
+      <c r="G18" s="290" t="n"/>
       <c r="H18" s="271" t="n"/>
       <c r="I18" s="271" t="n"/>
-      <c r="J18" s="288" t="inlineStr">
+      <c r="J18" s="285" t="inlineStr">
         <is>
           <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)
 CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
         </is>
       </c>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="inlineStr">
+      <c r="K18" s="290" t="n"/>
+      <c r="L18" s="290" t="inlineStr">
         <is>
           <t>Cuba redonda CR-30, escovada, cód. 01018116 / 90010181016. Ref.: Mekal. (DET PR003; Tab. R01)</t>
         </is>
       </c>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="32" t="n"/>
-      <c r="O18" s="32" t="inlineStr">
+      <c r="M18" s="290" t="n"/>
+      <c r="N18" s="290" t="n"/>
+      <c r="O18" s="290" t="inlineStr">
         <is>
           <t>Torneira de mesa bica alta para lavatório, cromada, linha Link, cód. 1198.C.LNK. Ref.: Deca. (DET PR003; Tab. R01)</t>
         </is>
       </c>
-      <c r="P18" s="32" t="n"/>
-      <c r="Q18" s="32" t="n"/>
-      <c r="R18" s="32" t="n"/>
-      <c r="S18" s="32" t="n"/>
-      <c r="T18" s="32" t="n"/>
-      <c r="U18" s="32" t="n"/>
-      <c r="V18" s="32" t="n"/>
-      <c r="W18" s="32" t="n"/>
+      <c r="P18" s="290" t="n"/>
+      <c r="Q18" s="290" t="n"/>
+      <c r="R18" s="290" t="n"/>
+      <c r="S18" s="290" t="n"/>
+      <c r="T18" s="290" t="n"/>
+      <c r="U18" s="290" t="n"/>
+      <c r="V18" s="290" t="n"/>
+      <c r="W18" s="290" t="n"/>
       <c r="X18" s="31" t="n"/>
       <c r="Y18" s="31" t="n"/>
-      <c r="Z18" s="32" t="n"/>
+      <c r="Z18" s="290" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
@@ -15108,19 +15122,19 @@
           <t>Piso em granito branco siena escovado, 85x130cm. Rejunte Infinity Hard, cor Branco Pérola ou Palha (validar com o Setor de Produto). (DET PR001, PR406/407; Tab. R01: paginação a definir)</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="290" t="inlineStr">
         <is>
           <t>Soleira em granito branco siena. (PR406)</t>
         </is>
       </c>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="D19" s="290" t="n"/>
+      <c r="E19" s="290" t="n"/>
+      <c r="F19" s="290" t="inlineStr">
         <is>
           <t>Rodapé semi-embutido em granito branco siena escovado, h=15cm (DET 22). (DET PR001, PR406/407; Tab. R01)</t>
         </is>
       </c>
-      <c r="G19" s="32" t="n"/>
+      <c r="G19" s="290" t="n"/>
       <c r="H19" s="271" t="inlineStr">
         <is>
           <t>Rodabanca em granito branco siena escovado, h=60cm
@@ -15128,39 +15142,39 @@
         </is>
       </c>
       <c r="I19" s="271" t="n"/>
-      <c r="J19" s="32" t="inlineStr">
+      <c r="J19" s="290" t="inlineStr">
         <is>
           <t>Bancada e ilha em granito branco siena escovado; parte seca h=90cm, área molhada com desnível 1cm h=92cm; suporte em metalon chumbado na parede; emendas seguem a paginação do piso. (PR406/407; Tab. R01)</t>
         </is>
       </c>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="inlineStr">
+      <c r="K19" s="290" t="n"/>
+      <c r="L19" s="290" t="inlineStr">
         <is>
           <t>Cuba de embutir 600x400x230mm em aço inox, linha Retta. Ref.: Mekal ou similar. (Tab. R01; PR406 sem modelo)</t>
         </is>
       </c>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="inlineStr">
+      <c r="M19" s="290" t="n"/>
+      <c r="N19" s="290" t="n"/>
+      <c r="O19" s="290" t="inlineStr">
         <is>
           <t>Monocomando de mesa para cozinha, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01; PR406 sem modelo)</t>
         </is>
       </c>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="32" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="32" t="n"/>
-      <c r="U19" s="32" t="n"/>
-      <c r="V19" s="32" t="n"/>
-      <c r="W19" s="32" t="n"/>
+      <c r="P19" s="290" t="n"/>
+      <c r="Q19" s="290" t="n"/>
+      <c r="R19" s="290" t="n"/>
+      <c r="S19" s="290" t="n"/>
+      <c r="T19" s="290" t="n"/>
+      <c r="U19" s="290" t="n"/>
+      <c r="V19" s="290" t="n"/>
+      <c r="W19" s="290" t="n"/>
       <c r="X19" s="31" t="inlineStr">
         <is>
           <t>Porta em marcenaria. (PR406/407)</t>
         </is>
       </c>
       <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="32" t="n"/>
+      <c r="Z19" s="290" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="45" t="inlineStr">
@@ -15173,19 +15187,19 @@
           <t>Piso em granito branco siena escovado, 85x130cm, ver paginação. Rejunte Infinity Hard, cor Branco Pérola ou Palha. (DET PR001, PR005; Tab. R01)</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="C20" s="290" t="inlineStr">
         <is>
           <t>Soleira indicada em planta, material não especificado. (DET PR005)</t>
         </is>
       </c>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="D20" s="290" t="n"/>
+      <c r="E20" s="290" t="n"/>
+      <c r="F20" s="290" t="inlineStr">
         <is>
           <t>Rodapé semi-embutido em granito branco siena escovado, h=15cm. (DET PR005)</t>
         </is>
       </c>
-      <c r="G20" s="32" t="n"/>
+      <c r="G20" s="290" t="n"/>
       <c r="H20" s="271" t="inlineStr">
         <is>
           <t>Parede em Formica Branco Real L515, 308x125cm. (DET PR005/PR006; Tab. R01)</t>
@@ -15196,40 +15210,40 @@
           <t>Forro de gesso com tabica metálica (DET 11) e cortineiro 25x16cm (DET 24). (DET PR006)</t>
         </is>
       </c>
-      <c r="J20" s="32" t="inlineStr">
+      <c r="J20" s="290" t="inlineStr">
         <is>
           <t>Bancada em granito branco siena escovado, molhada com 1cm de rebaixo, rodabanca h=60cm com topo polido; bancada seca com laterais polidas. (DET PR005/PR006; Tab. R01)</t>
         </is>
       </c>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="inlineStr">
+      <c r="K20" s="290" t="n"/>
+      <c r="L20" s="290" t="inlineStr">
         <is>
           <t>Tanque para lavanderia CT-60, escovado, cód. 01019616 / 90010196016, 2 unidades, instalados sob a pedra da bancada. Ref.: Mekal. (DET PR005; Tab. R01)</t>
         </is>
       </c>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
-      <c r="O20" s="32" t="inlineStr">
+      <c r="M20" s="290" t="n"/>
+      <c r="N20" s="290" t="n"/>
+      <c r="O20" s="290" t="inlineStr">
         <is>
           <t>Torneira de parede com arejador para cozinha, cromada, linha Link, cód. 1159.C.LNK, 2 unidades. Ref.: Deca. (DET PR005; Tab. R01)</t>
         </is>
       </c>
-      <c r="P20" s="32" t="n"/>
-      <c r="Q20" s="32" t="n"/>
-      <c r="R20" s="32" t="inlineStr">
+      <c r="P20" s="290" t="n"/>
+      <c r="Q20" s="290" t="n"/>
+      <c r="R20" s="290" t="inlineStr">
         <is>
           <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Link, cód. 4900.C.GD.LNK. Ref.: Deca. (DET PR005)</t>
         </is>
       </c>
-      <c r="S20" s="32" t="n"/>
-      <c r="T20" s="32" t="inlineStr">
+      <c r="S20" s="290" t="n"/>
+      <c r="T20" s="290" t="inlineStr">
         <is>
           <t>Ralo oculto 15x15cm, tampa revestida com a mesma pedra (o DET diz "mármore"; o piso é granito). (DET PR005)</t>
         </is>
       </c>
-      <c r="U20" s="32" t="n"/>
-      <c r="V20" s="32" t="n"/>
-      <c r="W20" s="32" t="inlineStr">
+      <c r="U20" s="290" t="n"/>
+      <c r="V20" s="290" t="n"/>
+      <c r="W20" s="290" t="inlineStr">
         <is>
           <t>Maçaneta Pado Sara, cromo acetinado, interna. Porta de segurança: fechadura digital FDE-600W. (DET PR005/PR006)</t>
         </is>
@@ -15241,7 +15255,7 @@
         </is>
       </c>
       <c r="Y20" s="31" t="n"/>
-      <c r="Z20" s="32" t="n"/>
+      <c r="Z20" s="290" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="45" t="inlineStr">
@@ -15254,15 +15268,15 @@
           <t>Piso em granito branco siena escovado. (DET PR007; Tab. R01: paginação a definir)</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="C21" s="290" t="n"/>
+      <c r="D21" s="290" t="inlineStr">
         <is>
           <t>Filete em granito na transição para o vinílico (DET 04). (DET PR007)</t>
         </is>
       </c>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
+      <c r="E21" s="290" t="n"/>
+      <c r="F21" s="290" t="n"/>
+      <c r="G21" s="290" t="n"/>
       <c r="H21" s="271" t="inlineStr">
         <is>
           <t>Revestimento Forma Branco AC retificado 32,5x59cm. Ref.: Eliane. (DET PR007; Tab. R01)</t>
@@ -15273,51 +15287,51 @@
           <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica, sanca 25x16cm. PD 298cm. (DET PR007)</t>
         </is>
       </c>
-      <c r="J21" s="32" t="inlineStr">
+      <c r="J21" s="290" t="inlineStr">
         <is>
           <t>Bancada em granito branco siena escovado. (DET PR007; Tab. R01)</t>
         </is>
       </c>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="inlineStr">
+      <c r="K21" s="290" t="n"/>
+      <c r="L21" s="290" t="inlineStr">
         <is>
           <t>Cuba redonda de embutir 31cm branca, linha L, cód. L.41.17. Ref.: Deca. (DET PR007; Tab. R01)</t>
         </is>
       </c>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="inlineStr">
+      <c r="M21" s="290" t="n"/>
+      <c r="N21" s="290" t="n"/>
+      <c r="O21" s="290" t="inlineStr">
         <is>
           <t>Torneira de mesa bica baixa para lavatório, cromada, linha Link, cód. 1197.C.LNK. Ref.: Deca. (DET PR007; Tab. R01)</t>
         </is>
       </c>
-      <c r="P21" s="32" t="inlineStr">
+      <c r="P21" s="290" t="inlineStr">
         <is>
           <t>Bacia com caixa acoplada branca, linha Axis, cód. KP.470.17. Ref.: Deca. (DET PR007; Tab. R01)</t>
         </is>
       </c>
-      <c r="Q21" s="32" t="inlineStr">
+      <c r="Q21" s="290" t="inlineStr">
         <is>
           <t>Ducha higiênica com registro e derivação, cromada, linha Link, cód. 1984.C.ACT.LNK.BR. Ref.: Deca. (DET PR007)</t>
         </is>
       </c>
-      <c r="R21" s="32" t="inlineStr">
+      <c r="R21" s="290" t="inlineStr">
         <is>
           <t>Acabamento para registro de gaveta e pressão até 1", cromado, Link, cód. 4900.C.PQ.LNK. Ref.: Deca. (DET PR007; Tab. R01)</t>
         </is>
       </c>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="inlineStr">
+      <c r="S21" s="290" t="n"/>
+      <c r="T21" s="290" t="inlineStr">
         <is>
           <t>Ralo linear oculto e ralo quadrado oculto. (DET PR007)</t>
         </is>
       </c>
-      <c r="U21" s="32" t="n"/>
-      <c r="V21" s="32" t="n"/>
-      <c r="W21" s="32" t="n"/>
+      <c r="U21" s="290" t="n"/>
+      <c r="V21" s="290" t="n"/>
+      <c r="W21" s="290" t="n"/>
       <c r="X21" s="31" t="n"/>
       <c r="Y21" s="31" t="n"/>
-      <c r="Z21" s="32" t="n"/>
+      <c r="Z21" s="290" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="45" t="inlineStr">
@@ -15330,42 +15344,42 @@
           <t>Piso vinílico Austin, linha Urban, 18x121cm. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="C22" s="290" t="n"/>
+      <c r="D22" s="290" t="inlineStr">
         <is>
           <t>Filete em granito na transição vinílico x granito (DET 04). (DET PR001)</t>
         </is>
       </c>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="E22" s="290" t="n"/>
+      <c r="F22" s="290" t="inlineStr">
         <is>
           <t>Rodapé Easy Y.01 120. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
         </is>
       </c>
-      <c r="G22" s="32" t="n"/>
+      <c r="G22" s="290" t="n"/>
       <c r="H22" s="271" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve. (Tab. R01)</t>
         </is>
       </c>
       <c r="I22" s="271" t="n"/>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="32" t="n"/>
-      <c r="M22" s="32" t="n"/>
-      <c r="N22" s="32" t="n"/>
-      <c r="O22" s="32" t="n"/>
-      <c r="P22" s="32" t="n"/>
-      <c r="Q22" s="32" t="n"/>
-      <c r="R22" s="32" t="n"/>
-      <c r="S22" s="32" t="n"/>
-      <c r="T22" s="32" t="n"/>
-      <c r="U22" s="32" t="n"/>
-      <c r="V22" s="32" t="n"/>
-      <c r="W22" s="32" t="n"/>
+      <c r="J22" s="290" t="n"/>
+      <c r="K22" s="290" t="n"/>
+      <c r="L22" s="290" t="n"/>
+      <c r="M22" s="290" t="n"/>
+      <c r="N22" s="290" t="n"/>
+      <c r="O22" s="290" t="n"/>
+      <c r="P22" s="290" t="n"/>
+      <c r="Q22" s="290" t="n"/>
+      <c r="R22" s="290" t="n"/>
+      <c r="S22" s="290" t="n"/>
+      <c r="T22" s="290" t="n"/>
+      <c r="U22" s="290" t="n"/>
+      <c r="V22" s="290" t="n"/>
+      <c r="W22" s="290" t="n"/>
       <c r="X22" s="31" t="n"/>
       <c r="Y22" s="31" t="n"/>
-      <c r="Z22" s="32" t="n"/>
+      <c r="Z22" s="290" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="45" t="inlineStr">
@@ -15378,30 +15392,30 @@
           <t>Piso em concreto. (DET PR001)</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
+      <c r="C23" s="290" t="n"/>
+      <c r="D23" s="290" t="n"/>
+      <c r="E23" s="290" t="n"/>
+      <c r="F23" s="290" t="n"/>
+      <c r="G23" s="290" t="n"/>
       <c r="H23" s="271" t="n"/>
       <c r="I23" s="271" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="32" t="n"/>
+      <c r="J23" s="290" t="n"/>
+      <c r="K23" s="290" t="n"/>
+      <c r="L23" s="290" t="n"/>
+      <c r="M23" s="290" t="n"/>
+      <c r="N23" s="290" t="n"/>
+      <c r="O23" s="290" t="n"/>
+      <c r="P23" s="290" t="n"/>
+      <c r="Q23" s="290" t="n"/>
+      <c r="R23" s="290" t="n"/>
+      <c r="S23" s="290" t="n"/>
+      <c r="T23" s="290" t="n"/>
+      <c r="U23" s="290" t="n"/>
+      <c r="V23" s="290" t="n"/>
+      <c r="W23" s="290" t="n"/>
       <c r="X23" s="31" t="n"/>
       <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="32" t="n"/>
+      <c r="Z23" s="290" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="45" t="inlineStr">
@@ -15414,15 +15428,15 @@
           <t>Piso em mármore travertino romano bruto. (DET PR003)</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="inlineStr">
+      <c r="C24" s="290" t="n"/>
+      <c r="D24" s="290" t="n"/>
+      <c r="E24" s="290" t="n"/>
+      <c r="F24" s="290" t="inlineStr">
         <is>
           <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR003)</t>
         </is>
       </c>
-      <c r="G24" s="32" t="n"/>
+      <c r="G24" s="290" t="n"/>
       <c r="H24" s="271" t="inlineStr">
         <is>
           <t>Parede pintada com tinta acrílica cor branco neve, acabamento acetinado
@@ -15430,23 +15444,23 @@
         </is>
       </c>
       <c r="I24" s="271" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="32" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
-      <c r="T24" s="32" t="n"/>
-      <c r="U24" s="32" t="n"/>
-      <c r="V24" s="32" t="n"/>
-      <c r="W24" s="32" t="n"/>
+      <c r="J24" s="290" t="n"/>
+      <c r="K24" s="290" t="n"/>
+      <c r="L24" s="290" t="n"/>
+      <c r="M24" s="290" t="n"/>
+      <c r="N24" s="290" t="n"/>
+      <c r="O24" s="290" t="n"/>
+      <c r="P24" s="290" t="n"/>
+      <c r="Q24" s="290" t="n"/>
+      <c r="R24" s="290" t="n"/>
+      <c r="S24" s="290" t="n"/>
+      <c r="T24" s="290" t="n"/>
+      <c r="U24" s="290" t="n"/>
+      <c r="V24" s="290" t="n"/>
+      <c r="W24" s="290" t="n"/>
       <c r="X24" s="31" t="n"/>
       <c r="Y24" s="31" t="n"/>
-      <c r="Z24" s="32" t="n"/>
+      <c r="Z24" s="290" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="45" t="inlineStr">
@@ -15459,15 +15473,15 @@
           <t>Piso em granito branco siena escovado. (DET PR003)</t>
         </is>
       </c>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="C25" s="290" t="n"/>
+      <c r="D25" s="290" t="n"/>
+      <c r="E25" s="290" t="n"/>
+      <c r="F25" s="290" t="inlineStr">
         <is>
           <t>Rodapé em granito branco siena escovado, semi-embutido, h=15cm. (DET PR003)</t>
         </is>
       </c>
-      <c r="G25" s="32" t="n"/>
+      <c r="G25" s="290" t="n"/>
       <c r="H25" s="271" t="inlineStr">
         <is>
           <t>Parede pintada com tinta acrílica cor branco neve, acabamento acetinado
@@ -15475,23 +15489,23 @@
         </is>
       </c>
       <c r="I25" s="271" t="n"/>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="32" t="n"/>
-      <c r="M25" s="32" t="n"/>
-      <c r="N25" s="32" t="n"/>
-      <c r="O25" s="32" t="n"/>
-      <c r="P25" s="32" t="n"/>
-      <c r="Q25" s="32" t="n"/>
-      <c r="R25" s="32" t="n"/>
-      <c r="S25" s="32" t="n"/>
-      <c r="T25" s="32" t="n"/>
-      <c r="U25" s="32" t="n"/>
-      <c r="V25" s="32" t="n"/>
-      <c r="W25" s="32" t="n"/>
+      <c r="J25" s="290" t="n"/>
+      <c r="K25" s="290" t="n"/>
+      <c r="L25" s="290" t="n"/>
+      <c r="M25" s="290" t="n"/>
+      <c r="N25" s="290" t="n"/>
+      <c r="O25" s="290" t="n"/>
+      <c r="P25" s="290" t="n"/>
+      <c r="Q25" s="290" t="n"/>
+      <c r="R25" s="290" t="n"/>
+      <c r="S25" s="290" t="n"/>
+      <c r="T25" s="290" t="n"/>
+      <c r="U25" s="290" t="n"/>
+      <c r="V25" s="290" t="n"/>
+      <c r="W25" s="290" t="n"/>
       <c r="X25" s="31" t="n"/>
       <c r="Y25" s="31" t="n"/>
-      <c r="Z25" s="32" t="n"/>
+      <c r="Z25" s="290" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="45" t="inlineStr">
@@ -15504,15 +15518,15 @@
           <t>Piso em granito ("revestimento conforme ambiente"). (PR721-728)</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="C26" s="290" t="n"/>
+      <c r="D26" s="290" t="n"/>
+      <c r="E26" s="290" t="n"/>
+      <c r="F26" s="290" t="inlineStr">
         <is>
           <t>Rodapé em granito semi-embutido, seguir alinhamento do piso (DET 22). (PR722/724/726/728)</t>
         </is>
       </c>
-      <c r="G26" s="32" t="n"/>
+      <c r="G26" s="290" t="n"/>
       <c r="H26" s="271" t="inlineStr">
         <is>
           <t>Parede pintada. (PR722/724/726/728)</t>
@@ -15523,27 +15537,27 @@
           <t>Forro em gesso com sanca: PD 259cm (Garden e Tipo), 267,5cm (Cobertura 1º nível), 272,5cm (Cobertura 2º nível); junta de dilatação em perfil metálico "Z" (DET 09); trechos em laje de concreto aparente. (PR721-728)</t>
         </is>
       </c>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="32" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="32" t="n"/>
-      <c r="T26" s="32" t="n"/>
-      <c r="U26" s="32" t="n"/>
-      <c r="V26" s="32" t="n"/>
-      <c r="W26" s="32" t="n"/>
+      <c r="J26" s="290" t="n"/>
+      <c r="K26" s="290" t="n"/>
+      <c r="L26" s="290" t="n"/>
+      <c r="M26" s="290" t="n"/>
+      <c r="N26" s="290" t="n"/>
+      <c r="O26" s="290" t="n"/>
+      <c r="P26" s="290" t="n"/>
+      <c r="Q26" s="290" t="n"/>
+      <c r="R26" s="290" t="n"/>
+      <c r="S26" s="290" t="n"/>
+      <c r="T26" s="290" t="n"/>
+      <c r="U26" s="290" t="n"/>
+      <c r="V26" s="290" t="n"/>
+      <c r="W26" s="290" t="n"/>
       <c r="X26" s="31" t="inlineStr">
         <is>
           <t>PCF1, PCF2, PE-A, P13, P23, PA05, PCF3, P15A, P15C (vão 90x240cm); material não especificado nas pranchas de circulação. (PR721-728)</t>
         </is>
       </c>
       <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="32" t="inlineStr">
+      <c r="Z26" s="290" t="inlineStr">
         <is>
           <t>Sirene de alarme e botoeira; hidrante nos halls conforme projeto PCI. (PR722-728)</t>
         </is>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -15,14 +15,18 @@
     <sheet name="PENDÊNCIAS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">OFFSET('CONTROLE DE REVISÕES '!$A$1,0,0,MAX(1,MAX(INDEX(('CONTROLE DE REVISÕES '!$A$1:$I$3000&amp;""&lt;&gt;"")*ROW('CONTROLE DE REVISÕES '!$A$1:$I$3000),0))),9)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'TÉRREO '!$1:$11,'TÉRREO '!$A:$A</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'TÉRREO '!$A$1:$AF$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">OFFSET('TÉRREO '!$A$1,0,0,MAX(11,MAX(INDEX(('TÉRREO '!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('TÉRREO '!$A$1:$AF$3000),0))),32)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2° PAVTO'!$1:$11,'2° PAVTO'!$A:$A</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2° PAVTO'!$A$1:$AF$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">OFFSET('2° PAVTO'!$A$1,0,0,MAX(11,MAX(INDEX(('2° PAVTO'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('2° PAVTO'!$A$1:$AF$3000),0))),32)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'PILOTIS'!$1:$11,'PILOTIS'!$A:$A</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'PILOTIS'!$A$1:$AF$63</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">OFFSET('PILOTIS'!$A$1,0,0,MAX(11,MAX(INDEX(('PILOTIS'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('PILOTIS'!$A$1:$AF$3000),0))),32)</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'APTO TIPO'!$1:$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">OFFSET('APTO TIPO'!$A$1,0,0,MAX(11,MAX(INDEX(('APTO TIPO'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('APTO TIPO'!$A$1:$AF$3000),0))),32)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'IMAGENS ESPECIFICAÇÕES '!$1:$11,'IMAGENS ESPECIFICAÇÕES '!$A:$A</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'IMAGENS ESPECIFICAÇÕES '!$A$1:$U$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">OFFSET('IMAGENS ESPECIFICAÇÕES '!$A$1,0,0,MAX(26,MAX(INDEX(('IMAGENS ESPECIFICAÇÕES '!$A$1:$U$3000&amp;""&lt;&gt;"")*ROW('IMAGENS ESPECIFICAÇÕES '!$A$1:$U$3000),0))),21)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">OFFSET('PENDÊNCIAS'!$A$1,0,0,MAX(1,MAX(INDEX(('PENDÊNCIAS'!$A$1:$E$3000&amp;""&lt;&gt;"")*ROW('PENDÊNCIAS'!$A$1:$E$3000),0))),5)</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -6196,6 +6200,7 @@
       <c r="H33" s="230" t="n"/>
       <c r="I33" s="217" t="n"/>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="E35" s="21" t="n"/>
     </row>
@@ -6252,7 +6257,7 @@
     <mergeCell ref="C11:I11"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="8" scale="71" fitToHeight="0"/>
+  <pageSetup orientation="portrait" paperSize="8" scale="71" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -6262,7 +6267,7 @@
   <sheetPr>
     <tabColor theme="0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AF55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
@@ -8893,7 +8898,7 @@
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" pageOrder="overThenDown"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" fitToWidth="1" pageOrder="overThenDown"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;L&amp;"Aptos Narrow,Negrito"&amp;18  Página &amp;P de &amp;N</oddFooter>
@@ -8915,7 +8920,7 @@
   <sheetPr>
     <tabColor theme="0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AF35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
@@ -10395,7 +10400,7 @@
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" pageOrder="overThenDown"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" fitToWidth="1" pageOrder="overThenDown"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;L&amp;"Aptos Narrow,Negrito"&amp;18  Página &amp;P de &amp;N</oddFooter>
@@ -10417,7 +10422,7 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AF64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
@@ -14054,7 +14059,7 @@
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" pageOrder="overThenDown"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" fitToWidth="1" pageOrder="overThenDown"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;L&amp;"Aptos Narrow,Negrito"&amp;18  Página &amp;P de &amp;N</oddFooter>
@@ -14076,7 +14081,7 @@
   <sheetPr>
     <tabColor theme="0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AF35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
@@ -15748,7 +15753,7 @@
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" pageOrder="overThenDown"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" fitToWidth="1" pageOrder="overThenDown"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -15758,7 +15763,7 @@
   <sheetPr>
     <tabColor theme="0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
@@ -16623,6 +16628,10 @@
     </row>
     <row r="27" ht="125.25" customHeight="1"/>
     <row r="28" ht="2.1" customHeight="1"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -16675,7 +16684,7 @@
     <mergeCell ref="G22:H22"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" pageOrder="overThenDown"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" fitToHeight="0" fitToWidth="1" pageOrder="overThenDown"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;L&amp;"Aptos Narrow,Negrito"&amp;18  Página &amp;P de &amp;N</oddFooter>
@@ -16721,6 +16730,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="265" t="inlineStr">
         <is>
@@ -17180,6 +17190,8 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="265" t="inlineStr">
         <is>
@@ -17410,6 +17422,8 @@
       <c r="D42" s="268" t="inlineStr"/>
       <c r="E42" s="268" t="inlineStr"/>
     </row>
+    <row r="43"/>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="265" t="inlineStr">
         <is>
@@ -17929,6 +17943,8 @@
       <c r="D75" s="268" t="inlineStr"/>
       <c r="E75" s="268" t="inlineStr"/>
     </row>
+    <row r="76"/>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="265" t="inlineStr">
         <is>
@@ -18106,6 +18122,7 @@
       </c>
       <c r="E86" s="268" t="inlineStr"/>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="279" t="inlineStr">
         <is>
@@ -23740,6 +23757,7 @@
         </is>
       </c>
     </row>
+    <row r="314"/>
     <row r="315">
       <c r="A315" s="279" t="inlineStr">
         <is>
@@ -23867,6 +23885,7 @@
         </is>
       </c>
     </row>
+    <row r="326"/>
     <row r="327">
       <c r="A327" s="279" t="inlineStr">
         <is>
@@ -28776,6 +28795,8 @@
         </is>
       </c>
     </row>
+    <row r="524"/>
+    <row r="525"/>
     <row r="526">
       <c r="B526" t="inlineStr">
         <is>
@@ -28860,6 +28881,7 @@
         </is>
       </c>
     </row>
+    <row r="533"/>
     <row r="534">
       <c r="A534" s="279" t="inlineStr">
         <is>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -11,8 +11,7 @@
     <sheet name="2° PAVTO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="PILOTIS" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="APTO TIPO" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="IMAGENS ESPECIFICAÇÕES " sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PENDÊNCIAS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PENDÊNCIAS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">OFFSET('CONTROLE DE REVISÕES '!$A$1,0,0,MAX(1,MAX(INDEX(('CONTROLE DE REVISÕES '!$A$1:$I$3000&amp;""&lt;&gt;"")*ROW('CONTROLE DE REVISÕES '!$A$1:$I$3000),0))),9)</definedName>
@@ -24,9 +23,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">OFFSET('PILOTIS'!$A$1,0,0,MAX(11,MAX(INDEX(('PILOTIS'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('PILOTIS'!$A$1:$AF$3000),0))),32)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'APTO TIPO'!$1:$11,'APTO TIPO'!$A:$A</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">OFFSET('APTO TIPO'!$A$1,0,0,MAX(11,MAX(INDEX(('APTO TIPO'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('APTO TIPO'!$A$1:$AF$3000),0))),32)</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'IMAGENS ESPECIFICAÇÕES '!$1:$11,'IMAGENS ESPECIFICAÇÕES '!$A:$A</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">OFFSET('IMAGENS ESPECIFICAÇÕES '!$A$1,0,0,MAX(26,MAX(INDEX(('IMAGENS ESPECIFICAÇÕES '!$A$1:$U$3000&amp;""&lt;&gt;"")*ROW('IMAGENS ESPECIFICAÇÕES '!$A$1:$U$3000),0))),21)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">OFFSET('PENDÊNCIAS'!$A$1,0,0,MAX(1,MAX(INDEX(('PENDÊNCIAS'!$A$1:$E$3000&amp;""&lt;&gt;"")*ROW('PENDÊNCIAS'!$A$1:$E$3000),0))),5)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">OFFSET('PENDÊNCIAS'!$A$1,0,0,MAX(1,MAX(INDEX(('PENDÊNCIAS'!$A$1:$E$3000&amp;""&lt;&gt;"")*ROW('PENDÊNCIAS'!$A$1:$E$3000),0))),5)</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -4607,805 +4604,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>394853</colOff>
-      <row>4</row>
-      <rowOff>72735</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1330036</colOff>
-      <row>5</row>
-      <rowOff>492183</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3366653" y="1749135"/>
-          <a:ext cx="935183" cy="914748"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>831275</colOff>
-      <row>0</row>
-      <rowOff>103909</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>2753592</colOff>
-      <row>3</row>
-      <rowOff>335785</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Imagem 6"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:srcRect b="16485"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="831275" y="103909"/>
-          <a:ext cx="1922317" cy="1470126"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>6</col>
-      <colOff>2247902</colOff>
-      <row>0</row>
-      <rowOff>100446</rowOff>
-    </from>
-    <to>
-      <col>7</col>
-      <colOff>1548246</colOff>
-      <row>3</row>
-      <rowOff>332322</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Imagem 7"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:srcRect b="16485"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="25650827" y="100446"/>
-          <a:ext cx="1913658" cy="1470126"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>19</col>
-      <colOff>1513612</colOff>
-      <row>0</row>
-      <rowOff>128154</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>1046019</colOff>
-      <row>3</row>
-      <rowOff>360030</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Imagem 8"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:srcRect b="16485"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="49910137" y="128154"/>
-          <a:ext cx="1913658" cy="1470126"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>370607</colOff>
-      <row>4</row>
-      <rowOff>117762</rowOff>
-    </from>
-    <ext cx="935183" cy="927787"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Imagem 4"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm flipH="1">
-          <a:off x="33212807" y="1794162"/>
-          <a:ext cx="935183" cy="927787"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>76200</colOff>
-      <row>12</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="981075" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>76200</colOff>
-      <row>12</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1562100" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1695450</colOff>
-      <row>12</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1428750" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3181350</colOff>
-      <row>12</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1438275" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>76200</colOff>
-      <row>12</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1428750" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>1562100</colOff>
-      <row>12</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1152525" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>76200</colOff>
-      <row>13</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1495425" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1628775</colOff>
-      <row>13</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1428750" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="981075" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1628775" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="981075" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1809750" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="942975" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>12</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1219200" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>12</col>
-      <colOff>1352550</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1190625" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>12</col>
-      <colOff>2600325</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1428750" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>76200</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1476375" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>1609725</colOff>
-      <row>14</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="2419350" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>76200</colOff>
-      <row>15</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1428750" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>76200</colOff>
-      <row>15</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1419225" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>1552575</colOff>
-      <row>15</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1419225" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -6043,7 +5241,7 @@
       <c r="B19" s="217" t="n"/>
       <c r="C19" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMAGENS ESPECIFICAÇÕES </t>
+          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
         </is>
       </c>
       <c r="D19" s="230" t="n"/>
@@ -6062,7 +5260,7 @@
       <c r="B20" s="217" t="n"/>
       <c r="C20" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMAGENS ESPECIFICAÇÕES </t>
+          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
         </is>
       </c>
       <c r="D20" s="230" t="n"/>
@@ -6081,7 +5279,7 @@
       <c r="B21" s="217" t="n"/>
       <c r="C21" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMAGENS ESPECIFICAÇÕES </t>
+          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
         </is>
       </c>
       <c r="D21" s="230" t="n"/>
@@ -6100,7 +5298,7 @@
       <c r="B22" s="221" t="n"/>
       <c r="C22" s="111" t="inlineStr">
         <is>
-          <t>IMAGENS ESPECIFICAÇÕES</t>
+          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
         </is>
       </c>
       <c r="D22" s="231" t="n"/>
@@ -6246,7 +5444,7 @@
       </c>
       <c r="E28" s="237" t="inlineStr">
         <is>
-          <t>Imagens das fichas TERMAS e VESTIÁRIOS - TERMAS da tabela v00 (págs. 7 e 8).</t>
+          <t>Imagens das fichas TERMAS e VESTIÁRIOS - TERMAS da tabela de acabamentos v00. Em 01/10/2026 a aba de imagens foi substituída pelo link "► VER IMAGEM (clique)" nas próprias células da grade.</t>
         </is>
       </c>
       <c r="F28" s="230" t="n"/>
@@ -12844,7 +12042,7 @@
       <c r="Y40" s="307" t="n"/>
       <c r="Z40" s="300" t="n"/>
     </row>
-    <row r="41" ht="224" customHeight="1">
+    <row r="41" ht="254" customHeight="1">
       <c r="A41" s="298" t="inlineStr">
         <is>
           <t>ESPAÇO TERMAS</t>
@@ -12852,7 +12050,8 @@
       </c>
       <c r="B41" s="320" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C41" s="300" t="n"/>
@@ -12868,7 +12067,8 @@
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-PA49 - Pilar em concreto rebocados e regularizados revestidos em mosaico de pastilhas, módulos de 32x259cm com pastilhas de 20x20mm, NARCISO Shading BlendDesenho e paginação conforme detalhamento. Argamassa e rejunte recomendados: Filgel plus 1101 bianco alabastro. Ref.:Bisazza. Amostra a ser aprovada pela GPA&amp;A</t>
+PA49 - Pilar em concreto rebocados e regularizados revestidos em mosaico de pastilhas, módulos de 32x259cm com pastilhas de 20x20mm, NARCISO Shading BlendDesenho e paginação conforme detalhamento. Argamassa e rejunte recomendados: Filgel plus 1101 bianco alabastro. Ref.:Bisazza. Amostra a ser aprovada pela GPA&amp;A
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I41" s="316" t="inlineStr">
@@ -12898,7 +12098,8 @@
       </c>
       <c r="U41" s="317" t="inlineStr">
         <is>
-          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V41" s="299" t="inlineStr">
@@ -13711,7 +12912,7 @@
       <c r="Y54" s="307" t="n"/>
       <c r="Z54" s="300" t="n"/>
     </row>
-    <row r="55" ht="194" customHeight="1">
+    <row r="55" ht="224" customHeight="1">
       <c r="A55" s="298" t="inlineStr">
         <is>
           <t>VESTIÁRIO FEM./MASC. - TERMAS</t>
@@ -13719,7 +12920,8 @@
       </c>
       <c r="B55" s="320" t="inlineStr">
         <is>
-          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+          <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C55" s="300" t="n"/>
@@ -13735,7 +12937,8 @@
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A
-PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I55" s="316" t="inlineStr">
@@ -13745,36 +12948,42 @@
       </c>
       <c r="J55" s="320" t="inlineStr">
         <is>
-          <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="K55" s="317" t="inlineStr">
         <is>
-          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="L55" s="320" t="inlineStr">
         <is>
-          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
+          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M55" s="308" t="n"/>
       <c r="N55" s="308" t="n"/>
       <c r="O55" s="320" t="inlineStr">
         <is>
-          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
+          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P55" s="316" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q55" s="300" t="n"/>
       <c r="R55" s="307" t="n"/>
       <c r="S55" s="320" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="T55" s="299" t="inlineStr">
@@ -13785,7 +12994,8 @@
       </c>
       <c r="U55" s="317" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V55" s="299" t="inlineStr">
@@ -14249,6 +13459,20 @@
     <mergeCell ref="V12:Z12"/>
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" tooltip="Abrir imagem: P10 - Piso elevado em mármore branco selecionado" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" tooltip="Abrir imagem: PA49 - Mosaico Bisazza (painel e pilar)" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" tooltip="Abrir imagem: D54 - Chuveiro de embutir no teto Raindream, Roca" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" tooltip="Abrir imagem: P10 - Piso elevado em mármore branco selecionado" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" tooltip="Abrir imagem: PA47 - Pintura com tinta mineral, cor 930, Terracor" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" tooltip="Abrir imagem: D73 - Bancada em mármore branco selecionado" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" tooltip="Abrir imagem: D38 - Espelho liso incolor 4mm" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" tooltip="Abrir imagem: D72 - Cuba de semi-encaixe slim, Deca" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" tooltip="Abrir imagem: D69 - Torneira com sensor Decalux, Deca" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" tooltip="Abrir imagem: D22 - Bacia Carrara / Panache e assento" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" tooltip="Abrir imagem: D33 - Monocomando para chuveiro Mix&amp;Match, Docol" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U55" tooltip="Abrir imagem: D70 - Chuveiro 200 de parede Docol Eden" r:id="rId12"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8" scale="38" pageOrder="overThenDown"/>
@@ -14264,7 +13488,7 @@
     <brk id="11" min="0" max="16383" man="1"/>
     <brk id="21" min="0" max="16383" man="1"/>
   </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -15986,945 +15210,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:AA33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
-  <cols>
-    <col width="44.7109375" customWidth="1" style="14" min="1" max="1"/>
-    <col width="70.5703125" customWidth="1" style="3" min="2" max="6"/>
-    <col width="39.42578125" customWidth="1" style="3" min="7" max="8"/>
-    <col width="35.7109375" customWidth="1" style="3" min="9" max="14"/>
-    <col width="40.28515625" customWidth="1" style="3" min="15" max="15"/>
-    <col width="42" customWidth="1" style="3" min="16" max="16"/>
-    <col width="35.7109375" customWidth="1" style="3" min="17" max="17"/>
-    <col width="42.5703125" customWidth="1" style="3" min="18" max="18"/>
-    <col width="35.7109375" customWidth="1" style="3" min="19" max="27"/>
-    <col width="9.140625" customWidth="1" style="3" min="28" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34.5" customHeight="1">
-      <c r="A1" s="153" t="n"/>
-      <c r="B1" s="137" t="inlineStr">
-        <is>
-          <t>GRADE DE ESPECIFICAÇÕES PARA ÁREA COMUM
-EDIFÍCIO JARDIM</t>
-        </is>
-      </c>
-      <c r="C1" s="209" t="n"/>
-      <c r="D1" s="209" t="n"/>
-      <c r="E1" s="209" t="n"/>
-      <c r="F1" s="208" t="n"/>
-      <c r="G1" s="113" t="n"/>
-      <c r="H1" s="208" t="n"/>
-      <c r="I1" s="248">
-        <f>B1</f>
-        <v/>
-      </c>
-      <c r="J1" s="209" t="n"/>
-      <c r="K1" s="209" t="n"/>
-      <c r="L1" s="209" t="n"/>
-      <c r="M1" s="209" t="n"/>
-      <c r="N1" s="209" t="n"/>
-      <c r="O1" s="209" t="n"/>
-      <c r="P1" s="209" t="n"/>
-      <c r="Q1" s="209" t="n"/>
-      <c r="R1" s="209" t="n"/>
-      <c r="S1" s="249" t="n"/>
-      <c r="T1" s="113" t="n"/>
-      <c r="U1" s="208" t="n"/>
-      <c r="V1" s="55" t="n"/>
-      <c r="W1" s="55" t="n"/>
-      <c r="X1" s="55" t="n"/>
-      <c r="Y1" s="55" t="n"/>
-      <c r="Z1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="238" t="n"/>
-      <c r="B2" s="210" t="n"/>
-      <c r="F2" s="211" t="n"/>
-      <c r="G2" s="210" t="n"/>
-      <c r="H2" s="211" t="n"/>
-      <c r="I2" s="210" t="n"/>
-      <c r="S2" s="250" t="n"/>
-      <c r="T2" s="210" t="n"/>
-      <c r="U2" s="211" t="n"/>
-      <c r="V2" s="55" t="n"/>
-      <c r="W2" s="55" t="n"/>
-      <c r="X2" s="55" t="n"/>
-      <c r="Y2" s="55" t="n"/>
-    </row>
-    <row r="3" ht="34.5" customHeight="1">
-      <c r="A3" s="238" t="n"/>
-      <c r="B3" s="210" t="n"/>
-      <c r="F3" s="211" t="n"/>
-      <c r="G3" s="210" t="n"/>
-      <c r="H3" s="211" t="n"/>
-      <c r="I3" s="210" t="n"/>
-      <c r="S3" s="250" t="n"/>
-      <c r="T3" s="210" t="n"/>
-      <c r="U3" s="211" t="n"/>
-      <c r="V3" s="55" t="n"/>
-      <c r="W3" s="55" t="n"/>
-      <c r="X3" s="55" t="n"/>
-      <c r="Y3" s="55" t="n"/>
-    </row>
-    <row r="4" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A4" s="239" t="n"/>
-      <c r="B4" s="213" t="n"/>
-      <c r="C4" s="216" t="n"/>
-      <c r="D4" s="216" t="n"/>
-      <c r="E4" s="216" t="n"/>
-      <c r="F4" s="214" t="n"/>
-      <c r="G4" s="213" t="n"/>
-      <c r="H4" s="214" t="n"/>
-      <c r="I4" s="251" t="n"/>
-      <c r="J4" s="223" t="n"/>
-      <c r="K4" s="223" t="n"/>
-      <c r="L4" s="223" t="n"/>
-      <c r="M4" s="223" t="n"/>
-      <c r="N4" s="223" t="n"/>
-      <c r="O4" s="223" t="n"/>
-      <c r="P4" s="223" t="n"/>
-      <c r="Q4" s="223" t="n"/>
-      <c r="R4" s="223" t="n"/>
-      <c r="S4" s="252" t="n"/>
-      <c r="T4" s="213" t="n"/>
-      <c r="U4" s="214" t="n"/>
-      <c r="V4" s="55" t="n"/>
-      <c r="W4" s="55" t="n"/>
-      <c r="X4" s="55" t="n"/>
-      <c r="Y4" s="55" t="n"/>
-    </row>
-    <row r="5" ht="39.95" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="127" t="inlineStr">
-        <is>
-          <t>PADRÃO DE FORMATAÇÃO: ITEM, LINHA, MARCA, TAMANHO, COR E/OU ACABAMENTOS. CÓDIGO. COR DE REJUNTE.</t>
-        </is>
-      </c>
-      <c r="C5" s="209" t="n"/>
-      <c r="D5" s="209" t="n"/>
-      <c r="E5" s="209" t="n"/>
-      <c r="F5" s="208" t="n"/>
-      <c r="G5" s="27" t="inlineStr">
-        <is>
-          <t>XXXXXXX</t>
-        </is>
-      </c>
-      <c r="H5" s="229" t="n"/>
-      <c r="I5" s="253" t="inlineStr">
-        <is>
-          <t>*ATENÇÃO: PARA TODOS OS REJUNTES, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO
-COM PROJETOS EXECUTIVOS DE ACORDO COM ALTURA DO CONTRAPISO</t>
-        </is>
-      </c>
-      <c r="S5" s="250" t="n"/>
-      <c r="T5" s="119" t="inlineStr">
-        <is>
-          <t>XXXXXX</t>
-        </is>
-      </c>
-      <c r="U5" s="240" t="n"/>
-      <c r="V5" s="56" t="n"/>
-      <c r="W5" s="56" t="n"/>
-      <c r="X5" s="56" t="n"/>
-      <c r="Y5" s="56" t="n"/>
-      <c r="Z5" s="198" t="n"/>
-    </row>
-    <row r="6" ht="43.5" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A6" s="52" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="B6" s="213" t="n"/>
-      <c r="C6" s="216" t="n"/>
-      <c r="D6" s="216" t="n"/>
-      <c r="E6" s="216" t="n"/>
-      <c r="F6" s="214" t="n"/>
-      <c r="G6" s="52" t="inlineStr">
-        <is>
-          <t>RESPONSÁVEL</t>
-        </is>
-      </c>
-      <c r="H6" s="226" t="n"/>
-      <c r="I6" s="210" t="n"/>
-      <c r="S6" s="250" t="n"/>
-      <c r="T6" s="201" t="inlineStr">
-        <is>
-          <t>RESPONSÁVEL</t>
-        </is>
-      </c>
-      <c r="U6" s="221" t="n"/>
-      <c r="V6" s="56" t="n"/>
-      <c r="W6" s="56" t="n"/>
-      <c r="X6" s="56" t="n"/>
-      <c r="Y6" s="56" t="n"/>
-      <c r="Z6" s="203" t="n"/>
-    </row>
-    <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>REV. R00</t>
-        </is>
-      </c>
-      <c r="B7" s="186" t="inlineStr">
-        <is>
-          <t>*ATENÇÃO: PARA TODOS OS REJUNTES E TEXTURAS, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO ARQUITETURA DE ACORDO COM ALTURA DO CONTRAPISO. A DEFINIÇÃO DA ALTURA DE RODABANCAS E TESTEIRAS DEVEM SER DEFINIDAS CASO A CASO CONFORME IMAGENS E/OU ELEMENTOS DO PROJETO, COMO PEITORIL E PAGINAÇÃO DA PAREDE. QUANDO O REVESTIMENTO DA PAREDE NÃO FOR CERÂMICO, CONSIDERAR UMA ALTURA MAIOR DE RODABANCA. AS ESPECIFICAÇÕES PODERAM SER ALTERADAS CONFORME DISPONIBILIDADE DE MERCADO, VALIDAR JUNTO A ARQUITETURA CASO NO MOMENTO DA COMPRA O ITEM TENHA SAÍDO DE LINHA.</t>
-        </is>
-      </c>
-      <c r="C7" s="209" t="n"/>
-      <c r="D7" s="209" t="n"/>
-      <c r="E7" s="209" t="n"/>
-      <c r="F7" s="208" t="n"/>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INFO. ANTERIOR </t>
-        </is>
-      </c>
-      <c r="H7" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INFO. REVISADA </t>
-        </is>
-      </c>
-      <c r="I7" s="254" t="inlineStr">
-        <is>
-          <t>*ATENÇÃO: PARA TODOS OS REJUNTES E TEXTURAS, FAZER TESTES E APROVAR COM ARQUITETURA. PARA TODOS OS RALOS, APROVAR MODELO ARQUITETURA DE ACORDO COM ALTURA DO CONTRAPISO. A DEFINIÇÃO DA ALTURA DE RODABANCAS E TESTEIRAS DEVEM SER DEFINIDAS CASO A CASO CONFORME IMAGENS E/OU ELEMENTOS DO PROJETO, COMO PEITORIL E PAGINAÇÃO DA PAREDE. QUANDO O REVESTIMENTO DA PAREDE NÃO FOR CERÂMICO, CONSIDERAR UMA ALTURA MAIOR DE RODABANCA. AS ESPECIFICAÇÕES PODERAM SER ALTERADAS CONFORME DISPONIBILIDADE DE MERCADO, VALIDAR JUNTO A ARQUITETURA CASO NO MOMENTO DA COMPRA O ITEM TENHA SAÍDO DE LINHA.</t>
-        </is>
-      </c>
-      <c r="J7" s="209" t="n"/>
-      <c r="K7" s="209" t="n"/>
-      <c r="L7" s="209" t="n"/>
-      <c r="M7" s="209" t="n"/>
-      <c r="N7" s="209" t="n"/>
-      <c r="O7" s="209" t="n"/>
-      <c r="P7" s="209" t="n"/>
-      <c r="Q7" s="209" t="n"/>
-      <c r="R7" s="209" t="n"/>
-      <c r="S7" s="249" t="n"/>
-      <c r="T7" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INFO. ANTERIOR </t>
-        </is>
-      </c>
-      <c r="U7" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INFO. REVISADA </t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="57" t="n"/>
-      <c r="AA7" s="58" t="n"/>
-    </row>
-    <row r="8" ht="69.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A8" s="52" t="inlineStr">
-        <is>
-          <t>REVISÃO</t>
-        </is>
-      </c>
-      <c r="B8" s="213" t="n"/>
-      <c r="C8" s="216" t="n"/>
-      <c r="D8" s="216" t="n"/>
-      <c r="E8" s="216" t="n"/>
-      <c r="F8" s="214" t="n"/>
-      <c r="G8" s="255" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="H8" s="226" t="n"/>
-      <c r="I8" s="251" t="n"/>
-      <c r="J8" s="223" t="n"/>
-      <c r="K8" s="223" t="n"/>
-      <c r="L8" s="223" t="n"/>
-      <c r="M8" s="223" t="n"/>
-      <c r="N8" s="223" t="n"/>
-      <c r="O8" s="223" t="n"/>
-      <c r="P8" s="223" t="n"/>
-      <c r="Q8" s="223" t="n"/>
-      <c r="R8" s="223" t="n"/>
-      <c r="S8" s="252" t="n"/>
-      <c r="T8" s="121" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="U8" s="221" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="193" t="n"/>
-    </row>
-    <row r="9" ht="14.1" customFormat="1" customHeight="1" s="6">
-      <c r="A9" s="5" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="193" t="n"/>
-      <c r="H9" s="193" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="10" t="n"/>
-      <c r="O9" s="10" t="n"/>
-      <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="10" t="n"/>
-      <c r="R9" s="10" t="n"/>
-      <c r="S9" s="10" t="n"/>
-      <c r="T9" s="10" t="n"/>
-      <c r="U9" s="10" t="n"/>
-      <c r="V9" s="11" t="n"/>
-      <c r="W9" s="10" t="n"/>
-      <c r="X9" s="10" t="n"/>
-      <c r="Y9" s="10" t="n"/>
-      <c r="Z9" s="10" t="n"/>
-      <c r="AA9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="152" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="C10" s="216" t="n"/>
-      <c r="D10" s="216" t="n"/>
-      <c r="E10" s="216" t="n"/>
-      <c r="F10" s="216" t="n"/>
-      <c r="G10" s="216" t="n"/>
-      <c r="H10" s="214" t="n"/>
-      <c r="I10" s="152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOUÇAS E METAIS </t>
-        </is>
-      </c>
-      <c r="J10" s="216" t="n"/>
-      <c r="K10" s="216" t="n"/>
-      <c r="L10" s="216" t="n"/>
-      <c r="M10" s="216" t="n"/>
-      <c r="N10" s="216" t="n"/>
-      <c r="O10" s="216" t="n"/>
-      <c r="P10" s="216" t="n"/>
-      <c r="Q10" s="216" t="n"/>
-      <c r="R10" s="214" t="n"/>
-      <c r="S10" s="152" t="inlineStr">
-        <is>
-          <t>COMPLEMENTARES</t>
-        </is>
-      </c>
-      <c r="T10" s="216" t="n"/>
-      <c r="U10" s="214" t="n"/>
-    </row>
-    <row r="11" ht="171.75" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A11" s="46" t="n"/>
-      <c r="B11" s="46" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C11" s="46" t="inlineStr">
-        <is>
-          <t>FILETE</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="inlineStr">
-        <is>
-          <t>PEITORIL</t>
-        </is>
-      </c>
-      <c r="E11" s="46" t="inlineStr">
-        <is>
-          <t>RODAPÉ</t>
-        </is>
-      </c>
-      <c r="F11" s="46" t="inlineStr">
-        <is>
-          <t>PAREDE</t>
-        </is>
-      </c>
-      <c r="G11" s="256" t="inlineStr">
-        <is>
-          <t>BANCADA</t>
-        </is>
-      </c>
-      <c r="H11" s="221" t="n"/>
-      <c r="I11" s="46" t="inlineStr">
-        <is>
-          <t>LOUÇAS, CUBAS E TANQUES</t>
-        </is>
-      </c>
-      <c r="J11" s="46" t="inlineStr">
-        <is>
-          <t>VÁLVULAS DE CUBAS E TANQUES</t>
-        </is>
-      </c>
-      <c r="K11" s="46" t="inlineStr">
-        <is>
-          <t>SIFÕES</t>
-        </is>
-      </c>
-      <c r="L11" s="46" t="inlineStr">
-        <is>
-          <t>TORNEIRAS</t>
-        </is>
-      </c>
-      <c r="M11" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> BACIAS SANITÁRIAS</t>
-        </is>
-      </c>
-      <c r="N11" s="46" t="inlineStr">
-        <is>
-          <t>DUCHAS HIGIÊNICAS</t>
-        </is>
-      </c>
-      <c r="O11" s="46" t="inlineStr">
-        <is>
-          <t>ACABAMENTOS DE REGISTROS GERAL</t>
-        </is>
-      </c>
-      <c r="P11" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACIONAMENTO DE CHUVEIRO </t>
-        </is>
-      </c>
-      <c r="Q11" s="46" t="inlineStr">
-        <is>
-          <t>RALOS</t>
-        </is>
-      </c>
-      <c r="R11" s="46" t="inlineStr">
-        <is>
-          <t>ACABAMENTOS ELÉTRICOS</t>
-        </is>
-      </c>
-      <c r="S11" s="46" t="inlineStr">
-        <is>
-          <t>MAÇANETAS</t>
-        </is>
-      </c>
-      <c r="T11" s="46" t="inlineStr">
-        <is>
-          <t>PORTAS</t>
-        </is>
-      </c>
-      <c r="U11" s="54" t="inlineStr">
-        <is>
-          <t>PORTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customFormat="1" customHeight="1" s="13" thickBot="1">
-      <c r="A12" s="51" t="n"/>
-      <c r="B12" s="124" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="C12" s="241" t="n"/>
-      <c r="D12" s="241" t="n"/>
-      <c r="E12" s="241" t="n"/>
-      <c r="F12" s="241" t="n"/>
-      <c r="G12" s="241" t="n"/>
-      <c r="H12" s="242" t="n"/>
-      <c r="I12" s="123" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="J12" s="241" t="n"/>
-      <c r="K12" s="241" t="n"/>
-      <c r="L12" s="241" t="n"/>
-      <c r="M12" s="241" t="n"/>
-      <c r="N12" s="241" t="n"/>
-      <c r="O12" s="241" t="n"/>
-      <c r="P12" s="241" t="n"/>
-      <c r="Q12" s="241" t="n"/>
-      <c r="R12" s="241" t="n"/>
-      <c r="S12" s="241" t="n"/>
-      <c r="T12" s="241" t="n"/>
-      <c r="U12" s="242" t="n"/>
-    </row>
-    <row r="13" ht="203.25" customHeight="1">
-      <c r="A13" s="156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMAGENS CONFORME ESPECIFICAÇÕES </t>
-        </is>
-      </c>
-      <c r="B13" s="257" t="inlineStr">
-        <is>
-          <t>ESPAÇO TERMAS
-P10 - Piso elevado em mármore branco selecionado</t>
-        </is>
-      </c>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="258" t="inlineStr">
-        <is>
-          <t>ESPAÇO TERMAS
-PA49 - Mosaico Bisazza (painel): New Sterlizia / Narciso</t>
-        </is>
-      </c>
-      <c r="G13" s="259" t="n"/>
-      <c r="H13" s="240" t="n"/>
-      <c r="I13" s="49" t="n"/>
-      <c r="J13" s="49" t="n"/>
-      <c r="K13" s="49" t="n"/>
-      <c r="L13" s="49" t="n"/>
-      <c r="M13" s="49" t="n"/>
-      <c r="N13" s="49" t="n"/>
-      <c r="O13" s="49" t="n"/>
-      <c r="P13" s="258" t="inlineStr">
-        <is>
-          <t>ESPAÇO TERMAS
-D54 - Chuveiro de embutir no teto Raindream, Roca</t>
-        </is>
-      </c>
-      <c r="Q13" s="49" t="n"/>
-      <c r="R13" s="49" t="n"/>
-      <c r="S13" s="49" t="n"/>
-      <c r="T13" s="49" t="n"/>
-      <c r="U13" s="48" t="n"/>
-    </row>
-    <row r="14" ht="203.25" customHeight="1">
-      <c r="A14" s="260" t="n"/>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="261" t="inlineStr">
-        <is>
-          <t>ESPAÇO TERMAS
-PA49 - Mosaico Bisazza (pilar): Narciso</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="n"/>
-      <c r="H14" s="217" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="32" t="n"/>
-      <c r="P14" s="32" t="n"/>
-      <c r="Q14" s="32" t="n"/>
-      <c r="R14" s="32" t="n"/>
-      <c r="S14" s="32" t="n"/>
-      <c r="T14" s="32" t="n"/>
-      <c r="U14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="203.25" customHeight="1">
-      <c r="A15" s="260" t="n"/>
-      <c r="B15" s="262" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-P10 - Piso elevado em mármore branco selecionado</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D38 - Espelho liso incolor 4mm</t>
-        </is>
-      </c>
-      <c r="G15" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D73 - Bancada em mármore branco selecionado</t>
-        </is>
-      </c>
-      <c r="H15" s="217" t="n"/>
-      <c r="I15" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D72 - Cuba de semi-encaixe slim, Deca</t>
-        </is>
-      </c>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D69 - Torneira com sensor Decalux, Deca</t>
-        </is>
-      </c>
-      <c r="M15" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D22 - Bacia Carrara (Deca) / Panache (Kohler) e assento</t>
-        </is>
-      </c>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="32" t="n"/>
-      <c r="P15" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D33 - Monocomando para chuveiro Mix&amp;Match, Docol</t>
-        </is>
-      </c>
-      <c r="Q15" s="32" t="n"/>
-      <c r="R15" s="32" t="n"/>
-      <c r="S15" s="32" t="n"/>
-      <c r="T15" s="32" t="n"/>
-      <c r="U15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="203.25" customHeight="1">
-      <c r="A16" s="260" t="n"/>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-PA47 - Pintura com tinta mineral, cor 930, Terracor</t>
-        </is>
-      </c>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="217" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="261" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEM./MASC. - TERMAS
-D70 - Chuveiro 200 de parede Docol Eden</t>
-        </is>
-      </c>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="32" t="n"/>
-      <c r="S16" s="32" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="203.25" customHeight="1">
-      <c r="A17" s="260" t="n"/>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="33" t="n"/>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="217" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
-      <c r="O17" s="32" t="n"/>
-      <c r="P17" s="32" t="n"/>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="32" t="n"/>
-      <c r="S17" s="32" t="n"/>
-      <c r="T17" s="32" t="n"/>
-      <c r="U17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="203.25" customHeight="1">
-      <c r="A18" s="260" t="n"/>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="33" t="n"/>
-      <c r="G18" s="32" t="n"/>
-      <c r="H18" s="217" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="32" t="n"/>
-      <c r="O18" s="32" t="n"/>
-      <c r="P18" s="32" t="n"/>
-      <c r="Q18" s="32" t="n"/>
-      <c r="R18" s="32" t="n"/>
-      <c r="S18" s="32" t="n"/>
-      <c r="T18" s="32" t="n"/>
-      <c r="U18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="203.25" customHeight="1" thickBot="1">
-      <c r="A19" s="260" t="n"/>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="33" t="n"/>
-      <c r="G19" s="32" t="n"/>
-      <c r="H19" s="217" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="32" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="32" t="n"/>
-      <c r="U19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="203.25" customHeight="1">
-      <c r="A20" s="156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMAGENS CONFORME ESPECIFICAÇÕES </t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="F20" s="33" t="n"/>
-      <c r="G20" s="32" t="n"/>
-      <c r="H20" s="217" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
-      <c r="O20" s="32" t="n"/>
-      <c r="P20" s="32" t="n"/>
-      <c r="Q20" s="32" t="n"/>
-      <c r="R20" s="32" t="n"/>
-      <c r="S20" s="32" t="n"/>
-      <c r="T20" s="32" t="n"/>
-      <c r="U20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="203.25" customHeight="1">
-      <c r="A21" s="260" t="n"/>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="217" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="n"/>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="203.25" customHeight="1">
-      <c r="A22" s="260" t="n"/>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="34" t="n"/>
-      <c r="G22" s="32" t="n"/>
-      <c r="H22" s="217" t="n"/>
-      <c r="I22" s="32" t="n"/>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="32" t="n"/>
-      <c r="M22" s="32" t="n"/>
-      <c r="N22" s="32" t="n"/>
-      <c r="O22" s="32" t="n"/>
-      <c r="P22" s="32" t="n"/>
-      <c r="Q22" s="32" t="n"/>
-      <c r="R22" s="32" t="n"/>
-      <c r="S22" s="31" t="n"/>
-      <c r="T22" s="34" t="n"/>
-      <c r="U22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="203.25" customHeight="1">
-      <c r="A23" s="260" t="n"/>
-      <c r="B23" s="34" t="n"/>
-      <c r="C23" s="34" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="34" t="n"/>
-      <c r="F23" s="34" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="217" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="35" t="n"/>
-      <c r="U23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="203.25" customHeight="1">
-      <c r="A24" s="260" t="n"/>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="217" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="37" t="n"/>
-      <c r="K24" s="37" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="35" t="n"/>
-      <c r="U24" s="35" t="n"/>
-    </row>
-    <row r="25" ht="203.25" customHeight="1">
-      <c r="A25" s="260" t="n"/>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35" t="n"/>
-      <c r="D25" s="37" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="32" t="n"/>
-      <c r="H25" s="217" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="32" t="n"/>
-      <c r="M25" s="32" t="n"/>
-      <c r="N25" s="32" t="n"/>
-      <c r="O25" s="32" t="n"/>
-      <c r="P25" s="32" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-      <c r="R25" s="32" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="35" t="n"/>
-      <c r="U25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="203.25" customHeight="1">
-      <c r="A26" s="260" t="n"/>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="37" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="217" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="35" t="n"/>
-      <c r="K26" s="35" t="n"/>
-      <c r="L26" s="35" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="31" t="n"/>
-      <c r="T26" s="32" t="n"/>
-      <c r="U26" s="32" t="n"/>
-    </row>
-    <row r="27" ht="125.25" customHeight="1"/>
-    <row r="28" ht="2.1" customHeight="1"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33">
-      <c r="P33" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="T1:U4"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:F4"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I5:S6"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="Z1:AA4"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B5:F6"/>
-    <mergeCell ref="G1:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I1:S4"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="B7:F8"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I12:U12"/>
-    <mergeCell ref="I7:S8"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="G22:H22"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" pageOrder="overThenDown"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"Aptos Narrow,Negrito"&amp;18  Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="8" min="0" max="25" man="1"/>
-  </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="68">
+  <fonts count="70">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -442,8 +442,20 @@
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="00243F2E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -500,6 +512,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00243F2E"/>
       </patternFill>
     </fill>
   </fills>
@@ -1415,7 +1437,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="324">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2285,6 +2307,12 @@
     </xf>
     <xf numFmtId="0" fontId="67" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3543,7 +3571,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip cstate="print" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3584,7 +3612,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip cstate="print" r:embed="rId23"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3627,7 +3655,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId12"/>
+        <a:blip cstate="print" r:embed="rId24"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3670,7 +3698,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId13"/>
+        <a:blip cstate="print" r:embed="rId25"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3713,7 +3741,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId14"/>
+        <a:blip cstate="print" r:embed="rId26"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -4052,6 +4080,342 @@
         <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>676275</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3486150" cy="2743200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>962025</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2914650" cy="2743200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>676275</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3486150" cy="2743200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>923925</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3000375" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>923925</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3000375" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>923925</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3000375" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>923925</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3000375" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>923925</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3000375" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>923925</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3000375" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>38100</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="4762500" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>40</col>
+      <colOff>38100</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="4762500" cy="2028825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>41</col>
+      <colOff>371475</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="4105275" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5241,7 +5605,7 @@
       <c r="B19" s="217" t="n"/>
       <c r="C19" s="61" t="inlineStr">
         <is>
-          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
+          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
         </is>
       </c>
       <c r="D19" s="230" t="n"/>
@@ -5260,7 +5624,7 @@
       <c r="B20" s="217" t="n"/>
       <c r="C20" s="61" t="inlineStr">
         <is>
-          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
+          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
         </is>
       </c>
       <c r="D20" s="230" t="n"/>
@@ -5279,7 +5643,7 @@
       <c r="B21" s="217" t="n"/>
       <c r="C21" s="61" t="inlineStr">
         <is>
-          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
+          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
         </is>
       </c>
       <c r="D21" s="230" t="n"/>
@@ -5298,7 +5662,7 @@
       <c r="B22" s="221" t="n"/>
       <c r="C22" s="111" t="inlineStr">
         <is>
-          <t>IMAGENS: LINK "VER IMAGEM" NAS CÉLULAS DA GRADE</t>
+          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
         </is>
       </c>
       <c r="D22" s="231" t="n"/>
@@ -5444,7 +5808,7 @@
       </c>
       <c r="E28" s="237" t="inlineStr">
         <is>
-          <t>Imagens das fichas TERMAS e VESTIÁRIOS - TERMAS da tabela de acabamentos v00. Em 01/10/2026 a aba de imagens foi substituída pelo link "► VER IMAGEM (clique)" nas próprias células da grade.</t>
+          <t>Imagens das fichas TERMAS e VESTIÁRIOS - TERMAS da tabela de acabamentos v00. Em 02/10/2026 passaram para a própria aba PILOTIS, à direita da grade (a partir da coluna AH); o link "► VER IMAGEM (clique)" na célula leva à foto e "◄ VOLTAR" retorna.</t>
         </is>
       </c>
       <c r="F28" s="230" t="n"/>
@@ -9799,7 +10163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF64"/>
+  <dimension ref="A1:AQ64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9834,6 +10198,18 @@
     <col width="31" customWidth="1" min="30" max="30"/>
     <col width="31" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="72" customWidth="1" min="34" max="34"/>
+    <col width="72" customWidth="1" min="35" max="35"/>
+    <col width="72" customWidth="1" min="36" max="36"/>
+    <col width="72" customWidth="1" min="37" max="37"/>
+    <col width="72" customWidth="1" min="38" max="38"/>
+    <col width="72" customWidth="1" min="39" max="39"/>
+    <col width="72" customWidth="1" min="40" max="40"/>
+    <col width="72" customWidth="1" min="41" max="41"/>
+    <col width="72" customWidth="1" min="42" max="42"/>
+    <col width="72" customWidth="1" min="43" max="43"/>
+    <col width="72" customWidth="1" min="44" max="44"/>
+    <col width="72" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
@@ -10398,6 +10774,11 @@
 COMPLEMENTARES</t>
         </is>
       </c>
+      <c r="AH11" s="322" t="inlineStr">
+        <is>
+          <t>IMAGENS DAS ESPECIFICAÇÕES (fora da área de impressão)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customFormat="1" customHeight="1" s="13" thickBot="1">
       <c r="A12" s="51" t="n"/>
@@ -12115,6 +12496,24 @@
       </c>
       <c r="Y41" s="307" t="n"/>
       <c r="Z41" s="300" t="n"/>
+      <c r="AH41" s="323" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado
+◄ VOLTAR para B41</t>
+        </is>
+      </c>
+      <c r="AI41" s="323" t="inlineStr">
+        <is>
+          <t>PA49 - Mosaico Bisazza (painel e pilar)
+◄ VOLTAR para H41</t>
+        </is>
+      </c>
+      <c r="AJ41" s="323" t="inlineStr">
+        <is>
+          <t>D54 - Chuveiro de embutir no teto Raindream, Roca
+◄ VOLTAR para U41</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="89" customHeight="1">
       <c r="A42" s="298" t="inlineStr">
@@ -13018,6 +13417,60 @@
 D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
         </is>
       </c>
+      <c r="AH55" s="323" t="inlineStr">
+        <is>
+          <t>P10 - Piso elevado em mármore branco selecionado
+◄ VOLTAR para B55</t>
+        </is>
+      </c>
+      <c r="AI55" s="323" t="inlineStr">
+        <is>
+          <t>PA47 - Pintura com tinta mineral, cor 930, Terracor
+◄ VOLTAR para H55</t>
+        </is>
+      </c>
+      <c r="AJ55" s="323" t="inlineStr">
+        <is>
+          <t>D73 - Bancada em mármore branco selecionado
+◄ VOLTAR para J55</t>
+        </is>
+      </c>
+      <c r="AK55" s="323" t="inlineStr">
+        <is>
+          <t>D38 - Espelho liso incolor 4mm
+◄ VOLTAR para K55</t>
+        </is>
+      </c>
+      <c r="AL55" s="323" t="inlineStr">
+        <is>
+          <t>D72 - Cuba de semi-encaixe slim, Deca
+◄ VOLTAR para L55</t>
+        </is>
+      </c>
+      <c r="AM55" s="323" t="inlineStr">
+        <is>
+          <t>D69 - Torneira com sensor Decalux, Deca
+◄ VOLTAR para O55</t>
+        </is>
+      </c>
+      <c r="AN55" s="323" t="inlineStr">
+        <is>
+          <t>D22 - Bacia Carrara / Panache e assento
+◄ VOLTAR para P55</t>
+        </is>
+      </c>
+      <c r="AO55" s="323" t="inlineStr">
+        <is>
+          <t>D33 - Monocomando para chuveiro Mix&amp;Match, Docol
+◄ VOLTAR para S55</t>
+        </is>
+      </c>
+      <c r="AP55" s="323" t="inlineStr">
+        <is>
+          <t>D70 - Chuveiro 200 de parede Docol Eden
+◄ VOLTAR para U55</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="298" t="inlineStr">
@@ -13426,8 +13879,9 @@
       <c r="Z64" s="300" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="L10:U10"/>
+    <mergeCell ref="AH11:AQ11"/>
     <mergeCell ref="B10:K10"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="T5:U5"/>
@@ -13460,18 +13914,30 @@
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" tooltip="Abrir imagem: P10 - Piso elevado em mármore branco selecionado" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" tooltip="Abrir imagem: PA49 - Mosaico Bisazza (painel e pilar)" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" tooltip="Abrir imagem: D54 - Chuveiro de embutir no teto Raindream, Roca" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" tooltip="Abrir imagem: P10 - Piso elevado em mármore branco selecionado" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" tooltip="Abrir imagem: PA47 - Pintura com tinta mineral, cor 930, Terracor" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" tooltip="Abrir imagem: D73 - Bancada em mármore branco selecionado" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" tooltip="Abrir imagem: D38 - Espelho liso incolor 4mm" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" tooltip="Abrir imagem: D72 - Cuba de semi-encaixe slim, Deca" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" tooltip="Abrir imagem: D69 - Torneira com sensor Decalux, Deca" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" tooltip="Abrir imagem: D22 - Bacia Carrara / Panache e assento" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" tooltip="Abrir imagem: D33 - Monocomando para chuveiro Mix&amp;Match, Docol" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U55" tooltip="Abrir imagem: D70 - Chuveiro 200 de parede Docol Eden" r:id="rId12"/>
+    <hyperlink ref="B41" location="'PILOTIS'!AH41" tooltip="Ver imagem: P10 - Piso elevado em mármore branco selecionado"/>
+    <hyperlink ref="H41" location="'PILOTIS'!AI41" tooltip="Ver imagem: PA49 - Mosaico Bisazza (painel e pilar)"/>
+    <hyperlink ref="U41" location="'PILOTIS'!AJ41" tooltip="Ver imagem: D54 - Chuveiro de embutir no teto Raindream, Roca"/>
+    <hyperlink ref="AH41" location="'PILOTIS'!B41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI41" location="'PILOTIS'!H41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ41" location="'PILOTIS'!U41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B55" location="'PILOTIS'!AH55" tooltip="Ver imagem: P10 - Piso elevado em mármore branco selecionado"/>
+    <hyperlink ref="H55" location="'PILOTIS'!AI55" tooltip="Ver imagem: PA47 - Pintura com tinta mineral, cor 930, Terracor"/>
+    <hyperlink ref="J55" location="'PILOTIS'!AJ55" tooltip="Ver imagem: D73 - Bancada em mármore branco selecionado"/>
+    <hyperlink ref="K55" location="'PILOTIS'!AK55" tooltip="Ver imagem: D38 - Espelho liso incolor 4mm"/>
+    <hyperlink ref="L55" location="'PILOTIS'!AL55" tooltip="Ver imagem: D72 - Cuba de semi-encaixe slim, Deca"/>
+    <hyperlink ref="O55" location="'PILOTIS'!AM55" tooltip="Ver imagem: D69 - Torneira com sensor Decalux, Deca"/>
+    <hyperlink ref="P55" location="'PILOTIS'!AN55" tooltip="Ver imagem: D22 - Bacia Carrara / Panache e assento"/>
+    <hyperlink ref="S55" location="'PILOTIS'!AO55" tooltip="Ver imagem: D33 - Monocomando para chuveiro Mix&amp;Match, Docol"/>
+    <hyperlink ref="U55" location="'PILOTIS'!AP55" tooltip="Ver imagem: D70 - Chuveiro 200 de parede Docol Eden"/>
+    <hyperlink ref="AH55" location="'PILOTIS'!B55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI55" location="'PILOTIS'!H55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ55" location="'PILOTIS'!J55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK55" location="'PILOTIS'!K55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL55" location="'PILOTIS'!L55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM55" location="'PILOTIS'!O55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AN55" location="'PILOTIS'!P55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AO55" location="'PILOTIS'!S55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AP55" location="'PILOTIS'!U55" tooltip="Voltar para a grade"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
@@ -13488,7 +13954,7 @@
     <brk id="11" min="0" max="16383" man="1"/>
     <brk id="21" min="0" max="16383" man="1"/>
   </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -11,7 +11,8 @@
     <sheet name="2° PAVTO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="PILOTIS" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="APTO TIPO" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="PENDÊNCIAS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONFLITOS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PENDÊNCIAS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">OFFSET('CONTROLE DE REVISÕES '!$A$1,0,0,MAX(1,MAX(INDEX(('CONTROLE DE REVISÕES '!$A$1:$I$3000&amp;""&lt;&gt;"")*ROW('CONTROLE DE REVISÕES '!$A$1:$I$3000),0))),9)</definedName>
@@ -23,7 +24,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">OFFSET('PILOTIS'!$A$1,0,0,MAX(11,MAX(INDEX(('PILOTIS'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('PILOTIS'!$A$1:$AF$3000),0))),32)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'APTO TIPO'!$1:$11,'APTO TIPO'!$A:$A</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">OFFSET('APTO TIPO'!$A$1,0,0,MAX(11,MAX(INDEX(('APTO TIPO'!$A$1:$AF$3000&amp;""&lt;&gt;"")*ROW('APTO TIPO'!$A$1:$AF$3000),0))),32)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">OFFSET('PENDÊNCIAS'!$A$1,0,0,MAX(1,MAX(INDEX(('PENDÊNCIAS'!$A$1:$E$3000&amp;""&lt;&gt;"")*ROW('PENDÊNCIAS'!$A$1:$E$3000),0))),5)</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'CONFLITOS'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">OFFSET('CONFLITOS'!$A$1,0,0,MAX(4,MAX(INDEX(('CONFLITOS'!$A$1:$H$3000&amp;""&lt;&gt;"")*ROW('CONFLITOS'!$A$1:$H$3000),0))),8)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">OFFSET('PENDÊNCIAS'!$A$1,0,0,MAX(1,MAX(INDEX(('PENDÊNCIAS'!$A$1:$E$3000&amp;""&lt;&gt;"")*ROW('PENDÊNCIAS'!$A$1:$E$3000),0))),5)</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="75">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -454,8 +457,36 @@
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -524,8 +555,18 @@
         <fgColor rgb="00243F2E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="73">
+  <borders count="74">
     <border>
       <left/>
       <right/>
@@ -1424,6 +1465,20 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="008C8C8C"/>
+      </left>
+      <right style="thin">
+        <color rgb="008C8C8C"/>
+      </right>
+      <top style="thin">
+        <color rgb="008C8C8C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008C8C8C"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -1437,7 +1492,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="324">
+  <cellXfs count="335">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2313,6 +2368,39 @@
     </xf>
     <xf numFmtId="0" fontId="68" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="65" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="13" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="14" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -6708,7 +6796,7 @@
           <t>ANTECÂMARA(ECLUSA PEDESTRE)</t>
         </is>
       </c>
-      <c r="B16" s="299" t="inlineStr">
+      <c r="B16" s="307" t="inlineStr">
         <is>
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -6716,18 +6804,18 @@
       <c r="C16" s="300" t="n"/>
       <c r="D16" s="300" t="n"/>
       <c r="E16" s="300" t="n"/>
-      <c r="F16" s="301" t="inlineStr">
+      <c r="F16" s="308" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G16" s="300" t="n"/>
-      <c r="H16" s="301" t="inlineStr">
+      <c r="H16" s="308" t="inlineStr">
         <is>
           <t>PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I16" s="301" t="inlineStr">
+      <c r="I16" s="308" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -6744,13 +6832,13 @@
       <c r="S16" s="300" t="n"/>
       <c r="T16" s="300" t="n"/>
       <c r="U16" s="300" t="n"/>
-      <c r="V16" s="301" t="inlineStr">
+      <c r="V16" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W16" s="300" t="n"/>
-      <c r="X16" s="299" t="inlineStr">
+      <c r="X16" s="307" t="inlineStr">
         <is>
           <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
 D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -6774,7 +6862,7 @@
       <c r="C17" s="300" t="n"/>
       <c r="D17" s="300" t="n"/>
       <c r="E17" s="300" t="n"/>
-      <c r="F17" s="301" t="inlineStr">
+      <c r="F17" s="308" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.
 ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
@@ -6787,7 +6875,7 @@
 CONFLITO – Arquitetura: ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
         </is>
       </c>
-      <c r="I17" s="301" t="inlineStr">
+      <c r="I17" s="308" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
 ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
@@ -6805,7 +6893,7 @@
       <c r="S17" s="300" t="n"/>
       <c r="T17" s="300" t="n"/>
       <c r="U17" s="300" t="n"/>
-      <c r="V17" s="301" t="inlineStr">
+      <c r="V17" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
@@ -6821,7 +6909,7 @@
           <t>LAVABO GUARITA</t>
         </is>
       </c>
-      <c r="B18" s="299" t="inlineStr">
+      <c r="B18" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -6829,18 +6917,18 @@
       <c r="C18" s="300" t="n"/>
       <c r="D18" s="300" t="n"/>
       <c r="E18" s="300" t="n"/>
-      <c r="F18" s="301" t="inlineStr">
+      <c r="F18" s="308" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G18" s="300" t="n"/>
-      <c r="H18" s="301" t="inlineStr">
+      <c r="H18" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
         </is>
       </c>
-      <c r="I18" s="301" t="inlineStr">
+      <c r="I18" s="308" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -6869,7 +6957,7 @@
           <t>CIRCULAÇÃO GUARITA</t>
         </is>
       </c>
-      <c r="B19" s="299" t="inlineStr">
+      <c r="B19" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -6877,18 +6965,18 @@
       <c r="C19" s="300" t="n"/>
       <c r="D19" s="300" t="n"/>
       <c r="E19" s="300" t="n"/>
-      <c r="F19" s="301" t="inlineStr">
+      <c r="F19" s="308" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G19" s="300" t="n"/>
-      <c r="H19" s="301" t="inlineStr">
+      <c r="H19" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I19" s="301" t="inlineStr">
+      <c r="I19" s="308" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -6917,7 +7005,7 @@
           <t>LOBBY ENTRADA</t>
         </is>
       </c>
-      <c r="B20" s="299" t="inlineStr">
+      <c r="B20" s="307" t="inlineStr">
         <is>
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -6925,13 +7013,13 @@
       <c r="C20" s="300" t="n"/>
       <c r="D20" s="300" t="n"/>
       <c r="E20" s="300" t="n"/>
-      <c r="F20" s="301" t="inlineStr">
+      <c r="F20" s="308" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G20" s="300" t="n"/>
-      <c r="H20" s="301" t="inlineStr">
+      <c r="H20" s="308" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
@@ -6939,7 +7027,7 @@
 PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I20" s="301" t="inlineStr">
+      <c r="I20" s="308" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
 T12 - Forro em chapa metálica dourada colada sobre MDF cru 6mm aparafusado em estrutura auxiliar do guarda corpo em metalon</t>
@@ -6957,20 +7045,20 @@
       <c r="S20" s="300" t="n"/>
       <c r="T20" s="300" t="n"/>
       <c r="U20" s="300" t="n"/>
-      <c r="V20" s="301" t="inlineStr">
+      <c r="V20" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W20" s="300" t="n"/>
-      <c r="X20" s="299" t="inlineStr">
+      <c r="X20" s="307" t="inlineStr">
         <is>
           <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
 D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y20" s="302" t="n"/>
-      <c r="Z20" s="301" t="inlineStr">
+      <c r="Z20" s="308" t="inlineStr">
         <is>
           <t>D63 - Guarda corpo em chapa metálica dourada colada sobre fechamento em MDF cru 6mm aparafusado em estrutura auxiliar de metalon. Dimensões e detalhes conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -6982,7 +7070,7 @@
           <t>HALL ELEVADORES</t>
         </is>
       </c>
-      <c r="B21" s="299" t="inlineStr">
+      <c r="B21" s="307" t="inlineStr">
         <is>
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -6990,20 +7078,20 @@
       <c r="C21" s="300" t="n"/>
       <c r="D21" s="300" t="n"/>
       <c r="E21" s="300" t="n"/>
-      <c r="F21" s="301" t="inlineStr">
+      <c r="F21" s="308" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G21" s="300" t="n"/>
-      <c r="H21" s="301" t="inlineStr">
+      <c r="H21" s="308" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA54 - Parede em alvenaria regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I21" s="301" t="inlineStr">
+      <c r="I21" s="308" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7020,7 +7108,7 @@
       <c r="S21" s="300" t="n"/>
       <c r="T21" s="300" t="n"/>
       <c r="U21" s="300" t="n"/>
-      <c r="V21" s="301" t="inlineStr">
+      <c r="V21" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
@@ -7028,7 +7116,7 @@
       <c r="W21" s="300" t="n"/>
       <c r="X21" s="302" t="n"/>
       <c r="Y21" s="302" t="n"/>
-      <c r="Z21" s="301" t="inlineStr">
+      <c r="Z21" s="308" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -7040,7 +7128,7 @@
           <t>CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
         </is>
       </c>
-      <c r="B22" s="299" t="inlineStr">
+      <c r="B22" s="307" t="inlineStr">
         <is>
           <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -7048,18 +7136,18 @@
       <c r="C22" s="300" t="n"/>
       <c r="D22" s="300" t="n"/>
       <c r="E22" s="300" t="n"/>
-      <c r="F22" s="301" t="inlineStr">
+      <c r="F22" s="308" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G22" s="300" t="n"/>
-      <c r="H22" s="301" t="inlineStr">
+      <c r="H22" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I22" s="301" t="inlineStr">
+      <c r="I22" s="308" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7088,7 +7176,7 @@
           <t xml:space="preserve">HALL GARGEM </t>
         </is>
       </c>
-      <c r="B23" s="299" t="inlineStr">
+      <c r="B23" s="307" t="inlineStr">
         <is>
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -7096,19 +7184,19 @@
       <c r="C23" s="300" t="n"/>
       <c r="D23" s="300" t="n"/>
       <c r="E23" s="300" t="n"/>
-      <c r="F23" s="305" t="inlineStr">
+      <c r="F23" s="324" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G23" s="300" t="n"/>
-      <c r="H23" s="301" t="inlineStr">
+      <c r="H23" s="308" t="inlineStr">
         <is>
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I23" s="301" t="inlineStr">
+      <c r="I23" s="308" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7125,20 +7213,20 @@
       <c r="S23" s="300" t="n"/>
       <c r="T23" s="300" t="n"/>
       <c r="U23" s="300" t="n"/>
-      <c r="V23" s="301" t="inlineStr">
+      <c r="V23" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W23" s="300" t="n"/>
-      <c r="X23" s="299" t="inlineStr">
+      <c r="X23" s="307" t="inlineStr">
         <is>
           <t>D44 - Porta pivotante em MDF com acabamento em pintura acrílica fosca. Tom a definir. Dimensões conforme Mapa de Esquadrias. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 D45 - Porta pivotante em MDF com acabamento em pintura acrílica fosca. Tom a definir. Dimensões conforme Mapa de Esquadrias. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y23" s="302" t="n"/>
-      <c r="Z23" s="301" t="inlineStr">
+      <c r="Z23" s="308" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -7150,7 +7238,7 @@
           <t xml:space="preserve">GARAGEM </t>
         </is>
       </c>
-      <c r="B24" s="299" t="inlineStr">
+      <c r="B24" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -7160,12 +7248,12 @@
       <c r="E24" s="300" t="n"/>
       <c r="F24" s="300" t="n"/>
       <c r="G24" s="300" t="n"/>
-      <c r="H24" s="301" t="inlineStr">
+      <c r="H24" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I24" s="301" t="inlineStr">
+      <c r="I24" s="308" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -7194,7 +7282,7 @@
           <t>CASA DE BOMBAS</t>
         </is>
       </c>
-      <c r="B25" s="299" t="inlineStr">
+      <c r="B25" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -7204,12 +7292,12 @@
       <c r="E25" s="300" t="n"/>
       <c r="F25" s="306" t="n"/>
       <c r="G25" s="300" t="n"/>
-      <c r="H25" s="299" t="inlineStr">
+      <c r="H25" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I25" s="299" t="inlineStr">
+      <c r="I25" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -7270,7 +7358,7 @@
           <t xml:space="preserve">CIRCULAÇÃO </t>
         </is>
       </c>
-      <c r="B27" s="299" t="inlineStr">
+      <c r="B27" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7278,18 +7366,18 @@
       <c r="C27" s="300" t="n"/>
       <c r="D27" s="308" t="n"/>
       <c r="E27" s="300" t="n"/>
-      <c r="F27" s="299" t="inlineStr">
+      <c r="F27" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G27" s="300" t="n"/>
-      <c r="H27" s="299" t="inlineStr">
+      <c r="H27" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I27" s="299" t="inlineStr">
+      <c r="I27" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7318,7 +7406,7 @@
           <t>I.S P.C.D</t>
         </is>
       </c>
-      <c r="B28" s="299" t="inlineStr">
+      <c r="B28" s="307" t="inlineStr">
         <is>
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -7326,29 +7414,29 @@
       <c r="C28" s="300" t="n"/>
       <c r="D28" s="307" t="n"/>
       <c r="E28" s="308" t="n"/>
-      <c r="F28" s="299" t="inlineStr">
+      <c r="F28" s="307" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G28" s="300" t="n"/>
-      <c r="H28" s="299" t="inlineStr">
+      <c r="H28" s="307" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I28" s="301" t="inlineStr">
+      <c r="I28" s="308" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J28" s="301" t="inlineStr">
+      <c r="J28" s="308" t="inlineStr">
         <is>
           <t>D65 - Bancada em pedra natural Basaltina com cuba esculpida e bandeja removível. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K28" s="301" t="inlineStr">
+      <c r="K28" s="308" t="inlineStr">
         <is>
           <t>D37 - Armário em MDF Kahimir ref. Arauco com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF 12mm com acabamento da lateral das portas cantoneiras em aço inox polido e lateral do armário em chapa de aço inox polido. Dimensões e desenho conforme detalhamento. Obs.: MDF possui certificação FSC.</t>
         </is>
@@ -7356,12 +7444,12 @@
       <c r="L28" s="300" t="n"/>
       <c r="M28" s="300" t="n"/>
       <c r="N28" s="300" t="n"/>
-      <c r="O28" s="301" t="inlineStr">
+      <c r="O28" s="308" t="inlineStr">
         <is>
           <t>D66 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento grafite escovado, cód.: 01739870. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P28" s="301" t="inlineStr">
+      <c r="P28" s="308" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7369,25 +7457,25 @@
       <c r="Q28" s="300" t="n"/>
       <c r="R28" s="300" t="n"/>
       <c r="S28" s="300" t="n"/>
-      <c r="T28" s="299" t="inlineStr">
+      <c r="T28" s="307" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve</t>
         </is>
       </c>
       <c r="U28" s="300" t="n"/>
-      <c r="V28" s="299" t="inlineStr">
+      <c r="V28" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W28" s="307" t="n"/>
-      <c r="X28" s="299" t="inlineStr">
+      <c r="X28" s="307" t="inlineStr">
         <is>
           <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y28" s="302" t="n"/>
-      <c r="Z28" s="299" t="inlineStr">
+      <c r="Z28" s="307" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -7401,7 +7489,7 @@
           <t>VESTÍBULO</t>
         </is>
       </c>
-      <c r="B29" s="299" t="inlineStr">
+      <c r="B29" s="307" t="inlineStr">
         <is>
           <t>P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados na pedra devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -7409,19 +7497,19 @@
       <c r="C29" s="300" t="n"/>
       <c r="D29" s="300" t="n"/>
       <c r="E29" s="308" t="n"/>
-      <c r="F29" s="301" t="inlineStr">
+      <c r="F29" s="308" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G29" s="307" t="n"/>
-      <c r="H29" s="299" t="inlineStr">
+      <c r="H29" s="307" t="inlineStr">
         <is>
           <t>PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA55 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro 4mm temperado, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I29" s="299" t="inlineStr">
+      <c r="I29" s="307" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7438,13 +7526,13 @@
       <c r="S29" s="300" t="n"/>
       <c r="T29" s="300" t="n"/>
       <c r="U29" s="300" t="n"/>
-      <c r="V29" s="299" t="inlineStr">
+      <c r="V29" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W29" s="300" t="n"/>
-      <c r="X29" s="301" t="inlineStr">
+      <c r="X29" s="308" t="inlineStr">
         <is>
           <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
 D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -7459,7 +7547,7 @@
           <t>CONCIERGE</t>
         </is>
       </c>
-      <c r="B30" s="299" t="inlineStr">
+      <c r="B30" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7467,18 +7555,18 @@
       <c r="C30" s="300" t="n"/>
       <c r="D30" s="300" t="n"/>
       <c r="E30" s="308" t="n"/>
-      <c r="F30" s="301" t="inlineStr">
+      <c r="F30" s="308" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G30" s="307" t="n"/>
-      <c r="H30" s="299" t="inlineStr">
+      <c r="H30" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I30" s="299" t="inlineStr">
+      <c r="I30" s="307" t="inlineStr">
         <is>
           <t>ARQ-T19 - código não existe no quadro de tetos (01 a 06); conferir na planta</t>
         </is>
@@ -7507,7 +7595,7 @@
           <t>DELIVERY</t>
         </is>
       </c>
-      <c r="B31" s="299" t="inlineStr">
+      <c r="B31" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7515,18 +7603,18 @@
       <c r="C31" s="300" t="n"/>
       <c r="D31" s="308" t="n"/>
       <c r="E31" s="308" t="n"/>
-      <c r="F31" s="299" t="inlineStr">
+      <c r="F31" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G31" s="300" t="n"/>
-      <c r="H31" s="299" t="inlineStr">
+      <c r="H31" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I31" s="299" t="inlineStr">
+      <c r="I31" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7555,7 +7643,7 @@
           <t xml:space="preserve">CIRCULAÇÃO SERVIÇO </t>
         </is>
       </c>
-      <c r="B32" s="299" t="inlineStr">
+      <c r="B32" s="307" t="inlineStr">
         <is>
           <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -7563,18 +7651,18 @@
       <c r="C32" s="300" t="n"/>
       <c r="D32" s="308" t="n"/>
       <c r="E32" s="308" t="n"/>
-      <c r="F32" s="299" t="inlineStr">
+      <c r="F32" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G32" s="300" t="n"/>
-      <c r="H32" s="299" t="inlineStr">
+      <c r="H32" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I32" s="299" t="inlineStr">
+      <c r="I32" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7603,7 +7691,7 @@
           <t>CAR WASH</t>
         </is>
       </c>
-      <c r="B33" s="299" t="inlineStr">
+      <c r="B33" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -7613,12 +7701,12 @@
       <c r="E33" s="300" t="n"/>
       <c r="F33" s="307" t="n"/>
       <c r="G33" s="300" t="n"/>
-      <c r="H33" s="299" t="inlineStr">
+      <c r="H33" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I33" s="299" t="inlineStr">
+      <c r="I33" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -7647,7 +7735,7 @@
           <t xml:space="preserve">BICICLETÁRIO </t>
         </is>
       </c>
-      <c r="B34" s="299" t="inlineStr">
+      <c r="B34" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -7657,12 +7745,12 @@
       <c r="E34" s="308" t="n"/>
       <c r="F34" s="307" t="n"/>
       <c r="G34" s="300" t="n"/>
-      <c r="H34" s="299" t="inlineStr">
+      <c r="H34" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA13 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Acabamento de meia parede com porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Paginação e altura conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I34" s="299" t="inlineStr">
+      <c r="I34" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -7691,7 +7779,7 @@
           <t xml:space="preserve">ZELADORIA </t>
         </is>
       </c>
-      <c r="B35" s="299" t="inlineStr">
+      <c r="B35" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7699,18 +7787,18 @@
       <c r="C35" s="300" t="n"/>
       <c r="D35" s="307" t="n"/>
       <c r="E35" s="308" t="n"/>
-      <c r="F35" s="299" t="inlineStr">
+      <c r="F35" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G35" s="300" t="n"/>
-      <c r="H35" s="299" t="inlineStr">
+      <c r="H35" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I35" s="299" t="inlineStr">
+      <c r="I35" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7739,7 +7827,7 @@
           <t>ARS 1</t>
         </is>
       </c>
-      <c r="B36" s="299" t="inlineStr">
+      <c r="B36" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7749,12 +7837,12 @@
       <c r="E36" s="308" t="n"/>
       <c r="F36" s="307" t="n"/>
       <c r="G36" s="300" t="n"/>
-      <c r="H36" s="299" t="inlineStr">
+      <c r="H36" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I36" s="299" t="inlineStr">
+      <c r="I36" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7783,7 +7871,7 @@
           <t>ARS 2</t>
         </is>
       </c>
-      <c r="B37" s="299" t="inlineStr">
+      <c r="B37" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7793,12 +7881,12 @@
       <c r="E37" s="308" t="n"/>
       <c r="F37" s="307" t="n"/>
       <c r="G37" s="300" t="n"/>
-      <c r="H37" s="299" t="inlineStr">
+      <c r="H37" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I37" s="299" t="inlineStr">
+      <c r="I37" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7827,7 +7915,7 @@
           <t>ARS 3</t>
         </is>
       </c>
-      <c r="B38" s="299" t="inlineStr">
+      <c r="B38" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7837,12 +7925,12 @@
       <c r="E38" s="308" t="n"/>
       <c r="F38" s="307" t="n"/>
       <c r="G38" s="300" t="n"/>
-      <c r="H38" s="299" t="inlineStr">
+      <c r="H38" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I38" s="299" t="inlineStr">
+      <c r="I38" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7871,7 +7959,7 @@
           <t>SALA MOTORISTA</t>
         </is>
       </c>
-      <c r="B39" s="299" t="inlineStr">
+      <c r="B39" s="307" t="inlineStr">
         <is>
           <t>ARQ-P06 - Piso em porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7879,18 +7967,18 @@
       <c r="C39" s="300" t="n"/>
       <c r="D39" s="307" t="n"/>
       <c r="E39" s="308" t="n"/>
-      <c r="F39" s="299" t="inlineStr">
+      <c r="F39" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G39" s="300" t="n"/>
-      <c r="H39" s="299" t="inlineStr">
+      <c r="H39" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
         </is>
       </c>
-      <c r="I39" s="299" t="inlineStr">
+      <c r="I39" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -7919,7 +8007,7 @@
           <t>DML</t>
         </is>
       </c>
-      <c r="B40" s="299" t="inlineStr">
+      <c r="B40" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -7929,12 +8017,12 @@
       <c r="E40" s="308" t="n"/>
       <c r="F40" s="307" t="n"/>
       <c r="G40" s="300" t="n"/>
-      <c r="H40" s="299" t="inlineStr">
+      <c r="H40" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I40" s="299" t="inlineStr">
+      <c r="I40" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -7963,7 +8051,7 @@
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="B41" s="299" t="inlineStr">
+      <c r="B41" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -7973,12 +8061,12 @@
       <c r="E41" s="308" t="n"/>
       <c r="F41" s="307" t="n"/>
       <c r="G41" s="300" t="n"/>
-      <c r="H41" s="299" t="inlineStr">
+      <c r="H41" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I41" s="299" t="inlineStr">
+      <c r="I41" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -8007,7 +8095,7 @@
           <t>VEST. FEMININO</t>
         </is>
       </c>
-      <c r="B42" s="299" t="inlineStr">
+      <c r="B42" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -8017,12 +8105,12 @@
       <c r="E42" s="308" t="n"/>
       <c r="F42" s="307" t="n"/>
       <c r="G42" s="300" t="n"/>
-      <c r="H42" s="299" t="inlineStr">
+      <c r="H42" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I42" s="299" t="inlineStr">
+      <c r="I42" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -8051,7 +8139,7 @@
           <t>VEST. MASC.</t>
         </is>
       </c>
-      <c r="B43" s="299" t="inlineStr">
+      <c r="B43" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -8061,12 +8149,12 @@
       <c r="E43" s="308" t="n"/>
       <c r="F43" s="307" t="n"/>
       <c r="G43" s="300" t="n"/>
-      <c r="H43" s="299" t="inlineStr">
+      <c r="H43" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I43" s="299" t="inlineStr">
+      <c r="I43" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -8095,7 +8183,7 @@
           <t>ESTAR/COPA FUNCIONÁRIOS</t>
         </is>
       </c>
-      <c r="B44" s="299" t="inlineStr">
+      <c r="B44" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -8105,12 +8193,12 @@
       <c r="E44" s="308" t="n"/>
       <c r="F44" s="307" t="n"/>
       <c r="G44" s="300" t="n"/>
-      <c r="H44" s="299" t="inlineStr">
+      <c r="H44" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I44" s="299" t="inlineStr">
+      <c r="I44" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -8139,7 +8227,7 @@
           <t xml:space="preserve">CIRCULAÇÃO </t>
         </is>
       </c>
-      <c r="B45" s="299" t="inlineStr">
+      <c r="B45" s="307" t="inlineStr">
         <is>
           <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -8147,18 +8235,18 @@
       <c r="C45" s="300" t="n"/>
       <c r="D45" s="307" t="n"/>
       <c r="E45" s="308" t="n"/>
-      <c r="F45" s="299" t="inlineStr">
+      <c r="F45" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="G45" s="300" t="n"/>
-      <c r="H45" s="299" t="inlineStr">
+      <c r="H45" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I45" s="299" t="inlineStr">
+      <c r="I45" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -8187,7 +8275,7 @@
           <t>GERADOR</t>
         </is>
       </c>
-      <c r="B46" s="299" t="inlineStr">
+      <c r="B46" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -8197,12 +8285,12 @@
       <c r="E46" s="308" t="n"/>
       <c r="F46" s="300" t="n"/>
       <c r="G46" s="300" t="n"/>
-      <c r="H46" s="299" t="inlineStr">
+      <c r="H46" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I46" s="299" t="inlineStr">
+      <c r="I46" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -8231,7 +8319,7 @@
           <t>VAGAS BOX</t>
         </is>
       </c>
-      <c r="B47" s="299" t="inlineStr">
+      <c r="B47" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -8241,12 +8329,12 @@
       <c r="E47" s="308" t="n"/>
       <c r="F47" s="300" t="n"/>
       <c r="G47" s="300" t="n"/>
-      <c r="H47" s="299" t="inlineStr">
+      <c r="H47" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I47" s="299" t="inlineStr">
+      <c r="I47" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -8275,7 +8363,7 @@
           <t>QUADROS ELÉTRICOS</t>
         </is>
       </c>
-      <c r="B48" s="299" t="inlineStr">
+      <c r="B48" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -8285,12 +8373,12 @@
       <c r="E48" s="308" t="n"/>
       <c r="F48" s="300" t="n"/>
       <c r="G48" s="300" t="n"/>
-      <c r="H48" s="299" t="inlineStr">
+      <c r="H48" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I48" s="299" t="inlineStr">
+      <c r="I48" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -8319,7 +8407,7 @@
           <t>ACESSO E SAÍDA DE VEÍCULOS</t>
         </is>
       </c>
-      <c r="B49" s="299" t="inlineStr">
+      <c r="B49" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -8329,12 +8417,12 @@
       <c r="E49" s="308" t="n"/>
       <c r="F49" s="300" t="n"/>
       <c r="G49" s="300" t="n"/>
-      <c r="H49" s="299" t="inlineStr">
+      <c r="H49" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I49" s="299" t="n"/>
+      <c r="I49" s="307" t="n"/>
       <c r="J49" s="307" t="n"/>
       <c r="K49" s="300" t="n"/>
       <c r="L49" s="307" t="n"/>
@@ -8359,7 +8447,7 @@
           <t>ESTACIONAMENTO VISITANTES</t>
         </is>
       </c>
-      <c r="B50" s="299" t="inlineStr">
+      <c r="B50" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -8369,12 +8457,12 @@
       <c r="E50" s="308" t="n"/>
       <c r="F50" s="300" t="n"/>
       <c r="G50" s="300" t="n"/>
-      <c r="H50" s="299" t="inlineStr">
+      <c r="H50" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I50" s="299" t="inlineStr">
+      <c r="I50" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -8403,7 +8491,7 @@
           <t>RAMPA VEÍCULOS</t>
         </is>
       </c>
-      <c r="B51" s="299" t="inlineStr">
+      <c r="B51" s="307" t="inlineStr">
         <is>
           <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
         </is>
@@ -8413,12 +8501,12 @@
       <c r="E51" s="308" t="n"/>
       <c r="F51" s="300" t="n"/>
       <c r="G51" s="300" t="n"/>
-      <c r="H51" s="299" t="inlineStr">
+      <c r="H51" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I51" s="299" t="inlineStr">
+      <c r="I51" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -8447,7 +8535,7 @@
           <t>DEPÓSITO (A=8,85 m²)</t>
         </is>
       </c>
-      <c r="B52" s="299" t="inlineStr">
+      <c r="B52" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -8457,12 +8545,12 @@
       <c r="E52" s="308" t="n"/>
       <c r="F52" s="300" t="n"/>
       <c r="G52" s="300" t="n"/>
-      <c r="H52" s="299" t="inlineStr">
+      <c r="H52" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I52" s="299" t="inlineStr">
+      <c r="I52" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -8491,7 +8579,7 @@
           <t>SERVIÇO JUNTO AO PORTÃO (A=6,87 m²)</t>
         </is>
       </c>
-      <c r="B53" s="299" t="inlineStr">
+      <c r="B53" s="307" t="inlineStr">
         <is>
           <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -8499,18 +8587,18 @@
       <c r="C53" s="300" t="n"/>
       <c r="D53" s="307" t="n"/>
       <c r="E53" s="308" t="n"/>
-      <c r="F53" s="301" t="inlineStr">
+      <c r="F53" s="308" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G53" s="300" t="n"/>
-      <c r="H53" s="299" t="inlineStr">
+      <c r="H53" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
         </is>
       </c>
-      <c r="I53" s="299" t="inlineStr">
+      <c r="I53" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -8539,7 +8627,7 @@
           <t>CIRCULAÇÃO JUNTO À ESCADA (A=4,06 m²)</t>
         </is>
       </c>
-      <c r="B54" s="299" t="inlineStr">
+      <c r="B54" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -8547,14 +8635,14 @@
       <c r="C54" s="300" t="n"/>
       <c r="D54" s="307" t="n"/>
       <c r="E54" s="308" t="n"/>
-      <c r="F54" s="301" t="n"/>
+      <c r="F54" s="308" t="n"/>
       <c r="G54" s="300" t="n"/>
-      <c r="H54" s="299" t="inlineStr">
+      <c r="H54" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I54" s="299" t="inlineStr">
+      <c r="I54" s="307" t="inlineStr">
         <is>
           <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9286,7 +9374,7 @@
           <t>CASA DE BOMBAS PISCINA 1</t>
         </is>
       </c>
-      <c r="B13" s="309" t="inlineStr">
+      <c r="B13" s="325" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9296,12 +9384,12 @@
       <c r="E13" s="296" t="n"/>
       <c r="F13" s="296" t="n"/>
       <c r="G13" s="296" t="n"/>
-      <c r="H13" s="310" t="inlineStr">
+      <c r="H13" s="326" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I13" s="310" t="inlineStr">
+      <c r="I13" s="326" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9330,7 +9418,7 @@
           <t>SHAFT ELÉTRICA</t>
         </is>
       </c>
-      <c r="B14" s="299" t="inlineStr">
+      <c r="B14" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9340,12 +9428,12 @@
       <c r="E14" s="300" t="n"/>
       <c r="F14" s="300" t="n"/>
       <c r="G14" s="300" t="n"/>
-      <c r="H14" s="301" t="inlineStr">
+      <c r="H14" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I14" s="301" t="inlineStr">
+      <c r="I14" s="308" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9438,7 +9526,7 @@
           <t>CIRCULAÇÃO/ANTECÂMARA</t>
         </is>
       </c>
-      <c r="B17" s="299" t="inlineStr">
+      <c r="B17" s="307" t="inlineStr">
         <is>
           <t>ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -9446,18 +9534,18 @@
       <c r="C17" s="300" t="n"/>
       <c r="D17" s="300" t="n"/>
       <c r="E17" s="300" t="n"/>
-      <c r="F17" s="301" t="inlineStr">
+      <c r="F17" s="308" t="inlineStr">
         <is>
           <t>ARQ-RD20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G17" s="300" t="n"/>
-      <c r="H17" s="301" t="inlineStr">
+      <c r="H17" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I17" s="301" t="inlineStr">
+      <c r="I17" s="308" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
 ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
@@ -9487,7 +9575,7 @@
           <t>PRESSURIZAÇÃO/ANTECÂMARA</t>
         </is>
       </c>
-      <c r="B18" s="299" t="inlineStr">
+      <c r="B18" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9497,12 +9585,12 @@
       <c r="E18" s="300" t="n"/>
       <c r="F18" s="300" t="n"/>
       <c r="G18" s="300" t="n"/>
-      <c r="H18" s="301" t="inlineStr">
+      <c r="H18" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I18" s="301" t="inlineStr">
+      <c r="I18" s="308" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9531,7 +9619,7 @@
           <t>ÁREA TÉCNICA 1</t>
         </is>
       </c>
-      <c r="B19" s="299" t="inlineStr">
+      <c r="B19" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9541,12 +9629,12 @@
       <c r="E19" s="300" t="n"/>
       <c r="F19" s="300" t="n"/>
       <c r="G19" s="300" t="n"/>
-      <c r="H19" s="301" t="inlineStr">
+      <c r="H19" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I19" s="301" t="inlineStr">
+      <c r="I19" s="308" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9575,7 +9663,7 @@
           <t>ÁREA TÉCNICA 2</t>
         </is>
       </c>
-      <c r="B20" s="299" t="inlineStr">
+      <c r="B20" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9585,12 +9673,12 @@
       <c r="E20" s="300" t="n"/>
       <c r="F20" s="312" t="n"/>
       <c r="G20" s="300" t="n"/>
-      <c r="H20" s="301" t="inlineStr">
+      <c r="H20" s="308" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I20" s="301" t="inlineStr">
+      <c r="I20" s="308" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9619,7 +9707,7 @@
           <t>GARAGEM</t>
         </is>
       </c>
-      <c r="B21" s="299" t="inlineStr">
+      <c r="B21" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -9629,12 +9717,12 @@
       <c r="E21" s="300" t="n"/>
       <c r="F21" s="306" t="n"/>
       <c r="G21" s="300" t="n"/>
-      <c r="H21" s="299" t="inlineStr">
+      <c r="H21" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I21" s="299" t="inlineStr">
+      <c r="I21" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9663,7 +9751,7 @@
           <t>VAGAS BOX</t>
         </is>
       </c>
-      <c r="B22" s="299" t="inlineStr">
+      <c r="B22" s="307" t="inlineStr">
         <is>
           <t>ARQ-P01 - Piso em concreto mecanizado com acabamento polido. Vagas demarcadas em pintura epóxi fosca de tom cinza médio com requadro em faixa de pintura epóxi fosca de tom cinza chumbo.</t>
         </is>
@@ -9673,12 +9761,12 @@
       <c r="E22" s="300" t="n"/>
       <c r="F22" s="306" t="n"/>
       <c r="G22" s="300" t="n"/>
-      <c r="H22" s="299" t="inlineStr">
+      <c r="H22" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I22" s="299" t="inlineStr">
+      <c r="I22" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9707,7 +9795,7 @@
           <t>TELECOM</t>
         </is>
       </c>
-      <c r="B23" s="299" t="inlineStr">
+      <c r="B23" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9717,12 +9805,12 @@
       <c r="E23" s="300" t="n"/>
       <c r="F23" s="307" t="n"/>
       <c r="G23" s="300" t="n"/>
-      <c r="H23" s="299" t="inlineStr">
+      <c r="H23" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I23" s="299" t="inlineStr">
+      <c r="I23" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9751,7 +9839,7 @@
           <t>SALA DE SEGURANÇA</t>
         </is>
       </c>
-      <c r="B24" s="299" t="inlineStr">
+      <c r="B24" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9761,12 +9849,12 @@
       <c r="E24" s="308" t="n"/>
       <c r="F24" s="307" t="n"/>
       <c r="G24" s="300" t="n"/>
-      <c r="H24" s="299" t="inlineStr">
+      <c r="H24" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I24" s="301" t="inlineStr">
+      <c r="I24" s="308" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9795,7 +9883,7 @@
           <t>CASA DE BOMBAS PISCINA 2 (FUNDO)</t>
         </is>
       </c>
-      <c r="B25" s="299" t="inlineStr">
+      <c r="B25" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9805,12 +9893,12 @@
       <c r="E25" s="308" t="n"/>
       <c r="F25" s="300" t="n"/>
       <c r="G25" s="307" t="n"/>
-      <c r="H25" s="299" t="inlineStr">
+      <c r="H25" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I25" s="299" t="inlineStr">
+      <c r="I25" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9839,7 +9927,7 @@
           <t>DML</t>
         </is>
       </c>
-      <c r="B26" s="299" t="inlineStr">
+      <c r="B26" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9849,12 +9937,12 @@
       <c r="E26" s="308" t="n"/>
       <c r="F26" s="300" t="n"/>
       <c r="G26" s="307" t="n"/>
-      <c r="H26" s="299" t="inlineStr">
+      <c r="H26" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA12 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca branca. Ref.: branco neve; Suvinil. Acabamento de meia parede em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
         </is>
       </c>
-      <c r="I26" s="299" t="inlineStr">
+      <c r="I26" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9883,7 +9971,7 @@
           <t>RESERVATÓRIO INFERIOR</t>
         </is>
       </c>
-      <c r="B27" s="299" t="inlineStr">
+      <c r="B27" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9893,12 +9981,12 @@
       <c r="E27" s="308" t="n"/>
       <c r="F27" s="307" t="n"/>
       <c r="G27" s="300" t="n"/>
-      <c r="H27" s="299" t="inlineStr">
+      <c r="H27" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I27" s="299" t="inlineStr">
+      <c r="I27" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9927,7 +10015,7 @@
           <t>HALL TÉCNICO/CIRCULAÇÃO</t>
         </is>
       </c>
-      <c r="B28" s="299" t="inlineStr">
+      <c r="B28" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -9937,12 +10025,12 @@
       <c r="E28" s="308" t="n"/>
       <c r="F28" s="307" t="n"/>
       <c r="G28" s="300" t="n"/>
-      <c r="H28" s="299" t="inlineStr">
+      <c r="H28" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I28" s="299" t="inlineStr">
+      <c r="I28" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -9971,7 +10059,7 @@
           <t>RAMPA VEÍCULOS</t>
         </is>
       </c>
-      <c r="B29" s="299" t="inlineStr">
+      <c r="B29" s="307" t="inlineStr">
         <is>
           <t>ARQ-P04 - Piso em concreto mecanizado com acabamento em ladrilho hidráulico antiderrapante cinza, tom concreto. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -9981,12 +10069,12 @@
       <c r="E29" s="308" t="n"/>
       <c r="F29" s="307" t="n"/>
       <c r="G29" s="300" t="n"/>
-      <c r="H29" s="299" t="inlineStr">
+      <c r="H29" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA07 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza claro. Pintura de meia parede em epóxi monolítico de tom cinza médio, com arremate em faixa com tinta epóxi fosca de cor cinza chumbo. Altura conforme projeto arquitetônico. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I29" s="299" t="inlineStr">
+      <c r="I29" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -10015,7 +10103,7 @@
           <t>CIRCULAÇÃO ÁREA TÉCNICA (A=14,54 m²)</t>
         </is>
       </c>
-      <c r="B30" s="299" t="inlineStr">
+      <c r="B30" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -10025,12 +10113,12 @@
       <c r="E30" s="308" t="n"/>
       <c r="F30" s="307" t="n"/>
       <c r="G30" s="300" t="n"/>
-      <c r="H30" s="299" t="inlineStr">
+      <c r="H30" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I30" s="299" t="inlineStr">
+      <c r="I30" s="307" t="inlineStr">
         <is>
           <t>ARQ-T03 - Laje nervurada em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -10059,7 +10147,7 @@
           <t>CIRCULAÇÃO JUNTO À ESCADA (A=3,07 m²)</t>
         </is>
       </c>
-      <c r="B31" s="299" t="inlineStr">
+      <c r="B31" s="307" t="inlineStr">
         <is>
           <t>ARQ-P02 - Piso em concreto mecanizado com acabamento polido.</t>
         </is>
@@ -10069,12 +10157,12 @@
       <c r="E31" s="308" t="n"/>
       <c r="F31" s="307" t="n"/>
       <c r="G31" s="300" t="n"/>
-      <c r="H31" s="299" t="inlineStr">
+      <c r="H31" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I31" s="299" t="inlineStr">
+      <c r="I31" s="307" t="inlineStr">
         <is>
           <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -10826,7 +10914,7 @@
           <t>LOBBY PILOTIS</t>
         </is>
       </c>
-      <c r="B13" s="313" t="inlineStr">
+      <c r="B13" s="327" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -10841,14 +10929,14 @@
         </is>
       </c>
       <c r="G13" s="296" t="n"/>
-      <c r="H13" s="315" t="inlineStr">
+      <c r="H13" s="314" t="inlineStr">
         <is>
           <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA58 - Pilar em concreto, com enchimento, revestido em pedra natural Basaltina conforme detalhamento.Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I13" s="315" t="inlineStr">
+      <c r="I13" s="314" t="inlineStr">
         <is>
           <t>FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
@@ -10870,13 +10958,13 @@
       <c r="S13" s="296" t="n"/>
       <c r="T13" s="296" t="n"/>
       <c r="U13" s="296" t="n"/>
-      <c r="V13" s="310" t="inlineStr">
+      <c r="V13" s="326" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W13" s="296" t="n"/>
-      <c r="X13" s="309" t="inlineStr">
+      <c r="X13" s="325" t="inlineStr">
         <is>
           <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
@@ -10893,7 +10981,7 @@
           <t>SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B14" s="316" t="inlineStr">
+      <c r="B14" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -10915,7 +11003,7 @@
 PA31 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 107, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I14" s="318" t="inlineStr">
+      <c r="I14" s="317" t="inlineStr">
         <is>
           <t>FO1 - Forro de absorção acústica composto por 1 manta de lã de pet com 35Kg/m³ de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar
 FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
@@ -10938,13 +11026,13 @@
       <c r="S14" s="300" t="n"/>
       <c r="T14" s="300" t="n"/>
       <c r="U14" s="300" t="n"/>
-      <c r="V14" s="301" t="inlineStr">
+      <c r="V14" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W14" s="300" t="n"/>
-      <c r="X14" s="299" t="inlineStr">
+      <c r="X14" s="307" t="inlineStr">
         <is>
           <t>D21 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxadores conforme detalhamento. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
 D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
@@ -11023,7 +11111,7 @@
           <t>I.S FEMININO</t>
         </is>
       </c>
-      <c r="B17" s="316" t="inlineStr">
+      <c r="B17" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -11043,7 +11131,7 @@
           <t>PA39 - Parede em alvenaria rebocada regularizada revestida em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I17" s="318" t="inlineStr">
+      <c r="I17" s="317" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -11066,7 +11154,7 @@
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P17" s="318" t="inlineStr">
+      <c r="P17" s="317" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -11076,19 +11164,19 @@
       <c r="S17" s="300" t="n"/>
       <c r="T17" s="300" t="n"/>
       <c r="U17" s="300" t="n"/>
-      <c r="V17" s="301" t="inlineStr">
+      <c r="V17" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W17" s="300" t="n"/>
-      <c r="X17" s="299" t="inlineStr">
+      <c r="X17" s="307" t="inlineStr">
         <is>
           <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y17" s="302" t="n"/>
-      <c r="Z17" s="318" t="inlineStr">
+      <c r="Z17" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -11102,7 +11190,7 @@
           <t>I.S MASCULINO</t>
         </is>
       </c>
-      <c r="B18" s="316" t="inlineStr">
+      <c r="B18" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -11122,7 +11210,7 @@
           <t>PA39 - Parede em alvenaria rebocada regularizada revestida em pedra mármore Barrocci Honed, acabamento levigado, espessura 2cm. Ref.: Brasigran. Paginação e dimensões conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I18" s="318" t="inlineStr">
+      <c r="I18" s="317" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -11145,7 +11233,7 @@
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P18" s="318" t="inlineStr">
+      <c r="P18" s="317" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -11155,19 +11243,19 @@
       <c r="S18" s="300" t="n"/>
       <c r="T18" s="300" t="n"/>
       <c r="U18" s="300" t="n"/>
-      <c r="V18" s="301" t="inlineStr">
+      <c r="V18" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W18" s="300" t="n"/>
-      <c r="X18" s="299" t="inlineStr">
+      <c r="X18" s="307" t="inlineStr">
         <is>
           <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y18" s="302" t="n"/>
-      <c r="Z18" s="318" t="inlineStr">
+      <c r="Z18" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -11213,7 +11301,7 @@
           <t>COZINHA SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B20" s="316" t="inlineStr">
+      <c r="B20" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -11234,7 +11322,7 @@
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="I20" s="318" t="inlineStr">
+      <c r="I20" s="317" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -11263,20 +11351,20 @@
       <c r="S20" s="300" t="n"/>
       <c r="T20" s="300" t="n"/>
       <c r="U20" s="300" t="n"/>
-      <c r="V20" s="301" t="inlineStr">
+      <c r="V20" s="308" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W20" s="300" t="n"/>
-      <c r="X20" s="299" t="inlineStr">
+      <c r="X20" s="307" t="inlineStr">
         <is>
           <t>D21 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxadores conforme detalhamento. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
 D74 - Porta pivotante estruturada, fechamento em MDF cru, acabamento face interna e externa em micropintura cor S168-Sayerlack. Puxador tipo cava, prever tranca. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y20" s="302" t="n"/>
-      <c r="Z20" s="301" t="inlineStr">
+      <c r="Z20" s="308" t="inlineStr">
         <is>
           <t>D82 - Prateleira em granito cinza Santa Rosa, acabamento escovado, embutido na alvenaria. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -11344,7 +11432,7 @@
           <t>CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
         </is>
       </c>
-      <c r="B22" s="299" t="inlineStr">
+      <c r="B22" s="307" t="inlineStr">
         <is>
           <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -11352,18 +11440,18 @@
       <c r="C22" s="306" t="n"/>
       <c r="D22" s="300" t="n"/>
       <c r="E22" s="300" t="n"/>
-      <c r="F22" s="299" t="inlineStr">
+      <c r="F22" s="307" t="inlineStr">
         <is>
           <t>ARQ-RD21 - Rodapé em granito cinza santa rosa, acabamento serrado, h=15cm, espessura 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="G22" s="300" t="n"/>
-      <c r="H22" s="299" t="inlineStr">
+      <c r="H22" s="307" t="inlineStr">
         <is>
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I22" s="299" t="inlineStr">
+      <c r="I22" s="307" t="inlineStr">
         <is>
           <t>ARQ-T01 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -11406,14 +11494,14 @@
         </is>
       </c>
       <c r="G23" s="300" t="n"/>
-      <c r="H23" s="316" t="inlineStr">
+      <c r="H23" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="I23" s="316" t="inlineStr">
+      <c r="I23" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -11436,7 +11524,7 @@
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P23" s="318" t="inlineStr">
+      <c r="P23" s="317" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -11446,19 +11534,19 @@
       <c r="S23" s="300" t="n"/>
       <c r="T23" s="300" t="n"/>
       <c r="U23" s="300" t="n"/>
-      <c r="V23" s="299" t="inlineStr">
+      <c r="V23" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W23" s="307" t="n"/>
-      <c r="X23" s="299" t="inlineStr">
+      <c r="X23" s="307" t="inlineStr">
         <is>
           <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y23" s="302" t="n"/>
-      <c r="Z23" s="316" t="inlineStr">
+      <c r="Z23" s="320" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -11486,14 +11574,14 @@
         </is>
       </c>
       <c r="G24" s="300" t="n"/>
-      <c r="H24" s="316" t="inlineStr">
+      <c r="H24" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="I24" s="316" t="inlineStr">
+      <c r="I24" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -11516,7 +11604,7 @@
           <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="P24" s="316" t="inlineStr">
+      <c r="P24" s="320" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -11526,19 +11614,19 @@
       <c r="S24" s="300" t="n"/>
       <c r="T24" s="307" t="n"/>
       <c r="U24" s="300" t="n"/>
-      <c r="V24" s="299" t="inlineStr">
+      <c r="V24" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W24" s="307" t="n"/>
-      <c r="X24" s="299" t="inlineStr">
+      <c r="X24" s="307" t="inlineStr">
         <is>
           <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y24" s="307" t="n"/>
-      <c r="Z24" s="316" t="inlineStr">
+      <c r="Z24" s="320" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -11584,7 +11672,7 @@
           <t>ESPAÇO KIDS</t>
         </is>
       </c>
-      <c r="B26" s="316" t="inlineStr">
+      <c r="B26" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P24 - Piso em contrapiso regularizado revestido em piso vinílico em manta, 2x20m, linha Polysafe Verona PUR, acabamento Rock Salt - cód: LRV-43. Paginação conforme detalhamento.</t>
@@ -11608,7 +11696,7 @@
 PA38 - Parede em alvenaria emassada regularizada, revestida em painel de marcenaria MDF Nude-linha VEL-Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.</t>
         </is>
       </c>
-      <c r="I26" s="318" t="inlineStr">
+      <c r="I26" s="317" t="inlineStr">
         <is>
           <t>FO1 - Forro de absorção acústica composto por 1 manta de lã de pet com 35Kg/m³ de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar
 FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
@@ -11627,20 +11715,20 @@
       <c r="S26" s="300" t="n"/>
       <c r="T26" s="307" t="n"/>
       <c r="U26" s="300" t="n"/>
-      <c r="V26" s="299" t="inlineStr">
+      <c r="V26" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W26" s="307" t="n"/>
-      <c r="X26" s="299" t="inlineStr">
+      <c r="X26" s="307" t="inlineStr">
         <is>
           <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y26" s="302" t="n"/>
-      <c r="Z26" s="299" t="inlineStr">
+      <c r="Z26" s="307" t="inlineStr">
         <is>
           <t>D18 - Módulos compostos por três peças hexagonais com estruturado em peças de madeira maciça,   fechamento em reguas de madeira 25mmx70mm. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D56 - Pendente sob medida em peças de madeira maciça 60x50mm fixados no teto através de cabos de aço e estrutura auxiliar no entreforro, com acabamento no forro em canopla, cor branca. Retroiluminação em fitas de led na parte superior com dimensionamentos conforme projeto luminotécnico. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
@@ -11653,7 +11741,7 @@
           <t>ESPAÇO GOURMET</t>
         </is>
       </c>
-      <c r="B27" s="316" t="inlineStr">
+      <c r="B27" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -11668,14 +11756,14 @@
         </is>
       </c>
       <c r="G27" s="307" t="n"/>
-      <c r="H27" s="316" t="inlineStr">
+      <c r="H27" s="320" t="inlineStr">
         <is>
           <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
 PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
 PA33 - Pilar em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="I27" s="316" t="inlineStr">
+      <c r="I27" s="320" t="inlineStr">
         <is>
           <t>FO1 - Forro de absorção acústica composto por 1 manta de lã de pet com 35Kg/m³ de densidade e 50mm de espessura, fixado perfis próprios metálicos, Ref.: Trisoft ou similar
 FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.</t>
@@ -11709,20 +11797,20 @@
       <c r="S27" s="300" t="n"/>
       <c r="T27" s="300" t="n"/>
       <c r="U27" s="300" t="n"/>
-      <c r="V27" s="299" t="inlineStr">
+      <c r="V27" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W27" s="300" t="n"/>
-      <c r="X27" s="301" t="inlineStr">
+      <c r="X27" s="308" t="inlineStr">
         <is>
           <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y27" s="300" t="n"/>
-      <c r="Z27" s="299" t="inlineStr">
+      <c r="Z27" s="307" t="inlineStr">
         <is>
           <t>D13 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
 D14 - Fechamento cego em mdf cru com acabamento em folha madeira natural caravalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
@@ -11770,7 +11858,7 @@
           <t>PISCINA DECOBERTA</t>
         </is>
       </c>
-      <c r="B29" s="316" t="inlineStr">
+      <c r="B29" s="320" t="inlineStr">
         <is>
           <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm.  Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A
 P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -11781,7 +11869,7 @@
       <c r="E29" s="308" t="n"/>
       <c r="F29" s="307" t="n"/>
       <c r="G29" s="300" t="n"/>
-      <c r="H29" s="316" t="inlineStr">
+      <c r="H29" s="320" t="inlineStr">
         <is>
           <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614.. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -11801,25 +11889,25 @@
       <c r="Q29" s="300" t="n"/>
       <c r="R29" s="300" t="n"/>
       <c r="S29" s="300" t="n"/>
-      <c r="T29" s="301" t="inlineStr">
+      <c r="T29" s="308" t="inlineStr">
         <is>
           <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U29" s="301" t="inlineStr">
+      <c r="U29" s="308" t="inlineStr">
         <is>
           <t>D79 - Chuveiro de piso para área externa em aço inox 316. cód.: DK5123B. Ref.: Doka</t>
         </is>
       </c>
       <c r="V29" s="302" t="n"/>
       <c r="W29" s="307" t="n"/>
-      <c r="X29" s="299" t="inlineStr">
+      <c r="X29" s="307" t="inlineStr">
         <is>
           <t>D77 - Porta pivotante para guarda corpo em vidro temperado laminado liso incolor com tubo para pivô em aço inox polido 1 1/4'' fixado no piso com barra lisa soltada com rosca na extremidade para fixação do vidro com botão de acabamento.</t>
         </is>
       </c>
       <c r="Y29" s="302" t="n"/>
-      <c r="Z29" s="299" t="inlineStr">
+      <c r="Z29" s="307" t="inlineStr">
         <is>
           <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
         </is>
@@ -11899,7 +11987,7 @@
           <t>BAR PISCINA</t>
         </is>
       </c>
-      <c r="B32" s="299" t="inlineStr">
+      <c r="B32" s="307" t="inlineStr">
         <is>
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -11907,38 +11995,38 @@
       <c r="C32" s="300" t="n"/>
       <c r="D32" s="308" t="n"/>
       <c r="E32" s="308" t="n"/>
-      <c r="F32" s="299" t="inlineStr">
+      <c r="F32" s="307" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G32" s="300" t="n"/>
-      <c r="H32" s="299" t="inlineStr">
+      <c r="H32" s="307" t="inlineStr">
         <is>
           <t>PA42 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento serrado, com arte em baixo relevo, corte a laser, profundidade 4mm Espessura da pedra: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA51 - Pilar em concreto aparente</t>
         </is>
       </c>
-      <c r="I32" s="299" t="inlineStr">
+      <c r="I32" s="307" t="inlineStr">
         <is>
           <t>T4 - Forro em madeira pinho autoclavado tonalizado, espessura de 3cm, réguas de 10cm.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J32" s="301" t="inlineStr">
+      <c r="J32" s="308" t="inlineStr">
         <is>
           <t>D46 - Bancada/Mesa em pedra sinterizada, Lava satin fusion collection. Espessura: 5mm. Ref: Neo Lhít. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="K32" s="300" t="n"/>
-      <c r="L32" s="301" t="inlineStr">
+      <c r="L32" s="308" t="inlineStr">
         <is>
           <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina</t>
         </is>
       </c>
       <c r="M32" s="300" t="n"/>
       <c r="N32" s="300" t="n"/>
-      <c r="O32" s="301" t="inlineStr">
+      <c r="O32" s="308" t="inlineStr">
         <is>
           <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
         </is>
@@ -11947,14 +12035,14 @@
       <c r="Q32" s="300" t="n"/>
       <c r="R32" s="300" t="n"/>
       <c r="S32" s="300" t="n"/>
-      <c r="T32" s="301" t="inlineStr">
+      <c r="T32" s="308" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
 D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
       <c r="U32" s="300" t="n"/>
-      <c r="V32" s="299" t="inlineStr">
+      <c r="V32" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
@@ -11962,7 +12050,7 @@
       <c r="W32" s="307" t="n"/>
       <c r="X32" s="302" t="n"/>
       <c r="Y32" s="302" t="n"/>
-      <c r="Z32" s="299" t="inlineStr">
+      <c r="Z32" s="307" t="inlineStr">
         <is>
           <t>D47 - Marcenaria sob bancada em MDF Kashimir ref. Arauco - portas e frente gavetas em reguas de madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador em cava na marcenaria. Apresentar amostra para aprovação GPA&amp;A Obs.: MDF possui certificação FSC. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
 D48 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
@@ -12009,7 +12097,7 @@
           <t>CIRCULAÇÃO VESTIÁRIOS</t>
         </is>
       </c>
-      <c r="B34" s="299" t="inlineStr">
+      <c r="B34" s="307" t="inlineStr">
         <is>
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -12019,12 +12107,12 @@
       <c r="E34" s="308" t="n"/>
       <c r="F34" s="307" t="n"/>
       <c r="G34" s="300" t="n"/>
-      <c r="H34" s="299" t="inlineStr">
+      <c r="H34" s="307" t="inlineStr">
         <is>
           <t>PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
-      <c r="I34" s="299" t="inlineStr">
+      <c r="I34" s="307" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -12041,7 +12129,7 @@
       <c r="S34" s="307" t="n"/>
       <c r="T34" s="307" t="n"/>
       <c r="U34" s="300" t="n"/>
-      <c r="V34" s="299" t="inlineStr">
+      <c r="V34" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
@@ -12057,7 +12145,7 @@
           <t>VESTIÁRIO FEMININO</t>
         </is>
       </c>
-      <c r="B35" s="316" t="inlineStr">
+      <c r="B35" s="320" t="inlineStr">
         <is>
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -12065,20 +12153,20 @@
       <c r="C35" s="300" t="n"/>
       <c r="D35" s="307" t="n"/>
       <c r="E35" s="308" t="n"/>
-      <c r="F35" s="299" t="inlineStr">
+      <c r="F35" s="307" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G35" s="300" t="n"/>
-      <c r="H35" s="316" t="inlineStr">
+      <c r="H35" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
 PA60 - Parede revestida em chapa de aço inox 304, acabamento polido. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I35" s="316" t="inlineStr">
+      <c r="I35" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -12103,7 +12191,7 @@
 CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
-      <c r="P35" s="316" t="inlineStr">
+      <c r="P35" s="320" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12126,19 +12214,19 @@
           <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="V35" s="299" t="inlineStr">
+      <c r="V35" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W35" s="307" t="n"/>
-      <c r="X35" s="299" t="inlineStr">
+      <c r="X35" s="307" t="inlineStr">
         <is>
           <t>D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
         </is>
       </c>
       <c r="Y35" s="307" t="n"/>
-      <c r="Z35" s="318" t="inlineStr">
+      <c r="Z35" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -12152,7 +12240,7 @@
           <t xml:space="preserve">VESTIÁRIO MASCULINO </t>
         </is>
       </c>
-      <c r="B36" s="316" t="inlineStr">
+      <c r="B36" s="320" t="inlineStr">
         <is>
           <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
@@ -12160,20 +12248,20 @@
       <c r="C36" s="300" t="n"/>
       <c r="D36" s="307" t="n"/>
       <c r="E36" s="308" t="n"/>
-      <c r="F36" s="299" t="inlineStr">
+      <c r="F36" s="307" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G36" s="300" t="n"/>
-      <c r="H36" s="316" t="inlineStr">
+      <c r="H36" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
 PA60 - Parede revestida em chapa de aço inox 304, acabamento polido. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I36" s="316" t="inlineStr">
+      <c r="I36" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -12198,7 +12286,7 @@
 CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
-      <c r="P36" s="316" t="inlineStr">
+      <c r="P36" s="320" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12221,19 +12309,19 @@
           <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="V36" s="299" t="inlineStr">
+      <c r="V36" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W36" s="307" t="n"/>
-      <c r="X36" s="299" t="inlineStr">
+      <c r="X36" s="307" t="inlineStr">
         <is>
           <t>D32 - Divisórias e portas pivotantes com estrutura em alumínio e fechamento em vidro, cor Dark Beige. Ref.: Duo. Puxador tipo cava com fechaduras tipo rolete espelho modelo redondo acabamento cromo-acetinado.</t>
         </is>
       </c>
       <c r="Y36" s="307" t="n"/>
-      <c r="Z36" s="318" t="inlineStr">
+      <c r="Z36" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -12247,7 +12335,7 @@
           <t>ACADEMIA</t>
         </is>
       </c>
-      <c r="B37" s="316" t="inlineStr">
+      <c r="B37" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P22 - Piso em contrapiso regularizado, revestido em piso emborrachado isolante e antiderrapante, acabamernto preto, placas 100x100cm. Espessura: 8mm. Paginação conforme detalhamento. Ref.: Rubberkap ou similar. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12262,7 +12350,7 @@
         </is>
       </c>
       <c r="G37" s="300" t="n"/>
-      <c r="H37" s="316" t="inlineStr">
+      <c r="H37" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA27 - Parede em alvenaria rebocada e regularizada revestida em espelho liso fumê 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
@@ -12271,7 +12359,7 @@
 PA30 - Pilar em concreto com acabamento em textura mineral Arch + Concrete ENG, Ref.: Novacolor. Fornecedor: Icolori (31)99952-2442. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I37" s="316" t="inlineStr">
+      <c r="I37" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
 FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.</t>
@@ -12289,19 +12377,19 @@
       <c r="S37" s="307" t="n"/>
       <c r="T37" s="307" t="n"/>
       <c r="U37" s="300" t="n"/>
-      <c r="V37" s="299" t="inlineStr">
+      <c r="V37" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W37" s="307" t="n"/>
-      <c r="X37" s="299" t="inlineStr">
+      <c r="X37" s="307" t="inlineStr">
         <is>
           <t>D57 - Porta de correr com duas folhas em vidro temperado liso incolor, com kit de instalação de sensor, modelo ES200. Ref.: Dorma</t>
         </is>
       </c>
       <c r="Y37" s="307" t="n"/>
-      <c r="Z37" s="301" t="inlineStr">
+      <c r="Z37" s="308" t="inlineStr">
         <is>
           <t>D3 - Estante em MDF Nero Rust Ref.: Berneck, desenho conforme detalhamento, Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
 D4 - Armário em marcenaria, estruturado, com espaço para central de sonorização e automação, quadro de distribuição embutido - verificar dimensões com projetos específico, desenho conforme detalhamento. Porta.  de giro com sistema fecho-toque, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
@@ -12349,7 +12437,7 @@
           <t>PISCINA RAIA</t>
         </is>
       </c>
-      <c r="B39" s="316" t="inlineStr">
+      <c r="B39" s="320" t="inlineStr">
         <is>
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -12359,7 +12447,7 @@
       <c r="E39" s="308" t="n"/>
       <c r="F39" s="300" t="n"/>
       <c r="G39" s="300" t="n"/>
-      <c r="H39" s="316" t="inlineStr">
+      <c r="H39" s="320" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12399,7 +12487,7 @@
       <c r="E40" s="308" t="n"/>
       <c r="F40" s="300" t="n"/>
       <c r="G40" s="300" t="n"/>
-      <c r="H40" s="316" t="inlineStr">
+      <c r="H40" s="320" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12438,7 +12526,7 @@
       <c r="C41" s="300" t="n"/>
       <c r="D41" s="307" t="n"/>
       <c r="E41" s="308" t="n"/>
-      <c r="F41" s="301" t="inlineStr">
+      <c r="F41" s="308" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
@@ -12452,7 +12540,7 @@
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
-      <c r="I41" s="316" t="inlineStr">
+      <c r="I41" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil
 T7 - Forro com resistência à umidade, especificação a ser definida. Projeto técnico a ser desenvolvido pelo fornecedor e validado pela GPAA&amp;A.</t>
@@ -12466,13 +12554,13 @@
       <c r="O41" s="307" t="n"/>
       <c r="P41" s="302" t="n"/>
       <c r="Q41" s="300" t="n"/>
-      <c r="R41" s="299" t="inlineStr">
+      <c r="R41" s="307" t="inlineStr">
         <is>
           <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
         </is>
       </c>
       <c r="S41" s="307" t="n"/>
-      <c r="T41" s="299" t="inlineStr">
+      <c r="T41" s="307" t="inlineStr">
         <is>
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
@@ -12483,13 +12571,13 @@
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
-      <c r="V41" s="299" t="inlineStr">
+      <c r="V41" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W41" s="307" t="n"/>
-      <c r="X41" s="299" t="inlineStr">
+      <c r="X41" s="307" t="inlineStr">
         <is>
           <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12549,18 +12637,18 @@
       <c r="O42" s="307" t="n"/>
       <c r="P42" s="302" t="n"/>
       <c r="Q42" s="300" t="n"/>
-      <c r="R42" s="299" t="inlineStr">
+      <c r="R42" s="307" t="inlineStr">
         <is>
           <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
         </is>
       </c>
       <c r="S42" s="307" t="n"/>
-      <c r="T42" s="299" t="inlineStr">
+      <c r="T42" s="307" t="inlineStr">
         <is>
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U42" s="301" t="inlineStr">
+      <c r="U42" s="308" t="inlineStr">
         <is>
           <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
@@ -12667,14 +12755,14 @@
         </is>
       </c>
       <c r="G45" s="300" t="n"/>
-      <c r="H45" s="316" t="inlineStr">
+      <c r="H45" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I45" s="316" t="inlineStr">
+      <c r="I45" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -12687,7 +12775,7 @@
         </is>
       </c>
       <c r="K45" s="300" t="n"/>
-      <c r="L45" s="316" t="inlineStr">
+      <c r="L45" s="320" t="inlineStr">
         <is>
           <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
 D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12695,7 +12783,7 @@
       </c>
       <c r="M45" s="308" t="n"/>
       <c r="N45" s="308" t="n"/>
-      <c r="O45" s="316" t="inlineStr">
+      <c r="O45" s="320" t="inlineStr">
         <is>
           <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
 D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
@@ -12707,13 +12795,13 @@
       <c r="S45" s="307" t="n"/>
       <c r="T45" s="307" t="n"/>
       <c r="U45" s="300" t="n"/>
-      <c r="V45" s="299" t="inlineStr">
+      <c r="V45" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W45" s="307" t="n"/>
-      <c r="X45" s="316" t="inlineStr">
+      <c r="X45" s="320" t="inlineStr">
         <is>
           <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12741,14 +12829,14 @@
         </is>
       </c>
       <c r="G46" s="300" t="n"/>
-      <c r="H46" s="316" t="inlineStr">
+      <c r="H46" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I46" s="316" t="inlineStr">
+      <c r="I46" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -12761,7 +12849,7 @@
         </is>
       </c>
       <c r="K46" s="300" t="n"/>
-      <c r="L46" s="299" t="inlineStr">
+      <c r="L46" s="307" t="inlineStr">
         <is>
           <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
 D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12769,7 +12857,7 @@
       </c>
       <c r="M46" s="308" t="n"/>
       <c r="N46" s="308" t="n"/>
-      <c r="O46" s="316" t="inlineStr">
+      <c r="O46" s="320" t="inlineStr">
         <is>
           <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
 D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
@@ -12781,13 +12869,13 @@
       <c r="S46" s="307" t="n"/>
       <c r="T46" s="307" t="n"/>
       <c r="U46" s="300" t="n"/>
-      <c r="V46" s="299" t="inlineStr">
+      <c r="V46" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W46" s="307" t="n"/>
-      <c r="X46" s="299" t="inlineStr">
+      <c r="X46" s="307" t="inlineStr">
         <is>
           <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
@@ -12801,7 +12889,7 @@
           <t>HALL VESTIÁRIOS</t>
         </is>
       </c>
-      <c r="B47" s="299" t="inlineStr">
+      <c r="B47" s="307" t="inlineStr">
         <is>
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -12809,19 +12897,19 @@
       <c r="C47" s="300" t="n"/>
       <c r="D47" s="307" t="n"/>
       <c r="E47" s="308" t="n"/>
-      <c r="F47" s="301" t="inlineStr">
+      <c r="F47" s="308" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G47" s="300" t="n"/>
-      <c r="H47" s="299" t="inlineStr">
+      <c r="H47" s="307" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I47" s="299" t="inlineStr">
+      <c r="I47" s="307" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -12840,7 +12928,7 @@
       <c r="U47" s="300" t="n"/>
       <c r="V47" s="302" t="n"/>
       <c r="W47" s="307" t="n"/>
-      <c r="X47" s="299" t="inlineStr">
+      <c r="X47" s="307" t="inlineStr">
         <is>
           <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
 D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
@@ -12855,7 +12943,7 @@
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="B48" s="299" t="inlineStr">
+      <c r="B48" s="307" t="inlineStr">
         <is>
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -12863,80 +12951,80 @@
       <c r="C48" s="300" t="n"/>
       <c r="D48" s="307" t="n"/>
       <c r="E48" s="308" t="n"/>
-      <c r="F48" s="301" t="inlineStr">
+      <c r="F48" s="308" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G48" s="300" t="n"/>
-      <c r="H48" s="299" t="inlineStr">
+      <c r="H48" s="307" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I48" s="299" t="inlineStr">
+      <c r="I48" s="307" t="inlineStr">
         <is>
           <t>T8 - Forro em gesso acartonado liso hidrofugante, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J48" s="299" t="inlineStr">
+      <c r="J48" s="307" t="inlineStr">
         <is>
           <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K48" s="301" t="inlineStr">
+      <c r="K48" s="308" t="inlineStr">
         <is>
           <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="L48" s="299" t="inlineStr">
+      <c r="L48" s="307" t="inlineStr">
         <is>
           <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
         </is>
       </c>
       <c r="M48" s="308" t="n"/>
       <c r="N48" s="308" t="n"/>
-      <c r="O48" s="299" t="inlineStr">
+      <c r="O48" s="307" t="inlineStr">
         <is>
           <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
         </is>
       </c>
-      <c r="P48" s="299" t="inlineStr">
+      <c r="P48" s="307" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q48" s="301" t="inlineStr">
+      <c r="Q48" s="308" t="inlineStr">
         <is>
           <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
         </is>
       </c>
       <c r="R48" s="307" t="n"/>
-      <c r="S48" s="299" t="inlineStr">
+      <c r="S48" s="307" t="inlineStr">
         <is>
           <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
         </is>
       </c>
-      <c r="T48" s="299" t="inlineStr">
+      <c r="T48" s="307" t="inlineStr">
         <is>
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U48" s="301" t="inlineStr">
+      <c r="U48" s="308" t="inlineStr">
         <is>
           <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="V48" s="299" t="inlineStr">
+      <c r="V48" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W48" s="307" t="n"/>
-      <c r="X48" s="299" t="n"/>
+      <c r="X48" s="307" t="n"/>
       <c r="Y48" s="307" t="n"/>
-      <c r="Z48" s="301" t="inlineStr">
+      <c r="Z48" s="308" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -12950,7 +13038,7 @@
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="B49" s="299" t="inlineStr">
+      <c r="B49" s="307" t="inlineStr">
         <is>
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -12958,80 +13046,80 @@
       <c r="C49" s="300" t="n"/>
       <c r="D49" s="307" t="n"/>
       <c r="E49" s="308" t="n"/>
-      <c r="F49" s="301" t="inlineStr">
+      <c r="F49" s="308" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G49" s="300" t="n"/>
-      <c r="H49" s="299" t="inlineStr">
+      <c r="H49" s="307" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I49" s="299" t="inlineStr">
+      <c r="I49" s="307" t="inlineStr">
         <is>
           <t>T8 - Forro em gesso acartonado liso hidrofugante, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J49" s="299" t="inlineStr">
+      <c r="J49" s="307" t="inlineStr">
         <is>
           <t>D73 - Bancada em pedra natural, mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="K49" s="301" t="inlineStr">
+      <c r="K49" s="308" t="inlineStr">
         <is>
           <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="L49" s="299" t="inlineStr">
+      <c r="L49" s="307" t="inlineStr">
         <is>
           <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
         </is>
       </c>
       <c r="M49" s="308" t="n"/>
       <c r="N49" s="308" t="n"/>
-      <c r="O49" s="299" t="inlineStr">
+      <c r="O49" s="307" t="inlineStr">
         <is>
           <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
         </is>
       </c>
-      <c r="P49" s="299" t="inlineStr">
+      <c r="P49" s="307" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
-      <c r="Q49" s="301" t="inlineStr">
+      <c r="Q49" s="308" t="inlineStr">
         <is>
           <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
         </is>
       </c>
       <c r="R49" s="307" t="n"/>
-      <c r="S49" s="299" t="inlineStr">
+      <c r="S49" s="307" t="inlineStr">
         <is>
           <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
         </is>
       </c>
-      <c r="T49" s="299" t="inlineStr">
+      <c r="T49" s="307" t="inlineStr">
         <is>
           <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
         </is>
       </c>
-      <c r="U49" s="301" t="inlineStr">
+      <c r="U49" s="308" t="inlineStr">
         <is>
           <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="V49" s="299" t="inlineStr">
+      <c r="V49" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W49" s="307" t="n"/>
-      <c r="X49" s="299" t="n"/>
+      <c r="X49" s="307" t="n"/>
       <c r="Y49" s="307" t="n"/>
-      <c r="Z49" s="301" t="inlineStr">
+      <c r="Z49" s="308" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -13045,7 +13133,7 @@
           <t>DML</t>
         </is>
       </c>
-      <c r="B50" s="316" t="inlineStr">
+      <c r="B50" s="320" t="inlineStr">
         <is>
           <t>P10 - Piso elevado em mármore branco selecionado, lote a ser aprovado, acabamento levigado. Espessura: 3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
@@ -13053,7 +13141,7 @@
       <c r="C50" s="300" t="n"/>
       <c r="D50" s="307" t="n"/>
       <c r="E50" s="308" t="n"/>
-      <c r="F50" s="318" t="inlineStr">
+      <c r="F50" s="317" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
@@ -13064,7 +13152,7 @@
           <t>PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I50" s="316" t="inlineStr">
+      <c r="I50" s="320" t="inlineStr">
         <is>
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -13150,7 +13238,7 @@
 ARQ-PA03 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza, tom a definir.</t>
         </is>
       </c>
-      <c r="I52" s="299" t="inlineStr">
+      <c r="I52" s="307" t="inlineStr">
         <is>
           <t>ARQ-T05 - Cobertura em telha sanduíche com estrutura espacial pintadas na cor cinza tom a definir.</t>
         </is>
@@ -13326,13 +13414,13 @@
       <c r="C55" s="300" t="n"/>
       <c r="D55" s="307" t="n"/>
       <c r="E55" s="308" t="n"/>
-      <c r="F55" s="318" t="inlineStr">
+      <c r="F55" s="317" t="inlineStr">
         <is>
           <t>PA23 - Rodapé em mármore branco selecionado embutido na alvenaria, lote a ser aprovado, acabamento levigado. Arremate de topo com perfil "U" em aço inox 10x10mm. Paginação e dimensões seguem paginação do piso e detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada na GPA&amp;A</t>
         </is>
       </c>
       <c r="G55" s="300" t="n"/>
-      <c r="H55" s="316" t="inlineStr">
+      <c r="H55" s="320" t="inlineStr">
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA47 - Parede em alvenaria emassada regularizada pintada com tinta mineral, cor 930, acabamento CQ. Ref.: Terracor. Amostra a ser aprovada pela GPA&amp;A
@@ -13340,7 +13428,7 @@
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
-      <c r="I55" s="316" t="inlineStr">
+      <c r="I55" s="320" t="inlineStr">
         <is>
           <t>T8 - Forro em gesso acartonado liso hidrofugante, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
@@ -13371,7 +13459,7 @@
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
-      <c r="P55" s="316" t="inlineStr">
+      <c r="P55" s="320" t="inlineStr">
         <is>
           <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
 ► VER IMAGEM (clique)</t>
@@ -13385,7 +13473,7 @@
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
-      <c r="T55" s="299" t="inlineStr">
+      <c r="T55" s="307" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
 D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
@@ -13397,20 +13485,20 @@
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
-      <c r="V55" s="299" t="inlineStr">
+      <c r="V55" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
       </c>
       <c r="W55" s="307" t="n"/>
-      <c r="X55" s="299" t="inlineStr">
+      <c r="X55" s="307" t="inlineStr">
         <is>
           <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
 D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y55" s="307" t="n"/>
-      <c r="Z55" s="318" t="inlineStr">
+      <c r="Z55" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
@@ -13574,7 +13662,7 @@
           <t>CIRCULAÇÃO</t>
         </is>
       </c>
-      <c r="B58" s="316" t="inlineStr">
+      <c r="B58" s="320" t="inlineStr">
         <is>
           <t>PI02 - Contrapiso flutuante: Contrapiso armado sobre painel de lã de vidro, (sistema optma piso, membrana flexível, 15mm de espessura, Ref.: ISOVER. Para evitar fissuras o contrapiso deverá ser armado com tela tipo "pop" soldada
 P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -13583,27 +13671,27 @@
       <c r="C58" s="300" t="n"/>
       <c r="D58" s="307" t="n"/>
       <c r="E58" s="308" t="n"/>
-      <c r="F58" s="318" t="inlineStr">
+      <c r="F58" s="317" t="inlineStr">
         <is>
           <t>PA20 - Rodapé de embutir em alvenaria em cantoneira metálica 50x15mm em alumínio anodizado pintado no tom da parede.</t>
         </is>
       </c>
       <c r="G58" s="300" t="n"/>
-      <c r="H58" s="316" t="inlineStr">
+      <c r="H58" s="320" t="inlineStr">
         <is>
           <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA58 - Pilar em concreto, com enchimento, revestido em pedra natural Basaltina conforme detalhamento.Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="I58" s="316" t="inlineStr">
+      <c r="I58" s="320" t="inlineStr">
         <is>
           <t>FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
       <c r="J58" s="320" t="n"/>
-      <c r="K58" s="318" t="inlineStr">
+      <c r="K58" s="317" t="inlineStr">
         <is>
           <t>D75 - Fechamento decorativo piso teto com quadro fixado no piso e no teto através de espaçadores e fechamento com desenho conforme base para corte de molde em CNC - peças em madeira maciça engenheirada, tonalizada,acabamento escovado, calandradas conforme molde. Ref.: Demuner. ATENÇÃO:a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
@@ -13618,7 +13706,7 @@
       <c r="S58" s="307" t="n"/>
       <c r="T58" s="307" t="n"/>
       <c r="U58" s="300" t="n"/>
-      <c r="V58" s="299" t="inlineStr">
+      <c r="V58" s="307" t="inlineStr">
         <is>
           <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
         </is>
@@ -13634,7 +13722,7 @@
           <t>ESTAR PISCINA / CIRCULAÇÃO</t>
         </is>
       </c>
-      <c r="B59" s="316" t="inlineStr">
+      <c r="B59" s="320" t="inlineStr">
         <is>
           <t>P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
 P8 - Piso elevado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofulgante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
@@ -13667,7 +13755,7 @@
       <c r="W59" s="307" t="n"/>
       <c r="X59" s="307" t="n"/>
       <c r="Y59" s="307" t="n"/>
-      <c r="Z59" s="301" t="inlineStr">
+      <c r="Z59" s="308" t="inlineStr">
         <is>
           <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
         </is>
@@ -13726,7 +13814,7 @@
       <c r="E61" s="308" t="n"/>
       <c r="F61" s="317" t="n"/>
       <c r="G61" s="300" t="n"/>
-      <c r="H61" s="316" t="inlineStr">
+      <c r="H61" s="320" t="inlineStr">
         <is>
           <t>ARQ-PA06 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica fosca cinza tom a definir. Meia parede pintada com tinta acrílica fosca na cor verde, tom a definir. Verificar altura conforme detalhamento.</t>
         </is>
@@ -13798,7 +13886,7 @@
           <t>APOIO QUADRAS</t>
         </is>
       </c>
-      <c r="B63" s="316" t="inlineStr">
+      <c r="B63" s="320" t="inlineStr">
         <is>
           <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
 P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
@@ -13810,7 +13898,7 @@
       <c r="F63" s="317" t="n"/>
       <c r="G63" s="300" t="n"/>
       <c r="H63" s="320" t="n"/>
-      <c r="I63" s="316" t="inlineStr">
+      <c r="I63" s="320" t="inlineStr">
         <is>
           <t>FO2 - Forro em gesso acartonado perfurado de absorção acústica, modelo cleneo quadrado, furação 12/25, sistema de instalação tipo FGE - estruturado, Ref.: Knauf Ceiling Solutions ou similar. Bordas ou "tabeiras" em gesso liso, com acabamento em tinta acrílica fosca, cor branco neve. Preenchimento superior com 1 manta de lã de pet com 35Kg/m³ de densidade de 50mm de espessura, Ref.: Trisoft ou similar.
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
@@ -13840,7 +13928,7 @@
           <t>CIRCULAÇÃO JUNTO À ESCADA (A=2,91 m²)</t>
         </is>
       </c>
-      <c r="B64" s="316" t="inlineStr">
+      <c r="B64" s="320" t="inlineStr">
         <is>
           <t>ARQ-P03 - Piso em concreto mecanizado com acabamento antiderrapante</t>
         </is>
@@ -13850,12 +13938,12 @@
       <c r="E64" s="308" t="n"/>
       <c r="F64" s="317" t="n"/>
       <c r="G64" s="300" t="n"/>
-      <c r="H64" s="316" t="inlineStr">
+      <c r="H64" s="320" t="inlineStr">
         <is>
           <t>ARQ-PA09 - Parede em alvenaria, emassada e regularizada, revestida em textura acrílica rolada fosca branca. Ref.: Branco Neve; Suvinil.</t>
         </is>
       </c>
-      <c r="I64" s="316" t="inlineStr">
+      <c r="I64" s="320" t="inlineStr">
         <is>
           <t>ARQ-T02 - Laje em concreto aparente com tratamento a ser indicado pelo projeto estrutural.</t>
         </is>
@@ -14611,7 +14699,7 @@
           <t>SALA / VARANDA DA SALA</t>
         </is>
       </c>
-      <c r="B13" s="299" t="inlineStr">
+      <c r="B13" s="307" t="inlineStr">
         <is>
           <t>Piso em mármore travertino romano bruto, 85x130cm, paginação conforme detalhamento. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). (DET PR001/PR002; Tab. R01)</t>
         </is>
@@ -14626,12 +14714,12 @@
         </is>
       </c>
       <c r="G13" s="300" t="n"/>
-      <c r="H13" s="301" t="inlineStr">
+      <c r="H13" s="308" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve, acabamento acetinado. (DET PR001; Tab. R01)</t>
         </is>
       </c>
-      <c r="I13" s="301" t="n"/>
+      <c r="I13" s="308" t="n"/>
       <c r="J13" s="300" t="n"/>
       <c r="K13" s="300" t="n"/>
       <c r="L13" s="300" t="n"/>
@@ -14664,7 +14752,7 @@
           <t>LAVABO</t>
         </is>
       </c>
-      <c r="B14" s="299" t="inlineStr">
+      <c r="B14" s="307" t="inlineStr">
         <is>
           <t>Piso em mármore travertino romano bruto. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). (DET PR004; Tab. R01)</t>
         </is>
@@ -14683,12 +14771,12 @@
         </is>
       </c>
       <c r="G14" s="300" t="n"/>
-      <c r="H14" s="301" t="inlineStr">
+      <c r="H14" s="308" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve, acabamento acetinado. (DET PR004; Tab. R01)</t>
         </is>
       </c>
-      <c r="I14" s="301" t="inlineStr">
+      <c r="I14" s="308" t="inlineStr">
         <is>
           <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica. PD 298cm. (DET PR004)</t>
         </is>
@@ -14746,7 +14834,7 @@
           <t>BANHO SUÍTE MASTER</t>
         </is>
       </c>
-      <c r="B15" s="299" t="inlineStr">
+      <c r="B15" s="307" t="inlineStr">
         <is>
           <t>11 - Piso em contrapiso regularizado, revestido em mármore travertino romano resinado. Rejunte creme ou marfim (ver padrão da chapa). Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408; Tab. R01: "bruto resinado")</t>
         </is>
@@ -14771,7 +14859,7 @@
 CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
         </is>
       </c>
-      <c r="I15" s="301" t="inlineStr">
+      <c r="I15" s="308" t="inlineStr">
         <is>
           <t>1 - Forro em gesso acartonado liso, tinta acrílica cor branco neve, acabamento fosco, junta de dilatação metálica branca. Ref.: Suvinil. Sanca (DET 20). (PR408)</t>
         </is>
@@ -14850,7 +14938,7 @@
           <t>BANHO SUÍTES</t>
         </is>
       </c>
-      <c r="B16" s="299" t="inlineStr">
+      <c r="B16" s="307" t="inlineStr">
         <is>
           <t>Piso em mármore travertino romano bruto resinado, paginado. Rejunte Infinity Hard, cor Areia ou Palha (validar com o Setor de Produto). Desnível do box 1cm. (DET PR008; Tab. R01)</t>
         </is>
@@ -14860,12 +14948,12 @@
       <c r="E16" s="300" t="n"/>
       <c r="F16" s="300" t="n"/>
       <c r="G16" s="300" t="n"/>
-      <c r="H16" s="301" t="inlineStr">
+      <c r="H16" s="308" t="inlineStr">
         <is>
           <t>Parede em mármore travertino romano bruto: piso ao teto na área do box e barrado semi-embutido até 110cm nas demais paredes; acima, pintura acrílica cor branco neve, acetinado. (DET PR008; Tab. R01)</t>
         </is>
       </c>
-      <c r="I16" s="301" t="inlineStr">
+      <c r="I16" s="308" t="inlineStr">
         <is>
           <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica e sanca. PD 298cm. (DET PR008)</t>
         </is>
@@ -14926,7 +15014,7 @@
           <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
         </is>
       </c>
-      <c r="B17" s="299" t="inlineStr">
+      <c r="B17" s="307" t="inlineStr">
         <is>
           <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (DET PR001/PR002; Tab. R01)</t>
         </is>
@@ -14945,12 +15033,12 @@
         </is>
       </c>
       <c r="G17" s="300" t="n"/>
-      <c r="H17" s="301" t="inlineStr">
+      <c r="H17" s="308" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve. (Tab. R01)</t>
         </is>
       </c>
-      <c r="I17" s="301" t="n"/>
+      <c r="I17" s="308" t="n"/>
       <c r="J17" s="300" t="n"/>
       <c r="K17" s="300" t="n"/>
       <c r="L17" s="300" t="n"/>
@@ -14975,7 +15063,7 @@
           <t>COPA NOTURNA</t>
         </is>
       </c>
-      <c r="B18" s="299" t="inlineStr">
+      <c r="B18" s="307" t="inlineStr">
         <is>
           <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (Tab. R01)</t>
         </is>
@@ -14989,8 +15077,8 @@
         </is>
       </c>
       <c r="G18" s="300" t="n"/>
-      <c r="H18" s="301" t="n"/>
-      <c r="I18" s="301" t="n"/>
+      <c r="H18" s="308" t="n"/>
+      <c r="I18" s="308" t="n"/>
       <c r="J18" s="304" t="inlineStr">
         <is>
           <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)
@@ -15028,7 +15116,7 @@
           <t>COZINHA / DESPENSAS</t>
         </is>
       </c>
-      <c r="B19" s="299" t="inlineStr">
+      <c r="B19" s="307" t="inlineStr">
         <is>
           <t>Piso em granito branco siena escovado, 85x130cm. Rejunte Infinity Hard, cor Branco Pérola ou Palha (validar com o Setor de Produto). (DET PR001, PR406/407; Tab. R01: paginação a definir)</t>
         </is>
@@ -15046,13 +15134,13 @@
         </is>
       </c>
       <c r="G19" s="300" t="n"/>
-      <c r="H19" s="301" t="inlineStr">
+      <c r="H19" s="308" t="inlineStr">
         <is>
           <t>Rodabanca em granito branco siena escovado, h=60cm
 Pintura acrílica; cor a definir (Tab. R01). (PR406/407)</t>
         </is>
       </c>
-      <c r="I19" s="301" t="n"/>
+      <c r="I19" s="308" t="n"/>
       <c r="J19" s="300" t="inlineStr">
         <is>
           <t>Bancada e ilha em granito branco siena escovado; parte seca h=90cm, área molhada com desnível 1cm h=92cm; suporte em metalon chumbado na parede; emendas seguem a paginação do piso. (PR406/407; Tab. R01)</t>
@@ -15093,7 +15181,7 @@
           <t>ÁREA DE SERVIÇO / CIRCULAÇÃO SERVIÇO</t>
         </is>
       </c>
-      <c r="B20" s="299" t="inlineStr">
+      <c r="B20" s="307" t="inlineStr">
         <is>
           <t>Piso em granito branco siena escovado, 85x130cm, ver paginação. Rejunte Infinity Hard, cor Branco Pérola ou Palha. (DET PR001, PR005; Tab. R01)</t>
         </is>
@@ -15111,12 +15199,12 @@
         </is>
       </c>
       <c r="G20" s="300" t="n"/>
-      <c r="H20" s="301" t="inlineStr">
+      <c r="H20" s="308" t="inlineStr">
         <is>
           <t>Parede em Formica Branco Real L515, 308x125cm. (DET PR005/PR006; Tab. R01)</t>
         </is>
       </c>
-      <c r="I20" s="301" t="inlineStr">
+      <c r="I20" s="308" t="inlineStr">
         <is>
           <t>Forro de gesso com tabica metálica (DET 11) e cortineiro 25x16cm (DET 24). (DET PR006)</t>
         </is>
@@ -15174,7 +15262,7 @@
           <t>BANHO SERVIÇO</t>
         </is>
       </c>
-      <c r="B21" s="299" t="inlineStr">
+      <c r="B21" s="307" t="inlineStr">
         <is>
           <t>Piso em granito branco siena escovado. (DET PR007; Tab. R01: paginação a definir)</t>
         </is>
@@ -15188,12 +15276,12 @@
       <c r="E21" s="300" t="n"/>
       <c r="F21" s="300" t="n"/>
       <c r="G21" s="300" t="n"/>
-      <c r="H21" s="301" t="inlineStr">
+      <c r="H21" s="308" t="inlineStr">
         <is>
           <t>Revestimento Forma Branco AC retificado 32,5x59cm. Ref.: Eliane. (DET PR007; Tab. R01)</t>
         </is>
       </c>
-      <c r="I21" s="301" t="inlineStr">
+      <c r="I21" s="308" t="inlineStr">
         <is>
           <t>Forro em gesso acartonado, pintura acrílica acetinada cor branco neve, tabica metálica, sanca 25x16cm. PD 298cm. (DET PR007)</t>
         </is>
@@ -15250,7 +15338,7 @@
           <t>QUARTO / ESTAR FUNCIONÁRIOS</t>
         </is>
       </c>
-      <c r="B22" s="299" t="inlineStr">
+      <c r="B22" s="307" t="inlineStr">
         <is>
           <t>Piso vinílico Austin, linha Urban, 18x121cm. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
         </is>
@@ -15268,12 +15356,12 @@
         </is>
       </c>
       <c r="G22" s="300" t="n"/>
-      <c r="H22" s="301" t="inlineStr">
+      <c r="H22" s="308" t="inlineStr">
         <is>
           <t>Pintura acrílica cor branco neve. (Tab. R01)</t>
         </is>
       </c>
-      <c r="I22" s="301" t="n"/>
+      <c r="I22" s="308" t="n"/>
       <c r="J22" s="300" t="n"/>
       <c r="K22" s="300" t="n"/>
       <c r="L22" s="300" t="n"/>
@@ -15298,7 +15386,7 @@
           <t>VARANDA TÉCNICA</t>
         </is>
       </c>
-      <c r="B23" s="299" t="inlineStr">
+      <c r="B23" s="307" t="inlineStr">
         <is>
           <t>Piso em concreto. (DET PR001)</t>
         </is>
@@ -15308,8 +15396,8 @@
       <c r="E23" s="300" t="n"/>
       <c r="F23" s="300" t="n"/>
       <c r="G23" s="300" t="n"/>
-      <c r="H23" s="301" t="n"/>
-      <c r="I23" s="301" t="n"/>
+      <c r="H23" s="308" t="n"/>
+      <c r="I23" s="308" t="n"/>
       <c r="J23" s="300" t="n"/>
       <c r="K23" s="300" t="n"/>
       <c r="L23" s="300" t="n"/>
@@ -15334,7 +15422,7 @@
           <t>HALL ELEVADOR SOCIAL (ANDAR)</t>
         </is>
       </c>
-      <c r="B24" s="299" t="inlineStr">
+      <c r="B24" s="307" t="inlineStr">
         <is>
           <t>Piso em mármore travertino romano bruto. (DET PR003)</t>
         </is>
@@ -15348,13 +15436,13 @@
         </is>
       </c>
       <c r="G24" s="300" t="n"/>
-      <c r="H24" s="301" t="inlineStr">
+      <c r="H24" s="308" t="inlineStr">
         <is>
           <t>Parede pintada com tinta acrílica cor branco neve, acabamento acetinado
 Aduela do elevador (2cm) em mármore travertino romano bruto. (DET PR003)</t>
         </is>
       </c>
-      <c r="I24" s="301" t="n"/>
+      <c r="I24" s="308" t="n"/>
       <c r="J24" s="300" t="n"/>
       <c r="K24" s="300" t="n"/>
       <c r="L24" s="300" t="n"/>
@@ -15379,7 +15467,7 @@
           <t>HALL ELEVADOR SERVIÇO (ANDAR)</t>
         </is>
       </c>
-      <c r="B25" s="299" t="inlineStr">
+      <c r="B25" s="307" t="inlineStr">
         <is>
           <t>Piso em granito branco siena escovado. (DET PR003)</t>
         </is>
@@ -15393,13 +15481,13 @@
         </is>
       </c>
       <c r="G25" s="300" t="n"/>
-      <c r="H25" s="301" t="inlineStr">
+      <c r="H25" s="308" t="inlineStr">
         <is>
           <t>Parede pintada com tinta acrílica cor branco neve, acabamento acetinado
 Aduela do elevador (2cm) em granito branco siena escovado. (DET PR003)</t>
         </is>
       </c>
-      <c r="I25" s="301" t="n"/>
+      <c r="I25" s="308" t="n"/>
       <c r="J25" s="300" t="n"/>
       <c r="K25" s="300" t="n"/>
       <c r="L25" s="300" t="n"/>
@@ -15424,7 +15512,7 @@
           <t>HALL SERVIÇO / ANTECÂMARA – GARDEN, TIPO E COBERTURA</t>
         </is>
       </c>
-      <c r="B26" s="299" t="inlineStr">
+      <c r="B26" s="307" t="inlineStr">
         <is>
           <t>Piso em granito ("revestimento conforme ambiente"). (PR721-728)</t>
         </is>
@@ -15438,12 +15526,12 @@
         </is>
       </c>
       <c r="G26" s="300" t="n"/>
-      <c r="H26" s="301" t="inlineStr">
+      <c r="H26" s="308" t="inlineStr">
         <is>
           <t>Parede pintada. (PR722/724/726/728)</t>
         </is>
       </c>
-      <c r="I26" s="301" t="inlineStr">
+      <c r="I26" s="308" t="inlineStr">
         <is>
           <t>Forro em gesso com sanca: PD 259cm (Garden e Tipo), 267,5cm (Cobertura 1º nível), 272,5cm (Cobertura 2º nível); junta de dilatação em perfil metálico "Z" (DET 09); trechos em laje de concreto aparente. (PR721-728)</t>
         </is>
@@ -15476,14 +15564,14 @@
     </row>
     <row r="27">
       <c r="A27" s="45" t="n"/>
-      <c r="B27" s="269" t="n"/>
+      <c r="B27" s="31" t="n"/>
       <c r="C27" s="32" t="n"/>
       <c r="D27" s="32" t="n"/>
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n"/>
-      <c r="H27" s="271" t="n"/>
-      <c r="I27" s="271" t="n"/>
+      <c r="H27" s="33" t="n"/>
+      <c r="I27" s="33" t="n"/>
       <c r="J27" s="32" t="n"/>
       <c r="K27" s="32" t="n"/>
       <c r="L27" s="32" t="n"/>
@@ -15504,14 +15592,14 @@
     </row>
     <row r="28">
       <c r="A28" s="45" t="n"/>
-      <c r="B28" s="269" t="n"/>
+      <c r="B28" s="31" t="n"/>
       <c r="C28" s="32" t="n"/>
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="32" t="n"/>
       <c r="F28" s="32" t="n"/>
       <c r="G28" s="32" t="n"/>
-      <c r="H28" s="271" t="n"/>
-      <c r="I28" s="271" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="33" t="n"/>
       <c r="J28" s="32" t="n"/>
       <c r="K28" s="32" t="n"/>
       <c r="L28" s="32" t="n"/>
@@ -15532,14 +15620,14 @@
     </row>
     <row r="29">
       <c r="A29" s="45" t="n"/>
-      <c r="B29" s="269" t="n"/>
+      <c r="B29" s="31" t="n"/>
       <c r="C29" s="32" t="n"/>
       <c r="D29" s="32" t="n"/>
       <c r="E29" s="32" t="n"/>
       <c r="F29" s="32" t="n"/>
       <c r="G29" s="32" t="n"/>
-      <c r="H29" s="271" t="n"/>
-      <c r="I29" s="271" t="n"/>
+      <c r="H29" s="33" t="n"/>
+      <c r="I29" s="33" t="n"/>
       <c r="J29" s="32" t="n"/>
       <c r="K29" s="32" t="n"/>
       <c r="L29" s="32" t="n"/>
@@ -15560,14 +15648,14 @@
     </row>
     <row r="30">
       <c r="A30" s="45" t="n"/>
-      <c r="B30" s="269" t="n"/>
+      <c r="B30" s="31" t="n"/>
       <c r="C30" s="32" t="n"/>
       <c r="D30" s="32" t="n"/>
       <c r="E30" s="32" t="n"/>
       <c r="F30" s="32" t="n"/>
       <c r="G30" s="32" t="n"/>
-      <c r="H30" s="271" t="n"/>
-      <c r="I30" s="271" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
       <c r="J30" s="32" t="n"/>
       <c r="K30" s="32" t="n"/>
       <c r="L30" s="32" t="n"/>
@@ -15588,14 +15676,14 @@
     </row>
     <row r="31">
       <c r="A31" s="45" t="n"/>
-      <c r="B31" s="269" t="n"/>
+      <c r="B31" s="31" t="n"/>
       <c r="C31" s="32" t="n"/>
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="32" t="n"/>
-      <c r="H31" s="271" t="n"/>
-      <c r="I31" s="271" t="n"/>
+      <c r="H31" s="33" t="n"/>
+      <c r="I31" s="33" t="n"/>
       <c r="J31" s="32" t="n"/>
       <c r="K31" s="32" t="n"/>
       <c r="L31" s="32" t="n"/>
@@ -15679,6 +15767,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="328" t="inlineStr">
+        <is>
+          <t>GRADE DE ESPECIFICAÇÕES · EDIFÍCIO JARDIM · ESPECIFICAÇÕES CONFLITANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="329" t="inlineStr">
+        <is>
+          <t>Células em que projetos diferentes trazem especificações diferentes para o mesmo item. As duas versões foram mantidas na grade, em vermelho claro, até a definição da arquitetura. Clique na célula (coluna F) para ir até ela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="330" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="330" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C4" s="330" t="inlineStr">
+        <is>
+          <t>AMBIENTE</t>
+        </is>
+      </c>
+      <c r="D4" s="330" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
+      <c r="E4" s="330" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="F4" s="330" t="inlineStr">
+        <is>
+          <t>CÉLULA</t>
+        </is>
+      </c>
+      <c r="G4" s="330" t="inlineStr">
+        <is>
+          <t>ESPECIFICAÇÕES CONFLITANTES (versões e fontes)</t>
+        </is>
+      </c>
+      <c r="H4" s="330" t="inlineStr">
+        <is>
+          <t>DEFINIÇÃO DA ARQUITETURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="117" customHeight="1">
+      <c r="A5" s="331" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="331" t="inlineStr">
+        <is>
+          <t>TÉRREO</t>
+        </is>
+      </c>
+      <c r="C5" s="332" t="inlineStr">
+        <is>
+          <t>GUARITA</t>
+        </is>
+      </c>
+      <c r="D5" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E5" s="331" t="inlineStr">
+        <is>
+          <t>PISO/REJUNTE</t>
+        </is>
+      </c>
+      <c r="F5" s="333" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="G5" s="334" t="inlineStr">
+        <is>
+          <t>P5 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Rejunte Infinity Hard cor Mocha ou cor Branco Pérola Deverá ser testado as duas opções de rejunte para escolher a que mais se aproxima do tom da peça. Amostra a ser aprovada pela GPA&amp;A.
+CONFLITO – Arquitetura: ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="H5" s="331" t="inlineStr"/>
+    </row>
+    <row r="6" ht="87" customHeight="1">
+      <c r="A6" s="331" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="331" t="inlineStr">
+        <is>
+          <t>TÉRREO</t>
+        </is>
+      </c>
+      <c r="C6" s="332" t="inlineStr">
+        <is>
+          <t>GUARITA</t>
+        </is>
+      </c>
+      <c r="D6" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E6" s="331" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="F6" s="333" t="inlineStr">
+        <is>
+          <t>H17</t>
+        </is>
+      </c>
+      <c r="G6" s="334" t="inlineStr">
+        <is>
+          <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+CONFLITO – Arquitetura: ARQ-PA02 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor a definir, acabamento acetinado.</t>
+        </is>
+      </c>
+      <c r="H6" s="331" t="inlineStr"/>
+    </row>
+    <row r="7" ht="102" customHeight="1">
+      <c r="A7" s="331" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C7" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="D7" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E7" s="331" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="F7" s="333" t="inlineStr">
+        <is>
+          <t>J35</t>
+        </is>
+      </c>
+      <c r="G7" s="334" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
+        </is>
+      </c>
+      <c r="H7" s="331" t="inlineStr"/>
+    </row>
+    <row r="8" ht="87" customHeight="1">
+      <c r="A8" s="331" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C8" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="D8" s="331" t="inlineStr">
+        <is>
+          <t>LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="E8" s="331" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="F8" s="333" t="inlineStr">
+        <is>
+          <t>O35</t>
+        </is>
+      </c>
+      <c r="G8" s="334" t="inlineStr">
+        <is>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+        </is>
+      </c>
+      <c r="H8" s="331" t="inlineStr"/>
+    </row>
+    <row r="9" ht="102" customHeight="1">
+      <c r="A9" s="331" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C9" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="D9" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E9" s="331" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="F9" s="333" t="inlineStr">
+        <is>
+          <t>J36</t>
+        </is>
+      </c>
+      <c r="G9" s="334" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
+        </is>
+      </c>
+      <c r="H9" s="331" t="inlineStr"/>
+    </row>
+    <row r="10" ht="87" customHeight="1">
+      <c r="A10" s="331" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C10" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="D10" s="331" t="inlineStr">
+        <is>
+          <t>LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="E10" s="331" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="F10" s="333" t="inlineStr">
+        <is>
+          <t>O36</t>
+        </is>
+      </c>
+      <c r="G10" s="334" t="inlineStr">
+        <is>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+        </is>
+      </c>
+      <c r="H10" s="331" t="inlineStr"/>
+    </row>
+    <row r="11" ht="57" customHeight="1">
+      <c r="A11" s="331" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="331" t="inlineStr">
+        <is>
+          <t>APTO TIPO</t>
+        </is>
+      </c>
+      <c r="C11" s="332" t="inlineStr">
+        <is>
+          <t>SALA / VARANDA DA SALA</t>
+        </is>
+      </c>
+      <c r="D11" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E11" s="331" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="F11" s="333" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="G11" s="334" t="inlineStr">
+        <is>
+          <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR001/PR002)
+CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+        </is>
+      </c>
+      <c r="H11" s="331" t="inlineStr"/>
+    </row>
+    <row r="12" ht="57" customHeight="1">
+      <c r="A12" s="331" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="331" t="inlineStr">
+        <is>
+          <t>APTO TIPO</t>
+        </is>
+      </c>
+      <c r="C12" s="332" t="inlineStr">
+        <is>
+          <t>LAVABO</t>
+        </is>
+      </c>
+      <c r="D12" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E12" s="331" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="F12" s="333" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="G12" s="334" t="inlineStr">
+        <is>
+          <t>Rodapé semi-embutido em mármore travertino romano bruto, h=15cm. (DET PR004)
+CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+        </is>
+      </c>
+      <c r="H12" s="331" t="inlineStr"/>
+    </row>
+    <row r="13" ht="117" customHeight="1">
+      <c r="A13" s="331" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="331" t="inlineStr">
+        <is>
+          <t>APTO TIPO</t>
+        </is>
+      </c>
+      <c r="C13" s="332" t="inlineStr">
+        <is>
+          <t>BANHO SUÍTE MASTER</t>
+        </is>
+      </c>
+      <c r="D13" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E13" s="331" t="inlineStr">
+        <is>
+          <t>PAREDE/REJUNTE</t>
+        </is>
+      </c>
+      <c r="F13" s="333" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="G13" s="334" t="inlineStr">
+        <is>
+          <t>14 - Parede revestida em mármore travertino romano resinado. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408)
+1 - Parede em alvenaria emassada e regularizada, pintada com tinta acrílica cor branco neve, acabamento acetinado. Ref.: Suvinil. (PR408)
+CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
+        </is>
+      </c>
+      <c r="H13" s="331" t="inlineStr"/>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="331" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="331" t="inlineStr">
+        <is>
+          <t>APTO TIPO</t>
+        </is>
+      </c>
+      <c r="C14" s="332" t="inlineStr">
+        <is>
+          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
+        </is>
+      </c>
+      <c r="D14" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E14" s="331" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="F14" s="333" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="G14" s="334" t="inlineStr">
+        <is>
+          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
+CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
+        </is>
+      </c>
+      <c r="H14" s="331" t="inlineStr"/>
+    </row>
+    <row r="15" ht="57" customHeight="1">
+      <c r="A15" s="331" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="331" t="inlineStr">
+        <is>
+          <t>APTO TIPO</t>
+        </is>
+      </c>
+      <c r="C15" s="332" t="inlineStr">
+        <is>
+          <t>COPA NOTURNA</t>
+        </is>
+      </c>
+      <c r="D15" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E15" s="331" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="F15" s="333" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="G15" s="334" t="inlineStr">
+        <is>
+          <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)
+CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
+        </is>
+      </c>
+      <c r="H15" s="331" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F5" location="'TÉRREO '!B17" tooltip="Ir para TÉRREO B17"/>
+    <hyperlink ref="F6" location="'TÉRREO '!H17" tooltip="Ir para TÉRREO H17"/>
+    <hyperlink ref="F7" location="'PILOTIS'!J35" tooltip="Ir para PILOTIS J35"/>
+    <hyperlink ref="F8" location="'PILOTIS'!O35" tooltip="Ir para PILOTIS O35"/>
+    <hyperlink ref="F9" location="'PILOTIS'!J36" tooltip="Ir para PILOTIS J36"/>
+    <hyperlink ref="F10" location="'PILOTIS'!O36" tooltip="Ir para PILOTIS O36"/>
+    <hyperlink ref="F11" location="'APTO TIPO'!F13" tooltip="Ir para APTO TIPO F13"/>
+    <hyperlink ref="F12" location="'APTO TIPO'!F14" tooltip="Ir para APTO TIPO F14"/>
+    <hyperlink ref="F13" location="'APTO TIPO'!H15" tooltip="Ir para APTO TIPO H15"/>
+    <hyperlink ref="F14" location="'APTO TIPO'!F17" tooltip="Ir para APTO TIPO F17"/>
+    <hyperlink ref="F15" location="'APTO TIPO'!J18" tooltip="Ir para APTO TIPO J18"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -12171,10 +12171,10 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J35" s="321" t="inlineStr">
+      <c r="J35" s="320" t="inlineStr">
         <is>
           <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
+OBS. – As pranchas 37 e 38 do detalhamento R04 indicam bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível (ver PENDÊNCIAS).</t>
         </is>
       </c>
       <c r="K35" s="317" t="inlineStr">
@@ -12185,10 +12185,10 @@
       <c r="L35" s="307" t="n"/>
       <c r="M35" s="308" t="n"/>
       <c r="N35" s="308" t="n"/>
-      <c r="O35" s="321" t="inlineStr">
+      <c r="O35" s="320" t="inlineStr">
         <is>
           <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+OBS. – As pranchas 37 e 38 do detalhamento R04 indicam torneira de mesa bica baixa Argon, Docol (ver PENDÊNCIAS).</t>
         </is>
       </c>
       <c r="P35" s="320" t="inlineStr">
@@ -12266,10 +12266,10 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J36" s="321" t="inlineStr">
+      <c r="J36" s="320" t="inlineStr">
         <is>
           <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
+OBS. – As pranchas 37 e 38 do detalhamento R04 indicam bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível (ver PENDÊNCIAS).</t>
         </is>
       </c>
       <c r="K36" s="317" t="inlineStr">
@@ -12280,10 +12280,10 @@
       <c r="L36" s="307" t="n"/>
       <c r="M36" s="308" t="n"/>
       <c r="N36" s="308" t="n"/>
-      <c r="O36" s="321" t="inlineStr">
+      <c r="O36" s="320" t="inlineStr">
         <is>
           <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+OBS. – As pranchas 37 e 38 do detalhamento R04 indicam torneira de mesa bica baixa Argon, Docol (ver PENDÊNCIAS).</t>
         </is>
       </c>
       <c r="P36" s="320" t="inlineStr">
@@ -14693,7 +14693,7 @@
       <c r="Y12" s="241" t="n"/>
       <c r="Z12" s="242" t="n"/>
     </row>
-    <row r="13" ht="89" customHeight="1">
+    <row r="13" ht="74" customHeight="1">
       <c r="A13" s="298" t="inlineStr">
         <is>
           <t>SALA / VARANDA DA SALA</t>
@@ -14707,10 +14707,9 @@
       <c r="C13" s="300" t="n"/>
       <c r="D13" s="300" t="n"/>
       <c r="E13" s="300" t="n"/>
-      <c r="F13" s="304" t="inlineStr">
-        <is>
-          <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR001/PR002)
-CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+      <c r="F13" s="317" t="inlineStr">
+        <is>
+          <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR001/PR002)</t>
         </is>
       </c>
       <c r="G13" s="300" t="n"/>
@@ -14764,10 +14763,9 @@
       </c>
       <c r="D14" s="300" t="n"/>
       <c r="E14" s="300" t="n"/>
-      <c r="F14" s="304" t="inlineStr">
-        <is>
-          <t>Rodapé semi-embutido em mármore travertino romano bruto, h=15cm. (DET PR004)
-CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+      <c r="F14" s="317" t="inlineStr">
+        <is>
+          <t>Rodapé semi-embutido em mármore travertino romano bruto, h=15cm. (DET PR004)</t>
         </is>
       </c>
       <c r="G14" s="300" t="n"/>
@@ -14828,7 +14826,7 @@
       <c r="Y14" s="302" t="n"/>
       <c r="Z14" s="300" t="n"/>
     </row>
-    <row r="15" ht="119" customHeight="1">
+    <row r="15" ht="104" customHeight="1">
       <c r="A15" s="298" t="inlineStr">
         <is>
           <t>BANHO SUÍTE MASTER</t>
@@ -14852,11 +14850,10 @@
         </is>
       </c>
       <c r="G15" s="300" t="n"/>
-      <c r="H15" s="304" t="inlineStr">
+      <c r="H15" s="317" t="inlineStr">
         <is>
           <t>14 - Parede revestida em mármore travertino romano resinado. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408)
-1 - Parede em alvenaria emassada e regularizada, pintada com tinta acrílica cor branco neve, acabamento acetinado. Ref.: Suvinil. (PR408)
-CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
+1 - Parede em alvenaria emassada e regularizada, pintada com tinta acrílica cor branco neve, acabamento acetinado. Ref.: Suvinil. (PR408)</t>
         </is>
       </c>
       <c r="I15" s="308" t="inlineStr">
@@ -15026,10 +15023,10 @@
         </is>
       </c>
       <c r="E17" s="300" t="n"/>
-      <c r="F17" s="304" t="inlineStr">
+      <c r="F17" s="317" t="inlineStr">
         <is>
           <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
-CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
+OBS. – A legenda de rodapé do DET PR001/PR002 indica h=6,5cm (ver PENDÊNCIAS).</t>
         </is>
       </c>
       <c r="G17" s="300" t="n"/>
@@ -15057,7 +15054,7 @@
       <c r="Y17" s="302" t="n"/>
       <c r="Z17" s="300" t="n"/>
     </row>
-    <row r="18" ht="89" customHeight="1">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="298" t="inlineStr">
         <is>
           <t>COPA NOTURNA</t>
@@ -15079,10 +15076,9 @@
       <c r="G18" s="300" t="n"/>
       <c r="H18" s="308" t="n"/>
       <c r="I18" s="308" t="n"/>
-      <c r="J18" s="304" t="inlineStr">
-        <is>
-          <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)
-CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
+      <c r="J18" s="317" t="inlineStr">
+        <is>
+          <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)</t>
         </is>
       </c>
       <c r="K18" s="300" t="n"/>
@@ -15767,7 +15763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15911,340 +15907,6 @@
       </c>
       <c r="H6" s="331" t="inlineStr"/>
     </row>
-    <row r="7" ht="102" customHeight="1">
-      <c r="A7" s="331" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="331" t="inlineStr">
-        <is>
-          <t>PILOTIS</t>
-        </is>
-      </c>
-      <c r="C7" s="332" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEMININO</t>
-        </is>
-      </c>
-      <c r="D7" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E7" s="331" t="inlineStr">
-        <is>
-          <t>BANCADA</t>
-        </is>
-      </c>
-      <c r="F7" s="333" t="inlineStr">
-        <is>
-          <t>J35</t>
-        </is>
-      </c>
-      <c r="G7" s="334" t="inlineStr">
-        <is>
-          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
-        </is>
-      </c>
-      <c r="H7" s="331" t="inlineStr"/>
-    </row>
-    <row r="8" ht="87" customHeight="1">
-      <c r="A8" s="331" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="331" t="inlineStr">
-        <is>
-          <t>PILOTIS</t>
-        </is>
-      </c>
-      <c r="C8" s="332" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO FEMININO</t>
-        </is>
-      </c>
-      <c r="D8" s="331" t="inlineStr">
-        <is>
-          <t>LOUÇAS E METAIS</t>
-        </is>
-      </c>
-      <c r="E8" s="331" t="inlineStr">
-        <is>
-          <t>TORNEIRAS</t>
-        </is>
-      </c>
-      <c r="F8" s="333" t="inlineStr">
-        <is>
-          <t>O35</t>
-        </is>
-      </c>
-      <c r="G8" s="334" t="inlineStr">
-        <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
-        </is>
-      </c>
-      <c r="H8" s="331" t="inlineStr"/>
-    </row>
-    <row r="9" ht="102" customHeight="1">
-      <c r="A9" s="331" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="331" t="inlineStr">
-        <is>
-          <t>PILOTIS</t>
-        </is>
-      </c>
-      <c r="C9" s="332" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO MASCULINO</t>
-        </is>
-      </c>
-      <c r="D9" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E9" s="331" t="inlineStr">
-        <is>
-          <t>BANCADA</t>
-        </is>
-      </c>
-      <c r="F9" s="333" t="inlineStr">
-        <is>
-          <t>J36</t>
-        </is>
-      </c>
-      <c r="G9" s="334" t="inlineStr">
-        <is>
-          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
-        </is>
-      </c>
-      <c r="H9" s="331" t="inlineStr"/>
-    </row>
-    <row r="10" ht="87" customHeight="1">
-      <c r="A10" s="331" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="331" t="inlineStr">
-        <is>
-          <t>PILOTIS</t>
-        </is>
-      </c>
-      <c r="C10" s="332" t="inlineStr">
-        <is>
-          <t>VESTIÁRIO MASCULINO</t>
-        </is>
-      </c>
-      <c r="D10" s="331" t="inlineStr">
-        <is>
-          <t>LOUÇAS E METAIS</t>
-        </is>
-      </c>
-      <c r="E10" s="331" t="inlineStr">
-        <is>
-          <t>TORNEIRAS</t>
-        </is>
-      </c>
-      <c r="F10" s="333" t="inlineStr">
-        <is>
-          <t>O36</t>
-        </is>
-      </c>
-      <c r="G10" s="334" t="inlineStr">
-        <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
-        </is>
-      </c>
-      <c r="H10" s="331" t="inlineStr"/>
-    </row>
-    <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="331" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="331" t="inlineStr">
-        <is>
-          <t>APTO TIPO</t>
-        </is>
-      </c>
-      <c r="C11" s="332" t="inlineStr">
-        <is>
-          <t>SALA / VARANDA DA SALA</t>
-        </is>
-      </c>
-      <c r="D11" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E11" s="331" t="inlineStr">
-        <is>
-          <t>RODAPÉ</t>
-        </is>
-      </c>
-      <c r="F11" s="333" t="inlineStr">
-        <is>
-          <t>F13</t>
-        </is>
-      </c>
-      <c r="G11" s="334" t="inlineStr">
-        <is>
-          <t>Rodapé em mármore travertino romano bruto, semi-embutido, h=15cm. (DET PR001/PR002)
-CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
-        </is>
-      </c>
-      <c r="H11" s="331" t="inlineStr"/>
-    </row>
-    <row r="12" ht="57" customHeight="1">
-      <c r="A12" s="331" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="331" t="inlineStr">
-        <is>
-          <t>APTO TIPO</t>
-        </is>
-      </c>
-      <c r="C12" s="332" t="inlineStr">
-        <is>
-          <t>LAVABO</t>
-        </is>
-      </c>
-      <c r="D12" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E12" s="331" t="inlineStr">
-        <is>
-          <t>RODAPÉ</t>
-        </is>
-      </c>
-      <c r="F12" s="333" t="inlineStr">
-        <is>
-          <t>F14</t>
-        </is>
-      </c>
-      <c r="G12" s="334" t="inlineStr">
-        <is>
-          <t>Rodapé semi-embutido em mármore travertino romano bruto, h=15cm. (DET PR004)
-CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
-        </is>
-      </c>
-      <c r="H12" s="331" t="inlineStr"/>
-    </row>
-    <row r="13" ht="117" customHeight="1">
-      <c r="A13" s="331" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="331" t="inlineStr">
-        <is>
-          <t>APTO TIPO</t>
-        </is>
-      </c>
-      <c r="C13" s="332" t="inlineStr">
-        <is>
-          <t>BANHO SUÍTE MASTER</t>
-        </is>
-      </c>
-      <c r="D13" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E13" s="331" t="inlineStr">
-        <is>
-          <t>PAREDE/REJUNTE</t>
-        </is>
-      </c>
-      <c r="F13" s="333" t="inlineStr">
-        <is>
-          <t>H15</t>
-        </is>
-      </c>
-      <c r="G13" s="334" t="inlineStr">
-        <is>
-          <t>14 - Parede revestida em mármore travertino romano resinado. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (PR408)
-1 - Parede em alvenaria emassada e regularizada, pintada com tinta acrílica cor branco neve, acabamento acetinado. Ref.: Suvinil. (PR408)
-CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
-        </is>
-      </c>
-      <c r="H13" s="331" t="inlineStr"/>
-    </row>
-    <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="331" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="331" t="inlineStr">
-        <is>
-          <t>APTO TIPO</t>
-        </is>
-      </c>
-      <c r="C14" s="332" t="inlineStr">
-        <is>
-          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
-        </is>
-      </c>
-      <c r="D14" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E14" s="331" t="inlineStr">
-        <is>
-          <t>RODAPÉ</t>
-        </is>
-      </c>
-      <c r="F14" s="333" t="inlineStr">
-        <is>
-          <t>F17</t>
-        </is>
-      </c>
-      <c r="G14" s="334" t="inlineStr">
-        <is>
-          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
-CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
-        </is>
-      </c>
-      <c r="H14" s="331" t="inlineStr"/>
-    </row>
-    <row r="15" ht="57" customHeight="1">
-      <c r="A15" s="331" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="331" t="inlineStr">
-        <is>
-          <t>APTO TIPO</t>
-        </is>
-      </c>
-      <c r="C15" s="332" t="inlineStr">
-        <is>
-          <t>COPA NOTURNA</t>
-        </is>
-      </c>
-      <c r="D15" s="331" t="inlineStr">
-        <is>
-          <t>REVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="E15" s="331" t="inlineStr">
-        <is>
-          <t>BANCADA</t>
-        </is>
-      </c>
-      <c r="F15" s="333" t="inlineStr">
-        <is>
-          <t>J18</t>
-        </is>
-      </c>
-      <c r="G15" s="334" t="inlineStr">
-        <is>
-          <t>Bancada esculpida em mármore travertino romano resinado. (DET PR003)
-CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
-        </is>
-      </c>
-      <c r="H15" s="331" t="inlineStr"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -16253,15 +15915,6 @@
   <hyperlinks>
     <hyperlink ref="F5" location="'TÉRREO '!B17" tooltip="Ir para TÉRREO B17"/>
     <hyperlink ref="F6" location="'TÉRREO '!H17" tooltip="Ir para TÉRREO H17"/>
-    <hyperlink ref="F7" location="'PILOTIS'!J35" tooltip="Ir para PILOTIS J35"/>
-    <hyperlink ref="F8" location="'PILOTIS'!O35" tooltip="Ir para PILOTIS O35"/>
-    <hyperlink ref="F9" location="'PILOTIS'!J36" tooltip="Ir para PILOTIS J36"/>
-    <hyperlink ref="F10" location="'PILOTIS'!O36" tooltip="Ir para PILOTIS O36"/>
-    <hyperlink ref="F11" location="'APTO TIPO'!F13" tooltip="Ir para APTO TIPO F13"/>
-    <hyperlink ref="F12" location="'APTO TIPO'!F14" tooltip="Ir para APTO TIPO F14"/>
-    <hyperlink ref="F13" location="'APTO TIPO'!H15" tooltip="Ir para APTO TIPO H15"/>
-    <hyperlink ref="F14" location="'APTO TIPO'!F17" tooltip="Ir para APTO TIPO F17"/>
-    <hyperlink ref="F15" location="'APTO TIPO'!J18" tooltip="Ir para APTO TIPO J18"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -23398,7 +23051,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Pranchas 37 e 38 citam torneira Argon (Docol) e bancada em granito Branco Siena; a lista R04 traz D29 (Decalux, Deca) e D36 (granito cinza Santa Rosa). Confirmar com a arquitetura.</t>
+          <t>Divergência interna do detalhamento R04: as pranchas 37 e 38 citam torneira Argon (Docol) e bancada em granito Branco Siena com duas cubas esculpidas; a lista R04 traz D29 (Decalux, Deca) e D36 (granito cinza Santa Rosa). Mantida a lista na grade, com OBS. Confirmar.</t>
         </is>
       </c>
     </row>
@@ -28474,7 +28127,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>RODAPÉ: CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+          <t>RODAPÉ: Tabela R01 divergente (prevalece o detalhamento): rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
         </is>
       </c>
     </row>
@@ -28486,7 +28139,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>RODAPÉ: CONFLITO – Tabela R01: rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
+          <t>RODAPÉ: Tabela R01 divergente (prevalece o detalhamento): rodapé DE SOBREPOR em mármore travertino romano bruto, h=15cm</t>
         </is>
       </c>
     </row>
@@ -28498,7 +28151,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>PAREDE/REJUNTE: CONFLITO – Tabela R01: parede em mármore travertino romano BRUTO paginado</t>
+          <t>PAREDE/REJUNTE: Tabela R01 divergente (prevalece o detalhamento): parede em mármore travertino romano BRUTO paginado</t>
         </is>
       </c>
     </row>
@@ -28510,7 +28163,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>RODAPÉ: CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm</t>
+          <t>RODAPÉ: divergência interna do detalhamento. O quadro do DET PR001 (e a Tabela R01) indicam h=10cm; a legenda de rodapé do DET PR001/PR002 indica h=6,5cm. Mantido h=10cm na grade. Confirmar.</t>
         </is>
       </c>
     </row>
@@ -28522,7 +28175,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>BANCADA: CONFLITO – Tabela R01: bancada "pintura acrílica, cor branco neve"</t>
+          <t>BANCADA: Tabela R01 divergente (prevalece o detalhamento): bancada "pintura acrílica, cor branco neve"</t>
         </is>
       </c>
     </row>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -1492,7 +1492,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="335">
+  <cellXfs count="336">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2401,6 +2401,9 @@
     </xf>
     <xf numFmtId="0" fontId="73" fillId="14" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="67" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -7566,9 +7569,10 @@
           <t>ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
       </c>
-      <c r="I30" s="307" t="inlineStr">
-        <is>
-          <t>ARQ-T19 - código não existe no quadro de tetos (01 a 06); conferir na planta</t>
+      <c r="I30" s="321" t="inlineStr">
+        <is>
+          <t>ARQ-T19 - código indicado na etiqueta de teto da planta PR003.
+CONFLITO – Quadro de tetos da própria PR003: só traz os códigos 01 a 06; o T19 não existe no quadro.</t>
         </is>
       </c>
       <c r="J30" s="307" t="n"/>
@@ -12171,10 +12175,10 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J35" s="320" t="inlineStr">
+      <c r="J35" s="321" t="inlineStr">
         <is>
           <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-OBS. – As pranchas 37 e 38 do detalhamento R04 indicam bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível (ver PENDÊNCIAS).</t>
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
         </is>
       </c>
       <c r="K35" s="317" t="inlineStr">
@@ -12185,10 +12189,10 @@
       <c r="L35" s="307" t="n"/>
       <c r="M35" s="308" t="n"/>
       <c r="N35" s="308" t="n"/>
-      <c r="O35" s="320" t="inlineStr">
+      <c r="O35" s="321" t="inlineStr">
         <is>
           <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-OBS. – As pranchas 37 e 38 do detalhamento R04 indicam torneira de mesa bica baixa Argon, Docol (ver PENDÊNCIAS).</t>
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
       <c r="P35" s="320" t="inlineStr">
@@ -12266,10 +12270,10 @@
           <t>T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
-      <c r="J36" s="320" t="inlineStr">
+      <c r="J36" s="321" t="inlineStr">
         <is>
           <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-OBS. – As pranchas 37 e 38 do detalhamento R04 indicam bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível (ver PENDÊNCIAS).</t>
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
         </is>
       </c>
       <c r="K36" s="317" t="inlineStr">
@@ -12280,10 +12284,10 @@
       <c r="L36" s="307" t="n"/>
       <c r="M36" s="308" t="n"/>
       <c r="N36" s="308" t="n"/>
-      <c r="O36" s="320" t="inlineStr">
+      <c r="O36" s="321" t="inlineStr">
         <is>
           <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-OBS. – As pranchas 37 e 38 do detalhamento R04 indicam torneira de mesa bica baixa Argon, Docol (ver PENDÊNCIAS).</t>
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
       <c r="P36" s="320" t="inlineStr">
@@ -15023,10 +15027,10 @@
         </is>
       </c>
       <c r="E17" s="300" t="n"/>
-      <c r="F17" s="317" t="inlineStr">
+      <c r="F17" s="335" t="inlineStr">
         <is>
           <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
-OBS. – A legenda de rodapé do DET PR001/PR002 indica h=6,5cm (ver PENDÊNCIAS).</t>
+CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm (o quadro da mesma prancha indica h=10cm)</t>
         </is>
       </c>
       <c r="G17" s="300" t="n"/>
@@ -15763,7 +15767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15907,6 +15911,228 @@
       </c>
       <c r="H6" s="331" t="inlineStr"/>
     </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="331" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="331" t="inlineStr">
+        <is>
+          <t>TÉRREO</t>
+        </is>
+      </c>
+      <c r="C7" s="332" t="inlineStr">
+        <is>
+          <t>CONCIERGE</t>
+        </is>
+      </c>
+      <c r="D7" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E7" s="331" t="inlineStr">
+        <is>
+          <t>TETO</t>
+        </is>
+      </c>
+      <c r="F7" s="333" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="G7" s="334" t="inlineStr">
+        <is>
+          <t>ARQ-T19 - código indicado na etiqueta de teto da planta PR003.
+CONFLITO – Quadro de tetos da própria PR003: só traz os códigos 01 a 06; o T19 não existe no quadro.</t>
+        </is>
+      </c>
+      <c r="H7" s="331" t="inlineStr"/>
+    </row>
+    <row r="8" ht="102" customHeight="1">
+      <c r="A8" s="331" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C8" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="D8" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E8" s="331" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="F8" s="333" t="inlineStr">
+        <is>
+          <t>J35</t>
+        </is>
+      </c>
+      <c r="G8" s="334" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
+        </is>
+      </c>
+      <c r="H8" s="331" t="inlineStr"/>
+    </row>
+    <row r="9" ht="87" customHeight="1">
+      <c r="A9" s="331" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C9" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO FEMININO</t>
+        </is>
+      </c>
+      <c r="D9" s="331" t="inlineStr">
+        <is>
+          <t>LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="E9" s="331" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="F9" s="333" t="inlineStr">
+        <is>
+          <t>O35</t>
+        </is>
+      </c>
+      <c r="G9" s="334" t="inlineStr">
+        <is>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+        </is>
+      </c>
+      <c r="H9" s="331" t="inlineStr"/>
+    </row>
+    <row r="10" ht="102" customHeight="1">
+      <c r="A10" s="331" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C10" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="D10" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E10" s="331" t="inlineStr">
+        <is>
+          <t>BANCADA</t>
+        </is>
+      </c>
+      <c r="F10" s="333" t="inlineStr">
+        <is>
+          <t>J36</t>
+        </is>
+      </c>
+      <c r="G10" s="334" t="inlineStr">
+        <is>
+          <t>D36 - Bancada e cubas esculpidas em granito cinza Santa Rosa, acabamento escovado. Desenho e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: bancada em granito Branco Siena com duas cubas esculpidas com bandeja removível</t>
+        </is>
+      </c>
+      <c r="H10" s="331" t="inlineStr"/>
+    </row>
+    <row r="11" ht="87" customHeight="1">
+      <c r="A11" s="331" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="331" t="inlineStr">
+        <is>
+          <t>PILOTIS</t>
+        </is>
+      </c>
+      <c r="C11" s="332" t="inlineStr">
+        <is>
+          <t>VESTIÁRIO MASCULINO</t>
+        </is>
+      </c>
+      <c r="D11" s="331" t="inlineStr">
+        <is>
+          <t>LOUÇAS E METAIS</t>
+        </is>
+      </c>
+      <c r="E11" s="331" t="inlineStr">
+        <is>
+          <t>TORNEIRAS</t>
+        </is>
+      </c>
+      <c r="F11" s="333" t="inlineStr">
+        <is>
+          <t>O36</t>
+        </is>
+      </c>
+      <c r="G11" s="334" t="inlineStr">
+        <is>
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+        </is>
+      </c>
+      <c r="H11" s="331" t="inlineStr"/>
+    </row>
+    <row r="12" ht="87" customHeight="1">
+      <c r="A12" s="331" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="331" t="inlineStr">
+        <is>
+          <t>APTO TIPO</t>
+        </is>
+      </c>
+      <c r="C12" s="332" t="inlineStr">
+        <is>
+          <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
+        </is>
+      </c>
+      <c r="D12" s="331" t="inlineStr">
+        <is>
+          <t>REVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="E12" s="331" t="inlineStr">
+        <is>
+          <t>RODAPÉ</t>
+        </is>
+      </c>
+      <c r="F12" s="333" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="G12" s="334" t="inlineStr">
+        <is>
+          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
+CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm (o quadro da mesma prancha indica h=10cm)</t>
+        </is>
+      </c>
+      <c r="H12" s="331" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -15915,6 +16141,12 @@
   <hyperlinks>
     <hyperlink ref="F5" location="'TÉRREO '!B17" tooltip="Ir para TÉRREO B17"/>
     <hyperlink ref="F6" location="'TÉRREO '!H17" tooltip="Ir para TÉRREO H17"/>
+    <hyperlink ref="F7" location="'TÉRREO '!I30" tooltip="Ir para TÉRREO I30"/>
+    <hyperlink ref="F8" location="'PILOTIS'!J35" tooltip="Ir para PILOTIS J35"/>
+    <hyperlink ref="F9" location="'PILOTIS'!O35" tooltip="Ir para PILOTIS O35"/>
+    <hyperlink ref="F10" location="'PILOTIS'!J36" tooltip="Ir para PILOTIS J36"/>
+    <hyperlink ref="F11" location="'PILOTIS'!O36" tooltip="Ir para PILOTIS O36"/>
+    <hyperlink ref="F12" location="'APTO TIPO'!F17" tooltip="Ir para APTO TIPO F17"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -23051,7 +23283,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Divergência interna do detalhamento R04: as pranchas 37 e 38 citam torneira Argon (Docol) e bancada em granito Branco Siena com duas cubas esculpidas; a lista R04 traz D29 (Decalux, Deca) e D36 (granito cinza Santa Rosa). Mantida a lista na grade, com OBS. Confirmar.</t>
+          <t>CONFLITO no detalhamento R04 (ver aba CONFLITOS): as pranchas 37 e 38 citam torneira Argon (Docol) e bancada em granito Branco Siena com duas cubas esculpidas; a lista R04 traz D29 (Decalux, Deca) e D36 (granito cinza Santa Rosa).</t>
         </is>
       </c>
     </row>
@@ -28059,7 +28291,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>A etiqueta de teto da planta PR003 traz □19, mas o quadro de tetos só vai de 01 a 06. Provável erro de etiqueta; confirmar com a arquitetura.</t>
+          <t>CONFLITO na própria planta (ver aba CONFLITOS): a etiqueta de teto da PR003 traz □19, mas o quadro de tetos da prancha só vai de 01 a 06. Confirmar com a arquitetura.</t>
         </is>
       </c>
     </row>
@@ -28163,7 +28395,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>RODAPÉ: divergência interna do detalhamento. O quadro do DET PR001 (e a Tabela R01) indicam h=10cm; a legenda de rodapé do DET PR001/PR002 indica h=6,5cm. Mantido h=10cm na grade. Confirmar.</t>
+          <t>RODAPÉ: CONFLITO na própria prancha (ver aba CONFLITOS). O quadro do DET PR001 indica h=10cm; a legenda de rodapé do DET PR001/PR002 indica h=6,5cm.</t>
         </is>
       </c>
     </row>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -11045,13 +11045,17 @@
       <c r="Y14" s="302" t="n"/>
       <c r="Z14" s="300" t="n"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="119" customHeight="1">
       <c r="A15" s="298" t="inlineStr">
         <is>
           <t>TERRAÇO SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B15" s="302" t="n"/>
+      <c r="B15" s="302" t="inlineStr">
+        <is>
+          <t>ARQ-P08 - Piso elevado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Planta PR011)</t>
+        </is>
+      </c>
       <c r="C15" s="300" t="n"/>
       <c r="D15" s="300" t="n"/>
       <c r="E15" s="300" t="n"/>
@@ -16686,7 +16690,11 @@
         </is>
       </c>
       <c r="C27" s="268" t="inlineStr"/>
-      <c r="D27" s="268" t="inlineStr"/>
+      <c r="D27" s="268" t="inlineStr">
+        <is>
+          <t>Tabela v00 e detalhamento R04 sem especificação de acabamento (a lista R04 só traz códigos sem descrição para "Varanda, terraço, piscina e prainha, braseiro"). A planta de arquitetura PR011 indica piso ○08 (ARQ-P08, lançado na grade) e guarda-corpos GC06/GC07 h=130cm. Sem indicação de rodapé, parede ou teto.</t>
+        </is>
+      </c>
       <c r="E27" s="268" t="inlineStr"/>
     </row>
     <row r="28">

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -6057,7 +6057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF55"/>
+  <dimension ref="A1:AF56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6761,13 +6761,17 @@
       <c r="Y14" s="295" t="n"/>
       <c r="Z14" s="296" t="n"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="89" customHeight="1">
       <c r="A15" s="294" t="inlineStr">
         <is>
           <t xml:space="preserve">RAMPA ACESSO PEDESTRES </t>
         </is>
       </c>
-      <c r="B15" s="295" t="n"/>
+      <c r="B15" s="295" t="inlineStr">
+        <is>
+          <t>ARQ-P21 - Piso em granito marrom absoluto serrado e envernizado, ou pedra sintética a definir. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (Planta PR003: plano inclinado - pedestres (social), i=4,99%)</t>
+        </is>
+      </c>
       <c r="C15" s="296" t="n"/>
       <c r="D15" s="296" t="n"/>
       <c r="E15" s="296" t="n"/>
@@ -8669,8 +8673,77 @@
       <c r="Y54" s="307" t="n"/>
       <c r="Z54" s="300" t="n"/>
     </row>
-    <row r="55">
-      <c r="S55" s="3" t="n"/>
+    <row r="55" ht="119" customHeight="1">
+      <c r="A55" s="298" t="inlineStr">
+        <is>
+          <t>PLANO INCLINADO - PEDESTRES (SERVIÇO)</t>
+        </is>
+      </c>
+      <c r="B55" s="307" t="inlineStr">
+        <is>
+          <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Planta PR003, i=3,83%)</t>
+        </is>
+      </c>
+      <c r="C55" s="300" t="n"/>
+      <c r="D55" s="307" t="n"/>
+      <c r="E55" s="308" t="n"/>
+      <c r="F55" s="308" t="n"/>
+      <c r="G55" s="300" t="n"/>
+      <c r="H55" s="307" t="n"/>
+      <c r="I55" s="307" t="n"/>
+      <c r="J55" s="307" t="n"/>
+      <c r="K55" s="300" t="n"/>
+      <c r="L55" s="307" t="n"/>
+      <c r="M55" s="308" t="n"/>
+      <c r="N55" s="308" t="n"/>
+      <c r="O55" s="307" t="n"/>
+      <c r="P55" s="302" t="n"/>
+      <c r="Q55" s="300" t="n"/>
+      <c r="R55" s="307" t="n"/>
+      <c r="S55" s="307" t="n"/>
+      <c r="T55" s="307" t="n"/>
+      <c r="U55" s="300" t="n"/>
+      <c r="V55" s="302" t="n"/>
+      <c r="W55" s="307" t="n"/>
+      <c r="X55" s="307" t="n"/>
+      <c r="Y55" s="307" t="n"/>
+      <c r="Z55" s="300" t="n"/>
+    </row>
+    <row r="56" ht="119" customHeight="1">
+      <c r="A56" s="298" t="inlineStr">
+        <is>
+          <t>PLANO INCLINADO - VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="B56" s="307" t="inlineStr">
+        <is>
+          <t>ARQ-P07 - Piso assentado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Planta PR003, dois trechos, i=3,50% e 3,28%)</t>
+        </is>
+      </c>
+      <c r="C56" s="300" t="n"/>
+      <c r="D56" s="307" t="n"/>
+      <c r="E56" s="308" t="n"/>
+      <c r="F56" s="308" t="n"/>
+      <c r="G56" s="300" t="n"/>
+      <c r="H56" s="307" t="n"/>
+      <c r="I56" s="307" t="n"/>
+      <c r="J56" s="307" t="n"/>
+      <c r="K56" s="300" t="n"/>
+      <c r="L56" s="307" t="n"/>
+      <c r="M56" s="308" t="n"/>
+      <c r="N56" s="308" t="n"/>
+      <c r="O56" s="307" t="n"/>
+      <c r="P56" s="302" t="n"/>
+      <c r="Q56" s="300" t="n"/>
+      <c r="R56" s="307" t="n"/>
+      <c r="S56" s="307" t="n"/>
+      <c r="T56" s="307" t="n"/>
+      <c r="U56" s="300" t="n"/>
+      <c r="V56" s="302" t="n"/>
+      <c r="W56" s="307" t="n"/>
+      <c r="X56" s="307" t="n"/>
+      <c r="Y56" s="307" t="n"/>
+      <c r="Z56" s="300" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -11828,13 +11901,17 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28" ht="119" customHeight="1">
       <c r="A28" s="298" t="inlineStr">
         <is>
           <t>VARANDA</t>
         </is>
       </c>
-      <c r="B28" s="307" t="n"/>
+      <c r="B28" s="307" t="inlineStr">
+        <is>
+          <t>ARQ-P08 - Piso elevado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Plantas PR011 e PR012)</t>
+        </is>
+      </c>
       <c r="C28" s="300" t="n"/>
       <c r="D28" s="300" t="n"/>
       <c r="E28" s="308" t="n"/>
@@ -16172,7 +16249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E544"/>
+  <dimension ref="A1:E553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -28335,7 +28412,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Pranchas de revisão anterior (R11 e R13 de 2025) às demais; não foram usadas.</t>
+          <t>Trecho 2 do 2º pavimento e do Pilotis; conferidas em 02/10/2026 (ver item 7).</t>
         </is>
       </c>
     </row>
@@ -28476,6 +28553,98 @@
       <c r="D544" t="inlineStr">
         <is>
           <t>DET indica "validar com o Setor de Produto"; PR001/PR002 "não liberado para execução, paginação poderá sofrer alterações".</t>
+        </is>
+      </c>
+    </row>
+    <row r="545"/>
+    <row r="546">
+      <c r="A546" s="279" t="inlineStr">
+        <is>
+          <t>7. CONFERÊNCIA VISUAL DAS PLANTAS DE ARQUITETURA (02/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Conferência visual</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Todos os ambientes das plantas PR003, PR004, PR005, PR007, PR008, PR009, PR011, PR012 e PR013 foram conferidos no desenho, etiqueta por etiqueta. Os ambientes já lançados estão de acordo com as plantas. Lista completa: levantamento/arquitetura/conferencia_etiquetas_arquitetura.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>PR008 e PR012</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>São o trecho 2 do 2º pavimento e do Pilotis (não revisões antigas, como estava anotado). PR008 só traz a rampa (○04 △07 □03, igual à PR009). PR012 traz a varanda (○08); piscinas, prainha e deck sem etiqueta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>PILOTIS – VARANDA</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Planta indica só piso ○08 (ARQ-P08), lançado na grade. Detalhamento R04 sem especificação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>PILOTIS – CIRCULAÇÕES EXTERNAS</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>As circulações de 40,36 m² (PR011), 59,22 m² e 83,52 m² (PR013) têm só piso ○08 (ARQ-P08), a mesma especificação já lançada em "CIRCULAÇÃO EXTERNA COBERTA/DESCOBERTA E VARANDA ESPAÇO KIDS". Não foi possível ligar cada uma às linhas "CIRCULAÇÃO JARDINS" e "CIRCULAÇÃO PLAYGROUND" pelo nome; confirmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>TÉRREO – PLANOS INCLINADOS</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Plano inclinado de pedestres (social) com ○21, lançado em RAMPA ACESSO PEDESTRES. Plano inclinado de pedestres (serviço) e de veículos com ○07, em linhas novas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>TÉRREO – MUROS</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Triângulo △04 isolado em três pontos do muro junto ao jardim (PR003): parede em textura acrílica fosca Terra Fértil, Suvinil. Não é um ambiente da grade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Sem etiqueta na planta</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Elevadores, escadas, I.S. P.C.D. e vestíbulo (Térreo), DML e jardinagem (Térreo), jardins sobre laje, piscinas, prainha, deck, playground, lounge quadras, saunas, apoio e DML do salão, lobby pilotis e circulações internas do Pilotis. Hall, lobby, antecâmara (eclusa), espaço kids, gourmet, salão, cozinha, I.S., termas, academia, bar e vestiários do Pilotis têm "ACABAMENTOS VER INTERIORES".</t>
         </is>
       </c>
     </row>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -12144,13 +12144,17 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="119" customHeight="1">
       <c r="A33" s="298" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO PLAYGROUND</t>
         </is>
       </c>
-      <c r="B33" s="307" t="n"/>
+      <c r="B33" s="307" t="inlineStr">
+        <is>
+          <t>ARQ-P08 - Piso elevado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Planta PR013: circulação junto ao playground)</t>
+        </is>
+      </c>
       <c r="C33" s="300" t="n"/>
       <c r="D33" s="307" t="n"/>
       <c r="E33" s="308" t="n"/>
@@ -12484,13 +12488,17 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="134" customHeight="1">
       <c r="A38" s="298" t="inlineStr">
         <is>
           <t xml:space="preserve">CIRCULAÇÃO JARDINS </t>
         </is>
       </c>
-      <c r="B38" s="307" t="n"/>
+      <c r="B38" s="307" t="inlineStr">
+        <is>
+          <t>ARQ-P08 - Piso elevado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Plantas PR011 e PR013: circulações externas junto aos jardins)</t>
+        </is>
+      </c>
       <c r="C38" s="300" t="n"/>
       <c r="D38" s="307" t="n"/>
       <c r="E38" s="308" t="n"/>
@@ -28608,7 +28616,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>As circulações de 40,36 m² (PR011), 59,22 m² e 83,52 m² (PR013) têm só piso ○08 (ARQ-P08), a mesma especificação já lançada em "CIRCULAÇÃO EXTERNA COBERTA/DESCOBERTA E VARANDA ESPAÇO KIDS". Não foi possível ligar cada uma às linhas "CIRCULAÇÃO JARDINS" e "CIRCULAÇÃO PLAYGROUND" pelo nome; confirmar.</t>
+          <t>As circulações de 40,36 m² (PR011), 59,22 m² e 83,52 m² (PR013) têm só piso ○08 (ARQ-P08), a mesma especificação já lançada em "CIRCULAÇÃO EXTERNA COBERTA/DESCOBERTA E VARANDA ESPAÇO KIDS". Lançadas como dois ambientes, "CIRCULAÇÃO JARDINS" e "CIRCULAÇÃO PLAYGROUND", conforme orientação de 02/10/2026.</t>
         </is>
       </c>
     </row>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -5538,7 +5538,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="91" t="inlineStr">
         <is>
-          <t xml:space="preserve">PÁGINA </t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="B11" s="217" t="n"/>
@@ -5557,13 +5557,13 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="59" t="inlineStr">
         <is>
-          <t>Página 01 de 11</t>
+          <t>CONTROLE DE REVISÕES</t>
         </is>
       </c>
       <c r="B12" s="217" t="n"/>
       <c r="C12" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMÁRIO E CONTROLE DE REVISÕES </t>
+          <t>SUMÁRIO E CONTROLE DE REVISÕES</t>
         </is>
       </c>
       <c r="D12" s="230" t="n"/>
@@ -5576,13 +5576,13 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="59" t="inlineStr">
         <is>
-          <t>Página 02 de11</t>
+          <t>TÉRREO</t>
         </is>
       </c>
       <c r="B13" s="217" t="n"/>
       <c r="C13" s="61" t="inlineStr">
         <is>
-          <t>ESPECIFICAÇÃO DE REVESTIMENTOS</t>
+          <t>ESPECIFICAÇÃO DE REVESTIMENTOS, LOUÇAS E METAIS E COMPLEMENTARES</t>
         </is>
       </c>
       <c r="D13" s="230" t="n"/>
@@ -5595,13 +5595,13 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="59" t="inlineStr">
         <is>
-          <t>Página 03 de 11</t>
+          <t>2° PAVTO</t>
         </is>
       </c>
       <c r="B14" s="217" t="n"/>
       <c r="C14" s="61" t="inlineStr">
         <is>
-          <t>ESPECIFICAÇÃO DE REVESTIMENTOS</t>
+          <t>ESPECIFICAÇÃO DE REVESTIMENTOS, LOUÇAS E METAIS E COMPLEMENTARES</t>
         </is>
       </c>
       <c r="D14" s="230" t="n"/>
@@ -5614,13 +5614,13 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="59" t="inlineStr">
         <is>
-          <t>Página 04 de 11</t>
+          <t>PILOTIS</t>
         </is>
       </c>
       <c r="B15" s="217" t="n"/>
       <c r="C15" s="61" t="inlineStr">
         <is>
-          <t>ESPECIFICAÇÃO DE LOUÇAS E METAIS</t>
+          <t>ESPECIFICAÇÃO DE REVESTIMENTOS, LOUÇAS E METAIS E COMPLEMENTARES; IMAGENS AO LADO DA GRADE (LINK "VER IMAGEM")</t>
         </is>
       </c>
       <c r="D15" s="230" t="n"/>
@@ -5633,13 +5633,13 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="59" t="inlineStr">
         <is>
-          <t>Página 05 de 11</t>
+          <t>APTO TIPO</t>
         </is>
       </c>
       <c r="B16" s="217" t="n"/>
       <c r="C16" s="61" t="inlineStr">
         <is>
-          <t>ESPECIFICAÇÃO DE LOUÇAS E METAIS</t>
+          <t>ESPECIFICAÇÃO DO APARTAMENTO TIPO</t>
         </is>
       </c>
       <c r="D16" s="230" t="n"/>
@@ -5652,13 +5652,13 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="59" t="inlineStr">
         <is>
-          <t>Página 06 de 11</t>
+          <t>CONFLITOS</t>
         </is>
       </c>
       <c r="B17" s="217" t="n"/>
       <c r="C17" s="61" t="inlineStr">
         <is>
-          <t>ESPECIFICAÇÃO DE COMPLEMENTARES</t>
+          <t>ESPECIFICAÇÕES CONFLITANTES (ARQUITETURA × DETALHAMENTO; PRANCHA × TABELA DA PRÓPRIA PRANCHA)</t>
         </is>
       </c>
       <c r="D17" s="230" t="n"/>
@@ -5671,13 +5671,13 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="59" t="inlineStr">
         <is>
-          <t>Página 07 de 11</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="B18" s="217" t="n"/>
       <c r="C18" s="61" t="inlineStr">
         <is>
-          <t>ESPECIFICAÇÃO DE COMPLEMENTARES</t>
+          <t>PENDÊNCIAS E RASTREABILIDADE DAS FONTES</t>
         </is>
       </c>
       <c r="D18" s="230" t="n"/>
@@ -5688,17 +5688,9 @@
       <c r="I18" s="217" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
-        <is>
-          <t>Página 08 de 11</t>
-        </is>
-      </c>
+      <c r="A19" s="59" t="n"/>
       <c r="B19" s="217" t="n"/>
-      <c r="C19" s="61" t="inlineStr">
-        <is>
-          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
-        </is>
-      </c>
+      <c r="C19" s="61" t="n"/>
       <c r="D19" s="230" t="n"/>
       <c r="E19" s="230" t="n"/>
       <c r="F19" s="230" t="n"/>
@@ -5707,17 +5699,9 @@
       <c r="I19" s="217" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
-        <is>
-          <t>Página 09 de 11</t>
-        </is>
-      </c>
+      <c r="A20" s="59" t="n"/>
       <c r="B20" s="217" t="n"/>
-      <c r="C20" s="61" t="inlineStr">
-        <is>
-          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
-        </is>
-      </c>
+      <c r="C20" s="61" t="n"/>
       <c r="D20" s="230" t="n"/>
       <c r="E20" s="230" t="n"/>
       <c r="F20" s="230" t="n"/>
@@ -5726,17 +5710,9 @@
       <c r="I20" s="217" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="59" t="inlineStr">
-        <is>
-          <t>Página 10 de 11</t>
-        </is>
-      </c>
+      <c r="A21" s="59" t="n"/>
       <c r="B21" s="217" t="n"/>
-      <c r="C21" s="61" t="inlineStr">
-        <is>
-          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
-        </is>
-      </c>
+      <c r="C21" s="61" t="n"/>
       <c r="D21" s="230" t="n"/>
       <c r="E21" s="230" t="n"/>
       <c r="F21" s="230" t="n"/>
@@ -5745,17 +5721,9 @@
       <c r="I21" s="217" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="99" t="inlineStr">
-        <is>
-          <t>Página 11 de 11</t>
-        </is>
-      </c>
+      <c r="A22" s="99" t="n"/>
       <c r="B22" s="221" t="n"/>
-      <c r="C22" s="111" t="inlineStr">
-        <is>
-          <t>IMAGENS: AO LADO DA GRADE (LINK "VER IMAGEM")</t>
-        </is>
-      </c>
+      <c r="C22" s="111" t="n"/>
       <c r="D22" s="231" t="n"/>
       <c r="E22" s="231" t="n"/>
       <c r="F22" s="231" t="n"/>
@@ -5821,56 +5789,60 @@
       <c r="I25" s="234" t="n"/>
     </row>
     <row r="26" ht="43.5" customHeight="1">
-      <c r="A26" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>R00</t>
         </is>
       </c>
-      <c r="D26" s="235" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>TODAS</t>
+        </is>
+      </c>
+      <c r="E26" s="61" t="inlineStr">
+        <is>
+          <t>Emissão inicial (primeira versão). Prevalece o detalhamento sobre a Tabela 01; divergências entre arquitetura e detalhamento, e entre prancha e tabela da própria prancha, ficam em vermelho e na aba CONFLITOS.</t>
+        </is>
+      </c>
+      <c r="F26" s="230" t="n"/>
+      <c r="G26" s="230" t="n"/>
+      <c r="H26" s="230" t="n"/>
+      <c r="I26" s="217" t="n"/>
+    </row>
+    <row r="27" ht="43.5" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>R00</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>PILOTIS (3º PAVIMENTO)</t>
         </is>
       </c>
-      <c r="E26" s="236" t="inlineStr">
-        <is>
-          <t>Emissão inicial. Especificações levantadas da Tabela de acabamentos Ed. Cidade Jardim v00 (19/06/2026).</t>
-        </is>
-      </c>
-      <c r="F26" s="228" t="n"/>
-      <c r="G26" s="228" t="n"/>
-      <c r="H26" s="228" t="n"/>
-      <c r="I26" s="229" t="n"/>
-    </row>
-    <row r="27" ht="43.5" customHeight="1">
-      <c r="A27" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>R00</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>TÉRREO E 2º PAVIMENTO</t>
-        </is>
-      </c>
-      <c r="E27" s="237" t="inlineStr">
-        <is>
-          <t>Sem especificações na tabela v00 (abrange somente o 3º pavimento - Pilotis). Aguardando informação.</t>
+      <c r="E27" s="61" t="inlineStr">
+        <is>
+          <t>Tabela de acabamentos Ed. Cidade Jardim v00 (19/06/2026), detalhamento de interiores R04 (23/04/2026) e plantas de arquitetura PR011 a PR013.</t>
         </is>
       </c>
       <c r="F27" s="230" t="n"/>
@@ -5879,8 +5851,10 @@
       <c r="I27" s="217" t="n"/>
     </row>
     <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="19" t="n">
-        <v>3</v>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
@@ -5892,14 +5866,14 @@
           <t>R00</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>IMAGENS ESPECIFICAÇÕES</t>
-        </is>
-      </c>
-      <c r="E28" s="237" t="inlineStr">
-        <is>
-          <t>Imagens das fichas TERMAS e VESTIÁRIOS - TERMAS da tabela de acabamentos v00. Em 02/10/2026 passaram para a própria aba PILOTIS, à direita da grade (a partir da coluna AH); o link "► VER IMAGEM (clique)" na célula leva à foto e "◄ VOLTAR" retorna.</t>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>TÉRREO E 2º PAVIMENTO</t>
+        </is>
+      </c>
+      <c r="E28" s="61" t="inlineStr">
+        <is>
+          <t>Detalhamento de interiores R04 (23/04/2026) e plantas de arquitetura CDJ-ARQ-EX PR003 a PR009, conferidas no desenho etiqueta por etiqueta.</t>
         </is>
       </c>
       <c r="F28" s="230" t="n"/>
@@ -5908,8 +5882,10 @@
       <c r="I28" s="217" t="n"/>
     </row>
     <row r="29" ht="43.5" customHeight="1">
-      <c r="A29" s="19" t="n">
-        <v>4</v>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
@@ -5923,12 +5899,12 @@
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>APTO TIPO</t>
         </is>
       </c>
       <c r="E29" s="61" t="inlineStr">
         <is>
-          <t>Nova aba com as pendências de especificação e a correspondência ambiente da tabela × linha da grade.</t>
+          <t>Tabela JARDIM-ACABAMENTOS R01 e detalhamento do apartamento (CDJ_DET_EX PR001-PR008, CDJ-ARQ-DT PR406/407/408).</t>
         </is>
       </c>
       <c r="F29" s="230" t="n"/>
@@ -5937,11 +5913,31 @@
       <c r="I29" s="217" t="n"/>
     </row>
     <row r="30" ht="43.5" customHeight="1">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="40" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="61" t="n"/>
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>R00</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>IMAGENS</t>
+        </is>
+      </c>
+      <c r="E30" s="61" t="inlineStr">
+        <is>
+          <t>Imagens das fichas TERMAS e VESTIÁRIOS - TERMAS na aba PILOTIS, à direita da grade (coluna AH em diante): "► VER IMAGEM (clique)" leva à foto e "◄ VOLTAR" retorna.</t>
+        </is>
+      </c>
       <c r="F30" s="230" t="n"/>
       <c r="G30" s="230" t="n"/>
       <c r="H30" s="230" t="n"/>
@@ -6661,7 +6657,7 @@
       <c r="A12" s="51" t="n"/>
       <c r="B12" s="124" t="inlineStr">
         <is>
-          <t>GERAL — SEM ESPECIFICAÇÕES NA TABELA DE ACABAMENTOS V00 (A TABELA ABRANGE SOMENTE O 3º PAVIMENTO - PILOTIS)</t>
+          <t>GERAL — TÉRREO PELO DETALHAMENTO DE INTERIORES R04 E PELAS PLANTAS DE ARQUITETURA PR003 A PR005</t>
         </is>
       </c>
       <c r="C12" s="241" t="n"/>
@@ -6703,14 +6699,14 @@
           <t>ELEVADORES SOCIAIS</t>
         </is>
       </c>
-      <c r="B13" s="295" t="n"/>
+      <c r="B13" s="327" t="n"/>
       <c r="C13" s="296" t="n"/>
       <c r="D13" s="296" t="n"/>
       <c r="E13" s="296" t="n"/>
       <c r="F13" s="296" t="n"/>
       <c r="G13" s="296" t="n"/>
-      <c r="H13" s="297" t="n"/>
-      <c r="I13" s="297" t="n"/>
+      <c r="H13" s="314" t="n"/>
+      <c r="I13" s="314" t="n"/>
       <c r="J13" s="296" t="n"/>
       <c r="K13" s="296" t="n"/>
       <c r="L13" s="296" t="n"/>
@@ -6725,8 +6721,8 @@
       <c r="U13" s="296" t="n"/>
       <c r="V13" s="296" t="n"/>
       <c r="W13" s="296" t="n"/>
-      <c r="X13" s="295" t="n"/>
-      <c r="Y13" s="295" t="n"/>
+      <c r="X13" s="327" t="n"/>
+      <c r="Y13" s="327" t="n"/>
       <c r="Z13" s="296" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -6735,14 +6731,14 @@
           <t>ELEVADOR SERVIÇO</t>
         </is>
       </c>
-      <c r="B14" s="295" t="n"/>
+      <c r="B14" s="327" t="n"/>
       <c r="C14" s="296" t="n"/>
       <c r="D14" s="296" t="n"/>
       <c r="E14" s="296" t="n"/>
       <c r="F14" s="296" t="n"/>
       <c r="G14" s="296" t="n"/>
-      <c r="H14" s="297" t="n"/>
-      <c r="I14" s="297" t="n"/>
+      <c r="H14" s="314" t="n"/>
+      <c r="I14" s="314" t="n"/>
       <c r="J14" s="296" t="n"/>
       <c r="K14" s="296" t="n"/>
       <c r="L14" s="296" t="n"/>
@@ -6757,17 +6753,17 @@
       <c r="U14" s="296" t="n"/>
       <c r="V14" s="296" t="n"/>
       <c r="W14" s="296" t="n"/>
-      <c r="X14" s="295" t="n"/>
-      <c r="Y14" s="295" t="n"/>
+      <c r="X14" s="327" t="n"/>
+      <c r="Y14" s="327" t="n"/>
       <c r="Z14" s="296" t="n"/>
     </row>
     <row r="15" ht="89" customHeight="1">
       <c r="A15" s="294" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMPA ACESSO PEDESTRES </t>
-        </is>
-      </c>
-      <c r="B15" s="295" t="inlineStr">
+          <t>RAMPA ACESSO PEDESTRES</t>
+        </is>
+      </c>
+      <c r="B15" s="327" t="inlineStr">
         <is>
           <t>ARQ-P21 - Piso em granito marrom absoluto serrado e envernizado, ou pedra sintética a definir. Paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. (Planta PR003: plano inclinado - pedestres (social), i=4,99%)</t>
         </is>
@@ -6777,8 +6773,8 @@
       <c r="E15" s="296" t="n"/>
       <c r="F15" s="296" t="n"/>
       <c r="G15" s="296" t="n"/>
-      <c r="H15" s="297" t="n"/>
-      <c r="I15" s="297" t="n"/>
+      <c r="H15" s="314" t="n"/>
+      <c r="I15" s="314" t="n"/>
       <c r="J15" s="296" t="n"/>
       <c r="K15" s="296" t="n"/>
       <c r="L15" s="296" t="n"/>
@@ -6793,8 +6789,8 @@
       <c r="U15" s="296" t="n"/>
       <c r="V15" s="296" t="n"/>
       <c r="W15" s="296" t="n"/>
-      <c r="X15" s="295" t="n"/>
-      <c r="Y15" s="295" t="n"/>
+      <c r="X15" s="327" t="n"/>
+      <c r="Y15" s="327" t="n"/>
       <c r="Z15" s="296" t="n"/>
     </row>
     <row r="16" ht="149" customHeight="1">
@@ -6819,7 +6815,7 @@
       <c r="G16" s="300" t="n"/>
       <c r="H16" s="308" t="inlineStr">
         <is>
-          <t>PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica, revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="I16" s="308" t="inlineStr">
@@ -6848,16 +6844,16 @@
       <c r="X16" s="307" t="inlineStr">
         <is>
           <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
-D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
-        </is>
-      </c>
-      <c r="Y16" s="302" t="n"/>
+D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="Y16" s="320" t="n"/>
       <c r="Z16" s="300" t="n"/>
     </row>
     <row r="17" ht="194" customHeight="1">
       <c r="A17" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUARITA </t>
+          <t>GUARITA</t>
         </is>
       </c>
       <c r="B17" s="303" t="inlineStr">
@@ -6906,8 +6902,8 @@
         </is>
       </c>
       <c r="W17" s="300" t="n"/>
-      <c r="X17" s="302" t="n"/>
-      <c r="Y17" s="302" t="n"/>
+      <c r="X17" s="320" t="n"/>
+      <c r="Y17" s="320" t="n"/>
       <c r="Z17" s="300" t="n"/>
     </row>
     <row r="18" ht="89" customHeight="1">
@@ -6954,8 +6950,8 @@
       <c r="U18" s="300" t="n"/>
       <c r="V18" s="300" t="n"/>
       <c r="W18" s="300" t="n"/>
-      <c r="X18" s="302" t="n"/>
-      <c r="Y18" s="302" t="n"/>
+      <c r="X18" s="320" t="n"/>
+      <c r="Y18" s="320" t="n"/>
       <c r="Z18" s="300" t="n"/>
     </row>
     <row r="19" ht="89" customHeight="1">
@@ -7002,8 +6998,8 @@
       <c r="U19" s="300" t="n"/>
       <c r="V19" s="300" t="n"/>
       <c r="W19" s="300" t="n"/>
-      <c r="X19" s="302" t="n"/>
-      <c r="Y19" s="302" t="n"/>
+      <c r="X19" s="320" t="n"/>
+      <c r="Y19" s="320" t="n"/>
       <c r="Z19" s="300" t="n"/>
     </row>
     <row r="20" ht="269" customHeight="1">
@@ -7031,7 +7027,7 @@
           <t>PA1 - Parede em alvenaria com reboco convencional 2,5cm, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
 PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA54 - Parede em alvenaria regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
-PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
+PA56 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica, revestimento em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="I20" s="308" t="inlineStr">
@@ -7061,10 +7057,10 @@
       <c r="X20" s="307" t="inlineStr">
         <is>
           <t>D41 - Porta estruturada em alumínio com fechamento interno e externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A
-D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
-        </is>
-      </c>
-      <c r="Y20" s="302" t="n"/>
+D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="Y20" s="320" t="n"/>
       <c r="Z20" s="308" t="inlineStr">
         <is>
           <t>D63 - Guarda corpo em chapa metálica dourada colada sobre fechamento em MDF cru 6mm aparafusado em estrutura auxiliar de metalon. Dimensões e detalhes conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -7121,8 +7117,8 @@
         </is>
       </c>
       <c r="W21" s="300" t="n"/>
-      <c r="X21" s="302" t="n"/>
-      <c r="Y21" s="302" t="n"/>
+      <c r="X21" s="320" t="n"/>
+      <c r="Y21" s="320" t="n"/>
       <c r="Z21" s="308" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -7132,7 +7128,7 @@
     <row r="22" ht="74" customHeight="1">
       <c r="A22" s="298" t="inlineStr">
         <is>
-          <t>CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+          <t>CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTECÂMARA</t>
         </is>
       </c>
       <c r="B22" s="307" t="inlineStr">
@@ -7173,14 +7169,14 @@
       <c r="U22" s="300" t="n"/>
       <c r="V22" s="300" t="n"/>
       <c r="W22" s="300" t="n"/>
-      <c r="X22" s="302" t="n"/>
-      <c r="Y22" s="302" t="n"/>
+      <c r="X22" s="320" t="n"/>
+      <c r="Y22" s="320" t="n"/>
       <c r="Z22" s="300" t="n"/>
     </row>
     <row r="23" ht="134" customHeight="1">
       <c r="A23" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HALL GARGEM </t>
+          <t>HALL GARAGEM</t>
         </is>
       </c>
       <c r="B23" s="307" t="inlineStr">
@@ -7232,7 +7228,7 @@
 D45 - Porta pivotante em MDF com acabamento em pintura acrílica fosca. Tom a definir. Dimensões conforme Mapa de Esquadrias. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="Y23" s="302" t="n"/>
+      <c r="Y23" s="320" t="n"/>
       <c r="Z23" s="308" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -7242,7 +7238,7 @@
     <row r="24" ht="74" customHeight="1">
       <c r="A24" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAGEM </t>
+          <t>GARAGEM</t>
         </is>
       </c>
       <c r="B24" s="307" t="inlineStr">
@@ -7279,8 +7275,8 @@
       <c r="U24" s="300" t="n"/>
       <c r="V24" s="300" t="n"/>
       <c r="W24" s="300" t="n"/>
-      <c r="X24" s="302" t="n"/>
-      <c r="Y24" s="302" t="n"/>
+      <c r="X24" s="320" t="n"/>
+      <c r="Y24" s="320" t="n"/>
       <c r="Z24" s="300" t="n"/>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -7321,10 +7317,10 @@
       <c r="S25" s="300" t="n"/>
       <c r="T25" s="300" t="n"/>
       <c r="U25" s="300" t="n"/>
-      <c r="V25" s="302" t="n"/>
+      <c r="V25" s="320" t="n"/>
       <c r="W25" s="306" t="n"/>
-      <c r="X25" s="302" t="n"/>
-      <c r="Y25" s="302" t="n"/>
+      <c r="X25" s="320" t="n"/>
+      <c r="Y25" s="320" t="n"/>
       <c r="Z25" s="300" t="n"/>
     </row>
     <row r="26" ht="60" customHeight="1">
@@ -7353,16 +7349,16 @@
       <c r="S26" s="300" t="n"/>
       <c r="T26" s="300" t="n"/>
       <c r="U26" s="300" t="n"/>
-      <c r="V26" s="302" t="n"/>
+      <c r="V26" s="320" t="n"/>
       <c r="W26" s="307" t="n"/>
-      <c r="X26" s="302" t="n"/>
-      <c r="Y26" s="302" t="n"/>
+      <c r="X26" s="320" t="n"/>
+      <c r="Y26" s="320" t="n"/>
       <c r="Z26" s="307" t="n"/>
     </row>
     <row r="27" ht="89" customHeight="1">
       <c r="A27" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIRCULAÇÃO </t>
+          <t>CIRCULAÇÃO</t>
         </is>
       </c>
       <c r="B27" s="307" t="inlineStr">
@@ -7394,14 +7390,14 @@
       <c r="L27" s="300" t="n"/>
       <c r="M27" s="308" t="n"/>
       <c r="N27" s="308" t="n"/>
-      <c r="O27" s="302" t="n"/>
-      <c r="P27" s="302" t="n"/>
+      <c r="O27" s="320" t="n"/>
+      <c r="P27" s="320" t="n"/>
       <c r="Q27" s="300" t="n"/>
       <c r="R27" s="307" t="n"/>
       <c r="S27" s="300" t="n"/>
       <c r="T27" s="307" t="n"/>
       <c r="U27" s="300" t="n"/>
-      <c r="V27" s="302" t="n"/>
+      <c r="V27" s="320" t="n"/>
       <c r="W27" s="307" t="n"/>
       <c r="X27" s="307" t="n"/>
       <c r="Y27" s="307" t="n"/>
@@ -7478,10 +7474,10 @@
       <c r="W28" s="307" t="n"/>
       <c r="X28" s="307" t="inlineStr">
         <is>
-          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
-        </is>
-      </c>
-      <c r="Y28" s="302" t="n"/>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="Y28" s="320" t="n"/>
       <c r="Z28" s="307" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
@@ -7513,7 +7509,7 @@
       <c r="H29" s="307" t="inlineStr">
         <is>
           <t>PA53 - Parede em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
-PA55 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica,  revestimento em vidro 4mm temperado, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
+PA55 - Parede em alvenaria regularizada emassada, pintada com tinta acrílica, revestimento em vidro 4mm temperado, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="I29" s="307" t="inlineStr">
@@ -7541,8 +7537,8 @@
       <c r="W29" s="300" t="n"/>
       <c r="X29" s="308" t="inlineStr">
         <is>
-          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
-D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D42 - Porta estruturada em alumínio com fechamento interno ao vestíbulo em vidro 4mm temperado, cor Prada, acabamento acidato; e fechamento externo em vidro extraclean, cor Nebbia, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y29" s="300" t="n"/>
@@ -7591,7 +7587,7 @@
       <c r="S30" s="300" t="n"/>
       <c r="T30" s="307" t="n"/>
       <c r="U30" s="300" t="n"/>
-      <c r="V30" s="302" t="n"/>
+      <c r="V30" s="320" t="n"/>
       <c r="W30" s="300" t="n"/>
       <c r="X30" s="300" t="n"/>
       <c r="Y30" s="300" t="n"/>
@@ -7639,16 +7635,16 @@
       <c r="S31" s="300" t="n"/>
       <c r="T31" s="300" t="n"/>
       <c r="U31" s="300" t="n"/>
-      <c r="V31" s="302" t="n"/>
+      <c r="V31" s="320" t="n"/>
       <c r="W31" s="307" t="n"/>
-      <c r="X31" s="302" t="n"/>
-      <c r="Y31" s="302" t="n"/>
+      <c r="X31" s="320" t="n"/>
+      <c r="Y31" s="320" t="n"/>
       <c r="Z31" s="307" t="n"/>
     </row>
     <row r="32" ht="104" customHeight="1">
       <c r="A32" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIRCULAÇÃO SERVIÇO </t>
+          <t>CIRCULAÇÃO SERVIÇO</t>
         </is>
       </c>
       <c r="B32" s="307" t="inlineStr">
@@ -7687,10 +7683,10 @@
       <c r="S32" s="300" t="n"/>
       <c r="T32" s="300" t="n"/>
       <c r="U32" s="300" t="n"/>
-      <c r="V32" s="302" t="n"/>
+      <c r="V32" s="320" t="n"/>
       <c r="W32" s="307" t="n"/>
-      <c r="X32" s="302" t="n"/>
-      <c r="Y32" s="302" t="n"/>
+      <c r="X32" s="320" t="n"/>
+      <c r="Y32" s="320" t="n"/>
       <c r="Z32" s="307" t="n"/>
     </row>
     <row r="33" ht="89" customHeight="1">
@@ -7731,7 +7727,7 @@
       <c r="S33" s="300" t="n"/>
       <c r="T33" s="300" t="n"/>
       <c r="U33" s="300" t="n"/>
-      <c r="V33" s="302" t="n"/>
+      <c r="V33" s="320" t="n"/>
       <c r="W33" s="300" t="n"/>
       <c r="X33" s="300" t="n"/>
       <c r="Y33" s="300" t="n"/>
@@ -7740,7 +7736,7 @@
     <row r="34" ht="89" customHeight="1">
       <c r="A34" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">BICICLETÁRIO </t>
+          <t>BICICLETÁRIO</t>
         </is>
       </c>
       <c r="B34" s="307" t="inlineStr">
@@ -7775,16 +7771,16 @@
       <c r="S34" s="300" t="n"/>
       <c r="T34" s="300" t="n"/>
       <c r="U34" s="300" t="n"/>
-      <c r="V34" s="302" t="n"/>
+      <c r="V34" s="320" t="n"/>
       <c r="W34" s="307" t="n"/>
-      <c r="X34" s="302" t="n"/>
-      <c r="Y34" s="302" t="n"/>
+      <c r="X34" s="320" t="n"/>
+      <c r="Y34" s="320" t="n"/>
       <c r="Z34" s="307" t="n"/>
     </row>
     <row r="35" ht="89" customHeight="1">
       <c r="A35" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADORIA </t>
+          <t>ZELADORIA</t>
         </is>
       </c>
       <c r="B35" s="307" t="inlineStr">
@@ -7817,13 +7813,13 @@
       <c r="M35" s="308" t="n"/>
       <c r="N35" s="308" t="n"/>
       <c r="O35" s="307" t="n"/>
-      <c r="P35" s="302" t="n"/>
+      <c r="P35" s="320" t="n"/>
       <c r="Q35" s="300" t="n"/>
       <c r="R35" s="307" t="n"/>
       <c r="S35" s="307" t="n"/>
       <c r="T35" s="307" t="n"/>
       <c r="U35" s="300" t="n"/>
-      <c r="V35" s="302" t="n"/>
+      <c r="V35" s="320" t="n"/>
       <c r="W35" s="307" t="n"/>
       <c r="X35" s="307" t="n"/>
       <c r="Y35" s="307" t="n"/>
@@ -7861,13 +7857,13 @@
       <c r="M36" s="308" t="n"/>
       <c r="N36" s="308" t="n"/>
       <c r="O36" s="307" t="n"/>
-      <c r="P36" s="302" t="n"/>
+      <c r="P36" s="320" t="n"/>
       <c r="Q36" s="300" t="n"/>
       <c r="R36" s="307" t="n"/>
       <c r="S36" s="307" t="n"/>
       <c r="T36" s="307" t="n"/>
       <c r="U36" s="300" t="n"/>
-      <c r="V36" s="302" t="n"/>
+      <c r="V36" s="320" t="n"/>
       <c r="W36" s="307" t="n"/>
       <c r="X36" s="307" t="n"/>
       <c r="Y36" s="307" t="n"/>
@@ -7905,13 +7901,13 @@
       <c r="M37" s="308" t="n"/>
       <c r="N37" s="308" t="n"/>
       <c r="O37" s="307" t="n"/>
-      <c r="P37" s="302" t="n"/>
+      <c r="P37" s="320" t="n"/>
       <c r="Q37" s="300" t="n"/>
       <c r="R37" s="307" t="n"/>
       <c r="S37" s="307" t="n"/>
       <c r="T37" s="307" t="n"/>
       <c r="U37" s="300" t="n"/>
-      <c r="V37" s="302" t="n"/>
+      <c r="V37" s="320" t="n"/>
       <c r="W37" s="307" t="n"/>
       <c r="X37" s="307" t="n"/>
       <c r="Y37" s="307" t="n"/>
@@ -7949,13 +7945,13 @@
       <c r="M38" s="308" t="n"/>
       <c r="N38" s="308" t="n"/>
       <c r="O38" s="307" t="n"/>
-      <c r="P38" s="302" t="n"/>
+      <c r="P38" s="320" t="n"/>
       <c r="Q38" s="300" t="n"/>
       <c r="R38" s="307" t="n"/>
       <c r="S38" s="307" t="n"/>
       <c r="T38" s="307" t="n"/>
       <c r="U38" s="300" t="n"/>
-      <c r="V38" s="302" t="n"/>
+      <c r="V38" s="320" t="n"/>
       <c r="W38" s="307" t="n"/>
       <c r="X38" s="307" t="n"/>
       <c r="Y38" s="307" t="n"/>
@@ -7997,13 +7993,13 @@
       <c r="M39" s="308" t="n"/>
       <c r="N39" s="308" t="n"/>
       <c r="O39" s="307" t="n"/>
-      <c r="P39" s="302" t="n"/>
+      <c r="P39" s="320" t="n"/>
       <c r="Q39" s="300" t="n"/>
       <c r="R39" s="307" t="n"/>
       <c r="S39" s="307" t="n"/>
       <c r="T39" s="307" t="n"/>
       <c r="U39" s="300" t="n"/>
-      <c r="V39" s="302" t="n"/>
+      <c r="V39" s="320" t="n"/>
       <c r="W39" s="307" t="n"/>
       <c r="X39" s="307" t="n"/>
       <c r="Y39" s="307" t="n"/>
@@ -8041,13 +8037,13 @@
       <c r="M40" s="308" t="n"/>
       <c r="N40" s="308" t="n"/>
       <c r="O40" s="307" t="n"/>
-      <c r="P40" s="302" t="n"/>
+      <c r="P40" s="320" t="n"/>
       <c r="Q40" s="300" t="n"/>
       <c r="R40" s="307" t="n"/>
       <c r="S40" s="307" t="n"/>
       <c r="T40" s="307" t="n"/>
       <c r="U40" s="300" t="n"/>
-      <c r="V40" s="302" t="n"/>
+      <c r="V40" s="320" t="n"/>
       <c r="W40" s="307" t="n"/>
       <c r="X40" s="307" t="n"/>
       <c r="Y40" s="307" t="n"/>
@@ -8085,13 +8081,13 @@
       <c r="M41" s="308" t="n"/>
       <c r="N41" s="308" t="n"/>
       <c r="O41" s="307" t="n"/>
-      <c r="P41" s="302" t="n"/>
+      <c r="P41" s="320" t="n"/>
       <c r="Q41" s="300" t="n"/>
       <c r="R41" s="307" t="n"/>
       <c r="S41" s="307" t="n"/>
       <c r="T41" s="307" t="n"/>
       <c r="U41" s="300" t="n"/>
-      <c r="V41" s="302" t="n"/>
+      <c r="V41" s="320" t="n"/>
       <c r="W41" s="307" t="n"/>
       <c r="X41" s="307" t="n"/>
       <c r="Y41" s="307" t="n"/>
@@ -8129,13 +8125,13 @@
       <c r="M42" s="308" t="n"/>
       <c r="N42" s="308" t="n"/>
       <c r="O42" s="307" t="n"/>
-      <c r="P42" s="302" t="n"/>
+      <c r="P42" s="320" t="n"/>
       <c r="Q42" s="300" t="n"/>
       <c r="R42" s="307" t="n"/>
       <c r="S42" s="307" t="n"/>
       <c r="T42" s="307" t="n"/>
       <c r="U42" s="300" t="n"/>
-      <c r="V42" s="302" t="n"/>
+      <c r="V42" s="320" t="n"/>
       <c r="W42" s="307" t="n"/>
       <c r="X42" s="307" t="n"/>
       <c r="Y42" s="307" t="n"/>
@@ -8173,13 +8169,13 @@
       <c r="M43" s="308" t="n"/>
       <c r="N43" s="308" t="n"/>
       <c r="O43" s="307" t="n"/>
-      <c r="P43" s="302" t="n"/>
+      <c r="P43" s="320" t="n"/>
       <c r="Q43" s="300" t="n"/>
       <c r="R43" s="307" t="n"/>
       <c r="S43" s="307" t="n"/>
       <c r="T43" s="307" t="n"/>
       <c r="U43" s="300" t="n"/>
-      <c r="V43" s="302" t="n"/>
+      <c r="V43" s="320" t="n"/>
       <c r="W43" s="307" t="n"/>
       <c r="X43" s="307" t="n"/>
       <c r="Y43" s="307" t="n"/>
@@ -8217,13 +8213,13 @@
       <c r="M44" s="308" t="n"/>
       <c r="N44" s="308" t="n"/>
       <c r="O44" s="307" t="n"/>
-      <c r="P44" s="302" t="n"/>
+      <c r="P44" s="320" t="n"/>
       <c r="Q44" s="300" t="n"/>
       <c r="R44" s="307" t="n"/>
       <c r="S44" s="307" t="n"/>
       <c r="T44" s="307" t="n"/>
       <c r="U44" s="300" t="n"/>
-      <c r="V44" s="302" t="n"/>
+      <c r="V44" s="320" t="n"/>
       <c r="W44" s="307" t="n"/>
       <c r="X44" s="307" t="n"/>
       <c r="Y44" s="307" t="n"/>
@@ -8232,7 +8228,7 @@
     <row r="45" ht="89" customHeight="1">
       <c r="A45" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIRCULAÇÃO </t>
+          <t>CIRCULAÇÃO</t>
         </is>
       </c>
       <c r="B45" s="307" t="inlineStr">
@@ -8265,13 +8261,13 @@
       <c r="M45" s="308" t="n"/>
       <c r="N45" s="308" t="n"/>
       <c r="O45" s="307" t="n"/>
-      <c r="P45" s="302" t="n"/>
+      <c r="P45" s="320" t="n"/>
       <c r="Q45" s="300" t="n"/>
       <c r="R45" s="307" t="n"/>
       <c r="S45" s="307" t="n"/>
       <c r="T45" s="307" t="n"/>
       <c r="U45" s="300" t="n"/>
-      <c r="V45" s="302" t="n"/>
+      <c r="V45" s="320" t="n"/>
       <c r="W45" s="307" t="n"/>
       <c r="X45" s="307" t="n"/>
       <c r="Y45" s="307" t="n"/>
@@ -8309,13 +8305,13 @@
       <c r="M46" s="308" t="n"/>
       <c r="N46" s="308" t="n"/>
       <c r="O46" s="307" t="n"/>
-      <c r="P46" s="302" t="n"/>
+      <c r="P46" s="320" t="n"/>
       <c r="Q46" s="300" t="n"/>
       <c r="R46" s="307" t="n"/>
       <c r="S46" s="307" t="n"/>
       <c r="T46" s="307" t="n"/>
       <c r="U46" s="300" t="n"/>
-      <c r="V46" s="302" t="n"/>
+      <c r="V46" s="320" t="n"/>
       <c r="W46" s="307" t="n"/>
       <c r="X46" s="307" t="n"/>
       <c r="Y46" s="307" t="n"/>
@@ -8353,13 +8349,13 @@
       <c r="M47" s="308" t="n"/>
       <c r="N47" s="308" t="n"/>
       <c r="O47" s="307" t="n"/>
-      <c r="P47" s="302" t="n"/>
+      <c r="P47" s="320" t="n"/>
       <c r="Q47" s="300" t="n"/>
       <c r="R47" s="307" t="n"/>
       <c r="S47" s="307" t="n"/>
       <c r="T47" s="307" t="n"/>
       <c r="U47" s="300" t="n"/>
-      <c r="V47" s="302" t="n"/>
+      <c r="V47" s="320" t="n"/>
       <c r="W47" s="307" t="n"/>
       <c r="X47" s="307" t="n"/>
       <c r="Y47" s="307" t="n"/>
@@ -8397,13 +8393,13 @@
       <c r="M48" s="308" t="n"/>
       <c r="N48" s="308" t="n"/>
       <c r="O48" s="307" t="n"/>
-      <c r="P48" s="302" t="n"/>
+      <c r="P48" s="320" t="n"/>
       <c r="Q48" s="300" t="n"/>
       <c r="R48" s="307" t="n"/>
       <c r="S48" s="307" t="n"/>
       <c r="T48" s="307" t="n"/>
       <c r="U48" s="300" t="n"/>
-      <c r="V48" s="302" t="n"/>
+      <c r="V48" s="320" t="n"/>
       <c r="W48" s="307" t="n"/>
       <c r="X48" s="307" t="n"/>
       <c r="Y48" s="307" t="n"/>
@@ -8437,13 +8433,13 @@
       <c r="M49" s="308" t="n"/>
       <c r="N49" s="308" t="n"/>
       <c r="O49" s="307" t="n"/>
-      <c r="P49" s="302" t="n"/>
+      <c r="P49" s="320" t="n"/>
       <c r="Q49" s="300" t="n"/>
       <c r="R49" s="307" t="n"/>
       <c r="S49" s="307" t="n"/>
       <c r="T49" s="307" t="n"/>
       <c r="U49" s="300" t="n"/>
-      <c r="V49" s="302" t="n"/>
+      <c r="V49" s="320" t="n"/>
       <c r="W49" s="307" t="n"/>
       <c r="X49" s="307" t="n"/>
       <c r="Y49" s="307" t="n"/>
@@ -8481,13 +8477,13 @@
       <c r="M50" s="308" t="n"/>
       <c r="N50" s="308" t="n"/>
       <c r="O50" s="307" t="n"/>
-      <c r="P50" s="302" t="n"/>
+      <c r="P50" s="320" t="n"/>
       <c r="Q50" s="300" t="n"/>
       <c r="R50" s="307" t="n"/>
       <c r="S50" s="307" t="n"/>
       <c r="T50" s="307" t="n"/>
       <c r="U50" s="300" t="n"/>
-      <c r="V50" s="302" t="n"/>
+      <c r="V50" s="320" t="n"/>
       <c r="W50" s="307" t="n"/>
       <c r="X50" s="307" t="n"/>
       <c r="Y50" s="307" t="n"/>
@@ -8525,13 +8521,13 @@
       <c r="M51" s="308" t="n"/>
       <c r="N51" s="308" t="n"/>
       <c r="O51" s="307" t="n"/>
-      <c r="P51" s="302" t="n"/>
+      <c r="P51" s="320" t="n"/>
       <c r="Q51" s="300" t="n"/>
       <c r="R51" s="307" t="n"/>
       <c r="S51" s="307" t="n"/>
       <c r="T51" s="307" t="n"/>
       <c r="U51" s="300" t="n"/>
-      <c r="V51" s="302" t="n"/>
+      <c r="V51" s="320" t="n"/>
       <c r="W51" s="307" t="n"/>
       <c r="X51" s="307" t="n"/>
       <c r="Y51" s="307" t="n"/>
@@ -8569,13 +8565,13 @@
       <c r="M52" s="308" t="n"/>
       <c r="N52" s="308" t="n"/>
       <c r="O52" s="307" t="n"/>
-      <c r="P52" s="302" t="n"/>
+      <c r="P52" s="320" t="n"/>
       <c r="Q52" s="300" t="n"/>
       <c r="R52" s="307" t="n"/>
       <c r="S52" s="307" t="n"/>
       <c r="T52" s="307" t="n"/>
       <c r="U52" s="300" t="n"/>
-      <c r="V52" s="302" t="n"/>
+      <c r="V52" s="320" t="n"/>
       <c r="W52" s="307" t="n"/>
       <c r="X52" s="307" t="n"/>
       <c r="Y52" s="307" t="n"/>
@@ -8617,13 +8613,13 @@
       <c r="M53" s="308" t="n"/>
       <c r="N53" s="308" t="n"/>
       <c r="O53" s="307" t="n"/>
-      <c r="P53" s="302" t="n"/>
+      <c r="P53" s="320" t="n"/>
       <c r="Q53" s="300" t="n"/>
       <c r="R53" s="307" t="n"/>
       <c r="S53" s="307" t="n"/>
       <c r="T53" s="307" t="n"/>
       <c r="U53" s="300" t="n"/>
-      <c r="V53" s="302" t="n"/>
+      <c r="V53" s="320" t="n"/>
       <c r="W53" s="307" t="n"/>
       <c r="X53" s="307" t="n"/>
       <c r="Y53" s="307" t="n"/>
@@ -8661,13 +8657,13 @@
       <c r="M54" s="308" t="n"/>
       <c r="N54" s="308" t="n"/>
       <c r="O54" s="307" t="n"/>
-      <c r="P54" s="302" t="n"/>
+      <c r="P54" s="320" t="n"/>
       <c r="Q54" s="300" t="n"/>
       <c r="R54" s="307" t="n"/>
       <c r="S54" s="307" t="n"/>
       <c r="T54" s="307" t="n"/>
       <c r="U54" s="300" t="n"/>
-      <c r="V54" s="302" t="n"/>
+      <c r="V54" s="320" t="n"/>
       <c r="W54" s="307" t="n"/>
       <c r="X54" s="307" t="n"/>
       <c r="Y54" s="307" t="n"/>
@@ -8697,13 +8693,13 @@
       <c r="M55" s="308" t="n"/>
       <c r="N55" s="308" t="n"/>
       <c r="O55" s="307" t="n"/>
-      <c r="P55" s="302" t="n"/>
+      <c r="P55" s="320" t="n"/>
       <c r="Q55" s="300" t="n"/>
       <c r="R55" s="307" t="n"/>
       <c r="S55" s="307" t="n"/>
       <c r="T55" s="307" t="n"/>
       <c r="U55" s="300" t="n"/>
-      <c r="V55" s="302" t="n"/>
+      <c r="V55" s="320" t="n"/>
       <c r="W55" s="307" t="n"/>
       <c r="X55" s="307" t="n"/>
       <c r="Y55" s="307" t="n"/>
@@ -8733,13 +8729,13 @@
       <c r="M56" s="308" t="n"/>
       <c r="N56" s="308" t="n"/>
       <c r="O56" s="307" t="n"/>
-      <c r="P56" s="302" t="n"/>
+      <c r="P56" s="320" t="n"/>
       <c r="Q56" s="300" t="n"/>
       <c r="R56" s="307" t="n"/>
       <c r="S56" s="307" t="n"/>
       <c r="T56" s="307" t="n"/>
       <c r="U56" s="300" t="n"/>
-      <c r="V56" s="302" t="n"/>
+      <c r="V56" s="320" t="n"/>
       <c r="W56" s="307" t="n"/>
       <c r="X56" s="307" t="n"/>
       <c r="Y56" s="307" t="n"/>
@@ -9409,7 +9405,7 @@
       <c r="A12" s="51" t="n"/>
       <c r="B12" s="124" t="inlineStr">
         <is>
-          <t>GERAL — SEM ESPECIFICAÇÕES NA TABELA DE ACABAMENTOS V00 (A TABELA ABRANGE SOMENTE O 3º PAVIMENTO - PILOTIS)</t>
+          <t>GERAL — 2º PAVIMENTO PELAS PLANTAS DE ARQUITETURA PR007 A PR009 (O DETALHAMENTO R04 SÓ TRAZ MOBILIÁRIO)</t>
         </is>
       </c>
       <c r="C12" s="241" t="n"/>
@@ -9485,8 +9481,8 @@
       <c r="U13" s="296" t="n"/>
       <c r="V13" s="296" t="n"/>
       <c r="W13" s="296" t="n"/>
-      <c r="X13" s="295" t="n"/>
-      <c r="Y13" s="295" t="n"/>
+      <c r="X13" s="327" t="n"/>
+      <c r="Y13" s="327" t="n"/>
       <c r="Z13" s="296" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -9529,24 +9525,24 @@
       <c r="U14" s="300" t="n"/>
       <c r="V14" s="300" t="n"/>
       <c r="W14" s="300" t="n"/>
-      <c r="X14" s="302" t="n"/>
-      <c r="Y14" s="302" t="n"/>
+      <c r="X14" s="320" t="n"/>
+      <c r="Y14" s="320" t="n"/>
       <c r="Z14" s="300" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HALL GARAGEM </t>
-        </is>
-      </c>
-      <c r="B15" s="302" t="n"/>
+          <t>HALL GARAGEM</t>
+        </is>
+      </c>
+      <c r="B15" s="320" t="n"/>
       <c r="C15" s="300" t="n"/>
       <c r="D15" s="300" t="n"/>
       <c r="E15" s="300" t="n"/>
       <c r="F15" s="300" t="n"/>
       <c r="G15" s="300" t="n"/>
-      <c r="H15" s="311" t="n"/>
-      <c r="I15" s="311" t="n"/>
+      <c r="H15" s="317" t="n"/>
+      <c r="I15" s="317" t="n"/>
       <c r="J15" s="300" t="n"/>
       <c r="K15" s="300" t="n"/>
       <c r="L15" s="300" t="n"/>
@@ -9561,8 +9557,8 @@
       <c r="U15" s="300" t="n"/>
       <c r="V15" s="300" t="n"/>
       <c r="W15" s="300" t="n"/>
-      <c r="X15" s="302" t="n"/>
-      <c r="Y15" s="302" t="n"/>
+      <c r="X15" s="320" t="n"/>
+      <c r="Y15" s="320" t="n"/>
       <c r="Z15" s="300" t="n"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -9571,14 +9567,14 @@
           <t>HALL ELEVADOR SOCIAL</t>
         </is>
       </c>
-      <c r="B16" s="302" t="n"/>
+      <c r="B16" s="320" t="n"/>
       <c r="C16" s="300" t="n"/>
       <c r="D16" s="300" t="n"/>
       <c r="E16" s="300" t="n"/>
       <c r="F16" s="300" t="n"/>
       <c r="G16" s="300" t="n"/>
-      <c r="H16" s="311" t="n"/>
-      <c r="I16" s="311" t="n"/>
+      <c r="H16" s="317" t="n"/>
+      <c r="I16" s="317" t="n"/>
       <c r="J16" s="300" t="n"/>
       <c r="K16" s="300" t="n"/>
       <c r="L16" s="300" t="n"/>
@@ -9593,8 +9589,8 @@
       <c r="U16" s="300" t="n"/>
       <c r="V16" s="300" t="n"/>
       <c r="W16" s="300" t="n"/>
-      <c r="X16" s="302" t="n"/>
-      <c r="Y16" s="302" t="n"/>
+      <c r="X16" s="320" t="n"/>
+      <c r="Y16" s="320" t="n"/>
       <c r="Z16" s="300" t="n"/>
     </row>
     <row r="17" ht="119" customHeight="1">
@@ -9642,8 +9638,8 @@
       <c r="U17" s="300" t="n"/>
       <c r="V17" s="300" t="n"/>
       <c r="W17" s="300" t="n"/>
-      <c r="X17" s="302" t="n"/>
-      <c r="Y17" s="302" t="n"/>
+      <c r="X17" s="320" t="n"/>
+      <c r="Y17" s="320" t="n"/>
       <c r="Z17" s="300" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -9686,8 +9682,8 @@
       <c r="U18" s="300" t="n"/>
       <c r="V18" s="300" t="n"/>
       <c r="W18" s="300" t="n"/>
-      <c r="X18" s="302" t="n"/>
-      <c r="Y18" s="302" t="n"/>
+      <c r="X18" s="320" t="n"/>
+      <c r="Y18" s="320" t="n"/>
       <c r="Z18" s="300" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -9730,8 +9726,8 @@
       <c r="U19" s="300" t="n"/>
       <c r="V19" s="300" t="n"/>
       <c r="W19" s="300" t="n"/>
-      <c r="X19" s="302" t="n"/>
-      <c r="Y19" s="302" t="n"/>
+      <c r="X19" s="320" t="n"/>
+      <c r="Y19" s="320" t="n"/>
       <c r="Z19" s="300" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -9774,8 +9770,8 @@
       <c r="U20" s="300" t="n"/>
       <c r="V20" s="300" t="n"/>
       <c r="W20" s="300" t="n"/>
-      <c r="X20" s="302" t="n"/>
-      <c r="Y20" s="302" t="n"/>
+      <c r="X20" s="320" t="n"/>
+      <c r="Y20" s="320" t="n"/>
       <c r="Z20" s="300" t="n"/>
     </row>
     <row r="21" ht="74" customHeight="1">
@@ -9816,10 +9812,10 @@
       <c r="S21" s="300" t="n"/>
       <c r="T21" s="300" t="n"/>
       <c r="U21" s="300" t="n"/>
-      <c r="V21" s="302" t="n"/>
+      <c r="V21" s="320" t="n"/>
       <c r="W21" s="306" t="n"/>
-      <c r="X21" s="302" t="n"/>
-      <c r="Y21" s="302" t="n"/>
+      <c r="X21" s="320" t="n"/>
+      <c r="Y21" s="320" t="n"/>
       <c r="Z21" s="300" t="n"/>
     </row>
     <row r="22" ht="74" customHeight="1">
@@ -9860,10 +9856,10 @@
       <c r="S22" s="300" t="n"/>
       <c r="T22" s="300" t="n"/>
       <c r="U22" s="300" t="n"/>
-      <c r="V22" s="302" t="n"/>
+      <c r="V22" s="320" t="n"/>
       <c r="W22" s="307" t="n"/>
-      <c r="X22" s="302" t="n"/>
-      <c r="Y22" s="302" t="n"/>
+      <c r="X22" s="320" t="n"/>
+      <c r="Y22" s="320" t="n"/>
       <c r="Z22" s="307" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -9897,14 +9893,14 @@
       <c r="L23" s="300" t="n"/>
       <c r="M23" s="308" t="n"/>
       <c r="N23" s="308" t="n"/>
-      <c r="O23" s="302" t="n"/>
-      <c r="P23" s="302" t="n"/>
+      <c r="O23" s="320" t="n"/>
+      <c r="P23" s="320" t="n"/>
       <c r="Q23" s="300" t="n"/>
       <c r="R23" s="307" t="n"/>
       <c r="S23" s="300" t="n"/>
       <c r="T23" s="307" t="n"/>
       <c r="U23" s="300" t="n"/>
-      <c r="V23" s="302" t="n"/>
+      <c r="V23" s="320" t="n"/>
       <c r="W23" s="307" t="n"/>
       <c r="X23" s="307" t="n"/>
       <c r="Y23" s="307" t="n"/>
@@ -9948,10 +9944,10 @@
       <c r="S24" s="300" t="n"/>
       <c r="T24" s="307" t="n"/>
       <c r="U24" s="300" t="n"/>
-      <c r="V24" s="302" t="n"/>
+      <c r="V24" s="320" t="n"/>
       <c r="W24" s="307" t="n"/>
-      <c r="X24" s="302" t="n"/>
-      <c r="Y24" s="302" t="n"/>
+      <c r="X24" s="320" t="n"/>
+      <c r="Y24" s="320" t="n"/>
       <c r="Z24" s="307" t="n"/>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -9992,7 +9988,7 @@
       <c r="S25" s="300" t="n"/>
       <c r="T25" s="300" t="n"/>
       <c r="U25" s="300" t="n"/>
-      <c r="V25" s="302" t="n"/>
+      <c r="V25" s="320" t="n"/>
       <c r="W25" s="300" t="n"/>
       <c r="X25" s="300" t="n"/>
       <c r="Y25" s="300" t="n"/>
@@ -10036,7 +10032,7 @@
       <c r="S26" s="300" t="n"/>
       <c r="T26" s="307" t="n"/>
       <c r="U26" s="300" t="n"/>
-      <c r="V26" s="302" t="n"/>
+      <c r="V26" s="320" t="n"/>
       <c r="W26" s="300" t="n"/>
       <c r="X26" s="300" t="n"/>
       <c r="Y26" s="300" t="n"/>
@@ -10080,10 +10076,10 @@
       <c r="S27" s="300" t="n"/>
       <c r="T27" s="300" t="n"/>
       <c r="U27" s="300" t="n"/>
-      <c r="V27" s="302" t="n"/>
+      <c r="V27" s="320" t="n"/>
       <c r="W27" s="307" t="n"/>
-      <c r="X27" s="302" t="n"/>
-      <c r="Y27" s="302" t="n"/>
+      <c r="X27" s="320" t="n"/>
+      <c r="Y27" s="320" t="n"/>
       <c r="Z27" s="307" t="n"/>
     </row>
     <row r="28" ht="60" customHeight="1">
@@ -10124,10 +10120,10 @@
       <c r="S28" s="300" t="n"/>
       <c r="T28" s="300" t="n"/>
       <c r="U28" s="300" t="n"/>
-      <c r="V28" s="302" t="n"/>
+      <c r="V28" s="320" t="n"/>
       <c r="W28" s="307" t="n"/>
-      <c r="X28" s="302" t="n"/>
-      <c r="Y28" s="302" t="n"/>
+      <c r="X28" s="320" t="n"/>
+      <c r="Y28" s="320" t="n"/>
       <c r="Z28" s="307" t="n"/>
     </row>
     <row r="29" ht="74" customHeight="1">
@@ -10168,10 +10164,10 @@
       <c r="S29" s="300" t="n"/>
       <c r="T29" s="300" t="n"/>
       <c r="U29" s="300" t="n"/>
-      <c r="V29" s="302" t="n"/>
+      <c r="V29" s="320" t="n"/>
       <c r="W29" s="307" t="n"/>
-      <c r="X29" s="302" t="n"/>
-      <c r="Y29" s="302" t="n"/>
+      <c r="X29" s="320" t="n"/>
+      <c r="Y29" s="320" t="n"/>
       <c r="Z29" s="307" t="n"/>
     </row>
     <row r="30" ht="60" customHeight="1">
@@ -10212,10 +10208,10 @@
       <c r="S30" s="300" t="n"/>
       <c r="T30" s="300" t="n"/>
       <c r="U30" s="300" t="n"/>
-      <c r="V30" s="302" t="n"/>
+      <c r="V30" s="320" t="n"/>
       <c r="W30" s="307" t="n"/>
-      <c r="X30" s="302" t="n"/>
-      <c r="Y30" s="302" t="n"/>
+      <c r="X30" s="320" t="n"/>
+      <c r="Y30" s="320" t="n"/>
       <c r="Z30" s="307" t="n"/>
     </row>
     <row r="31" ht="60" customHeight="1">
@@ -10256,10 +10252,10 @@
       <c r="S31" s="300" t="n"/>
       <c r="T31" s="300" t="n"/>
       <c r="U31" s="300" t="n"/>
-      <c r="V31" s="302" t="n"/>
+      <c r="V31" s="320" t="n"/>
       <c r="W31" s="307" t="n"/>
-      <c r="X31" s="302" t="n"/>
-      <c r="Y31" s="302" t="n"/>
+      <c r="X31" s="320" t="n"/>
+      <c r="Y31" s="320" t="n"/>
       <c r="Z31" s="307" t="n"/>
     </row>
     <row r="32"/>
@@ -10985,7 +10981,7 @@
       <c r="Y12" s="241" t="n"/>
       <c r="Z12" s="242" t="n"/>
     </row>
-    <row r="13" ht="299" customHeight="1">
+    <row r="13" ht="284" customHeight="1">
       <c r="A13" s="294" t="inlineStr">
         <is>
           <t>LOBBY PILOTIS</t>
@@ -11043,13 +11039,13 @@
       <c r="W13" s="296" t="n"/>
       <c r="X13" s="325" t="inlineStr">
         <is>
-          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
-D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+          <t>D19 - Porta pivotante estruturada, fechamento em MDF cru, face interna ao I.S. com acabamento em folha madeira natural carvalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
 D74 - Porta pivotante estruturada, fechamento em MDF cru, acabamento face interna e externa em micropintura cor S168-Sayerlack. Puxador tipo cava, prever tranca. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 D85 - Porta corta fogo em aço inox escovado. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
-      <c r="Y13" s="295" t="n"/>
+      <c r="Y13" s="327" t="n"/>
       <c r="Z13" s="296" t="n"/>
     </row>
     <row r="14" ht="284" customHeight="1">
@@ -11115,7 +11111,7 @@
 D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="Y14" s="302" t="n"/>
+      <c r="Y14" s="320" t="n"/>
       <c r="Z14" s="300" t="n"/>
     </row>
     <row r="15" ht="119" customHeight="1">
@@ -11124,7 +11120,7 @@
           <t>TERRAÇO SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B15" s="302" t="inlineStr">
+      <c r="B15" s="320" t="inlineStr">
         <is>
           <t>ARQ-P08 - Piso elevado em granito cinza santa rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material. (Planta PR011)</t>
         </is>
@@ -11134,8 +11130,8 @@
       <c r="E15" s="300" t="n"/>
       <c r="F15" s="300" t="n"/>
       <c r="G15" s="300" t="n"/>
-      <c r="H15" s="311" t="n"/>
-      <c r="I15" s="311" t="n"/>
+      <c r="H15" s="317" t="n"/>
+      <c r="I15" s="317" t="n"/>
       <c r="J15" s="300" t="n"/>
       <c r="K15" s="300" t="n"/>
       <c r="L15" s="300" t="n"/>
@@ -11150,8 +11146,8 @@
       <c r="U15" s="300" t="n"/>
       <c r="V15" s="300" t="n"/>
       <c r="W15" s="300" t="n"/>
-      <c r="X15" s="302" t="n"/>
-      <c r="Y15" s="302" t="n"/>
+      <c r="X15" s="320" t="n"/>
+      <c r="Y15" s="320" t="n"/>
       <c r="Z15" s="300" t="n"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -11160,14 +11156,14 @@
           <t>CIRCULAÇÃO SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="B16" s="302" t="n"/>
+      <c r="B16" s="320" t="n"/>
       <c r="C16" s="300" t="n"/>
       <c r="D16" s="300" t="n"/>
       <c r="E16" s="300" t="n"/>
       <c r="F16" s="300" t="n"/>
       <c r="G16" s="300" t="n"/>
-      <c r="H16" s="311" t="n"/>
-      <c r="I16" s="311" t="n"/>
+      <c r="H16" s="317" t="n"/>
+      <c r="I16" s="317" t="n"/>
       <c r="J16" s="300" t="n"/>
       <c r="K16" s="300" t="n"/>
       <c r="L16" s="300" t="n"/>
@@ -11182,8 +11178,8 @@
       <c r="U16" s="300" t="n"/>
       <c r="V16" s="300" t="n"/>
       <c r="W16" s="300" t="n"/>
-      <c r="X16" s="302" t="n"/>
-      <c r="Y16" s="302" t="n"/>
+      <c r="X16" s="320" t="n"/>
+      <c r="Y16" s="320" t="n"/>
       <c r="Z16" s="300" t="n"/>
     </row>
     <row r="17" ht="224" customHeight="1">
@@ -11256,7 +11252,7 @@
           <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="Y17" s="302" t="n"/>
+      <c r="Y17" s="320" t="n"/>
       <c r="Z17" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
@@ -11335,7 +11331,7 @@
           <t>D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="Y18" s="302" t="n"/>
+      <c r="Y18" s="320" t="n"/>
       <c r="Z18" s="317" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
@@ -11350,14 +11346,14 @@
           <t>APOIO COZINHA</t>
         </is>
       </c>
-      <c r="B19" s="302" t="n"/>
+      <c r="B19" s="320" t="n"/>
       <c r="C19" s="300" t="n"/>
       <c r="D19" s="300" t="n"/>
       <c r="E19" s="300" t="n"/>
       <c r="F19" s="300" t="n"/>
       <c r="G19" s="300" t="n"/>
-      <c r="H19" s="311" t="n"/>
-      <c r="I19" s="311" t="n"/>
+      <c r="H19" s="317" t="n"/>
+      <c r="I19" s="317" t="n"/>
       <c r="J19" s="300" t="n"/>
       <c r="K19" s="300" t="n"/>
       <c r="L19" s="300" t="n"/>
@@ -11372,8 +11368,8 @@
       <c r="U19" s="300" t="n"/>
       <c r="V19" s="300" t="n"/>
       <c r="W19" s="300" t="n"/>
-      <c r="X19" s="302" t="n"/>
-      <c r="Y19" s="302" t="n"/>
+      <c r="X19" s="320" t="n"/>
+      <c r="Y19" s="320" t="n"/>
       <c r="Z19" s="300" t="n"/>
     </row>
     <row r="20" ht="224" customHeight="1">
@@ -11423,7 +11419,7 @@
       <c r="N20" s="300" t="n"/>
       <c r="O20" s="317" t="inlineStr">
         <is>
-          <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scoth Brite, cód.: 94520022. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scotch Brite, cód.: 94520022. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário.</t>
         </is>
       </c>
       <c r="P20" s="300" t="n"/>
@@ -11444,7 +11440,7 @@
 D74 - Porta pivotante estruturada, fechamento em MDF cru, acabamento face interna e externa em micropintura cor S168-Sayerlack. Puxador tipo cava, prever tranca. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
-      <c r="Y20" s="302" t="n"/>
+      <c r="Y20" s="320" t="n"/>
       <c r="Z20" s="308" t="inlineStr">
         <is>
           <t>D82 - Prateleira em granito cinza Santa Rosa, acabamento escovado, embutido na alvenaria. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -11503,8 +11499,8 @@
       <c r="U21" s="300" t="n"/>
       <c r="V21" s="300" t="n"/>
       <c r="W21" s="300" t="n"/>
-      <c r="X21" s="302" t="n"/>
-      <c r="Y21" s="302" t="n"/>
+      <c r="X21" s="320" t="n"/>
+      <c r="Y21" s="320" t="n"/>
       <c r="Z21" s="300" t="n"/>
     </row>
     <row r="22" ht="104" customHeight="1">
@@ -11549,10 +11545,10 @@
       <c r="S22" s="300" t="n"/>
       <c r="T22" s="300" t="n"/>
       <c r="U22" s="300" t="n"/>
-      <c r="V22" s="302" t="n"/>
+      <c r="V22" s="320" t="n"/>
       <c r="W22" s="306" t="n"/>
-      <c r="X22" s="302" t="n"/>
-      <c r="Y22" s="302" t="n"/>
+      <c r="X22" s="320" t="n"/>
+      <c r="Y22" s="320" t="n"/>
       <c r="Z22" s="300" t="n"/>
     </row>
     <row r="23" ht="269" customHeight="1">
@@ -11578,7 +11574,7 @@
       <c r="H23" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
-PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
+PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural carvalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
@@ -11594,7 +11590,7 @@
       </c>
       <c r="K23" s="317" t="inlineStr">
         <is>
-          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural carvalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L23" s="300" t="n"/>
@@ -11623,10 +11619,10 @@
       <c r="W23" s="307" t="n"/>
       <c r="X23" s="307" t="inlineStr">
         <is>
-          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
-        </is>
-      </c>
-      <c r="Y23" s="302" t="n"/>
+          <t>D19 - Porta pivotante estruturada, fechamento em MDF cru, face interna ao I.S. com acabamento em folha madeira natural carvalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+      <c r="Y23" s="320" t="n"/>
       <c r="Z23" s="320" t="inlineStr">
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
@@ -11638,7 +11634,7 @@
     <row r="24" ht="269" customHeight="1">
       <c r="A24" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">I.S </t>
+          <t>I.S</t>
         </is>
       </c>
       <c r="B24" s="320" t="inlineStr">
@@ -11658,7 +11654,7 @@
       <c r="H24" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
-PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
+PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural carvalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
 PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
@@ -11674,7 +11670,7 @@
       </c>
       <c r="K24" s="317" t="inlineStr">
         <is>
-          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural carvalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L24" s="300" t="n"/>
@@ -11703,7 +11699,7 @@
       <c r="W24" s="307" t="n"/>
       <c r="X24" s="307" t="inlineStr">
         <is>
-          <t>D19 - Porta pivotante estruturada, fechamento em  MDF cru, face interna ao I.S. com acabamento em folha madeira natural caravalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+          <t>D19 - Porta pivotante estruturada, fechamento em MDF cru, face interna ao I.S. com acabamento em folha madeira natural carvalho tonalizado e face externa cor S168-Sayerlack. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="Y24" s="307" t="n"/>
@@ -11718,7 +11714,7 @@
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIRCULAÇÃO LAVABOS </t>
+          <t>CIRCULAÇÃO LAVABOS</t>
         </is>
       </c>
       <c r="B25" s="307" t="n"/>
@@ -11741,10 +11737,10 @@
       <c r="S25" s="300" t="n"/>
       <c r="T25" s="307" t="n"/>
       <c r="U25" s="300" t="n"/>
-      <c r="V25" s="302" t="n"/>
+      <c r="V25" s="320" t="n"/>
       <c r="W25" s="307" t="n"/>
-      <c r="X25" s="302" t="n"/>
-      <c r="Y25" s="302" t="n"/>
+      <c r="X25" s="320" t="n"/>
+      <c r="Y25" s="320" t="n"/>
       <c r="Z25" s="307" t="n"/>
     </row>
     <row r="26" ht="389" customHeight="1">
@@ -11771,7 +11767,7 @@
       <c r="H26" s="320" t="inlineStr">
         <is>
           <t>PA34 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
-PA35 - Parede em alvenaria emassada regularizada, revestida em MDF cru 8mm para regularização da superficie e acabamento em chapa metálica - #16 (aço carbono) colda sobre MDF ou fixada através de fita dupla face 3M -  finalização em micropintura cor S081-Sayerlack. Ver detalhes específicos e amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA35 - Parede em alvenaria emassada regularizada, revestida em MDF cru 8mm para regularização da superficie e acabamento em chapa metálica - #16 (aço carbono) colda sobre MDF ou fixada através de fita dupla face 3M - finalização em micropintura cor S081-Sayerlack. Ver detalhes específicos e amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA36 - Parede em alvenaria emassada regularizada, revestida em painel de MDF cru 8mm + chpa de 4mm com acabamento em mircropintura em cor N081-Sayerlack colada sobre MDF cru. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA37 - Parede emassada regularizada revestida com papel de parede degradê laranja 114-Branco casa. Cód Ref.: BR0114_B10099_PDP_TM. Amostra a ser aprovada pela GPA&amp;A.
 PA38 - Parede em alvenaria emassada regularizada, revestida em painel de marcenaria MDF Nude-linha VEL-Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.</t>
@@ -11804,14 +11800,14 @@
       <c r="W26" s="307" t="n"/>
       <c r="X26" s="307" t="inlineStr">
         <is>
-          <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
-D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
-        </is>
-      </c>
-      <c r="Y26" s="302" t="n"/>
+          <t>D11 - Porta pivotante estruturada, fechamento em MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural carvalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="Y26" s="320" t="n"/>
       <c r="Z26" s="307" t="inlineStr">
         <is>
-          <t>D18 - Módulos compostos por três peças hexagonais com estruturado em peças de madeira maciça,   fechamento em reguas de madeira 25mmx70mm. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+          <t>D18 - Módulos compostos por três peças hexagonais com estruturado em peças de madeira maciça, fechamento em reguas de madeira 25mmx70mm. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D56 - Pendente sob medida em peças de madeira maciça 60x50mm fixados no teto através de cabos de aço e estrutura auxiliar no entreforro, com acabamento no forro em canopla, cor branca. Retroiluminação em fitas de led na parte superior com dimensionamentos conforme projeto luminotécnico. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
@@ -11840,7 +11836,7 @@
       <c r="H27" s="320" t="inlineStr">
         <is>
           <t>PA44 - Parede em alvenaria emassada regularizada, revestida em massa acrílica texturizada cimento queimado, cor 107. Ref.: Terracor CQ. Amostra a ser aprovada pela GPA&amp;A.
-PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural caravalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
+PA32 - Parede em alvenaria emassada regularizada, revestida em mdf cru para regularização da superficie e acabamento em folha madeira natural carvalho tonalizado, acabamento. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural deve possuir certificação FSC ou CERFLOR
 PA33 - Pilar em alvenaria rebocada regularizada, revestida em pedra natural, Basaltina, acabamento frisado. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
@@ -11869,7 +11865,7 @@
       <c r="N27" s="307" t="n"/>
       <c r="O27" s="320" t="inlineStr">
         <is>
-          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
+          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.: REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
         </is>
       </c>
       <c r="P27" s="300" t="n"/>
@@ -11886,7 +11882,7 @@
       <c r="W27" s="300" t="n"/>
       <c r="X27" s="308" t="inlineStr">
         <is>
-          <t>D11 - Porta pivotante estruturada, fechamento em  MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural caravalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+          <t>D11 - Porta pivotante estruturada, fechamento em MDF cru, acabamento micro pintura face do kids cor S081-Sayerlack e acabamento face do gourmet em folha madeira natural carvalho tonalizado. Batente em cantoneira metálica conforme detalhe. Dimensões e desenho conforme detalhamento. Puxador Round linha Texture, 90cm, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 D83 - Porta pivotante estruturada fechamento em madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador metálico tipo alça padrão Demuner. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
@@ -11894,9 +11890,9 @@
       <c r="Z27" s="307" t="inlineStr">
         <is>
           <t>D13 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
-D14 - Fechamento cego em mdf cru com acabamento em folha madeira natural caravalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D14 - Fechamento cego em mdf cru com acabamento em folha madeira natural carvalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D15 - Armários em mdf cru com acabamento em folha madeira natural carvalho tonalizado. Puxadore integrado linha Sottile ref. ZEN - acabamento bronze 192mm. Consultar detalhamento.Amostra folha natural madeira com acabamenhto deverá ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
-D16 - Mesa em mdf cru com acabamento em folha madeira natural caravalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D16 - Mesa em mdf cru com acabamento em folha madeira natural carvalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D17 - Armários em ripas de madeira maciça tonalizada seguindo cor folha madeira - ripas de 20x20mm espaçadas 15mm. Portas de giro com puxador no trespasse. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
@@ -11931,7 +11927,7 @@
       <c r="S28" s="300" t="n"/>
       <c r="T28" s="307" t="n"/>
       <c r="U28" s="300" t="n"/>
-      <c r="V28" s="302" t="n"/>
+      <c r="V28" s="320" t="n"/>
       <c r="W28" s="300" t="n"/>
       <c r="X28" s="300" t="n"/>
       <c r="Y28" s="300" t="n"/>
@@ -11940,12 +11936,12 @@
     <row r="29" ht="224" customHeight="1">
       <c r="A29" s="298" t="inlineStr">
         <is>
-          <t>PISCINA DECOBERTA</t>
+          <t>PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="B29" s="320" t="inlineStr">
         <is>
-          <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm.  Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A
+          <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A
 P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
@@ -11956,7 +11952,7 @@
       <c r="G29" s="300" t="n"/>
       <c r="H29" s="320" t="inlineStr">
         <is>
-          <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614.. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+          <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="I29" s="307" t="n"/>
@@ -11984,14 +11980,14 @@
           <t>D79 - Chuveiro de piso para área externa em aço inox 316. cód.: DK5123B. Ref.: Doka</t>
         </is>
       </c>
-      <c r="V29" s="302" t="n"/>
+      <c r="V29" s="320" t="n"/>
       <c r="W29" s="307" t="n"/>
       <c r="X29" s="307" t="inlineStr">
         <is>
           <t>D77 - Porta pivotante para guarda corpo em vidro temperado laminado liso incolor com tubo para pivô em aço inox polido 1 1/4'' fixado no piso com barra lisa soltada com rosca na extremidade para fixação do vidro com botão de acabamento.</t>
         </is>
       </c>
-      <c r="Y29" s="302" t="n"/>
+      <c r="Y29" s="320" t="n"/>
       <c r="Z29" s="307" t="inlineStr">
         <is>
           <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
@@ -12006,7 +12002,7 @@
       </c>
       <c r="B30" s="320" t="inlineStr">
         <is>
-          <t>P26 - Piso em deck de madeira Cumaru com tecnica de carbonização Shugi Ban, reguas 20mmx100mmx2000m-acima. Ref.:Madeira Carbonizada.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+          <t>P26 - Piso em deck de madeira Cumaru com tecnica de carbonização Shugi Ban, reguas 20mmx100mmx2000m-acima. Ref.: Madeira Carbonizada. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="C30" s="300" t="n"/>
@@ -12028,10 +12024,10 @@
       <c r="S30" s="300" t="n"/>
       <c r="T30" s="300" t="n"/>
       <c r="U30" s="300" t="n"/>
-      <c r="V30" s="302" t="n"/>
+      <c r="V30" s="320" t="n"/>
       <c r="W30" s="307" t="n"/>
-      <c r="X30" s="302" t="n"/>
-      <c r="Y30" s="302" t="n"/>
+      <c r="X30" s="320" t="n"/>
+      <c r="Y30" s="320" t="n"/>
       <c r="Z30" s="307" t="n"/>
     </row>
     <row r="31" ht="60" customHeight="1">
@@ -12060,7 +12056,7 @@
       <c r="S31" s="300" t="n"/>
       <c r="T31" s="300" t="n"/>
       <c r="U31" s="300" t="n"/>
-      <c r="V31" s="302" t="n"/>
+      <c r="V31" s="320" t="n"/>
       <c r="W31" s="300" t="n"/>
       <c r="X31" s="300" t="n"/>
       <c r="Y31" s="300" t="n"/>
@@ -12074,7 +12070,7 @@
       </c>
       <c r="B32" s="307" t="inlineStr">
         <is>
-          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C32" s="300" t="n"/>
@@ -12094,7 +12090,7 @@
       </c>
       <c r="I32" s="307" t="inlineStr">
         <is>
-          <t>T4 - Forro em madeira pinho autoclavado tonalizado, espessura de 3cm, réguas de 10cm.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+          <t>T4 - Forro em madeira pinho autoclavado tonalizado, espessura de 3cm, réguas de 10cm. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
 T1 - Forro em gesso acartonado liso, com acabamento em tinta acrílica, cor branco neve, acabamento fosco, com junta dilatação metálica cor branca. Ref.: Suvinil</t>
         </is>
       </c>
@@ -12113,7 +12109,7 @@
       <c r="N32" s="300" t="n"/>
       <c r="O32" s="308" t="inlineStr">
         <is>
-          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.:  REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
+          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.: REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
         </is>
       </c>
       <c r="P32" s="300" t="n"/>
@@ -12133,13 +12129,13 @@
         </is>
       </c>
       <c r="W32" s="307" t="n"/>
-      <c r="X32" s="302" t="n"/>
-      <c r="Y32" s="302" t="n"/>
+      <c r="X32" s="320" t="n"/>
+      <c r="Y32" s="320" t="n"/>
       <c r="Z32" s="307" t="inlineStr">
         <is>
           <t>D47 - Marcenaria sob bancada em MDF Kashimir ref. Arauco - portas e frente gavetas em reguas de madeira maciça engenheirada reflorestada, tonalizada. Acabamento superfície escovada. Painel Bark. Ref.: Demuner. Puxador em cava na marcenaria. Apresentar amostra para aprovação GPA&amp;A Obs.: MDF possui certificação FSC. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
 D48 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
-D49 - Armários com interior em MDF madeirado e portas de giro ripadas -  ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria - prever fechamento face interna porta em vidro liso incolor 4mm. Prateleiras em MDF madeirado com iluminação em LED. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+D49 - Armários com interior em MDF madeirado e portas de giro ripadas - ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria - prever fechamento face interna porta em vidro liso incolor 4mm. Prateleiras em MDF madeirado com iluminação em LED. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D50 - Armário sob bancada com portas de giro ripadas para ventilação choppeira. Ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
@@ -12168,13 +12164,13 @@
       <c r="M33" s="308" t="n"/>
       <c r="N33" s="308" t="n"/>
       <c r="O33" s="307" t="n"/>
-      <c r="P33" s="302" t="n"/>
+      <c r="P33" s="320" t="n"/>
       <c r="Q33" s="300" t="n"/>
       <c r="R33" s="307" t="n"/>
       <c r="S33" s="307" t="n"/>
       <c r="T33" s="307" t="n"/>
       <c r="U33" s="300" t="n"/>
-      <c r="V33" s="302" t="n"/>
+      <c r="V33" s="320" t="n"/>
       <c r="W33" s="307" t="n"/>
       <c r="X33" s="307" t="n"/>
       <c r="Y33" s="307" t="n"/>
@@ -12188,7 +12184,7 @@
       </c>
       <c r="B34" s="307" t="inlineStr">
         <is>
-          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C34" s="300" t="n"/>
@@ -12212,7 +12208,7 @@
       <c r="M34" s="308" t="n"/>
       <c r="N34" s="308" t="n"/>
       <c r="O34" s="307" t="n"/>
-      <c r="P34" s="302" t="n"/>
+      <c r="P34" s="320" t="n"/>
       <c r="Q34" s="300" t="n"/>
       <c r="R34" s="307" t="n"/>
       <c r="S34" s="307" t="n"/>
@@ -12236,7 +12232,7 @@
       </c>
       <c r="B35" s="320" t="inlineStr">
         <is>
-          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C35" s="300" t="n"/>
@@ -12276,7 +12272,7 @@
       <c r="N35" s="308" t="n"/>
       <c r="O35" s="321" t="inlineStr">
         <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
 CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
@@ -12300,7 +12296,7 @@
       </c>
       <c r="U35" s="317" t="inlineStr">
         <is>
-          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
       <c r="V35" s="307" t="inlineStr">
@@ -12326,12 +12322,12 @@
     <row r="36" ht="224" customHeight="1">
       <c r="A36" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">VESTIÁRIO MASCULINO </t>
+          <t>VESTIÁRIO MASCULINO</t>
         </is>
       </c>
       <c r="B36" s="320" t="inlineStr">
         <is>
-          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado.  Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+          <t>P9 - Piso assentado em granito cinza Santa Rosa, acabamento serrado. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C36" s="300" t="n"/>
@@ -12371,7 +12367,7 @@
       <c r="N36" s="308" t="n"/>
       <c r="O36" s="321" t="inlineStr">
         <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
 CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
@@ -12395,7 +12391,7 @@
       </c>
       <c r="U36" s="317" t="inlineStr">
         <is>
-          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
       <c r="V36" s="307" t="inlineStr">
@@ -12442,7 +12438,7 @@
       <c r="H37" s="320" t="inlineStr">
         <is>
           <t>PA26 - Parede em alvenaria rebocada e regularizada revestida em espelho liso incolor 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
-PA27 - Parede em alvenaria rebocada e regularizada revestida em espelho liso fumê 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
+PA27 - Parede em alvenaria rebocada e regularizada revestida em espelho liso fumê 4mm colado sobre MDF cru 6mm aparafusado na alvenaria. Paginação e dimensões conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF deve possuir certificação FSC ou CERFLOR
 PA28 - Parede em alvenaria rebocada e regularizada revestida em painel de MDF Nero Rust. Paginação conforme detalhamento. Ref.: Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
 PA29 - Fechamento vertical estruturado com acabamento em painel de MDF Nero Rust. Paginação conforme detalhamento. Ref.: Berneck. Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
 PA30 - Pilar em concreto com acabamento em textura mineral Arch + Concrete ENG, Ref.: Novacolor. Fornecedor: Icolori (31)99952-2442. Amostra a ser aprovada pela GPA&amp;A</t>
@@ -12460,7 +12456,7 @@
       <c r="M37" s="308" t="n"/>
       <c r="N37" s="308" t="n"/>
       <c r="O37" s="307" t="n"/>
-      <c r="P37" s="302" t="n"/>
+      <c r="P37" s="320" t="n"/>
       <c r="Q37" s="300" t="n"/>
       <c r="R37" s="307" t="n"/>
       <c r="S37" s="307" t="n"/>
@@ -12481,7 +12477,7 @@
       <c r="Z37" s="308" t="inlineStr">
         <is>
           <t>D3 - Estante em MDF Nero Rust Ref.: Berneck, desenho conforme detalhamento, Amostra a ser aprovada pela GPA&amp;A. Obs.: MDF possui certificação FSC.
-D4 - Armário em marcenaria, estruturado, com espaço para central de sonorização e automação, quadro de distribuição embutido - verificar dimensões com projetos específico, desenho conforme detalhamento. Porta.  de giro com sistema fecho-toque, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
+D4 - Armário em marcenaria, estruturado, com espaço para central de sonorização e automação, quadro de distribuição embutido - verificar dimensões com projetos específico, desenho conforme detalhamento. Porta. de giro com sistema fecho-toque, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
 D5 - Painel estruturado com moldura, para encaixe de equipamento, desenho conforme detalhamento, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
 D6 - Anéis metálicos acabamento em micropintura perolizada, cor L098, Ref.: Sherwin Williams, fixados em pilar de concreto através de espassadores metálicos. Ver detalhamento. Apresentar protótipo e amostra pintura para aprovação GPA&amp;A.
 D7 - Mesa de apoio metálica em micropintura perolizada, cor L098, Ref.: Sherwin Williams, fixados em pilar de concreto através de estrutura auxiliar. Ver detalhamento. Apresentar protótipo e amostra pintura para aprovação GPA&amp;A.</t>
@@ -12491,7 +12487,7 @@
     <row r="38" ht="134" customHeight="1">
       <c r="A38" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIRCULAÇÃO JARDINS </t>
+          <t>CIRCULAÇÃO JARDINS</t>
         </is>
       </c>
       <c r="B38" s="307" t="inlineStr">
@@ -12512,13 +12508,13 @@
       <c r="M38" s="308" t="n"/>
       <c r="N38" s="308" t="n"/>
       <c r="O38" s="307" t="n"/>
-      <c r="P38" s="302" t="n"/>
+      <c r="P38" s="320" t="n"/>
       <c r="Q38" s="300" t="n"/>
       <c r="R38" s="307" t="n"/>
       <c r="S38" s="307" t="n"/>
       <c r="T38" s="307" t="n"/>
       <c r="U38" s="300" t="n"/>
-      <c r="V38" s="302" t="n"/>
+      <c r="V38" s="320" t="n"/>
       <c r="W38" s="307" t="n"/>
       <c r="X38" s="307" t="n"/>
       <c r="Y38" s="307" t="n"/>
@@ -12552,13 +12548,13 @@
       <c r="M39" s="308" t="n"/>
       <c r="N39" s="308" t="n"/>
       <c r="O39" s="307" t="n"/>
-      <c r="P39" s="302" t="n"/>
+      <c r="P39" s="320" t="n"/>
       <c r="Q39" s="300" t="n"/>
       <c r="R39" s="307" t="n"/>
       <c r="S39" s="307" t="n"/>
       <c r="T39" s="307" t="n"/>
       <c r="U39" s="300" t="n"/>
-      <c r="V39" s="302" t="n"/>
+      <c r="V39" s="320" t="n"/>
       <c r="W39" s="307" t="n"/>
       <c r="X39" s="307" t="n"/>
       <c r="Y39" s="307" t="n"/>
@@ -12567,12 +12563,12 @@
     <row r="40" ht="89" customHeight="1">
       <c r="A40" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPA </t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="B40" s="320" t="inlineStr">
         <is>
-          <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm.  Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A</t>
+          <t>P18 - Piso revestido em pastilhas de mármore branco selecionado, lote a ser aprovado, acabamento levigado, 3x3cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Amostra a ser aprovada pela GPA&amp;A</t>
         </is>
       </c>
       <c r="C40" s="300" t="n"/>
@@ -12592,13 +12588,13 @@
       <c r="M40" s="308" t="n"/>
       <c r="N40" s="308" t="n"/>
       <c r="O40" s="307" t="n"/>
-      <c r="P40" s="302" t="n"/>
+      <c r="P40" s="320" t="n"/>
       <c r="Q40" s="300" t="n"/>
       <c r="R40" s="307" t="n"/>
       <c r="S40" s="307" t="n"/>
       <c r="T40" s="307" t="n"/>
       <c r="U40" s="300" t="n"/>
-      <c r="V40" s="302" t="n"/>
+      <c r="V40" s="320" t="n"/>
       <c r="W40" s="307" t="n"/>
       <c r="X40" s="307" t="n"/>
       <c r="Y40" s="307" t="n"/>
@@ -12629,7 +12625,7 @@
         <is>
           <t>PA46 - Parede em alvenaria rebocada regularizada revestida em mármore branco selecionado, lote a ser aprovado. Espessura:2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
 PA48 - Parede rebocada e regularizada revestida em mármore branco selecionado, lote a ser aprovado, acabamento frisado com ranhuras de 4x4mm espassada a cada 12mm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
-PA49 - Pilar em concreto rebocados e regularizados revestidos em mosaico de pastilhas, módulos de 32x259cm com pastilhas de 20x20mm, NARCISO Shading BlendDesenho e paginação conforme detalhamento. Argamassa e rejunte recomendados: Filgel plus 1101 bianco alabastro. Ref.:Bisazza. Amostra a ser aprovada pela GPA&amp;A
+PA49 - Pilar em concreto rebocados e regularizados revestidos em mosaico de pastilhas, módulos de 32x259cm com pastilhas de 20x20mm, NARCISO Shading BlendDesenho e paginação conforme detalhamento. Argamassa e rejunte recomendados: Filgel plus 1101 bianco alabastro. Ref.: Bisazza. Amostra a ser aprovada pela GPA&amp;A
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
@@ -12645,7 +12641,7 @@
       <c r="M41" s="308" t="n"/>
       <c r="N41" s="308" t="n"/>
       <c r="O41" s="307" t="n"/>
-      <c r="P41" s="302" t="n"/>
+      <c r="P41" s="320" t="n"/>
       <c r="Q41" s="300" t="n"/>
       <c r="R41" s="307" t="inlineStr">
         <is>
@@ -12672,7 +12668,7 @@
       <c r="W41" s="307" t="n"/>
       <c r="X41" s="307" t="inlineStr">
         <is>
-          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y41" s="307" t="n"/>
@@ -12699,7 +12695,7 @@
     <row r="42" ht="89" customHeight="1">
       <c r="A42" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUNA VAPOR </t>
+          <t>SAUNA VAPOR</t>
         </is>
       </c>
       <c r="B42" s="320" t="inlineStr">
@@ -12728,7 +12724,7 @@
       <c r="M42" s="308" t="n"/>
       <c r="N42" s="308" t="n"/>
       <c r="O42" s="307" t="n"/>
-      <c r="P42" s="302" t="n"/>
+      <c r="P42" s="320" t="n"/>
       <c r="Q42" s="300" t="n"/>
       <c r="R42" s="307" t="inlineStr">
         <is>
@@ -12746,7 +12742,7 @@
           <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
-      <c r="V42" s="302" t="n"/>
+      <c r="V42" s="320" t="n"/>
       <c r="W42" s="307" t="n"/>
       <c r="X42" s="307" t="n"/>
       <c r="Y42" s="307" t="n"/>
@@ -12760,7 +12756,7 @@
       </c>
       <c r="B43" s="320" t="inlineStr">
         <is>
-          <t>P19 - Piso em contrapiso regularizado revestido com porcelanato padrão, coberto com piso tipo deck de madeira Cedro.Reguas 70mmx25mmx comprimento variável e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+          <t>P19 - Piso em contrapiso regularizado revestido com porcelanato padrão, coberto com piso tipo deck de madeira Cedro.Reguas 70mmx25mmx comprimento variável e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="C43" s="300" t="n"/>
@@ -12775,7 +12771,7 @@
       </c>
       <c r="I43" s="320" t="inlineStr">
         <is>
-          <t>T11 - Laje em concreto revestida em  conjunto com sarrafos de madeira 2,5x5cm a cada 35-40cm, lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+          <t>T11 - Laje em concreto revestida em conjunto com sarrafos de madeira 2,5x5cm a cada 35-40cm, lã de vidro 2,5cm de espessura e fechamento em réguas de madeira Cedro. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="J43" s="307" t="n"/>
@@ -12784,13 +12780,13 @@
       <c r="M43" s="308" t="n"/>
       <c r="N43" s="308" t="n"/>
       <c r="O43" s="307" t="n"/>
-      <c r="P43" s="302" t="n"/>
+      <c r="P43" s="320" t="n"/>
       <c r="Q43" s="300" t="n"/>
       <c r="R43" s="307" t="n"/>
       <c r="S43" s="307" t="n"/>
       <c r="T43" s="307" t="n"/>
       <c r="U43" s="300" t="n"/>
-      <c r="V43" s="302" t="n"/>
+      <c r="V43" s="320" t="n"/>
       <c r="W43" s="307" t="n"/>
       <c r="X43" s="307" t="n"/>
       <c r="Y43" s="307" t="n"/>
@@ -12816,13 +12812,13 @@
       <c r="M44" s="308" t="n"/>
       <c r="N44" s="308" t="n"/>
       <c r="O44" s="307" t="n"/>
-      <c r="P44" s="302" t="n"/>
+      <c r="P44" s="320" t="n"/>
       <c r="Q44" s="300" t="n"/>
       <c r="R44" s="307" t="n"/>
       <c r="S44" s="307" t="n"/>
       <c r="T44" s="307" t="n"/>
       <c r="U44" s="300" t="n"/>
-      <c r="V44" s="302" t="n"/>
+      <c r="V44" s="320" t="n"/>
       <c r="W44" s="307" t="n"/>
       <c r="X44" s="307" t="n"/>
       <c r="Y44" s="307" t="n"/>
@@ -12831,7 +12827,7 @@
     <row r="45" ht="344" customHeight="1">
       <c r="A45" s="298" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASSAGEM </t>
+          <t>MASSAGEM</t>
         </is>
       </c>
       <c r="B45" s="320" t="inlineStr">
@@ -12879,10 +12875,10 @@
       <c r="O45" s="320" t="inlineStr">
         <is>
           <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
-        </is>
-      </c>
-      <c r="P45" s="302" t="n"/>
+D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P45" s="320" t="n"/>
       <c r="Q45" s="300" t="n"/>
       <c r="R45" s="307" t="n"/>
       <c r="S45" s="307" t="n"/>
@@ -12896,7 +12892,7 @@
       <c r="W45" s="307" t="n"/>
       <c r="X45" s="320" t="inlineStr">
         <is>
-          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y45" s="307" t="n"/>
@@ -12953,10 +12949,10 @@
       <c r="O46" s="320" t="inlineStr">
         <is>
           <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
-        </is>
-      </c>
-      <c r="P46" s="302" t="n"/>
+D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+        </is>
+      </c>
+      <c r="P46" s="320" t="n"/>
       <c r="Q46" s="300" t="n"/>
       <c r="R46" s="307" t="n"/>
       <c r="S46" s="307" t="n"/>
@@ -12970,7 +12966,7 @@
       <c r="W46" s="307" t="n"/>
       <c r="X46" s="307" t="inlineStr">
         <is>
-          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y46" s="307" t="n"/>
@@ -13013,18 +13009,18 @@
       <c r="M47" s="308" t="n"/>
       <c r="N47" s="308" t="n"/>
       <c r="O47" s="307" t="n"/>
-      <c r="P47" s="302" t="n"/>
+      <c r="P47" s="320" t="n"/>
       <c r="Q47" s="300" t="n"/>
       <c r="R47" s="307" t="n"/>
       <c r="S47" s="307" t="n"/>
       <c r="T47" s="307" t="n"/>
       <c r="U47" s="300" t="n"/>
-      <c r="V47" s="302" t="n"/>
+      <c r="V47" s="320" t="n"/>
       <c r="W47" s="307" t="n"/>
       <c r="X47" s="307" t="inlineStr">
         <is>
-          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
-D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y47" s="307" t="n"/>
@@ -13068,7 +13064,7 @@
       </c>
       <c r="K48" s="308" t="inlineStr">
         <is>
-          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural carvalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L48" s="307" t="inlineStr">
@@ -13106,7 +13102,7 @@
       </c>
       <c r="U48" s="308" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
       <c r="V48" s="307" t="inlineStr">
@@ -13163,7 +13159,7 @@
       </c>
       <c r="K49" s="308" t="inlineStr">
         <is>
-          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural carvalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="L49" s="307" t="inlineStr">
@@ -13201,7 +13197,7 @@
       </c>
       <c r="U49" s="308" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
         </is>
       </c>
       <c r="V49" s="307" t="inlineStr">
@@ -13264,13 +13260,13 @@
           <t>D67 - Torneira de parede com arejador, para Jardim e Tanque, linha Izy, acabamento cromado. Cód. 1154.C37; Ref.: Deca.</t>
         </is>
       </c>
-      <c r="P50" s="302" t="n"/>
+      <c r="P50" s="320" t="n"/>
       <c r="Q50" s="300" t="n"/>
       <c r="R50" s="307" t="n"/>
       <c r="S50" s="307" t="n"/>
       <c r="T50" s="307" t="n"/>
       <c r="U50" s="300" t="n"/>
-      <c r="V50" s="302" t="n"/>
+      <c r="V50" s="320" t="n"/>
       <c r="W50" s="307" t="n"/>
       <c r="X50" s="307" t="n"/>
       <c r="Y50" s="307" t="n"/>
@@ -13296,13 +13292,13 @@
       <c r="M51" s="308" t="n"/>
       <c r="N51" s="308" t="n"/>
       <c r="O51" s="307" t="n"/>
-      <c r="P51" s="302" t="n"/>
+      <c r="P51" s="320" t="n"/>
       <c r="Q51" s="300" t="n"/>
       <c r="R51" s="307" t="n"/>
       <c r="S51" s="307" t="n"/>
       <c r="T51" s="307" t="n"/>
       <c r="U51" s="300" t="n"/>
-      <c r="V51" s="302" t="n"/>
+      <c r="V51" s="320" t="n"/>
       <c r="W51" s="307" t="n"/>
       <c r="X51" s="307" t="n"/>
       <c r="Y51" s="307" t="n"/>
@@ -13342,13 +13338,13 @@
       <c r="M52" s="308" t="n"/>
       <c r="N52" s="308" t="n"/>
       <c r="O52" s="307" t="n"/>
-      <c r="P52" s="302" t="n"/>
+      <c r="P52" s="320" t="n"/>
       <c r="Q52" s="300" t="n"/>
       <c r="R52" s="307" t="n"/>
       <c r="S52" s="307" t="n"/>
       <c r="T52" s="307" t="n"/>
       <c r="U52" s="300" t="n"/>
-      <c r="V52" s="302" t="n"/>
+      <c r="V52" s="320" t="n"/>
       <c r="W52" s="307" t="n"/>
       <c r="X52" s="307" t="n"/>
       <c r="Y52" s="307" t="n"/>
@@ -13378,7 +13374,7 @@
       <c r="G53" s="300" t="n"/>
       <c r="H53" s="320" t="inlineStr">
         <is>
-          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
+          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali off white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
 ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
@@ -13411,13 +13407,13 @@
           <t>27 - Torneira de parede com arejador, para jardim e tanque, cromado. Ref.: cód.:1154.C37; linha Izy; Deca</t>
         </is>
       </c>
-      <c r="P53" s="302" t="n"/>
+      <c r="P53" s="320" t="n"/>
       <c r="Q53" s="300" t="n"/>
       <c r="R53" s="307" t="n"/>
       <c r="S53" s="307" t="n"/>
       <c r="T53" s="307" t="n"/>
       <c r="U53" s="300" t="n"/>
-      <c r="V53" s="302" t="n"/>
+      <c r="V53" s="320" t="n"/>
       <c r="W53" s="307" t="n"/>
       <c r="X53" s="307" t="n"/>
       <c r="Y53" s="307" t="n"/>
@@ -13447,7 +13443,7 @@
       <c r="G54" s="300" t="n"/>
       <c r="H54" s="320" t="inlineStr">
         <is>
-          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
+          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali off white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
 ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
         </is>
@@ -13480,13 +13476,13 @@
           <t>27 - Torneira de parede com arejador, para jardim e tanque, cromado. Ref.: cód.:1154.C37; linha Izy; Deca</t>
         </is>
       </c>
-      <c r="P54" s="302" t="n"/>
+      <c r="P54" s="320" t="n"/>
       <c r="Q54" s="300" t="n"/>
       <c r="R54" s="307" t="n"/>
       <c r="S54" s="307" t="n"/>
       <c r="T54" s="307" t="n"/>
       <c r="U54" s="300" t="n"/>
-      <c r="V54" s="302" t="n"/>
+      <c r="V54" s="320" t="n"/>
       <c r="W54" s="307" t="n"/>
       <c r="X54" s="307" t="n"/>
       <c r="Y54" s="307" t="n"/>
@@ -13534,7 +13530,7 @@
       </c>
       <c r="K55" s="317" t="inlineStr">
         <is>
-          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural caravalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
+          <t>D38 - Armário em MDF cru e acabamento em folha madeira natural carvalho tonalizado, com portas em espelho liso incolor, polimento cristal 4mm colado sobre MDF cru 12mm com acabamento das bordas em cantoneiras em aço inox polido. Dimensões e desenho conforme detalhamento. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
@@ -13574,7 +13570,7 @@
       </c>
       <c r="U55" s="317" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol.  ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
 ► VER IMAGEM (clique)</t>
         </is>
       </c>
@@ -13586,8 +13582,8 @@
       <c r="W55" s="307" t="n"/>
       <c r="X55" s="307" t="inlineStr">
         <is>
-          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture,  com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
-D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura,  acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D39 - Porta estruturada em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.
+D43 - Painel e porta estruturados em alumínio com fechamento interno e externo em vidro, cor Prada, acabamento acidato. Dimensões conforme detalhamento. Ref.: Cinex. Puxador Round linha Texture, 90cm com fechadura, acabamento cromado acetinado. Ref.: La Fonte, Amostra a ser aprovada pela GPA&amp;A.</t>
         </is>
       </c>
       <c r="Y55" s="307" t="n"/>
@@ -13685,13 +13681,13 @@
       <c r="M56" s="308" t="n"/>
       <c r="N56" s="308" t="n"/>
       <c r="O56" s="320" t="n"/>
-      <c r="P56" s="302" t="n"/>
+      <c r="P56" s="320" t="n"/>
       <c r="Q56" s="300" t="n"/>
       <c r="R56" s="307" t="n"/>
       <c r="S56" s="307" t="n"/>
       <c r="T56" s="307" t="n"/>
       <c r="U56" s="300" t="n"/>
-      <c r="V56" s="302" t="n"/>
+      <c r="V56" s="320" t="n"/>
       <c r="W56" s="307" t="n"/>
       <c r="X56" s="307" t="n"/>
       <c r="Y56" s="307" t="n"/>
@@ -13737,13 +13733,13 @@
       <c r="M57" s="308" t="n"/>
       <c r="N57" s="308" t="n"/>
       <c r="O57" s="320" t="n"/>
-      <c r="P57" s="302" t="n"/>
+      <c r="P57" s="320" t="n"/>
       <c r="Q57" s="300" t="n"/>
       <c r="R57" s="307" t="n"/>
       <c r="S57" s="307" t="n"/>
       <c r="T57" s="307" t="n"/>
       <c r="U57" s="300" t="n"/>
-      <c r="V57" s="302" t="n"/>
+      <c r="V57" s="320" t="n"/>
       <c r="W57" s="307" t="n"/>
       <c r="X57" s="307" t="n"/>
       <c r="Y57" s="307" t="n"/>
@@ -13793,7 +13789,7 @@
       <c r="M58" s="308" t="n"/>
       <c r="N58" s="308" t="n"/>
       <c r="O58" s="320" t="n"/>
-      <c r="P58" s="302" t="n"/>
+      <c r="P58" s="320" t="n"/>
       <c r="Q58" s="300" t="n"/>
       <c r="R58" s="307" t="n"/>
       <c r="S58" s="307" t="n"/>
@@ -13818,7 +13814,7 @@
       <c r="B59" s="320" t="inlineStr">
         <is>
           <t>P28 - Piso assentado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
-P8 - Piso elevado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofulgante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+P8 - Piso elevado em granito cinza Santa Rosa, acabamento serrado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
         </is>
       </c>
       <c r="C59" s="300" t="n"/>
@@ -13834,7 +13830,7 @@
       <c r="M59" s="308" t="n"/>
       <c r="N59" s="308" t="n"/>
       <c r="O59" s="320" t="n"/>
-      <c r="P59" s="302" t="n"/>
+      <c r="P59" s="320" t="n"/>
       <c r="Q59" s="300" t="n"/>
       <c r="R59" s="307" t="n"/>
       <c r="S59" s="307" t="n"/>
@@ -13844,7 +13840,7 @@
         </is>
       </c>
       <c r="U59" s="300" t="n"/>
-      <c r="V59" s="302" t="n"/>
+      <c r="V59" s="320" t="n"/>
       <c r="W59" s="307" t="n"/>
       <c r="X59" s="307" t="n"/>
       <c r="Y59" s="307" t="n"/>
@@ -13878,13 +13874,13 @@
       <c r="M60" s="308" t="n"/>
       <c r="N60" s="308" t="n"/>
       <c r="O60" s="320" t="n"/>
-      <c r="P60" s="302" t="n"/>
+      <c r="P60" s="320" t="n"/>
       <c r="Q60" s="300" t="n"/>
       <c r="R60" s="307" t="n"/>
       <c r="S60" s="307" t="n"/>
       <c r="T60" s="307" t="n"/>
       <c r="U60" s="300" t="n"/>
-      <c r="V60" s="302" t="n"/>
+      <c r="V60" s="320" t="n"/>
       <c r="W60" s="307" t="n"/>
       <c r="X60" s="307" t="n"/>
       <c r="Y60" s="307" t="n"/>
@@ -13919,13 +13915,13 @@
       <c r="M61" s="308" t="n"/>
       <c r="N61" s="308" t="n"/>
       <c r="O61" s="320" t="n"/>
-      <c r="P61" s="302" t="n"/>
+      <c r="P61" s="320" t="n"/>
       <c r="Q61" s="300" t="n"/>
       <c r="R61" s="307" t="n"/>
       <c r="S61" s="307" t="n"/>
       <c r="T61" s="307" t="n"/>
       <c r="U61" s="300" t="n"/>
-      <c r="V61" s="302" t="n"/>
+      <c r="V61" s="320" t="n"/>
       <c r="W61" s="307" t="n"/>
       <c r="X61" s="307" t="n"/>
       <c r="Y61" s="307" t="n"/>
@@ -13961,13 +13957,13 @@
       <c r="M62" s="308" t="n"/>
       <c r="N62" s="308" t="n"/>
       <c r="O62" s="320" t="n"/>
-      <c r="P62" s="302" t="n"/>
+      <c r="P62" s="320" t="n"/>
       <c r="Q62" s="300" t="n"/>
       <c r="R62" s="307" t="n"/>
       <c r="S62" s="307" t="n"/>
       <c r="T62" s="307" t="n"/>
       <c r="U62" s="300" t="n"/>
-      <c r="V62" s="302" t="n"/>
+      <c r="V62" s="320" t="n"/>
       <c r="W62" s="307" t="n"/>
       <c r="X62" s="307" t="n"/>
       <c r="Y62" s="307" t="n"/>
@@ -13982,7 +13978,7 @@
       <c r="B63" s="320" t="inlineStr">
         <is>
           <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
-P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet.  ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
         </is>
       </c>
       <c r="C63" s="300" t="n"/>
@@ -14003,13 +13999,13 @@
       <c r="M63" s="308" t="n"/>
       <c r="N63" s="308" t="n"/>
       <c r="O63" s="320" t="n"/>
-      <c r="P63" s="302" t="n"/>
+      <c r="P63" s="320" t="n"/>
       <c r="Q63" s="300" t="n"/>
       <c r="R63" s="307" t="n"/>
       <c r="S63" s="307" t="n"/>
       <c r="T63" s="307" t="n"/>
       <c r="U63" s="300" t="n"/>
-      <c r="V63" s="302" t="n"/>
+      <c r="V63" s="320" t="n"/>
       <c r="W63" s="307" t="n"/>
       <c r="X63" s="307" t="n"/>
       <c r="Y63" s="307" t="n"/>
@@ -14047,13 +14043,13 @@
       <c r="M64" s="308" t="n"/>
       <c r="N64" s="308" t="n"/>
       <c r="O64" s="320" t="n"/>
-      <c r="P64" s="302" t="n"/>
+      <c r="P64" s="320" t="n"/>
       <c r="Q64" s="300" t="n"/>
       <c r="R64" s="307" t="n"/>
       <c r="S64" s="307" t="n"/>
       <c r="T64" s="307" t="n"/>
       <c r="U64" s="300" t="n"/>
-      <c r="V64" s="302" t="n"/>
+      <c r="V64" s="320" t="n"/>
       <c r="W64" s="307" t="n"/>
       <c r="X64" s="307" t="n"/>
       <c r="Y64" s="307" t="n"/>
@@ -14830,8 +14826,8 @@
       <c r="U13" s="300" t="n"/>
       <c r="V13" s="300" t="n"/>
       <c r="W13" s="300" t="n"/>
-      <c r="X13" s="302" t="n"/>
-      <c r="Y13" s="302" t="n"/>
+      <c r="X13" s="320" t="n"/>
+      <c r="Y13" s="320" t="n"/>
       <c r="Z13" s="300" t="inlineStr">
         <is>
           <t>Varanda: mureta h=90cm. (DET PR001)</t>
@@ -14911,12 +14907,12 @@
           <t>Maçaneta Pado Sara, cromo acetinado, interna. (DET PR004)</t>
         </is>
       </c>
-      <c r="X14" s="302" t="inlineStr">
+      <c r="X14" s="320" t="inlineStr">
         <is>
           <t>Porta piso-forro, cor branca, alizar 10cm. (DET PR004)</t>
         </is>
       </c>
-      <c r="Y14" s="302" t="n"/>
+      <c r="Y14" s="320" t="n"/>
       <c r="Z14" s="300" t="n"/>
     </row>
     <row r="15" ht="104" customHeight="1">
@@ -15014,12 +15010,12 @@
           <t>Maçaneta Sara cromo acetinado. Ref.: Pado. (PR408)</t>
         </is>
       </c>
-      <c r="X15" s="302" t="inlineStr">
+      <c r="X15" s="320" t="inlineStr">
         <is>
           <t>38 - Porta em marcenaria piso-forro, cor branca, alizar 10cm. (PR408)</t>
         </is>
       </c>
-      <c r="Y15" s="302" t="n"/>
+      <c r="Y15" s="320" t="n"/>
       <c r="Z15" s="300" t="n"/>
     </row>
     <row r="16" ht="74" customHeight="1">
@@ -15094,8 +15090,8 @@
       <c r="U16" s="300" t="n"/>
       <c r="V16" s="300" t="n"/>
       <c r="W16" s="300" t="n"/>
-      <c r="X16" s="302" t="n"/>
-      <c r="Y16" s="302" t="n"/>
+      <c r="X16" s="320" t="n"/>
+      <c r="Y16" s="320" t="n"/>
       <c r="Z16" s="300" t="n"/>
     </row>
     <row r="17" ht="89" customHeight="1">
@@ -15143,8 +15139,8 @@
       <c r="U17" s="300" t="n"/>
       <c r="V17" s="300" t="n"/>
       <c r="W17" s="300" t="n"/>
-      <c r="X17" s="302" t="n"/>
-      <c r="Y17" s="302" t="n"/>
+      <c r="X17" s="320" t="n"/>
+      <c r="Y17" s="320" t="n"/>
       <c r="Z17" s="300" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -15195,8 +15191,8 @@
       <c r="U18" s="300" t="n"/>
       <c r="V18" s="300" t="n"/>
       <c r="W18" s="300" t="n"/>
-      <c r="X18" s="302" t="n"/>
-      <c r="Y18" s="302" t="n"/>
+      <c r="X18" s="320" t="n"/>
+      <c r="Y18" s="320" t="n"/>
       <c r="Z18" s="300" t="n"/>
     </row>
     <row r="19" ht="74" customHeight="1">
@@ -15256,12 +15252,12 @@
       <c r="U19" s="300" t="n"/>
       <c r="V19" s="300" t="n"/>
       <c r="W19" s="300" t="n"/>
-      <c r="X19" s="302" t="inlineStr">
+      <c r="X19" s="320" t="inlineStr">
         <is>
           <t>Porta em marcenaria. (PR406/407)</t>
         </is>
       </c>
-      <c r="Y19" s="302" t="n"/>
+      <c r="Y19" s="320" t="n"/>
       <c r="Z19" s="300" t="n"/>
     </row>
     <row r="20" ht="74" customHeight="1">
@@ -15336,13 +15332,13 @@
           <t>Maçaneta Pado Sara, cromo acetinado, interna. Porta de segurança: fechadura digital FDE-600W. (DET PR005/PR006)</t>
         </is>
       </c>
-      <c r="X20" s="302" t="inlineStr">
+      <c r="X20" s="320" t="inlineStr">
         <is>
           <t>Porta piso-forro, cor branca, alizar 10cm
 Porta piso-forro especial de segurança, cor branca, alizar 10cm. (DET PR006)</t>
         </is>
       </c>
-      <c r="Y20" s="302" t="n"/>
+      <c r="Y20" s="320" t="n"/>
       <c r="Z20" s="300" t="n"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -15417,8 +15413,8 @@
       <c r="U21" s="300" t="n"/>
       <c r="V21" s="300" t="n"/>
       <c r="W21" s="300" t="n"/>
-      <c r="X21" s="302" t="n"/>
-      <c r="Y21" s="302" t="n"/>
+      <c r="X21" s="320" t="n"/>
+      <c r="Y21" s="320" t="n"/>
       <c r="Z21" s="300" t="n"/>
     </row>
     <row r="22" ht="60" customHeight="1">
@@ -15465,8 +15461,8 @@
       <c r="U22" s="300" t="n"/>
       <c r="V22" s="300" t="n"/>
       <c r="W22" s="300" t="n"/>
-      <c r="X22" s="302" t="n"/>
-      <c r="Y22" s="302" t="n"/>
+      <c r="X22" s="320" t="n"/>
+      <c r="Y22" s="320" t="n"/>
       <c r="Z22" s="300" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -15501,8 +15497,8 @@
       <c r="U23" s="300" t="n"/>
       <c r="V23" s="300" t="n"/>
       <c r="W23" s="300" t="n"/>
-      <c r="X23" s="302" t="n"/>
-      <c r="Y23" s="302" t="n"/>
+      <c r="X23" s="320" t="n"/>
+      <c r="Y23" s="320" t="n"/>
       <c r="Z23" s="300" t="n"/>
     </row>
     <row r="24" ht="60" customHeight="1">
@@ -15546,8 +15542,8 @@
       <c r="U24" s="300" t="n"/>
       <c r="V24" s="300" t="n"/>
       <c r="W24" s="300" t="n"/>
-      <c r="X24" s="302" t="n"/>
-      <c r="Y24" s="302" t="n"/>
+      <c r="X24" s="320" t="n"/>
+      <c r="Y24" s="320" t="n"/>
       <c r="Z24" s="300" t="n"/>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -15591,8 +15587,8 @@
       <c r="U25" s="300" t="n"/>
       <c r="V25" s="300" t="n"/>
       <c r="W25" s="300" t="n"/>
-      <c r="X25" s="302" t="n"/>
-      <c r="Y25" s="302" t="n"/>
+      <c r="X25" s="320" t="n"/>
+      <c r="Y25" s="320" t="n"/>
       <c r="Z25" s="300" t="n"/>
     </row>
     <row r="26" ht="89" customHeight="1">
@@ -15639,12 +15635,12 @@
       <c r="U26" s="300" t="n"/>
       <c r="V26" s="300" t="n"/>
       <c r="W26" s="300" t="n"/>
-      <c r="X26" s="302" t="inlineStr">
+      <c r="X26" s="320" t="inlineStr">
         <is>
           <t>PCF1, PCF2, PE-A, P13, P23, PA05, PCF3, P15A, P15C (vão 90x240cm); material não especificado nas pranchas de circulação. (PR721-728)</t>
         </is>
       </c>
-      <c r="Y26" s="302" t="n"/>
+      <c r="Y26" s="320" t="n"/>
       <c r="Z26" s="300" t="inlineStr">
         <is>
           <t>Sirene de alarme e botoeira; hidrante nos halls conforme projeto PCI. (PR722-728)</t>
@@ -15653,14 +15649,14 @@
     </row>
     <row r="27">
       <c r="A27" s="45" t="n"/>
-      <c r="B27" s="31" t="n"/>
+      <c r="B27" s="245" t="n"/>
       <c r="C27" s="32" t="n"/>
       <c r="D27" s="32" t="n"/>
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n"/>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="33" t="n"/>
+      <c r="H27" s="246" t="n"/>
+      <c r="I27" s="246" t="n"/>
       <c r="J27" s="32" t="n"/>
       <c r="K27" s="32" t="n"/>
       <c r="L27" s="32" t="n"/>
@@ -15675,20 +15671,20 @@
       <c r="U27" s="32" t="n"/>
       <c r="V27" s="32" t="n"/>
       <c r="W27" s="32" t="n"/>
-      <c r="X27" s="31" t="n"/>
-      <c r="Y27" s="31" t="n"/>
+      <c r="X27" s="245" t="n"/>
+      <c r="Y27" s="245" t="n"/>
       <c r="Z27" s="32" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="45" t="n"/>
-      <c r="B28" s="31" t="n"/>
+      <c r="B28" s="245" t="n"/>
       <c r="C28" s="32" t="n"/>
       <c r="D28" s="32" t="n"/>
       <c r="E28" s="32" t="n"/>
       <c r="F28" s="32" t="n"/>
       <c r="G28" s="32" t="n"/>
-      <c r="H28" s="33" t="n"/>
-      <c r="I28" s="33" t="n"/>
+      <c r="H28" s="246" t="n"/>
+      <c r="I28" s="246" t="n"/>
       <c r="J28" s="32" t="n"/>
       <c r="K28" s="32" t="n"/>
       <c r="L28" s="32" t="n"/>
@@ -15703,20 +15699,20 @@
       <c r="U28" s="32" t="n"/>
       <c r="V28" s="32" t="n"/>
       <c r="W28" s="32" t="n"/>
-      <c r="X28" s="31" t="n"/>
-      <c r="Y28" s="31" t="n"/>
+      <c r="X28" s="245" t="n"/>
+      <c r="Y28" s="245" t="n"/>
       <c r="Z28" s="32" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="45" t="n"/>
-      <c r="B29" s="31" t="n"/>
+      <c r="B29" s="245" t="n"/>
       <c r="C29" s="32" t="n"/>
       <c r="D29" s="32" t="n"/>
       <c r="E29" s="32" t="n"/>
       <c r="F29" s="32" t="n"/>
       <c r="G29" s="32" t="n"/>
-      <c r="H29" s="33" t="n"/>
-      <c r="I29" s="33" t="n"/>
+      <c r="H29" s="246" t="n"/>
+      <c r="I29" s="246" t="n"/>
       <c r="J29" s="32" t="n"/>
       <c r="K29" s="32" t="n"/>
       <c r="L29" s="32" t="n"/>
@@ -15731,20 +15727,20 @@
       <c r="U29" s="32" t="n"/>
       <c r="V29" s="32" t="n"/>
       <c r="W29" s="32" t="n"/>
-      <c r="X29" s="31" t="n"/>
-      <c r="Y29" s="31" t="n"/>
+      <c r="X29" s="245" t="n"/>
+      <c r="Y29" s="245" t="n"/>
       <c r="Z29" s="32" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="45" t="n"/>
-      <c r="B30" s="31" t="n"/>
+      <c r="B30" s="245" t="n"/>
       <c r="C30" s="32" t="n"/>
       <c r="D30" s="32" t="n"/>
       <c r="E30" s="32" t="n"/>
       <c r="F30" s="32" t="n"/>
       <c r="G30" s="32" t="n"/>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="33" t="n"/>
+      <c r="H30" s="246" t="n"/>
+      <c r="I30" s="246" t="n"/>
       <c r="J30" s="32" t="n"/>
       <c r="K30" s="32" t="n"/>
       <c r="L30" s="32" t="n"/>
@@ -15759,20 +15755,20 @@
       <c r="U30" s="32" t="n"/>
       <c r="V30" s="32" t="n"/>
       <c r="W30" s="32" t="n"/>
-      <c r="X30" s="31" t="n"/>
-      <c r="Y30" s="31" t="n"/>
+      <c r="X30" s="245" t="n"/>
+      <c r="Y30" s="245" t="n"/>
       <c r="Z30" s="32" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="45" t="n"/>
-      <c r="B31" s="31" t="n"/>
+      <c r="B31" s="245" t="n"/>
       <c r="C31" s="32" t="n"/>
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="32" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="33" t="n"/>
+      <c r="H31" s="246" t="n"/>
+      <c r="I31" s="246" t="n"/>
       <c r="J31" s="32" t="n"/>
       <c r="K31" s="32" t="n"/>
       <c r="L31" s="32" t="n"/>
@@ -15787,8 +15783,8 @@
       <c r="U31" s="32" t="n"/>
       <c r="V31" s="32" t="n"/>
       <c r="W31" s="32" t="n"/>
-      <c r="X31" s="31" t="n"/>
-      <c r="Y31" s="31" t="n"/>
+      <c r="X31" s="245" t="n"/>
+      <c r="Y31" s="245" t="n"/>
       <c r="Z31" s="32" t="n"/>
     </row>
     <row r="32"/>
@@ -16074,7 +16070,7 @@
       </c>
       <c r="H8" s="331" t="inlineStr"/>
     </row>
-    <row r="9" ht="87" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="331" t="n">
         <v>5</v>
       </c>
@@ -16105,7 +16101,7 @@
       </c>
       <c r="G9" s="334" t="inlineStr">
         <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
 CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
@@ -16148,7 +16144,7 @@
       </c>
       <c r="H10" s="331" t="inlineStr"/>
     </row>
-    <row r="11" ht="87" customHeight="1">
+    <row r="11" ht="72" customHeight="1">
       <c r="A11" s="331" t="n">
         <v>7</v>
       </c>
@@ -16179,7 +16175,7 @@
       </c>
       <c r="G11" s="334" t="inlineStr">
         <is>
-          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca  ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+          <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
 CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
         </is>
       </c>
@@ -16277,7 +16273,7 @@
     <row r="2">
       <c r="A2" s="264" t="inlineStr">
         <is>
-          <t>Fonte: Tabela de acabamentos Ed. Cidade Jardim v00 (19/06/2026). Emissão 30/09/2026, REV. R00.</t>
+          <t>Fontes: Tabela de acabamentos Ed. Cidade Jardim v00 (19/06/2026); detalhamento de interiores R04 (23/04/2026); plantas de arquitetura CDJ-ARQ-EX PR003–PR013; apartamento tipo: tabela JARDIM-ACABAMENTOS R01 e detalhamento. Emissão 30/09/2026, REV. R00.</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16653,7 @@
       </c>
       <c r="D19" s="268" t="inlineStr">
         <is>
-          <t>Referência grafada "Khali pff white". Considerado Khali off white AC (Eliane).</t>
+          <t>Referência grafada "Khali off white". Considerado Khali off white AC (Eliane).</t>
         </is>
       </c>
       <c r="E19" s="268" t="inlineStr">
@@ -16732,12 +16728,12 @@
       </c>
       <c r="D22" s="268" t="inlineStr">
         <is>
-          <t>A tabela v00 só traz o 3º pavimento - Pilotis. Abas mantidas sem preenchimento.</t>
+          <t>A tabela v00 só traz o 3º pavimento - Pilotis. As abas foram preenchidas pelo detalhamento R04 e pelas plantas de arquitetura (ver itens 5 e 7).</t>
         </is>
       </c>
       <c r="E22" s="268" t="inlineStr">
         <is>
-          <t>Tabela v00</t>
+          <t>Tabela v00 → R04 e arquitetura</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16742,7 @@
     <row r="25">
       <c r="A25" s="265" t="inlineStr">
         <is>
-          <t>2. AMBIENTES DO MODELO (PILOTIS) SEM INFORMAÇÃO NA TABELA</t>
+          <t>2. AMBIENTES DO MODELO (PILOTIS) SEM INFORMAÇÃO NA TABELA V00 — SITUAÇÃO ATUAL</t>
         </is>
       </c>
     </row>
@@ -16761,9 +16757,13 @@
           <t>AMBIENTE NO MODELO</t>
         </is>
       </c>
-      <c r="C26" s="266" t="inlineStr"/>
-      <c r="D26" s="266" t="inlineStr"/>
-      <c r="E26" s="266" t="inlineStr"/>
+      <c r="C26" s="266" t="n"/>
+      <c r="D26" s="266" t="inlineStr">
+        <is>
+          <t>SITUAÇÃO</t>
+        </is>
+      </c>
+      <c r="E26" s="266" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="267" t="n">
@@ -16774,13 +16774,13 @@
           <t>TERRAÇO SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="C27" s="268" t="inlineStr"/>
+      <c r="C27" s="268" t="n"/>
       <c r="D27" s="268" t="inlineStr">
         <is>
           <t>Tabela v00 e detalhamento R04 sem especificação de acabamento (a lista R04 só traz códigos sem descrição para "Varanda, terraço, piscina e prainha, braseiro"). A planta de arquitetura PR011 indica piso ○08 (ARQ-P08, lançado na grade) e guarda-corpos GC06/GC07 h=130cm. Sem indicação de rodapé, parede ou teto.</t>
         </is>
       </c>
-      <c r="E27" s="268" t="inlineStr"/>
+      <c r="E27" s="268" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="267" t="n">
@@ -16791,9 +16791,13 @@
           <t>CIRCULAÇÃO SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="C28" s="268" t="inlineStr"/>
-      <c r="D28" s="268" t="inlineStr"/>
-      <c r="E28" s="268" t="inlineStr"/>
+      <c r="C28" s="268" t="n"/>
+      <c r="D28" s="268" t="inlineStr">
+        <is>
+          <t>Sem especificação em nenhuma fonte recebida (tabela v00, detalhamento R04 e plantas de arquitetura sem etiqueta). Definir.</t>
+        </is>
+      </c>
+      <c r="E28" s="268" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="267" t="n">
@@ -16804,9 +16808,13 @@
           <t>APOIO COZINHA</t>
         </is>
       </c>
-      <c r="C29" s="268" t="inlineStr"/>
-      <c r="D29" s="268" t="inlineStr"/>
-      <c r="E29" s="268" t="inlineStr"/>
+      <c r="C29" s="268" t="n"/>
+      <c r="D29" s="268" t="inlineStr">
+        <is>
+          <t>Sem especificação em nenhuma fonte recebida (tabela v00, detalhamento R04 e plantas de arquitetura sem etiqueta). Definir.</t>
+        </is>
+      </c>
+      <c r="E29" s="268" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="267" t="n">
@@ -16817,9 +16825,13 @@
           <t>CIRCULAÇÃO/ANTECÂMARA ELEVADOR SERVIÇO</t>
         </is>
       </c>
-      <c r="C30" s="268" t="inlineStr"/>
-      <c r="D30" s="268" t="inlineStr"/>
-      <c r="E30" s="268" t="inlineStr"/>
+      <c r="C30" s="268" t="n"/>
+      <c r="D30" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E30" s="268" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="267" t="n">
@@ -16830,9 +16842,13 @@
           <t>CIRCULAÇÃO LAVABOS</t>
         </is>
       </c>
-      <c r="C31" s="268" t="inlineStr"/>
-      <c r="D31" s="268" t="inlineStr"/>
-      <c r="E31" s="268" t="inlineStr"/>
+      <c r="C31" s="268" t="n"/>
+      <c r="D31" s="268" t="inlineStr">
+        <is>
+          <t>Sem especificação em nenhuma fonte recebida (tabela v00, detalhamento R04 e plantas de arquitetura sem etiqueta). Definir.</t>
+        </is>
+      </c>
+      <c r="E31" s="268" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="267" t="n">
@@ -16843,9 +16859,13 @@
           <t>VARANDA</t>
         </is>
       </c>
-      <c r="C32" s="268" t="inlineStr"/>
-      <c r="D32" s="268" t="inlineStr"/>
-      <c r="E32" s="268" t="inlineStr"/>
+      <c r="C32" s="268" t="n"/>
+      <c r="D32" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E32" s="268" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="267" t="n">
@@ -16856,9 +16876,13 @@
           <t>PLAYGROUND</t>
         </is>
       </c>
-      <c r="C33" s="268" t="inlineStr"/>
-      <c r="D33" s="268" t="inlineStr"/>
-      <c r="E33" s="268" t="inlineStr"/>
+      <c r="C33" s="268" t="n"/>
+      <c r="D33" s="268" t="inlineStr">
+        <is>
+          <t>Sem especificação em nenhuma fonte recebida (tabela v00, detalhamento R04 e plantas de arquitetura sem etiqueta). Definir.</t>
+        </is>
+      </c>
+      <c r="E33" s="268" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="267" t="n">
@@ -16869,9 +16893,13 @@
           <t>BAR PISCINA</t>
         </is>
       </c>
-      <c r="C34" s="268" t="inlineStr"/>
-      <c r="D34" s="268" t="inlineStr"/>
-      <c r="E34" s="268" t="inlineStr"/>
+      <c r="C34" s="268" t="n"/>
+      <c r="D34" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E34" s="268" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="267" t="n">
@@ -16882,9 +16910,13 @@
           <t>CIRCULAÇÃO PLAYGROUND</t>
         </is>
       </c>
-      <c r="C35" s="268" t="inlineStr"/>
-      <c r="D35" s="268" t="inlineStr"/>
-      <c r="E35" s="268" t="inlineStr"/>
+      <c r="C35" s="268" t="n"/>
+      <c r="D35" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E35" s="268" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="267" t="n">
@@ -16895,9 +16927,13 @@
           <t>CIRCULAÇÃO VESTIÁRIOS</t>
         </is>
       </c>
-      <c r="C36" s="268" t="inlineStr"/>
-      <c r="D36" s="268" t="inlineStr"/>
-      <c r="E36" s="268" t="inlineStr"/>
+      <c r="C36" s="268" t="n"/>
+      <c r="D36" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E36" s="268" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="267" t="n">
@@ -16908,9 +16944,13 @@
           <t>CIRCULAÇÃO JARDINS</t>
         </is>
       </c>
-      <c r="C37" s="268" t="inlineStr"/>
-      <c r="D37" s="268" t="inlineStr"/>
-      <c r="E37" s="268" t="inlineStr"/>
+      <c r="C37" s="268" t="n"/>
+      <c r="D37" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E37" s="268" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="267" t="n">
@@ -16921,9 +16961,13 @@
           <t>CIRCULAÇÃO MASSAGEM/BELEZA</t>
         </is>
       </c>
-      <c r="C38" s="268" t="inlineStr"/>
-      <c r="D38" s="268" t="inlineStr"/>
-      <c r="E38" s="268" t="inlineStr"/>
+      <c r="C38" s="268" t="n"/>
+      <c r="D38" s="268" t="inlineStr">
+        <is>
+          <t>Sem especificação em nenhuma fonte recebida (tabela v00, detalhamento R04 e plantas de arquitetura sem etiqueta). Definir.</t>
+        </is>
+      </c>
+      <c r="E38" s="268" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="267" t="n">
@@ -16934,9 +16978,13 @@
           <t>HALL VESTIÁRIOS</t>
         </is>
       </c>
-      <c r="C39" s="268" t="inlineStr"/>
-      <c r="D39" s="268" t="inlineStr"/>
-      <c r="E39" s="268" t="inlineStr"/>
+      <c r="C39" s="268" t="n"/>
+      <c r="D39" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E39" s="268" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="267" t="n">
@@ -16947,9 +16995,13 @@
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="C40" s="268" t="inlineStr"/>
-      <c r="D40" s="268" t="inlineStr"/>
-      <c r="E40" s="268" t="inlineStr"/>
+      <c r="C40" s="268" t="n"/>
+      <c r="D40" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E40" s="268" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="267" t="n">
@@ -16960,9 +17012,13 @@
           <t>VEST. P.C.D</t>
         </is>
       </c>
-      <c r="C41" s="268" t="inlineStr"/>
-      <c r="D41" s="268" t="inlineStr"/>
-      <c r="E41" s="268" t="inlineStr"/>
+      <c r="C41" s="268" t="n"/>
+      <c r="D41" s="268" t="inlineStr">
+        <is>
+          <t>Preenchido pelo detalhamento R04 e/ou pelas plantas de arquitetura.</t>
+        </is>
+      </c>
+      <c r="E41" s="268" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="267" t="n">
@@ -16973,9 +17029,13 @@
           <t>LOUNGE QUADRAS</t>
         </is>
       </c>
-      <c r="C42" s="268" t="inlineStr"/>
-      <c r="D42" s="268" t="inlineStr"/>
-      <c r="E42" s="268" t="inlineStr"/>
+      <c r="C42" s="268" t="n"/>
+      <c r="D42" s="268" t="inlineStr">
+        <is>
+          <t>Sem especificação em nenhuma fonte recebida (tabela v00, detalhamento R04 e plantas de arquitetura sem etiqueta). Definir.</t>
+        </is>
+      </c>
+      <c r="E42" s="268" t="n"/>
     </row>
     <row r="43"/>
     <row r="44"/>
@@ -17002,8 +17062,8 @@
           <t>LINHA(S) NA GRADE</t>
         </is>
       </c>
-      <c r="D46" s="266" t="inlineStr"/>
-      <c r="E46" s="266" t="inlineStr"/>
+      <c r="D46" s="266" t="n"/>
+      <c r="E46" s="266" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="267" t="n">
@@ -17019,8 +17079,8 @@
           <t>LOBBY PILOTIS</t>
         </is>
       </c>
-      <c r="D47" s="268" t="inlineStr"/>
-      <c r="E47" s="268" t="inlineStr"/>
+      <c r="D47" s="268" t="n"/>
+      <c r="E47" s="268" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="267" t="n">
@@ -17036,8 +17096,8 @@
           <t>SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="D48" s="268" t="inlineStr"/>
-      <c r="E48" s="268" t="inlineStr"/>
+      <c r="D48" s="268" t="n"/>
+      <c r="E48" s="268" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="267" t="n">
@@ -17053,8 +17113,8 @@
           <t>I.S FEMININO, I.S MASCULINO</t>
         </is>
       </c>
-      <c r="D49" s="268" t="inlineStr"/>
-      <c r="E49" s="268" t="inlineStr"/>
+      <c r="D49" s="268" t="n"/>
+      <c r="E49" s="268" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="267" t="n">
@@ -17070,8 +17130,8 @@
           <t>COZINHA SALÃO DE FESTAS</t>
         </is>
       </c>
-      <c r="D50" s="268" t="inlineStr"/>
-      <c r="E50" s="268" t="inlineStr"/>
+      <c r="D50" s="268" t="n"/>
+      <c r="E50" s="268" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="267" t="n">
@@ -17087,8 +17147,8 @@
           <t>DML</t>
         </is>
       </c>
-      <c r="D51" s="268" t="inlineStr"/>
-      <c r="E51" s="268" t="inlineStr"/>
+      <c r="D51" s="268" t="n"/>
+      <c r="E51" s="268" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="267" t="n">
@@ -17104,8 +17164,8 @@
           <t>I.S P.C.D, I.S</t>
         </is>
       </c>
-      <c r="D52" s="268" t="inlineStr"/>
-      <c r="E52" s="268" t="inlineStr"/>
+      <c r="D52" s="268" t="n"/>
+      <c r="E52" s="268" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="267" t="n">
@@ -17121,8 +17181,8 @@
           <t>ESPAÇO KIDS</t>
         </is>
       </c>
-      <c r="D53" s="268" t="inlineStr"/>
-      <c r="E53" s="268" t="inlineStr"/>
+      <c r="D53" s="268" t="n"/>
+      <c r="E53" s="268" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="267" t="n">
@@ -17138,8 +17198,8 @@
           <t>ESPAÇO GOURMET</t>
         </is>
       </c>
-      <c r="D54" s="268" t="inlineStr"/>
-      <c r="E54" s="268" t="inlineStr"/>
+      <c r="D54" s="268" t="n"/>
+      <c r="E54" s="268" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="267" t="n">
@@ -17152,11 +17212,11 @@
       </c>
       <c r="C55" s="268" t="inlineStr">
         <is>
-          <t>PISCINA DECOBERTA</t>
-        </is>
-      </c>
-      <c r="D55" s="268" t="inlineStr"/>
-      <c r="E55" s="268" t="inlineStr"/>
+          <t>PISCINA DESCOBERTA</t>
+        </is>
+      </c>
+      <c r="D55" s="268" t="n"/>
+      <c r="E55" s="268" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="267" t="n">
@@ -17172,8 +17232,8 @@
           <t>DECK</t>
         </is>
       </c>
-      <c r="D56" s="268" t="inlineStr"/>
-      <c r="E56" s="268" t="inlineStr"/>
+      <c r="D56" s="268" t="n"/>
+      <c r="E56" s="268" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="267" t="n">
@@ -17189,8 +17249,8 @@
           <t>VESTIÁRIO FEMININO, VESTIÁRIO MASCULINO</t>
         </is>
       </c>
-      <c r="D57" s="268" t="inlineStr"/>
-      <c r="E57" s="268" t="inlineStr"/>
+      <c r="D57" s="268" t="n"/>
+      <c r="E57" s="268" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="267" t="n">
@@ -17206,8 +17266,8 @@
           <t>ACADEMIA</t>
         </is>
       </c>
-      <c r="D58" s="268" t="inlineStr"/>
-      <c r="E58" s="268" t="inlineStr"/>
+      <c r="D58" s="268" t="n"/>
+      <c r="E58" s="268" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="267" t="n">
@@ -17223,8 +17283,8 @@
           <t>PISCINA RAIA, SPA</t>
         </is>
       </c>
-      <c r="D59" s="268" t="inlineStr"/>
-      <c r="E59" s="268" t="inlineStr"/>
+      <c r="D59" s="268" t="n"/>
+      <c r="E59" s="268" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="267" t="n">
@@ -17240,8 +17300,8 @@
           <t>ESPAÇO TERMAS</t>
         </is>
       </c>
-      <c r="D60" s="268" t="inlineStr"/>
-      <c r="E60" s="268" t="inlineStr"/>
+      <c r="D60" s="268" t="n"/>
+      <c r="E60" s="268" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="267" t="n">
@@ -17257,8 +17317,8 @@
           <t>SAUNA VAPOR</t>
         </is>
       </c>
-      <c r="D61" s="268" t="inlineStr"/>
-      <c r="E61" s="268" t="inlineStr"/>
+      <c r="D61" s="268" t="n"/>
+      <c r="E61" s="268" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="267" t="n">
@@ -17274,8 +17334,8 @@
           <t>SAUNA SECA</t>
         </is>
       </c>
-      <c r="D62" s="268" t="inlineStr"/>
-      <c r="E62" s="268" t="inlineStr"/>
+      <c r="D62" s="268" t="n"/>
+      <c r="E62" s="268" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="267" t="n">
@@ -17291,8 +17351,8 @@
           <t>MASSAGEM</t>
         </is>
       </c>
-      <c r="D63" s="268" t="inlineStr"/>
-      <c r="E63" s="268" t="inlineStr"/>
+      <c r="D63" s="268" t="n"/>
+      <c r="E63" s="268" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="267" t="n">
@@ -17308,8 +17368,8 @@
           <t>BELEZA</t>
         </is>
       </c>
-      <c r="D64" s="268" t="inlineStr"/>
-      <c r="E64" s="268" t="inlineStr"/>
+      <c r="D64" s="268" t="n"/>
+      <c r="E64" s="268" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="267" t="n">
@@ -17325,8 +17385,8 @@
           <t>QUADRA TÊNIS</t>
         </is>
       </c>
-      <c r="D65" s="268" t="inlineStr"/>
-      <c r="E65" s="268" t="inlineStr"/>
+      <c r="D65" s="268" t="n"/>
+      <c r="E65" s="268" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="267" t="n">
@@ -17342,8 +17402,8 @@
           <t>DEP JARDIM, DEPÓSITO</t>
         </is>
       </c>
-      <c r="D66" s="268" t="inlineStr"/>
-      <c r="E66" s="268" t="inlineStr"/>
+      <c r="D66" s="268" t="n"/>
+      <c r="E66" s="268" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="267" t="n">
@@ -17359,8 +17419,8 @@
           <t>VESTIÁRIO FEM./MASC. - TERMAS (linha nova)</t>
         </is>
       </c>
-      <c r="D67" s="268" t="inlineStr"/>
-      <c r="E67" s="268" t="inlineStr"/>
+      <c r="D67" s="268" t="n"/>
+      <c r="E67" s="268" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="267" t="n">
@@ -17376,8 +17436,8 @@
           <t>ESCADA DE INCÊNDIO (linha nova)</t>
         </is>
       </c>
-      <c r="D68" s="268" t="inlineStr"/>
-      <c r="E68" s="268" t="inlineStr"/>
+      <c r="D68" s="268" t="n"/>
+      <c r="E68" s="268" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="267" t="n">
@@ -17393,8 +17453,8 @@
           <t>ANTECÂMARA (linha nova)</t>
         </is>
       </c>
-      <c r="D69" s="268" t="inlineStr"/>
-      <c r="E69" s="268" t="inlineStr"/>
+      <c r="D69" s="268" t="n"/>
+      <c r="E69" s="268" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="267" t="n">
@@ -17410,8 +17470,8 @@
           <t>CIRCULAÇÃO (linha nova)</t>
         </is>
       </c>
-      <c r="D70" s="268" t="inlineStr"/>
-      <c r="E70" s="268" t="inlineStr"/>
+      <c r="D70" s="268" t="n"/>
+      <c r="E70" s="268" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="267" t="n">
@@ -17427,8 +17487,8 @@
           <t>ESTAR PISCINA / CIRCULAÇÃO (linha nova)</t>
         </is>
       </c>
-      <c r="D71" s="268" t="inlineStr"/>
-      <c r="E71" s="268" t="inlineStr"/>
+      <c r="D71" s="268" t="n"/>
+      <c r="E71" s="268" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="267" t="n">
@@ -17444,8 +17504,8 @@
           <t>CIRCULAÇÃO EXTERNA COBERTA/DESCOBERTA E VARANDA ESPAÇO KIDS (linha nova)</t>
         </is>
       </c>
-      <c r="D72" s="268" t="inlineStr"/>
-      <c r="E72" s="268" t="inlineStr"/>
+      <c r="D72" s="268" t="n"/>
+      <c r="E72" s="268" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="267" t="n">
@@ -17461,8 +17521,8 @@
           <t>ESCADA EXTERNA (linha nova)</t>
         </is>
       </c>
-      <c r="D73" s="268" t="inlineStr"/>
-      <c r="E73" s="268" t="inlineStr"/>
+      <c r="D73" s="268" t="n"/>
+      <c r="E73" s="268" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="267" t="n">
@@ -17478,8 +17538,8 @@
           <t>QUADRA INFANTIL (linha nova)</t>
         </is>
       </c>
-      <c r="D74" s="268" t="inlineStr"/>
-      <c r="E74" s="268" t="inlineStr"/>
+      <c r="D74" s="268" t="n"/>
+      <c r="E74" s="268" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="267" t="n">
@@ -17495,8 +17555,8 @@
           <t>APOIO QUADRAS (linha nova)</t>
         </is>
       </c>
-      <c r="D75" s="268" t="inlineStr"/>
-      <c r="E75" s="268" t="inlineStr"/>
+      <c r="D75" s="268" t="n"/>
+      <c r="E75" s="268" t="n"/>
     </row>
     <row r="76"/>
     <row r="77"/>
@@ -17528,7 +17588,7 @@
           <t>CRITÉRIO</t>
         </is>
       </c>
-      <c r="E79" s="266" t="inlineStr"/>
+      <c r="E79" s="266" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="267" t="n">
@@ -17549,7 +17609,7 @@
           <t>Transcrição direta.</t>
         </is>
       </c>
-      <c r="E80" s="268" t="inlineStr"/>
+      <c r="E80" s="268" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="267" t="n">
@@ -17570,7 +17630,7 @@
           <t>Revestimentos e pinturas (códigos PA, 01, 06, 09, 12...).</t>
         </is>
       </c>
-      <c r="E81" s="268" t="inlineStr"/>
+      <c r="E81" s="268" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="267" t="n">
@@ -17591,7 +17651,7 @@
           <t>Espelhos sobre armário, fechamentos e painéis decorativos (códigos D), perfis de transição.</t>
         </is>
       </c>
-      <c r="E82" s="268" t="inlineStr"/>
+      <c r="E82" s="268" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="267" t="n">
@@ -17612,7 +17672,7 @@
           <t>P28 (D43) - painel e porta em alumínio e vidro (Massagem).</t>
         </is>
       </c>
-      <c r="E83" s="268" t="inlineStr"/>
+      <c r="E83" s="268" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="267" t="n">
@@ -17633,7 +17693,7 @@
           <t>Bancadas em BANCADA; prateleira e testeira em OUTROS REVESTIMENTOS.</t>
         </is>
       </c>
-      <c r="E84" s="268" t="inlineStr"/>
+      <c r="E84" s="268" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="267" t="n">
@@ -17654,7 +17714,7 @@
           <t>Separado por item; chuveiros em OUTROS LOUÇAS E METAIS.</t>
         </is>
       </c>
-      <c r="E85" s="268" t="inlineStr"/>
+      <c r="E85" s="268" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="267" t="n">
@@ -17675,13 +17735,13 @@
           <t>Ralos em RALOS; saboneteira, porta-papel e papeleira em OUTROS COMPLEMENTARES.</t>
         </is>
       </c>
-      <c r="E86" s="268" t="inlineStr"/>
+      <c r="E86" s="268" t="n"/>
     </row>
     <row r="87"/>
     <row r="88">
       <c r="A88" s="279" t="inlineStr">
         <is>
-          <t>3. LEVANTAMENTO PELOS PROJETOS DE DETALHAMENTO R04 (23/04/2026)</t>
+          <t>5. LEVANTAMENTO PELOS PROJETOS DE DETALHAMENTO R04 (23/04/2026)</t>
         </is>
       </c>
     </row>
@@ -18943,7 +19003,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PILOTIS – PISCINA DECOBERTA</t>
+          <t>PILOTIS – PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -18968,7 +19028,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PILOTIS – PISCINA DECOBERTA</t>
+          <t>PILOTIS – PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -18993,7 +19053,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PILOTIS – PISCINA DECOBERTA</t>
+          <t>PILOTIS – PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -19018,12 +19078,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PILOTIS – PISCINA DECOBERTA</t>
+          <t>PILOTIS – PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>OUTROS  LOUÇAS E METAIS</t>
+          <t>OUTROS LOUÇAS E METAIS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19043,7 +19103,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PILOTIS – PISCINA DECOBERTA</t>
+          <t>PILOTIS – PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -19068,7 +19128,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PILOTIS – PISCINA DECOBERTA</t>
+          <t>PILOTIS – PISCINA DESCOBERTA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -20323,7 +20383,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>OUTROS  LOUÇAS E METAIS</t>
+          <t>OUTROS LOUÇAS E METAIS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21073,7 +21133,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>OUTROS  LOUÇAS E METAIS</t>
+          <t>OUTROS LOUÇAS E METAIS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -21473,7 +21533,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>OUTROS  LOUÇAS E METAIS</t>
+          <t>OUTROS LOUÇAS E METAIS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -22693,7 +22753,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -22718,7 +22778,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -22743,7 +22803,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -22768,7 +22828,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -22793,7 +22853,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -22818,7 +22878,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -22843,7 +22903,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>TÉRREO – HALL GARGEM</t>
+          <t>TÉRREO – HALL GARAGEM</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -23316,7 +23376,7 @@
     <row r="315">
       <c r="A315" s="279" t="inlineStr">
         <is>
-          <t>4. OBSERVAÇÕES DO LEVANTAMENTO R04</t>
+          <t>6. OBSERVAÇÕES DO LEVANTAMENTO R04</t>
         </is>
       </c>
     </row>
@@ -23444,7 +23504,7 @@
     <row r="327">
       <c r="A327" s="279" t="inlineStr">
         <is>
-          <t>5. ESPECIFICAÇÕES DAS PLANTAS DE ARQUITETURA (CDJ-ARQ-EX PR003–PR013, Quadro de Especificações - Geral)</t>
+          <t>7. ESPECIFICAÇÕES DAS PLANTAS DE ARQUITETURA (CDJ-ARQ-EX PR003–PR013, Quadro de Especificações - Geral)</t>
         </is>
       </c>
     </row>
@@ -23781,7 +23841,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTECÂMARA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -23806,7 +23866,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTECÂMARA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -23831,7 +23891,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTECÂMARA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -23856,7 +23916,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTICÂRA</t>
+          <t>TÉRREO – CIRCULAÇÃO ELEVADOR DE SERVIÇO/ANTECÂMARA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -28016,7 +28076,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII | 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali off white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII | 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -28116,7 +28176,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali pff white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII | 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
+          <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali off white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII | 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -28440,7 +28500,7 @@
     <row r="534">
       <c r="A534" s="279" t="inlineStr">
         <is>
-          <t>6. APARTAMENTO TIPO (pasta DTL - DETALHAMENTO / APARTAMENTOS)</t>
+          <t>8. APARTAMENTO TIPO (pasta DTL - DETALHAMENTO / APARTAMENTOS)</t>
         </is>
       </c>
     </row>
@@ -28568,7 +28628,7 @@
     <row r="546">
       <c r="A546" s="279" t="inlineStr">
         <is>
-          <t>7. CONFERÊNCIA VISUAL DAS PLANTAS DE ARQUITETURA (02/10/2026)</t>
+          <t>9. CONFERÊNCIA VISUAL DAS PLANTAS DE ARQUITETURA (02/10/2026)</t>
         </is>
       </c>
     </row>

--- a/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
+++ b/especificacoes/CDJ-GRE-ARQ-AC-R00.xlsx
@@ -2578,7 +2578,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip cstate="print" r:embed="rId39"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2619,7 +2619,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip cstate="print" r:embed="rId40"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -2662,7 +2662,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId12"/>
+        <a:blip cstate="print" r:embed="rId41"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -2705,7 +2705,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId13"/>
+        <a:blip cstate="print" r:embed="rId42"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -2748,7 +2748,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId14"/>
+        <a:blip cstate="print" r:embed="rId43"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3087,6 +3087,818 @@
         <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1971675</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="895350" cy="895350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1209675</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2419350" cy="2419350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1590675</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1657350" cy="1657350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>22</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1876425</colOff>
+      <row>27</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1085850" cy="1085850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1876425</colOff>
+      <row>28</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1085850" cy="1085850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1390650</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2057400" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>18</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>26</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>29</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>30</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>36</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>37</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>41</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>42</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>43</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>44</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>31</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="771525" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1876425</colOff>
+      <row>27</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1085850" cy="1085850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1933575</colOff>
+      <row>27</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="971550" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1790700</colOff>
+      <row>27</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1885950</colOff>
+      <row>27</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1885950</colOff>
+      <row>27</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>38</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3662,7 +4474,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
+        <a:blip cstate="print" r:embed="rId130"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3703,7 +4515,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId23"/>
+        <a:blip cstate="print" r:embed="rId131"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3746,7 +4558,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId24"/>
+        <a:blip cstate="print" r:embed="rId132"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3789,7 +4601,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId25"/>
+        <a:blip cstate="print" r:embed="rId133"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -3832,7 +4644,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId26"/>
+        <a:blip cstate="print" r:embed="rId134"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -4514,6 +5326,3030 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1114425</colOff>
+      <row>12</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2609850" cy="2609850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1114425</colOff>
+      <row>13</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2609850" cy="2609850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1209675</colOff>
+      <row>22</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2419350" cy="2419350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1209675</colOff>
+      <row>23</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2419350" cy="2419350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>447675</colOff>
+      <row>25</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3943350" cy="3943350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>638175</colOff>
+      <row>26</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3562350" cy="3562350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>923925</colOff>
+      <row>31</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2990850" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>33</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>828675</colOff>
+      <row>36</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3181350" cy="3181350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1304925</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2228850" cy="2228850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>733425</colOff>
+      <row>44</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3371850" cy="3371850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>733425</colOff>
+      <row>45</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3371850" cy="3371850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1876425</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1085850" cy="1085850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1876425</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1085850" cy="1085850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>42</col>
+      <colOff>1495425</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1495425</colOff>
+      <row>57</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1590675</colOff>
+      <row>52</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1666875" cy="1638300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1590675</colOff>
+      <row>53</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1666875" cy="1638300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1638300</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1571625" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1638300</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1571625" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1419225</colOff>
+      <row>22</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2009775" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1419225</colOff>
+      <row>23</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2009775" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1638300</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1571625" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1638300</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1571625" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1933575</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="971550" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1933575</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="971550" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>838200</colOff>
+      <row>31</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3162300" cy="3162300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1419225</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2009775" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1419225</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2009775" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>43</col>
+      <colOff>1419225</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2009775" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1552575</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1552575</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1304925</colOff>
+      <row>22</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2228850" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1304925</colOff>
+      <row>23</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2228850" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1552575</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1552575</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1885950</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1885950</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>44</col>
+      <colOff>1552575</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1552575</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1552575</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1304925</colOff>
+      <row>22</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2228850" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1304925</colOff>
+      <row>23</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2228850" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1552575</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1552575</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1885950</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1885950</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>1552575</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1733550" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1409700</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1409700</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1123950</colOff>
+      <row>22</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2590800" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1123950</colOff>
+      <row>23</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2590800" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1857375</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1133475" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1495425</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1495425</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1981200</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="876300" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>49</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1981200</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="876300" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2038350</colOff>
+      <row>49</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1600200</colOff>
+      <row>52</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1638300" cy="1638300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1600200</colOff>
+      <row>53</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1638300" cy="1638300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>638175</colOff>
+      <row>26</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3562350" cy="3562350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>923925</colOff>
+      <row>31</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2990850" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>781050</colOff>
+      <row>26</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3276600" cy="3562350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1047750</colOff>
+      <row>31</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2743200" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1409700</colOff>
+      <row>28</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1409700</colOff>
+      <row>28</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1323975</colOff>
+      <row>58</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2200275" cy="2200275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1409700</colOff>
+      <row>28</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>838200</colOff>
+      <row>31</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3162300" cy="3162300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1409700</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1409700</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1219200</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2400300" cy="2400300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>41</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1790700</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1790700</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>46</col>
+      <colOff>1409700</colOff>
+      <row>54</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>1409700</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>1409700</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1790700</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1790700</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>40</col>
+      <colOff>1495425</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>40</col>
+      <colOff>1495425</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1847850" cy="1847850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>1885950</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>1885950</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>41</col>
+      <colOff>1409700</colOff>
+      <row>34</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>41</col>
+      <colOff>1409700</colOff>
+      <row>35</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2019300" cy="2019300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>40</col>
+      <colOff>1790700</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>40</col>
+      <colOff>1790700</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId115"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1304925</colOff>
+      <row>40</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2228850" cy="2228850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2038350</colOff>
+      <row>41</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId117"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1885950</colOff>
+      <row>41</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1076325" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1028700</colOff>
+      <row>44</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2781300" cy="3543300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1028700</colOff>
+      <row>45</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="2781300" cy="3543300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId120"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>647700</colOff>
+      <row>44</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3543300" cy="3543300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId121"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>647700</colOff>
+      <row>45</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3543300" cy="3543300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="127" name="Image 127" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId122"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>41</col>
+      <colOff>1790700</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="128" name="Image 128" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId123"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>41</col>
+      <colOff>1790700</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId124"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>42</col>
+      <colOff>1790700</colOff>
+      <row>47</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId125"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>42</col>
+      <colOff>1790700</colOff>
+      <row>48</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1257300" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId126"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1685925</colOff>
+      <row>52</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1466850" cy="1466850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId127"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>1685925</colOff>
+      <row>53</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1466850" cy="1466850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId128"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>581025</colOff>
+      <row>62</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="3676650" cy="2209800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId129"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -4540,7 +8376,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip cstate="print" r:embed="rId46"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4581,7 +8417,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip cstate="print" r:embed="rId47"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -4624,7 +8460,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId12"/>
+        <a:blip cstate="print" r:embed="rId48"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -4667,7 +8503,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId13"/>
+        <a:blip cstate="print" r:embed="rId49"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -4710,7 +8546,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId14"/>
+        <a:blip cstate="print" r:embed="rId50"/>
         <a:srcRect b="16485"/>
         <a:stretch>
           <a:fillRect/>
@@ -5056,6 +8892,1014 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2085975</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="676275" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2085975</colOff>
+      <row>13</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="676275" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1981200</colOff>
+      <row>13</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="876300" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>2085975</colOff>
+      <row>13</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="676275" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>2124075</colOff>
+      <row>13</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2085975</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="676275" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>2085975</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="676275" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>1981200</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="876300" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>1981200</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="876300" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>2038350</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>1981200</colOff>
+      <row>14</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="876300" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2124075</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2124075</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>2124075</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>2038350</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>18</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>2124075</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>1952625</colOff>
+      <row>15</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="933450" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1733550</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1371600" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>1733550</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1371600" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1895475</colOff>
+      <row>16</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1047750" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>1895475</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="1047750" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>2124075</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>2124075</colOff>
+      <row>17</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2124075</colOff>
+      <row>18</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2124075</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2124075</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>2038350</colOff>
+      <row>19</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2124075</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>2124075</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>2038350</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>2124075</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="590550" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>38</col>
+      <colOff>2038350</colOff>
+      <row>20</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>2038350</colOff>
+      <row>21</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>2038350</colOff>
+      <row>21</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="762000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6053,7 +10897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF56"/>
+  <dimension ref="A1:AQ56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6088,6 +10932,26 @@
     <col width="31" customWidth="1" min="30" max="30"/>
     <col width="31" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="72" customWidth="1" min="34" max="34"/>
+    <col width="72" customWidth="1" min="35" max="35"/>
+    <col width="72" customWidth="1" min="36" max="36"/>
+    <col width="72" customWidth="1" min="37" max="37"/>
+    <col width="72" customWidth="1" min="38" max="38"/>
+    <col width="72" customWidth="1" min="39" max="39"/>
+    <col width="72" customWidth="1" min="40" max="40"/>
+    <col width="72" customWidth="1" min="41" max="41"/>
+    <col width="72" customWidth="1" min="42" max="42"/>
+    <col width="72" customWidth="1" min="43" max="43"/>
+    <col width="72" customWidth="1" min="44" max="44"/>
+    <col width="72" customWidth="1" min="45" max="45"/>
+    <col width="72" customWidth="1" min="46" max="46"/>
+    <col width="72" customWidth="1" min="47" max="47"/>
+    <col width="72" customWidth="1" min="48" max="48"/>
+    <col width="72" customWidth="1" min="49" max="49"/>
+    <col width="72" customWidth="1" min="50" max="50"/>
+    <col width="72" customWidth="1" min="51" max="51"/>
+    <col width="72" customWidth="1" min="52" max="52"/>
+    <col width="72" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
@@ -6652,6 +11516,11 @@
 COMPLEMENTARES</t>
         </is>
       </c>
+      <c r="AH11" s="322" t="inlineStr">
+        <is>
+          <t>IMAGENS DAS ESPECIFICAÇÕES (fora da área de impressão)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customFormat="1" customHeight="1" s="13" thickBot="1">
       <c r="A12" s="51" t="n"/>
@@ -6837,7 +11706,8 @@
       <c r="U16" s="300" t="n"/>
       <c r="V16" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W16" s="300" t="n"/>
@@ -6849,8 +11719,15 @@
       </c>
       <c r="Y16" s="320" t="n"/>
       <c r="Z16" s="300" t="n"/>
-    </row>
-    <row r="17" ht="194" customHeight="1">
+      <c r="AH16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="224" customHeight="1">
       <c r="A17" s="298" t="inlineStr">
         <is>
           <t>GUARITA</t>
@@ -6859,7 +11736,8 @@
       <c r="B17" s="303" t="inlineStr">
         <is>
           <t>P5 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Rejunte Infinity Hard cor Mocha ou cor Branco Pérola Deverá ser testado as duas opções de rejunte para escolher a que mais se aproxima do tom da peça. Amostra a ser aprovada pela GPA&amp;A.
-CONFLITO – Arquitetura: ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+CONFLITO – Arquitetura: ARQ-P13 - Piso em pedra natural Basaltina. Espessura: 2cm. Dimensões e paginação conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C17" s="300" t="n"/>
@@ -6898,15 +11776,30 @@
       <c r="U17" s="300" t="n"/>
       <c r="V17" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W17" s="300" t="n"/>
       <c r="X17" s="320" t="n"/>
       <c r="Y17" s="320" t="n"/>
       <c r="Z17" s="300" t="n"/>
-    </row>
-    <row r="18" ht="89" customHeight="1">
+      <c r="AH17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V17</t>
+        </is>
+      </c>
+      <c r="AI17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
       <c r="A18" s="298" t="inlineStr">
         <is>
           <t>LAVABO GUARITA</t>
@@ -6914,7 +11807,8 @@
       </c>
       <c r="B18" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C18" s="300" t="n"/>
@@ -6922,7 +11816,8 @@
       <c r="E18" s="300" t="n"/>
       <c r="F18" s="308" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G18" s="300" t="n"/>
@@ -6953,8 +11848,15 @@
       <c r="X18" s="320" t="n"/>
       <c r="Y18" s="320" t="n"/>
       <c r="Z18" s="300" t="n"/>
-    </row>
-    <row r="19" ht="89" customHeight="1">
+      <c r="AH18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B18, F18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
       <c r="A19" s="298" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO GUARITA</t>
@@ -6962,7 +11864,8 @@
       </c>
       <c r="B19" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C19" s="300" t="n"/>
@@ -6970,7 +11873,8 @@
       <c r="E19" s="300" t="n"/>
       <c r="F19" s="308" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G19" s="300" t="n"/>
@@ -7001,6 +11905,13 @@
       <c r="X19" s="320" t="n"/>
       <c r="Y19" s="320" t="n"/>
       <c r="Z19" s="300" t="n"/>
+      <c r="AH19" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B19, F19</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="269" customHeight="1">
       <c r="A20" s="298" t="inlineStr">
@@ -7050,7 +11961,8 @@
       <c r="U20" s="300" t="n"/>
       <c r="V20" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W20" s="300" t="n"/>
@@ -7064,6 +11976,13 @@
       <c r="Z20" s="308" t="inlineStr">
         <is>
           <t>D63 - Guarda corpo em chapa metálica dourada colada sobre fechamento em MDF cru 6mm aparafusado em estrutura auxiliar de metalon. Dimensões e detalhes conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="AH20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V20</t>
         </is>
       </c>
     </row>
@@ -7113,7 +12032,8 @@
       <c r="U21" s="300" t="n"/>
       <c r="V21" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W21" s="300" t="n"/>
@@ -7122,6 +12042,13 @@
       <c r="Z21" s="308" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="AH21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V21</t>
         </is>
       </c>
     </row>
@@ -7218,7 +12145,8 @@
       <c r="U23" s="300" t="n"/>
       <c r="V23" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W23" s="300" t="n"/>
@@ -7232,6 +12160,13 @@
       <c r="Z23" s="308" t="inlineStr">
         <is>
           <t>D64 - Quadro para elevador em chapa metálica 8mm com acabamento em pintura eletrostática, cor branca. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="AH23" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V23</t>
         </is>
       </c>
     </row>
@@ -7355,7 +12290,7 @@
       <c r="Y26" s="320" t="n"/>
       <c r="Z26" s="307" t="n"/>
     </row>
-    <row r="27" ht="89" customHeight="1">
+    <row r="27" ht="120" customHeight="1">
       <c r="A27" s="298" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO</t>
@@ -7363,7 +12298,8 @@
       </c>
       <c r="B27" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C27" s="300" t="n"/>
@@ -7371,7 +12307,8 @@
       <c r="E27" s="300" t="n"/>
       <c r="F27" s="307" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G27" s="300" t="n"/>
@@ -7402,8 +12339,15 @@
       <c r="X27" s="307" t="n"/>
       <c r="Y27" s="307" t="n"/>
       <c r="Z27" s="307" t="n"/>
-    </row>
-    <row r="28" ht="149" customHeight="1">
+      <c r="AH27" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B27, F27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="164" customHeight="1">
       <c r="A28" s="298" t="inlineStr">
         <is>
           <t>I.S P.C.D</t>
@@ -7449,12 +12393,14 @@
       <c r="N28" s="300" t="n"/>
       <c r="O28" s="308" t="inlineStr">
         <is>
-          <t>D66 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento grafite escovado, cód.: 01739870. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D66 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento grafite escovado, cód.: 01739870. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P28" s="308" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q28" s="300" t="n"/>
@@ -7462,13 +12408,15 @@
       <c r="S28" s="300" t="n"/>
       <c r="T28" s="307" t="inlineStr">
         <is>
-          <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve</t>
+          <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U28" s="300" t="n"/>
       <c r="V28" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W28" s="307" t="n"/>
@@ -7482,7 +12430,50 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH28" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V28</t>
+        </is>
+      </c>
+      <c r="AI28" s="323" t="inlineStr">
+        <is>
+          <t>WEB-03 - Monocomando Bica Baixa de Mesa para Lavatório Mix&amp;Match Grafite Escovado Docol (90017398070) (Docol)
+Imagem de referência da web
+◄ VOLTAR para O28</t>
+        </is>
+      </c>
+      <c r="AJ28" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P28</t>
+        </is>
+      </c>
+      <c r="AK28" s="323" t="inlineStr">
+        <is>
+          <t>WEB-05 - Ralo Square Tampa Lisa Inox 15x15cm Elleve (Elleve)
+Imagem de referência da web
+◄ VOLTAR para T28</t>
+        </is>
+      </c>
+      <c r="AL28" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z28</t>
+        </is>
+      </c>
+      <c r="AM28" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z28</t>
         </is>
       </c>
     </row>
@@ -7531,7 +12522,8 @@
       <c r="U29" s="300" t="n"/>
       <c r="V29" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W29" s="300" t="n"/>
@@ -7543,8 +12535,15 @@
       </c>
       <c r="Y29" s="300" t="n"/>
       <c r="Z29" s="307" t="n"/>
-    </row>
-    <row r="30" ht="89" customHeight="1">
+      <c r="AH29" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1">
       <c r="A30" s="298" t="inlineStr">
         <is>
           <t>CONCIERGE</t>
@@ -7552,7 +12551,8 @@
       </c>
       <c r="B30" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C30" s="300" t="n"/>
@@ -7560,7 +12560,8 @@
       <c r="E30" s="308" t="n"/>
       <c r="F30" s="308" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G30" s="307" t="n"/>
@@ -7592,8 +12593,15 @@
       <c r="X30" s="300" t="n"/>
       <c r="Y30" s="300" t="n"/>
       <c r="Z30" s="307" t="n"/>
-    </row>
-    <row r="31" ht="89" customHeight="1">
+      <c r="AH30" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B30, F30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
       <c r="A31" s="298" t="inlineStr">
         <is>
           <t>DELIVERY</t>
@@ -7601,7 +12609,8 @@
       </c>
       <c r="B31" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C31" s="300" t="n"/>
@@ -7609,7 +12618,8 @@
       <c r="E31" s="308" t="n"/>
       <c r="F31" s="307" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G31" s="300" t="n"/>
@@ -7640,8 +12650,15 @@
       <c r="X31" s="320" t="n"/>
       <c r="Y31" s="320" t="n"/>
       <c r="Z31" s="307" t="n"/>
-    </row>
-    <row r="32" ht="104" customHeight="1">
+      <c r="AH31" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B31, F31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
       <c r="A32" s="298" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO SERVIÇO</t>
@@ -7657,7 +12674,8 @@
       <c r="E32" s="308" t="n"/>
       <c r="F32" s="307" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G32" s="300" t="n"/>
@@ -7688,6 +12706,13 @@
       <c r="X32" s="320" t="n"/>
       <c r="Y32" s="320" t="n"/>
       <c r="Z32" s="307" t="n"/>
+      <c r="AH32" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para F32</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="89" customHeight="1">
       <c r="A33" s="298" t="inlineStr">
@@ -7777,7 +12802,7 @@
       <c r="Y34" s="320" t="n"/>
       <c r="Z34" s="307" t="n"/>
     </row>
-    <row r="35" ht="89" customHeight="1">
+    <row r="35" ht="120" customHeight="1">
       <c r="A35" s="298" t="inlineStr">
         <is>
           <t>ZELADORIA</t>
@@ -7785,7 +12810,8 @@
       </c>
       <c r="B35" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C35" s="300" t="n"/>
@@ -7793,7 +12819,8 @@
       <c r="E35" s="308" t="n"/>
       <c r="F35" s="307" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G35" s="300" t="n"/>
@@ -7824,8 +12851,15 @@
       <c r="X35" s="307" t="n"/>
       <c r="Y35" s="307" t="n"/>
       <c r="Z35" s="300" t="n"/>
-    </row>
-    <row r="36" ht="74" customHeight="1">
+      <c r="AH35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B35, F35</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1">
       <c r="A36" s="298" t="inlineStr">
         <is>
           <t>ARS 1</t>
@@ -7833,7 +12867,8 @@
       </c>
       <c r="B36" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C36" s="300" t="n"/>
@@ -7843,7 +12878,8 @@
       <c r="G36" s="300" t="n"/>
       <c r="H36" s="307" t="inlineStr">
         <is>
-          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I36" s="307" t="inlineStr">
@@ -7868,8 +12904,15 @@
       <c r="X36" s="307" t="n"/>
       <c r="Y36" s="307" t="n"/>
       <c r="Z36" s="300" t="n"/>
-    </row>
-    <row r="37" ht="74" customHeight="1">
+      <c r="AH36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B36, H36</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1">
       <c r="A37" s="298" t="inlineStr">
         <is>
           <t>ARS 2</t>
@@ -7877,7 +12920,8 @@
       </c>
       <c r="B37" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C37" s="300" t="n"/>
@@ -7887,7 +12931,8 @@
       <c r="G37" s="300" t="n"/>
       <c r="H37" s="307" t="inlineStr">
         <is>
-          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I37" s="307" t="inlineStr">
@@ -7912,8 +12957,15 @@
       <c r="X37" s="307" t="n"/>
       <c r="Y37" s="307" t="n"/>
       <c r="Z37" s="300" t="n"/>
-    </row>
-    <row r="38" ht="74" customHeight="1">
+      <c r="AH37" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B37, H37</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
       <c r="A38" s="298" t="inlineStr">
         <is>
           <t>ARS 3</t>
@@ -7921,7 +12973,8 @@
       </c>
       <c r="B38" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C38" s="300" t="n"/>
@@ -7931,7 +12984,8 @@
       <c r="G38" s="300" t="n"/>
       <c r="H38" s="307" t="inlineStr">
         <is>
-          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I38" s="307" t="inlineStr">
@@ -7956,8 +13010,15 @@
       <c r="X38" s="307" t="n"/>
       <c r="Y38" s="307" t="n"/>
       <c r="Z38" s="300" t="n"/>
-    </row>
-    <row r="39" ht="74" customHeight="1">
+      <c r="AH38" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B38, H38</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
       <c r="A39" s="298" t="inlineStr">
         <is>
           <t>SALA MOTORISTA</t>
@@ -7965,7 +13026,8 @@
       </c>
       <c r="B39" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P06 - Piso em porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P06 - Piso em porcelanato padrão cimentício 120x120cm, espessura 1cm, com acabamento fosco (antiderrapante). Ref.: CITTA SGR HARD; cód. 61588; Portinari. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C39" s="300" t="n"/>
@@ -8004,6 +13066,13 @@
       <c r="X39" s="307" t="n"/>
       <c r="Y39" s="307" t="n"/>
       <c r="Z39" s="300" t="n"/>
+      <c r="AH39" s="323" t="inlineStr">
+        <is>
+          <t>WEB-08 - Porcelanato Citta SGR Hard 120x120 61588 - Portinari (Portinari)
+Imagem de referência da web
+◄ VOLTAR para B39</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="74" customHeight="1">
       <c r="A40" s="298" t="inlineStr">
@@ -8049,7 +13118,7 @@
       <c r="Y40" s="307" t="n"/>
       <c r="Z40" s="300" t="n"/>
     </row>
-    <row r="41" ht="74" customHeight="1">
+    <row r="41" ht="120" customHeight="1">
       <c r="A41" s="298" t="inlineStr">
         <is>
           <t>VEST. P.C.D</t>
@@ -8057,7 +13126,8 @@
       </c>
       <c r="B41" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C41" s="300" t="n"/>
@@ -8067,7 +13137,8 @@
       <c r="G41" s="300" t="n"/>
       <c r="H41" s="307" t="inlineStr">
         <is>
-          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I41" s="307" t="inlineStr">
@@ -8092,8 +13163,15 @@
       <c r="X41" s="307" t="n"/>
       <c r="Y41" s="307" t="n"/>
       <c r="Z41" s="300" t="n"/>
-    </row>
-    <row r="42" ht="74" customHeight="1">
+      <c r="AH41" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B41, H41</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
       <c r="A42" s="298" t="inlineStr">
         <is>
           <t>VEST. FEMININO</t>
@@ -8101,7 +13179,8 @@
       </c>
       <c r="B42" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C42" s="300" t="n"/>
@@ -8111,7 +13190,8 @@
       <c r="G42" s="300" t="n"/>
       <c r="H42" s="307" t="inlineStr">
         <is>
-          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I42" s="307" t="inlineStr">
@@ -8136,8 +13216,15 @@
       <c r="X42" s="307" t="n"/>
       <c r="Y42" s="307" t="n"/>
       <c r="Z42" s="300" t="n"/>
-    </row>
-    <row r="43" ht="74" customHeight="1">
+      <c r="AH42" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B42, H42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
       <c r="A43" s="298" t="inlineStr">
         <is>
           <t>VEST. MASC.</t>
@@ -8145,7 +13232,8 @@
       </c>
       <c r="B43" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C43" s="300" t="n"/>
@@ -8155,7 +13243,8 @@
       <c r="G43" s="300" t="n"/>
       <c r="H43" s="307" t="inlineStr">
         <is>
-          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.</t>
+          <t>ARQ-PA11 - Parede revestida em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I43" s="307" t="inlineStr">
@@ -8180,8 +13269,15 @@
       <c r="X43" s="307" t="n"/>
       <c r="Y43" s="307" t="n"/>
       <c r="Z43" s="300" t="n"/>
-    </row>
-    <row r="44" ht="74" customHeight="1">
+      <c r="AH43" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B43, H43</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
       <c r="A44" s="298" t="inlineStr">
         <is>
           <t>ESTAR/COPA FUNCIONÁRIOS</t>
@@ -8189,7 +13285,8 @@
       </c>
       <c r="B44" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C44" s="300" t="n"/>
@@ -8224,8 +13321,15 @@
       <c r="X44" s="307" t="n"/>
       <c r="Y44" s="307" t="n"/>
       <c r="Z44" s="300" t="n"/>
-    </row>
-    <row r="45" ht="89" customHeight="1">
+      <c r="AH44" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B44</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="120" customHeight="1">
       <c r="A45" s="298" t="inlineStr">
         <is>
           <t>CIRCULAÇÃO</t>
@@ -8233,7 +13337,8 @@
       </c>
       <c r="B45" s="307" t="inlineStr">
         <is>
-          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C45" s="300" t="n"/>
@@ -8241,7 +13346,8 @@
       <c r="E45" s="308" t="n"/>
       <c r="F45" s="307" t="inlineStr">
         <is>
-          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G45" s="300" t="n"/>
@@ -8272,6 +13378,13 @@
       <c r="X45" s="307" t="n"/>
       <c r="Y45" s="307" t="n"/>
       <c r="Z45" s="300" t="n"/>
+      <c r="AH45" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B45, F45</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="298" t="inlineStr">
@@ -8742,8 +13855,9 @@
       <c r="Z56" s="300" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="L10:U10"/>
+    <mergeCell ref="AH11:AQ11"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="T5:U5"/>
     <mergeCell ref="B1:I4"/>
@@ -8775,6 +13889,78 @@
     <mergeCell ref="V12:Z12"/>
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="V16" location="'TÉRREO '!AH16" tooltip="Ver imagem"/>
+    <hyperlink ref="AH16" location="'TÉRREO '!V16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B17" location="'TÉRREO '!AI17" tooltip="Ver imagem"/>
+    <hyperlink ref="V17" location="'TÉRREO '!AH17" tooltip="Ver imagem"/>
+    <hyperlink ref="AH17" location="'TÉRREO '!V17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI17" location="'TÉRREO '!B17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B18" location="'TÉRREO '!AH18" tooltip="Ver imagem"/>
+    <hyperlink ref="F18" location="'TÉRREO '!AH18" tooltip="Ver imagem"/>
+    <hyperlink ref="AH18" location="'TÉRREO '!B18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B19" location="'TÉRREO '!AH19" tooltip="Ver imagem"/>
+    <hyperlink ref="F19" location="'TÉRREO '!AH19" tooltip="Ver imagem"/>
+    <hyperlink ref="AH19" location="'TÉRREO '!B19" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V20" location="'TÉRREO '!AH20" tooltip="Ver imagem"/>
+    <hyperlink ref="AH20" location="'TÉRREO '!V20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V21" location="'TÉRREO '!AH21" tooltip="Ver imagem"/>
+    <hyperlink ref="AH21" location="'TÉRREO '!V21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V23" location="'TÉRREO '!AH23" tooltip="Ver imagem"/>
+    <hyperlink ref="AH23" location="'TÉRREO '!V23" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B27" location="'TÉRREO '!AH27" tooltip="Ver imagem"/>
+    <hyperlink ref="F27" location="'TÉRREO '!AH27" tooltip="Ver imagem"/>
+    <hyperlink ref="AH27" location="'TÉRREO '!B27" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O28" location="'TÉRREO '!AI28" tooltip="Ver imagem"/>
+    <hyperlink ref="P28" location="'TÉRREO '!AJ28" tooltip="Ver imagem"/>
+    <hyperlink ref="T28" location="'TÉRREO '!AK28" tooltip="Ver imagem"/>
+    <hyperlink ref="V28" location="'TÉRREO '!AH28" tooltip="Ver imagem"/>
+    <hyperlink ref="Z28" location="'TÉRREO '!AL28" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH28" location="'TÉRREO '!V28" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI28" location="'TÉRREO '!O28" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ28" location="'TÉRREO '!P28" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK28" location="'TÉRREO '!T28" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL28" location="'TÉRREO '!Z28" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM28" location="'TÉRREO '!Z28" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V29" location="'TÉRREO '!AH29" tooltip="Ver imagem"/>
+    <hyperlink ref="AH29" location="'TÉRREO '!V29" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B30" location="'TÉRREO '!AH30" tooltip="Ver imagem"/>
+    <hyperlink ref="F30" location="'TÉRREO '!AH30" tooltip="Ver imagem"/>
+    <hyperlink ref="AH30" location="'TÉRREO '!B30" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B31" location="'TÉRREO '!AH31" tooltip="Ver imagem"/>
+    <hyperlink ref="F31" location="'TÉRREO '!AH31" tooltip="Ver imagem"/>
+    <hyperlink ref="AH31" location="'TÉRREO '!B31" tooltip="Voltar para a grade"/>
+    <hyperlink ref="F32" location="'TÉRREO '!AH32" tooltip="Ver imagem"/>
+    <hyperlink ref="AH32" location="'TÉRREO '!F32" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B35" location="'TÉRREO '!AH35" tooltip="Ver imagem"/>
+    <hyperlink ref="F35" location="'TÉRREO '!AH35" tooltip="Ver imagem"/>
+    <hyperlink ref="AH35" location="'TÉRREO '!B35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B36" location="'TÉRREO '!AH36" tooltip="Ver imagem"/>
+    <hyperlink ref="H36" location="'TÉRREO '!AH36" tooltip="Ver imagem"/>
+    <hyperlink ref="AH36" location="'TÉRREO '!B36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B37" location="'TÉRREO '!AH37" tooltip="Ver imagem"/>
+    <hyperlink ref="H37" location="'TÉRREO '!AH37" tooltip="Ver imagem"/>
+    <hyperlink ref="AH37" location="'TÉRREO '!B37" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B38" location="'TÉRREO '!AH38" tooltip="Ver imagem"/>
+    <hyperlink ref="H38" location="'TÉRREO '!AH38" tooltip="Ver imagem"/>
+    <hyperlink ref="AH38" location="'TÉRREO '!B38" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B39" location="'TÉRREO '!AH39" tooltip="Ver imagem"/>
+    <hyperlink ref="AH39" location="'TÉRREO '!B39" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B41" location="'TÉRREO '!AH41" tooltip="Ver imagem"/>
+    <hyperlink ref="H41" location="'TÉRREO '!AH41" tooltip="Ver imagem"/>
+    <hyperlink ref="AH41" location="'TÉRREO '!B41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B42" location="'TÉRREO '!AH42" tooltip="Ver imagem"/>
+    <hyperlink ref="H42" location="'TÉRREO '!AH42" tooltip="Ver imagem"/>
+    <hyperlink ref="AH42" location="'TÉRREO '!B42" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B43" location="'TÉRREO '!AH43" tooltip="Ver imagem"/>
+    <hyperlink ref="H43" location="'TÉRREO '!AH43" tooltip="Ver imagem"/>
+    <hyperlink ref="AH43" location="'TÉRREO '!B43" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B44" location="'TÉRREO '!AH44" tooltip="Ver imagem"/>
+    <hyperlink ref="AH44" location="'TÉRREO '!B44" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B45" location="'TÉRREO '!AH45" tooltip="Ver imagem"/>
+    <hyperlink ref="F45" location="'TÉRREO '!AH45" tooltip="Ver imagem"/>
+    <hyperlink ref="AH45" location="'TÉRREO '!B45" tooltip="Voltar para a grade"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8" scale="38" pageOrder="overThenDown"/>
@@ -10324,7 +15510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AQ64"/>
+  <dimension ref="A1:AU64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10371,6 +15557,14 @@
     <col width="72" customWidth="1" min="43" max="43"/>
     <col width="72" customWidth="1" min="44" max="44"/>
     <col width="72" customWidth="1" min="45" max="45"/>
+    <col width="72" customWidth="1" min="46" max="46"/>
+    <col width="72" customWidth="1" min="47" max="47"/>
+    <col width="72" customWidth="1" min="48" max="48"/>
+    <col width="72" customWidth="1" min="49" max="49"/>
+    <col width="72" customWidth="1" min="50" max="50"/>
+    <col width="72" customWidth="1" min="51" max="51"/>
+    <col width="72" customWidth="1" min="52" max="52"/>
+    <col width="72" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
@@ -11033,7 +16227,8 @@
       <c r="U13" s="296" t="n"/>
       <c r="V13" s="326" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W13" s="296" t="n"/>
@@ -11047,6 +16242,13 @@
       </c>
       <c r="Y13" s="327" t="n"/>
       <c r="Z13" s="296" t="n"/>
+      <c r="AH13" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V13</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="284" customHeight="1">
       <c r="A14" s="298" t="inlineStr">
@@ -11101,7 +16303,8 @@
       <c r="U14" s="300" t="n"/>
       <c r="V14" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W14" s="300" t="n"/>
@@ -11113,6 +16316,13 @@
       </c>
       <c r="Y14" s="320" t="n"/>
       <c r="Z14" s="300" t="n"/>
+      <c r="AH14" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V14</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="119" customHeight="1">
       <c r="A15" s="298" t="inlineStr">
@@ -11228,12 +16438,14 @@
       <c r="N17" s="300" t="n"/>
       <c r="O17" s="317" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P17" s="317" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q17" s="300" t="n"/>
@@ -11243,7 +16455,8 @@
       <c r="U17" s="300" t="n"/>
       <c r="V17" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W17" s="300" t="n"/>
@@ -11257,7 +16470,43 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V17</t>
+        </is>
+      </c>
+      <c r="AI17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P17</t>
+        </is>
+      </c>
+      <c r="AJ17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z17</t>
+        </is>
+      </c>
+      <c r="AK17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z17</t>
+        </is>
+      </c>
+      <c r="AL17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-11 - Monocomando bica baixa de mesa para lavatório Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para O17</t>
         </is>
       </c>
     </row>
@@ -11307,12 +16556,14 @@
       <c r="N18" s="300" t="n"/>
       <c r="O18" s="317" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P18" s="317" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q18" s="300" t="n"/>
@@ -11322,7 +16573,8 @@
       <c r="U18" s="300" t="n"/>
       <c r="V18" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W18" s="300" t="n"/>
@@ -11336,7 +16588,43 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V18</t>
+        </is>
+      </c>
+      <c r="AI18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P18</t>
+        </is>
+      </c>
+      <c r="AJ18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z18</t>
+        </is>
+      </c>
+      <c r="AK18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z18</t>
+        </is>
+      </c>
+      <c r="AL18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-11 - Monocomando bica baixa de mesa para lavatório Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para O18</t>
         </is>
       </c>
     </row>
@@ -11396,7 +16684,8 @@
       <c r="H20" s="317" t="inlineStr">
         <is>
           <t>PA43 - Parede emassada regularizada, revestida com fórmica cor Almond L112, acabamento mate. Ref.: Formica. Dimensões e paginações conforme detalhamento. Amostra a ser aprovada pela GPA&amp;A.
-PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.</t>
+PA52 - Parede rebocada regularizada, revestida em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.Obs.: Resina ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I20" s="317" t="inlineStr">
@@ -11412,14 +16701,16 @@
       <c r="K20" s="300" t="n"/>
       <c r="L20" s="317" t="inlineStr">
         <is>
-          <t>D80 - Cuba de embutir, Dora 70 em aço inox, 70x40cm, acabamento acetinado, cód.: BL R6. Ref.: Tramontina</t>
+          <t>D80 - Cuba de embutir, Dora 70 em aço inox, 70x40cm, acabamento acetinado, cód.: BL R6. Ref.: Tramontina
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M20" s="300" t="n"/>
       <c r="N20" s="300" t="n"/>
       <c r="O20" s="317" t="inlineStr">
         <is>
-          <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scotch Brite, cód.: 94520022. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D81 - Monocomando de mesa, modelo Angolare, acabamento Scotch Brite, cód.: 94520022. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P20" s="300" t="n"/>
@@ -11430,7 +16721,8 @@
       <c r="U20" s="300" t="n"/>
       <c r="V20" s="308" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W20" s="300" t="n"/>
@@ -11444,6 +16736,34 @@
       <c r="Z20" s="308" t="inlineStr">
         <is>
           <t>D82 - Prateleira em granito cinza Santa Rosa, acabamento escovado, embutido na alvenaria. Amostra a ser aprovada pela GPA&amp;A</t>
+        </is>
+      </c>
+      <c r="AH20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V20</t>
+        </is>
+      </c>
+      <c r="AI20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-12 - Almond (L112) - Formica (Formica)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para H20</t>
+        </is>
+      </c>
+      <c r="AJ20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-13 - Cuba de Embutir Dora 70 BL R6 em Aço Inox Acetinado Tramontina (94016102) (Tramontina)
+Imagem de referência da web
+◄ VOLTAR para L20</t>
+        </is>
+      </c>
+      <c r="AK20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-14 - Misturador Monocomando Angolare Inox com Acabamento Scotch Brite e Bica Articulada Tramontina (Tramontina)
+Imagem de referência da web
+◄ VOLTAR para O20</t>
         </is>
       </c>
     </row>
@@ -11481,14 +16801,16 @@
       <c r="K21" s="300" t="n"/>
       <c r="L21" s="317" t="inlineStr">
         <is>
-          <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.: TQ.01.17, Ref.: Deca</t>
+          <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.: TQ.01.17, Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M21" s="300" t="n"/>
       <c r="N21" s="300" t="n"/>
       <c r="O21" s="317" t="inlineStr">
         <is>
-          <t>D67 - Torneira de parede com arejador, para jardim e tanque, linha Izy, acabamento cromado. Cód.: 1154 C37; Ref.: Deca</t>
+          <t>D67 - Torneira de parede com arejador, para jardim e tanque, linha Izy, acabamento cromado. Cód.: 1154 C37; Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P21" s="300" t="n"/>
@@ -11502,6 +16824,20 @@
       <c r="X21" s="320" t="n"/>
       <c r="Y21" s="320" t="n"/>
       <c r="Z21" s="300" t="n"/>
+      <c r="AH21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-15 - Tanque de Louça 56x42cm 18 Litros TQ1/SC Branco - Ref. TQ.01.17 - DECA (Deca)
+Imagem de referência da web
+◄ VOLTAR para L21</t>
+        </is>
+      </c>
+      <c r="AI21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-16 - Torneira para Uso Geral com Arejador 1154 Izy C37 Cromado Deca (Deca)
+Imagem de referência da web
+◄ VOLTAR para O21</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="104" customHeight="1">
       <c r="A22" s="298" t="inlineStr">
@@ -11598,12 +16934,14 @@
       <c r="N23" s="300" t="n"/>
       <c r="O23" s="317" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P23" s="317" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q23" s="300" t="n"/>
@@ -11613,7 +16951,8 @@
       <c r="U23" s="300" t="n"/>
       <c r="V23" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W23" s="307" t="n"/>
@@ -11627,7 +16966,43 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH23" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V23</t>
+        </is>
+      </c>
+      <c r="AI23" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P23</t>
+        </is>
+      </c>
+      <c r="AJ23" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z23</t>
+        </is>
+      </c>
+      <c r="AK23" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z23</t>
+        </is>
+      </c>
+      <c r="AL23" s="323" t="inlineStr">
+        <is>
+          <t>WEB-11 - Monocomando bica baixa de mesa para lavatório Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para O23</t>
         </is>
       </c>
     </row>
@@ -11678,12 +17053,14 @@
       <c r="N24" s="308" t="n"/>
       <c r="O24" s="320" t="inlineStr">
         <is>
-          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.</t>
+          <t>D23 - Monocomando de mesa para lavatório, linha Mix&amp;Match, bica baixa, acabamento cromado, cód.: 90017398006. Ref.: Docol. Obs.: Se necessário instalar cardal para aquecimento de água. ATENÇÃO: vazão máxima de 6 l/min, instalar redutor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P24" s="320" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q24" s="300" t="n"/>
@@ -11693,7 +17070,8 @@
       <c r="U24" s="300" t="n"/>
       <c r="V24" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W24" s="307" t="n"/>
@@ -11707,7 +17085,43 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH24" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V24</t>
+        </is>
+      </c>
+      <c r="AI24" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P24</t>
+        </is>
+      </c>
+      <c r="AJ24" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z24</t>
+        </is>
+      </c>
+      <c r="AK24" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z24</t>
+        </is>
+      </c>
+      <c r="AL24" s="323" t="inlineStr">
+        <is>
+          <t>WEB-11 - Monocomando bica baixa de mesa para lavatório Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para O24</t>
         </is>
       </c>
     </row>
@@ -11794,7 +17208,8 @@
       <c r="U26" s="300" t="n"/>
       <c r="V26" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W26" s="307" t="n"/>
@@ -11809,6 +17224,13 @@
         <is>
           <t>D18 - Módulos compostos por três peças hexagonais com estruturado em peças de madeira maciça, fechamento em reguas de madeira 25mmx70mm. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D56 - Pendente sob medida em peças de madeira maciça 60x50mm fixados no teto através de cabos de aço e estrutura auxiliar no entreforro, com acabamento no forro em canopla, cor branca. Retroiluminação em fitas de led na parte superior com dimensionamentos conforme projeto luminotécnico. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+      <c r="AH26" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V26</t>
         </is>
       </c>
     </row>
@@ -11858,14 +17280,16 @@
       </c>
       <c r="L27" s="320" t="inlineStr">
         <is>
-          <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina</t>
+          <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M27" s="307" t="n"/>
       <c r="N27" s="307" t="n"/>
       <c r="O27" s="320" t="inlineStr">
         <is>
-          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.: REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
+          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.: REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P27" s="300" t="n"/>
@@ -11876,7 +17300,8 @@
       <c r="U27" s="300" t="n"/>
       <c r="V27" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W27" s="300" t="n"/>
@@ -11894,6 +17319,27 @@
 D15 - Armários em mdf cru com acabamento em folha madeira natural carvalho tonalizado. Puxadore integrado linha Sottile ref. ZEN - acabamento bronze 192mm. Consultar detalhamento.Amostra folha natural madeira com acabamenhto deverá ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D16 - Mesa em mdf cru com acabamento em folha madeira natural carvalho tonalizado. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D17 - Armários em ripas de madeira maciça tonalizada seguindo cor folha madeira - ripas de 20x20mm espaçadas 15mm. Portas de giro com puxador no trespasse. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+      <c r="AH27" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V27</t>
+        </is>
+      </c>
+      <c r="AI27" s="323" t="inlineStr">
+        <is>
+          <t>WEB-17 - Cuba Aço Inox Tramontina Quadrum 70cm Scotch Brite Design Collection (94000103) (Tramontina)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para L27</t>
+        </is>
+      </c>
+      <c r="AJ27" s="323" t="inlineStr">
+        <is>
+          <t>WEB-18 - Misturador Monocomando Monde Filter Aço Inox Saída Adicional Água Filtrada + Filtro 3M Tramontina (94520025) (Tramontina)
+Imagem de referência da web
+◄ VOLTAR para O27</t>
         </is>
       </c>
     </row>
@@ -11952,7 +17398,8 @@
       <c r="G29" s="300" t="n"/>
       <c r="H29" s="320" t="inlineStr">
         <is>
-          <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A</t>
+          <t>PA59 - Parede revestida em pastilha Jatobá, acabamento cinza cimento brilhante, 5x5cm. Cód.: CJC1614. Ref.: Ceramicasa. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I29" s="307" t="n"/>
@@ -11972,12 +17419,14 @@
       <c r="S29" s="300" t="n"/>
       <c r="T29" s="308" t="inlineStr">
         <is>
-          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
+          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U29" s="308" t="inlineStr">
         <is>
-          <t>D79 - Chuveiro de piso para área externa em aço inox 316. cód.: DK5123B. Ref.: Doka</t>
+          <t>D79 - Chuveiro de piso para área externa em aço inox 316. cód.: DK5123B. Ref.: Doka
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V29" s="320" t="n"/>
@@ -11991,6 +17440,27 @@
       <c r="Z29" s="307" t="inlineStr">
         <is>
           <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
+        </is>
+      </c>
+      <c r="AH29" s="323" t="inlineStr">
+        <is>
+          <t>WEB-19 - Pastilha Jatobá Design 5X5 JC1614 Cinza Cimento Brilhante 30,3X30,3 (Ceramicasa)
+Imagem de referência da web
+◄ VOLTAR para H29</t>
+        </is>
+      </c>
+      <c r="AI29" s="323" t="inlineStr">
+        <is>
+          <t>WEB-20 - Ralo Linear Elleve Versatile Tampa Oculta 75cm - 4257 (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T29</t>
+        </is>
+      </c>
+      <c r="AJ29" s="323" t="inlineStr">
+        <is>
+          <t>WEB-21 - Chuveiro Área Externa Doka Brushed (Aço Inox 316) DK5123B (Doka)
+Imagem de referência da web
+◄ VOLTAR para U29</t>
         </is>
       </c>
     </row>
@@ -12102,14 +17572,16 @@
       <c r="K32" s="300" t="n"/>
       <c r="L32" s="308" t="inlineStr">
         <is>
-          <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina</t>
+          <t>D10 - Cuba Design Collection Quadrum 70 em Aço Inox com Acabamento Scotch Brite. Cód Ref.: REF 94007103. Ref.: Tramontina
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M32" s="300" t="n"/>
       <c r="N32" s="300" t="n"/>
       <c r="O32" s="308" t="inlineStr">
         <is>
-          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.: REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário</t>
+          <t>D9 - Misturador Monocomando Monde Filter Plus em Aço Inox com Saída Adicional para Água Filtrada + Filtro 3M. Cód Ref.: REF 94520025. Ref.: Tramontina. ATENÇÃO: vazão máxima de 9 l/min, instalar redutor de vazão se necessário
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P32" s="300" t="n"/>
@@ -12119,13 +17591,15 @@
       <c r="T32" s="308" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
-D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U32" s="300" t="n"/>
       <c r="V32" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W32" s="307" t="n"/>
@@ -12137,6 +17611,41 @@
 D48 - Estante suspensa em tubo retangular 25x25mm em aço inox com pintura ouro velho. Fixada no teto através de estrutura auxiliar. Apresentar amostra pintura e solda para aprovação GPA&amp;A.
 D49 - Armários com interior em MDF madeirado e portas de giro ripadas - ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria - prever fechamento face interna porta em vidro liso incolor 4mm. Prateleiras em MDF madeirado com iluminação em LED. Dimensões e desenho conforme detalhamento.Amostra a ser aprovada pela GPA&amp;A. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR
 D50 - Armário sob bancada com portas de giro ripadas para ventilação choppeira. Ripas de 20x20mm espaçadas 15mm - puxador executado na marcenaria. ATENÇÃO: o MDF e a lâmina natural devem possuir certificação FSC ou CERFLOR</t>
+        </is>
+      </c>
+      <c r="AH32" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V32</t>
+        </is>
+      </c>
+      <c r="AI32" s="323" t="inlineStr">
+        <is>
+          <t>WEB-05 - Ralo Square Tampa Lisa Inox 15x15cm Elleve (Elleve)
+Imagem de referência da web
+◄ VOLTAR para T32</t>
+        </is>
+      </c>
+      <c r="AJ32" s="323" t="inlineStr">
+        <is>
+          <t>WEB-17 - Cuba Aço Inox Tramontina Quadrum 70cm Scotch Brite Design Collection (94000103) (Tramontina)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para L32</t>
+        </is>
+      </c>
+      <c r="AK32" s="323" t="inlineStr">
+        <is>
+          <t>WEB-18 - Misturador Monocomando Monde Filter Aço Inox Saída Adicional Água Filtrada + Filtro 3M Tramontina (94520025) (Tramontina)
+Imagem de referência da web
+◄ VOLTAR para O32</t>
+        </is>
+      </c>
+      <c r="AL32" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T32</t>
         </is>
       </c>
     </row>
@@ -12216,13 +17725,21 @@
       <c r="U34" s="300" t="n"/>
       <c r="V34" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W34" s="307" t="n"/>
       <c r="X34" s="307" t="n"/>
       <c r="Y34" s="307" t="n"/>
       <c r="Z34" s="300" t="n"/>
+      <c r="AH34" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V34</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="224" customHeight="1">
       <c r="A35" s="298" t="inlineStr">
@@ -12273,35 +17790,41 @@
       <c r="O35" s="321" t="inlineStr">
         <is>
           <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P35" s="320" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q35" s="300" t="n"/>
       <c r="R35" s="307" t="n"/>
       <c r="S35" s="320" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="T35" s="320" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
-D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U35" s="317" t="inlineStr">
         <is>
-          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V35" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W35" s="307" t="n"/>
@@ -12315,7 +17838,71 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V35</t>
+        </is>
+      </c>
+      <c r="AI35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P35</t>
+        </is>
+      </c>
+      <c r="AJ35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-05 - Ralo Square Tampa Lisa Inox 15x15cm Elleve (Elleve)
+Imagem de referência da web
+◄ VOLTAR para T35</t>
+        </is>
+      </c>
+      <c r="AK35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z35</t>
+        </is>
+      </c>
+      <c r="AL35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z35</t>
+        </is>
+      </c>
+      <c r="AM35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T35</t>
+        </is>
+      </c>
+      <c r="AN35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-23 - Torneira Com Sensor Mesa Redonda Decalux Nova - 1188CN (Deca)
+Imagem de referência da web
+◄ VOLTAR para O35</t>
+        </is>
+      </c>
+      <c r="AO35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-24 - Acabamento monocomando para chuveiro e ducha higienica 1/2" Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para S35</t>
+        </is>
+      </c>
+      <c r="AP35" s="323" t="inlineStr">
+        <is>
+          <t>WEB-25 - Chuveiro R200 de parede DocolEden cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para U35</t>
         </is>
       </c>
     </row>
@@ -12368,35 +17955,41 @@
       <c r="O36" s="321" t="inlineStr">
         <is>
           <t>D29 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol</t>
+CONFLITO – Pranchas 37 e 38 do detalhamento R04: torneira de mesa bica baixa Argon, Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P36" s="320" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q36" s="300" t="n"/>
       <c r="R36" s="307" t="n"/>
       <c r="S36" s="320" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="T36" s="320" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
-D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U36" s="317" t="inlineStr">
         <is>
-          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D31 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V36" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W36" s="307" t="n"/>
@@ -12410,7 +18003,71 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V36</t>
+        </is>
+      </c>
+      <c r="AI36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P36</t>
+        </is>
+      </c>
+      <c r="AJ36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-05 - Ralo Square Tampa Lisa Inox 15x15cm Elleve (Elleve)
+Imagem de referência da web
+◄ VOLTAR para T36</t>
+        </is>
+      </c>
+      <c r="AK36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z36</t>
+        </is>
+      </c>
+      <c r="AL36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z36</t>
+        </is>
+      </c>
+      <c r="AM36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T36</t>
+        </is>
+      </c>
+      <c r="AN36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-23 - Torneira Com Sensor Mesa Redonda Decalux Nova - 1188CN (Deca)
+Imagem de referência da web
+◄ VOLTAR para O36</t>
+        </is>
+      </c>
+      <c r="AO36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-24 - Acabamento monocomando para chuveiro e ducha higienica 1/2" Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para S36</t>
+        </is>
+      </c>
+      <c r="AP36" s="323" t="inlineStr">
+        <is>
+          <t>WEB-25 - Chuveiro R200 de parede DocolEden cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para U36</t>
         </is>
       </c>
     </row>
@@ -12464,7 +18121,8 @@
       <c r="U37" s="300" t="n"/>
       <c r="V37" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W37" s="307" t="n"/>
@@ -12481,6 +18139,13 @@
 D5 - Painel estruturado com moldura, para encaixe de equipamento, desenho conforme detalhamento, acabamento em MDF Nero Rust. Ref.: Berneck. Obs.: MDF possui certificação FSC.
 D6 - Anéis metálicos acabamento em micropintura perolizada, cor L098, Ref.: Sherwin Williams, fixados em pilar de concreto através de espassadores metálicos. Ver detalhamento. Apresentar protótipo e amostra pintura para aprovação GPA&amp;A.
 D7 - Mesa de apoio metálica em micropintura perolizada, cor L098, Ref.: Sherwin Williams, fixados em pilar de concreto através de estrutura auxiliar. Ver detalhamento. Apresentar protótipo e amostra pintura para aprovação GPA&amp;A.</t>
+        </is>
+      </c>
+      <c r="AH37" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V37</t>
         </is>
       </c>
     </row>
@@ -12645,13 +18310,15 @@
       <c r="Q41" s="300" t="n"/>
       <c r="R41" s="307" t="inlineStr">
         <is>
-          <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
+          <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S41" s="307" t="n"/>
       <c r="T41" s="307" t="inlineStr">
         <is>
-          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U41" s="317" t="inlineStr">
@@ -12662,7 +18329,8 @@
       </c>
       <c r="V41" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W41" s="307" t="n"/>
@@ -12691,8 +18359,29 @@
 ◄ VOLTAR para U41</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="89" customHeight="1">
+      <c r="AK41" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V41</t>
+        </is>
+      </c>
+      <c r="AL41" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T41</t>
+        </is>
+      </c>
+      <c r="AM41" s="323" t="inlineStr">
+        <is>
+          <t>WEB-26 - Acabamento para registro DocolBase 3/4" Mix&amp;Match cromado (00926406 / 90009264006) (Docol)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para R41</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
       <c r="A42" s="298" t="inlineStr">
         <is>
           <t>SAUNA VAPOR</t>
@@ -12728,18 +18417,21 @@
       <c r="Q42" s="300" t="n"/>
       <c r="R42" s="307" t="inlineStr">
         <is>
-          <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol</t>
+          <t>D58 - Acabamento para registro DocolBase, linha Mix&amp;Match, acabamento cromado. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S42" s="307" t="n"/>
       <c r="T42" s="307" t="inlineStr">
         <is>
-          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U42" s="308" t="inlineStr">
         <is>
-          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D54 - Chuveiro de embutir no teto Raindream, Roca, acabamento cromado, cód.: A5B3250C0C. Ref.: Roca. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V42" s="320" t="n"/>
@@ -12747,6 +18439,27 @@
       <c r="X42" s="307" t="n"/>
       <c r="Y42" s="307" t="n"/>
       <c r="Z42" s="300" t="n"/>
+      <c r="AH42" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T42</t>
+        </is>
+      </c>
+      <c r="AI42" s="323" t="inlineStr">
+        <is>
+          <t>WEB-26 - Acabamento para registro DocolBase 3/4" Mix&amp;Match cromado (00926406 / 90009264006) (Docol)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para R42</t>
+        </is>
+      </c>
+      <c r="AJ42" s="323" t="inlineStr">
+        <is>
+          <t>WEB-27 - Chuveiro quadrado 350x350 Raindream de teto / braco nao incluso (Roca)
+Imagem de referência da web
+◄ VOLTAR para U42</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="104" customHeight="1">
       <c r="A43" s="298" t="inlineStr">
@@ -12867,7 +18580,8 @@
       <c r="L45" s="320" t="inlineStr">
         <is>
           <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
-D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M45" s="308" t="n"/>
@@ -12875,7 +18589,8 @@
       <c r="O45" s="320" t="inlineStr">
         <is>
           <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P45" s="320" t="n"/>
@@ -12886,7 +18601,8 @@
       <c r="U45" s="300" t="n"/>
       <c r="V45" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W45" s="307" t="n"/>
@@ -12897,6 +18613,27 @@
       </c>
       <c r="Y45" s="307" t="n"/>
       <c r="Z45" s="300" t="n"/>
+      <c r="AH45" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V45</t>
+        </is>
+      </c>
+      <c r="AI45" s="323" t="inlineStr">
+        <is>
+          <t>WEB-28 - Cuba Ametista 26 de Apoio 53x36x26 (Sabbia)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para L45</t>
+        </is>
+      </c>
+      <c r="AJ45" s="323" t="inlineStr">
+        <is>
+          <t>WEB-29 - Torneira Presence de mesa para cozinha Mix&amp;Match grafite escovado (Docol)
+Imagem de referência da web
+◄ VOLTAR para O45</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="344" customHeight="1">
       <c r="A46" s="298" t="inlineStr">
@@ -12941,7 +18678,8 @@
       <c r="L46" s="307" t="inlineStr">
         <is>
           <t>D55 - Cuba de apoio, modelo Ametista 26, cor branco, cód.:121003002. Ref.: Sabbia
-D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.</t>
+D62 - Cuba esculpida em mármore branco selecionado, lote a ser aprovado. Interior da cuba e bandeja removível em mármore liso. Fechamento lateral em mármore frisado e fechamento frontal em placa de mármore frisado fixado com imã em estrutura auxiliar de metalon. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M46" s="308" t="n"/>
@@ -12949,7 +18687,8 @@
       <c r="O46" s="320" t="inlineStr">
         <is>
           <t>D51 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
-D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.</t>
+D53 - Torneira de mesa, linha Mix&amp;Match Presence, com sensor, acabamento grafite escovado. Cód.: 90015460070 Ref.: Docol ATENÇÃO: vazão máxima de 6 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P46" s="320" t="n"/>
@@ -12960,7 +18699,8 @@
       <c r="U46" s="300" t="n"/>
       <c r="V46" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W46" s="307" t="n"/>
@@ -12971,6 +18711,27 @@
       </c>
       <c r="Y46" s="307" t="n"/>
       <c r="Z46" s="300" t="n"/>
+      <c r="AH46" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V46</t>
+        </is>
+      </c>
+      <c r="AI46" s="323" t="inlineStr">
+        <is>
+          <t>WEB-28 - Cuba Ametista 26 de Apoio 53x36x26 (Sabbia)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para L46</t>
+        </is>
+      </c>
+      <c r="AJ46" s="323" t="inlineStr">
+        <is>
+          <t>WEB-29 - Torneira Presence de mesa para cozinha Mix&amp;Match grafite escovado (Docol)
+Imagem de referência da web
+◄ VOLTAR para O46</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="149" customHeight="1">
       <c r="A47" s="298" t="inlineStr">
@@ -13026,7 +18787,7 @@
       <c r="Y47" s="307" t="n"/>
       <c r="Z47" s="300" t="n"/>
     </row>
-    <row r="48" ht="134" customHeight="1">
+    <row r="48" ht="164" customHeight="1">
       <c r="A48" s="298" t="inlineStr">
         <is>
           <t>VEST. P.C.D</t>
@@ -13069,45 +18830,53 @@
       </c>
       <c r="L48" s="307" t="inlineStr">
         <is>
-          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
+          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M48" s="308" t="n"/>
       <c r="N48" s="308" t="n"/>
       <c r="O48" s="307" t="inlineStr">
         <is>
-          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
+          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P48" s="307" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q48" s="308" t="inlineStr">
         <is>
-          <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
+          <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="R48" s="307" t="n"/>
       <c r="S48" s="307" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="T48" s="307" t="inlineStr">
         <is>
-          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U48" s="308" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V48" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W48" s="307" t="n"/>
@@ -13117,11 +18886,82 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="134" customHeight="1">
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V48</t>
+        </is>
+      </c>
+      <c r="AI48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P48</t>
+        </is>
+      </c>
+      <c r="AJ48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z48</t>
+        </is>
+      </c>
+      <c r="AK48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z48</t>
+        </is>
+      </c>
+      <c r="AL48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T48</t>
+        </is>
+      </c>
+      <c r="AM48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-23 - Torneira Com Sensor Mesa Redonda Decalux Nova - 1188CN (Deca)
+Imagem de referência da web
+◄ VOLTAR para O48</t>
+        </is>
+      </c>
+      <c r="AN48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-24 - Acabamento monocomando para chuveiro e ducha higienica 1/2" Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para S48</t>
+        </is>
+      </c>
+      <c r="AO48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-25 - Chuveiro R200 de parede DocolEden cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para U48</t>
+        </is>
+      </c>
+      <c r="AP48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-30 - Cuba Semiencaixe Com Mesa Deca Slim 40cm Branco L.61040.M.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para L48</t>
+        </is>
+      </c>
+      <c r="AQ48" s="323" t="inlineStr">
+        <is>
+          <t>WEB-31 - Ducha higienica com registro e derivacao Mix&amp;Match cromado (00931606) (Docol)
+Imagem de referência da web
+◄ VOLTAR para Q48</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="164" customHeight="1">
       <c r="A49" s="298" t="inlineStr">
         <is>
           <t>VEST. P.C.D</t>
@@ -13164,45 +19004,53 @@
       </c>
       <c r="L49" s="307" t="inlineStr">
         <is>
-          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca</t>
+          <t>D72 - Cuba de semiencaixe, linha Slim, cor branco, cód.: L.61040.M.17. Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M49" s="308" t="n"/>
       <c r="N49" s="308" t="n"/>
       <c r="O49" s="307" t="inlineStr">
         <is>
-          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca</t>
+          <t>D69 - Torneira de mesa com sensor bivolt e bateria, linha Decalux, acabamento cromado, cód.: 1188.C.N. Ref.: Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P49" s="307" t="inlineStr">
         <is>
-          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.</t>
+          <t>D22 - Bacia Sanitária com caixa acoplada, linha Carrara, acabamento branco, cód.: P.606.17. Ref.: Deca OU Bacia Sanitária com caixa acoplada, linha Panache, acabamento branco, cód.: K-18395BR-0.Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q49" s="308" t="inlineStr">
         <is>
-          <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol</t>
+          <t>D84 - Ducha higiênica com registro e derivação de parede linha Mix&amp;Match, acabamento cromado. Cód.: 90009316006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="R49" s="307" t="n"/>
       <c r="S49" s="307" t="inlineStr">
         <is>
-          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol</t>
+          <t>D33 - Monocomando para chuveiro, linha Mix&amp;Match, acabamento cromado, cód.:90009312006. Ref.: Docol
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="T49" s="307" t="inlineStr">
         <is>
-          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+          <t>D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U49" s="308" t="inlineStr">
         <is>
-          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.</t>
+          <t>D70 - Chuveiro 200 de parede, com tubo reto, linha DocolEden, acabamento cromado, cód.:90008879006. Ref.: Docol. ATENÇÃO: vazão máxima de 8 l/min, instalar restritor de vazão se necessário.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="V49" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W49" s="307" t="n"/>
@@ -13212,11 +19060,82 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="119" customHeight="1">
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
+        </is>
+      </c>
+      <c r="AH49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V49</t>
+        </is>
+      </c>
+      <c r="AI49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P49</t>
+        </is>
+      </c>
+      <c r="AJ49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z49</t>
+        </is>
+      </c>
+      <c r="AK49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z49</t>
+        </is>
+      </c>
+      <c r="AL49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T49</t>
+        </is>
+      </c>
+      <c r="AM49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-23 - Torneira Com Sensor Mesa Redonda Decalux Nova - 1188CN (Deca)
+Imagem de referência da web
+◄ VOLTAR para O49</t>
+        </is>
+      </c>
+      <c r="AN49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-24 - Acabamento monocomando para chuveiro e ducha higienica 1/2" Mix&amp;Match cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para S49</t>
+        </is>
+      </c>
+      <c r="AO49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-25 - Chuveiro R200 de parede DocolEden cromado (Docol)
+Imagem de referência da web
+◄ VOLTAR para U49</t>
+        </is>
+      </c>
+      <c r="AP49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-30 - Cuba Semiencaixe Com Mesa Deca Slim 40cm Branco L.61040.M.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para L49</t>
+        </is>
+      </c>
+      <c r="AQ49" s="323" t="inlineStr">
+        <is>
+          <t>WEB-31 - Ducha higienica com registro e derivacao Mix&amp;Match cromado (00931606) (Docol)
+Imagem de referência da web
+◄ VOLTAR para Q49</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="120" customHeight="1">
       <c r="A50" s="298" t="inlineStr">
         <is>
           <t>DML</t>
@@ -13250,14 +19169,16 @@
       <c r="K50" s="300" t="n"/>
       <c r="L50" s="320" t="inlineStr">
         <is>
-          <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.TQ.01.17.; Ref.: Deca.</t>
+          <t>D68 - Tanque em cerâmica 18L cor branco fosco. Cód.TQ.01.17.; Ref.: Deca.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M50" s="308" t="n"/>
       <c r="N50" s="308" t="n"/>
       <c r="O50" s="320" t="inlineStr">
         <is>
-          <t>D67 - Torneira de parede com arejador, para Jardim e Tanque, linha Izy, acabamento cromado. Cód. 1154.C37; Ref.: Deca.</t>
+          <t>D67 - Torneira de parede com arejador, para Jardim e Tanque, linha Izy, acabamento cromado. Cód. 1154.C37; Ref.: Deca.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P50" s="320" t="n"/>
@@ -13271,6 +19192,20 @@
       <c r="X50" s="307" t="n"/>
       <c r="Y50" s="307" t="n"/>
       <c r="Z50" s="300" t="n"/>
+      <c r="AH50" s="323" t="inlineStr">
+        <is>
+          <t>WEB-15 - Tanque de Louça 56x42cm 18 Litros TQ1/SC Branco - Ref. TQ.01.17 - DECA (Deca)
+Imagem de referência da web
+◄ VOLTAR para L50</t>
+        </is>
+      </c>
+      <c r="AI50" s="323" t="inlineStr">
+        <is>
+          <t>WEB-16 - Torneira para Uso Geral com Arejador 1154 Izy C37 Cromado Deca (Deca)
+Imagem de referência da web
+◄ VOLTAR para O50</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="298" t="inlineStr">
@@ -13350,7 +19285,7 @@
       <c r="Y52" s="307" t="n"/>
       <c r="Z52" s="300" t="n"/>
     </row>
-    <row r="53" ht="164" customHeight="1">
+    <row r="53" ht="194" customHeight="1">
       <c r="A53" s="298" t="inlineStr">
         <is>
           <t>DEP JARDIM</t>
@@ -13359,7 +19294,8 @@
       <c r="B53" s="320" t="inlineStr">
         <is>
           <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
-ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C53" s="300" t="n"/>
@@ -13368,7 +19304,8 @@
       <c r="F53" s="317" t="inlineStr">
         <is>
           <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
-ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G53" s="300" t="n"/>
@@ -13376,7 +19313,8 @@
         <is>
           <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali off white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
-ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I53" s="320" t="inlineStr">
@@ -13397,14 +19335,16 @@
       </c>
       <c r="L53" s="320" t="inlineStr">
         <is>
-          <t>26 - Tanque de embutir CT-50, Mekal, escovado cód.: 90010195016</t>
+          <t>26 - Tanque de embutir CT-50, Mekal, escovado cód.: 90010195016
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M53" s="308" t="n"/>
       <c r="N53" s="308" t="n"/>
       <c r="O53" s="320" t="inlineStr">
         <is>
-          <t>27 - Torneira de parede com arejador, para jardim e tanque, cromado. Ref.: cód.:1154.C37; linha Izy; Deca</t>
+          <t>27 - Torneira de parede com arejador, para jardim e tanque, cromado. Ref.: cód.:1154.C37; linha Izy; Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P53" s="320" t="n"/>
@@ -13418,8 +19358,29 @@
       <c r="X53" s="307" t="n"/>
       <c r="Y53" s="307" t="n"/>
       <c r="Z53" s="300" t="n"/>
-    </row>
-    <row r="54" ht="164" customHeight="1">
+      <c r="AH53" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B53, F53, H53</t>
+        </is>
+      </c>
+      <c r="AI53" s="323" t="inlineStr">
+        <is>
+          <t>WEB-16 - Torneira para Uso Geral com Arejador 1154 Izy C37 Cromado Deca (Deca)
+Imagem de referência da web
+◄ VOLTAR para O53</t>
+        </is>
+      </c>
+      <c r="AJ53" s="323" t="inlineStr">
+        <is>
+          <t>WEB-32 - Tanque de Embutir ou Sobrepor Lavanderia Mekal CT-50 50x40x23cm Inox Escovado (Mekal)
+Imagem de referência da web
+◄ VOLTAR para L53</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="194" customHeight="1">
       <c r="A54" s="298" t="inlineStr">
         <is>
           <t>DEPÓSITO</t>
@@ -13428,7 +19389,8 @@
       <c r="B54" s="320" t="inlineStr">
         <is>
           <t>05 - Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
-ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+ARQ-P05 - Piso em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C54" s="300" t="n"/>
@@ -13437,7 +19399,8 @@
       <c r="F54" s="317" t="inlineStr">
         <is>
           <t>19 - Rodapé para Piso Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, ref.: Khali off white AC linha Khali; Eliane, assentado com argamassa colante em pó ACIII
-ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.</t>
+ARQ-RD19 - Rodapé em porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado. Paginação e altura conforme detalhamento. Ref.: Khali Off White AC; Linha Khali; Eliane. Amostra a ser aprovada pela GPA&amp;A.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G54" s="300" t="n"/>
@@ -13445,7 +19408,8 @@
         <is>
           <t>12 - Revestimento Porcelanato off white 60x60cm, espessura 1cm, com acabamento acetinado, Ref.: Khali off white AC, linha Khali; Eliane, assentado com argamassa colante em pó ACIII
 01| 21 - Pintura acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil, sobre paredes - Reboco (1 demão selador + 3 demãos Latex acrílico)
-ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.</t>
+ARQ-PA01 - Parede em alvenaria, emassada e regularizada, pintada com tinta acrílica, cor branco neve, acabamento acetinado. Ref.: Suvinil.
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I54" s="320" t="inlineStr">
@@ -13466,14 +19430,16 @@
       </c>
       <c r="L54" s="320" t="inlineStr">
         <is>
-          <t>26 - Tanque de embutir CT-50, Mekal, escovado cód.: 90010195016</t>
+          <t>26 - Tanque de embutir CT-50, Mekal, escovado cód.: 90010195016
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M54" s="308" t="n"/>
       <c r="N54" s="308" t="n"/>
       <c r="O54" s="320" t="inlineStr">
         <is>
-          <t>27 - Torneira de parede com arejador, para jardim e tanque, cromado. Ref.: cód.:1154.C37; linha Izy; Deca</t>
+          <t>27 - Torneira de parede com arejador, para jardim e tanque, cromado. Ref.: cód.:1154.C37; linha Izy; Deca
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P54" s="320" t="n"/>
@@ -13487,6 +19453,27 @@
       <c r="X54" s="307" t="n"/>
       <c r="Y54" s="307" t="n"/>
       <c r="Z54" s="300" t="n"/>
+      <c r="AH54" s="323" t="inlineStr">
+        <is>
+          <t>WEB-02 - Porcelanato Khali Off White Acetinado 60x60 - Eliane (Eliane)
+Imagem de referência da web
+◄ VOLTAR para B54, F54, H54</t>
+        </is>
+      </c>
+      <c r="AI54" s="323" t="inlineStr">
+        <is>
+          <t>WEB-16 - Torneira para Uso Geral com Arejador 1154 Izy C37 Cromado Deca (Deca)
+Imagem de referência da web
+◄ VOLTAR para O54</t>
+        </is>
+      </c>
+      <c r="AJ54" s="323" t="inlineStr">
+        <is>
+          <t>WEB-32 - Tanque de Embutir ou Sobrepor Lavanderia Mekal CT-50 50x40x23cm Inox Escovado (Mekal)
+Imagem de referência da web
+◄ VOLTAR para L54</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="224" customHeight="1">
       <c r="A55" s="298" t="inlineStr">
@@ -13565,7 +19552,8 @@
       <c r="T55" s="307" t="inlineStr">
         <is>
           <t>D34 - Ralo 15x15cm com tampa lisa em aço inox, linha Square. Ref.: Elleve
-D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve</t>
+D35 - Ralo linear com tampa lisa em aço inox. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U55" s="317" t="inlineStr">
@@ -13576,7 +19564,8 @@
       </c>
       <c r="V55" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W55" s="307" t="n"/>
@@ -13591,7 +19580,8 @@
         <is>
           <t>D27 - Porta papel higiênico duplo em aço inox, modelo Cai Cai, cód.:70.100. Ref.: Draco
 D26 - Saboneteira de pressão em aço inox, instalação na parede, modelo Prime Press Espuma, cód.:70.032. Ref.: Draco
-D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco</t>
+D28 - Papeleira em aço Inox para papel interfolhado, modelo Basic, cód.:74.103. Ref.: Draco
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="AH55" s="323" t="inlineStr">
@@ -13646,6 +19636,41 @@
         <is>
           <t>D70 - Chuveiro 200 de parede Docol Eden
 ◄ VOLTAR para U55</t>
+        </is>
+      </c>
+      <c r="AQ55" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V55</t>
+        </is>
+      </c>
+      <c r="AR55" s="323" t="inlineStr">
+        <is>
+          <t>WEB-05 - Ralo Square Tampa Lisa Inox 15x15cm Elleve (Elleve)
+Imagem de referência da web
+◄ VOLTAR para T55</t>
+        </is>
+      </c>
+      <c r="AS55" s="323" t="inlineStr">
+        <is>
+          <t>WEB-06 - Saboneteira Espuma Pressão Parede PRIME PRESS 70.032 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z55</t>
+        </is>
+      </c>
+      <c r="AT55" s="323" t="inlineStr">
+        <is>
+          <t>WEB-07 - Papeleira Inox Papel Interfolhado BASIC 74.103 (Draco)
+Imagem de referência da web
+◄ VOLTAR para Z55</t>
+        </is>
+      </c>
+      <c r="AU55" s="323" t="inlineStr">
+        <is>
+          <t>WEB-22 - Ralo Linear Smart Tampa Inox Sifonado 60cm Elleve (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T55</t>
         </is>
       </c>
     </row>
@@ -13797,13 +19822,21 @@
       <c r="U58" s="300" t="n"/>
       <c r="V58" s="307" t="inlineStr">
         <is>
-          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand</t>
+          <t>D12 - Acabamento de tomadas e interruptores, linha Arteor, cor a definir conforme superfície a ser instalado. Ref.: Legrand
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W58" s="307" t="n"/>
       <c r="X58" s="307" t="n"/>
       <c r="Y58" s="307" t="n"/>
       <c r="Z58" s="300" t="n"/>
+      <c r="AH58" s="323" t="inlineStr">
+        <is>
+          <t>WEB-01 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V58</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="239" customHeight="1">
       <c r="A59" s="298" t="inlineStr">
@@ -13836,7 +19869,8 @@
       <c r="S59" s="307" t="n"/>
       <c r="T59" s="320" t="inlineStr">
         <is>
-          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve</t>
+          <t>D78 - Ralo linear oculto para encaixe de granito. Dimensões conforme detalhamento. Ref.: Elleve
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="U59" s="300" t="n"/>
@@ -13847,6 +19881,13 @@
       <c r="Z59" s="308" t="inlineStr">
         <is>
           <t>D76 - Guarda corpo em vidro temperado laminado liso incolor embutido no piso com ancoragem mínima de 70mm através de perfil fixador em aço inox e espaçamento entre vidros de 30mm.</t>
+        </is>
+      </c>
+      <c r="AH59" s="323" t="inlineStr">
+        <is>
+          <t>WEB-20 - Ralo Linear Elleve Versatile Tampa Oculta 75cm - 4257 (Elleve)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para T59</t>
         </is>
       </c>
     </row>
@@ -13969,7 +20010,7 @@
       <c r="Y62" s="307" t="n"/>
       <c r="Z62" s="300" t="n"/>
     </row>
-    <row r="63" ht="209" customHeight="1">
+    <row r="63" ht="239" customHeight="1">
       <c r="A63" s="298" t="inlineStr">
         <is>
           <t>APOIO QUADRAS</t>
@@ -13978,7 +20019,8 @@
       <c r="B63" s="320" t="inlineStr">
         <is>
           <t>P7 - Piso assentado em granito cinza Santa Rosa, acabamento escovado, Espessura: 2cm. Dimensões e paginação conforme detalhamento. Rejunte em massa plástica a ser tonalizada de acordo com a cor da pedra. Amostra a ser aprovada pela GPA&amp;A. Obs.: Resina, hidrofugante ou outros acabamentos aplicados no granito devem ser foscos e não podem alterar ou escurecer a cor original do material.
-P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR</t>
+P27 - Piso em deck de madeira, modelo Tauari Teak encaixe macho e femea, acabamento com cavilha, reguas 20mmx100mmx2000m-acima. Ref.: Indusparquet. ATENÇÃO: a madeira deve possuir certificação FSC ou CERFLOR
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C63" s="300" t="n"/>
@@ -14010,6 +20052,13 @@
       <c r="X63" s="307" t="n"/>
       <c r="Y63" s="307" t="n"/>
       <c r="Z63" s="300" t="n"/>
+      <c r="AH63" s="323" t="inlineStr">
+        <is>
+          <t>WEB-33 - Tauari Teak Assoalho (Piso Pronto) (Indusparquet)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para B63</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="298" t="inlineStr">
@@ -14091,21 +20140,217 @@
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B41" location="'PILOTIS'!AH41" tooltip="Ver imagem: P10 - Piso elevado em mármore branco selecionado"/>
-    <hyperlink ref="H41" location="'PILOTIS'!AI41" tooltip="Ver imagem: PA49 - Mosaico Bisazza (painel e pilar)"/>
-    <hyperlink ref="U41" location="'PILOTIS'!AJ41" tooltip="Ver imagem: D54 - Chuveiro de embutir no teto Raindream, Roca"/>
+    <hyperlink ref="V13" location="'PILOTIS'!AH13" tooltip="Ver imagem"/>
+    <hyperlink ref="AH13" location="'PILOTIS'!V13" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V14" location="'PILOTIS'!AH14" tooltip="Ver imagem"/>
+    <hyperlink ref="AH14" location="'PILOTIS'!V14" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O17" location="'PILOTIS'!AL17" tooltip="Ver imagem"/>
+    <hyperlink ref="P17" location="'PILOTIS'!AI17" tooltip="Ver imagem"/>
+    <hyperlink ref="V17" location="'PILOTIS'!AH17" tooltip="Ver imagem"/>
+    <hyperlink ref="Z17" location="'PILOTIS'!AJ17" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH17" location="'PILOTIS'!V17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI17" location="'PILOTIS'!P17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ17" location="'PILOTIS'!Z17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK17" location="'PILOTIS'!Z17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL17" location="'PILOTIS'!O17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O18" location="'PILOTIS'!AL18" tooltip="Ver imagem"/>
+    <hyperlink ref="P18" location="'PILOTIS'!AI18" tooltip="Ver imagem"/>
+    <hyperlink ref="V18" location="'PILOTIS'!AH18" tooltip="Ver imagem"/>
+    <hyperlink ref="Z18" location="'PILOTIS'!AJ18" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH18" location="'PILOTIS'!V18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI18" location="'PILOTIS'!P18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ18" location="'PILOTIS'!Z18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK18" location="'PILOTIS'!Z18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL18" location="'PILOTIS'!O18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="H20" location="'PILOTIS'!AI20" tooltip="Ver imagem"/>
+    <hyperlink ref="L20" location="'PILOTIS'!AJ20" tooltip="Ver imagem"/>
+    <hyperlink ref="O20" location="'PILOTIS'!AK20" tooltip="Ver imagem"/>
+    <hyperlink ref="V20" location="'PILOTIS'!AH20" tooltip="Ver imagem"/>
+    <hyperlink ref="AH20" location="'PILOTIS'!V20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI20" location="'PILOTIS'!H20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ20" location="'PILOTIS'!L20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK20" location="'PILOTIS'!O20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L21" location="'PILOTIS'!AH21" tooltip="Ver imagem"/>
+    <hyperlink ref="O21" location="'PILOTIS'!AI21" tooltip="Ver imagem"/>
+    <hyperlink ref="AH21" location="'PILOTIS'!L21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI21" location="'PILOTIS'!O21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O23" location="'PILOTIS'!AL23" tooltip="Ver imagem"/>
+    <hyperlink ref="P23" location="'PILOTIS'!AI23" tooltip="Ver imagem"/>
+    <hyperlink ref="V23" location="'PILOTIS'!AH23" tooltip="Ver imagem"/>
+    <hyperlink ref="Z23" location="'PILOTIS'!AJ23" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH23" location="'PILOTIS'!V23" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI23" location="'PILOTIS'!P23" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ23" location="'PILOTIS'!Z23" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK23" location="'PILOTIS'!Z23" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL23" location="'PILOTIS'!O23" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O24" location="'PILOTIS'!AL24" tooltip="Ver imagem"/>
+    <hyperlink ref="P24" location="'PILOTIS'!AI24" tooltip="Ver imagem"/>
+    <hyperlink ref="V24" location="'PILOTIS'!AH24" tooltip="Ver imagem"/>
+    <hyperlink ref="Z24" location="'PILOTIS'!AJ24" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH24" location="'PILOTIS'!V24" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI24" location="'PILOTIS'!P24" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ24" location="'PILOTIS'!Z24" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK24" location="'PILOTIS'!Z24" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL24" location="'PILOTIS'!O24" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V26" location="'PILOTIS'!AH26" tooltip="Ver imagem"/>
+    <hyperlink ref="AH26" location="'PILOTIS'!V26" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L27" location="'PILOTIS'!AI27" tooltip="Ver imagem"/>
+    <hyperlink ref="O27" location="'PILOTIS'!AJ27" tooltip="Ver imagem"/>
+    <hyperlink ref="V27" location="'PILOTIS'!AH27" tooltip="Ver imagem"/>
+    <hyperlink ref="AH27" location="'PILOTIS'!V27" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI27" location="'PILOTIS'!L27" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ27" location="'PILOTIS'!O27" tooltip="Voltar para a grade"/>
+    <hyperlink ref="H29" location="'PILOTIS'!AH29" tooltip="Ver imagem"/>
+    <hyperlink ref="T29" location="'PILOTIS'!AI29" tooltip="Ver imagem"/>
+    <hyperlink ref="U29" location="'PILOTIS'!AJ29" tooltip="Ver imagem"/>
+    <hyperlink ref="AH29" location="'PILOTIS'!H29" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI29" location="'PILOTIS'!T29" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ29" location="'PILOTIS'!U29" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L32" location="'PILOTIS'!AJ32" tooltip="Ver imagem"/>
+    <hyperlink ref="O32" location="'PILOTIS'!AK32" tooltip="Ver imagem"/>
+    <hyperlink ref="T32" location="'PILOTIS'!AI32" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="V32" location="'PILOTIS'!AH32" tooltip="Ver imagem"/>
+    <hyperlink ref="AH32" location="'PILOTIS'!V32" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI32" location="'PILOTIS'!T32" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ32" location="'PILOTIS'!L32" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK32" location="'PILOTIS'!O32" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL32" location="'PILOTIS'!T32" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V34" location="'PILOTIS'!AH34" tooltip="Ver imagem"/>
+    <hyperlink ref="AH34" location="'PILOTIS'!V34" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O35" location="'PILOTIS'!AN35" tooltip="Ver imagem"/>
+    <hyperlink ref="P35" location="'PILOTIS'!AI35" tooltip="Ver imagem"/>
+    <hyperlink ref="S35" location="'PILOTIS'!AO35" tooltip="Ver imagem"/>
+    <hyperlink ref="T35" location="'PILOTIS'!AJ35" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="U35" location="'PILOTIS'!AP35" tooltip="Ver imagem"/>
+    <hyperlink ref="V35" location="'PILOTIS'!AH35" tooltip="Ver imagem"/>
+    <hyperlink ref="Z35" location="'PILOTIS'!AK35" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH35" location="'PILOTIS'!V35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI35" location="'PILOTIS'!P35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ35" location="'PILOTIS'!T35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK35" location="'PILOTIS'!Z35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL35" location="'PILOTIS'!Z35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM35" location="'PILOTIS'!T35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AN35" location="'PILOTIS'!O35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AO35" location="'PILOTIS'!S35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AP35" location="'PILOTIS'!U35" tooltip="Voltar para a grade"/>
+    <hyperlink ref="O36" location="'PILOTIS'!AN36" tooltip="Ver imagem"/>
+    <hyperlink ref="P36" location="'PILOTIS'!AI36" tooltip="Ver imagem"/>
+    <hyperlink ref="S36" location="'PILOTIS'!AO36" tooltip="Ver imagem"/>
+    <hyperlink ref="T36" location="'PILOTIS'!AJ36" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="U36" location="'PILOTIS'!AP36" tooltip="Ver imagem"/>
+    <hyperlink ref="V36" location="'PILOTIS'!AH36" tooltip="Ver imagem"/>
+    <hyperlink ref="Z36" location="'PILOTIS'!AK36" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH36" location="'PILOTIS'!V36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI36" location="'PILOTIS'!P36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ36" location="'PILOTIS'!T36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK36" location="'PILOTIS'!Z36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL36" location="'PILOTIS'!Z36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM36" location="'PILOTIS'!T36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AN36" location="'PILOTIS'!O36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AO36" location="'PILOTIS'!S36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AP36" location="'PILOTIS'!U36" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V37" location="'PILOTIS'!AH37" tooltip="Ver imagem"/>
+    <hyperlink ref="AH37" location="'PILOTIS'!V37" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B41" location="'PILOTIS'!AH41" tooltip="Ver imagem"/>
+    <hyperlink ref="H41" location="'PILOTIS'!AI41" tooltip="Ver imagem"/>
+    <hyperlink ref="R41" location="'PILOTIS'!AM41" tooltip="Ver imagem"/>
+    <hyperlink ref="T41" location="'PILOTIS'!AL41" tooltip="Ver imagem"/>
+    <hyperlink ref="U41" location="'PILOTIS'!AJ41" tooltip="Ver imagem"/>
+    <hyperlink ref="V41" location="'PILOTIS'!AK41" tooltip="Ver imagem"/>
     <hyperlink ref="AH41" location="'PILOTIS'!B41" tooltip="Voltar para a grade"/>
     <hyperlink ref="AI41" location="'PILOTIS'!H41" tooltip="Voltar para a grade"/>
     <hyperlink ref="AJ41" location="'PILOTIS'!U41" tooltip="Voltar para a grade"/>
-    <hyperlink ref="B55" location="'PILOTIS'!AH55" tooltip="Ver imagem: P10 - Piso elevado em mármore branco selecionado"/>
-    <hyperlink ref="H55" location="'PILOTIS'!AI55" tooltip="Ver imagem: PA47 - Pintura com tinta mineral, cor 930, Terracor"/>
-    <hyperlink ref="J55" location="'PILOTIS'!AJ55" tooltip="Ver imagem: D73 - Bancada em mármore branco selecionado"/>
-    <hyperlink ref="K55" location="'PILOTIS'!AK55" tooltip="Ver imagem: D38 - Espelho liso incolor 4mm"/>
-    <hyperlink ref="L55" location="'PILOTIS'!AL55" tooltip="Ver imagem: D72 - Cuba de semi-encaixe slim, Deca"/>
-    <hyperlink ref="O55" location="'PILOTIS'!AM55" tooltip="Ver imagem: D69 - Torneira com sensor Decalux, Deca"/>
-    <hyperlink ref="P55" location="'PILOTIS'!AN55" tooltip="Ver imagem: D22 - Bacia Carrara / Panache e assento"/>
-    <hyperlink ref="S55" location="'PILOTIS'!AO55" tooltip="Ver imagem: D33 - Monocomando para chuveiro Mix&amp;Match, Docol"/>
-    <hyperlink ref="U55" location="'PILOTIS'!AP55" tooltip="Ver imagem: D70 - Chuveiro 200 de parede Docol Eden"/>
+    <hyperlink ref="AK41" location="'PILOTIS'!V41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL41" location="'PILOTIS'!T41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM41" location="'PILOTIS'!R41" tooltip="Voltar para a grade"/>
+    <hyperlink ref="R42" location="'PILOTIS'!AI42" tooltip="Ver imagem"/>
+    <hyperlink ref="T42" location="'PILOTIS'!AH42" tooltip="Ver imagem"/>
+    <hyperlink ref="U42" location="'PILOTIS'!AJ42" tooltip="Ver imagem"/>
+    <hyperlink ref="AH42" location="'PILOTIS'!T42" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI42" location="'PILOTIS'!R42" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ42" location="'PILOTIS'!U42" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L45" location="'PILOTIS'!AI45" tooltip="Ver imagem"/>
+    <hyperlink ref="O45" location="'PILOTIS'!AJ45" tooltip="Ver imagem"/>
+    <hyperlink ref="V45" location="'PILOTIS'!AH45" tooltip="Ver imagem"/>
+    <hyperlink ref="AH45" location="'PILOTIS'!V45" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI45" location="'PILOTIS'!L45" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ45" location="'PILOTIS'!O45" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L46" location="'PILOTIS'!AI46" tooltip="Ver imagem"/>
+    <hyperlink ref="O46" location="'PILOTIS'!AJ46" tooltip="Ver imagem"/>
+    <hyperlink ref="V46" location="'PILOTIS'!AH46" tooltip="Ver imagem"/>
+    <hyperlink ref="AH46" location="'PILOTIS'!V46" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI46" location="'PILOTIS'!L46" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ46" location="'PILOTIS'!O46" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L48" location="'PILOTIS'!AP48" tooltip="Ver imagem"/>
+    <hyperlink ref="O48" location="'PILOTIS'!AM48" tooltip="Ver imagem"/>
+    <hyperlink ref="P48" location="'PILOTIS'!AI48" tooltip="Ver imagem"/>
+    <hyperlink ref="Q48" location="'PILOTIS'!AQ48" tooltip="Ver imagem"/>
+    <hyperlink ref="S48" location="'PILOTIS'!AN48" tooltip="Ver imagem"/>
+    <hyperlink ref="T48" location="'PILOTIS'!AL48" tooltip="Ver imagem"/>
+    <hyperlink ref="U48" location="'PILOTIS'!AO48" tooltip="Ver imagem"/>
+    <hyperlink ref="V48" location="'PILOTIS'!AH48" tooltip="Ver imagem"/>
+    <hyperlink ref="Z48" location="'PILOTIS'!AJ48" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH48" location="'PILOTIS'!V48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI48" location="'PILOTIS'!P48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ48" location="'PILOTIS'!Z48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK48" location="'PILOTIS'!Z48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL48" location="'PILOTIS'!T48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM48" location="'PILOTIS'!O48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AN48" location="'PILOTIS'!S48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AO48" location="'PILOTIS'!U48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AP48" location="'PILOTIS'!L48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AQ48" location="'PILOTIS'!Q48" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L49" location="'PILOTIS'!AP49" tooltip="Ver imagem"/>
+    <hyperlink ref="O49" location="'PILOTIS'!AM49" tooltip="Ver imagem"/>
+    <hyperlink ref="P49" location="'PILOTIS'!AI49" tooltip="Ver imagem"/>
+    <hyperlink ref="Q49" location="'PILOTIS'!AQ49" tooltip="Ver imagem"/>
+    <hyperlink ref="S49" location="'PILOTIS'!AN49" tooltip="Ver imagem"/>
+    <hyperlink ref="T49" location="'PILOTIS'!AL49" tooltip="Ver imagem"/>
+    <hyperlink ref="U49" location="'PILOTIS'!AO49" tooltip="Ver imagem"/>
+    <hyperlink ref="V49" location="'PILOTIS'!AH49" tooltip="Ver imagem"/>
+    <hyperlink ref="Z49" location="'PILOTIS'!AJ49" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH49" location="'PILOTIS'!V49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI49" location="'PILOTIS'!P49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ49" location="'PILOTIS'!Z49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK49" location="'PILOTIS'!Z49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL49" location="'PILOTIS'!T49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM49" location="'PILOTIS'!O49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AN49" location="'PILOTIS'!S49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AO49" location="'PILOTIS'!U49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AP49" location="'PILOTIS'!L49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AQ49" location="'PILOTIS'!Q49" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L50" location="'PILOTIS'!AH50" tooltip="Ver imagem"/>
+    <hyperlink ref="O50" location="'PILOTIS'!AI50" tooltip="Ver imagem"/>
+    <hyperlink ref="AH50" location="'PILOTIS'!L50" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI50" location="'PILOTIS'!O50" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B53" location="'PILOTIS'!AH53" tooltip="Ver imagem"/>
+    <hyperlink ref="F53" location="'PILOTIS'!AH53" tooltip="Ver imagem"/>
+    <hyperlink ref="H53" location="'PILOTIS'!AH53" tooltip="Ver imagem"/>
+    <hyperlink ref="L53" location="'PILOTIS'!AJ53" tooltip="Ver imagem"/>
+    <hyperlink ref="O53" location="'PILOTIS'!AI53" tooltip="Ver imagem"/>
+    <hyperlink ref="AH53" location="'PILOTIS'!B53" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI53" location="'PILOTIS'!O53" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ53" location="'PILOTIS'!L53" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B54" location="'PILOTIS'!AH54" tooltip="Ver imagem"/>
+    <hyperlink ref="F54" location="'PILOTIS'!AH54" tooltip="Ver imagem"/>
+    <hyperlink ref="H54" location="'PILOTIS'!AH54" tooltip="Ver imagem"/>
+    <hyperlink ref="L54" location="'PILOTIS'!AJ54" tooltip="Ver imagem"/>
+    <hyperlink ref="O54" location="'PILOTIS'!AI54" tooltip="Ver imagem"/>
+    <hyperlink ref="AH54" location="'PILOTIS'!B54" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI54" location="'PILOTIS'!O54" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ54" location="'PILOTIS'!L54" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B55" location="'PILOTIS'!AH55" tooltip="Ver imagem"/>
+    <hyperlink ref="H55" location="'PILOTIS'!AI55" tooltip="Ver imagem"/>
+    <hyperlink ref="J55" location="'PILOTIS'!AJ55" tooltip="Ver imagem"/>
+    <hyperlink ref="K55" location="'PILOTIS'!AK55" tooltip="Ver imagem"/>
+    <hyperlink ref="L55" location="'PILOTIS'!AL55" tooltip="Ver imagem"/>
+    <hyperlink ref="O55" location="'PILOTIS'!AM55" tooltip="Ver imagem"/>
+    <hyperlink ref="P55" location="'PILOTIS'!AN55" tooltip="Ver imagem"/>
+    <hyperlink ref="S55" location="'PILOTIS'!AO55" tooltip="Ver imagem"/>
+    <hyperlink ref="T55" location="'PILOTIS'!AR55" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="U55" location="'PILOTIS'!AP55" tooltip="Ver imagem"/>
+    <hyperlink ref="V55" location="'PILOTIS'!AQ55" tooltip="Ver imagem"/>
+    <hyperlink ref="Z55" location="'PILOTIS'!AS55" tooltip="Ver imagem (2 imagens lado a lado)"/>
     <hyperlink ref="AH55" location="'PILOTIS'!B55" tooltip="Voltar para a grade"/>
     <hyperlink ref="AI55" location="'PILOTIS'!H55" tooltip="Voltar para a grade"/>
     <hyperlink ref="AJ55" location="'PILOTIS'!J55" tooltip="Voltar para a grade"/>
@@ -14115,6 +20360,17 @@
     <hyperlink ref="AN55" location="'PILOTIS'!P55" tooltip="Voltar para a grade"/>
     <hyperlink ref="AO55" location="'PILOTIS'!S55" tooltip="Voltar para a grade"/>
     <hyperlink ref="AP55" location="'PILOTIS'!U55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AQ55" location="'PILOTIS'!V55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AR55" location="'PILOTIS'!T55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AS55" location="'PILOTIS'!Z55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AT55" location="'PILOTIS'!Z55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AU55" location="'PILOTIS'!T55" tooltip="Voltar para a grade"/>
+    <hyperlink ref="V58" location="'PILOTIS'!AH58" tooltip="Ver imagem"/>
+    <hyperlink ref="AH58" location="'PILOTIS'!V58" tooltip="Voltar para a grade"/>
+    <hyperlink ref="T59" location="'PILOTIS'!AH59" tooltip="Ver imagem"/>
+    <hyperlink ref="AH59" location="'PILOTIS'!T59" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B63" location="'PILOTIS'!AH63" tooltip="Ver imagem"/>
+    <hyperlink ref="AH63" location="'PILOTIS'!B63" tooltip="Voltar para a grade"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
@@ -14142,7 +20398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF35"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="24"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14177,6 +20433,26 @@
     <col width="31" customWidth="1" min="30" max="30"/>
     <col width="31" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="72" customWidth="1" min="34" max="34"/>
+    <col width="72" customWidth="1" min="35" max="35"/>
+    <col width="72" customWidth="1" min="36" max="36"/>
+    <col width="72" customWidth="1" min="37" max="37"/>
+    <col width="72" customWidth="1" min="38" max="38"/>
+    <col width="72" customWidth="1" min="39" max="39"/>
+    <col width="72" customWidth="1" min="40" max="40"/>
+    <col width="72" customWidth="1" min="41" max="41"/>
+    <col width="72" customWidth="1" min="42" max="42"/>
+    <col width="72" customWidth="1" min="43" max="43"/>
+    <col width="72" customWidth="1" min="44" max="44"/>
+    <col width="72" customWidth="1" min="45" max="45"/>
+    <col width="72" customWidth="1" min="46" max="46"/>
+    <col width="72" customWidth="1" min="47" max="47"/>
+    <col width="72" customWidth="1" min="48" max="48"/>
+    <col width="72" customWidth="1" min="49" max="49"/>
+    <col width="72" customWidth="1" min="50" max="50"/>
+    <col width="72" customWidth="1" min="51" max="51"/>
+    <col width="72" customWidth="1" min="52" max="52"/>
+    <col width="72" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
@@ -14741,6 +21017,11 @@
 COMPLEMENTARES</t>
         </is>
       </c>
+      <c r="AH11" s="322" t="inlineStr">
+        <is>
+          <t>IMAGENS DAS ESPECIFICAÇÕES (fora da área de impressão)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customFormat="1" customHeight="1" s="13" thickBot="1">
       <c r="A12" s="51" t="n"/>
@@ -14834,7 +21115,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="104" customHeight="1">
+    <row r="14" ht="134" customHeight="1">
       <c r="A14" s="298" t="inlineStr">
         <is>
           <t>LAVABO</t>
@@ -14879,19 +21160,22 @@
       <c r="N14" s="300" t="n"/>
       <c r="O14" s="300" t="inlineStr">
         <is>
-          <t>Torneira de mesa bica baixa para lavatório, cromado, linha Unic, cód. 1197.C90. Ref.: Deca. (DET PR004; Tab. R01)</t>
+          <t>Torneira de mesa bica baixa para lavatório, cromado, linha Unic, cód. 1197.C90. Ref.: Deca. (DET PR004; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P14" s="300" t="inlineStr">
         <is>
-          <t>Bacia convencional suspensa branca, linha LK, cód. P.232.17. Ref.: Deca. Caixa de descarga embutida para alvenaria. (DET PR004; Tab. R01)</t>
+          <t>Bacia convencional suspensa branca, linha LK, cód. P.232.17. Ref.: Deca. Caixa de descarga embutida para alvenaria. (DET PR004; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q14" s="300" t="n"/>
       <c r="R14" s="300" t="inlineStr">
         <is>
           <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Unic, cód. 4900.C90.GD. Ref.: Deca
-Acabamento para caixa de descarga embutida, cromado, H Quadra Duo, cód. 4900.C.HQD.DUO. Ref.: Deca. (DET PR004)</t>
+Acabamento para caixa de descarga embutida, cromado, H Quadra Duo, cód. 4900.C.HQD.DUO. Ref.: Deca. (DET PR004)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S14" s="300" t="n"/>
@@ -14914,8 +21198,36 @@
       </c>
       <c r="Y14" s="320" t="n"/>
       <c r="Z14" s="300" t="n"/>
-    </row>
-    <row r="15" ht="104" customHeight="1">
+      <c r="AH14" s="323" t="inlineStr">
+        <is>
+          <t>WEB-34 - Torneira Lavatorio Mesa Bica Baixa Deca Unic Cromado 1197.C90 (Deca)
+Imagem de referência da web
+◄ VOLTAR para O14</t>
+        </is>
+      </c>
+      <c r="AI14" s="323" t="inlineStr">
+        <is>
+          <t>WEB-35 - Bacia Convencional Suspensa LK Deca Branco P.232.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P14</t>
+        </is>
+      </c>
+      <c r="AJ14" s="323" t="inlineStr">
+        <is>
+          <t>WEB-36 - Acabamento Gaveta 1 1/4 e 1 1/2 Unic Deca 4900.C90.GD (Deca)
+Imagem de referência da web
+◄ VOLTAR para R14</t>
+        </is>
+      </c>
+      <c r="AK14" s="323" t="inlineStr">
+        <is>
+          <t>WEB-37 - Acabamento para caixa de descarga embutida Pneumatica Quadra Duo 4900.C.HQD.DUO (Duo)
+Imagem de referência da web
+◄ VOLTAR para R14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="134" customHeight="1">
       <c r="A15" s="298" t="inlineStr">
         <is>
           <t>BANHO SUÍTE MASTER</t>
@@ -14958,20 +21270,23 @@
       <c r="K15" s="300" t="n"/>
       <c r="L15" s="300" t="inlineStr">
         <is>
-          <t>33 - Cuba de apoio retangular Jader Almeida 670x495x120mm, branca, cód. L.310.17. Ref.: Deca. (PR408; Tab. R01)</t>
+          <t>33 - Cuba de apoio retangular Jader Almeida 670x495x120mm, branca, cód. L.310.17. Ref.: Deca. (PR408; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M15" s="300" t="n"/>
       <c r="N15" s="300" t="n"/>
       <c r="O15" s="300" t="inlineStr">
         <is>
-          <t>36 - Misturador monocomando de mesa bica alta para lavatório, Level cromado, cód. 2885.C26. Ref.: Deca. (PR408; Tab. R01)</t>
+          <t>36 - Misturador monocomando de mesa bica alta para lavatório, Level cromado, cód. 2885.C26. Ref.: Deca. (PR408; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P15" s="300" t="inlineStr">
         <is>
           <t>34 - Bacia convencional Carrara branca com caixa acoplada e acionamento duo, cód. P.606.17. Ref.: Deca. (PR408; Tab. R01)
-46 - Bidê 3 furos Carrara branco, cód. B.60.17. Ref.: Deca. (PR408; Tab. R01)</t>
+46 - Bidê 3 furos Carrara branco, cód. B.60.17. Ref.: Deca. (PR408; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q15" s="300" t="inlineStr">
@@ -14981,7 +21296,8 @@
       </c>
       <c r="R15" s="300" t="inlineStr">
         <is>
-          <t>49 - Acabamento para registro Level cromado, cód. 4900.C26.PQ. Ref.: Deca. (PR408)</t>
+          <t>49 - Acabamento para registro Level cromado, cód. 4900.C26.PQ. Ref.: Deca. (PR408)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S15" s="300" t="inlineStr">
@@ -15002,12 +21318,14 @@
       </c>
       <c r="V15" s="300" t="inlineStr">
         <is>
-          <t>39 - Tomadas e interruptores Arteor quadrado branco. Ref.: Legrand. (PR408)</t>
+          <t>39 - Tomadas e interruptores Arteor quadrado branco. Ref.: Legrand. (PR408)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="W15" s="300" t="inlineStr">
         <is>
-          <t>Maçaneta Sara cromo acetinado. Ref.: Pado. (PR408)</t>
+          <t>Maçaneta Sara cromo acetinado. Ref.: Pado. (PR408)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="X15" s="320" t="inlineStr">
@@ -15017,8 +21335,57 @@
       </c>
       <c r="Y15" s="320" t="n"/>
       <c r="Z15" s="300" t="n"/>
-    </row>
-    <row r="16" ht="74" customHeight="1">
+      <c r="AH15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-04 - Bacia para Caixa Acoplada Dual Flux Carrara P.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P15</t>
+        </is>
+      </c>
+      <c r="AI15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-38 - Cuba Jader Almeida Apoio Retangular Deca L.310.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para L15</t>
+        </is>
+      </c>
+      <c r="AJ15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-39 - Misturador Monocomando Lavatorio Mesa Bica Alta Deca Level Cromado 2885.C26 (Deca)
+Imagem de referência da web
+◄ VOLTAR para O15</t>
+        </is>
+      </c>
+      <c r="AK15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-40 - Bide Com 3 Furos Carrara Deca B.60.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P15</t>
+        </is>
+      </c>
+      <c r="AL15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-41 - Acabamento Para Registro De Gaveta E Pressao Ate 1 Level Cromado 4900.C26.PQ (Deca)
+Imagem de referência da web
+◄ VOLTAR para R15</t>
+        </is>
+      </c>
+      <c r="AM15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-42 - Arteor Conjunto 4x2 Branco com Interruptor Simples e Tomada 2P+T 10A (Legrand)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para V15</t>
+        </is>
+      </c>
+      <c r="AN15" s="323" t="inlineStr">
+        <is>
+          <t>WEB-43 - Fechadura Sara em Zamac Cromo Acetinado Interna (Pado)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para W15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
       <c r="A16" s="298" t="inlineStr">
         <is>
           <t>BANHO SUÍTES</t>
@@ -15052,34 +21419,40 @@
       <c r="K16" s="300" t="n"/>
       <c r="L16" s="300" t="inlineStr">
         <is>
-          <t>Cuba retangular de apoio 60cm com deck, branca, linha Slim, cód. L.13060.M.17. Ref.: Deca. (DET PR008; Tab. R01)</t>
+          <t>Cuba retangular de apoio 60cm com deck, branca, linha Slim, cód. L.13060.M.17. Ref.: Deca. (DET PR008; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M16" s="300" t="n"/>
       <c r="N16" s="300" t="n"/>
       <c r="O16" s="300" t="inlineStr">
         <is>
-          <t>Misturador monocomando de mesa bica baixa para lavatório, cromado, linha Level, cód. 2875.C26. Ref.: Deca. (DET PR008; Tab. R01)</t>
+          <t>Misturador monocomando de mesa bica baixa para lavatório, cromado, linha Level, cód. 2875.C26. Ref.: Deca. (DET PR008; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P16" s="300" t="inlineStr">
         <is>
-          <t>Bacia convencional Carrara branca com caixa acoplada, cód. KP.606.17. Ref.: Deca. (DET PR008; Tab. R01)</t>
+          <t>Bacia convencional Carrara branca com caixa acoplada, cód. KP.606.17. Ref.: Deca. (DET PR008; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q16" s="300" t="inlineStr">
         <is>
-          <t>Ducha higiênica com registro e derivação, cromada, linha Level. Ref.: Deca. (DET PR008; Tab. R01)</t>
+          <t>Ducha higiênica com registro e derivação, cromada, linha Level. Ref.: Deca. (DET PR008; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="R16" s="300" t="inlineStr">
         <is>
-          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Level, cód. 4900.C26.GD. Ref.: Deca. (DET PR008)</t>
+          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Level, cód. 4900.C26.GD. Ref.: Deca. (DET PR008)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S16" s="300" t="inlineStr">
         <is>
-          <t>Acabamento monocomando para chuveiro, cromado, linha Level, cód. 4993.C26.CHU. Ref.: Deca. (DET PR008; Tab. R01)</t>
+          <t>Acabamento monocomando para chuveiro, cromado, linha Level, cód. 4993.C26.CHU. Ref.: Deca. (DET PR008; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="T16" s="300" t="inlineStr">
@@ -15093,8 +21466,50 @@
       <c r="X16" s="320" t="n"/>
       <c r="Y16" s="320" t="n"/>
       <c r="Z16" s="300" t="n"/>
-    </row>
-    <row r="17" ht="89" customHeight="1">
+      <c r="AH16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-44 - Cuba Slim Apoio Deca Retangular Com Mesa 60cm Branco L.13060.M.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para L16</t>
+        </is>
+      </c>
+      <c r="AI16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-45 - Misturador Deca Monocomando Lavatório Level 2875.C26 (Deca)
+Imagem de referência da web
+◄ VOLTAR para O16</t>
+        </is>
+      </c>
+      <c r="AJ16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-46 - Kit Completo Bacia Carrara Com Caixa Acoplada Deca Branco KP.606.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para P16</t>
+        </is>
+      </c>
+      <c r="AK16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-47 - Ducha Higiênica Deca Level 1984.C26.ACT.CR com Registro e Derivação Cromada (Deca)
+Imagem de referência da web
+◄ VOLTAR para Q16</t>
+        </is>
+      </c>
+      <c r="AL16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-48 - Acabamento Registro Gaveta Grande 1 1/2 e 1 1/4 Deca Level Cromado 4900.C26.GD (Deca)
+Imagem de referência da web
+◄ VOLTAR para R16</t>
+        </is>
+      </c>
+      <c r="AM16" s="323" t="inlineStr">
+        <is>
+          <t>WEB-49 - Acabamento Deca Level 4993.C26.CHU P/ Chuveiro Monocomando Cromado (Deca)
+Imagem de referência da web
+◄ VOLTAR para S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
       <c r="A17" s="298" t="inlineStr">
         <is>
           <t>SUÍTES / QUARTOS / CIRCULAÇÃO / CLOSET / ESTAR ÍNTIMO</t>
@@ -15102,7 +21517,8 @@
       </c>
       <c r="B17" s="307" t="inlineStr">
         <is>
-          <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (DET PR001/PR002; Tab. R01)</t>
+          <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (DET PR001/PR002; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C17" s="300" t="n"/>
@@ -15115,7 +21531,8 @@
       <c r="F17" s="335" t="inlineStr">
         <is>
           <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01; quadro do DET PR001)
-CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm (o quadro da mesma prancha indica h=10cm)</t>
+CONFLITO – Legenda de rodapé do DET PR001/PR002: h=6,5cm (o quadro da mesma prancha indica h=10cm)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G17" s="300" t="n"/>
@@ -15142,8 +21559,22 @@
       <c r="X17" s="320" t="n"/>
       <c r="Y17" s="320" t="n"/>
       <c r="Z17" s="300" t="n"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+      <c r="AH17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-50 - Cumaru Assoalho Piso Pronto (Indusparquet)
+Imagem de referência da web
+◄ VOLTAR para B17</t>
+        </is>
+      </c>
+      <c r="AI17" s="323" t="inlineStr">
+        <is>
+          <t>WEB-51 - Rodapé Especial (cumaru maciço, 65 a 200mm) (Indusparquet)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para F17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
       <c r="A18" s="298" t="inlineStr">
         <is>
           <t>COPA NOTURNA</t>
@@ -15151,7 +21582,8 @@
       </c>
       <c r="B18" s="307" t="inlineStr">
         <is>
-          <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (Tab. R01)</t>
+          <t>Piso em cumaru, assoalho piso pronto. Ref.: Indusparquet. (Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C18" s="300" t="n"/>
@@ -15159,7 +21591,8 @@
       <c r="E18" s="300" t="n"/>
       <c r="F18" s="300" t="inlineStr">
         <is>
-          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01)</t>
+          <t>Rodapé maciço com o mesmo acabamento do piso, h=10cm. Ref.: Indusparquet. (Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G18" s="300" t="n"/>
@@ -15173,14 +21606,16 @@
       <c r="K18" s="300" t="n"/>
       <c r="L18" s="300" t="inlineStr">
         <is>
-          <t>Cuba redonda CR-30, escovada, cód. 01018116 / 90010181016. Ref.: Mekal. (DET PR003; Tab. R01)</t>
+          <t>Cuba redonda CR-30, escovada, cód. 01018116 / 90010181016. Ref.: Mekal. (DET PR003; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M18" s="300" t="n"/>
       <c r="N18" s="300" t="n"/>
       <c r="O18" s="300" t="inlineStr">
         <is>
-          <t>Torneira de mesa bica alta para lavatório, cromada, linha Link, cód. 1198.C.LNK. Ref.: Deca. (DET PR003; Tab. R01)</t>
+          <t>Torneira de mesa bica alta para lavatório, cromada, linha Link, cód. 1198.C.LNK. Ref.: Deca. (DET PR003; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P18" s="300" t="n"/>
@@ -15194,8 +21629,36 @@
       <c r="X18" s="320" t="n"/>
       <c r="Y18" s="320" t="n"/>
       <c r="Z18" s="300" t="n"/>
-    </row>
-    <row r="19" ht="74" customHeight="1">
+      <c r="AH18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-50 - Cumaru Assoalho Piso Pronto (Indusparquet)
+Imagem de referência da web
+◄ VOLTAR para B18</t>
+        </is>
+      </c>
+      <c r="AI18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-51 - Rodapé Especial (cumaru maciço, 65 a 200mm) (Indusparquet)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para F18</t>
+        </is>
+      </c>
+      <c r="AJ18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-52 - Cuba Redonda Embutir Mekal CR30 Extra Aco Inox 30x30 Escovado 90010181016 (Mekal)
+Imagem de referência da web
+◄ VOLTAR para L18</t>
+        </is>
+      </c>
+      <c r="AK18" s="323" t="inlineStr">
+        <is>
+          <t>WEB-53 - Torneira Bica alta Mesa para Cuba de Apoio modelo Link Deca 1198.C.LNK (Deca)
+Imagem de referência da web
+◄ VOLTAR para O18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
       <c r="A19" s="298" t="inlineStr">
         <is>
           <t>COZINHA / DESPENSAS</t>
@@ -15234,14 +21697,16 @@
       <c r="K19" s="300" t="n"/>
       <c r="L19" s="300" t="inlineStr">
         <is>
-          <t>Cuba de embutir 600x400x230mm em aço inox, linha Retta. Ref.: Mekal ou similar. (Tab. R01; PR406 sem modelo)</t>
+          <t>Cuba de embutir 600x400x230mm em aço inox, linha Retta. Ref.: Mekal ou similar. (Tab. R01; PR406 sem modelo)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M19" s="300" t="n"/>
       <c r="N19" s="300" t="n"/>
       <c r="O19" s="300" t="inlineStr">
         <is>
-          <t>Monocomando de mesa para cozinha, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01; PR406 sem modelo)</t>
+          <t>Monocomando de mesa para cozinha, cromado, linha Level. Ref.: Deca ou similar. (Tab. R01; PR406 sem modelo)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P19" s="300" t="n"/>
@@ -15259,8 +21724,22 @@
       </c>
       <c r="Y19" s="320" t="n"/>
       <c r="Z19" s="300" t="n"/>
-    </row>
-    <row r="20" ht="74" customHeight="1">
+      <c r="AH19" s="323" t="inlineStr">
+        <is>
+          <t>WEB-47 - Ducha Higiênica Deca Level 1984.C26.ACT.CR com Registro e Derivação Cromada (Deca)
+Imagem de referência da web
+◄ VOLTAR para O19</t>
+        </is>
+      </c>
+      <c r="AI19" s="323" t="inlineStr">
+        <is>
+          <t>WEB-54 - Cuba Embutir e Sobrepor Inox 304 Mekal Linha Reta R10 Escovada 600X400 LR60 90020502016 (Mekal)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para L19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
       <c r="A20" s="298" t="inlineStr">
         <is>
           <t>ÁREA DE SERVIÇO / CIRCULAÇÃO SERVIÇO</t>
@@ -15302,21 +21781,24 @@
       <c r="K20" s="300" t="n"/>
       <c r="L20" s="300" t="inlineStr">
         <is>
-          <t>Tanque para lavanderia CT-60, escovado, cód. 01019616 / 90010196016, 2 unidades, instalados sob a pedra da bancada. Ref.: Mekal. (DET PR005; Tab. R01)</t>
+          <t>Tanque para lavanderia CT-60, escovado, cód. 01019616 / 90010196016, 2 unidades, instalados sob a pedra da bancada. Ref.: Mekal. (DET PR005; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M20" s="300" t="n"/>
       <c r="N20" s="300" t="n"/>
       <c r="O20" s="300" t="inlineStr">
         <is>
-          <t>Torneira de parede com arejador para cozinha, cromada, linha Link, cód. 1159.C.LNK, 2 unidades. Ref.: Deca. (DET PR005; Tab. R01)</t>
+          <t>Torneira de parede com arejador para cozinha, cromada, linha Link, cód. 1159.C.LNK, 2 unidades. Ref.: Deca. (DET PR005; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P20" s="300" t="n"/>
       <c r="Q20" s="300" t="n"/>
       <c r="R20" s="300" t="inlineStr">
         <is>
-          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Link, cód. 4900.C.GD.LNK. Ref.: Deca. (DET PR005)</t>
+          <t>Acabamento para registro de gaveta 1 1/4" e 1 1/2", cromado, Link, cód. 4900.C.GD.LNK. Ref.: Deca. (DET PR005)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S20" s="300" t="n"/>
@@ -15340,8 +21822,29 @@
       </c>
       <c r="Y20" s="320" t="n"/>
       <c r="Z20" s="300" t="n"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+      <c r="AH20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-55 - Tanque Mekal Embutir/Sobrepor CT60 Aco Inox 60x50 Escovado 90010196016 (Mekal)
+Imagem de referência da web
+◄ VOLTAR para L20</t>
+        </is>
+      </c>
+      <c r="AI20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-56 - Torneira Parede pia C/ Arejador Articulado Link Deca 1159.C.LNK (Deca)
+Imagem de referência da web
+◄ VOLTAR para O20</t>
+        </is>
+      </c>
+      <c r="AJ20" s="323" t="inlineStr">
+        <is>
+          <t>WEB-57 - Acabamento para Registro 1.1/2 4900.C.GD.LNK Link Deca (Deca)
+Imagem de referência da web
+◄ VOLTAR para R20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
       <c r="A21" s="298" t="inlineStr">
         <is>
           <t>BANHO SERVIÇO</t>
@@ -15363,7 +21866,8 @@
       <c r="G21" s="300" t="n"/>
       <c r="H21" s="308" t="inlineStr">
         <is>
-          <t>Revestimento Forma Branco AC retificado 32,5x59cm. Ref.: Eliane. (DET PR007; Tab. R01)</t>
+          <t>Revestimento Forma Branco AC retificado 32,5x59cm. Ref.: Eliane. (DET PR007; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="I21" s="308" t="inlineStr">
@@ -15379,29 +21883,34 @@
       <c r="K21" s="300" t="n"/>
       <c r="L21" s="300" t="inlineStr">
         <is>
-          <t>Cuba redonda de embutir 31cm branca, linha L, cód. L.41.17. Ref.: Deca. (DET PR007; Tab. R01)</t>
+          <t>Cuba redonda de embutir 31cm branca, linha L, cód. L.41.17. Ref.: Deca. (DET PR007; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="M21" s="300" t="n"/>
       <c r="N21" s="300" t="n"/>
       <c r="O21" s="300" t="inlineStr">
         <is>
-          <t>Torneira de mesa bica baixa para lavatório, cromada, linha Link, cód. 1197.C.LNK. Ref.: Deca. (DET PR007; Tab. R01)</t>
+          <t>Torneira de mesa bica baixa para lavatório, cromada, linha Link, cód. 1197.C.LNK. Ref.: Deca. (DET PR007; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="P21" s="300" t="inlineStr">
         <is>
-          <t>Bacia com caixa acoplada branca, linha Axis, cód. KP.470.17. Ref.: Deca. (DET PR007; Tab. R01)</t>
+          <t>Bacia com caixa acoplada branca, linha Axis, cód. KP.470.17. Ref.: Deca. (DET PR007; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="Q21" s="300" t="inlineStr">
         <is>
-          <t>Ducha higiênica com registro e derivação, cromada, linha Link, cód. 1984.C.ACT.LNK.BR. Ref.: Deca. (DET PR007)</t>
+          <t>Ducha higiênica com registro e derivação, cromada, linha Link, cód. 1984.C.ACT.LNK.BR. Ref.: Deca. (DET PR007)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="R21" s="300" t="inlineStr">
         <is>
-          <t>Acabamento para registro de gaveta e pressão até 1", cromado, Link, cód. 4900.C.PQ.LNK. Ref.: Deca. (DET PR007; Tab. R01)</t>
+          <t>Acabamento para registro de gaveta e pressão até 1", cromado, Link, cód. 4900.C.PQ.LNK. Ref.: Deca. (DET PR007; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="S21" s="300" t="n"/>
@@ -15416,8 +21925,50 @@
       <c r="X21" s="320" t="n"/>
       <c r="Y21" s="320" t="n"/>
       <c r="Z21" s="300" t="n"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+      <c r="AH21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-58 - Revestimento Eliane Forma Branco 32,5x59 Acetinado (Eliane)
+Imagem de referência da web
+◄ VOLTAR para H21</t>
+        </is>
+      </c>
+      <c r="AI21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-59 - Cuba De Embutir Redonda Deca L.41.17 (Deca)
+Imagem de referência da web
+◄ VOLTAR para L21</t>
+        </is>
+      </c>
+      <c r="AJ21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-60 - Torneira Mesa Bica Baixa Link Deca 1197.C.LNK (Deca)
+Imagem de referência da web
+◄ VOLTAR para O21</t>
+        </is>
+      </c>
+      <c r="AK21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-61 - Kit Completo Bacia com Caixa Acoplada Axis Branco Deca (Deca)
+Imagem de referência da web
+◄ VOLTAR para P21</t>
+        </is>
+      </c>
+      <c r="AL21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-62 - Ducha Higiênica Deca Link C/ Registro 1984.C.ACT.LNK.BR (Deca)
+Imagem de referência da web
+◄ VOLTAR para Q21</t>
+        </is>
+      </c>
+      <c r="AM21" s="323" t="inlineStr">
+        <is>
+          <t>WEB-63 - Acabamento Deca Link 4900.C.PQ.LNK P/ Registro Cromada 1/2', 3/4' e 1' (Deca)
+Imagem de referência da web
+◄ VOLTAR para R21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
       <c r="A22" s="298" t="inlineStr">
         <is>
           <t>QUARTO / ESTAR FUNCIONÁRIOS</t>
@@ -15425,7 +21976,8 @@
       </c>
       <c r="B22" s="307" t="inlineStr">
         <is>
-          <t>Piso vinílico Austin, linha Urban, 18x121cm. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
+          <t>Piso vinílico Austin, linha Urban, 18x121cm. Ref.: Durafloor. (DET PR001; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="C22" s="300" t="n"/>
@@ -15437,7 +21989,8 @@
       <c r="E22" s="300" t="n"/>
       <c r="F22" s="300" t="inlineStr">
         <is>
-          <t>Rodapé Easy Y.01 120. Ref.: Durafloor. (DET PR001; Tab. R01)</t>
+          <t>Rodapé Easy Y.01 120. Ref.: Durafloor. (DET PR001; Tab. R01)
+► VER IMAGEM (clique)</t>
         </is>
       </c>
       <c r="G22" s="300" t="n"/>
@@ -15464,6 +22017,20 @@
       <c r="X22" s="320" t="n"/>
       <c r="Y22" s="320" t="n"/>
       <c r="Z22" s="300" t="n"/>
+      <c r="AH22" s="323" t="inlineStr">
+        <is>
+          <t>WEB-64 - Piso Vinílico Durafloor Urban Austin (40069631) (Durafloor)
+Imagem de referência da web
+◄ VOLTAR para B22</t>
+        </is>
+      </c>
+      <c r="AI22" s="323" t="inlineStr">
+        <is>
+          <t>WEB-65 - Rodapé Durafloor MDF Easy Y-01 12cm Branco Polar (Durafloor)
+Imagem de referência da web - CONFERIR
+◄ VOLTAR para F22</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="298" t="inlineStr">
@@ -15794,8 +22361,9 @@
       <c r="S35" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="L10:U10"/>
+    <mergeCell ref="AH11:AQ11"/>
     <mergeCell ref="B10:K10"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="T5:U5"/>
@@ -15827,6 +22395,78 @@
     <mergeCell ref="V12:Z12"/>
     <mergeCell ref="V7:AD8"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O14" location="'APTO TIPO'!AH14" tooltip="Ver imagem"/>
+    <hyperlink ref="P14" location="'APTO TIPO'!AI14" tooltip="Ver imagem"/>
+    <hyperlink ref="R14" location="'APTO TIPO'!AJ14" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="AH14" location="'APTO TIPO'!O14" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI14" location="'APTO TIPO'!P14" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ14" location="'APTO TIPO'!R14" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK14" location="'APTO TIPO'!R14" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L15" location="'APTO TIPO'!AI15" tooltip="Ver imagem"/>
+    <hyperlink ref="O15" location="'APTO TIPO'!AJ15" tooltip="Ver imagem"/>
+    <hyperlink ref="P15" location="'APTO TIPO'!AH15" tooltip="Ver imagem (2 imagens lado a lado)"/>
+    <hyperlink ref="R15" location="'APTO TIPO'!AL15" tooltip="Ver imagem"/>
+    <hyperlink ref="V15" location="'APTO TIPO'!AM15" tooltip="Ver imagem"/>
+    <hyperlink ref="W15" location="'APTO TIPO'!AN15" tooltip="Ver imagem"/>
+    <hyperlink ref="AH15" location="'APTO TIPO'!P15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI15" location="'APTO TIPO'!L15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ15" location="'APTO TIPO'!O15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK15" location="'APTO TIPO'!P15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL15" location="'APTO TIPO'!R15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM15" location="'APTO TIPO'!V15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AN15" location="'APTO TIPO'!W15" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L16" location="'APTO TIPO'!AH16" tooltip="Ver imagem"/>
+    <hyperlink ref="O16" location="'APTO TIPO'!AI16" tooltip="Ver imagem"/>
+    <hyperlink ref="P16" location="'APTO TIPO'!AJ16" tooltip="Ver imagem"/>
+    <hyperlink ref="Q16" location="'APTO TIPO'!AK16" tooltip="Ver imagem"/>
+    <hyperlink ref="R16" location="'APTO TIPO'!AL16" tooltip="Ver imagem"/>
+    <hyperlink ref="S16" location="'APTO TIPO'!AM16" tooltip="Ver imagem"/>
+    <hyperlink ref="AH16" location="'APTO TIPO'!L16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI16" location="'APTO TIPO'!O16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ16" location="'APTO TIPO'!P16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK16" location="'APTO TIPO'!Q16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL16" location="'APTO TIPO'!R16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM16" location="'APTO TIPO'!S16" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B17" location="'APTO TIPO'!AH17" tooltip="Ver imagem"/>
+    <hyperlink ref="F17" location="'APTO TIPO'!AI17" tooltip="Ver imagem"/>
+    <hyperlink ref="AH17" location="'APTO TIPO'!B17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI17" location="'APTO TIPO'!F17" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B18" location="'APTO TIPO'!AH18" tooltip="Ver imagem"/>
+    <hyperlink ref="F18" location="'APTO TIPO'!AI18" tooltip="Ver imagem"/>
+    <hyperlink ref="L18" location="'APTO TIPO'!AJ18" tooltip="Ver imagem"/>
+    <hyperlink ref="O18" location="'APTO TIPO'!AK18" tooltip="Ver imagem"/>
+    <hyperlink ref="AH18" location="'APTO TIPO'!B18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI18" location="'APTO TIPO'!F18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ18" location="'APTO TIPO'!L18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK18" location="'APTO TIPO'!O18" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L19" location="'APTO TIPO'!AI19" tooltip="Ver imagem"/>
+    <hyperlink ref="O19" location="'APTO TIPO'!AH19" tooltip="Ver imagem"/>
+    <hyperlink ref="AH19" location="'APTO TIPO'!O19" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI19" location="'APTO TIPO'!L19" tooltip="Voltar para a grade"/>
+    <hyperlink ref="L20" location="'APTO TIPO'!AH20" tooltip="Ver imagem"/>
+    <hyperlink ref="O20" location="'APTO TIPO'!AI20" tooltip="Ver imagem"/>
+    <hyperlink ref="R20" location="'APTO TIPO'!AJ20" tooltip="Ver imagem"/>
+    <hyperlink ref="AH20" location="'APTO TIPO'!L20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI20" location="'APTO TIPO'!O20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ20" location="'APTO TIPO'!R20" tooltip="Voltar para a grade"/>
+    <hyperlink ref="H21" location="'APTO TIPO'!AH21" tooltip="Ver imagem"/>
+    <hyperlink ref="L21" location="'APTO TIPO'!AI21" tooltip="Ver imagem"/>
+    <hyperlink ref="O21" location="'APTO TIPO'!AJ21" tooltip="Ver imagem"/>
+    <hyperlink ref="P21" location="'APTO TIPO'!AK21" tooltip="Ver imagem"/>
+    <hyperlink ref="Q21" location="'APTO TIPO'!AL21" tooltip="Ver imagem"/>
+    <hyperlink ref="R21" location="'APTO TIPO'!AM21" tooltip="Ver imagem"/>
+    <hyperlink ref="AH21" location="'APTO TIPO'!H21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI21" location="'APTO TIPO'!L21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AJ21" location="'APTO TIPO'!O21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AK21" location="'APTO TIPO'!P21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AL21" location="'APTO TIPO'!Q21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AM21" location="'APTO TIPO'!R21" tooltip="Voltar para a grade"/>
+    <hyperlink ref="B22" location="'APTO TIPO'!AH22" tooltip="Ver imagem"/>
+    <hyperlink ref="F22" location="'APTO TIPO'!AI22" tooltip="Ver imagem"/>
+    <hyperlink ref="AH22" location="'APTO TIPO'!B22" tooltip="Voltar para a grade"/>
+    <hyperlink ref="AI22" location="'APTO TIPO'!F22" tooltip="Voltar para a grade"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8" scale="38" pageOrder="overThenDown"/>
